--- a/data/global/2026-06-week01/titles.xlsx
+++ b/data/global/2026-06-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L198"/>
+  <dimension ref="A1:L199"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Dua Lipa - Physical (Live From Mexico)</v>
+        <v>שלומי שבת עמיר בניון – היכן אתה?</v>
       </c>
       <c r="B2" t="str">
-        <v>3 days ago</v>
+        <v>2026-06-01</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=xZAe-d3bXTs</v>
+        <v>https://yosmusic.com/%d7%a9%d7%9c%d7%95%d7%9e%d7%99-%d7%a9%d7%91%d7%aa-%d7%a2%d7%9e%d7%99%d7%a8-%d7%91%d7%a0%d7%99%d7%95%d7%9f-%d7%94%d7%99%d7%9b%d7%9f-%d7%90%d7%aa%d7%94/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-06-01</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>3 days ago</v>
+        <v>הדואט בין שלומי שבת לבין עמיר בניון בנוי כמסע רוחני־קיומי: מצד אחד וידוי אישי, שבור ואינטימי. מצד שני זעקה גדולה שמופנית כלפי מעלה, אל האל או אל העצמי האבוד. הפתיחה ("הייתי קם עוזב הכול") נשמעת כמו הצהרת בריחה. הדובר מוכן</v>
       </c>
       <c r="G2" t="str">
         <v/>
       </c>
       <c r="H2" t="str">
-        <v>Dua Lipa</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Dua Lipa - Physical (Live From Mexico) - Dua Lipa</v>
+        <v>שלומי שבת עמיר בניון – היכן אתה?</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Dagny - Rain (Lyric Video)</v>
+        <v>Dua Lipa - Physical (Live From Mexico)</v>
       </c>
       <c r="B3" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=j3ZJwczZoUQ</v>
+        <v>https://www.youtube.com/watch?v=xZAe-d3bXTs</v>
       </c>
       <c r="D3" t="str">
         <v>2026-06-01</v>
@@ -489,13 +489,13 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
       </c>
       <c r="H3" t="str">
-        <v>Dagny</v>
+        <v>Dua Lipa</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Dagny - Rain (Lyric Video) - Dagny</v>
+        <v>Dua Lipa - Physical (Live From Mexico) - Dua Lipa</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Modern Talking - Cheri Cheri Lady (Auf los geht's los, 14.09.1985)</v>
+        <v>Dagny - Rain (Lyric Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=c0LtTVKNwNA</v>
+        <v>https://www.youtube.com/watch?v=j3ZJwczZoUQ</v>
       </c>
       <c r="D4" t="str">
         <v>2026-06-01</v>
@@ -527,13 +527,13 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>Modern Talking Offiziell</v>
+        <v>Dagny</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Modern Talking - Cheri Cheri Lady (Auf los geht's los, 14.09.1985) - Modern Talking Offiziell</v>
+        <v>Dagny - Rain (Lyric Video) - Dagny</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Jonas Blue - Girl (Official Lyric Video)</v>
+        <v>Modern Talking - Cheri Cheri Lady (Auf los geht's los, 14.09.1985)</v>
       </c>
       <c r="B5" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=FTUe3jzUqXU</v>
+        <v>https://www.youtube.com/watch?v=c0LtTVKNwNA</v>
       </c>
       <c r="D5" t="str">
         <v>2026-06-01</v>
@@ -565,13 +565,13 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>Defected Records and Jonas Blue</v>
+        <v>Modern Talking Offiziell</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Jonas Blue - Girl (Official Lyric Video) - Defected Records and Jonas Blue</v>
+        <v>Modern Talking - Cheri Cheri Lady (Auf los geht's los, 14.09.1985) - Modern Talking Offiziell</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Dogpark - Don't Lie (Visualizer)</v>
+        <v>Jonas Blue - Girl (Official Lyric Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=is7qKBRycJI</v>
+        <v>https://www.youtube.com/watch?v=FTUe3jzUqXU</v>
       </c>
       <c r="D6" t="str">
         <v>2026-06-01</v>
@@ -603,13 +603,13 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
       </c>
       <c r="H6" t="str">
-        <v>Dogpark</v>
+        <v>Defected Records and Jonas Blue</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Dogpark - Don't Lie (Visualizer) - Dogpark</v>
+        <v>Jonas Blue - Girl (Official Lyric Video) - Defected Records and Jonas Blue</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>elijah woods - L-O-V-E (Treehouse Sessions)</v>
+        <v>Dogpark - Don't Lie (Visualizer)</v>
       </c>
       <c r="B7" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=q5kN7eH6rgo</v>
+        <v>https://www.youtube.com/watch?v=is7qKBRycJI</v>
       </c>
       <c r="D7" t="str">
         <v>2026-06-01</v>
@@ -641,13 +641,13 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>elijah woods</v>
+        <v>Dogpark</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>elijah woods - L-O-V-E (Treehouse Sessions) - elijah woods</v>
+        <v>Dogpark - Don't Lie (Visualizer) - Dogpark</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Lauren Alaina - Better Off (Official Audio)</v>
+        <v>elijah woods - L-O-V-E (Treehouse Sessions)</v>
       </c>
       <c r="B8" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=Vj-ong3XNHM</v>
+        <v>https://www.youtube.com/watch?v=q5kN7eH6rgo</v>
       </c>
       <c r="D8" t="str">
         <v>2026-06-01</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>Lauren Alaina</v>
+        <v>elijah woods</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Lauren Alaina - Better Off (Official Audio) - Lauren Alaina</v>
+        <v>elijah woods - L-O-V-E (Treehouse Sessions) - elijah woods</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Lauren Sanderson - ARE YOU REALLY HERE? (Lyric Video)</v>
+        <v>Lauren Alaina - Better Off (Official Audio)</v>
       </c>
       <c r="B9" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=u7Et_hbMZUA</v>
+        <v>https://www.youtube.com/watch?v=Vj-ong3XNHM</v>
       </c>
       <c r="D9" t="str">
         <v>2026-06-01</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>Lauren Sanderson</v>
+        <v>Lauren Alaina</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Lauren Sanderson - ARE YOU REALLY HERE? (Lyric Video) - Lauren Sanderson</v>
+        <v>Lauren Alaina - Better Off (Official Audio) - Lauren Alaina</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Nightly – blue jeans (Official Lyric Video)</v>
+        <v>Lauren Sanderson - ARE YOU REALLY HERE? (Lyric Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=LnA3xkXUwaM</v>
+        <v>https://www.youtube.com/watch?v=u7Et_hbMZUA</v>
       </c>
       <c r="D10" t="str">
         <v>2026-06-01</v>
@@ -755,13 +755,13 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>NIGHTLY</v>
+        <v>Lauren Sanderson</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Nightly – blue jeans (Official Lyric Video) - NIGHTLY</v>
+        <v>Lauren Sanderson - ARE YOU REALLY HERE? (Lyric Video) - Lauren Sanderson</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Dasha - Mad About It (Official Visualizer)</v>
+        <v>Nightly – blue jeans (Official Lyric Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=Ae1gf_7p3H8</v>
+        <v>https://www.youtube.com/watch?v=LnA3xkXUwaM</v>
       </c>
       <c r="D11" t="str">
         <v>2026-06-01</v>
@@ -793,13 +793,13 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>Dasha</v>
+        <v>NIGHTLY</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Dasha - Mad About It (Official Visualizer) - Dasha</v>
+        <v>Nightly – blue jeans (Official Lyric Video) - NIGHTLY</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Ariana Grande - hate that i made you love me (official lyric video)</v>
+        <v>Dasha - Mad About It (Official Visualizer)</v>
       </c>
       <c r="B12" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=v1t4MTqdfyI</v>
+        <v>https://www.youtube.com/watch?v=Ae1gf_7p3H8</v>
       </c>
       <c r="D12" t="str">
         <v>2026-06-01</v>
@@ -831,13 +831,13 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>Ariana Grande</v>
+        <v>Dasha</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Ariana Grande - hate that i made you love me (official lyric video) - Ariana Grande</v>
+        <v>Dasha - Mad About It (Official Visualizer) - Dasha</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Max McNown - Something To Someone (Performance Video)</v>
+        <v>Ariana Grande - hate that i made you love me (official lyric video)</v>
       </c>
       <c r="B13" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=4Ki4ejT86YM</v>
+        <v>https://www.youtube.com/watch?v=v1t4MTqdfyI</v>
       </c>
       <c r="D13" t="str">
         <v>2026-06-01</v>
@@ -869,13 +869,13 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>Max McNown</v>
+        <v>Ariana Grande</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Max McNown - Something To Someone (Performance Video) - Max McNown</v>
+        <v>Ariana Grande - hate that i made you love me (official lyric video) - Ariana Grande</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Bebe Rexha &amp; David Guetta - Sad Girls (Official Visual)</v>
+        <v>Max McNown - Something To Someone (Performance Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=P8UqZ5IF-QE</v>
+        <v>https://www.youtube.com/watch?v=4Ki4ejT86YM</v>
       </c>
       <c r="D14" t="str">
         <v>2026-06-01</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>Bebe Rexha</v>
+        <v>Max McNown</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Bebe Rexha &amp; David Guetta - Sad Girls (Official Visual) - Bebe Rexha</v>
+        <v>Max McNown - Something To Someone (Performance Video) - Max McNown</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Knox - Long Story Short (Official Video)</v>
+        <v>Bebe Rexha &amp; David Guetta - Sad Girls (Official Visual)</v>
       </c>
       <c r="B15" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=5OGY6hCELfg</v>
+        <v>https://www.youtube.com/watch?v=P8UqZ5IF-QE</v>
       </c>
       <c r="D15" t="str">
         <v>2026-06-01</v>
@@ -945,13 +945,13 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>Knox</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Knox - Long Story Short (Official Video) - Knox</v>
+        <v>Bebe Rexha &amp; David Guetta - Sad Girls (Official Visual) - Bebe Rexha</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Sofia Camara - The Last Encounter</v>
+        <v>Knox - Long Story Short (Official Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=E9kN4HLGG1c</v>
+        <v>https://www.youtube.com/watch?v=5OGY6hCELfg</v>
       </c>
       <c r="D16" t="str">
         <v>2026-06-01</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>Sofia Camara</v>
+        <v>Knox</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Sofia Camara - The Last Encounter - Sofia Camara</v>
+        <v>Knox - Long Story Short (Official Video) - Knox</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Official Music Video: "Flowers" -- Alexander James</v>
+        <v>Sofia Camara - The Last Encounter</v>
       </c>
       <c r="B17" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=aZ4WP0P92tM</v>
+        <v>https://www.youtube.com/watch?v=E9kN4HLGG1c</v>
       </c>
       <c r="D17" t="str">
         <v>2026-06-01</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>Alexander James</v>
+        <v>Sofia Camara</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Official Music Video: "Flowers" -- Alexander James - Alexander James</v>
+        <v>Sofia Camara - The Last Encounter - Sofia Camara</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>almost monday - skinny dip (official video)</v>
+        <v>Official Music Video: "Flowers" -- Alexander James</v>
       </c>
       <c r="B18" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=hOxZDoaIzKQ</v>
+        <v>https://www.youtube.com/watch?v=aZ4WP0P92tM</v>
       </c>
       <c r="D18" t="str">
         <v>2026-06-01</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>almost monday</v>
+        <v>Alexander James</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>almost monday - skinny dip (official video) - almost monday</v>
+        <v>Official Music Video: "Flowers" -- Alexander James - Alexander James</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Kip Moore - The Darkness (Official)</v>
+        <v>almost monday - skinny dip (official video)</v>
       </c>
       <c r="B19" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=lTqqixCt5Mk</v>
+        <v>https://www.youtube.com/watch?v=hOxZDoaIzKQ</v>
       </c>
       <c r="D19" t="str">
         <v>2026-06-01</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>Kip Moore</v>
+        <v>almost monday</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Kip Moore - The Darkness (Official) - Kip Moore</v>
+        <v>almost monday - skinny dip (official video) - almost monday</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Paul McCartney - Come Inside (Lyric Video)</v>
+        <v>Kip Moore - The Darkness (Official)</v>
       </c>
       <c r="B20" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=C8Zw_Cbm2V0</v>
+        <v>https://www.youtube.com/watch?v=lTqqixCt5Mk</v>
       </c>
       <c r="D20" t="str">
         <v>2026-06-01</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>PAUL McCARTNEY</v>
+        <v>Kip Moore</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Paul McCartney - Come Inside (Lyric Video) - PAUL McCARTNEY</v>
+        <v>Kip Moore - The Darkness (Official) - Kip Moore</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Santana, Becky G - Mi Gran Amor (Official Lyric Video)</v>
+        <v>Paul McCartney - Come Inside (Lyric Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=btdBd_Yee8E</v>
+        <v>https://www.youtube.com/watch?v=C8Zw_Cbm2V0</v>
       </c>
       <c r="D21" t="str">
         <v>2026-06-01</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>Santana</v>
+        <v>PAUL McCARTNEY</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Santana, Becky G - Mi Gran Amor (Official Lyric Video) - Santana</v>
+        <v>Paul McCartney - Come Inside (Lyric Video) - PAUL McCARTNEY</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Dua Lipa - Training Season (Live From Mexico)</v>
+        <v>Santana, Becky G - Mi Gran Amor (Official Lyric Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=Va8Udsvqigs</v>
+        <v>https://www.youtube.com/watch?v=btdBd_Yee8E</v>
       </c>
       <c r="D22" t="str">
         <v>2026-06-01</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>Dua Lipa</v>
+        <v>Santana</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Dua Lipa - Training Season (Live From Mexico) - Dua Lipa</v>
+        <v>Santana, Becky G - Mi Gran Amor (Official Lyric Video) - Santana</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Charley - Liar</v>
+        <v>Dua Lipa - Training Season (Live From Mexico)</v>
       </c>
       <c r="B23" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=3Erfj2Eecgw</v>
+        <v>https://www.youtube.com/watch?v=Va8Udsvqigs</v>
       </c>
       <c r="D23" t="str">
         <v>2026-06-01</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>Charley</v>
+        <v>Dua Lipa</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Charley - Liar - Charley</v>
+        <v>Dua Lipa - Training Season (Live From Mexico) - Dua Lipa</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (ft Gabito Ballesteros) [Visualizer]</v>
+        <v>Charley - Liar</v>
       </c>
       <c r="B24" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=em5ryETDkAo</v>
+        <v>https://www.youtube.com/watch?v=3Erfj2Eecgw</v>
       </c>
       <c r="D24" t="str">
         <v>2026-06-01</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>David Guetta and Jennifer Lopez</v>
+        <v>Charley</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (ft Gabito Ballesteros) [Visualizer] - David Guetta and Jennifer Lopez</v>
+        <v>Charley - Liar - Charley</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Jordana Bryant - Too Little Too Late (Official Audio)</v>
+        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (ft Gabito Ballesteros) [Visualizer]</v>
       </c>
       <c r="B25" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=AmwNx9qlOpA</v>
+        <v>https://www.youtube.com/watch?v=em5ryETDkAo</v>
       </c>
       <c r="D25" t="str">
         <v>2026-06-01</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>Jordana Bryant</v>
+        <v>David Guetta and Jennifer Lopez</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Jordana Bryant - Too Little Too Late (Official Audio) - Jordana Bryant</v>
+        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (ft Gabito Ballesteros) [Visualizer] - David Guetta and Jennifer Lopez</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Lewis Capaldi - Stay Love</v>
+        <v>Jordana Bryant - Too Little Too Late (Official Audio)</v>
       </c>
       <c r="B26" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=9Pud3BqPpq0</v>
+        <v>https://www.youtube.com/watch?v=AmwNx9qlOpA</v>
       </c>
       <c r="D26" t="str">
         <v>2026-06-01</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>Lewis Capaldi</v>
+        <v>Jordana Bryant</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Lewis Capaldi - Stay Love - Lewis Capaldi</v>
+        <v>Jordana Bryant - Too Little Too Late (Official Audio) - Jordana Bryant</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Surreal World of Oddities - Pulling At My Strings - Official Music Video | 4K</v>
+        <v>Lewis Capaldi - Stay Love</v>
       </c>
       <c r="B27" t="str">
-        <v>4 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=fMt-f2aUW3c</v>
+        <v>https://www.youtube.com/watch?v=9Pud3BqPpq0</v>
       </c>
       <c r="D27" t="str">
         <v>2026-06-01</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>4 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
       </c>
       <c r="H27" t="str">
-        <v>Kelly Boesch AI Art</v>
+        <v>Lewis Capaldi</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Surreal World of Oddities - Pulling At My Strings - Official Music Video | 4K - Kelly Boesch AI Art</v>
+        <v>Lewis Capaldi - Stay Love - Lewis Capaldi</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Julia Cole - Love You to Death (Official Video)</v>
+        <v>Surreal World of Oddities - Pulling At My Strings - Official Music Video | 4K</v>
       </c>
       <c r="B28" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=dWgmFc2QuLY</v>
+        <v>https://www.youtube.com/watch?v=fMt-f2aUW3c</v>
       </c>
       <c r="D28" t="str">
         <v>2026-06-01</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>Julia Cole Music</v>
+        <v>Kelly Boesch AI Art</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Julia Cole - Love You to Death (Official Video) - Julia Cole Music</v>
+        <v>Surreal World of Oddities - Pulling At My Strings - Official Music Video | 4K - Kelly Boesch AI Art</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Victor Biliac - De-ai fi tu salcie la mal ( Cover Edit )</v>
+        <v>Julia Cole - Love You to Death (Official Video)</v>
       </c>
       <c r="B29" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=v3c0kG-V2zk</v>
+        <v>https://www.youtube.com/watch?v=dWgmFc2QuLY</v>
       </c>
       <c r="D29" t="str">
         <v>2026-06-01</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>VictorBiliac</v>
+        <v>Julia Cole Music</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Victor Biliac - De-ai fi tu salcie la mal ( Cover Edit ) - VictorBiliac</v>
+        <v>Julia Cole - Love You to Death (Official Video) - Julia Cole Music</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Lolo Zouaï - Coquelicot (feat. disiz) (Official Video)</v>
+        <v>Victor Biliac - De-ai fi tu salcie la mal ( Cover Edit )</v>
       </c>
       <c r="B30" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=-4p6FkrOGT4</v>
+        <v>https://www.youtube.com/watch?v=v3c0kG-V2zk</v>
       </c>
       <c r="D30" t="str">
         <v>2026-06-01</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>Lolo Zouaï and disiz</v>
+        <v>VictorBiliac</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Lolo Zouaï - Coquelicot (feat. disiz) (Official Video) - Lolo Zouaï and disiz</v>
+        <v>Victor Biliac - De-ai fi tu salcie la mal ( Cover Edit ) - VictorBiliac</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Jungle - The Wave (Official Video)</v>
+        <v>Lolo Zouaï - Coquelicot (feat. disiz) (Official Video)</v>
       </c>
       <c r="B31" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=DW1vUkqNvqQ</v>
+        <v>https://www.youtube.com/watch?v=-4p6FkrOGT4</v>
       </c>
       <c r="D31" t="str">
         <v>2026-06-01</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>Jungle4eva</v>
+        <v>Lolo Zouaï and disiz</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Jungle - The Wave (Official Video) - Jungle4eva</v>
+        <v>Lolo Zouaï - Coquelicot (feat. disiz) (Official Video) - Lolo Zouaï and disiz</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Daytime TV – Sun (Official Music Video)</v>
+        <v>Jungle - The Wave (Official Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=Jqo4ra_ch-M</v>
+        <v>https://www.youtube.com/watch?v=DW1vUkqNvqQ</v>
       </c>
       <c r="D32" t="str">
         <v>2026-06-01</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
       </c>
       <c r="H32" t="str">
-        <v>DAYTIME TV</v>
+        <v>Jungle4eva</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Daytime TV – Sun (Official Music Video) - DAYTIME TV</v>
+        <v>Jungle - The Wave (Official Video) - Jungle4eva</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Surreal and Strange AI Video | Not Made For The Cage | Kelly Boesch - 4K</v>
+        <v>Daytime TV – Sun (Official Music Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>2 weeks ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=ACNj3L2bzV8</v>
+        <v>https://www.youtube.com/watch?v=Jqo4ra_ch-M</v>
       </c>
       <c r="D33" t="str">
         <v>2026-06-01</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>2 weeks ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>Kelly Boesch AI Art</v>
+        <v>DAYTIME TV</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Surreal and Strange AI Video | Not Made For The Cage | Kelly Boesch - 4K - Kelly Boesch AI Art</v>
+        <v>Daytime TV – Sun (Official Music Video) - DAYTIME TV</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Bruno Mars - Risk It All [Live From The Romantic Tour]</v>
+        <v>Surreal and Strange AI Video | Not Made For The Cage | Kelly Boesch - 4K</v>
       </c>
       <c r="B34" t="str">
-        <v>5 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=aFbueod4reQ</v>
+        <v>https://www.youtube.com/watch?v=ACNj3L2bzV8</v>
       </c>
       <c r="D34" t="str">
         <v>2026-06-01</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>5 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>Bruno Mars</v>
+        <v>Kelly Boesch AI Art</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Bruno Mars - Risk It All [Live From The Romantic Tour] - Bruno Mars</v>
+        <v>Surreal and Strange AI Video | Not Made For The Cage | Kelly Boesch - 4K - Kelly Boesch AI Art</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Keith Urban - Summer Breeze (52nd American Music Awards)</v>
+        <v>Bruno Mars - Risk It All [Live From The Romantic Tour]</v>
       </c>
       <c r="B35" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=zn-4eVoqofQ</v>
+        <v>https://www.youtube.com/watch?v=aFbueod4reQ</v>
       </c>
       <c r="D35" t="str">
         <v>2026-06-01</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
       </c>
       <c r="H35" t="str">
-        <v>Keith Urban</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Keith Urban - Summer Breeze (52nd American Music Awards) - Keith Urban</v>
+        <v>Bruno Mars - Risk It All [Live From The Romantic Tour] - Bruno Mars</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Nelly Furtado, Boi-1Da, Canada Soccer - ELECTRIC CIRCUS (Official Music Video)</v>
+        <v>Keith Urban - Summer Breeze (52nd American Music Awards)</v>
       </c>
       <c r="B36" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=lHYEMWFuErM</v>
+        <v>https://www.youtube.com/watch?v=zn-4eVoqofQ</v>
       </c>
       <c r="D36" t="str">
         <v>2026-06-01</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>Nelly Furtado</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Nelly Furtado, Boi-1Da, Canada Soccer - ELECTRIC CIRCUS (Official Music Video) - Nelly Furtado</v>
+        <v>Keith Urban - Summer Breeze (52nd American Music Awards) - Keith Urban</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Teddy Swims - Mr. Know It All (Live from the AMAs)</v>
+        <v>Nelly Furtado, Boi-1Da, Canada Soccer - ELECTRIC CIRCUS (Official Music Video)</v>
       </c>
       <c r="B37" t="str">
-        <v>5 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=ttM4gWkhZBk</v>
+        <v>https://www.youtube.com/watch?v=lHYEMWFuErM</v>
       </c>
       <c r="D37" t="str">
         <v>2026-06-01</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>5 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>Teddy Swims and American Music Awards</v>
+        <v>Nelly Furtado</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Teddy Swims - Mr. Know It All (Live from the AMAs) - Teddy Swims and American Music Awards</v>
+        <v>Nelly Furtado, Boi-1Da, Canada Soccer - ELECTRIC CIRCUS (Official Music Video) - Nelly Furtado</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Shakira, Burna Boy - Dai Dai (Official Video)</v>
+        <v>Teddy Swims - Mr. Know It All (Live from the AMAs)</v>
       </c>
       <c r="B38" t="str">
-        <v>8 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=fcnDmrtj6Sk</v>
+        <v>https://www.youtube.com/watch?v=ttM4gWkhZBk</v>
       </c>
       <c r="D38" t="str">
         <v>2026-06-01</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>8 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
       </c>
       <c r="H38" t="str">
-        <v>Shakira and 2 more</v>
+        <v>Teddy Swims and American Music Awards</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Shakira, Burna Boy - Dai Dai (Official Video) - Shakira and 2 more</v>
+        <v>Teddy Swims - Mr. Know It All (Live from the AMAs) - Teddy Swims and American Music Awards</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards)</v>
+        <v>Shakira, Burna Boy - Dai Dai (Official Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=wacpnp83cJg</v>
+        <v>https://www.youtube.com/watch?v=fcnDmrtj6Sk</v>
       </c>
       <c r="D39" t="str">
         <v>2026-06-01</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
       </c>
       <c r="H39" t="str">
-        <v>Lainey Wilson</v>
+        <v>Shakira and 2 more</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards) - Lainey Wilson</v>
+        <v>Shakira, Burna Boy - Dai Dai (Official Video) - Shakira and 2 more</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ]</v>
+        <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards)</v>
       </c>
       <c r="B40" t="str">
-        <v>9 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=w8FTnkNVmq0</v>
+        <v>https://www.youtube.com/watch?v=wacpnp83cJg</v>
       </c>
       <c r="D40" t="str">
         <v>2026-06-01</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>9 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
       </c>
       <c r="H40" t="str">
-        <v>Duran Duran</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ] - Duran Duran</v>
+        <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards) - Lainey Wilson</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Nico Santos - Optimist</v>
+        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ]</v>
       </c>
       <c r="B41" t="str">
-        <v>11 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=JA6PIcBeKZ0</v>
+        <v>https://www.youtube.com/watch?v=w8FTnkNVmq0</v>
       </c>
       <c r="D41" t="str">
         <v>2026-06-01</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>11 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
       </c>
       <c r="H41" t="str">
-        <v>Nico Santos</v>
+        <v>Duran Duran</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Nico Santos - Optimist - Nico Santos</v>
+        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ] - Duran Duran</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Def Leppard - Personal Jesus (Live at Caesars Palace)</v>
+        <v>Nico Santos - Optimist</v>
       </c>
       <c r="B42" t="str">
-        <v>8 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=k5SRMgdG4L4</v>
+        <v>https://www.youtube.com/watch?v=JA6PIcBeKZ0</v>
       </c>
       <c r="D42" t="str">
         <v>2026-06-01</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>8 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
       </c>
       <c r="H42" t="str">
-        <v>DEF LEPPARD</v>
+        <v>Nico Santos</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Def Leppard - Personal Jesus (Live at Caesars Palace) - DEF LEPPARD</v>
+        <v>Nico Santos - Optimist - Nico Santos</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer)</v>
+        <v>Def Leppard - Personal Jesus (Live at Caesars Palace)</v>
       </c>
       <c r="B43" t="str">
-        <v>9 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=eWSwy9GU2L8</v>
+        <v>https://www.youtube.com/watch?v=k5SRMgdG4L4</v>
       </c>
       <c r="D43" t="str">
         <v>2026-06-01</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>9 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
       </c>
       <c r="H43" t="str">
-        <v>Will Linley</v>
+        <v>DEF LEPPARD</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer) - Will Linley</v>
+        <v>Def Leppard - Personal Jesus (Live at Caesars Palace) - DEF LEPPARD</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Kylie Minogue - Story (Official Lyric Video)</v>
+        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer)</v>
       </c>
       <c r="B44" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=fv7_1qKo8mg</v>
+        <v>https://www.youtube.com/watch?v=eWSwy9GU2L8</v>
       </c>
       <c r="D44" t="str">
         <v>2026-06-01</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
       </c>
       <c r="H44" t="str">
-        <v>Kylie Minogue</v>
+        <v>Will Linley</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Kylie Minogue - Story (Official Lyric Video) - Kylie Minogue</v>
+        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer) - Will Linley</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video)</v>
+        <v>Kylie Minogue - Story (Official Lyric Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=3KUQx2s1fQc</v>
+        <v>https://www.youtube.com/watch?v=fv7_1qKo8mg</v>
       </c>
       <c r="D45" t="str">
         <v>2026-06-01</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
       </c>
       <c r="H45" t="str">
-        <v>Billy Raffoul</v>
+        <v>Kylie Minogue</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video) - Billy Raffoul</v>
+        <v>Kylie Minogue - Story (Official Lyric Video) - Kylie Minogue</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025)</v>
+        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video)</v>
       </c>
       <c r="B46" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=vWf4uiLvwF8</v>
+        <v>https://www.youtube.com/watch?v=3KUQx2s1fQc</v>
       </c>
       <c r="D46" t="str">
         <v>2026-06-01</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>The Offspring</v>
+        <v>Billy Raffoul</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025) - The Offspring</v>
+        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video) - Billy Raffoul</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024)</v>
+        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025)</v>
       </c>
       <c r="B47" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=9xjMaXegmWM</v>
+        <v>https://www.youtube.com/watch?v=vWf4uiLvwF8</v>
       </c>
       <c r="D47" t="str">
         <v>2026-06-01</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>David Gilmour</v>
+        <v>The Offspring</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024) - David Gilmour</v>
+        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025) - The Offspring</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Scorpions - Delicate Dance (Madison Square Garden 2022)</v>
+        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024)</v>
       </c>
       <c r="B48" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=yAjEr9WLTnU</v>
+        <v>https://www.youtube.com/watch?v=9xjMaXegmWM</v>
       </c>
       <c r="D48" t="str">
         <v>2026-06-01</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>Scorpions</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Scorpions - Delicate Dance (Madison Square Garden 2022) - Scorpions</v>
+        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024) - David Gilmour</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston)</v>
+        <v>Scorpions - Delicate Dance (Madison Square Garden 2022)</v>
       </c>
       <c r="B49" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=oRw4PqBzGc0</v>
+        <v>https://www.youtube.com/watch?v=yAjEr9WLTnU</v>
       </c>
       <c r="D49" t="str">
         <v>2026-06-01</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>Brandon Lake and NICK JONAS</v>
+        <v>Scorpions</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston) - Brandon Lake and NICK JONAS</v>
+        <v>Scorpions - Delicate Dance (Madison Square Garden 2022) - Scorpions</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video)</v>
+        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston)</v>
       </c>
       <c r="B50" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=OKf_IOGxFQo</v>
+        <v>https://www.youtube.com/watch?v=oRw4PqBzGc0</v>
       </c>
       <c r="D50" t="str">
         <v>2026-06-01</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>Kygo and Dan Tyminski</v>
+        <v>Brandon Lake and NICK JONAS</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video) - Kygo and Dan Tyminski</v>
+        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston) - Brandon Lake and NICK JONAS</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>The Warning - Ego (Official Video)</v>
+        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=CG6Q5i75bR4</v>
+        <v>https://www.youtube.com/watch?v=OKf_IOGxFQo</v>
       </c>
       <c r="D51" t="str">
         <v>2026-06-01</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>The Warning</v>
+        <v>Kygo and Dan Tyminski</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>The Warning - Ego (Official Video) - The Warning</v>
+        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video) - Kygo and Dan Tyminski</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>paris jackson - teenage drama (official lyric video)</v>
+        <v>The Warning - Ego (Official Video)</v>
       </c>
       <c r="B52" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=kVfDArNljos</v>
+        <v>https://www.youtube.com/watch?v=CG6Q5i75bR4</v>
       </c>
       <c r="D52" t="str">
         <v>2026-06-01</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>paris jackson</v>
+        <v>The Warning</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>paris jackson - teenage drama (official lyric video) - paris jackson</v>
+        <v>The Warning - Ego (Official Video) - The Warning</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Minelli - Sun Goes Down | Official Visualizer</v>
+        <v>paris jackson - teenage drama (official lyric video)</v>
       </c>
       <c r="B53" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=xOsjm-AwN5I</v>
+        <v>https://www.youtube.com/watch?v=kVfDArNljos</v>
       </c>
       <c r="D53" t="str">
         <v>2026-06-01</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>Minelli</v>
+        <v>paris jackson</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Minelli - Sun Goes Down | Official Visualizer - Minelli</v>
+        <v>paris jackson - teenage drama (official lyric video) - paris jackson</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Maggie Rose - Gentle Man (Official Studio Video)</v>
+        <v>Minelli - Sun Goes Down | Official Visualizer</v>
       </c>
       <c r="B54" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=aWNK-vWrN60</v>
+        <v>https://www.youtube.com/watch?v=xOsjm-AwN5I</v>
       </c>
       <c r="D54" t="str">
         <v>2026-06-01</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>Maggie Rose</v>
+        <v>Minelli</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Maggie Rose - Gentle Man (Official Studio Video) - Maggie Rose</v>
+        <v>Minelli - Sun Goes Down | Official Visualizer - Minelli</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer]</v>
+        <v>Maggie Rose - Gentle Man (Official Studio Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=mN5AZBrVq9I</v>
+        <v>https://www.youtube.com/watch?v=aWNK-vWrN60</v>
       </c>
       <c r="D55" t="str">
         <v>2026-06-01</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>David Guetta</v>
+        <v>Maggie Rose</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer] - David Guetta</v>
+        <v>Maggie Rose - Gentle Man (Official Studio Video) - Maggie Rose</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video)</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer]</v>
       </c>
       <c r="B56" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=0PTufEGRAVQ</v>
+        <v>https://www.youtube.com/watch?v=mN5AZBrVq9I</v>
       </c>
       <c r="D56" t="str">
         <v>2026-06-01</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>Chris Young and Shaylen</v>
+        <v>David Guetta</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video) - Chris Young and Shaylen</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer] - David Guetta</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Lauv - Pretty Little Things</v>
+        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video)</v>
       </c>
       <c r="B57" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=_JBfanFvHnA</v>
+        <v>https://www.youtube.com/watch?v=0PTufEGRAVQ</v>
       </c>
       <c r="D57" t="str">
         <v>2026-06-01</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>Lauv</v>
+        <v>Chris Young and Shaylen</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Lauv - Pretty Little Things - Lauv</v>
+        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video) - Chris Young and Shaylen</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Icona Pop - Butterfly Feelings (Official Audio)</v>
+        <v>Lauv - Pretty Little Things</v>
       </c>
       <c r="B58" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=bXA_Q75QZTs</v>
+        <v>https://www.youtube.com/watch?v=_JBfanFvHnA</v>
       </c>
       <c r="D58" t="str">
         <v>2026-06-01</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>Icona Pop</v>
+        <v>Lauv</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Icona Pop - Butterfly Feelings (Official Audio) - Icona Pop</v>
+        <v>Lauv - Pretty Little Things - Lauv</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Will Swinton - Only One (Official Video)</v>
+        <v>Icona Pop - Butterfly Feelings (Official Audio)</v>
       </c>
       <c r="B59" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=A0KzP-zm9hA</v>
+        <v>https://www.youtube.com/watch?v=bXA_Q75QZTs</v>
       </c>
       <c r="D59" t="str">
         <v>2026-06-01</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>Will Swinton</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Will Swinton - Only One (Official Video) - Will Swinton</v>
+        <v>Icona Pop - Butterfly Feelings (Official Audio) - Icona Pop</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Dean Lewis - Escape (Official Video)</v>
+        <v>Will Swinton - Only One (Official Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=BZRaTXCkhcg</v>
+        <v>https://www.youtube.com/watch?v=A0KzP-zm9hA</v>
       </c>
       <c r="D60" t="str">
         <v>2026-06-01</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>Dean Lewis</v>
+        <v>Will Swinton</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Dean Lewis - Escape (Official Video) - Dean Lewis</v>
+        <v>Will Swinton - Only One (Official Video) - Will Swinton</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico]</v>
+        <v>Dean Lewis - Escape (Official Video)</v>
       </c>
       <c r="B61" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=PNm0hf_zZJY</v>
+        <v>https://www.youtube.com/watch?v=BZRaTXCkhcg</v>
       </c>
       <c r="D61" t="str">
         <v>2026-06-01</v>
@@ -2693,13 +2693,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>Dua Lipa and OficialMana</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico] - Dua Lipa and OficialMana</v>
+        <v>Dean Lewis - Escape (Official Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Niall Horan - End of an Era (Lyric Video)</v>
+        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico]</v>
       </c>
       <c r="B62" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=EUNNmAAe5gQ</v>
+        <v>https://www.youtube.com/watch?v=PNm0hf_zZJY</v>
       </c>
       <c r="D62" t="str">
         <v>2026-06-01</v>
@@ -2731,13 +2731,13 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>Niall Horan</v>
+        <v>Dua Lipa and OficialMana</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Niall Horan - End of an Era (Lyric Video) - Niall Horan</v>
+        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico] - Dua Lipa and OficialMana</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Olivia Rodrigo - the cure (Official Music Video)</v>
+        <v>Niall Horan - End of an Era (Lyric Video)</v>
       </c>
       <c r="B63" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=B402rKl4bUg</v>
+        <v>https://www.youtube.com/watch?v=EUNNmAAe5gQ</v>
       </c>
       <c r="D63" t="str">
         <v>2026-06-01</v>
@@ -2769,13 +2769,13 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>Olivia Rodrigo</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Olivia Rodrigo - the cure (Official Music Video) - Olivia Rodrigo</v>
+        <v>Niall Horan - End of an Era (Lyric Video) - Niall Horan</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Ruel - Debbie Don't Cry (Official Music Video)</v>
+        <v>Olivia Rodrigo - the cure (Official Music Video)</v>
       </c>
       <c r="B64" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=iz7wuk0GOwI</v>
+        <v>https://www.youtube.com/watch?v=B402rKl4bUg</v>
       </c>
       <c r="D64" t="str">
         <v>2026-06-01</v>
@@ -2807,13 +2807,13 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>RUEL</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Ruel - Debbie Don't Cry (Official Music Video) - RUEL</v>
+        <v>Olivia Rodrigo - the cure (Official Music Video) - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>TINI - Down (LIVE)</v>
+        <v>Ruel - Debbie Don't Cry (Official Music Video)</v>
       </c>
       <c r="B65" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=ADbFeQUPTrk</v>
+        <v>https://www.youtube.com/watch?v=iz7wuk0GOwI</v>
       </c>
       <c r="D65" t="str">
         <v>2026-06-01</v>
@@ -2845,13 +2845,13 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>TINI</v>
+        <v>RUEL</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>TINI - Down (LIVE) - TINI</v>
+        <v>Ruel - Debbie Don't Cry (Official Music Video) - RUEL</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Charli xcx - SS26 (Official Video)</v>
+        <v>TINI - Down (LIVE)</v>
       </c>
       <c r="B66" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=twLhSqabby0</v>
+        <v>https://www.youtube.com/watch?v=ADbFeQUPTrk</v>
       </c>
       <c r="D66" t="str">
         <v>2026-06-01</v>
@@ -2883,13 +2883,13 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>Charli xcx</v>
+        <v>TINI</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Charli xcx - SS26 (Official Video) - Charli xcx</v>
+        <v>TINI - Down (LIVE) - TINI</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Dua Lipa - Live From Mexico</v>
+        <v>Charli xcx - SS26 (Official Video)</v>
       </c>
       <c r="B67" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=vZYVkitGXBU</v>
+        <v>https://www.youtube.com/watch?v=twLhSqabby0</v>
       </c>
       <c r="D67" t="str">
         <v>2026-06-01</v>
@@ -2921,13 +2921,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>Dua Lipa</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Dua Lipa - Live From Mexico - Dua Lipa</v>
+        <v>Charli xcx - SS26 (Official Video) - Charli xcx</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Matilda Mann - 'The Fig Tree' (Official Video)</v>
+        <v>Dua Lipa - Live From Mexico</v>
       </c>
       <c r="B68" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=XPyubkkkw44</v>
+        <v>https://www.youtube.com/watch?v=vZYVkitGXBU</v>
       </c>
       <c r="D68" t="str">
         <v>2026-06-01</v>
@@ -2959,13 +2959,13 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>Matilda Mann</v>
+        <v>Dua Lipa</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Matilda Mann - 'The Fig Tree' (Official Video) - Matilda Mann</v>
+        <v>Dua Lipa - Live From Mexico - Dua Lipa</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Ella Langley - Be Her (61st Academy of Country Music Awards)</v>
+        <v>Matilda Mann - 'The Fig Tree' (Official Video)</v>
       </c>
       <c r="B69" t="str">
-        <v>11 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=4KbYfH7EAm8</v>
+        <v>https://www.youtube.com/watch?v=XPyubkkkw44</v>
       </c>
       <c r="D69" t="str">
         <v>2026-06-01</v>
@@ -2997,13 +2997,13 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>11 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>Ella Langley</v>
+        <v>Matilda Mann</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Ella Langley - Be Her (61st Academy of Country Music Awards) - Ella Langley</v>
+        <v>Matilda Mann - 'The Fig Tree' (Official Video) - Matilda Mann</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Nothing But Thieves - Evolution (Official Audio)</v>
+        <v>Ella Langley - Be Her (61st Academy of Country Music Awards)</v>
       </c>
       <c r="B70" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=Kcs-4EZSUW0</v>
+        <v>https://www.youtube.com/watch?v=4KbYfH7EAm8</v>
       </c>
       <c r="D70" t="str">
         <v>2026-06-01</v>
@@ -3035,13 +3035,13 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Nothing But Thieves - Evolution (Official Audio) - Nothing But Thieves</v>
+        <v>Ella Langley - Be Her (61st Academy of Country Music Awards) - Ella Langley</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO)</v>
+        <v>Nothing But Thieves - Evolution (Official Audio)</v>
       </c>
       <c r="B71" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=HiLT1jzDZb4</v>
+        <v>https://www.youtube.com/watch?v=Kcs-4EZSUW0</v>
       </c>
       <c r="D71" t="str">
         <v>2026-06-01</v>
@@ -3073,13 +3073,13 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>kesha</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO) - kesha</v>
+        <v>Nothing But Thieves - Evolution (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify</v>
+        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO)</v>
       </c>
       <c r="B72" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=_WGsJYCCfU8</v>
+        <v>https://www.youtube.com/watch?v=HiLT1jzDZb4</v>
       </c>
       <c r="D72" t="str">
         <v>2026-06-01</v>
@@ -3111,13 +3111,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>Holly Humberstone</v>
+        <v>kesha</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify - Holly Humberstone</v>
+        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO) - kesha</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Foo Fighters - Of All People (Official Video)</v>
+        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify</v>
       </c>
       <c r="B73" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=r_iMzMrCQs0</v>
+        <v>https://www.youtube.com/watch?v=_WGsJYCCfU8</v>
       </c>
       <c r="D73" t="str">
         <v>2026-06-01</v>
@@ -3149,13 +3149,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>Foo Fighters</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Foo Fighters - Of All People (Official Video) - Foo Fighters</v>
+        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify - Holly Humberstone</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>'From Me To You' by The Beatles, performed by The Young Analogues</v>
+        <v>Foo Fighters - Of All People (Official Video)</v>
       </c>
       <c r="B74" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=cLiyO2t3xd0</v>
+        <v>https://www.youtube.com/watch?v=r_iMzMrCQs0</v>
       </c>
       <c r="D74" t="str">
         <v>2026-06-01</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>The Analogues</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>'From Me To You' by The Beatles, performed by The Young Analogues - The Analogues</v>
+        <v>Foo Fighters - Of All People (Official Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video]</v>
+        <v>'From Me To You' by The Beatles, performed by The Young Analogues</v>
       </c>
       <c r="B75" t="str">
-        <v>12 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=O67Q25sMhyU</v>
+        <v>https://www.youtube.com/watch?v=cLiyO2t3xd0</v>
       </c>
       <c r="D75" t="str">
         <v>2026-06-01</v>
@@ -3225,13 +3225,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>12 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>Rod Stewart</v>
+        <v>The Analogues</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video] - Rod Stewart</v>
+        <v>'From Me To You' by The Beatles, performed by The Young Analogues - The Analogues</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Blue October - 18th Floor Balcony (Official Music Video)</v>
+        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video]</v>
       </c>
       <c r="B76" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=tPfbOjz-hRs</v>
+        <v>https://www.youtube.com/watch?v=O67Q25sMhyU</v>
       </c>
       <c r="D76" t="str">
         <v>2026-06-01</v>
@@ -3263,13 +3263,13 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>Blue October</v>
+        <v>Rod Stewart</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Blue October - 18th Floor Balcony (Official Music Video) - Blue October</v>
+        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video] - Rod Stewart</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Far Caspian - hum (Official Video)</v>
+        <v>Blue October - 18th Floor Balcony (Official Music Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=qqXrLDhGJRk</v>
+        <v>https://www.youtube.com/watch?v=tPfbOjz-hRs</v>
       </c>
       <c r="D77" t="str">
         <v>2026-06-01</v>
@@ -3301,13 +3301,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>Far Caspian</v>
+        <v>Blue October</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Far Caspian - hum (Official Video) - Far Caspian</v>
+        <v>Blue October - 18th Floor Balcony (Official Music Video) - Blue October</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Kenia Os - Love Bombing</v>
+        <v>Far Caspian - hum (Official Video)</v>
       </c>
       <c r="B78" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=ZuWA3pAyriQ</v>
+        <v>https://www.youtube.com/watch?v=qqXrLDhGJRk</v>
       </c>
       <c r="D78" t="str">
         <v>2026-06-01</v>
@@ -3339,13 +3339,13 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>Kenia Os</v>
+        <v>Far Caspian</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Kenia Os - Love Bombing - Kenia Os</v>
+        <v>Far Caspian - hum (Official Video) - Far Caspian</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026</v>
+        <v>Kenia Os - Love Bombing</v>
       </c>
       <c r="B79" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=ftJR_CrRsig</v>
+        <v>https://www.youtube.com/watch?v=ZuWA3pAyriQ</v>
       </c>
       <c r="D79" t="str">
         <v>2026-06-01</v>
@@ -3377,13 +3377,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>Purple Disco Machine</v>
+        <v>Kenia Os</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026 - Purple Disco Machine</v>
+        <v>Kenia Os - Love Bombing - Kenia Os</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026</v>
       </c>
       <c r="B80" t="str">
-        <v>2 weeks ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=EltgrumKJfk</v>
+        <v>https://www.youtube.com/watch?v=ftJR_CrRsig</v>
       </c>
       <c r="D80" t="str">
         <v>2026-06-01</v>
@@ -3415,13 +3415,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>2 weeks ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Purple Disco Machine</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026 - Eurovision Song Contest</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026 - Purple Disco Machine</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹</v>
+        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026</v>
       </c>
       <c r="B81" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=EykAYQj99GU</v>
+        <v>https://www.youtube.com/watch?v=EltgrumKJfk</v>
       </c>
       <c r="D81" t="str">
         <v>2026-06-01</v>
@@ -3453,7 +3453,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹 - Eurovision Song Contest</v>
+        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026</v>
+        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹</v>
       </c>
       <c r="B82" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=doGkDemPcFE</v>
+        <v>https://www.youtube.com/watch?v=EykAYQj99GU</v>
       </c>
       <c r="D82" t="str">
         <v>2026-06-01</v>
@@ -3491,7 +3491,7 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026</v>
+        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B83" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=rNpFNJLhSfA</v>
+        <v>https://www.youtube.com/watch?v=doGkDemPcFE</v>
       </c>
       <c r="D83" t="str">
         <v>2026-06-01</v>
@@ -3529,7 +3529,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026</v>
+        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B84" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=TpMQ6dhcvvE</v>
+        <v>https://www.youtube.com/watch?v=rNpFNJLhSfA</v>
       </c>
       <c r="D84" t="str">
         <v>2026-06-01</v>
@@ -3567,7 +3567,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​</v>
+        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B85" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=ppCyj5DxO8s</v>
+        <v>https://www.youtube.com/watch?v=TpMQ6dhcvvE</v>
       </c>
       <c r="D85" t="str">
         <v>2026-06-01</v>
@@ -3605,7 +3605,7 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​ - Eurovision Song Contest</v>
+        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Evanescence – Who Will You Follow (Official Music Video)</v>
+        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​</v>
       </c>
       <c r="B86" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=ak4Ti54Y6rY</v>
+        <v>https://www.youtube.com/watch?v=ppCyj5DxO8s</v>
       </c>
       <c r="D86" t="str">
         <v>2026-06-01</v>
@@ -3643,13 +3643,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>Evanescence</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Evanescence – Who Will You Follow (Official Music Video) - Evanescence</v>
+        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​ - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>DEEP PURPLE – ARROGANT BOY (Official Video)</v>
+        <v>Evanescence – Who Will You Follow (Official Music Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=SoSr0sStFaE</v>
+        <v>https://www.youtube.com/watch?v=ak4Ti54Y6rY</v>
       </c>
       <c r="D87" t="str">
         <v>2026-06-01</v>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>earMUSIC and Deep Purple Official</v>
+        <v>Evanescence</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>DEEP PURPLE – ARROGANT BOY (Official Video) - earMUSIC and Deep Purple Official</v>
+        <v>Evanescence – Who Will You Follow (Official Music Video) - Evanescence</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video]</v>
+        <v>DEEP PURPLE – ARROGANT BOY (Official Video)</v>
       </c>
       <c r="B88" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=9iCw89UajaQ</v>
+        <v>https://www.youtube.com/watch?v=SoSr0sStFaE</v>
       </c>
       <c r="D88" t="str">
         <v>2026-06-01</v>
@@ -3719,13 +3719,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>Armin van Buuren</v>
+        <v>earMUSIC and Deep Purple Official</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>DEEP PURPLE – ARROGANT BOY (Official Video) - earMUSIC and Deep Purple Official</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Madison Cunningham - "Take Two" (Live in Chicago)</v>
+        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B89" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=bUBLlJXtjqE</v>
+        <v>https://www.youtube.com/watch?v=9iCw89UajaQ</v>
       </c>
       <c r="D89" t="str">
         <v>2026-06-01</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>Madison Cunningham</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Madison Cunningham - "Take Two" (Live in Chicago) - Madison Cunningham</v>
+        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Johnny Orlando - Heads Up (Official Video)</v>
+        <v>Madison Cunningham - "Take Two" (Live in Chicago)</v>
       </c>
       <c r="B90" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=s5mClhWsajE</v>
+        <v>https://www.youtube.com/watch?v=bUBLlJXtjqE</v>
       </c>
       <c r="D90" t="str">
         <v>2026-06-01</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>Johnny Orlando</v>
+        <v>Madison Cunningham</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Johnny Orlando - Heads Up (Official Video) - Johnny Orlando</v>
+        <v>Madison Cunningham - "Take Two" (Live in Chicago) - Madison Cunningham</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Carver Jones - BEST FRIEND (Official Video)</v>
+        <v>Johnny Orlando - Heads Up (Official Video)</v>
       </c>
       <c r="B91" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=96xxxpZ5uxI</v>
+        <v>https://www.youtube.com/watch?v=s5mClhWsajE</v>
       </c>
       <c r="D91" t="str">
         <v>2026-06-01</v>
@@ -3833,13 +3833,13 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>Carver Jones</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Carver Jones - BEST FRIEND (Official Video) - Carver Jones</v>
+        <v>Johnny Orlando - Heads Up (Official Video) - Johnny Orlando</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Jazmin Bean - Darling (Official Music Video)</v>
+        <v>Carver Jones - BEST FRIEND (Official Video)</v>
       </c>
       <c r="B92" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=N4uW3ZcowBM</v>
+        <v>https://www.youtube.com/watch?v=96xxxpZ5uxI</v>
       </c>
       <c r="D92" t="str">
         <v>2026-06-01</v>
@@ -3871,13 +3871,13 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
       </c>
       <c r="H92" t="str">
-        <v>Jazmin bean</v>
+        <v>Carver Jones</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Jazmin Bean - Darling (Official Music Video) - Jazmin bean</v>
+        <v>Carver Jones - BEST FRIEND (Official Video) - Carver Jones</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Baby Queen - Word Vomit (Official Visualiser)</v>
+        <v>Jazmin Bean - Darling (Official Music Video)</v>
       </c>
       <c r="B93" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=T-bo4Klq_js</v>
+        <v>https://www.youtube.com/watch?v=N4uW3ZcowBM</v>
       </c>
       <c r="D93" t="str">
         <v>2026-06-01</v>
@@ -3909,13 +3909,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>Baby Queen</v>
+        <v>Jazmin bean</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Baby Queen - Word Vomit (Official Visualiser) - Baby Queen</v>
+        <v>Jazmin Bean - Darling (Official Music Video) - Jazmin bean</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Switchfoot - Absolution (Official Audio)</v>
+        <v>Baby Queen - Word Vomit (Official Visualiser)</v>
       </c>
       <c r="B94" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=nCOSfMdKq9k</v>
+        <v>https://www.youtube.com/watch?v=T-bo4Klq_js</v>
       </c>
       <c r="D94" t="str">
         <v>2026-06-01</v>
@@ -3947,13 +3947,13 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
       </c>
       <c r="H94" t="str">
-        <v>Switchfoot</v>
+        <v>Baby Queen</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Switchfoot - Absolution (Official Audio) - Switchfoot</v>
+        <v>Baby Queen - Word Vomit (Official Visualiser) - Baby Queen</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Grace Potter - Love Me Not (Official Audio)</v>
+        <v>Switchfoot - Absolution (Official Audio)</v>
       </c>
       <c r="B95" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=W3v0HAxDTUY</v>
+        <v>https://www.youtube.com/watch?v=nCOSfMdKq9k</v>
       </c>
       <c r="D95" t="str">
         <v>2026-06-01</v>
@@ -3985,13 +3985,13 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
       </c>
       <c r="H95" t="str">
-        <v>Grace Potter</v>
+        <v>Switchfoot</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Grace Potter - Love Me Not (Official Audio) - Grace Potter</v>
+        <v>Switchfoot - Absolution (Official Audio) - Switchfoot</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986)</v>
+        <v>Grace Potter - Love Me Not (Official Audio)</v>
       </c>
       <c r="B96" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=Dhy4xH662vE</v>
+        <v>https://www.youtube.com/watch?v=W3v0HAxDTUY</v>
       </c>
       <c r="D96" t="str">
         <v>2026-06-01</v>
@@ -4023,13 +4023,13 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
       </c>
       <c r="H96" t="str">
-        <v>Modern Talking Offiziell</v>
+        <v>Grace Potter</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986) - Modern Talking Offiziell</v>
+        <v>Grace Potter - Love Me Not (Official Audio) - Grace Potter</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>The All-American Rejects - Clothesline (Official Lyric Video)</v>
+        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986)</v>
       </c>
       <c r="B97" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=y9axmk3NjrA</v>
+        <v>https://www.youtube.com/watch?v=Dhy4xH662vE</v>
       </c>
       <c r="D97" t="str">
         <v>2026-06-01</v>
@@ -4061,13 +4061,13 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
       </c>
       <c r="H97" t="str">
-        <v>The All-American Rejects</v>
+        <v>Modern Talking Offiziell</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>The All-American Rejects - Clothesline (Official Lyric Video) - The All-American Rejects</v>
+        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986) - Modern Talking Offiziell</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Henry Moodie - MISS U (Official Visualiser)</v>
+        <v>The All-American Rejects - Clothesline (Official Lyric Video)</v>
       </c>
       <c r="B98" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=l_lroRlSmTE</v>
+        <v>https://www.youtube.com/watch?v=y9axmk3NjrA</v>
       </c>
       <c r="D98" t="str">
         <v>2026-06-01</v>
@@ -4099,13 +4099,13 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
       </c>
       <c r="H98" t="str">
-        <v>Henry Moodie</v>
+        <v>The All-American Rejects</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Henry Moodie - MISS U (Official Visualiser) - Henry Moodie</v>
+        <v>The All-American Rejects - Clothesline (Official Lyric Video) - The All-American Rejects</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Spacey Jane - I Never See Her (Official Music Video)</v>
+        <v>Henry Moodie - MISS U (Official Visualiser)</v>
       </c>
       <c r="B99" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=q6tyEMN5haA</v>
+        <v>https://www.youtube.com/watch?v=l_lroRlSmTE</v>
       </c>
       <c r="D99" t="str">
         <v>2026-06-01</v>
@@ -4137,13 +4137,13 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
       </c>
       <c r="H99" t="str">
-        <v>Spacey Jane</v>
+        <v>Henry Moodie</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Spacey Jane - I Never See Her (Official Music Video) - Spacey Jane</v>
+        <v>Henry Moodie - MISS U (Official Visualiser) - Henry Moodie</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video)</v>
+        <v>Spacey Jane - I Never See Her (Official Music Video)</v>
       </c>
       <c r="B100" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=qacdvCqOZGc</v>
+        <v>https://www.youtube.com/watch?v=q6tyEMN5haA</v>
       </c>
       <c r="D100" t="str">
         <v>2026-06-01</v>
@@ -4175,13 +4175,13 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
       </c>
       <c r="H100" t="str">
-        <v>Megan Moroney</v>
+        <v>Spacey Jane</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video) - Megan Moroney</v>
+        <v>Spacey Jane - I Never See Her (Official Music Video) - Spacey Jane</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Matt Hansen - Orchid (Official Visualiser)</v>
+        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video)</v>
       </c>
       <c r="B101" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=otVYamnbOhY</v>
+        <v>https://www.youtube.com/watch?v=qacdvCqOZGc</v>
       </c>
       <c r="D101" t="str">
         <v>2026-06-01</v>
@@ -4213,13 +4213,13 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G101" t="str">
         <v/>
       </c>
       <c r="H101" t="str">
-        <v>Matt Hansen</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Matt Hansen - Orchid (Official Visualiser) - Matt Hansen</v>
+        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>hate that i made you love me</v>
+        <v>Matt Hansen - Orchid (Official Visualiser)</v>
       </c>
       <c r="B102" t="str">
-        <v/>
+        <v>2w ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/hate-that-i-made-you-love-me/6763656876</v>
+        <v>https://www.youtube.com/watch?v=otVYamnbOhY</v>
       </c>
       <c r="D102" t="str">
         <v>2026-06-01</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>petal</v>
+        <v>2w ago</v>
       </c>
       <c r="G102" t="str">
-        <v>3:17</v>
+        <v/>
       </c>
       <c r="H102" t="str">
-        <v>Ariana Grande</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/ariana-grande/412778295</v>
+        <v/>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/hate-that-i-made-you-love-me/1895420989</v>
+        <v/>
       </c>
       <c r="L102" t="str">
-        <v>hate that i made you love me - Ariana Grande</v>
+        <v>Matt Hansen - Orchid (Official Visualiser) - Matt Hansen</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Come Inside</v>
+        <v>hate that i made you love me</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/come-inside/1887403093</v>
+        <v>https://music.apple.com/us/song/hate-that-i-made-you-love-me/6763656876</v>
       </c>
       <c r="D103" t="str">
         <v>2026-06-01</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>The Boys of Dungeon Lane</v>
+        <v>petal</v>
       </c>
       <c r="G103" t="str">
-        <v>3:13</v>
+        <v>3:17</v>
       </c>
       <c r="H103" t="str">
-        <v>Paul McCartney</v>
+        <v>Ariana Grande</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/paul-mccartney/12224</v>
+        <v>https://music.apple.com/us/artist/ariana-grande/412778295</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/come-inside/1887402919</v>
+        <v>https://music.apple.com/us/album/hate-that-i-made-you-love-me/1895420989</v>
       </c>
       <c r="L103" t="str">
-        <v>Come Inside - Paul McCartney</v>
+        <v>hate that i made you love me - Ariana Grande</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Game Time</v>
+        <v>Come Inside</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/game-time/6771157200</v>
+        <v>https://music.apple.com/us/song/come-inside/1887403093</v>
       </c>
       <c r="D104" t="str">
         <v>2026-06-01</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>Game Time (FIFA World Cup 2026™) - Single</v>
+        <v>The Boys of Dungeon Lane</v>
       </c>
       <c r="G104" t="str">
-        <v>3:26</v>
+        <v>3:13</v>
       </c>
       <c r="H104" t="str">
-        <v>Future</v>
+        <v>Paul McCartney</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/future/128050210</v>
+        <v>https://music.apple.com/us/artist/paul-mccartney/12224</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/game-time/6771157186</v>
+        <v>https://music.apple.com/us/album/come-inside/1887402919</v>
       </c>
       <c r="L104" t="str">
-        <v>Game Time - Future</v>
+        <v>Come Inside - Paul McCartney</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Motion Party (Remix)</v>
+        <v>Game Time</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/motion-party-remix/6773413965</v>
+        <v>https://music.apple.com/us/song/game-time/6771157200</v>
       </c>
       <c r="D105" t="str">
         <v>2026-06-01</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>Motion Party (Remix) - Single</v>
+        <v>Game Time (FIFA World Cup 2026™) - Single</v>
       </c>
       <c r="G105" t="str">
-        <v>2:36</v>
+        <v>3:26</v>
       </c>
       <c r="H105" t="str">
-        <v>Bossman Dlow</v>
+        <v>Future</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/bossman-dlow/1474308236</v>
+        <v>https://music.apple.com/us/artist/future/128050210</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/motion-party-remix/6773413953</v>
+        <v>https://music.apple.com/us/album/game-time/6771157186</v>
       </c>
       <c r="L105" t="str">
-        <v>Motion Party (Remix) - Bossman Dlow</v>
+        <v>Game Time - Future</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Aquel diciembre</v>
+        <v>Motion Party (Remix)</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/aquel-diciembre/6769580010</v>
+        <v>https://music.apple.com/us/song/motion-party-remix/6773413965</v>
       </c>
       <c r="D106" t="str">
         <v>2026-06-01</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>Do Not Disturb: Late Checkout</v>
+        <v>Motion Party (Remix) - Single</v>
       </c>
       <c r="G106" t="str">
-        <v>3:22</v>
+        <v>2:36</v>
       </c>
       <c r="H106" t="str">
-        <v>Young Miko</v>
+        <v>Bossman Dlow</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/young-miko/1576521417</v>
+        <v>https://music.apple.com/us/artist/bossman-dlow/1474308236</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/aquel-diciembre/6769579992</v>
+        <v>https://music.apple.com/us/album/motion-party-remix/6773413953</v>
       </c>
       <c r="L106" t="str">
-        <v>Aquel diciembre - Young Miko</v>
+        <v>Motion Party (Remix) - Bossman Dlow</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Handle</v>
+        <v>Aquel diciembre</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/handle/6771922623</v>
+        <v>https://music.apple.com/us/song/aquel-diciembre/6769580010</v>
       </c>
       <c r="D107" t="str">
         <v>2026-06-01</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>Blue Island</v>
+        <v>Do Not Disturb: Late Checkout</v>
       </c>
       <c r="G107" t="str">
-        <v>3:06</v>
+        <v>3:22</v>
       </c>
       <c r="H107" t="str">
-        <v>Ravyn Lenae</v>
+        <v>Young Miko</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/ravyn-lenae/1044417443</v>
+        <v>https://music.apple.com/us/artist/young-miko/1576521417</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/handle/6771922622</v>
+        <v>https://music.apple.com/us/album/aquel-diciembre/6769579992</v>
       </c>
       <c r="L107" t="str">
-        <v>Handle - Ravyn Lenae</v>
+        <v>Aquel diciembre - Young Miko</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>The Wave</v>
+        <v>Handle</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/the-wave/1886730541</v>
+        <v>https://music.apple.com/us/song/handle/6771922623</v>
       </c>
       <c r="D108" t="str">
         <v>2026-06-01</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Sunshine</v>
+        <v>Blue Island</v>
       </c>
       <c r="G108" t="str">
-        <v>3:22</v>
+        <v>3:06</v>
       </c>
       <c r="H108" t="str">
-        <v>Jungle</v>
+        <v>Ravyn Lenae</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/jungle/825833522</v>
+        <v>https://music.apple.com/us/artist/ravyn-lenae/1044417443</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/the-wave/1886730527</v>
+        <v>https://music.apple.com/us/album/handle/6771922622</v>
       </c>
       <c r="L108" t="str">
-        <v>The Wave - Jungle</v>
+        <v>Handle - Ravyn Lenae</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>STOP</v>
+        <v>The Wave</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/stop/6771161771</v>
+        <v>https://music.apple.com/us/song/the-wave/1886730541</v>
       </c>
       <c r="D109" t="str">
         <v>2026-06-01</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>are you mad at me? - Single</v>
+        <v>Sunshine</v>
       </c>
       <c r="G109" t="str">
-        <v>2:56</v>
+        <v>3:22</v>
       </c>
       <c r="H109" t="str">
-        <v>Bella Kay</v>
+        <v>Jungle</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
+        <v>https://music.apple.com/us/artist/jungle/825833522</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/stop/6771161760</v>
+        <v>https://music.apple.com/us/album/the-wave/1886730527</v>
       </c>
       <c r="L109" t="str">
-        <v>STOP - Bella Kay</v>
+        <v>The Wave - Jungle</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Here (Apple Music Sessions)</v>
+        <v>STOP</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/here-apple-music-sessions/1878235516</v>
+        <v>https://music.apple.com/us/song/stop/6771161771</v>
       </c>
       <c r="D110" t="str">
         <v>2026-06-01</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Apple Music Sessions</v>
+        <v>are you mad at me? - Single</v>
       </c>
       <c r="G110" t="str">
-        <v>3:08</v>
+        <v>2:56</v>
       </c>
       <c r="H110" t="str">
-        <v>Mumford &amp; Sons</v>
+        <v>Bella Kay</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/mumford-sons/307699986</v>
+        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/here-apple-music-sessions/1878235330</v>
+        <v>https://music.apple.com/us/album/stop/6771161760</v>
       </c>
       <c r="L110" t="str">
-        <v>Here (Apple Music Sessions) - Mumford &amp; Sons</v>
+        <v>STOP - Bella Kay</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Talk On The Hill</v>
+        <v>Here (Apple Music Sessions)</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/talk-on-the-hill/6769524458</v>
+        <v>https://music.apple.com/us/song/here-apple-music-sessions/1878235516</v>
       </c>
       <c r="D111" t="str">
         <v>2026-06-01</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>The Thread</v>
+        <v>Apple Music Sessions</v>
       </c>
       <c r="G111" t="str">
-        <v>3:27</v>
+        <v>3:08</v>
       </c>
       <c r="H111" t="str">
-        <v>WILLOW</v>
+        <v>Mumford &amp; Sons</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/willow/400531893</v>
+        <v>https://music.apple.com/us/artist/mumford-sons/307699986</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/talk-on-the-hill/6769524450</v>
+        <v>https://music.apple.com/us/album/here-apple-music-sessions/1878235330</v>
       </c>
       <c r="L111" t="str">
-        <v>Talk On The Hill - WILLOW</v>
+        <v>Here (Apple Music Sessions) - Mumford &amp; Sons</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>No Fear</v>
+        <v>Talk On The Hill</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/no-fear/1880484493</v>
+        <v>https://music.apple.com/us/song/talk-on-the-hill/6769524458</v>
       </c>
       <c r="D112" t="str">
         <v>2026-06-01</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>For Love of Grace &amp; the Hereafter</v>
+        <v>The Thread</v>
       </c>
       <c r="G112" t="str">
-        <v>3:38</v>
+        <v>3:27</v>
       </c>
       <c r="H112" t="str">
-        <v>Iceage</v>
+        <v>WILLOW</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/iceage/406846711</v>
+        <v>https://music.apple.com/us/artist/willow/400531893</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/no-fear/1880484160</v>
+        <v>https://music.apple.com/us/album/talk-on-the-hill/6769524450</v>
       </c>
       <c r="L112" t="str">
-        <v>No Fear - Iceage</v>
+        <v>Talk On The Hill - WILLOW</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Hostage (feat. 21 Savage)</v>
+        <v>No Fear</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/hostage-feat-21-savage/6774372288</v>
+        <v>https://music.apple.com/us/song/no-fear/1880484493</v>
       </c>
       <c r="D113" t="str">
         <v>2026-06-01</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Big Mama</v>
+        <v>For Love of Grace &amp; the Hereafter</v>
       </c>
       <c r="G113" t="str">
-        <v>3:11</v>
+        <v>3:38</v>
       </c>
       <c r="H113" t="str">
-        <v>Latto</v>
+        <v>Iceage</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/latto/419799506</v>
+        <v>https://music.apple.com/us/artist/iceage/406846711</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/hostage-feat-21-savage/6774372200</v>
+        <v>https://music.apple.com/us/album/no-fear/1880484160</v>
       </c>
       <c r="L113" t="str">
-        <v>Hostage (feat. 21 Savage) - Latto</v>
+        <v>No Fear - Iceage</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Sad Girls</v>
+        <v>Hostage (feat. 21 Savage)</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/sad-girls/6768814374</v>
+        <v>https://music.apple.com/us/song/hostage-feat-21-savage/6774372288</v>
       </c>
       <c r="D114" t="str">
         <v>2026-06-01</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Sad Girls - Single</v>
+        <v>Big Mama</v>
       </c>
       <c r="G114" t="str">
-        <v>2:48</v>
+        <v>3:11</v>
       </c>
       <c r="H114" t="str">
-        <v>Bebe Rexha</v>
+        <v>Latto</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/bebe-rexha/466059563</v>
+        <v>https://music.apple.com/us/artist/latto/419799506</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/sad-girls/6768814373</v>
+        <v>https://music.apple.com/us/album/hostage-feat-21-savage/6774372200</v>
       </c>
       <c r="L114" t="str">
-        <v>Sad Girls - Bebe Rexha</v>
+        <v>Hostage (feat. 21 Savage) - Latto</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Salvame Hoy (feat. Gabito Ballesteros)</v>
+        <v>Sad Girls</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/salvame-hoy-feat-gabito-ballesteros/6765697019</v>
+        <v>https://music.apple.com/us/song/sad-girls/6768814374</v>
       </c>
       <c r="D115" t="str">
         <v>2026-06-01</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Salvame Hoy (feat. Gabito Ballesteros) - Single</v>
+        <v>Sad Girls - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>3:35</v>
+        <v>2:48</v>
       </c>
       <c r="H115" t="str">
-        <v>Jennifer Lopez</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/jennifer-lopez/463009</v>
+        <v>https://music.apple.com/us/artist/bebe-rexha/466059563</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/salvame-hoy-feat-gabito-ballesteros/1896041010</v>
+        <v>https://music.apple.com/us/album/sad-girls/6768814373</v>
       </c>
       <c r="L115" t="str">
-        <v>Salvame Hoy (feat. Gabito Ballesteros) - Jennifer Lopez</v>
+        <v>Sad Girls - Bebe Rexha</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Rubio</v>
+        <v>Salvame Hoy (feat. Gabito Ballesteros)</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/rubio/6770655339</v>
+        <v>https://music.apple.com/us/song/salvame-hoy-feat-gabito-ballesteros/6765697019</v>
       </c>
       <c r="D116" t="str">
         <v>2026-06-01</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>La Voz Favorita</v>
+        <v>Salvame Hoy (feat. Gabito Ballesteros) - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>4:42</v>
+        <v>3:35</v>
       </c>
       <c r="H116" t="str">
-        <v>Jay Wheeler</v>
+        <v>Jennifer Lopez</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/jay-wheeler/164376380</v>
+        <v>https://music.apple.com/us/artist/jennifer-lopez/463009</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/rubio/6770654729</v>
+        <v>https://music.apple.com/us/album/salvame-hoy-feat-gabito-ballesteros/1896041010</v>
       </c>
       <c r="L116" t="str">
-        <v>Rubio - Jay Wheeler</v>
+        <v>Salvame Hoy (feat. Gabito Ballesteros) - Jennifer Lopez</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Pary</v>
+        <v>Rubio</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/pary/6767367748</v>
+        <v>https://music.apple.com/us/song/rubio/6770655339</v>
       </c>
       <c r="D117" t="str">
         <v>2026-06-01</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Con dolor - EP</v>
+        <v>La Voz Favorita</v>
       </c>
       <c r="G117" t="str">
-        <v>2:52</v>
+        <v>4:42</v>
       </c>
       <c r="H117" t="str">
-        <v>Grupo Frontera</v>
+        <v>Jay Wheeler</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
+        <v>https://music.apple.com/us/artist/jay-wheeler/164376380</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/pary/6767367501</v>
+        <v>https://music.apple.com/us/album/rubio/6770654729</v>
       </c>
       <c r="L117" t="str">
-        <v>Pary - Grupo Frontera</v>
+        <v>Rubio - Jay Wheeler</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Think As You Drunk</v>
+        <v>Pary</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/think-as-you-drunk/6770725979</v>
+        <v>https://music.apple.com/us/song/pary/6767367748</v>
       </c>
       <c r="D118" t="str">
         <v>2026-06-01</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>That's Just Me</v>
+        <v>Con dolor - EP</v>
       </c>
       <c r="G118" t="str">
-        <v>3:48</v>
+        <v>2:52</v>
       </c>
       <c r="H118" t="str">
-        <v>Riley Green</v>
+        <v>Grupo Frontera</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/riley-green/662432971</v>
+        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/think-as-you-drunk/6770725355</v>
+        <v>https://music.apple.com/us/album/pary/6767367501</v>
       </c>
       <c r="L118" t="str">
-        <v>Think As You Drunk - Riley Green</v>
+        <v>Pary - Grupo Frontera</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Play Your Games</v>
+        <v>Think As You Drunk</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/play-your-games/6772932837</v>
+        <v>https://music.apple.com/us/song/think-as-you-drunk/6770725979</v>
       </c>
       <c r="D119" t="str">
         <v>2026-06-01</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Play Your Games - Single</v>
+        <v>That's Just Me</v>
       </c>
       <c r="G119" t="str">
-        <v>3:15</v>
+        <v>3:48</v>
       </c>
       <c r="H119" t="str">
-        <v>Greta Van Fleet</v>
+        <v>Riley Green</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/greta-van-fleet/646178956</v>
+        <v>https://music.apple.com/us/artist/riley-green/662432971</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/play-your-games/6772932835</v>
+        <v>https://music.apple.com/us/album/think-as-you-drunk/6770725355</v>
       </c>
       <c r="L119" t="str">
-        <v>Play Your Games - Greta Van Fleet</v>
+        <v>Think As You Drunk - Riley Green</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello)</v>
+        <v>Play Your Games</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/adjourn-it-feat-serj-tankian-roman-morello/6769340216</v>
+        <v>https://music.apple.com/us/song/play-your-games/6772932837</v>
       </c>
       <c r="D120" t="str">
         <v>2026-06-01</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello) - Single</v>
+        <v>Play Your Games - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>2:47</v>
+        <v>3:15</v>
       </c>
       <c r="H120" t="str">
-        <v>Tom Morello</v>
+        <v>Greta Van Fleet</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/tom-morello/466357</v>
+        <v>https://music.apple.com/us/artist/greta-van-fleet/646178956</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/adjourn-it-feat-serj-tankian-roman-morello/6769340214</v>
+        <v>https://music.apple.com/us/album/play-your-games/6772932835</v>
       </c>
       <c r="L120" t="str">
-        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello) - Tom Morello</v>
+        <v>Play Your Games - Greta Van Fleet</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Essex_Honey.mp3</v>
+        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello)</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/essex-honey-mp3/6771169447</v>
+        <v>https://music.apple.com/us/song/adjourn-it-feat-serj-tankian-roman-morello/6769340216</v>
       </c>
       <c r="D121" t="str">
         <v>2026-06-01</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Essex_Honey.mp3 - Single</v>
+        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello) - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>4:49</v>
+        <v>2:47</v>
       </c>
       <c r="H121" t="str">
-        <v>Blood Orange</v>
+        <v>Tom Morello</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/blood-orange/440698865</v>
+        <v>https://music.apple.com/us/artist/tom-morello/466357</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/essex-honey-mp3/6771169151</v>
+        <v>https://music.apple.com/us/album/adjourn-it-feat-serj-tankian-roman-morello/6769340214</v>
       </c>
       <c r="L121" t="str">
-        <v>Essex_Honey.mp3 - Blood Orange</v>
+        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello) - Tom Morello</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>minute</v>
+        <v>Essex_Honey.mp3</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/minute/1875303122</v>
+        <v>https://music.apple.com/us/song/essex-honey-mp3/6771169447</v>
       </c>
       <c r="D122" t="str">
         <v>2026-06-01</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>ghosted - EP</v>
+        <v>Essex_Honey.mp3 - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>2:59</v>
+        <v>4:49</v>
       </c>
       <c r="H122" t="str">
-        <v>Saint Harison</v>
+        <v>Blood Orange</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/saint-harison/1639595302</v>
+        <v>https://music.apple.com/us/artist/blood-orange/440698865</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/minute/1875302904</v>
+        <v>https://music.apple.com/us/album/essex-honey-mp3/6771169151</v>
       </c>
       <c r="L122" t="str">
-        <v>minute - Saint Harison</v>
+        <v>Essex_Honey.mp3 - Blood Orange</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>THE LIVING</v>
+        <v>minute</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/the-living/1894092345</v>
+        <v>https://music.apple.com/us/song/minute/1875303122</v>
       </c>
       <c r="D123" t="str">
         <v>2026-06-01</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>COSMIC OPERA ACT II</v>
+        <v>ghosted - EP</v>
       </c>
       <c r="G123" t="str">
-        <v>2:48</v>
+        <v>2:59</v>
       </c>
       <c r="H123" t="str">
-        <v>Labrinth</v>
+        <v>Saint Harison</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
+        <v>https://music.apple.com/us/artist/saint-harison/1639595302</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/the-living/1894092339</v>
+        <v>https://music.apple.com/us/album/minute/1875302904</v>
       </c>
       <c r="L123" t="str">
-        <v>THE LIVING - Labrinth</v>
+        <v>minute - Saint Harison</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Thug</v>
+        <v>THE LIVING</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/thug/6769289966</v>
+        <v>https://music.apple.com/us/song/the-living/1894092345</v>
       </c>
       <c r="D124" t="str">
         <v>2026-06-01</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Thug - Single</v>
+        <v>COSMIC OPERA ACT II</v>
       </c>
       <c r="G124" t="str">
-        <v>2:25</v>
+        <v>2:48</v>
       </c>
       <c r="H124" t="str">
-        <v>G Herbo</v>
+        <v>Labrinth</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/g-herbo/1036753321</v>
+        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/thug/6769289953</v>
+        <v>https://music.apple.com/us/album/the-living/1894092339</v>
       </c>
       <c r="L124" t="str">
-        <v>Thug - G Herbo</v>
+        <v>THE LIVING - Labrinth</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Clap</v>
+        <v>Thug</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/clap/6769903711</v>
+        <v>https://music.apple.com/us/song/thug/6769289966</v>
       </c>
       <c r="D125" t="str">
         <v>2026-06-01</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Clap - Single</v>
+        <v>Thug - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>2:04</v>
+        <v>2:25</v>
       </c>
       <c r="H125" t="str">
-        <v>Polo G</v>
+        <v>G Herbo</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/polo-g/1159371412</v>
+        <v>https://music.apple.com/us/artist/g-herbo/1036753321</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/clap/6769903710</v>
+        <v>https://music.apple.com/us/album/thug/6769289953</v>
       </c>
       <c r="L125" t="str">
-        <v>Clap - Polo G</v>
+        <v>Thug - G Herbo</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>GANG BIZNESS</v>
+        <v>Clap</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/gang-bizness/6772383809</v>
+        <v>https://music.apple.com/us/song/clap/6769903711</v>
       </c>
       <c r="D126" t="str">
         <v>2026-06-01</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>THE GENTLEMEN'S CLUB</v>
+        <v>Clap - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>2:47</v>
+        <v>2:04</v>
       </c>
       <c r="H126" t="str">
-        <v>YG</v>
+        <v>Polo G</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/yg/189792075</v>
+        <v>https://music.apple.com/us/artist/polo-g/1159371412</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/gang-bizness/6772383681</v>
+        <v>https://music.apple.com/us/album/clap/6769903710</v>
       </c>
       <c r="L126" t="str">
-        <v>GANG BIZNESS - YG</v>
+        <v>Clap - Polo G</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>UR HEARTBEAT (WHO DO U THINK ABOUT AT 2AM?)</v>
+        <v>GANG BIZNESS</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/ur-heartbeat-who-do-u-think-about-at-2am/6765534140</v>
+        <v>https://music.apple.com/us/song/gang-bizness/6772383809</v>
       </c>
       <c r="D127" t="str">
         <v>2026-06-01</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>A LITTLE VENGEANCE</v>
+        <v>THE GENTLEMEN'S CLUB</v>
       </c>
       <c r="G127" t="str">
-        <v>2:50</v>
+        <v>2:47</v>
       </c>
       <c r="H127" t="str">
-        <v>Jessie Reyez</v>
+        <v>YG</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
+        <v>https://music.apple.com/us/artist/yg/189792075</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/ur-heartbeat-who-do-u-think-about-at-2am/1895983502</v>
+        <v>https://music.apple.com/us/album/gang-bizness/6772383681</v>
       </c>
       <c r="L127" t="str">
-        <v>UR HEARTBEAT (WHO DO U THINK ABOUT AT 2AM?) - Jessie Reyez</v>
+        <v>GANG BIZNESS - YG</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Joshua Tree</v>
+        <v>UR HEARTBEAT (WHO DO U THINK ABOUT AT 2AM?)</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/joshua-tree/6771859148</v>
+        <v>https://music.apple.com/us/song/ur-heartbeat-who-do-u-think-about-at-2am/6765534140</v>
       </c>
       <c r="D128" t="str">
         <v>2026-06-01</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Euphoria: Season 3 (HBO Original Series Soundtrack)</v>
+        <v>A LITTLE VENGEANCE</v>
       </c>
       <c r="G128" t="str">
         <v>2:50</v>
       </c>
       <c r="H128" t="str">
-        <v>Hans Zimmer</v>
+        <v>Jessie Reyez</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/hans-zimmer/454295032</v>
+        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/joshua-tree/6771858464</v>
+        <v>https://music.apple.com/us/album/ur-heartbeat-who-do-u-think-about-at-2am/1895983502</v>
       </c>
       <c r="L128" t="str">
-        <v>Joshua Tree - Hans Zimmer</v>
+        <v>UR HEARTBEAT (WHO DO U THINK ABOUT AT 2AM?) - Jessie Reyez</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Mi Gran Amor</v>
+        <v>Joshua Tree</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/mi-gran-amor/6773365775</v>
+        <v>https://music.apple.com/us/song/joshua-tree/6771859148</v>
       </c>
       <c r="D129" t="str">
         <v>2026-06-01</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Mi Gran Amor - Single</v>
+        <v>Euphoria: Season 3 (HBO Original Series Soundtrack)</v>
       </c>
       <c r="G129" t="str">
-        <v>3:37</v>
+        <v>2:50</v>
       </c>
       <c r="H129" t="str">
-        <v>Santana</v>
+        <v>Hans Zimmer</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/santana/217174</v>
+        <v>https://music.apple.com/us/artist/hans-zimmer/454295032</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/mi-gran-amor/6773365236</v>
+        <v>https://music.apple.com/us/album/joshua-tree/6771858464</v>
       </c>
       <c r="L129" t="str">
-        <v>Mi Gran Amor - Santana</v>
+        <v>Joshua Tree - Hans Zimmer</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>london</v>
+        <v>Mi Gran Amor</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/london/6770745672</v>
+        <v>https://music.apple.com/us/song/mi-gran-amor/6773365775</v>
       </c>
       <c r="D130" t="str">
         <v>2026-06-01</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>stardust - EP</v>
+        <v>Mi Gran Amor - Single</v>
       </c>
       <c r="G130" t="str">
-        <v>3:23</v>
+        <v>3:37</v>
       </c>
       <c r="H130" t="str">
-        <v>Freya Skye</v>
+        <v>Santana</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/freya-skye/1541643053</v>
+        <v>https://music.apple.com/us/artist/santana/217174</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/london/6770745662</v>
+        <v>https://music.apple.com/us/album/mi-gran-amor/6773365236</v>
       </c>
       <c r="L130" t="str">
-        <v>london - Freya Skye</v>
+        <v>Mi Gran Amor - Santana</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Caution</v>
+        <v>london</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/caution/6768487482</v>
+        <v>https://music.apple.com/us/song/london/6770745672</v>
       </c>
       <c r="D131" t="str">
         <v>2026-06-01</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>K-POPS! (Music from and inspired by K-POPS! Motion Picture)</v>
+        <v>stardust - EP</v>
       </c>
       <c r="G131" t="str">
-        <v>2:43</v>
+        <v>3:23</v>
       </c>
       <c r="H131" t="str">
-        <v>NMIXX</v>
+        <v>Freya Skye</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/nmixx/1600411676</v>
+        <v>https://music.apple.com/us/artist/freya-skye/1541643053</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/caution/6768487478</v>
+        <v>https://music.apple.com/us/album/london/6770745662</v>
       </c>
       <c r="L131" t="str">
-        <v>Caution - NMIXX</v>
+        <v>london - Freya Skye</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>LEMONADE (feat. Becky G)</v>
+        <v>Caution</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/lemonade-feat-becky-g/1893742425</v>
+        <v>https://music.apple.com/us/song/caution/6768487482</v>
       </c>
       <c r="D132" t="str">
         <v>2026-06-01</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>LEMONADE - The 2nd Album</v>
+        <v>K-POPS! (Music from and inspired by K-POPS! Motion Picture)</v>
       </c>
       <c r="G132" t="str">
-        <v>3:07</v>
+        <v>2:43</v>
       </c>
       <c r="H132" t="str">
-        <v>aespa</v>
+        <v>NMIXX</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
+        <v>https://music.apple.com/us/artist/nmixx/1600411676</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/lemonade-feat-becky-g/1893742002</v>
+        <v>https://music.apple.com/us/album/caution/6768487478</v>
       </c>
       <c r="L132" t="str">
-        <v>LEMONADE (feat. Becky G) - aespa</v>
+        <v>Caution - NMIXX</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Take Me Back (Leave Me There)</v>
+        <v>LEMONADE (feat. Becky G)</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/take-me-back-leave-me-there/1892466278</v>
+        <v>https://music.apple.com/us/song/lemonade-feat-becky-g/1893742425</v>
       </c>
       <c r="D133" t="str">
         <v>2026-06-01</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Banks Of The Trinity</v>
+        <v>LEMONADE - The 2nd Album</v>
       </c>
       <c r="G133" t="str">
-        <v>2:58</v>
+        <v>3:07</v>
       </c>
       <c r="H133" t="str">
-        <v>Cody Johnson</v>
+        <v>aespa</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
+        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/take-me-back-leave-me-there/1892465981</v>
+        <v>https://music.apple.com/us/album/lemonade-feat-becky-g/1893742002</v>
       </c>
       <c r="L133" t="str">
-        <v>Take Me Back (Leave Me There) - Cody Johnson</v>
+        <v>LEMONADE (feat. Becky G) - aespa</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Cheap Thrills</v>
+        <v>Take Me Back (Leave Me There)</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/cheap-thrills/6771156732</v>
+        <v>https://music.apple.com/us/song/take-me-back-leave-me-there/1892466278</v>
       </c>
       <c r="D134" t="str">
         <v>2026-06-01</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Cheap Thrills - Single</v>
+        <v>Banks Of The Trinity</v>
       </c>
       <c r="G134" t="str">
-        <v>2:42</v>
+        <v>2:58</v>
       </c>
       <c r="H134" t="str">
-        <v>Gavin Adcock</v>
+        <v>Cody Johnson</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/gavin-adcock/1580645019</v>
+        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/cheap-thrills/6771156723</v>
+        <v>https://music.apple.com/us/album/take-me-back-leave-me-there/1892465981</v>
       </c>
       <c r="L134" t="str">
-        <v>Cheap Thrills - Gavin Adcock</v>
+        <v>Take Me Back (Leave Me There) - Cody Johnson</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>ME VALE V</v>
+        <v>Cheap Thrills</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/me-vale-v/6769567844</v>
+        <v>https://music.apple.com/us/song/cheap-thrills/6771156732</v>
       </c>
       <c r="D135" t="str">
         <v>2026-06-01</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>ACOMODO</v>
+        <v>Cheap Thrills - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>3:06</v>
+        <v>2:42</v>
       </c>
       <c r="H135" t="str">
-        <v>Tito Double P</v>
+        <v>Gavin Adcock</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/tito-double-p/1690905306</v>
+        <v>https://music.apple.com/us/artist/gavin-adcock/1580645019</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/me-vale-v/6769567568</v>
+        <v>https://music.apple.com/us/album/cheap-thrills/6771156723</v>
       </c>
       <c r="L135" t="str">
-        <v>ME VALE V - Tito Double P</v>
+        <v>Cheap Thrills - Gavin Adcock</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Bug In The Cake</v>
+        <v>ME VALE V</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/bug-in-the-cake/1880470542</v>
+        <v>https://music.apple.com/us/song/me-vale-v/6769567844</v>
       </c>
       <c r="D136" t="str">
         <v>2026-06-01</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Be Sweet To Me</v>
+        <v>ACOMODO</v>
       </c>
       <c r="G136" t="str">
-        <v>2:48</v>
+        <v>3:06</v>
       </c>
       <c r="H136" t="str">
-        <v>Violet Grohl</v>
+        <v>Tito Double P</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
+        <v>https://music.apple.com/us/artist/tito-double-p/1690905306</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/bug-in-the-cake/1880470537</v>
+        <v>https://music.apple.com/us/album/me-vale-v/6769567568</v>
       </c>
       <c r="L136" t="str">
-        <v>Bug In The Cake - Violet Grohl</v>
+        <v>ME VALE V - Tito Double P</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Coil</v>
+        <v>Bug In The Cake</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/coil/6766858354</v>
+        <v>https://music.apple.com/us/song/bug-in-the-cake/1880470542</v>
       </c>
       <c r="D137" t="str">
         <v>2026-06-01</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Rumspringa</v>
+        <v>Be Sweet To Me</v>
       </c>
       <c r="G137" t="str">
-        <v>3:54</v>
+        <v>2:48</v>
       </c>
       <c r="H137" t="str">
-        <v>ear</v>
+        <v>Violet Grohl</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/ear/1829661500</v>
+        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/coil/6766858352</v>
+        <v>https://music.apple.com/us/album/bug-in-the-cake/1880470537</v>
       </c>
       <c r="L137" t="str">
-        <v>Coil - ear</v>
+        <v>Bug In The Cake - Violet Grohl</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Smugglers &amp; Scholars (feat. Killer Mike)</v>
+        <v>Coil</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/smugglers-scholars-feat-killer-mike/6769424017</v>
+        <v>https://music.apple.com/us/song/coil/6766858354</v>
       </c>
       <c r="D138" t="str">
         <v>2026-06-01</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Smugglers &amp; Scholars (feat. Killer Mike) - Single</v>
+        <v>Rumspringa</v>
       </c>
       <c r="G138" t="str">
-        <v>3:30</v>
+        <v>3:54</v>
       </c>
       <c r="H138" t="str">
-        <v>Kneecap</v>
+        <v>ear</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
+        <v>https://music.apple.com/us/artist/ear/1829661500</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/smugglers-scholars-feat-killer-mike/6769423676</v>
+        <v>https://music.apple.com/us/album/coil/6766858352</v>
       </c>
       <c r="L138" t="str">
-        <v>Smugglers &amp; Scholars (feat. Killer Mike) - Kneecap</v>
+        <v>Coil - ear</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Out of my Head</v>
+        <v>Smugglers &amp; Scholars (feat. Killer Mike)</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/out-of-my-head/6767725166</v>
+        <v>https://music.apple.com/us/song/smugglers-scholars-feat-killer-mike/6769424017</v>
       </c>
       <c r="D139" t="str">
         <v>2026-06-01</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>I Forgot / Out of my Head - Single</v>
+        <v>Smugglers &amp; Scholars (feat. Killer Mike) - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>3:04</v>
+        <v>3:30</v>
       </c>
       <c r="H139" t="str">
-        <v>Cara Delevingne</v>
+        <v>Kneecap</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/cara-delevingne/1204798982</v>
+        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/out-of-my-head/6767725156</v>
+        <v>https://music.apple.com/us/album/smugglers-scholars-feat-killer-mike/6769423676</v>
       </c>
       <c r="L139" t="str">
-        <v>Out of my Head - Cara Delevingne</v>
+        <v>Smugglers &amp; Scholars (feat. Killer Mike) - Kneecap</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Passenger Princess</v>
+        <v>Out of my Head</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/passenger-princess/6771012228</v>
+        <v>https://music.apple.com/us/song/out-of-my-head/6767725166</v>
       </c>
       <c r="D140" t="str">
         <v>2026-06-01</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Passenger Princess - Single</v>
+        <v>I Forgot / Out of my Head - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>3:18</v>
+        <v>3:04</v>
       </c>
       <c r="H140" t="str">
-        <v>Perrie</v>
+        <v>Cara Delevingne</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/perrie/1729865272</v>
+        <v>https://music.apple.com/us/artist/cara-delevingne/1204798982</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/passenger-princess/6771012223</v>
+        <v>https://music.apple.com/us/album/out-of-my-head/6767725156</v>
       </c>
       <c r="L140" t="str">
-        <v>Passenger Princess - Perrie</v>
+        <v>Out of my Head - Cara Delevingne</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Man of the House</v>
+        <v>Passenger Princess</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/man-of-the-house/1893733057</v>
+        <v>https://music.apple.com/us/song/passenger-princess/6771012228</v>
       </c>
       <c r="D141" t="str">
         <v>2026-06-01</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>SE9</v>
+        <v>Passenger Princess - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>2:35</v>
+        <v>3:18</v>
       </c>
       <c r="H141" t="str">
-        <v>Skye Newman</v>
+        <v>Perrie</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/skye-newman/1799174381</v>
+        <v>https://music.apple.com/us/artist/perrie/1729865272</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/man-of-the-house/1893733056</v>
+        <v>https://music.apple.com/us/album/passenger-princess/6771012223</v>
       </c>
       <c r="L141" t="str">
-        <v>Man of the House - Skye Newman</v>
+        <v>Passenger Princess - Perrie</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Beautiful Freeks</v>
+        <v>Man of the House</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/beautiful-freeks/6764602396</v>
+        <v>https://music.apple.com/us/song/man-of-the-house/1893733057</v>
       </c>
       <c r="D142" t="str">
         <v>2026-06-01</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Beautiful Freeks - Single</v>
+        <v>SE9</v>
       </c>
       <c r="G142" t="str">
-        <v>2:37</v>
+        <v>2:35</v>
       </c>
       <c r="H142" t="str">
-        <v>MEEK</v>
+        <v>Skye Newman</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/meek/1784432868</v>
+        <v>https://music.apple.com/us/artist/skye-newman/1799174381</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/beautiful-freeks/6764602393</v>
+        <v>https://music.apple.com/us/album/man-of-the-house/1893733056</v>
       </c>
       <c r="L142" t="str">
-        <v>Beautiful Freeks - MEEK</v>
+        <v>Man of the House - Skye Newman</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Slave to the Rithm (feat. Bring Me The Horizon) [I Hate Models Never Alone Remix]</v>
+        <v>Beautiful Freeks</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/slave-to-the-rithm-feat-bring-me-the-horizon-i/6771972616</v>
+        <v>https://music.apple.com/us/song/beautiful-freeks/6764602396</v>
       </c>
       <c r="D143" t="str">
         <v>2026-06-01</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Slave to the Rithm (I Hate Models Never Alone Remix) [feat. Bring Me The Horizon] - Single</v>
+        <v>Beautiful Freeks - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>4:34</v>
+        <v>2:37</v>
       </c>
       <c r="H143" t="str">
-        <v>ILLENIUM</v>
+        <v>MEEK</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/illenium/645420096</v>
+        <v>https://music.apple.com/us/artist/meek/1784432868</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/slave-to-the-rithm-feat-bring-me-the-horizon-i/6771972613</v>
+        <v>https://music.apple.com/us/album/beautiful-freeks/6764602393</v>
       </c>
       <c r="L143" t="str">
-        <v>Slave to the Rithm (feat. Bring Me The Horizon) [I Hate Models Never Alone Remix] - ILLENIUM</v>
+        <v>Beautiful Freeks - MEEK</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Beg For Me (JADE Remix)</v>
+        <v>Slave to the Rithm (feat. Bring Me The Horizon) [I Hate Models Never Alone Remix]</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/beg-for-me-jade-remix/6771474203</v>
+        <v>https://music.apple.com/us/song/slave-to-the-rithm-feat-bring-me-the-horizon-i/6771972616</v>
       </c>
       <c r="D144" t="str">
         <v>2026-06-01</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Beg For Me (Remix) - Single</v>
+        <v>Slave to the Rithm (I Hate Models Never Alone Remix) [feat. Bring Me The Horizon] - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>2:50</v>
+        <v>4:34</v>
       </c>
       <c r="H144" t="str">
-        <v>Lily Allen</v>
+        <v>ILLENIUM</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/lily-allen/157063999</v>
+        <v>https://music.apple.com/us/artist/illenium/645420096</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/beg-for-me-jade-remix/6771474201</v>
+        <v>https://music.apple.com/us/album/slave-to-the-rithm-feat-bring-me-the-horizon-i/6771972613</v>
       </c>
       <c r="L144" t="str">
-        <v>Beg For Me (JADE Remix) - Lily Allen</v>
+        <v>Slave to the Rithm (feat. Bring Me The Horizon) [I Hate Models Never Alone Remix] - ILLENIUM</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>ABOVE IT</v>
+        <v>Beg For Me (JADE Remix)</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/above-it/6766248703</v>
+        <v>https://music.apple.com/us/song/beg-for-me-jade-remix/6771474203</v>
       </c>
       <c r="D145" t="str">
         <v>2026-06-01</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>GET THE TABLES - Single</v>
+        <v>Beg For Me (Remix) - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>1:45</v>
+        <v>2:50</v>
       </c>
       <c r="H145" t="str">
-        <v>Andy Mineo</v>
+        <v>Lily Allen</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/andy-mineo/257538441</v>
+        <v>https://music.apple.com/us/artist/lily-allen/157063999</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/above-it/6766248699</v>
+        <v>https://music.apple.com/us/album/beg-for-me-jade-remix/6771474201</v>
       </c>
       <c r="L145" t="str">
-        <v>ABOVE IT - Andy Mineo</v>
+        <v>Beg For Me (JADE Remix) - Lily Allen</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>THE JESUS GENERATION</v>
+        <v>ABOVE IT</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/the-jesus-generation/6773948895</v>
+        <v>https://music.apple.com/us/song/above-it/6766248703</v>
       </c>
       <c r="D146" t="str">
         <v>2026-06-01</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>THE JESUS GENERATION - Single</v>
+        <v>GET THE TABLES - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>4:15</v>
+        <v>1:45</v>
       </c>
       <c r="H146" t="str">
-        <v>Forrest Frank</v>
+        <v>Andy Mineo</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/forrest-frank/1436657314</v>
+        <v>https://music.apple.com/us/artist/andy-mineo/257538441</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/the-jesus-generation/6773948742</v>
+        <v>https://music.apple.com/us/album/above-it/6766248699</v>
       </c>
       <c r="L146" t="str">
-        <v>THE JESUS GENERATION - Forrest Frank</v>
+        <v>ABOVE IT - Andy Mineo</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Is It Over Now?</v>
+        <v>THE JESUS GENERATION</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/is-it-over-now/6767564750</v>
+        <v>https://music.apple.com/us/song/the-jesus-generation/6773948895</v>
       </c>
       <c r="D147" t="str">
         <v>2026-06-01</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Is It Over Now? - Single</v>
+        <v>THE JESUS GENERATION - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>3:39</v>
+        <v>4:15</v>
       </c>
       <c r="H147" t="str">
-        <v>Elderbrook</v>
+        <v>Forrest Frank</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/elderbrook/736829657</v>
+        <v>https://music.apple.com/us/artist/forrest-frank/1436657314</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/is-it-over-now/6767564746</v>
+        <v>https://music.apple.com/us/album/the-jesus-generation/6773948742</v>
       </c>
       <c r="L147" t="str">
-        <v>Is It Over Now? - Elderbrook</v>
+        <v>THE JESUS GENERATION - Forrest Frank</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>12 Steps</v>
+        <v>Is It Over Now?</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/12-steps/6769559623</v>
+        <v>https://music.apple.com/us/song/is-it-over-now/6767564750</v>
       </c>
       <c r="D148" t="str">
         <v>2026-06-01</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>12 Steps - Single</v>
+        <v>Is It Over Now? - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>3:11</v>
+        <v>3:39</v>
       </c>
       <c r="H148" t="str">
-        <v>Dexter and The Moonrocks</v>
+        <v>Elderbrook</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/dexter-and-the-moonrocks/1581657500</v>
+        <v>https://music.apple.com/us/artist/elderbrook/736829657</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/12-steps/6769559618</v>
+        <v>https://music.apple.com/us/album/is-it-over-now/6767564746</v>
       </c>
       <c r="L148" t="str">
-        <v>12 Steps - Dexter and The Moonrocks</v>
+        <v>Is It Over Now? - Elderbrook</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Over And Over</v>
+        <v>12 Steps</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/over-and-over/6771585908</v>
+        <v>https://music.apple.com/us/song/12-steps/6769559623</v>
       </c>
       <c r="D149" t="str">
         <v>2026-06-01</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>It's A Dying Art</v>
+        <v>12 Steps - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>4:38</v>
+        <v>3:11</v>
       </c>
       <c r="H149" t="str">
-        <v>Little Big Town</v>
+        <v>Dexter and The Moonrocks</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/little-big-town/513770</v>
+        <v>https://music.apple.com/us/artist/dexter-and-the-moonrocks/1581657500</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/over-and-over/6771585889</v>
+        <v>https://music.apple.com/us/album/12-steps/6769559618</v>
       </c>
       <c r="L149" t="str">
-        <v>Over And Over - Little Big Town</v>
+        <v>12 Steps - Dexter and The Moonrocks</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>AMAPOLA</v>
+        <v>Over And Over</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/amapola/6769560428</v>
+        <v>https://music.apple.com/us/song/over-and-over/6771585908</v>
       </c>
       <c r="D150" t="str">
         <v>2026-06-01</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Ricky y Mau</v>
+        <v>It's A Dying Art</v>
       </c>
       <c r="G150" t="str">
-        <v>2:22</v>
+        <v>4:38</v>
       </c>
       <c r="H150" t="str">
-        <v>Mau y Ricky</v>
+        <v>Little Big Town</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/mau-y-ricky/1096068683</v>
+        <v>https://music.apple.com/us/artist/little-big-town/513770</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/amapola/6769559985</v>
+        <v>https://music.apple.com/us/album/over-and-over/6771585889</v>
       </c>
       <c r="L150" t="str">
-        <v>AMAPOLA - Mau y Ricky</v>
+        <v>Over And Over - Little Big Town</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Mad About It</v>
+        <v>AMAPOLA</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/mad-about-it/6767425272</v>
+        <v>https://music.apple.com/us/song/amapola/6769560428</v>
       </c>
       <c r="D151" t="str">
         <v>2026-06-01</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Mad About It - Single</v>
+        <v>Ricky y Mau</v>
       </c>
       <c r="G151" t="str">
-        <v>2:37</v>
+        <v>2:22</v>
       </c>
       <c r="H151" t="str">
-        <v>Dasha</v>
+        <v>Mau y Ricky</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/dasha/1462663731</v>
+        <v>https://music.apple.com/us/artist/mau-y-ricky/1096068683</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/mad-about-it/6767425271</v>
+        <v>https://music.apple.com/us/album/amapola/6769559985</v>
       </c>
       <c r="L151" t="str">
-        <v>Mad About It - Dasha</v>
+        <v>AMAPOLA - Mau y Ricky</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Love’s a Gun</v>
+        <v>Mad About It</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/loves-a-gun/6771898253</v>
+        <v>https://music.apple.com/us/song/mad-about-it/6767425272</v>
       </c>
       <c r="D152" t="str">
         <v>2026-06-01</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Love’s a Gun - Single</v>
+        <v>Mad About It - Single</v>
       </c>
       <c r="G152" t="str">
-        <v>2:59</v>
+        <v>2:37</v>
       </c>
       <c r="H152" t="str">
-        <v>Daniel Seavey</v>
+        <v>Dasha</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/daniel-seavey/1646124302</v>
+        <v>https://music.apple.com/us/artist/dasha/1462663731</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/loves-a-gun/6771897951</v>
+        <v>https://music.apple.com/us/album/mad-about-it/6767425271</v>
       </c>
       <c r="L152" t="str">
-        <v>Love’s a Gun - Daniel Seavey</v>
+        <v>Mad About It - Dasha</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Long Story Short</v>
+        <v>Love’s a Gun</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/long-story-short/6770700866</v>
+        <v>https://music.apple.com/us/song/loves-a-gun/6771898253</v>
       </c>
       <c r="D153" t="str">
         <v>2026-06-01</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Long Story Short - Single</v>
+        <v>Love’s a Gun - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>2:48</v>
+        <v>2:59</v>
       </c>
       <c r="H153" t="str">
-        <v>Knox</v>
+        <v>Daniel Seavey</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/knox/1547519433</v>
+        <v>https://music.apple.com/us/artist/daniel-seavey/1646124302</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/long-story-short/6770700853</v>
+        <v>https://music.apple.com/us/album/loves-a-gun/6771897951</v>
       </c>
       <c r="L153" t="str">
-        <v>Long Story Short - Knox</v>
+        <v>Love’s a Gun - Daniel Seavey</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>blue jeans</v>
+        <v>Long Story Short</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/blue-jeans/6770529591</v>
+        <v>https://music.apple.com/us/song/long-story-short/6770700866</v>
       </c>
       <c r="D154" t="str">
         <v>2026-06-01</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>blue jeans - Single</v>
+        <v>Long Story Short - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>2:37</v>
+        <v>2:48</v>
       </c>
       <c r="H154" t="str">
-        <v>Nightly</v>
+        <v>Knox</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/nightly/352310972</v>
+        <v>https://music.apple.com/us/artist/knox/1547519433</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/blue-jeans/6770529589</v>
+        <v>https://music.apple.com/us/album/long-story-short/6770700853</v>
       </c>
       <c r="L154" t="str">
-        <v>blue jeans - Nightly</v>
+        <v>Long Story Short - Knox</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Que Gacho</v>
+        <v>blue jeans</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/que-gacho/6770628420</v>
+        <v>https://music.apple.com/us/song/blue-jeans/6770529591</v>
       </c>
       <c r="D155" t="str">
         <v>2026-06-01</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Que Gacho - Single</v>
+        <v>blue jeans - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>3:13</v>
+        <v>2:37</v>
       </c>
       <c r="H155" t="str">
-        <v>Luis R Conriquez</v>
+        <v>Nightly</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
+        <v>https://music.apple.com/us/artist/nightly/352310972</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/que-gacho/6770628419</v>
+        <v>https://music.apple.com/us/album/blue-jeans/6770529589</v>
       </c>
       <c r="L155" t="str">
-        <v>Que Gacho - Luis R Conriquez</v>
+        <v>blue jeans - Nightly</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>same God</v>
+        <v>Que Gacho</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/same-god/1878232616</v>
+        <v>https://music.apple.com/us/song/que-gacho/6770628420</v>
       </c>
       <c r="D156" t="str">
         <v>2026-06-01</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>I HOPE THIS HELPS</v>
+        <v>Que Gacho - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>3:34</v>
+        <v>3:13</v>
       </c>
       <c r="H156" t="str">
-        <v>Alana Springsteen</v>
+        <v>Luis R Conriquez</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/alana-springsteen/1309335606</v>
+        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/same-god/1878232194</v>
+        <v>https://music.apple.com/us/album/que-gacho/6770628419</v>
       </c>
       <c r="L156" t="str">
-        <v>same God - Alana Springsteen</v>
+        <v>Que Gacho - Luis R Conriquez</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>emotional swaggage</v>
+        <v>same God</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/emotional-swaggage/6767397453</v>
+        <v>https://music.apple.com/us/song/same-god/1878232616</v>
       </c>
       <c r="D157" t="str">
         <v>2026-06-01</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>IDCASH</v>
+        <v>I HOPE THIS HELPS</v>
       </c>
       <c r="G157" t="str">
-        <v>2:12</v>
+        <v>3:34</v>
       </c>
       <c r="H157" t="str">
-        <v>IDK</v>
+        <v>Alana Springsteen</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/idk/1578186947</v>
+        <v>https://music.apple.com/us/artist/alana-springsteen/1309335606</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/emotional-swaggage/6767397348</v>
+        <v>https://music.apple.com/us/album/same-god/1878232194</v>
       </c>
       <c r="L157" t="str">
-        <v>emotional swaggage - IDK</v>
+        <v>same God - Alana Springsteen</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Baby Driver</v>
+        <v>emotional swaggage</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/baby-driver/6769152279</v>
+        <v>https://music.apple.com/us/song/emotional-swaggage/6767397453</v>
       </c>
       <c r="D158" t="str">
         <v>2026-06-01</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Baby Driver - Single</v>
+        <v>IDCASH</v>
       </c>
       <c r="G158" t="str">
-        <v>3:36</v>
+        <v>2:12</v>
       </c>
       <c r="H158" t="str">
-        <v>070 Shake</v>
+        <v>IDK</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/070-shake/1097177293</v>
+        <v>https://music.apple.com/us/artist/idk/1578186947</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/baby-driver/6769152273</v>
+        <v>https://music.apple.com/us/album/emotional-swaggage/6767397348</v>
       </c>
       <c r="L158" t="str">
-        <v>Baby Driver - 070 Shake</v>
+        <v>emotional swaggage - IDK</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>More! More! More!</v>
+        <v>Baby Driver</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/more-more-more/6770600105</v>
+        <v>https://music.apple.com/us/song/baby-driver/6769152279</v>
       </c>
       <c r="D159" t="str">
         <v>2026-06-01</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>REBECCA</v>
+        <v>Baby Driver - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>2:55</v>
+        <v>3:36</v>
       </c>
       <c r="H159" t="str">
-        <v>Becky Hill</v>
+        <v>070 Shake</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/becky-hill/533839517</v>
+        <v>https://music.apple.com/us/artist/070-shake/1097177293</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/more-more-more/6770600098</v>
+        <v>https://music.apple.com/us/album/baby-driver/6769152273</v>
       </c>
       <c r="L159" t="str">
-        <v>More! More! More! - Becky Hill</v>
+        <v>Baby Driver - 070 Shake</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Young Again</v>
+        <v>More! More! More!</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/young-again/1877229743</v>
+        <v>https://music.apple.com/us/song/more-more-more/6770600105</v>
       </c>
       <c r="D160" t="str">
         <v>2026-06-01</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>EI8HT</v>
+        <v>REBECCA</v>
       </c>
       <c r="G160" t="str">
-        <v>3:36</v>
+        <v>2:55</v>
       </c>
       <c r="H160" t="str">
-        <v>Shinedown</v>
+        <v>Becky Hill</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/shinedown/1883858</v>
+        <v>https://music.apple.com/us/artist/becky-hill/533839517</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/young-again/1877229738</v>
+        <v>https://music.apple.com/us/album/more-more-more/6770600098</v>
       </c>
       <c r="L160" t="str">
-        <v>Young Again - Shinedown</v>
+        <v>More! More! More! - Becky Hill</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>skinny dip</v>
+        <v>Young Again</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/skinny-dip/6769856281</v>
+        <v>https://music.apple.com/us/song/young-again/1877229743</v>
       </c>
       <c r="D161" t="str">
         <v>2026-06-01</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>skinny dip - Single</v>
+        <v>EI8HT</v>
       </c>
       <c r="G161" t="str">
-        <v>3:12</v>
+        <v>3:36</v>
       </c>
       <c r="H161" t="str">
-        <v>almost monday</v>
+        <v>Shinedown</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/almost-monday/1300723925</v>
+        <v>https://music.apple.com/us/artist/shinedown/1883858</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/skinny-dip/6769855907</v>
+        <v>https://music.apple.com/us/album/young-again/1877229738</v>
       </c>
       <c r="L161" t="str">
-        <v>skinny dip - almost monday</v>
+        <v>Young Again - Shinedown</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>girls like girls (from the motion picture)</v>
+        <v>skinny dip</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/girls-like-girls-from-the-motion-picture/1893704575</v>
+        <v>https://music.apple.com/us/song/skinny-dip/6769856281</v>
       </c>
       <c r="D162" t="str">
         <v>2026-06-01</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>girls like girls the album</v>
+        <v>skinny dip - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>4:14</v>
+        <v>3:12</v>
       </c>
       <c r="H162" t="str">
-        <v>Hayley Kiyoko</v>
+        <v>almost monday</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/hayley-kiyoko/325569584</v>
+        <v>https://music.apple.com/us/artist/almost-monday/1300723925</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/girls-like-girls-from-the-motion-picture/1893704396</v>
+        <v>https://music.apple.com/us/album/skinny-dip/6769855907</v>
       </c>
       <c r="L162" t="str">
-        <v>girls like girls (from the motion picture) - Hayley Kiyoko</v>
+        <v>skinny dip - almost monday</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Better Off</v>
+        <v>girls like girls (from the motion picture)</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/better-off/6772045367</v>
+        <v>https://music.apple.com/us/song/girls-like-girls-from-the-motion-picture/1893704575</v>
       </c>
       <c r="D163" t="str">
         <v>2026-06-01</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Stages</v>
+        <v>girls like girls the album</v>
       </c>
       <c r="G163" t="str">
-        <v>3:16</v>
+        <v>4:14</v>
       </c>
       <c r="H163" t="str">
-        <v>Lauren Alaina</v>
+        <v>Hayley Kiyoko</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/lauren-alaina/425028816</v>
+        <v>https://music.apple.com/us/artist/hayley-kiyoko/325569584</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/better-off/6772044978</v>
+        <v>https://music.apple.com/us/album/girls-like-girls-from-the-motion-picture/1893704396</v>
       </c>
       <c r="L163" t="str">
-        <v>Better Off - Lauren Alaina</v>
+        <v>girls like girls (from the motion picture) - Hayley Kiyoko</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Everythang Pinka (feat. Teezo Touchdown)</v>
+        <v>Better Off</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/everythang-pinka-feat-teezo-touchdown/6772026590</v>
+        <v>https://music.apple.com/us/song/better-off/6772045367</v>
       </c>
       <c r="D164" t="str">
         <v>2026-06-01</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Everythang Pinka (feat. Teezo Touchdown) - Single</v>
+        <v>Stages</v>
       </c>
       <c r="G164" t="str">
-        <v>2:48</v>
+        <v>3:16</v>
       </c>
       <c r="H164" t="str">
-        <v>Monaleo</v>
+        <v>Lauren Alaina</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/monaleo/1495603374</v>
+        <v>https://music.apple.com/us/artist/lauren-alaina/425028816</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/everythang-pinka-feat-teezo-touchdown/6772026586</v>
+        <v>https://music.apple.com/us/album/better-off/6772044978</v>
       </c>
       <c r="L164" t="str">
-        <v>Everythang Pinka (feat. Teezo Touchdown) - Monaleo</v>
+        <v>Better Off - Lauren Alaina</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Lost in translation...</v>
+        <v>Everythang Pinka (feat. Teezo Touchdown)</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/lost-in-translation/1870971556</v>
+        <v>https://music.apple.com/us/song/everythang-pinka-feat-teezo-touchdown/6772026590</v>
       </c>
       <c r="D165" t="str">
         <v>2026-06-01</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Dream inside a dream…</v>
+        <v>Everythang Pinka (feat. Teezo Touchdown) - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>3:30</v>
+        <v>2:48</v>
       </c>
       <c r="H165" t="str">
-        <v>R3HAB</v>
+        <v>Monaleo</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/r3hab/331900515</v>
+        <v>https://music.apple.com/us/artist/monaleo/1495603374</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/lost-in-translation/1870971550</v>
+        <v>https://music.apple.com/us/album/everythang-pinka-feat-teezo-touchdown/6772026586</v>
       </c>
       <c r="L165" t="str">
-        <v>Lost in translation... - R3HAB</v>
+        <v>Everythang Pinka (feat. Teezo Touchdown) - Monaleo</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Call Security</v>
+        <v>Lost in translation...</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/call-security/6769296603</v>
+        <v>https://music.apple.com/us/song/lost-in-translation/1870971556</v>
       </c>
       <c r="D166" t="str">
         <v>2026-06-01</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>U, Me &amp; My Ego</v>
+        <v>Dream inside a dream…</v>
       </c>
       <c r="G166" t="str">
-        <v>3:22</v>
+        <v>3:30</v>
       </c>
       <c r="H166" t="str">
-        <v>Chxrry</v>
+        <v>R3HAB</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/chxrry/1520135642</v>
+        <v>https://music.apple.com/us/artist/r3hab/331900515</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/call-security/6769296591</v>
+        <v>https://music.apple.com/us/album/lost-in-translation/1870971550</v>
       </c>
       <c r="L166" t="str">
-        <v>Call Security - Chxrry</v>
+        <v>Lost in translation... - R3HAB</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>chaotic</v>
+        <v>Call Security</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/chaotic/6767629281</v>
+        <v>https://music.apple.com/us/song/call-security/6769296603</v>
       </c>
       <c r="D167" t="str">
         <v>2026-06-01</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>scars to prove it</v>
+        <v>U, Me &amp; My Ego</v>
       </c>
       <c r="G167" t="str">
-        <v>3:14</v>
+        <v>3:22</v>
       </c>
       <c r="H167" t="str">
-        <v>Hailey Picardi</v>
+        <v>Chxrry</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
+        <v>https://music.apple.com/us/artist/chxrry/1520135642</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/chaotic/6767626506</v>
+        <v>https://music.apple.com/us/album/call-security/6769296591</v>
       </c>
       <c r="L167" t="str">
-        <v>chaotic - Hailey Picardi</v>
+        <v>Call Security - Chxrry</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Keep It To Yourself</v>
+        <v>chaotic</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/keep-it-to-yourself/6771099675</v>
+        <v>https://music.apple.com/us/song/chaotic/6767629281</v>
       </c>
       <c r="D168" t="str">
         <v>2026-06-01</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>LOVE IS THE LAW</v>
+        <v>scars to prove it</v>
       </c>
       <c r="G168" t="str">
-        <v>4:17</v>
+        <v>3:14</v>
       </c>
       <c r="H168" t="str">
-        <v>Love Spells</v>
+        <v>Hailey Picardi</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/love-spells/1597025563</v>
+        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/keep-it-to-yourself/6771099661</v>
+        <v>https://music.apple.com/us/album/chaotic/6767626506</v>
       </c>
       <c r="L168" t="str">
-        <v>Keep It To Yourself - Love Spells</v>
+        <v>chaotic - Hailey Picardi</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Something to Someone</v>
+        <v>Keep It To Yourself</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/something-to-someone/6767255424</v>
+        <v>https://music.apple.com/us/song/keep-it-to-yourself/6771099675</v>
       </c>
       <c r="D169" t="str">
         <v>2026-06-01</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Something to Someone - Single</v>
+        <v>LOVE IS THE LAW</v>
       </c>
       <c r="G169" t="str">
-        <v>3:55</v>
+        <v>4:17</v>
       </c>
       <c r="H169" t="str">
-        <v>Max McNown</v>
+        <v>Love Spells</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
+        <v>https://music.apple.com/us/artist/love-spells/1597025563</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/something-to-someone/1896445136</v>
+        <v>https://music.apple.com/us/album/keep-it-to-yourself/6771099661</v>
       </c>
       <c r="L169" t="str">
-        <v>Something to Someone - Max McNown</v>
+        <v>Keep It To Yourself - Love Spells</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Green Screen (1pm)</v>
+        <v>Something to Someone</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/green-screen-1pm/6766279426</v>
+        <v>https://music.apple.com/us/song/something-to-someone/6767255424</v>
       </c>
       <c r="D170" t="str">
         <v>2026-06-01</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>The Hours: High Noon</v>
+        <v>Something to Someone - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>2:10</v>
+        <v>3:55</v>
       </c>
       <c r="H170" t="str">
-        <v>Cautious Clay</v>
+        <v>Max McNown</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/cautious-clay/1064628701</v>
+        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/green-screen-1pm/1896264236</v>
+        <v>https://music.apple.com/us/album/something-to-someone/1896445136</v>
       </c>
       <c r="L170" t="str">
-        <v>Green Screen (1pm) - Cautious Clay</v>
+        <v>Something to Someone - Max McNown</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Scoreboard</v>
+        <v>Green Screen (1pm)</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/scoreboard/6767255746</v>
+        <v>https://music.apple.com/us/song/green-screen-1pm/6766279426</v>
       </c>
       <c r="D171" t="str">
         <v>2026-06-01</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>I Just Wanna Be Loved</v>
+        <v>The Hours: High Noon</v>
       </c>
       <c r="G171" t="str">
-        <v>3:24</v>
+        <v>2:10</v>
       </c>
       <c r="H171" t="str">
-        <v>Gabriella Rose</v>
+        <v>Cautious Clay</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/gabriella-rose/645706232</v>
+        <v>https://music.apple.com/us/artist/cautious-clay/1064628701</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/scoreboard/1896445371</v>
+        <v>https://music.apple.com/us/album/green-screen-1pm/1896264236</v>
       </c>
       <c r="L171" t="str">
-        <v>Scoreboard - Gabriella Rose</v>
+        <v>Green Screen (1pm) - Cautious Clay</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>High</v>
+        <v>Scoreboard</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/high/6773775211</v>
+        <v>https://music.apple.com/us/song/scoreboard/6767255746</v>
       </c>
       <c r="D172" t="str">
         <v>2026-06-01</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Payback Is A Dog (EP)</v>
+        <v>I Just Wanna Be Loved</v>
       </c>
       <c r="G172" t="str">
-        <v>2:55</v>
+        <v>3:24</v>
       </c>
       <c r="H172" t="str">
-        <v>Nia Smith</v>
+        <v>Gabriella Rose</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/nia-smith/1755576018</v>
+        <v>https://music.apple.com/us/artist/gabriella-rose/645706232</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/high/6773775203</v>
+        <v>https://music.apple.com/us/album/scoreboard/1896445371</v>
       </c>
       <c r="L172" t="str">
-        <v>High - Nia Smith</v>
+        <v>Scoreboard - Gabriella Rose</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Ay Gyal</v>
+        <v>High</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/ay-gyal/6771885805</v>
+        <v>https://music.apple.com/us/song/high/6773775211</v>
       </c>
       <c r="D173" t="str">
         <v>2026-06-01</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Ay Gyal - Single</v>
+        <v>Payback Is A Dog (EP)</v>
       </c>
       <c r="G173" t="str">
-        <v>2:12</v>
+        <v>2:55</v>
       </c>
       <c r="H173" t="str">
-        <v>1Ski OG</v>
+        <v>Nia Smith</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
+        <v>https://music.apple.com/us/artist/nia-smith/1755576018</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/ay-gyal/6771885803</v>
+        <v>https://music.apple.com/us/album/high/6773775203</v>
       </c>
       <c r="L173" t="str">
-        <v>Ay Gyal - 1Ski OG</v>
+        <v>High - Nia Smith</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>always knew</v>
+        <v>Ay Gyal</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/always-knew/6762864274</v>
+        <v>https://music.apple.com/us/song/ay-gyal/6771885805</v>
       </c>
       <c r="D174" t="str">
         <v>2026-06-01</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>always knew - Single</v>
+        <v>Ay Gyal - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>3:25</v>
+        <v>2:12</v>
       </c>
       <c r="H174" t="str">
-        <v>Biscits</v>
+        <v>1Ski OG</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/biscits/1185553226</v>
+        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/always-knew/1895047928</v>
+        <v>https://music.apple.com/us/album/ay-gyal/6771885803</v>
       </c>
       <c r="L174" t="str">
-        <v>always knew - Biscits</v>
+        <v>Ay Gyal - 1Ski OG</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Cigarette Burns</v>
+        <v>always knew</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/cigarette-burns/6770691000</v>
+        <v>https://music.apple.com/us/song/always-knew/6762864274</v>
       </c>
       <c r="D175" t="str">
         <v>2026-06-01</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Heartland Rock and Roll</v>
+        <v>always knew - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>2:41</v>
+        <v>3:25</v>
       </c>
       <c r="H175" t="str">
-        <v>Corey Kent</v>
+        <v>Biscits</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/corey-kent/1171544097</v>
+        <v>https://music.apple.com/us/artist/biscits/1185553226</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/cigarette-burns/6770690867</v>
+        <v>https://music.apple.com/us/album/always-knew/1895047928</v>
       </c>
       <c r="L175" t="str">
-        <v>Cigarette Burns - Corey Kent</v>
+        <v>always knew - Biscits</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Let You Down</v>
+        <v>Cigarette Burns</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/let-you-down/6773362320</v>
+        <v>https://music.apple.com/us/song/cigarette-burns/6770691000</v>
       </c>
       <c r="D176" t="str">
         <v>2026-06-01</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>El Relevo</v>
+        <v>Heartland Rock and Roll</v>
       </c>
       <c r="G176" t="str">
-        <v>4:14</v>
+        <v>2:41</v>
       </c>
       <c r="H176" t="str">
-        <v>Luis Figueroa</v>
+        <v>Corey Kent</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/luis-figueroa/395266944</v>
+        <v>https://music.apple.com/us/artist/corey-kent/1171544097</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/let-you-down/6773362108</v>
+        <v>https://music.apple.com/us/album/cigarette-burns/6770690867</v>
       </c>
       <c r="L176" t="str">
-        <v>Let You Down - Luis Figueroa</v>
+        <v>Cigarette Burns - Corey Kent</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Starless</v>
+        <v>Let You Down</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/starless/6770568779</v>
+        <v>https://music.apple.com/us/song/let-you-down/6773362320</v>
       </c>
       <c r="D177" t="str">
         <v>2026-06-01</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Starless - Single</v>
+        <v>El Relevo</v>
       </c>
       <c r="G177" t="str">
-        <v>4:32</v>
+        <v>4:14</v>
       </c>
       <c r="H177" t="str">
-        <v>A Perfect Circle</v>
+        <v>Luis Figueroa</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/a-perfect-circle/652503</v>
+        <v>https://music.apple.com/us/artist/luis-figueroa/395266944</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/starless/6770568776</v>
+        <v>https://music.apple.com/us/album/let-you-down/6773362108</v>
       </c>
       <c r="L177" t="str">
-        <v>Starless - A Perfect Circle</v>
+        <v>Let You Down - Luis Figueroa</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Looking For You</v>
+        <v>Starless</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/looking-for-you/6768355609</v>
+        <v>https://music.apple.com/us/song/starless/6770568779</v>
       </c>
       <c r="D178" t="str">
         <v>2026-06-01</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Looking For You - Single</v>
+        <v>Starless - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>3:19</v>
+        <v>4:32</v>
       </c>
       <c r="H178" t="str">
-        <v>Gable Price and Friends</v>
+        <v>A Perfect Circle</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/gable-price-and-friends/1441378212</v>
+        <v>https://music.apple.com/us/artist/a-perfect-circle/652503</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/looking-for-you/6768355596</v>
+        <v>https://music.apple.com/us/album/starless/6770568776</v>
       </c>
       <c r="L178" t="str">
-        <v>Looking For You - Gable Price and Friends</v>
+        <v>Starless - A Perfect Circle</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>FOCUSED</v>
+        <v>Looking For You</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/focused/1887909237</v>
+        <v>https://music.apple.com/us/song/looking-for-you/6768355609</v>
       </c>
       <c r="D179" t="str">
         <v>2026-06-01</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>FOCUSED - Single</v>
+        <v>Looking For You - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>2:23</v>
+        <v>3:19</v>
       </c>
       <c r="H179" t="str">
-        <v>Shepherd</v>
+        <v>Gable Price and Friends</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/shepherd/1192803216</v>
+        <v>https://music.apple.com/us/artist/gable-price-and-friends/1441378212</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/focused/1887909236</v>
+        <v>https://music.apple.com/us/album/looking-for-you/6768355596</v>
       </c>
       <c r="L179" t="str">
-        <v>FOCUSED - Shepherd</v>
+        <v>Looking For You - Gable Price and Friends</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Tú Ni En Cuenta</v>
+        <v>FOCUSED</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/tu-ni-en-cuenta/6767701804</v>
+        <v>https://music.apple.com/us/song/focused/1887909237</v>
       </c>
       <c r="D180" t="str">
         <v>2026-06-01</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Tú Ni En Cuenta - Single</v>
+        <v>FOCUSED - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>3:23</v>
+        <v>2:23</v>
       </c>
       <c r="H180" t="str">
-        <v>Banda MS de Sergio Lizárraga</v>
+        <v>Shepherd</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/banda-ms-de-sergio-liz%C3%A1rraga/413048014</v>
+        <v>https://music.apple.com/us/artist/shepherd/1192803216</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/tu-ni-en-cuenta/6767701803</v>
+        <v>https://music.apple.com/us/album/focused/1887909236</v>
       </c>
       <c r="L180" t="str">
-        <v>Tú Ni En Cuenta - Banda MS de Sergio Lizárraga</v>
+        <v>FOCUSED - Shepherd</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>dream state</v>
+        <v>Tú Ni En Cuenta</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/dream-state/6765596009</v>
+        <v>https://music.apple.com/us/song/tu-ni-en-cuenta/6767701804</v>
       </c>
       <c r="D181" t="str">
         <v>2026-06-01</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>dream state - Single</v>
+        <v>Tú Ni En Cuenta - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>4:01</v>
+        <v>3:23</v>
       </c>
       <c r="H181" t="str">
-        <v>Martin Luke Brown</v>
+        <v>Banda MS de Sergio Lizárraga</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/martin-luke-brown/883292185</v>
+        <v>https://music.apple.com/us/artist/banda-ms-de-sergio-liz%C3%A1rraga/413048014</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/dream-state/1896004790</v>
+        <v>https://music.apple.com/us/album/tu-ni-en-cuenta/6767701803</v>
       </c>
       <c r="L181" t="str">
-        <v>dream state - Martin Luke Brown</v>
+        <v>Tú Ni En Cuenta - Banda MS de Sergio Lizárraga</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Needle (feat. Spencer Cullum)</v>
+        <v>dream state</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/needle-feat-spencer-cullum/6767618217</v>
+        <v>https://music.apple.com/us/song/dream-state/6765596009</v>
       </c>
       <c r="D182" t="str">
         <v>2026-06-01</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Needle (feat. Spencer Cullum) - Single</v>
+        <v>dream state - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>3:39</v>
+        <v>4:01</v>
       </c>
       <c r="H182" t="str">
-        <v>Mynolia</v>
+        <v>Martin Luke Brown</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/mynolia/1444347510</v>
+        <v>https://music.apple.com/us/artist/martin-luke-brown/883292185</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/needle-feat-spencer-cullum/6767618203</v>
+        <v>https://music.apple.com/us/album/dream-state/1896004790</v>
       </c>
       <c r="L182" t="str">
-        <v>Needle (feat. Spencer Cullum) - Mynolia</v>
+        <v>dream state - Martin Luke Brown</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>You Retreat In Time And Space</v>
+        <v>Needle (feat. Spencer Cullum)</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/you-retreat-in-time-and-space/1890015660</v>
+        <v>https://music.apple.com/us/song/needle-feat-spencer-cullum/6767618217</v>
       </c>
       <c r="D183" t="str">
         <v>2026-06-01</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Inferno</v>
+        <v>Needle (feat. Spencer Cullum) - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>5:25</v>
+        <v>3:39</v>
       </c>
       <c r="H183" t="str">
-        <v>Boards of Canada</v>
+        <v>Mynolia</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/boards-of-canada/2989314</v>
+        <v>https://music.apple.com/us/artist/mynolia/1444347510</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/you-retreat-in-time-and-space/1890015523</v>
+        <v>https://music.apple.com/us/album/needle-feat-spencer-cullum/6767618203</v>
       </c>
       <c r="L183" t="str">
-        <v>You Retreat In Time And Space - Boards of Canada</v>
+        <v>Needle (feat. Spencer Cullum) - Mynolia</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>It's Happening (To Me)</v>
+        <v>You Retreat In Time And Space</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/its-happening-to-me/6764723461</v>
+        <v>https://music.apple.com/us/song/you-retreat-in-time-and-space/1890015660</v>
       </c>
       <c r="D184" t="str">
         <v>2026-06-01</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>It's Happening (To Me) - Single</v>
+        <v>Inferno</v>
       </c>
       <c r="G184" t="str">
-        <v>2:34</v>
+        <v>5:25</v>
       </c>
       <c r="H184" t="str">
-        <v>Delroy Edwards</v>
+        <v>Boards of Canada</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/delroy-edwards/591790909</v>
+        <v>https://music.apple.com/us/artist/boards-of-canada/2989314</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/its-happening-to-me/1895893472</v>
+        <v>https://music.apple.com/us/album/you-retreat-in-time-and-space/1890015523</v>
       </c>
       <c r="L184" t="str">
-        <v>It's Happening (To Me) - Delroy Edwards</v>
+        <v>You Retreat In Time And Space - Boards of Canada</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>FCUK</v>
+        <v>It's Happening (To Me)</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/fcuk/6769623577</v>
+        <v>https://music.apple.com/us/song/its-happening-to-me/6764723461</v>
       </c>
       <c r="D185" t="str">
         <v>2026-06-01</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>FCUK - Single</v>
+        <v>It's Happening (To Me) - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>2:22</v>
+        <v>2:34</v>
       </c>
       <c r="H185" t="str">
-        <v>H.LLS</v>
+        <v>Delroy Edwards</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/h-lls/1751287958</v>
+        <v>https://music.apple.com/us/artist/delroy-edwards/591790909</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/fcuk/6769623566</v>
+        <v>https://music.apple.com/us/album/its-happening-to-me/1895893472</v>
       </c>
       <c r="L185" t="str">
-        <v>FCUK - H.LLS</v>
+        <v>It's Happening (To Me) - Delroy Edwards</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Higher</v>
+        <v>FCUK</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/higher/1880124200</v>
+        <v>https://music.apple.com/us/song/fcuk/6769623577</v>
       </c>
       <c r="D186" t="str">
         <v>2026-06-01</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Run, Run Pure Beauty</v>
+        <v>FCUK - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>4:06</v>
+        <v>2:22</v>
       </c>
       <c r="H186" t="str">
-        <v>Francis of Delirium</v>
+        <v>H.LLS</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/francis-of-delirium/1485902996</v>
+        <v>https://music.apple.com/us/artist/h-lls/1751287958</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/higher/1880123731</v>
+        <v>https://music.apple.com/us/album/fcuk/6769623566</v>
       </c>
       <c r="L186" t="str">
-        <v>Higher - Francis of Delirium</v>
+        <v>FCUK - H.LLS</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>B.U.N</v>
+        <v>Higher</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/b-u-n/6763272338</v>
+        <v>https://music.apple.com/us/song/higher/1880124200</v>
       </c>
       <c r="D187" t="str">
         <v>2026-06-01</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>B.U.N - Single</v>
+        <v>Run, Run Pure Beauty</v>
       </c>
       <c r="G187" t="str">
-        <v>3:43</v>
+        <v>4:06</v>
       </c>
       <c r="H187" t="str">
-        <v>Roll Deep</v>
+        <v>Francis of Delirium</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/roll-deep/3083873</v>
+        <v>https://music.apple.com/us/artist/francis-of-delirium/1485902996</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/b-u-n/1895242397</v>
+        <v>https://music.apple.com/us/album/higher/1880123731</v>
       </c>
       <c r="L187" t="str">
-        <v>B.U.N - Roll Deep</v>
+        <v>Higher - Francis of Delirium</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Only Love (feat. Pa Salieu)</v>
+        <v>B.U.N</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/only-love-feat-pa-salieu/6767014290</v>
+        <v>https://music.apple.com/us/song/b-u-n/6763272338</v>
       </c>
       <c r="D188" t="str">
         <v>2026-06-01</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Here Because of Hope</v>
+        <v>B.U.N - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>3:22</v>
+        <v>3:43</v>
       </c>
       <c r="H188" t="str">
-        <v>Ezra Collective</v>
+        <v>Roll Deep</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/ezra-collective/1103640281</v>
+        <v>https://music.apple.com/us/artist/roll-deep/3083873</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/only-love-feat-pa-salieu/6767014278</v>
+        <v>https://music.apple.com/us/album/b-u-n/1895242397</v>
       </c>
       <c r="L188" t="str">
-        <v>Only Love (feat. Pa Salieu) - Ezra Collective</v>
+        <v>B.U.N - Roll Deep</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Beautiful Things 1st scene/audition</v>
+        <v>Only Love (feat. Pa Salieu)</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/beautiful-things-1st-scene-audition/6771942631</v>
+        <v>https://music.apple.com/us/song/only-love-feat-pa-salieu/6767014290</v>
       </c>
       <c r="D189" t="str">
         <v>2026-06-01</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>UNDRA</v>
+        <v>Here Because of Hope</v>
       </c>
       <c r="G189" t="str">
-        <v>2:49</v>
+        <v>3:22</v>
       </c>
       <c r="H189" t="str">
-        <v>reggie</v>
+        <v>Ezra Collective</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/reggie/1526587068</v>
+        <v>https://music.apple.com/us/artist/ezra-collective/1103640281</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/beautiful-things-1st-scene-audition/6771942630</v>
+        <v>https://music.apple.com/us/album/only-love-feat-pa-salieu/6767014278</v>
       </c>
       <c r="L189" t="str">
-        <v>Beautiful Things 1st scene/audition - reggie</v>
+        <v>Only Love (feat. Pa Salieu) - Ezra Collective</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>HEAVEN'S ON FIRE</v>
+        <v>Beautiful Things 1st scene/audition</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/heavens-on-fire/6771110730</v>
+        <v>https://music.apple.com/us/song/beautiful-things-1st-scene-audition/6771942631</v>
       </c>
       <c r="D190" t="str">
         <v>2026-06-01</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>HEAVEN'S ON FIRE</v>
+        <v>UNDRA</v>
       </c>
       <c r="G190" t="str">
-        <v>2:54</v>
+        <v>2:49</v>
       </c>
       <c r="H190" t="str">
-        <v>Johnny Huynh</v>
+        <v>reggie</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/johnny-huynh/1708540956</v>
+        <v>https://music.apple.com/us/artist/reggie/1526587068</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/heavens-on-fire/6771110729</v>
+        <v>https://music.apple.com/us/album/beautiful-things-1st-scene-audition/6771942630</v>
       </c>
       <c r="L190" t="str">
-        <v>HEAVEN'S ON FIRE - Johnny Huynh</v>
+        <v>Beautiful Things 1st scene/audition - reggie</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Fallen Angel</v>
+        <v>HEAVEN'S ON FIRE</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/fallen-angel/6771161222</v>
+        <v>https://music.apple.com/us/song/heavens-on-fire/6771110730</v>
       </c>
       <c r="D191" t="str">
         <v>2026-06-01</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>You Don't Know My Name</v>
+        <v>HEAVEN'S ON FIRE</v>
       </c>
       <c r="G191" t="str">
-        <v>3:05</v>
+        <v>2:54</v>
       </c>
       <c r="H191" t="str">
-        <v>Baby J</v>
+        <v>Johnny Huynh</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/baby-j/1513690931</v>
+        <v>https://music.apple.com/us/artist/johnny-huynh/1708540956</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/fallen-angel/6771161180</v>
+        <v>https://music.apple.com/us/album/heavens-on-fire/6771110729</v>
       </c>
       <c r="L191" t="str">
-        <v>Fallen Angel - Baby J</v>
+        <v>HEAVEN'S ON FIRE - Johnny Huynh</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>The Last Encounter</v>
+        <v>Fallen Angel</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/the-last-encounter/6767395134</v>
+        <v>https://music.apple.com/us/song/fallen-angel/6771161222</v>
       </c>
       <c r="D192" t="str">
         <v>2026-06-01</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>The Last Encounter - Single</v>
+        <v>You Don't Know My Name</v>
       </c>
       <c r="G192" t="str">
-        <v>3:04</v>
+        <v>3:05</v>
       </c>
       <c r="H192" t="str">
-        <v>Sofia Camara</v>
+        <v>Baby J</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/sofia-camara/1506432156</v>
+        <v>https://music.apple.com/us/artist/baby-j/1513690931</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/the-last-encounter/6767395133</v>
+        <v>https://music.apple.com/us/album/fallen-angel/6771161180</v>
       </c>
       <c r="L192" t="str">
-        <v>The Last Encounter - Sofia Camara</v>
+        <v>Fallen Angel - Baby J</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>We Fall</v>
+        <v>The Last Encounter</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/we-fall/6769218917</v>
+        <v>https://music.apple.com/us/song/the-last-encounter/6767395134</v>
       </c>
       <c r="D193" t="str">
         <v>2026-06-01</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>We Fall - Single</v>
+        <v>The Last Encounter - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>4:01</v>
+        <v>3:04</v>
       </c>
       <c r="H193" t="str">
-        <v>MOIO</v>
+        <v>Sofia Camara</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/moio/1664183608</v>
+        <v>https://music.apple.com/us/artist/sofia-camara/1506432156</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/we-fall/6769218915</v>
+        <v>https://music.apple.com/us/album/the-last-encounter/6767395133</v>
       </c>
       <c r="L193" t="str">
-        <v>We Fall - MOIO</v>
+        <v>The Last Encounter - Sofia Camara</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>You Don't Know Me</v>
+        <v>We Fall</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/you-dont-know-me/6769214417</v>
+        <v>https://music.apple.com/us/song/we-fall/6769218917</v>
       </c>
       <c r="D194" t="str">
         <v>2026-06-01</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>You Don’t Know Me - Single</v>
+        <v>We Fall - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>3:50</v>
+        <v>4:01</v>
       </c>
       <c r="H194" t="str">
-        <v>Isabel Dumaa</v>
+        <v>MOIO</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/isabel-dumaa/1631481156</v>
+        <v>https://music.apple.com/us/artist/moio/1664183608</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/you-dont-know-me/6769214410</v>
+        <v>https://music.apple.com/us/album/we-fall/6769218915</v>
       </c>
       <c r="L194" t="str">
-        <v>You Don't Know Me - Isabel Dumaa</v>
+        <v>We Fall - MOIO</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Hold Up, Say What?</v>
+        <v>You Don't Know Me</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/hold-up-say-what/1879853511</v>
+        <v>https://music.apple.com/us/song/you-dont-know-me/6769214417</v>
       </c>
       <c r="D195" t="str">
         <v>2026-06-01</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>House Of Mirrors</v>
+        <v>You Don’t Know Me - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>4:04</v>
+        <v>3:50</v>
       </c>
       <c r="H195" t="str">
-        <v>All Them Witches</v>
+        <v>Isabel Dumaa</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/all-them-witches/534924603</v>
+        <v>https://music.apple.com/us/artist/isabel-dumaa/1631481156</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/hold-up-say-what/1879853502</v>
+        <v>https://music.apple.com/us/album/you-dont-know-me/6769214410</v>
       </c>
       <c r="L195" t="str">
-        <v>Hold Up, Say What? - All Them Witches</v>
+        <v>You Don't Know Me - Isabel Dumaa</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Iodine</v>
+        <v>Hold Up, Say What?</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/iodine/1871211805</v>
+        <v>https://music.apple.com/us/song/hold-up-say-what/1879853511</v>
       </c>
       <c r="D196" t="str">
         <v>2026-06-01</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Neverending</v>
+        <v>House Of Mirrors</v>
       </c>
       <c r="G196" t="str">
-        <v>3:40</v>
+        <v>4:04</v>
       </c>
       <c r="H196" t="str">
-        <v>Monolord</v>
+        <v>All Them Witches</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/monolord/833749384</v>
+        <v>https://music.apple.com/us/artist/all-them-witches/534924603</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/iodine/1871211801</v>
+        <v>https://music.apple.com/us/album/hold-up-say-what/1879853502</v>
       </c>
       <c r="L196" t="str">
-        <v>Iodine - Monolord</v>
+        <v>Hold Up, Say What? - All Them Witches</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>I Speak Forgotten Voices</v>
+        <v>Iodine</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/i-speak-forgotten-voices/1878083625</v>
+        <v>https://music.apple.com/us/song/iodine/1871211805</v>
       </c>
       <c r="D197" t="str">
         <v>2026-06-01</v>
@@ -7861,68 +7861,106 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>...By the Word...</v>
+        <v>Neverending</v>
       </c>
       <c r="G197" t="str">
-        <v>5:01</v>
+        <v>3:40</v>
       </c>
       <c r="H197" t="str">
-        <v>Trelldom</v>
+        <v>Monolord</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/trelldom/256586618</v>
+        <v>https://music.apple.com/us/artist/monolord/833749384</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/i-speak-forgotten-voices/1878083622</v>
+        <v>https://music.apple.com/us/album/iodine/1871211801</v>
       </c>
       <c r="L197" t="str">
-        <v>I Speak Forgotten Voices - Trelldom</v>
+        <v>Iodine - Monolord</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
+        <v>I Speak Forgotten Voices</v>
+      </c>
+      <c r="B198" t="str">
+        <v/>
+      </c>
+      <c r="C198" t="str">
+        <v>https://music.apple.com/us/song/i-speak-forgotten-voices/1878083625</v>
+      </c>
+      <c r="D198" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="E198" t="str">
+        <v/>
+      </c>
+      <c r="F198" t="str">
+        <v>...By the Word...</v>
+      </c>
+      <c r="G198" t="str">
+        <v>5:01</v>
+      </c>
+      <c r="H198" t="str">
+        <v>Trelldom</v>
+      </c>
+      <c r="I198" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J198" t="str">
+        <v>https://music.apple.com/us/artist/trelldom/256586618</v>
+      </c>
+      <c r="K198" t="str">
+        <v>https://music.apple.com/us/album/i-speak-forgotten-voices/1878083622</v>
+      </c>
+      <c r="L198" t="str">
+        <v>I Speak Forgotten Voices - Trelldom</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
         <v>Rats in the Temple</v>
       </c>
-      <c r="B198" t="str">
-        <v/>
-      </c>
-      <c r="C198" t="str">
+      <c r="B199" t="str">
+        <v/>
+      </c>
+      <c r="C199" t="str">
         <v>https://music.apple.com/us/song/rats-in-the-temple/6764627559</v>
       </c>
-      <c r="D198" t="str">
-        <v>2026-06-01</v>
-      </c>
-      <c r="E198" t="str">
-        <v/>
-      </c>
-      <c r="F198" t="str">
+      <c r="D199" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="E199" t="str">
+        <v/>
+      </c>
+      <c r="F199" t="str">
         <v>Rats in the Temple</v>
       </c>
-      <c r="G198" t="str">
+      <c r="G199" t="str">
         <v>4:45</v>
       </c>
-      <c r="H198" t="str">
+      <c r="H199" t="str">
         <v>Flotsam and Jetsam</v>
       </c>
-      <c r="I198" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J198" t="str">
+      <c r="I199" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J199" t="str">
         <v>https://music.apple.com/us/artist/flotsam-and-jetsam/162270</v>
       </c>
-      <c r="K198" t="str">
+      <c r="K199" t="str">
         <v>https://music.apple.com/us/album/rats-in-the-temple/1895855647</v>
       </c>
-      <c r="L198" t="str">
+      <c r="L199" t="str">
         <v>Rats in the Temple - Flotsam and Jetsam</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L198"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L199"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-06-week01/titles.xlsx
+++ b/data/global/2026-06-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L199"/>
+  <dimension ref="A1:L201"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שלומי שבת עמיר בניון – היכן אתה?</v>
+        <v>אלירן בוזגלו - מחרוזת והלב 2026</v>
       </c>
       <c r="B2" t="str">
         <v>2026-06-01</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a9%d7%9c%d7%95%d7%9e%d7%99-%d7%a9%d7%91%d7%aa-%d7%a2%d7%9e%d7%99%d7%a8-%d7%91%d7%a0%d7%99%d7%95%d7%9f-%d7%94%d7%99%d7%9b%d7%9f-%d7%90%d7%aa%d7%94/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411150&amp;sid=db79b057e91704f5824c4dbc912b8a71</v>
       </c>
       <c r="D2" t="str">
         <v>2026-06-01</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>הדואט בין שלומי שבת לבין עמיר בניון בנוי כמסע רוחני־קיומי: מצד אחד וידוי אישי, שבור ואינטימי. מצד שני זעקה גדולה שמופנית כלפי מעלה, אל האל או אל העצמי האבוד. הפתיחה ("הייתי קם עוזב הכול") נשמעת כמו הצהרת בריחה. הדובר מוכן</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שלומי שבת עמיר בניון – היכן אתה?</v>
+        <v>אלירן בוזגלו - מחרוזת והלב 2026</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Dua Lipa - Physical (Live From Mexico)</v>
+        <v>אביחי אוחנה - נתת לי חיים</v>
       </c>
       <c r="B3" t="str">
-        <v>3d ago</v>
+        <v>2026-06-01</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=xZAe-d3bXTs</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411149&amp;sid=db79b057e91704f5824c4dbc912b8a71</v>
       </c>
       <c r="D3" t="str">
         <v>2026-06-01</v>
@@ -489,16 +489,16 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>3d ago</v>
+        <v/>
       </c>
       <c r="G3" t="str">
         <v/>
       </c>
       <c r="H3" t="str">
-        <v>Dua Lipa</v>
+        <v/>
       </c>
       <c r="I3" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Dua Lipa - Physical (Live From Mexico) - Dua Lipa</v>
+        <v>אביחי אוחנה - נתת לי חיים</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Dagny - Rain (Lyric Video)</v>
+        <v>אבי בר - מחרוזת שקטים 2026</v>
       </c>
       <c r="B4" t="str">
-        <v>3d ago</v>
+        <v>2026-06-01</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=j3ZJwczZoUQ</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411148&amp;sid=db79b057e91704f5824c4dbc912b8a71</v>
       </c>
       <c r="D4" t="str">
         <v>2026-06-01</v>
@@ -527,16 +527,16 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>3d ago</v>
+        <v/>
       </c>
       <c r="G4" t="str">
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>Dagny</v>
+        <v/>
       </c>
       <c r="I4" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Dagny - Rain (Lyric Video) - Dagny</v>
+        <v>אבי בר - מחרוזת שקטים 2026</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Modern Talking - Cheri Cheri Lady (Auf los geht's los, 14.09.1985)</v>
+        <v>Dua Lipa - Physical (Live From Mexico)</v>
       </c>
       <c r="B5" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=c0LtTVKNwNA</v>
+        <v>https://www.youtube.com/watch?v=xZAe-d3bXTs</v>
       </c>
       <c r="D5" t="str">
         <v>2026-06-01</v>
@@ -565,13 +565,13 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>Modern Talking Offiziell</v>
+        <v>Dua Lipa</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Modern Talking - Cheri Cheri Lady (Auf los geht's los, 14.09.1985) - Modern Talking Offiziell</v>
+        <v>Dua Lipa - Physical (Live From Mexico) - Dua Lipa</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Jonas Blue - Girl (Official Lyric Video)</v>
+        <v>Dagny - Rain (Lyric Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=FTUe3jzUqXU</v>
+        <v>https://www.youtube.com/watch?v=j3ZJwczZoUQ</v>
       </c>
       <c r="D6" t="str">
         <v>2026-06-01</v>
@@ -603,13 +603,13 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
       </c>
       <c r="H6" t="str">
-        <v>Defected Records and Jonas Blue</v>
+        <v>Dagny</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Jonas Blue - Girl (Official Lyric Video) - Defected Records and Jonas Blue</v>
+        <v>Dagny - Rain (Lyric Video) - Dagny</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Dogpark - Don't Lie (Visualizer)</v>
+        <v>Modern Talking - Cheri Cheri Lady (Auf los geht's los, 14.09.1985)</v>
       </c>
       <c r="B7" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=is7qKBRycJI</v>
+        <v>https://www.youtube.com/watch?v=c0LtTVKNwNA</v>
       </c>
       <c r="D7" t="str">
         <v>2026-06-01</v>
@@ -641,13 +641,13 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>Dogpark</v>
+        <v>Modern Talking Offiziell</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Dogpark - Don't Lie (Visualizer) - Dogpark</v>
+        <v>Modern Talking - Cheri Cheri Lady (Auf los geht's los, 14.09.1985) - Modern Talking Offiziell</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>elijah woods - L-O-V-E (Treehouse Sessions)</v>
+        <v>Jonas Blue - Girl (Official Lyric Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=q5kN7eH6rgo</v>
+        <v>https://www.youtube.com/watch?v=FTUe3jzUqXU</v>
       </c>
       <c r="D8" t="str">
         <v>2026-06-01</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>elijah woods</v>
+        <v>Defected Records and Jonas Blue</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>elijah woods - L-O-V-E (Treehouse Sessions) - elijah woods</v>
+        <v>Jonas Blue - Girl (Official Lyric Video) - Defected Records and Jonas Blue</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Lauren Alaina - Better Off (Official Audio)</v>
+        <v>Dogpark - Don't Lie (Visualizer)</v>
       </c>
       <c r="B9" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=Vj-ong3XNHM</v>
+        <v>https://www.youtube.com/watch?v=is7qKBRycJI</v>
       </c>
       <c r="D9" t="str">
         <v>2026-06-01</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>Lauren Alaina</v>
+        <v>Dogpark</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Lauren Alaina - Better Off (Official Audio) - Lauren Alaina</v>
+        <v>Dogpark - Don't Lie (Visualizer) - Dogpark</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Lauren Sanderson - ARE YOU REALLY HERE? (Lyric Video)</v>
+        <v>elijah woods - L-O-V-E (Treehouse Sessions)</v>
       </c>
       <c r="B10" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=u7Et_hbMZUA</v>
+        <v>https://www.youtube.com/watch?v=q5kN7eH6rgo</v>
       </c>
       <c r="D10" t="str">
         <v>2026-06-01</v>
@@ -755,13 +755,13 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>Lauren Sanderson</v>
+        <v>elijah woods</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Lauren Sanderson - ARE YOU REALLY HERE? (Lyric Video) - Lauren Sanderson</v>
+        <v>elijah woods - L-O-V-E (Treehouse Sessions) - elijah woods</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Nightly – blue jeans (Official Lyric Video)</v>
+        <v>Lauren Alaina - Better Off (Official Audio)</v>
       </c>
       <c r="B11" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=LnA3xkXUwaM</v>
+        <v>https://www.youtube.com/watch?v=Vj-ong3XNHM</v>
       </c>
       <c r="D11" t="str">
         <v>2026-06-01</v>
@@ -793,13 +793,13 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>NIGHTLY</v>
+        <v>Lauren Alaina</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Nightly – blue jeans (Official Lyric Video) - NIGHTLY</v>
+        <v>Lauren Alaina - Better Off (Official Audio) - Lauren Alaina</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Dasha - Mad About It (Official Visualizer)</v>
+        <v>Lauren Sanderson - ARE YOU REALLY HERE? (Lyric Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=Ae1gf_7p3H8</v>
+        <v>https://www.youtube.com/watch?v=u7Et_hbMZUA</v>
       </c>
       <c r="D12" t="str">
         <v>2026-06-01</v>
@@ -831,13 +831,13 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>Dasha</v>
+        <v>Lauren Sanderson</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Dasha - Mad About It (Official Visualizer) - Dasha</v>
+        <v>Lauren Sanderson - ARE YOU REALLY HERE? (Lyric Video) - Lauren Sanderson</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Ariana Grande - hate that i made you love me (official lyric video)</v>
+        <v>Nightly – blue jeans (Official Lyric Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=v1t4MTqdfyI</v>
+        <v>https://www.youtube.com/watch?v=LnA3xkXUwaM</v>
       </c>
       <c r="D13" t="str">
         <v>2026-06-01</v>
@@ -869,13 +869,13 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>Ariana Grande</v>
+        <v>NIGHTLY</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Ariana Grande - hate that i made you love me (official lyric video) - Ariana Grande</v>
+        <v>Nightly – blue jeans (Official Lyric Video) - NIGHTLY</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Max McNown - Something To Someone (Performance Video)</v>
+        <v>Dasha - Mad About It (Official Visualizer)</v>
       </c>
       <c r="B14" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=4Ki4ejT86YM</v>
+        <v>https://www.youtube.com/watch?v=Ae1gf_7p3H8</v>
       </c>
       <c r="D14" t="str">
         <v>2026-06-01</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>Max McNown</v>
+        <v>Dasha</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Max McNown - Something To Someone (Performance Video) - Max McNown</v>
+        <v>Dasha - Mad About It (Official Visualizer) - Dasha</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Bebe Rexha &amp; David Guetta - Sad Girls (Official Visual)</v>
+        <v>Ariana Grande - hate that i made you love me (official lyric video)</v>
       </c>
       <c r="B15" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=P8UqZ5IF-QE</v>
+        <v>https://www.youtube.com/watch?v=v1t4MTqdfyI</v>
       </c>
       <c r="D15" t="str">
         <v>2026-06-01</v>
@@ -945,13 +945,13 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>Bebe Rexha</v>
+        <v>Ariana Grande</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Bebe Rexha &amp; David Guetta - Sad Girls (Official Visual) - Bebe Rexha</v>
+        <v>Ariana Grande - hate that i made you love me (official lyric video) - Ariana Grande</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Knox - Long Story Short (Official Video)</v>
+        <v>Max McNown - Something To Someone (Performance Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=5OGY6hCELfg</v>
+        <v>https://www.youtube.com/watch?v=4Ki4ejT86YM</v>
       </c>
       <c r="D16" t="str">
         <v>2026-06-01</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>Knox</v>
+        <v>Max McNown</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Knox - Long Story Short (Official Video) - Knox</v>
+        <v>Max McNown - Something To Someone (Performance Video) - Max McNown</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Sofia Camara - The Last Encounter</v>
+        <v>Bebe Rexha &amp; David Guetta - Sad Girls (Official Visual)</v>
       </c>
       <c r="B17" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=E9kN4HLGG1c</v>
+        <v>https://www.youtube.com/watch?v=P8UqZ5IF-QE</v>
       </c>
       <c r="D17" t="str">
         <v>2026-06-01</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>Sofia Camara</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Sofia Camara - The Last Encounter - Sofia Camara</v>
+        <v>Bebe Rexha &amp; David Guetta - Sad Girls (Official Visual) - Bebe Rexha</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Official Music Video: "Flowers" -- Alexander James</v>
+        <v>Knox - Long Story Short (Official Video)</v>
       </c>
       <c r="B18" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=aZ4WP0P92tM</v>
+        <v>https://www.youtube.com/watch?v=5OGY6hCELfg</v>
       </c>
       <c r="D18" t="str">
         <v>2026-06-01</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>Alexander James</v>
+        <v>Knox</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Official Music Video: "Flowers" -- Alexander James - Alexander James</v>
+        <v>Knox - Long Story Short (Official Video) - Knox</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>almost monday - skinny dip (official video)</v>
+        <v>Sofia Camara - The Last Encounter</v>
       </c>
       <c r="B19" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=hOxZDoaIzKQ</v>
+        <v>https://www.youtube.com/watch?v=E9kN4HLGG1c</v>
       </c>
       <c r="D19" t="str">
         <v>2026-06-01</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>almost monday</v>
+        <v>Sofia Camara</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>almost monday - skinny dip (official video) - almost monday</v>
+        <v>Sofia Camara - The Last Encounter - Sofia Camara</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Kip Moore - The Darkness (Official)</v>
+        <v>Official Music Video: "Flowers" -- Alexander James</v>
       </c>
       <c r="B20" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=lTqqixCt5Mk</v>
+        <v>https://www.youtube.com/watch?v=aZ4WP0P92tM</v>
       </c>
       <c r="D20" t="str">
         <v>2026-06-01</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>Kip Moore</v>
+        <v>Alexander James</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Kip Moore - The Darkness (Official) - Kip Moore</v>
+        <v>Official Music Video: "Flowers" -- Alexander James - Alexander James</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Paul McCartney - Come Inside (Lyric Video)</v>
+        <v>almost monday - skinny dip (official video)</v>
       </c>
       <c r="B21" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=C8Zw_Cbm2V0</v>
+        <v>https://www.youtube.com/watch?v=hOxZDoaIzKQ</v>
       </c>
       <c r="D21" t="str">
         <v>2026-06-01</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>PAUL McCARTNEY</v>
+        <v>almost monday</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Paul McCartney - Come Inside (Lyric Video) - PAUL McCARTNEY</v>
+        <v>almost monday - skinny dip (official video) - almost monday</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Santana, Becky G - Mi Gran Amor (Official Lyric Video)</v>
+        <v>Kip Moore - The Darkness (Official)</v>
       </c>
       <c r="B22" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=btdBd_Yee8E</v>
+        <v>https://www.youtube.com/watch?v=lTqqixCt5Mk</v>
       </c>
       <c r="D22" t="str">
         <v>2026-06-01</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>Santana</v>
+        <v>Kip Moore</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Santana, Becky G - Mi Gran Amor (Official Lyric Video) - Santana</v>
+        <v>Kip Moore - The Darkness (Official) - Kip Moore</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Dua Lipa - Training Season (Live From Mexico)</v>
+        <v>Paul McCartney - Come Inside (Lyric Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=Va8Udsvqigs</v>
+        <v>https://www.youtube.com/watch?v=C8Zw_Cbm2V0</v>
       </c>
       <c r="D23" t="str">
         <v>2026-06-01</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>Dua Lipa</v>
+        <v>PAUL McCARTNEY</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Dua Lipa - Training Season (Live From Mexico) - Dua Lipa</v>
+        <v>Paul McCartney - Come Inside (Lyric Video) - PAUL McCARTNEY</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Charley - Liar</v>
+        <v>Santana, Becky G - Mi Gran Amor (Official Lyric Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=3Erfj2Eecgw</v>
+        <v>https://www.youtube.com/watch?v=btdBd_Yee8E</v>
       </c>
       <c r="D24" t="str">
         <v>2026-06-01</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>Charley</v>
+        <v>Santana</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Charley - Liar - Charley</v>
+        <v>Santana, Becky G - Mi Gran Amor (Official Lyric Video) - Santana</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (ft Gabito Ballesteros) [Visualizer]</v>
+        <v>Dua Lipa - Training Season (Live From Mexico)</v>
       </c>
       <c r="B25" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=em5ryETDkAo</v>
+        <v>https://www.youtube.com/watch?v=Va8Udsvqigs</v>
       </c>
       <c r="D25" t="str">
         <v>2026-06-01</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>David Guetta and Jennifer Lopez</v>
+        <v>Dua Lipa</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (ft Gabito Ballesteros) [Visualizer] - David Guetta and Jennifer Lopez</v>
+        <v>Dua Lipa - Training Season (Live From Mexico) - Dua Lipa</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Jordana Bryant - Too Little Too Late (Official Audio)</v>
+        <v>Charley - Liar</v>
       </c>
       <c r="B26" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=AmwNx9qlOpA</v>
+        <v>https://www.youtube.com/watch?v=3Erfj2Eecgw</v>
       </c>
       <c r="D26" t="str">
         <v>2026-06-01</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>Jordana Bryant</v>
+        <v>Charley</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Jordana Bryant - Too Little Too Late (Official Audio) - Jordana Bryant</v>
+        <v>Charley - Liar - Charley</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Lewis Capaldi - Stay Love</v>
+        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (ft Gabito Ballesteros) [Visualizer]</v>
       </c>
       <c r="B27" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=9Pud3BqPpq0</v>
+        <v>https://www.youtube.com/watch?v=em5ryETDkAo</v>
       </c>
       <c r="D27" t="str">
         <v>2026-06-01</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
       </c>
       <c r="H27" t="str">
-        <v>Lewis Capaldi</v>
+        <v>David Guetta and Jennifer Lopez</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Lewis Capaldi - Stay Love - Lewis Capaldi</v>
+        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (ft Gabito Ballesteros) [Visualizer] - David Guetta and Jennifer Lopez</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Surreal World of Oddities - Pulling At My Strings - Official Music Video | 4K</v>
+        <v>Jordana Bryant - Too Little Too Late (Official Audio)</v>
       </c>
       <c r="B28" t="str">
-        <v>4d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=fMt-f2aUW3c</v>
+        <v>https://www.youtube.com/watch?v=AmwNx9qlOpA</v>
       </c>
       <c r="D28" t="str">
         <v>2026-06-01</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>4d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>Kelly Boesch AI Art</v>
+        <v>Jordana Bryant</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Surreal World of Oddities - Pulling At My Strings - Official Music Video | 4K - Kelly Boesch AI Art</v>
+        <v>Jordana Bryant - Too Little Too Late (Official Audio) - Jordana Bryant</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Julia Cole - Love You to Death (Official Video)</v>
+        <v>Lewis Capaldi - Stay Love</v>
       </c>
       <c r="B29" t="str">
-        <v>4d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=dWgmFc2QuLY</v>
+        <v>https://www.youtube.com/watch?v=9Pud3BqPpq0</v>
       </c>
       <c r="D29" t="str">
         <v>2026-06-01</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>4d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>Julia Cole Music</v>
+        <v>Lewis Capaldi</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Julia Cole - Love You to Death (Official Video) - Julia Cole Music</v>
+        <v>Lewis Capaldi - Stay Love - Lewis Capaldi</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Victor Biliac - De-ai fi tu salcie la mal ( Cover Edit )</v>
+        <v>Surreal World of Oddities - Pulling At My Strings - Official Music Video | 4K</v>
       </c>
       <c r="B30" t="str">
-        <v>4d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=v3c0kG-V2zk</v>
+        <v>https://www.youtube.com/watch?v=fMt-f2aUW3c</v>
       </c>
       <c r="D30" t="str">
         <v>2026-06-01</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>4d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>VictorBiliac</v>
+        <v>Kelly Boesch AI Art</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Victor Biliac - De-ai fi tu salcie la mal ( Cover Edit ) - VictorBiliac</v>
+        <v>Surreal World of Oddities - Pulling At My Strings - Official Music Video | 4K - Kelly Boesch AI Art</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Lolo Zouaï - Coquelicot (feat. disiz) (Official Video)</v>
+        <v>Julia Cole - Love You to Death (Official Video)</v>
       </c>
       <c r="B31" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=-4p6FkrOGT4</v>
+        <v>https://www.youtube.com/watch?v=dWgmFc2QuLY</v>
       </c>
       <c r="D31" t="str">
         <v>2026-06-01</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>Lolo Zouaï and disiz</v>
+        <v>Julia Cole Music</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Lolo Zouaï - Coquelicot (feat. disiz) (Official Video) - Lolo Zouaï and disiz</v>
+        <v>Julia Cole - Love You to Death (Official Video) - Julia Cole Music</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Jungle - The Wave (Official Video)</v>
+        <v>Victor Biliac - De-ai fi tu salcie la mal ( Cover Edit )</v>
       </c>
       <c r="B32" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=DW1vUkqNvqQ</v>
+        <v>https://www.youtube.com/watch?v=v3c0kG-V2zk</v>
       </c>
       <c r="D32" t="str">
         <v>2026-06-01</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
       </c>
       <c r="H32" t="str">
-        <v>Jungle4eva</v>
+        <v>VictorBiliac</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Jungle - The Wave (Official Video) - Jungle4eva</v>
+        <v>Victor Biliac - De-ai fi tu salcie la mal ( Cover Edit ) - VictorBiliac</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Daytime TV – Sun (Official Music Video)</v>
+        <v>Lolo Zouaï - Coquelicot (feat. disiz) (Official Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=Jqo4ra_ch-M</v>
+        <v>https://www.youtube.com/watch?v=-4p6FkrOGT4</v>
       </c>
       <c r="D33" t="str">
         <v>2026-06-01</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>DAYTIME TV</v>
+        <v>Lolo Zouaï and disiz</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Daytime TV – Sun (Official Music Video) - DAYTIME TV</v>
+        <v>Lolo Zouaï - Coquelicot (feat. disiz) (Official Video) - Lolo Zouaï and disiz</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Surreal and Strange AI Video | Not Made For The Cage | Kelly Boesch - 4K</v>
+        <v>Jungle - The Wave (Official Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>2w ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=ACNj3L2bzV8</v>
+        <v>https://www.youtube.com/watch?v=DW1vUkqNvqQ</v>
       </c>
       <c r="D34" t="str">
         <v>2026-06-01</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>2w ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>Kelly Boesch AI Art</v>
+        <v>Jungle4eva</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Surreal and Strange AI Video | Not Made For The Cage | Kelly Boesch - 4K - Kelly Boesch AI Art</v>
+        <v>Jungle - The Wave (Official Video) - Jungle4eva</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Bruno Mars - Risk It All [Live From The Romantic Tour]</v>
+        <v>Daytime TV – Sun (Official Music Video)</v>
       </c>
       <c r="B35" t="str">
-        <v>5d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=aFbueod4reQ</v>
+        <v>https://www.youtube.com/watch?v=Jqo4ra_ch-M</v>
       </c>
       <c r="D35" t="str">
         <v>2026-06-01</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>5d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
       </c>
       <c r="H35" t="str">
-        <v>Bruno Mars</v>
+        <v>DAYTIME TV</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Bruno Mars - Risk It All [Live From The Romantic Tour] - Bruno Mars</v>
+        <v>Daytime TV – Sun (Official Music Video) - DAYTIME TV</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Keith Urban - Summer Breeze (52nd American Music Awards)</v>
+        <v>Surreal and Strange AI Video | Not Made For The Cage | Kelly Boesch - 4K</v>
       </c>
       <c r="B36" t="str">
-        <v>5d ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=zn-4eVoqofQ</v>
+        <v>https://www.youtube.com/watch?v=ACNj3L2bzV8</v>
       </c>
       <c r="D36" t="str">
         <v>2026-06-01</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>5d ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>Keith Urban</v>
+        <v>Kelly Boesch AI Art</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Keith Urban - Summer Breeze (52nd American Music Awards) - Keith Urban</v>
+        <v>Surreal and Strange AI Video | Not Made For The Cage | Kelly Boesch - 4K - Kelly Boesch AI Art</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Nelly Furtado, Boi-1Da, Canada Soccer - ELECTRIC CIRCUS (Official Music Video)</v>
+        <v>Bruno Mars - Risk It All [Live From The Romantic Tour]</v>
       </c>
       <c r="B37" t="str">
-        <v>6d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=lHYEMWFuErM</v>
+        <v>https://www.youtube.com/watch?v=aFbueod4reQ</v>
       </c>
       <c r="D37" t="str">
         <v>2026-06-01</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>6d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>Nelly Furtado</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Nelly Furtado, Boi-1Da, Canada Soccer - ELECTRIC CIRCUS (Official Music Video) - Nelly Furtado</v>
+        <v>Bruno Mars - Risk It All [Live From The Romantic Tour] - Bruno Mars</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Teddy Swims - Mr. Know It All (Live from the AMAs)</v>
+        <v>Keith Urban - Summer Breeze (52nd American Music Awards)</v>
       </c>
       <c r="B38" t="str">
-        <v>6d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=ttM4gWkhZBk</v>
+        <v>https://www.youtube.com/watch?v=zn-4eVoqofQ</v>
       </c>
       <c r="D38" t="str">
         <v>2026-06-01</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>6d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
       </c>
       <c r="H38" t="str">
-        <v>Teddy Swims and American Music Awards</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Teddy Swims - Mr. Know It All (Live from the AMAs) - Teddy Swims and American Music Awards</v>
+        <v>Keith Urban - Summer Breeze (52nd American Music Awards) - Keith Urban</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Shakira, Burna Boy - Dai Dai (Official Video)</v>
+        <v>Nelly Furtado, Boi-1Da, Canada Soccer - ELECTRIC CIRCUS (Official Music Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>8d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=fcnDmrtj6Sk</v>
+        <v>https://www.youtube.com/watch?v=lHYEMWFuErM</v>
       </c>
       <c r="D39" t="str">
         <v>2026-06-01</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>8d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
       </c>
       <c r="H39" t="str">
-        <v>Shakira and 2 more</v>
+        <v>Nelly Furtado</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Shakira, Burna Boy - Dai Dai (Official Video) - Shakira and 2 more</v>
+        <v>Nelly Furtado, Boi-1Da, Canada Soccer - ELECTRIC CIRCUS (Official Music Video) - Nelly Furtado</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards)</v>
+        <v>Teddy Swims - Mr. Know It All (Live from the AMAs)</v>
       </c>
       <c r="B40" t="str">
-        <v>8d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=wacpnp83cJg</v>
+        <v>https://www.youtube.com/watch?v=ttM4gWkhZBk</v>
       </c>
       <c r="D40" t="str">
         <v>2026-06-01</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>8d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
       </c>
       <c r="H40" t="str">
-        <v>Lainey Wilson</v>
+        <v>Teddy Swims and American Music Awards</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards) - Lainey Wilson</v>
+        <v>Teddy Swims - Mr. Know It All (Live from the AMAs) - Teddy Swims and American Music Awards</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ]</v>
+        <v>Shakira, Burna Boy - Dai Dai (Official Video)</v>
       </c>
       <c r="B41" t="str">
-        <v>9d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=w8FTnkNVmq0</v>
+        <v>https://www.youtube.com/watch?v=fcnDmrtj6Sk</v>
       </c>
       <c r="D41" t="str">
         <v>2026-06-01</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>9d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
       </c>
       <c r="H41" t="str">
-        <v>Duran Duran</v>
+        <v>Shakira and 2 more</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ] - Duran Duran</v>
+        <v>Shakira, Burna Boy - Dai Dai (Official Video) - Shakira and 2 more</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Nico Santos - Optimist</v>
+        <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards)</v>
       </c>
       <c r="B42" t="str">
-        <v>11d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=JA6PIcBeKZ0</v>
+        <v>https://www.youtube.com/watch?v=wacpnp83cJg</v>
       </c>
       <c r="D42" t="str">
         <v>2026-06-01</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>11d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
       </c>
       <c r="H42" t="str">
-        <v>Nico Santos</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Nico Santos - Optimist - Nico Santos</v>
+        <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards) - Lainey Wilson</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Def Leppard - Personal Jesus (Live at Caesars Palace)</v>
+        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ]</v>
       </c>
       <c r="B43" t="str">
-        <v>8d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=k5SRMgdG4L4</v>
+        <v>https://www.youtube.com/watch?v=w8FTnkNVmq0</v>
       </c>
       <c r="D43" t="str">
         <v>2026-06-01</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>8d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
       </c>
       <c r="H43" t="str">
-        <v>DEF LEPPARD</v>
+        <v>Duran Duran</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Def Leppard - Personal Jesus (Live at Caesars Palace) - DEF LEPPARD</v>
+        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ] - Duran Duran</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer)</v>
+        <v>Nico Santos - Optimist</v>
       </c>
       <c r="B44" t="str">
-        <v>9d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=eWSwy9GU2L8</v>
+        <v>https://www.youtube.com/watch?v=JA6PIcBeKZ0</v>
       </c>
       <c r="D44" t="str">
         <v>2026-06-01</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>9d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
       </c>
       <c r="H44" t="str">
-        <v>Will Linley</v>
+        <v>Nico Santos</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer) - Will Linley</v>
+        <v>Nico Santos - Optimist - Nico Santos</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Kylie Minogue - Story (Official Lyric Video)</v>
+        <v>Def Leppard - Personal Jesus (Live at Caesars Palace)</v>
       </c>
       <c r="B45" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=fv7_1qKo8mg</v>
+        <v>https://www.youtube.com/watch?v=k5SRMgdG4L4</v>
       </c>
       <c r="D45" t="str">
         <v>2026-06-01</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
       </c>
       <c r="H45" t="str">
-        <v>Kylie Minogue</v>
+        <v>DEF LEPPARD</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Kylie Minogue - Story (Official Lyric Video) - Kylie Minogue</v>
+        <v>Def Leppard - Personal Jesus (Live at Caesars Palace) - DEF LEPPARD</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video)</v>
+        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer)</v>
       </c>
       <c r="B46" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=3KUQx2s1fQc</v>
+        <v>https://www.youtube.com/watch?v=eWSwy9GU2L8</v>
       </c>
       <c r="D46" t="str">
         <v>2026-06-01</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>Billy Raffoul</v>
+        <v>Will Linley</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video) - Billy Raffoul</v>
+        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer) - Will Linley</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025)</v>
+        <v>Kylie Minogue - Story (Official Lyric Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=vWf4uiLvwF8</v>
+        <v>https://www.youtube.com/watch?v=fv7_1qKo8mg</v>
       </c>
       <c r="D47" t="str">
         <v>2026-06-01</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>The Offspring</v>
+        <v>Kylie Minogue</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025) - The Offspring</v>
+        <v>Kylie Minogue - Story (Official Lyric Video) - Kylie Minogue</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024)</v>
+        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=9xjMaXegmWM</v>
+        <v>https://www.youtube.com/watch?v=3KUQx2s1fQc</v>
       </c>
       <c r="D48" t="str">
         <v>2026-06-01</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>David Gilmour</v>
+        <v>Billy Raffoul</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024) - David Gilmour</v>
+        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video) - Billy Raffoul</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Scorpions - Delicate Dance (Madison Square Garden 2022)</v>
+        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025)</v>
       </c>
       <c r="B49" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=yAjEr9WLTnU</v>
+        <v>https://www.youtube.com/watch?v=vWf4uiLvwF8</v>
       </c>
       <c r="D49" t="str">
         <v>2026-06-01</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>Scorpions</v>
+        <v>The Offspring</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Scorpions - Delicate Dance (Madison Square Garden 2022) - Scorpions</v>
+        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025) - The Offspring</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston)</v>
+        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024)</v>
       </c>
       <c r="B50" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=oRw4PqBzGc0</v>
+        <v>https://www.youtube.com/watch?v=9xjMaXegmWM</v>
       </c>
       <c r="D50" t="str">
         <v>2026-06-01</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>Brandon Lake and NICK JONAS</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston) - Brandon Lake and NICK JONAS</v>
+        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024) - David Gilmour</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video)</v>
+        <v>Scorpions - Delicate Dance (Madison Square Garden 2022)</v>
       </c>
       <c r="B51" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=OKf_IOGxFQo</v>
+        <v>https://www.youtube.com/watch?v=yAjEr9WLTnU</v>
       </c>
       <c r="D51" t="str">
         <v>2026-06-01</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>Kygo and Dan Tyminski</v>
+        <v>Scorpions</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video) - Kygo and Dan Tyminski</v>
+        <v>Scorpions - Delicate Dance (Madison Square Garden 2022) - Scorpions</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>The Warning - Ego (Official Video)</v>
+        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston)</v>
       </c>
       <c r="B52" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=CG6Q5i75bR4</v>
+        <v>https://www.youtube.com/watch?v=oRw4PqBzGc0</v>
       </c>
       <c r="D52" t="str">
         <v>2026-06-01</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>The Warning</v>
+        <v>Brandon Lake and NICK JONAS</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>The Warning - Ego (Official Video) - The Warning</v>
+        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston) - Brandon Lake and NICK JONAS</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>paris jackson - teenage drama (official lyric video)</v>
+        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B53" t="str">
-        <v>9d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=kVfDArNljos</v>
+        <v>https://www.youtube.com/watch?v=OKf_IOGxFQo</v>
       </c>
       <c r="D53" t="str">
         <v>2026-06-01</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>9d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>paris jackson</v>
+        <v>Kygo and Dan Tyminski</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>paris jackson - teenage drama (official lyric video) - paris jackson</v>
+        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video) - Kygo and Dan Tyminski</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Minelli - Sun Goes Down | Official Visualizer</v>
+        <v>The Warning - Ego (Official Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>9d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=xOsjm-AwN5I</v>
+        <v>https://www.youtube.com/watch?v=CG6Q5i75bR4</v>
       </c>
       <c r="D54" t="str">
         <v>2026-06-01</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>9d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>Minelli</v>
+        <v>The Warning</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Minelli - Sun Goes Down | Official Visualizer - Minelli</v>
+        <v>The Warning - Ego (Official Video) - The Warning</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Maggie Rose - Gentle Man (Official Studio Video)</v>
+        <v>paris jackson - teenage drama (official lyric video)</v>
       </c>
       <c r="B55" t="str">
-        <v>9d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=aWNK-vWrN60</v>
+        <v>https://www.youtube.com/watch?v=kVfDArNljos</v>
       </c>
       <c r="D55" t="str">
         <v>2026-06-01</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>9d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>Maggie Rose</v>
+        <v>paris jackson</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Maggie Rose - Gentle Man (Official Studio Video) - Maggie Rose</v>
+        <v>paris jackson - teenage drama (official lyric video) - paris jackson</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer]</v>
+        <v>Minelli - Sun Goes Down | Official Visualizer</v>
       </c>
       <c r="B56" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=mN5AZBrVq9I</v>
+        <v>https://www.youtube.com/watch?v=xOsjm-AwN5I</v>
       </c>
       <c r="D56" t="str">
         <v>2026-06-01</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>David Guetta</v>
+        <v>Minelli</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer] - David Guetta</v>
+        <v>Minelli - Sun Goes Down | Official Visualizer - Minelli</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video)</v>
+        <v>Maggie Rose - Gentle Man (Official Studio Video)</v>
       </c>
       <c r="B57" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=0PTufEGRAVQ</v>
+        <v>https://www.youtube.com/watch?v=aWNK-vWrN60</v>
       </c>
       <c r="D57" t="str">
         <v>2026-06-01</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>Chris Young and Shaylen</v>
+        <v>Maggie Rose</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video) - Chris Young and Shaylen</v>
+        <v>Maggie Rose - Gentle Man (Official Studio Video) - Maggie Rose</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Lauv - Pretty Little Things</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer]</v>
       </c>
       <c r="B58" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=_JBfanFvHnA</v>
+        <v>https://www.youtube.com/watch?v=mN5AZBrVq9I</v>
       </c>
       <c r="D58" t="str">
         <v>2026-06-01</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>Lauv</v>
+        <v>David Guetta</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Lauv - Pretty Little Things - Lauv</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer] - David Guetta</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Icona Pop - Butterfly Feelings (Official Audio)</v>
+        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=bXA_Q75QZTs</v>
+        <v>https://www.youtube.com/watch?v=0PTufEGRAVQ</v>
       </c>
       <c r="D59" t="str">
         <v>2026-06-01</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>Icona Pop</v>
+        <v>Chris Young and Shaylen</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Icona Pop - Butterfly Feelings (Official Audio) - Icona Pop</v>
+        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video) - Chris Young and Shaylen</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Will Swinton - Only One (Official Video)</v>
+        <v>Lauv - Pretty Little Things</v>
       </c>
       <c r="B60" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=A0KzP-zm9hA</v>
+        <v>https://www.youtube.com/watch?v=_JBfanFvHnA</v>
       </c>
       <c r="D60" t="str">
         <v>2026-06-01</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>Will Swinton</v>
+        <v>Lauv</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Will Swinton - Only One (Official Video) - Will Swinton</v>
+        <v>Lauv - Pretty Little Things - Lauv</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Dean Lewis - Escape (Official Video)</v>
+        <v>Icona Pop - Butterfly Feelings (Official Audio)</v>
       </c>
       <c r="B61" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=BZRaTXCkhcg</v>
+        <v>https://www.youtube.com/watch?v=bXA_Q75QZTs</v>
       </c>
       <c r="D61" t="str">
         <v>2026-06-01</v>
@@ -2693,13 +2693,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>Dean Lewis</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Dean Lewis - Escape (Official Video) - Dean Lewis</v>
+        <v>Icona Pop - Butterfly Feelings (Official Audio) - Icona Pop</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico]</v>
+        <v>Will Swinton - Only One (Official Video)</v>
       </c>
       <c r="B62" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=PNm0hf_zZJY</v>
+        <v>https://www.youtube.com/watch?v=A0KzP-zm9hA</v>
       </c>
       <c r="D62" t="str">
         <v>2026-06-01</v>
@@ -2731,13 +2731,13 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>Dua Lipa and OficialMana</v>
+        <v>Will Swinton</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico] - Dua Lipa and OficialMana</v>
+        <v>Will Swinton - Only One (Official Video) - Will Swinton</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Niall Horan - End of an Era (Lyric Video)</v>
+        <v>Dean Lewis - Escape (Official Video)</v>
       </c>
       <c r="B63" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=EUNNmAAe5gQ</v>
+        <v>https://www.youtube.com/watch?v=BZRaTXCkhcg</v>
       </c>
       <c r="D63" t="str">
         <v>2026-06-01</v>
@@ -2769,13 +2769,13 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>Niall Horan</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Niall Horan - End of an Era (Lyric Video) - Niall Horan</v>
+        <v>Dean Lewis - Escape (Official Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Olivia Rodrigo - the cure (Official Music Video)</v>
+        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico]</v>
       </c>
       <c r="B64" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=B402rKl4bUg</v>
+        <v>https://www.youtube.com/watch?v=PNm0hf_zZJY</v>
       </c>
       <c r="D64" t="str">
         <v>2026-06-01</v>
@@ -2807,13 +2807,13 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>Olivia Rodrigo</v>
+        <v>Dua Lipa and OficialMana</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Olivia Rodrigo - the cure (Official Music Video) - Olivia Rodrigo</v>
+        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico] - Dua Lipa and OficialMana</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Ruel - Debbie Don't Cry (Official Music Video)</v>
+        <v>Niall Horan - End of an Era (Lyric Video)</v>
       </c>
       <c r="B65" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=iz7wuk0GOwI</v>
+        <v>https://www.youtube.com/watch?v=EUNNmAAe5gQ</v>
       </c>
       <c r="D65" t="str">
         <v>2026-06-01</v>
@@ -2845,13 +2845,13 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>RUEL</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Ruel - Debbie Don't Cry (Official Music Video) - RUEL</v>
+        <v>Niall Horan - End of an Era (Lyric Video) - Niall Horan</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>TINI - Down (LIVE)</v>
+        <v>Olivia Rodrigo - the cure (Official Music Video)</v>
       </c>
       <c r="B66" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=ADbFeQUPTrk</v>
+        <v>https://www.youtube.com/watch?v=B402rKl4bUg</v>
       </c>
       <c r="D66" t="str">
         <v>2026-06-01</v>
@@ -2883,13 +2883,13 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>TINI</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>TINI - Down (LIVE) - TINI</v>
+        <v>Olivia Rodrigo - the cure (Official Music Video) - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Charli xcx - SS26 (Official Video)</v>
+        <v>Ruel - Debbie Don't Cry (Official Music Video)</v>
       </c>
       <c r="B67" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=twLhSqabby0</v>
+        <v>https://www.youtube.com/watch?v=iz7wuk0GOwI</v>
       </c>
       <c r="D67" t="str">
         <v>2026-06-01</v>
@@ -2921,13 +2921,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>Charli xcx</v>
+        <v>RUEL</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Charli xcx - SS26 (Official Video) - Charli xcx</v>
+        <v>Ruel - Debbie Don't Cry (Official Music Video) - RUEL</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Dua Lipa - Live From Mexico</v>
+        <v>TINI - Down (LIVE)</v>
       </c>
       <c r="B68" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=vZYVkitGXBU</v>
+        <v>https://www.youtube.com/watch?v=ADbFeQUPTrk</v>
       </c>
       <c r="D68" t="str">
         <v>2026-06-01</v>
@@ -2959,13 +2959,13 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>Dua Lipa</v>
+        <v>TINI</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Dua Lipa - Live From Mexico - Dua Lipa</v>
+        <v>TINI - Down (LIVE) - TINI</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Matilda Mann - 'The Fig Tree' (Official Video)</v>
+        <v>Charli xcx - SS26 (Official Video)</v>
       </c>
       <c r="B69" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=XPyubkkkw44</v>
+        <v>https://www.youtube.com/watch?v=twLhSqabby0</v>
       </c>
       <c r="D69" t="str">
         <v>2026-06-01</v>
@@ -2997,13 +2997,13 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>Matilda Mann</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Matilda Mann - 'The Fig Tree' (Official Video) - Matilda Mann</v>
+        <v>Charli xcx - SS26 (Official Video) - Charli xcx</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Ella Langley - Be Her (61st Academy of Country Music Awards)</v>
+        <v>Dua Lipa - Live From Mexico</v>
       </c>
       <c r="B70" t="str">
-        <v>11d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=4KbYfH7EAm8</v>
+        <v>https://www.youtube.com/watch?v=vZYVkitGXBU</v>
       </c>
       <c r="D70" t="str">
         <v>2026-06-01</v>
@@ -3035,13 +3035,13 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>11d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>Ella Langley</v>
+        <v>Dua Lipa</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Ella Langley - Be Her (61st Academy of Country Music Awards) - Ella Langley</v>
+        <v>Dua Lipa - Live From Mexico - Dua Lipa</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Nothing But Thieves - Evolution (Official Audio)</v>
+        <v>Matilda Mann - 'The Fig Tree' (Official Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=Kcs-4EZSUW0</v>
+        <v>https://www.youtube.com/watch?v=XPyubkkkw44</v>
       </c>
       <c r="D71" t="str">
         <v>2026-06-01</v>
@@ -3073,13 +3073,13 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Matilda Mann</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Nothing But Thieves - Evolution (Official Audio) - Nothing But Thieves</v>
+        <v>Matilda Mann - 'The Fig Tree' (Official Video) - Matilda Mann</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO)</v>
+        <v>Ella Langley - Be Her (61st Academy of Country Music Awards)</v>
       </c>
       <c r="B72" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=HiLT1jzDZb4</v>
+        <v>https://www.youtube.com/watch?v=4KbYfH7EAm8</v>
       </c>
       <c r="D72" t="str">
         <v>2026-06-01</v>
@@ -3111,13 +3111,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>kesha</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO) - kesha</v>
+        <v>Ella Langley - Be Her (61st Academy of Country Music Awards) - Ella Langley</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify</v>
+        <v>Nothing But Thieves - Evolution (Official Audio)</v>
       </c>
       <c r="B73" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=_WGsJYCCfU8</v>
+        <v>https://www.youtube.com/watch?v=Kcs-4EZSUW0</v>
       </c>
       <c r="D73" t="str">
         <v>2026-06-01</v>
@@ -3149,13 +3149,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>Holly Humberstone</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify - Holly Humberstone</v>
+        <v>Nothing But Thieves - Evolution (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Foo Fighters - Of All People (Official Video)</v>
+        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO)</v>
       </c>
       <c r="B74" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=r_iMzMrCQs0</v>
+        <v>https://www.youtube.com/watch?v=HiLT1jzDZb4</v>
       </c>
       <c r="D74" t="str">
         <v>2026-06-01</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>Foo Fighters</v>
+        <v>kesha</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Foo Fighters - Of All People (Official Video) - Foo Fighters</v>
+        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO) - kesha</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>'From Me To You' by The Beatles, performed by The Young Analogues</v>
+        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify</v>
       </c>
       <c r="B75" t="str">
-        <v>11d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=cLiyO2t3xd0</v>
+        <v>https://www.youtube.com/watch?v=_WGsJYCCfU8</v>
       </c>
       <c r="D75" t="str">
         <v>2026-06-01</v>
@@ -3225,13 +3225,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>11d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>The Analogues</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>'From Me To You' by The Beatles, performed by The Young Analogues - The Analogues</v>
+        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify - Holly Humberstone</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video]</v>
+        <v>Foo Fighters - Of All People (Official Video)</v>
       </c>
       <c r="B76" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=O67Q25sMhyU</v>
+        <v>https://www.youtube.com/watch?v=r_iMzMrCQs0</v>
       </c>
       <c r="D76" t="str">
         <v>2026-06-01</v>
@@ -3263,13 +3263,13 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>Rod Stewart</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video] - Rod Stewart</v>
+        <v>Foo Fighters - Of All People (Official Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Blue October - 18th Floor Balcony (Official Music Video)</v>
+        <v>'From Me To You' by The Beatles, performed by The Young Analogues</v>
       </c>
       <c r="B77" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=tPfbOjz-hRs</v>
+        <v>https://www.youtube.com/watch?v=cLiyO2t3xd0</v>
       </c>
       <c r="D77" t="str">
         <v>2026-06-01</v>
@@ -3301,13 +3301,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>Blue October</v>
+        <v>The Analogues</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Blue October - 18th Floor Balcony (Official Music Video) - Blue October</v>
+        <v>'From Me To You' by The Beatles, performed by The Young Analogues - The Analogues</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Far Caspian - hum (Official Video)</v>
+        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video]</v>
       </c>
       <c r="B78" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=qqXrLDhGJRk</v>
+        <v>https://www.youtube.com/watch?v=O67Q25sMhyU</v>
       </c>
       <c r="D78" t="str">
         <v>2026-06-01</v>
@@ -3339,13 +3339,13 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>Far Caspian</v>
+        <v>Rod Stewart</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Far Caspian - hum (Official Video) - Far Caspian</v>
+        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video] - Rod Stewart</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Kenia Os - Love Bombing</v>
+        <v>Blue October - 18th Floor Balcony (Official Music Video)</v>
       </c>
       <c r="B79" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=ZuWA3pAyriQ</v>
+        <v>https://www.youtube.com/watch?v=tPfbOjz-hRs</v>
       </c>
       <c r="D79" t="str">
         <v>2026-06-01</v>
@@ -3377,13 +3377,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>Kenia Os</v>
+        <v>Blue October</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Kenia Os - Love Bombing - Kenia Os</v>
+        <v>Blue October - 18th Floor Balcony (Official Music Video) - Blue October</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026</v>
+        <v>Far Caspian - hum (Official Video)</v>
       </c>
       <c r="B80" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=ftJR_CrRsig</v>
+        <v>https://www.youtube.com/watch?v=qqXrLDhGJRk</v>
       </c>
       <c r="D80" t="str">
         <v>2026-06-01</v>
@@ -3415,13 +3415,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>Purple Disco Machine</v>
+        <v>Far Caspian</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026 - Purple Disco Machine</v>
+        <v>Far Caspian - hum (Official Video) - Far Caspian</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026</v>
+        <v>Kenia Os - Love Bombing</v>
       </c>
       <c r="B81" t="str">
-        <v>2w ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=EltgrumKJfk</v>
+        <v>https://www.youtube.com/watch?v=ZuWA3pAyriQ</v>
       </c>
       <c r="D81" t="str">
         <v>2026-06-01</v>
@@ -3453,13 +3453,13 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>2w ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
       </c>
       <c r="H81" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Kenia Os</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Kenia Os - Love Bombing - Kenia Os</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026</v>
       </c>
       <c r="B82" t="str">
-        <v>2w ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=EykAYQj99GU</v>
+        <v>https://www.youtube.com/watch?v=ftJR_CrRsig</v>
       </c>
       <c r="D82" t="str">
         <v>2026-06-01</v>
@@ -3491,13 +3491,13 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>2w ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
       </c>
       <c r="H82" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Purple Disco Machine</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹 - Eurovision Song Contest</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026 - Purple Disco Machine</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026</v>
+        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026</v>
       </c>
       <c r="B83" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=doGkDemPcFE</v>
+        <v>https://www.youtube.com/watch?v=EltgrumKJfk</v>
       </c>
       <c r="D83" t="str">
         <v>2026-06-01</v>
@@ -3529,7 +3529,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026</v>
+        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹</v>
       </c>
       <c r="B84" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=rNpFNJLhSfA</v>
+        <v>https://www.youtube.com/watch?v=EykAYQj99GU</v>
       </c>
       <c r="D84" t="str">
         <v>2026-06-01</v>
@@ -3567,7 +3567,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026</v>
+        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B85" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=TpMQ6dhcvvE</v>
+        <v>https://www.youtube.com/watch?v=doGkDemPcFE</v>
       </c>
       <c r="D85" t="str">
         <v>2026-06-01</v>
@@ -3605,7 +3605,7 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​</v>
+        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B86" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=ppCyj5DxO8s</v>
+        <v>https://www.youtube.com/watch?v=rNpFNJLhSfA</v>
       </c>
       <c r="D86" t="str">
         <v>2026-06-01</v>
@@ -3643,7 +3643,7 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​ - Eurovision Song Contest</v>
+        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Evanescence – Who Will You Follow (Official Music Video)</v>
+        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B87" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=ak4Ti54Y6rY</v>
+        <v>https://www.youtube.com/watch?v=TpMQ6dhcvvE</v>
       </c>
       <c r="D87" t="str">
         <v>2026-06-01</v>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>Evanescence</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Evanescence – Who Will You Follow (Official Music Video) - Evanescence</v>
+        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>DEEP PURPLE – ARROGANT BOY (Official Video)</v>
+        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​</v>
       </c>
       <c r="B88" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=SoSr0sStFaE</v>
+        <v>https://www.youtube.com/watch?v=ppCyj5DxO8s</v>
       </c>
       <c r="D88" t="str">
         <v>2026-06-01</v>
@@ -3719,13 +3719,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>earMUSIC and Deep Purple Official</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>DEEP PURPLE – ARROGANT BOY (Official Video) - earMUSIC and Deep Purple Official</v>
+        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​ - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video]</v>
+        <v>Evanescence – Who Will You Follow (Official Music Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=9iCw89UajaQ</v>
+        <v>https://www.youtube.com/watch?v=ak4Ti54Y6rY</v>
       </c>
       <c r="D89" t="str">
         <v>2026-06-01</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>Armin van Buuren</v>
+        <v>Evanescence</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Evanescence – Who Will You Follow (Official Music Video) - Evanescence</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Madison Cunningham - "Take Two" (Live in Chicago)</v>
+        <v>DEEP PURPLE – ARROGANT BOY (Official Video)</v>
       </c>
       <c r="B90" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=bUBLlJXtjqE</v>
+        <v>https://www.youtube.com/watch?v=SoSr0sStFaE</v>
       </c>
       <c r="D90" t="str">
         <v>2026-06-01</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>Madison Cunningham</v>
+        <v>earMUSIC and Deep Purple Official</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Madison Cunningham - "Take Two" (Live in Chicago) - Madison Cunningham</v>
+        <v>DEEP PURPLE – ARROGANT BOY (Official Video) - earMUSIC and Deep Purple Official</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Johnny Orlando - Heads Up (Official Video)</v>
+        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B91" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=s5mClhWsajE</v>
+        <v>https://www.youtube.com/watch?v=9iCw89UajaQ</v>
       </c>
       <c r="D91" t="str">
         <v>2026-06-01</v>
@@ -3833,13 +3833,13 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>Johnny Orlando</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Johnny Orlando - Heads Up (Official Video) - Johnny Orlando</v>
+        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Carver Jones - BEST FRIEND (Official Video)</v>
+        <v>Madison Cunningham - "Take Two" (Live in Chicago)</v>
       </c>
       <c r="B92" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=96xxxpZ5uxI</v>
+        <v>https://www.youtube.com/watch?v=bUBLlJXtjqE</v>
       </c>
       <c r="D92" t="str">
         <v>2026-06-01</v>
@@ -3871,13 +3871,13 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
       </c>
       <c r="H92" t="str">
-        <v>Carver Jones</v>
+        <v>Madison Cunningham</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Carver Jones - BEST FRIEND (Official Video) - Carver Jones</v>
+        <v>Madison Cunningham - "Take Two" (Live in Chicago) - Madison Cunningham</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Jazmin Bean - Darling (Official Music Video)</v>
+        <v>Johnny Orlando - Heads Up (Official Video)</v>
       </c>
       <c r="B93" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=N4uW3ZcowBM</v>
+        <v>https://www.youtube.com/watch?v=s5mClhWsajE</v>
       </c>
       <c r="D93" t="str">
         <v>2026-06-01</v>
@@ -3909,13 +3909,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>Jazmin bean</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Jazmin Bean - Darling (Official Music Video) - Jazmin bean</v>
+        <v>Johnny Orlando - Heads Up (Official Video) - Johnny Orlando</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Baby Queen - Word Vomit (Official Visualiser)</v>
+        <v>Carver Jones - BEST FRIEND (Official Video)</v>
       </c>
       <c r="B94" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=T-bo4Klq_js</v>
+        <v>https://www.youtube.com/watch?v=96xxxpZ5uxI</v>
       </c>
       <c r="D94" t="str">
         <v>2026-06-01</v>
@@ -3947,13 +3947,13 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
       </c>
       <c r="H94" t="str">
-        <v>Baby Queen</v>
+        <v>Carver Jones</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Baby Queen - Word Vomit (Official Visualiser) - Baby Queen</v>
+        <v>Carver Jones - BEST FRIEND (Official Video) - Carver Jones</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Switchfoot - Absolution (Official Audio)</v>
+        <v>Jazmin Bean - Darling (Official Music Video)</v>
       </c>
       <c r="B95" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=nCOSfMdKq9k</v>
+        <v>https://www.youtube.com/watch?v=N4uW3ZcowBM</v>
       </c>
       <c r="D95" t="str">
         <v>2026-06-01</v>
@@ -3985,13 +3985,13 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
       </c>
       <c r="H95" t="str">
-        <v>Switchfoot</v>
+        <v>Jazmin bean</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Switchfoot - Absolution (Official Audio) - Switchfoot</v>
+        <v>Jazmin Bean - Darling (Official Music Video) - Jazmin bean</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Grace Potter - Love Me Not (Official Audio)</v>
+        <v>Baby Queen - Word Vomit (Official Visualiser)</v>
       </c>
       <c r="B96" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=W3v0HAxDTUY</v>
+        <v>https://www.youtube.com/watch?v=T-bo4Klq_js</v>
       </c>
       <c r="D96" t="str">
         <v>2026-06-01</v>
@@ -4023,13 +4023,13 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
       </c>
       <c r="H96" t="str">
-        <v>Grace Potter</v>
+        <v>Baby Queen</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Grace Potter - Love Me Not (Official Audio) - Grace Potter</v>
+        <v>Baby Queen - Word Vomit (Official Visualiser) - Baby Queen</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986)</v>
+        <v>Switchfoot - Absolution (Official Audio)</v>
       </c>
       <c r="B97" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=Dhy4xH662vE</v>
+        <v>https://www.youtube.com/watch?v=nCOSfMdKq9k</v>
       </c>
       <c r="D97" t="str">
         <v>2026-06-01</v>
@@ -4061,13 +4061,13 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
       </c>
       <c r="H97" t="str">
-        <v>Modern Talking Offiziell</v>
+        <v>Switchfoot</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986) - Modern Talking Offiziell</v>
+        <v>Switchfoot - Absolution (Official Audio) - Switchfoot</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>The All-American Rejects - Clothesline (Official Lyric Video)</v>
+        <v>Grace Potter - Love Me Not (Official Audio)</v>
       </c>
       <c r="B98" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=y9axmk3NjrA</v>
+        <v>https://www.youtube.com/watch?v=W3v0HAxDTUY</v>
       </c>
       <c r="D98" t="str">
         <v>2026-06-01</v>
@@ -4099,13 +4099,13 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
       </c>
       <c r="H98" t="str">
-        <v>The All-American Rejects</v>
+        <v>Grace Potter</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>The All-American Rejects - Clothesline (Official Lyric Video) - The All-American Rejects</v>
+        <v>Grace Potter - Love Me Not (Official Audio) - Grace Potter</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Henry Moodie - MISS U (Official Visualiser)</v>
+        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.08.1986)</v>
       </c>
       <c r="B99" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=l_lroRlSmTE</v>
+        <v>https://www.youtube.com/watch?v=Dhy4xH662vE</v>
       </c>
       <c r="D99" t="str">
         <v>2026-06-01</v>
@@ -4137,13 +4137,13 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
       </c>
       <c r="H99" t="str">
-        <v>Henry Moodie</v>
+        <v>Modern Talking Offiziell</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Henry Moodie - MISS U (Official Visualiser) - Henry Moodie</v>
+        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.08.1986) - Modern Talking Offiziell</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Spacey Jane - I Never See Her (Official Music Video)</v>
+        <v>The All-American Rejects - Clothesline (Official Lyric Video)</v>
       </c>
       <c r="B100" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=q6tyEMN5haA</v>
+        <v>https://www.youtube.com/watch?v=y9axmk3NjrA</v>
       </c>
       <c r="D100" t="str">
         <v>2026-06-01</v>
@@ -4175,13 +4175,13 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
       </c>
       <c r="H100" t="str">
-        <v>Spacey Jane</v>
+        <v>The All-American Rejects</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Spacey Jane - I Never See Her (Official Music Video) - Spacey Jane</v>
+        <v>The All-American Rejects - Clothesline (Official Lyric Video) - The All-American Rejects</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video)</v>
+        <v>Henry Moodie - MISS U (Official Visualiser)</v>
       </c>
       <c r="B101" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=qacdvCqOZGc</v>
+        <v>https://www.youtube.com/watch?v=l_lroRlSmTE</v>
       </c>
       <c r="D101" t="str">
         <v>2026-06-01</v>
@@ -4213,13 +4213,13 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G101" t="str">
         <v/>
       </c>
       <c r="H101" t="str">
-        <v>Megan Moroney</v>
+        <v>Henry Moodie</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video) - Megan Moroney</v>
+        <v>Henry Moodie - MISS U (Official Visualiser) - Henry Moodie</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Matt Hansen - Orchid (Official Visualiser)</v>
+        <v>Spacey Jane - I Never See Her (Official Music Video)</v>
       </c>
       <c r="B102" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=otVYamnbOhY</v>
+        <v>https://www.youtube.com/watch?v=q6tyEMN5haA</v>
       </c>
       <c r="D102" t="str">
         <v>2026-06-01</v>
@@ -4251,13 +4251,13 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G102" t="str">
         <v/>
       </c>
       <c r="H102" t="str">
-        <v>Matt Hansen</v>
+        <v>Spacey Jane</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4269,18 +4269,18 @@
         <v/>
       </c>
       <c r="L102" t="str">
-        <v>Matt Hansen - Orchid (Official Visualiser) - Matt Hansen</v>
+        <v>Spacey Jane - I Never See Her (Official Music Video) - Spacey Jane</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>hate that i made you love me</v>
+        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video)</v>
       </c>
       <c r="B103" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/hate-that-i-made-you-love-me/6763656876</v>
+        <v>https://www.youtube.com/watch?v=qacdvCqOZGc</v>
       </c>
       <c r="D103" t="str">
         <v>2026-06-01</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>petal</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G103" t="str">
-        <v>3:17</v>
+        <v/>
       </c>
       <c r="H103" t="str">
-        <v>Ariana Grande</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/ariana-grande/412778295</v>
+        <v/>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/hate-that-i-made-you-love-me/1895420989</v>
+        <v/>
       </c>
       <c r="L103" t="str">
-        <v>hate that i made you love me - Ariana Grande</v>
+        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Come Inside</v>
+        <v>Matt Hansen - Orchid (Official Visualiser)</v>
       </c>
       <c r="B104" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/come-inside/1887403093</v>
+        <v>https://www.youtube.com/watch?v=otVYamnbOhY</v>
       </c>
       <c r="D104" t="str">
         <v>2026-06-01</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>The Boys of Dungeon Lane</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G104" t="str">
-        <v>3:13</v>
+        <v/>
       </c>
       <c r="H104" t="str">
-        <v>Paul McCartney</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/paul-mccartney/12224</v>
+        <v/>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/come-inside/1887402919</v>
+        <v/>
       </c>
       <c r="L104" t="str">
-        <v>Come Inside - Paul McCartney</v>
+        <v>Matt Hansen - Orchid (Official Visualiser) - Matt Hansen</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Game Time</v>
+        <v>hate that i made you love me</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/game-time/6771157200</v>
+        <v>https://music.apple.com/us/song/hate-that-i-made-you-love-me/6763656876</v>
       </c>
       <c r="D105" t="str">
         <v>2026-06-01</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>Game Time (FIFA World Cup 2026™) - Single</v>
+        <v>petal</v>
       </c>
       <c r="G105" t="str">
-        <v>3:26</v>
+        <v>3:17</v>
       </c>
       <c r="H105" t="str">
-        <v>Future</v>
+        <v>Ariana Grande</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/future/128050210</v>
+        <v>https://music.apple.com/us/artist/ariana-grande/412778295</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/game-time/6771157186</v>
+        <v>https://music.apple.com/us/album/hate-that-i-made-you-love-me/1895420989</v>
       </c>
       <c r="L105" t="str">
-        <v>Game Time - Future</v>
+        <v>hate that i made you love me - Ariana Grande</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Motion Party (Remix)</v>
+        <v>Come Inside</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/motion-party-remix/6773413965</v>
+        <v>https://music.apple.com/us/song/come-inside/1887403093</v>
       </c>
       <c r="D106" t="str">
         <v>2026-06-01</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>Motion Party (Remix) - Single</v>
+        <v>The Boys of Dungeon Lane</v>
       </c>
       <c r="G106" t="str">
-        <v>2:36</v>
+        <v>3:13</v>
       </c>
       <c r="H106" t="str">
-        <v>Bossman Dlow</v>
+        <v>Paul McCartney</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/bossman-dlow/1474308236</v>
+        <v>https://music.apple.com/us/artist/paul-mccartney/12224</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/motion-party-remix/6773413953</v>
+        <v>https://music.apple.com/us/album/come-inside/1887402919</v>
       </c>
       <c r="L106" t="str">
-        <v>Motion Party (Remix) - Bossman Dlow</v>
+        <v>Come Inside - Paul McCartney</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Aquel diciembre</v>
+        <v>Game Time</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/aquel-diciembre/6769580010</v>
+        <v>https://music.apple.com/us/song/game-time/6771157200</v>
       </c>
       <c r="D107" t="str">
         <v>2026-06-01</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>Do Not Disturb: Late Checkout</v>
+        <v>Game Time (FIFA World Cup 2026™) - Single</v>
       </c>
       <c r="G107" t="str">
-        <v>3:22</v>
+        <v>3:26</v>
       </c>
       <c r="H107" t="str">
-        <v>Young Miko</v>
+        <v>Future</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/young-miko/1576521417</v>
+        <v>https://music.apple.com/us/artist/future/128050210</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/aquel-diciembre/6769579992</v>
+        <v>https://music.apple.com/us/album/game-time/6771157186</v>
       </c>
       <c r="L107" t="str">
-        <v>Aquel diciembre - Young Miko</v>
+        <v>Game Time - Future</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Handle</v>
+        <v>Motion Party (Remix)</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/handle/6771922623</v>
+        <v>https://music.apple.com/us/song/motion-party-remix/6773413965</v>
       </c>
       <c r="D108" t="str">
         <v>2026-06-01</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Blue Island</v>
+        <v>Motion Party (Remix) - Single</v>
       </c>
       <c r="G108" t="str">
-        <v>3:06</v>
+        <v>2:36</v>
       </c>
       <c r="H108" t="str">
-        <v>Ravyn Lenae</v>
+        <v>Bossman Dlow</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/ravyn-lenae/1044417443</v>
+        <v>https://music.apple.com/us/artist/bossman-dlow/1474308236</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/handle/6771922622</v>
+        <v>https://music.apple.com/us/album/motion-party-remix/6773413953</v>
       </c>
       <c r="L108" t="str">
-        <v>Handle - Ravyn Lenae</v>
+        <v>Motion Party (Remix) - Bossman Dlow</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>The Wave</v>
+        <v>Aquel diciembre</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/the-wave/1886730541</v>
+        <v>https://music.apple.com/us/song/aquel-diciembre/6769580010</v>
       </c>
       <c r="D109" t="str">
         <v>2026-06-01</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>Sunshine</v>
+        <v>Do Not Disturb: Late Checkout</v>
       </c>
       <c r="G109" t="str">
         <v>3:22</v>
       </c>
       <c r="H109" t="str">
-        <v>Jungle</v>
+        <v>Young Miko</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/jungle/825833522</v>
+        <v>https://music.apple.com/us/artist/young-miko/1576521417</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/the-wave/1886730527</v>
+        <v>https://music.apple.com/us/album/aquel-diciembre/6769579992</v>
       </c>
       <c r="L109" t="str">
-        <v>The Wave - Jungle</v>
+        <v>Aquel diciembre - Young Miko</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>STOP</v>
+        <v>Handle</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/stop/6771161771</v>
+        <v>https://music.apple.com/us/song/handle/6771922623</v>
       </c>
       <c r="D110" t="str">
         <v>2026-06-01</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>are you mad at me? - Single</v>
+        <v>Blue Island</v>
       </c>
       <c r="G110" t="str">
-        <v>2:56</v>
+        <v>3:06</v>
       </c>
       <c r="H110" t="str">
-        <v>Bella Kay</v>
+        <v>Ravyn Lenae</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
+        <v>https://music.apple.com/us/artist/ravyn-lenae/1044417443</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/stop/6771161760</v>
+        <v>https://music.apple.com/us/album/handle/6771922622</v>
       </c>
       <c r="L110" t="str">
-        <v>STOP - Bella Kay</v>
+        <v>Handle - Ravyn Lenae</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Here (Apple Music Sessions)</v>
+        <v>The Wave</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/here-apple-music-sessions/1878235516</v>
+        <v>https://music.apple.com/us/song/the-wave/1886730541</v>
       </c>
       <c r="D111" t="str">
         <v>2026-06-01</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Apple Music Sessions</v>
+        <v>Sunshine</v>
       </c>
       <c r="G111" t="str">
-        <v>3:08</v>
+        <v>3:22</v>
       </c>
       <c r="H111" t="str">
-        <v>Mumford &amp; Sons</v>
+        <v>Jungle</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/mumford-sons/307699986</v>
+        <v>https://music.apple.com/us/artist/jungle/825833522</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/here-apple-music-sessions/1878235330</v>
+        <v>https://music.apple.com/us/album/the-wave/1886730527</v>
       </c>
       <c r="L111" t="str">
-        <v>Here (Apple Music Sessions) - Mumford &amp; Sons</v>
+        <v>The Wave - Jungle</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Talk On The Hill</v>
+        <v>STOP</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/talk-on-the-hill/6769524458</v>
+        <v>https://music.apple.com/us/song/stop/6771161771</v>
       </c>
       <c r="D112" t="str">
         <v>2026-06-01</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>The Thread</v>
+        <v>are you mad at me? - Single</v>
       </c>
       <c r="G112" t="str">
-        <v>3:27</v>
+        <v>2:56</v>
       </c>
       <c r="H112" t="str">
-        <v>WILLOW</v>
+        <v>Bella Kay</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/willow/400531893</v>
+        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/talk-on-the-hill/6769524450</v>
+        <v>https://music.apple.com/us/album/stop/6771161760</v>
       </c>
       <c r="L112" t="str">
-        <v>Talk On The Hill - WILLOW</v>
+        <v>STOP - Bella Kay</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>No Fear</v>
+        <v>Here (Apple Music Sessions)</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/no-fear/1880484493</v>
+        <v>https://music.apple.com/us/song/here-apple-music-sessions/1878235516</v>
       </c>
       <c r="D113" t="str">
         <v>2026-06-01</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>For Love of Grace &amp; the Hereafter</v>
+        <v>Apple Music Sessions</v>
       </c>
       <c r="G113" t="str">
-        <v>3:38</v>
+        <v>3:08</v>
       </c>
       <c r="H113" t="str">
-        <v>Iceage</v>
+        <v>Mumford &amp; Sons</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/iceage/406846711</v>
+        <v>https://music.apple.com/us/artist/mumford-sons/307699986</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/no-fear/1880484160</v>
+        <v>https://music.apple.com/us/album/here-apple-music-sessions/1878235330</v>
       </c>
       <c r="L113" t="str">
-        <v>No Fear - Iceage</v>
+        <v>Here (Apple Music Sessions) - Mumford &amp; Sons</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Hostage (feat. 21 Savage)</v>
+        <v>Talk On The Hill</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/hostage-feat-21-savage/6774372288</v>
+        <v>https://music.apple.com/us/song/talk-on-the-hill/6769524458</v>
       </c>
       <c r="D114" t="str">
         <v>2026-06-01</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Big Mama</v>
+        <v>The Thread</v>
       </c>
       <c r="G114" t="str">
-        <v>3:11</v>
+        <v>3:27</v>
       </c>
       <c r="H114" t="str">
-        <v>Latto</v>
+        <v>WILLOW</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/latto/419799506</v>
+        <v>https://music.apple.com/us/artist/willow/400531893</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/hostage-feat-21-savage/6774372200</v>
+        <v>https://music.apple.com/us/album/talk-on-the-hill/6769524450</v>
       </c>
       <c r="L114" t="str">
-        <v>Hostage (feat. 21 Savage) - Latto</v>
+        <v>Talk On The Hill - WILLOW</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Sad Girls</v>
+        <v>No Fear</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/sad-girls/6768814374</v>
+        <v>https://music.apple.com/us/song/no-fear/1880484493</v>
       </c>
       <c r="D115" t="str">
         <v>2026-06-01</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Sad Girls - Single</v>
+        <v>For Love of Grace &amp; the Hereafter</v>
       </c>
       <c r="G115" t="str">
-        <v>2:48</v>
+        <v>3:38</v>
       </c>
       <c r="H115" t="str">
-        <v>Bebe Rexha</v>
+        <v>Iceage</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/bebe-rexha/466059563</v>
+        <v>https://music.apple.com/us/artist/iceage/406846711</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/sad-girls/6768814373</v>
+        <v>https://music.apple.com/us/album/no-fear/1880484160</v>
       </c>
       <c r="L115" t="str">
-        <v>Sad Girls - Bebe Rexha</v>
+        <v>No Fear - Iceage</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Salvame Hoy (feat. Gabito Ballesteros)</v>
+        <v>Hostage</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/salvame-hoy-feat-gabito-ballesteros/6765697019</v>
+        <v>https://music.apple.com/us/song/hostage/6774372288</v>
       </c>
       <c r="D116" t="str">
         <v>2026-06-01</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Salvame Hoy (feat. Gabito Ballesteros) - Single</v>
+        <v>Big Mama</v>
       </c>
       <c r="G116" t="str">
-        <v>3:35</v>
+        <v>3:11</v>
       </c>
       <c r="H116" t="str">
-        <v>Jennifer Lopez</v>
+        <v>Latto</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/jennifer-lopez/463009</v>
+        <v>https://music.apple.com/us/artist/latto/419799506</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/salvame-hoy-feat-gabito-ballesteros/1896041010</v>
+        <v>https://music.apple.com/us/album/hostage/6774372200</v>
       </c>
       <c r="L116" t="str">
-        <v>Salvame Hoy (feat. Gabito Ballesteros) - Jennifer Lopez</v>
+        <v>Hostage - Latto</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Rubio</v>
+        <v>Sad Girls</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/rubio/6770655339</v>
+        <v>https://music.apple.com/us/song/sad-girls/6768814374</v>
       </c>
       <c r="D117" t="str">
         <v>2026-06-01</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>La Voz Favorita</v>
+        <v>Sad Girls - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>4:42</v>
+        <v>2:48</v>
       </c>
       <c r="H117" t="str">
-        <v>Jay Wheeler</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/jay-wheeler/164376380</v>
+        <v>https://music.apple.com/us/artist/bebe-rexha/466059563</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/rubio/6770654729</v>
+        <v>https://music.apple.com/us/album/sad-girls/6768814373</v>
       </c>
       <c r="L117" t="str">
-        <v>Rubio - Jay Wheeler</v>
+        <v>Sad Girls - Bebe Rexha</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Pary</v>
+        <v>Salvame Hoy (feat. Gabito Ballesteros)</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/pary/6767367748</v>
+        <v>https://music.apple.com/us/song/salvame-hoy-feat-gabito-ballesteros/6765697019</v>
       </c>
       <c r="D118" t="str">
         <v>2026-06-01</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Con dolor - EP</v>
+        <v>Salvame Hoy (feat. Gabito Ballesteros) - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>2:52</v>
+        <v>3:35</v>
       </c>
       <c r="H118" t="str">
-        <v>Grupo Frontera</v>
+        <v>Jennifer Lopez</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
+        <v>https://music.apple.com/us/artist/jennifer-lopez/463009</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/pary/6767367501</v>
+        <v>https://music.apple.com/us/album/salvame-hoy-feat-gabito-ballesteros/1896041010</v>
       </c>
       <c r="L118" t="str">
-        <v>Pary - Grupo Frontera</v>
+        <v>Salvame Hoy (feat. Gabito Ballesteros) - Jennifer Lopez</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Think As You Drunk</v>
+        <v>Rubio</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/think-as-you-drunk/6770725979</v>
+        <v>https://music.apple.com/us/song/rubio/6770655339</v>
       </c>
       <c r="D119" t="str">
         <v>2026-06-01</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>That's Just Me</v>
+        <v>La Voz Favorita</v>
       </c>
       <c r="G119" t="str">
-        <v>3:48</v>
+        <v>4:42</v>
       </c>
       <c r="H119" t="str">
-        <v>Riley Green</v>
+        <v>Jay Wheeler</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/riley-green/662432971</v>
+        <v>https://music.apple.com/us/artist/jay-wheeler/164376380</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/think-as-you-drunk/6770725355</v>
+        <v>https://music.apple.com/us/album/rubio/6770654729</v>
       </c>
       <c r="L119" t="str">
-        <v>Think As You Drunk - Riley Green</v>
+        <v>Rubio - Jay Wheeler</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Play Your Games</v>
+        <v>Pary</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/play-your-games/6772932837</v>
+        <v>https://music.apple.com/us/song/pary/6767367748</v>
       </c>
       <c r="D120" t="str">
         <v>2026-06-01</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Play Your Games - Single</v>
+        <v>Con dolor - EP</v>
       </c>
       <c r="G120" t="str">
-        <v>3:15</v>
+        <v>2:52</v>
       </c>
       <c r="H120" t="str">
-        <v>Greta Van Fleet</v>
+        <v>Grupo Frontera</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/greta-van-fleet/646178956</v>
+        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/play-your-games/6772932835</v>
+        <v>https://music.apple.com/us/album/pary/6767367501</v>
       </c>
       <c r="L120" t="str">
-        <v>Play Your Games - Greta Van Fleet</v>
+        <v>Pary - Grupo Frontera</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello)</v>
+        <v>Think As You Drunk</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/adjourn-it-feat-serj-tankian-roman-morello/6769340216</v>
+        <v>https://music.apple.com/us/song/think-as-you-drunk/6770725979</v>
       </c>
       <c r="D121" t="str">
         <v>2026-06-01</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello) - Single</v>
+        <v>That's Just Me</v>
       </c>
       <c r="G121" t="str">
-        <v>2:47</v>
+        <v>3:48</v>
       </c>
       <c r="H121" t="str">
-        <v>Tom Morello</v>
+        <v>Riley Green</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/tom-morello/466357</v>
+        <v>https://music.apple.com/us/artist/riley-green/662432971</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/adjourn-it-feat-serj-tankian-roman-morello/6769340214</v>
+        <v>https://music.apple.com/us/album/think-as-you-drunk/6770725355</v>
       </c>
       <c r="L121" t="str">
-        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello) - Tom Morello</v>
+        <v>Think As You Drunk - Riley Green</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Essex_Honey.mp3</v>
+        <v>Play Your Games</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/essex-honey-mp3/6771169447</v>
+        <v>https://music.apple.com/us/song/play-your-games/6772932837</v>
       </c>
       <c r="D122" t="str">
         <v>2026-06-01</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Essex_Honey.mp3 - Single</v>
+        <v>Play Your Games - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>4:49</v>
+        <v>3:15</v>
       </c>
       <c r="H122" t="str">
-        <v>Blood Orange</v>
+        <v>Greta Van Fleet</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/blood-orange/440698865</v>
+        <v>https://music.apple.com/us/artist/greta-van-fleet/646178956</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/essex-honey-mp3/6771169151</v>
+        <v>https://music.apple.com/us/album/play-your-games/6772932835</v>
       </c>
       <c r="L122" t="str">
-        <v>Essex_Honey.mp3 - Blood Orange</v>
+        <v>Play Your Games - Greta Van Fleet</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>minute</v>
+        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello)</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/minute/1875303122</v>
+        <v>https://music.apple.com/us/song/adjourn-it-feat-serj-tankian-roman-morello/6769340216</v>
       </c>
       <c r="D123" t="str">
         <v>2026-06-01</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>ghosted - EP</v>
+        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello) - Single</v>
       </c>
       <c r="G123" t="str">
-        <v>2:59</v>
+        <v>2:47</v>
       </c>
       <c r="H123" t="str">
-        <v>Saint Harison</v>
+        <v>Tom Morello</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/saint-harison/1639595302</v>
+        <v>https://music.apple.com/us/artist/tom-morello/466357</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/minute/1875302904</v>
+        <v>https://music.apple.com/us/album/adjourn-it-feat-serj-tankian-roman-morello/6769340214</v>
       </c>
       <c r="L123" t="str">
-        <v>minute - Saint Harison</v>
+        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello) - Tom Morello</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>THE LIVING</v>
+        <v>Essex_Honey.mp3</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/the-living/1894092345</v>
+        <v>https://music.apple.com/us/song/essex-honey-mp3/6771169447</v>
       </c>
       <c r="D124" t="str">
         <v>2026-06-01</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>COSMIC OPERA ACT II</v>
+        <v>Essex_Honey.mp3 - Single</v>
       </c>
       <c r="G124" t="str">
-        <v>2:48</v>
+        <v>4:49</v>
       </c>
       <c r="H124" t="str">
-        <v>Labrinth</v>
+        <v>Blood Orange</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
+        <v>https://music.apple.com/us/artist/blood-orange/440698865</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/the-living/1894092339</v>
+        <v>https://music.apple.com/us/album/essex-honey-mp3/6771169151</v>
       </c>
       <c r="L124" t="str">
-        <v>THE LIVING - Labrinth</v>
+        <v>Essex_Honey.mp3 - Blood Orange</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Thug</v>
+        <v>minute</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/thug/6769289966</v>
+        <v>https://music.apple.com/us/song/minute/1875303122</v>
       </c>
       <c r="D125" t="str">
         <v>2026-06-01</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Thug - Single</v>
+        <v>ghosted - EP</v>
       </c>
       <c r="G125" t="str">
-        <v>2:25</v>
+        <v>2:59</v>
       </c>
       <c r="H125" t="str">
-        <v>G Herbo</v>
+        <v>Saint Harison</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/g-herbo/1036753321</v>
+        <v>https://music.apple.com/us/artist/saint-harison/1639595302</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/thug/6769289953</v>
+        <v>https://music.apple.com/us/album/minute/1875302904</v>
       </c>
       <c r="L125" t="str">
-        <v>Thug - G Herbo</v>
+        <v>minute - Saint Harison</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Clap</v>
+        <v>THE LIVING</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/clap/6769903711</v>
+        <v>https://music.apple.com/us/song/the-living/1894092345</v>
       </c>
       <c r="D126" t="str">
         <v>2026-06-01</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Clap - Single</v>
+        <v>COSMIC OPERA ACT II</v>
       </c>
       <c r="G126" t="str">
-        <v>2:04</v>
+        <v>2:48</v>
       </c>
       <c r="H126" t="str">
-        <v>Polo G</v>
+        <v>Labrinth</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/polo-g/1159371412</v>
+        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/clap/6769903710</v>
+        <v>https://music.apple.com/us/album/the-living/1894092339</v>
       </c>
       <c r="L126" t="str">
-        <v>Clap - Polo G</v>
+        <v>THE LIVING - Labrinth</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>GANG BIZNESS</v>
+        <v>Thug</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/gang-bizness/6772383809</v>
+        <v>https://music.apple.com/us/song/thug/6769289966</v>
       </c>
       <c r="D127" t="str">
         <v>2026-06-01</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>THE GENTLEMEN'S CLUB</v>
+        <v>Thug - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>2:47</v>
+        <v>2:25</v>
       </c>
       <c r="H127" t="str">
-        <v>YG</v>
+        <v>G Herbo</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/yg/189792075</v>
+        <v>https://music.apple.com/us/artist/g-herbo/1036753321</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/gang-bizness/6772383681</v>
+        <v>https://music.apple.com/us/album/thug/6769289953</v>
       </c>
       <c r="L127" t="str">
-        <v>GANG BIZNESS - YG</v>
+        <v>Thug - G Herbo</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>UR HEARTBEAT (WHO DO U THINK ABOUT AT 2AM?)</v>
+        <v>Clap</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/ur-heartbeat-who-do-u-think-about-at-2am/6765534140</v>
+        <v>https://music.apple.com/us/song/clap/6769903711</v>
       </c>
       <c r="D128" t="str">
         <v>2026-06-01</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>A LITTLE VENGEANCE</v>
+        <v>Clap - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>2:50</v>
+        <v>2:04</v>
       </c>
       <c r="H128" t="str">
-        <v>Jessie Reyez</v>
+        <v>Polo G</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
+        <v>https://music.apple.com/us/artist/polo-g/1159371412</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/ur-heartbeat-who-do-u-think-about-at-2am/1895983502</v>
+        <v>https://music.apple.com/us/album/clap/6769903710</v>
       </c>
       <c r="L128" t="str">
-        <v>UR HEARTBEAT (WHO DO U THINK ABOUT AT 2AM?) - Jessie Reyez</v>
+        <v>Clap - Polo G</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Joshua Tree</v>
+        <v>GANG BIZNESS</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/joshua-tree/6771859148</v>
+        <v>https://music.apple.com/us/song/gang-bizness/6772383809</v>
       </c>
       <c r="D129" t="str">
         <v>2026-06-01</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Euphoria: Season 3 (HBO Original Series Soundtrack)</v>
+        <v>THE GENTLEMEN'S CLUB</v>
       </c>
       <c r="G129" t="str">
-        <v>2:50</v>
+        <v>2:47</v>
       </c>
       <c r="H129" t="str">
-        <v>Hans Zimmer</v>
+        <v>YG</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/hans-zimmer/454295032</v>
+        <v>https://music.apple.com/us/artist/yg/189792075</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/joshua-tree/6771858464</v>
+        <v>https://music.apple.com/us/album/gang-bizness/6772383681</v>
       </c>
       <c r="L129" t="str">
-        <v>Joshua Tree - Hans Zimmer</v>
+        <v>GANG BIZNESS - YG</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Mi Gran Amor</v>
+        <v>UR HEARTBEAT (WHO DO U THINK ABOUT AT 2AM?)</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/mi-gran-amor/6773365775</v>
+        <v>https://music.apple.com/us/song/ur-heartbeat-who-do-u-think-about-at-2am/6765534140</v>
       </c>
       <c r="D130" t="str">
         <v>2026-06-01</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Mi Gran Amor - Single</v>
+        <v>A LITTLE VENGEANCE</v>
       </c>
       <c r="G130" t="str">
-        <v>3:37</v>
+        <v>2:50</v>
       </c>
       <c r="H130" t="str">
-        <v>Santana</v>
+        <v>Jessie Reyez</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/santana/217174</v>
+        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/mi-gran-amor/6773365236</v>
+        <v>https://music.apple.com/us/album/ur-heartbeat-who-do-u-think-about-at-2am/1895983502</v>
       </c>
       <c r="L130" t="str">
-        <v>Mi Gran Amor - Santana</v>
+        <v>UR HEARTBEAT (WHO DO U THINK ABOUT AT 2AM?) - Jessie Reyez</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>london</v>
+        <v>Joshua Tree</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/london/6770745672</v>
+        <v>https://music.apple.com/us/song/joshua-tree/6771859148</v>
       </c>
       <c r="D131" t="str">
         <v>2026-06-01</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>stardust - EP</v>
+        <v>Euphoria: Season 3 (HBO Original Series Soundtrack)</v>
       </c>
       <c r="G131" t="str">
-        <v>3:23</v>
+        <v>2:50</v>
       </c>
       <c r="H131" t="str">
-        <v>Freya Skye</v>
+        <v>Hans Zimmer</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/freya-skye/1541643053</v>
+        <v>https://music.apple.com/us/artist/hans-zimmer/454295032</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/london/6770745662</v>
+        <v>https://music.apple.com/us/album/joshua-tree/6771858464</v>
       </c>
       <c r="L131" t="str">
-        <v>london - Freya Skye</v>
+        <v>Joshua Tree - Hans Zimmer</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Caution</v>
+        <v>Mi Gran Amor</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/caution/6768487482</v>
+        <v>https://music.apple.com/us/song/mi-gran-amor/6773365775</v>
       </c>
       <c r="D132" t="str">
         <v>2026-06-01</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>K-POPS! (Music from and inspired by K-POPS! Motion Picture)</v>
+        <v>Mi Gran Amor - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>2:43</v>
+        <v>3:37</v>
       </c>
       <c r="H132" t="str">
-        <v>NMIXX</v>
+        <v>Santana</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/nmixx/1600411676</v>
+        <v>https://music.apple.com/us/artist/santana/217174</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/caution/6768487478</v>
+        <v>https://music.apple.com/us/album/mi-gran-amor/6773365236</v>
       </c>
       <c r="L132" t="str">
-        <v>Caution - NMIXX</v>
+        <v>Mi Gran Amor - Santana</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>LEMONADE (feat. Becky G)</v>
+        <v>london</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/lemonade-feat-becky-g/1893742425</v>
+        <v>https://music.apple.com/us/song/london/6770745672</v>
       </c>
       <c r="D133" t="str">
         <v>2026-06-01</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>LEMONADE - The 2nd Album</v>
+        <v>stardust - EP</v>
       </c>
       <c r="G133" t="str">
-        <v>3:07</v>
+        <v>3:23</v>
       </c>
       <c r="H133" t="str">
-        <v>aespa</v>
+        <v>Freya Skye</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
+        <v>https://music.apple.com/us/artist/freya-skye/1541643053</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/lemonade-feat-becky-g/1893742002</v>
+        <v>https://music.apple.com/us/album/london/6770745662</v>
       </c>
       <c r="L133" t="str">
-        <v>LEMONADE (feat. Becky G) - aespa</v>
+        <v>london - Freya Skye</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Take Me Back (Leave Me There)</v>
+        <v>Caution</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/take-me-back-leave-me-there/1892466278</v>
+        <v>https://music.apple.com/us/song/caution/6768487482</v>
       </c>
       <c r="D134" t="str">
         <v>2026-06-01</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Banks Of The Trinity</v>
+        <v>K-POPS! (Music from and inspired by K-POPS! Motion Picture)</v>
       </c>
       <c r="G134" t="str">
-        <v>2:58</v>
+        <v>2:43</v>
       </c>
       <c r="H134" t="str">
-        <v>Cody Johnson</v>
+        <v>NMIXX</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
+        <v>https://music.apple.com/us/artist/nmixx/1600411676</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/take-me-back-leave-me-there/1892465981</v>
+        <v>https://music.apple.com/us/album/caution/6768487478</v>
       </c>
       <c r="L134" t="str">
-        <v>Take Me Back (Leave Me There) - Cody Johnson</v>
+        <v>Caution - NMIXX</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Cheap Thrills</v>
+        <v>LEMONADE (feat. Becky G)</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/cheap-thrills/6771156732</v>
+        <v>https://music.apple.com/us/song/lemonade-feat-becky-g/1893742425</v>
       </c>
       <c r="D135" t="str">
         <v>2026-06-01</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Cheap Thrills - Single</v>
+        <v>LEMONADE - The 2nd Album</v>
       </c>
       <c r="G135" t="str">
-        <v>2:42</v>
+        <v>3:07</v>
       </c>
       <c r="H135" t="str">
-        <v>Gavin Adcock</v>
+        <v>aespa</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/gavin-adcock/1580645019</v>
+        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/cheap-thrills/6771156723</v>
+        <v>https://music.apple.com/us/album/lemonade-feat-becky-g/1893742002</v>
       </c>
       <c r="L135" t="str">
-        <v>Cheap Thrills - Gavin Adcock</v>
+        <v>LEMONADE (feat. Becky G) - aespa</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>ME VALE V</v>
+        <v>Take Me Back (Leave Me There)</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/me-vale-v/6769567844</v>
+        <v>https://music.apple.com/us/song/take-me-back-leave-me-there/1892466278</v>
       </c>
       <c r="D136" t="str">
         <v>2026-06-01</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>ACOMODO</v>
+        <v>Banks Of The Trinity</v>
       </c>
       <c r="G136" t="str">
-        <v>3:06</v>
+        <v>2:58</v>
       </c>
       <c r="H136" t="str">
-        <v>Tito Double P</v>
+        <v>Cody Johnson</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/tito-double-p/1690905306</v>
+        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/me-vale-v/6769567568</v>
+        <v>https://music.apple.com/us/album/take-me-back-leave-me-there/1892465981</v>
       </c>
       <c r="L136" t="str">
-        <v>ME VALE V - Tito Double P</v>
+        <v>Take Me Back (Leave Me There) - Cody Johnson</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Bug In The Cake</v>
+        <v>Cheap Thrills</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/bug-in-the-cake/1880470542</v>
+        <v>https://music.apple.com/us/song/cheap-thrills/6771156732</v>
       </c>
       <c r="D137" t="str">
         <v>2026-06-01</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Be Sweet To Me</v>
+        <v>Cheap Thrills - Single</v>
       </c>
       <c r="G137" t="str">
-        <v>2:48</v>
+        <v>2:42</v>
       </c>
       <c r="H137" t="str">
-        <v>Violet Grohl</v>
+        <v>Gavin Adcock</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
+        <v>https://music.apple.com/us/artist/gavin-adcock/1580645019</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/bug-in-the-cake/1880470537</v>
+        <v>https://music.apple.com/us/album/cheap-thrills/6771156723</v>
       </c>
       <c r="L137" t="str">
-        <v>Bug In The Cake - Violet Grohl</v>
+        <v>Cheap Thrills - Gavin Adcock</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Coil</v>
+        <v>ME VALE V</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/coil/6766858354</v>
+        <v>https://music.apple.com/us/song/me-vale-v/6769567844</v>
       </c>
       <c r="D138" t="str">
         <v>2026-06-01</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Rumspringa</v>
+        <v>ACOMODO</v>
       </c>
       <c r="G138" t="str">
-        <v>3:54</v>
+        <v>3:06</v>
       </c>
       <c r="H138" t="str">
-        <v>ear</v>
+        <v>Tito Double P</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/ear/1829661500</v>
+        <v>https://music.apple.com/us/artist/tito-double-p/1690905306</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/coil/6766858352</v>
+        <v>https://music.apple.com/us/album/me-vale-v/6769567568</v>
       </c>
       <c r="L138" t="str">
-        <v>Coil - ear</v>
+        <v>ME VALE V - Tito Double P</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Smugglers &amp; Scholars (feat. Killer Mike)</v>
+        <v>Bug In The Cake</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/smugglers-scholars-feat-killer-mike/6769424017</v>
+        <v>https://music.apple.com/us/song/bug-in-the-cake/1880470542</v>
       </c>
       <c r="D139" t="str">
         <v>2026-06-01</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Smugglers &amp; Scholars (feat. Killer Mike) - Single</v>
+        <v>Be Sweet To Me</v>
       </c>
       <c r="G139" t="str">
-        <v>3:30</v>
+        <v>2:48</v>
       </c>
       <c r="H139" t="str">
-        <v>Kneecap</v>
+        <v>Violet Grohl</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
+        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/smugglers-scholars-feat-killer-mike/6769423676</v>
+        <v>https://music.apple.com/us/album/bug-in-the-cake/1880470537</v>
       </c>
       <c r="L139" t="str">
-        <v>Smugglers &amp; Scholars (feat. Killer Mike) - Kneecap</v>
+        <v>Bug In The Cake - Violet Grohl</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Out of my Head</v>
+        <v>Coil</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/out-of-my-head/6767725166</v>
+        <v>https://music.apple.com/us/song/coil/6766858354</v>
       </c>
       <c r="D140" t="str">
         <v>2026-06-01</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>I Forgot / Out of my Head - Single</v>
+        <v>Rumspringa</v>
       </c>
       <c r="G140" t="str">
-        <v>3:04</v>
+        <v>3:54</v>
       </c>
       <c r="H140" t="str">
-        <v>Cara Delevingne</v>
+        <v>ear</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/cara-delevingne/1204798982</v>
+        <v>https://music.apple.com/us/artist/ear/1829661500</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/out-of-my-head/6767725156</v>
+        <v>https://music.apple.com/us/album/coil/6766858352</v>
       </c>
       <c r="L140" t="str">
-        <v>Out of my Head - Cara Delevingne</v>
+        <v>Coil - ear</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Passenger Princess</v>
+        <v>Smugglers &amp; Scholars (feat. Killer Mike)</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/passenger-princess/6771012228</v>
+        <v>https://music.apple.com/us/song/smugglers-scholars-feat-killer-mike/6769424017</v>
       </c>
       <c r="D141" t="str">
         <v>2026-06-01</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Passenger Princess - Single</v>
+        <v>Smugglers &amp; Scholars (feat. Killer Mike) - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>3:18</v>
+        <v>3:30</v>
       </c>
       <c r="H141" t="str">
-        <v>Perrie</v>
+        <v>Kneecap</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/perrie/1729865272</v>
+        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/passenger-princess/6771012223</v>
+        <v>https://music.apple.com/us/album/smugglers-scholars-feat-killer-mike/6769423676</v>
       </c>
       <c r="L141" t="str">
-        <v>Passenger Princess - Perrie</v>
+        <v>Smugglers &amp; Scholars (feat. Killer Mike) - Kneecap</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Man of the House</v>
+        <v>Out of my Head</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/man-of-the-house/1893733057</v>
+        <v>https://music.apple.com/us/song/out-of-my-head/6767725166</v>
       </c>
       <c r="D142" t="str">
         <v>2026-06-01</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>SE9</v>
+        <v>I Forgot / Out of my Head - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>2:35</v>
+        <v>3:04</v>
       </c>
       <c r="H142" t="str">
-        <v>Skye Newman</v>
+        <v>Cara Delevingne</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/skye-newman/1799174381</v>
+        <v>https://music.apple.com/us/artist/cara-delevingne/1204798982</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/man-of-the-house/1893733056</v>
+        <v>https://music.apple.com/us/album/out-of-my-head/6767725156</v>
       </c>
       <c r="L142" t="str">
-        <v>Man of the House - Skye Newman</v>
+        <v>Out of my Head - Cara Delevingne</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Beautiful Freeks</v>
+        <v>Passenger Princess</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/beautiful-freeks/6764602396</v>
+        <v>https://music.apple.com/us/song/passenger-princess/6771012228</v>
       </c>
       <c r="D143" t="str">
         <v>2026-06-01</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Beautiful Freeks - Single</v>
+        <v>Passenger Princess - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>2:37</v>
+        <v>3:18</v>
       </c>
       <c r="H143" t="str">
-        <v>MEEK</v>
+        <v>Perrie</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/meek/1784432868</v>
+        <v>https://music.apple.com/us/artist/perrie/1729865272</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/beautiful-freeks/6764602393</v>
+        <v>https://music.apple.com/us/album/passenger-princess/6771012223</v>
       </c>
       <c r="L143" t="str">
-        <v>Beautiful Freeks - MEEK</v>
+        <v>Passenger Princess - Perrie</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Slave to the Rithm (feat. Bring Me The Horizon) [I Hate Models Never Alone Remix]</v>
+        <v>Man of the House</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/slave-to-the-rithm-feat-bring-me-the-horizon-i/6771972616</v>
+        <v>https://music.apple.com/us/song/man-of-the-house/1893733057</v>
       </c>
       <c r="D144" t="str">
         <v>2026-06-01</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Slave to the Rithm (I Hate Models Never Alone Remix) [feat. Bring Me The Horizon] - Single</v>
+        <v>SE9</v>
       </c>
       <c r="G144" t="str">
-        <v>4:34</v>
+        <v>2:35</v>
       </c>
       <c r="H144" t="str">
-        <v>ILLENIUM</v>
+        <v>Skye Newman</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/illenium/645420096</v>
+        <v>https://music.apple.com/us/artist/skye-newman/1799174381</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/slave-to-the-rithm-feat-bring-me-the-horizon-i/6771972613</v>
+        <v>https://music.apple.com/us/album/man-of-the-house/1893733056</v>
       </c>
       <c r="L144" t="str">
-        <v>Slave to the Rithm (feat. Bring Me The Horizon) [I Hate Models Never Alone Remix] - ILLENIUM</v>
+        <v>Man of the House - Skye Newman</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Beg For Me (JADE Remix)</v>
+        <v>Beautiful Freeks</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/beg-for-me-jade-remix/6771474203</v>
+        <v>https://music.apple.com/us/song/beautiful-freeks/6764602396</v>
       </c>
       <c r="D145" t="str">
         <v>2026-06-01</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Beg For Me (Remix) - Single</v>
+        <v>Beautiful Freeks - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>2:50</v>
+        <v>2:37</v>
       </c>
       <c r="H145" t="str">
-        <v>Lily Allen</v>
+        <v>MEEK</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/lily-allen/157063999</v>
+        <v>https://music.apple.com/us/artist/meek/1784432868</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/beg-for-me-jade-remix/6771474201</v>
+        <v>https://music.apple.com/us/album/beautiful-freeks/6764602393</v>
       </c>
       <c r="L145" t="str">
-        <v>Beg For Me (JADE Remix) - Lily Allen</v>
+        <v>Beautiful Freeks - MEEK</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>ABOVE IT</v>
+        <v>Slave to the Rithm (feat. Bring Me The Horizon) [I Hate Models Never Alone Remix]</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/above-it/6766248703</v>
+        <v>https://music.apple.com/us/song/slave-to-the-rithm-feat-bring-me-the-horizon-i/6771972616</v>
       </c>
       <c r="D146" t="str">
         <v>2026-06-01</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>GET THE TABLES - Single</v>
+        <v>Slave to the Rithm (I Hate Models Never Alone Remix) [feat. Bring Me The Horizon] - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>1:45</v>
+        <v>4:34</v>
       </c>
       <c r="H146" t="str">
-        <v>Andy Mineo</v>
+        <v>ILLENIUM</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/andy-mineo/257538441</v>
+        <v>https://music.apple.com/us/artist/illenium/645420096</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/above-it/6766248699</v>
+        <v>https://music.apple.com/us/album/slave-to-the-rithm-feat-bring-me-the-horizon-i/6771972613</v>
       </c>
       <c r="L146" t="str">
-        <v>ABOVE IT - Andy Mineo</v>
+        <v>Slave to the Rithm (feat. Bring Me The Horizon) [I Hate Models Never Alone Remix] - ILLENIUM</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>THE JESUS GENERATION</v>
+        <v>Beg For Me (JADE Remix)</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/the-jesus-generation/6773948895</v>
+        <v>https://music.apple.com/us/song/beg-for-me-jade-remix/6771474203</v>
       </c>
       <c r="D147" t="str">
         <v>2026-06-01</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>THE JESUS GENERATION - Single</v>
+        <v>Beg For Me (Remix) - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>4:15</v>
+        <v>2:50</v>
       </c>
       <c r="H147" t="str">
-        <v>Forrest Frank</v>
+        <v>Lily Allen</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/forrest-frank/1436657314</v>
+        <v>https://music.apple.com/us/artist/lily-allen/157063999</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/the-jesus-generation/6773948742</v>
+        <v>https://music.apple.com/us/album/beg-for-me-jade-remix/6771474201</v>
       </c>
       <c r="L147" t="str">
-        <v>THE JESUS GENERATION - Forrest Frank</v>
+        <v>Beg For Me (JADE Remix) - Lily Allen</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Is It Over Now?</v>
+        <v>ABOVE IT</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/is-it-over-now/6767564750</v>
+        <v>https://music.apple.com/us/song/above-it/6766248703</v>
       </c>
       <c r="D148" t="str">
         <v>2026-06-01</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Is It Over Now? - Single</v>
+        <v>GET THE TABLES - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>3:39</v>
+        <v>1:45</v>
       </c>
       <c r="H148" t="str">
-        <v>Elderbrook</v>
+        <v>Andy Mineo</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/elderbrook/736829657</v>
+        <v>https://music.apple.com/us/artist/andy-mineo/257538441</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/is-it-over-now/6767564746</v>
+        <v>https://music.apple.com/us/album/above-it/6766248699</v>
       </c>
       <c r="L148" t="str">
-        <v>Is It Over Now? - Elderbrook</v>
+        <v>ABOVE IT - Andy Mineo</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>12 Steps</v>
+        <v>THE JESUS GENERATION</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/12-steps/6769559623</v>
+        <v>https://music.apple.com/us/song/the-jesus-generation/6773948895</v>
       </c>
       <c r="D149" t="str">
         <v>2026-06-01</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>12 Steps - Single</v>
+        <v>THE JESUS GENERATION - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>3:11</v>
+        <v>4:15</v>
       </c>
       <c r="H149" t="str">
-        <v>Dexter and The Moonrocks</v>
+        <v>Forrest Frank</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/dexter-and-the-moonrocks/1581657500</v>
+        <v>https://music.apple.com/us/artist/forrest-frank/1436657314</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/12-steps/6769559618</v>
+        <v>https://music.apple.com/us/album/the-jesus-generation/6773948742</v>
       </c>
       <c r="L149" t="str">
-        <v>12 Steps - Dexter and The Moonrocks</v>
+        <v>THE JESUS GENERATION - Forrest Frank</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Over And Over</v>
+        <v>Is It Over Now?</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/over-and-over/6771585908</v>
+        <v>https://music.apple.com/us/song/is-it-over-now/6767564750</v>
       </c>
       <c r="D150" t="str">
         <v>2026-06-01</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>It's A Dying Art</v>
+        <v>Is It Over Now? - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>4:38</v>
+        <v>3:39</v>
       </c>
       <c r="H150" t="str">
-        <v>Little Big Town</v>
+        <v>Elderbrook</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/little-big-town/513770</v>
+        <v>https://music.apple.com/us/artist/elderbrook/736829657</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/over-and-over/6771585889</v>
+        <v>https://music.apple.com/us/album/is-it-over-now/6767564746</v>
       </c>
       <c r="L150" t="str">
-        <v>Over And Over - Little Big Town</v>
+        <v>Is It Over Now? - Elderbrook</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>AMAPOLA</v>
+        <v>12 Steps</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/amapola/6769560428</v>
+        <v>https://music.apple.com/us/song/12-steps/6769559623</v>
       </c>
       <c r="D151" t="str">
         <v>2026-06-01</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Ricky y Mau</v>
+        <v>12 Steps - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>2:22</v>
+        <v>3:11</v>
       </c>
       <c r="H151" t="str">
-        <v>Mau y Ricky</v>
+        <v>Dexter and The Moonrocks</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/mau-y-ricky/1096068683</v>
+        <v>https://music.apple.com/us/artist/dexter-and-the-moonrocks/1581657500</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/amapola/6769559985</v>
+        <v>https://music.apple.com/us/album/12-steps/6769559618</v>
       </c>
       <c r="L151" t="str">
-        <v>AMAPOLA - Mau y Ricky</v>
+        <v>12 Steps - Dexter and The Moonrocks</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Mad About It</v>
+        <v>Over And Over</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/mad-about-it/6767425272</v>
+        <v>https://music.apple.com/us/song/over-and-over/6771585908</v>
       </c>
       <c r="D152" t="str">
         <v>2026-06-01</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Mad About It - Single</v>
+        <v>It's A Dying Art</v>
       </c>
       <c r="G152" t="str">
-        <v>2:37</v>
+        <v>4:38</v>
       </c>
       <c r="H152" t="str">
-        <v>Dasha</v>
+        <v>Little Big Town</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/dasha/1462663731</v>
+        <v>https://music.apple.com/us/artist/little-big-town/513770</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/mad-about-it/6767425271</v>
+        <v>https://music.apple.com/us/album/over-and-over/6771585889</v>
       </c>
       <c r="L152" t="str">
-        <v>Mad About It - Dasha</v>
+        <v>Over And Over - Little Big Town</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Love’s a Gun</v>
+        <v>AMAPOLA</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/loves-a-gun/6771898253</v>
+        <v>https://music.apple.com/us/song/amapola/6769560428</v>
       </c>
       <c r="D153" t="str">
         <v>2026-06-01</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Love’s a Gun - Single</v>
+        <v>Ricky y Mau</v>
       </c>
       <c r="G153" t="str">
-        <v>2:59</v>
+        <v>2:22</v>
       </c>
       <c r="H153" t="str">
-        <v>Daniel Seavey</v>
+        <v>Mau y Ricky</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/daniel-seavey/1646124302</v>
+        <v>https://music.apple.com/us/artist/mau-y-ricky/1096068683</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/loves-a-gun/6771897951</v>
+        <v>https://music.apple.com/us/album/amapola/6769559985</v>
       </c>
       <c r="L153" t="str">
-        <v>Love’s a Gun - Daniel Seavey</v>
+        <v>AMAPOLA - Mau y Ricky</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Long Story Short</v>
+        <v>Mad About It</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/long-story-short/6770700866</v>
+        <v>https://music.apple.com/us/song/mad-about-it/6767425272</v>
       </c>
       <c r="D154" t="str">
         <v>2026-06-01</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Long Story Short - Single</v>
+        <v>Mad About It - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>2:48</v>
+        <v>2:37</v>
       </c>
       <c r="H154" t="str">
-        <v>Knox</v>
+        <v>Dasha</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/knox/1547519433</v>
+        <v>https://music.apple.com/us/artist/dasha/1462663731</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/long-story-short/6770700853</v>
+        <v>https://music.apple.com/us/album/mad-about-it/6767425271</v>
       </c>
       <c r="L154" t="str">
-        <v>Long Story Short - Knox</v>
+        <v>Mad About It - Dasha</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>blue jeans</v>
+        <v>Love’s a Gun</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/blue-jeans/6770529591</v>
+        <v>https://music.apple.com/us/song/loves-a-gun/6771898253</v>
       </c>
       <c r="D155" t="str">
         <v>2026-06-01</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>blue jeans - Single</v>
+        <v>Love’s a Gun - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>2:37</v>
+        <v>2:59</v>
       </c>
       <c r="H155" t="str">
-        <v>Nightly</v>
+        <v>Daniel Seavey</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/nightly/352310972</v>
+        <v>https://music.apple.com/us/artist/daniel-seavey/1646124302</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/blue-jeans/6770529589</v>
+        <v>https://music.apple.com/us/album/loves-a-gun/6771897951</v>
       </c>
       <c r="L155" t="str">
-        <v>blue jeans - Nightly</v>
+        <v>Love’s a Gun - Daniel Seavey</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Que Gacho</v>
+        <v>Long Story Short</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/que-gacho/6770628420</v>
+        <v>https://music.apple.com/us/song/long-story-short/6770700866</v>
       </c>
       <c r="D156" t="str">
         <v>2026-06-01</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Que Gacho - Single</v>
+        <v>Long Story Short - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>3:13</v>
+        <v>2:48</v>
       </c>
       <c r="H156" t="str">
-        <v>Luis R Conriquez</v>
+        <v>Knox</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
+        <v>https://music.apple.com/us/artist/knox/1547519433</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/que-gacho/6770628419</v>
+        <v>https://music.apple.com/us/album/long-story-short/6770700853</v>
       </c>
       <c r="L156" t="str">
-        <v>Que Gacho - Luis R Conriquez</v>
+        <v>Long Story Short - Knox</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>same God</v>
+        <v>blue jeans</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/same-god/1878232616</v>
+        <v>https://music.apple.com/us/song/blue-jeans/6770529591</v>
       </c>
       <c r="D157" t="str">
         <v>2026-06-01</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>I HOPE THIS HELPS</v>
+        <v>blue jeans - Single</v>
       </c>
       <c r="G157" t="str">
-        <v>3:34</v>
+        <v>2:37</v>
       </c>
       <c r="H157" t="str">
-        <v>Alana Springsteen</v>
+        <v>Nightly</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/alana-springsteen/1309335606</v>
+        <v>https://music.apple.com/us/artist/nightly/352310972</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/same-god/1878232194</v>
+        <v>https://music.apple.com/us/album/blue-jeans/6770529589</v>
       </c>
       <c r="L157" t="str">
-        <v>same God - Alana Springsteen</v>
+        <v>blue jeans - Nightly</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>emotional swaggage</v>
+        <v>Que Gacho</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/emotional-swaggage/6767397453</v>
+        <v>https://music.apple.com/us/song/que-gacho/6770628420</v>
       </c>
       <c r="D158" t="str">
         <v>2026-06-01</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>IDCASH</v>
+        <v>Que Gacho - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>2:12</v>
+        <v>3:13</v>
       </c>
       <c r="H158" t="str">
-        <v>IDK</v>
+        <v>Luis R Conriquez</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/idk/1578186947</v>
+        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/emotional-swaggage/6767397348</v>
+        <v>https://music.apple.com/us/album/que-gacho/6770628419</v>
       </c>
       <c r="L158" t="str">
-        <v>emotional swaggage - IDK</v>
+        <v>Que Gacho - Luis R Conriquez</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Baby Driver</v>
+        <v>same God</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/baby-driver/6769152279</v>
+        <v>https://music.apple.com/us/song/same-god/1878232616</v>
       </c>
       <c r="D159" t="str">
         <v>2026-06-01</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Baby Driver - Single</v>
+        <v>I HOPE THIS HELPS</v>
       </c>
       <c r="G159" t="str">
-        <v>3:36</v>
+        <v>3:34</v>
       </c>
       <c r="H159" t="str">
-        <v>070 Shake</v>
+        <v>Alana Springsteen</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/070-shake/1097177293</v>
+        <v>https://music.apple.com/us/artist/alana-springsteen/1309335606</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/baby-driver/6769152273</v>
+        <v>https://music.apple.com/us/album/same-god/1878232194</v>
       </c>
       <c r="L159" t="str">
-        <v>Baby Driver - 070 Shake</v>
+        <v>same God - Alana Springsteen</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>More! More! More!</v>
+        <v>emotional swaggage</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/more-more-more/6770600105</v>
+        <v>https://music.apple.com/us/song/emotional-swaggage/6767397453</v>
       </c>
       <c r="D160" t="str">
         <v>2026-06-01</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>REBECCA</v>
+        <v>IDCASH</v>
       </c>
       <c r="G160" t="str">
-        <v>2:55</v>
+        <v>2:12</v>
       </c>
       <c r="H160" t="str">
-        <v>Becky Hill</v>
+        <v>IDK</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/becky-hill/533839517</v>
+        <v>https://music.apple.com/us/artist/idk/1578186947</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/more-more-more/6770600098</v>
+        <v>https://music.apple.com/us/album/emotional-swaggage/6767397348</v>
       </c>
       <c r="L160" t="str">
-        <v>More! More! More! - Becky Hill</v>
+        <v>emotional swaggage - IDK</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Young Again</v>
+        <v>Baby Driver</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/young-again/1877229743</v>
+        <v>https://music.apple.com/us/song/baby-driver/6769152279</v>
       </c>
       <c r="D161" t="str">
         <v>2026-06-01</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>EI8HT</v>
+        <v>Baby Driver - Single</v>
       </c>
       <c r="G161" t="str">
         <v>3:36</v>
       </c>
       <c r="H161" t="str">
-        <v>Shinedown</v>
+        <v>070 Shake</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/shinedown/1883858</v>
+        <v>https://music.apple.com/us/artist/070-shake/1097177293</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/young-again/1877229738</v>
+        <v>https://music.apple.com/us/album/baby-driver/6769152273</v>
       </c>
       <c r="L161" t="str">
-        <v>Young Again - Shinedown</v>
+        <v>Baby Driver - 070 Shake</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>skinny dip</v>
+        <v>More! More! More!</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/skinny-dip/6769856281</v>
+        <v>https://music.apple.com/us/song/more-more-more/6770600105</v>
       </c>
       <c r="D162" t="str">
         <v>2026-06-01</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>skinny dip - Single</v>
+        <v>REBECCA</v>
       </c>
       <c r="G162" t="str">
-        <v>3:12</v>
+        <v>2:55</v>
       </c>
       <c r="H162" t="str">
-        <v>almost monday</v>
+        <v>Becky Hill</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/almost-monday/1300723925</v>
+        <v>https://music.apple.com/us/artist/becky-hill/533839517</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/skinny-dip/6769855907</v>
+        <v>https://music.apple.com/us/album/more-more-more/6770600098</v>
       </c>
       <c r="L162" t="str">
-        <v>skinny dip - almost monday</v>
+        <v>More! More! More! - Becky Hill</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>girls like girls (from the motion picture)</v>
+        <v>Young Again</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/girls-like-girls-from-the-motion-picture/1893704575</v>
+        <v>https://music.apple.com/us/song/young-again/1877229743</v>
       </c>
       <c r="D163" t="str">
         <v>2026-06-01</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>girls like girls the album</v>
+        <v>EI8HT</v>
       </c>
       <c r="G163" t="str">
-        <v>4:14</v>
+        <v>3:36</v>
       </c>
       <c r="H163" t="str">
-        <v>Hayley Kiyoko</v>
+        <v>Shinedown</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/hayley-kiyoko/325569584</v>
+        <v>https://music.apple.com/us/artist/shinedown/1883858</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/girls-like-girls-from-the-motion-picture/1893704396</v>
+        <v>https://music.apple.com/us/album/young-again/1877229738</v>
       </c>
       <c r="L163" t="str">
-        <v>girls like girls (from the motion picture) - Hayley Kiyoko</v>
+        <v>Young Again - Shinedown</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Better Off</v>
+        <v>skinny dip</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/better-off/6772045367</v>
+        <v>https://music.apple.com/us/song/skinny-dip/6769856281</v>
       </c>
       <c r="D164" t="str">
         <v>2026-06-01</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Stages</v>
+        <v>skinny dip - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>3:16</v>
+        <v>3:12</v>
       </c>
       <c r="H164" t="str">
-        <v>Lauren Alaina</v>
+        <v>almost monday</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/lauren-alaina/425028816</v>
+        <v>https://music.apple.com/us/artist/almost-monday/1300723925</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/better-off/6772044978</v>
+        <v>https://music.apple.com/us/album/skinny-dip/6769855907</v>
       </c>
       <c r="L164" t="str">
-        <v>Better Off - Lauren Alaina</v>
+        <v>skinny dip - almost monday</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Everythang Pinka (feat. Teezo Touchdown)</v>
+        <v>girls like girls (from the motion picture)</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/everythang-pinka-feat-teezo-touchdown/6772026590</v>
+        <v>https://music.apple.com/us/song/girls-like-girls-from-the-motion-picture/1893704575</v>
       </c>
       <c r="D165" t="str">
         <v>2026-06-01</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Everythang Pinka (feat. Teezo Touchdown) - Single</v>
+        <v>girls like girls the album</v>
       </c>
       <c r="G165" t="str">
-        <v>2:48</v>
+        <v>4:14</v>
       </c>
       <c r="H165" t="str">
-        <v>Monaleo</v>
+        <v>Hayley Kiyoko</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/monaleo/1495603374</v>
+        <v>https://music.apple.com/us/artist/hayley-kiyoko/325569584</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/everythang-pinka-feat-teezo-touchdown/6772026586</v>
+        <v>https://music.apple.com/us/album/girls-like-girls-from-the-motion-picture/1893704396</v>
       </c>
       <c r="L165" t="str">
-        <v>Everythang Pinka (feat. Teezo Touchdown) - Monaleo</v>
+        <v>girls like girls (from the motion picture) - Hayley Kiyoko</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Lost in translation...</v>
+        <v>Better Off</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/lost-in-translation/1870971556</v>
+        <v>https://music.apple.com/us/song/better-off/6772045367</v>
       </c>
       <c r="D166" t="str">
         <v>2026-06-01</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Dream inside a dream…</v>
+        <v>Stages</v>
       </c>
       <c r="G166" t="str">
-        <v>3:30</v>
+        <v>3:16</v>
       </c>
       <c r="H166" t="str">
-        <v>R3HAB</v>
+        <v>Lauren Alaina</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/r3hab/331900515</v>
+        <v>https://music.apple.com/us/artist/lauren-alaina/425028816</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/lost-in-translation/1870971550</v>
+        <v>https://music.apple.com/us/album/better-off/6772044978</v>
       </c>
       <c r="L166" t="str">
-        <v>Lost in translation... - R3HAB</v>
+        <v>Better Off - Lauren Alaina</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Call Security</v>
+        <v>Everythang Pinka (feat. Teezo Touchdown)</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/call-security/6769296603</v>
+        <v>https://music.apple.com/us/song/everythang-pinka-feat-teezo-touchdown/6772026590</v>
       </c>
       <c r="D167" t="str">
         <v>2026-06-01</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>U, Me &amp; My Ego</v>
+        <v>Everythang Pinka (feat. Teezo Touchdown) - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>3:22</v>
+        <v>2:48</v>
       </c>
       <c r="H167" t="str">
-        <v>Chxrry</v>
+        <v>Monaleo</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/chxrry/1520135642</v>
+        <v>https://music.apple.com/us/artist/monaleo/1495603374</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/call-security/6769296591</v>
+        <v>https://music.apple.com/us/album/everythang-pinka-feat-teezo-touchdown/6772026586</v>
       </c>
       <c r="L167" t="str">
-        <v>Call Security - Chxrry</v>
+        <v>Everythang Pinka (feat. Teezo Touchdown) - Monaleo</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>chaotic</v>
+        <v>Lost in translation...</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/chaotic/6767629281</v>
+        <v>https://music.apple.com/us/song/lost-in-translation/1870971556</v>
       </c>
       <c r="D168" t="str">
         <v>2026-06-01</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>scars to prove it</v>
+        <v>Dream inside a dream…</v>
       </c>
       <c r="G168" t="str">
-        <v>3:14</v>
+        <v>3:30</v>
       </c>
       <c r="H168" t="str">
-        <v>Hailey Picardi</v>
+        <v>R3HAB</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
+        <v>https://music.apple.com/us/artist/r3hab/331900515</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/chaotic/6767626506</v>
+        <v>https://music.apple.com/us/album/lost-in-translation/1870971550</v>
       </c>
       <c r="L168" t="str">
-        <v>chaotic - Hailey Picardi</v>
+        <v>Lost in translation... - R3HAB</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Keep It To Yourself</v>
+        <v>Call Security</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/keep-it-to-yourself/6771099675</v>
+        <v>https://music.apple.com/us/song/call-security/6769296603</v>
       </c>
       <c r="D169" t="str">
         <v>2026-06-01</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>LOVE IS THE LAW</v>
+        <v>U, Me &amp; My Ego</v>
       </c>
       <c r="G169" t="str">
-        <v>4:17</v>
+        <v>3:22</v>
       </c>
       <c r="H169" t="str">
-        <v>Love Spells</v>
+        <v>Chxrry</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/love-spells/1597025563</v>
+        <v>https://music.apple.com/us/artist/chxrry/1520135642</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/keep-it-to-yourself/6771099661</v>
+        <v>https://music.apple.com/us/album/call-security/6769296591</v>
       </c>
       <c r="L169" t="str">
-        <v>Keep It To Yourself - Love Spells</v>
+        <v>Call Security - Chxrry</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Something to Someone</v>
+        <v>chaotic</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/something-to-someone/6767255424</v>
+        <v>https://music.apple.com/us/song/chaotic/6767629281</v>
       </c>
       <c r="D170" t="str">
         <v>2026-06-01</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Something to Someone - Single</v>
+        <v>scars to prove it</v>
       </c>
       <c r="G170" t="str">
-        <v>3:55</v>
+        <v>3:14</v>
       </c>
       <c r="H170" t="str">
-        <v>Max McNown</v>
+        <v>Hailey Picardi</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
+        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/something-to-someone/1896445136</v>
+        <v>https://music.apple.com/us/album/chaotic/6767626506</v>
       </c>
       <c r="L170" t="str">
-        <v>Something to Someone - Max McNown</v>
+        <v>chaotic - Hailey Picardi</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Green Screen (1pm)</v>
+        <v>Keep It To Yourself</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/green-screen-1pm/6766279426</v>
+        <v>https://music.apple.com/us/song/keep-it-to-yourself/6771099675</v>
       </c>
       <c r="D171" t="str">
         <v>2026-06-01</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>The Hours: High Noon</v>
+        <v>LOVE IS THE LAW</v>
       </c>
       <c r="G171" t="str">
-        <v>2:10</v>
+        <v>4:17</v>
       </c>
       <c r="H171" t="str">
-        <v>Cautious Clay</v>
+        <v>Love Spells</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/cautious-clay/1064628701</v>
+        <v>https://music.apple.com/us/artist/love-spells/1597025563</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/green-screen-1pm/1896264236</v>
+        <v>https://music.apple.com/us/album/keep-it-to-yourself/6771099661</v>
       </c>
       <c r="L171" t="str">
-        <v>Green Screen (1pm) - Cautious Clay</v>
+        <v>Keep It To Yourself - Love Spells</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Scoreboard</v>
+        <v>Something to Someone</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/scoreboard/6767255746</v>
+        <v>https://music.apple.com/us/song/something-to-someone/6767255424</v>
       </c>
       <c r="D172" t="str">
         <v>2026-06-01</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>I Just Wanna Be Loved</v>
+        <v>Something to Someone - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>3:24</v>
+        <v>3:55</v>
       </c>
       <c r="H172" t="str">
-        <v>Gabriella Rose</v>
+        <v>Max McNown</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/gabriella-rose/645706232</v>
+        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/scoreboard/1896445371</v>
+        <v>https://music.apple.com/us/album/something-to-someone/1896445136</v>
       </c>
       <c r="L172" t="str">
-        <v>Scoreboard - Gabriella Rose</v>
+        <v>Something to Someone - Max McNown</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>High</v>
+        <v>Green Screen (1pm)</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/high/6773775211</v>
+        <v>https://music.apple.com/us/song/green-screen-1pm/6766279426</v>
       </c>
       <c r="D173" t="str">
         <v>2026-06-01</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Payback Is A Dog (EP)</v>
+        <v>The Hours: High Noon</v>
       </c>
       <c r="G173" t="str">
-        <v>2:55</v>
+        <v>2:10</v>
       </c>
       <c r="H173" t="str">
-        <v>Nia Smith</v>
+        <v>Cautious Clay</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/nia-smith/1755576018</v>
+        <v>https://music.apple.com/us/artist/cautious-clay/1064628701</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/high/6773775203</v>
+        <v>https://music.apple.com/us/album/green-screen-1pm/1896264236</v>
       </c>
       <c r="L173" t="str">
-        <v>High - Nia Smith</v>
+        <v>Green Screen (1pm) - Cautious Clay</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Ay Gyal</v>
+        <v>Scoreboard</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/ay-gyal/6771885805</v>
+        <v>https://music.apple.com/us/song/scoreboard/6767255746</v>
       </c>
       <c r="D174" t="str">
         <v>2026-06-01</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Ay Gyal - Single</v>
+        <v>I Just Wanna Be Loved</v>
       </c>
       <c r="G174" t="str">
-        <v>2:12</v>
+        <v>3:24</v>
       </c>
       <c r="H174" t="str">
-        <v>1Ski OG</v>
+        <v>Gabriella Rose</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
+        <v>https://music.apple.com/us/artist/gabriella-rose/645706232</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/ay-gyal/6771885803</v>
+        <v>https://music.apple.com/us/album/scoreboard/1896445371</v>
       </c>
       <c r="L174" t="str">
-        <v>Ay Gyal - 1Ski OG</v>
+        <v>Scoreboard - Gabriella Rose</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>always knew</v>
+        <v>High</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/always-knew/6762864274</v>
+        <v>https://music.apple.com/us/song/high/6773775211</v>
       </c>
       <c r="D175" t="str">
         <v>2026-06-01</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>always knew - Single</v>
+        <v>Payback Is A Dog (EP)</v>
       </c>
       <c r="G175" t="str">
-        <v>3:25</v>
+        <v>2:55</v>
       </c>
       <c r="H175" t="str">
-        <v>Biscits</v>
+        <v>Nia Smith</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/biscits/1185553226</v>
+        <v>https://music.apple.com/us/artist/nia-smith/1755576018</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/always-knew/1895047928</v>
+        <v>https://music.apple.com/us/album/high/6773775203</v>
       </c>
       <c r="L175" t="str">
-        <v>always knew - Biscits</v>
+        <v>High - Nia Smith</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Cigarette Burns</v>
+        <v>Ay Gyal</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/cigarette-burns/6770691000</v>
+        <v>https://music.apple.com/us/song/ay-gyal/6771885805</v>
       </c>
       <c r="D176" t="str">
         <v>2026-06-01</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Heartland Rock and Roll</v>
+        <v>Ay Gyal - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>2:41</v>
+        <v>2:12</v>
       </c>
       <c r="H176" t="str">
-        <v>Corey Kent</v>
+        <v>1Ski OG</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/corey-kent/1171544097</v>
+        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/cigarette-burns/6770690867</v>
+        <v>https://music.apple.com/us/album/ay-gyal/6771885803</v>
       </c>
       <c r="L176" t="str">
-        <v>Cigarette Burns - Corey Kent</v>
+        <v>Ay Gyal - 1Ski OG</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Let You Down</v>
+        <v>always knew</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/let-you-down/6773362320</v>
+        <v>https://music.apple.com/us/song/always-knew/6762864274</v>
       </c>
       <c r="D177" t="str">
         <v>2026-06-01</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>El Relevo</v>
+        <v>always knew - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>4:14</v>
+        <v>3:25</v>
       </c>
       <c r="H177" t="str">
-        <v>Luis Figueroa</v>
+        <v>Biscits</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/luis-figueroa/395266944</v>
+        <v>https://music.apple.com/us/artist/biscits/1185553226</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/let-you-down/6773362108</v>
+        <v>https://music.apple.com/us/album/always-knew/1895047928</v>
       </c>
       <c r="L177" t="str">
-        <v>Let You Down - Luis Figueroa</v>
+        <v>always knew - Biscits</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Starless</v>
+        <v>Cigarette Burns</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/starless/6770568779</v>
+        <v>https://music.apple.com/us/song/cigarette-burns/6770691000</v>
       </c>
       <c r="D178" t="str">
         <v>2026-06-01</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Starless - Single</v>
+        <v>Heartland Rock and Roll</v>
       </c>
       <c r="G178" t="str">
-        <v>4:32</v>
+        <v>2:41</v>
       </c>
       <c r="H178" t="str">
-        <v>A Perfect Circle</v>
+        <v>Corey Kent</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/a-perfect-circle/652503</v>
+        <v>https://music.apple.com/us/artist/corey-kent/1171544097</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/starless/6770568776</v>
+        <v>https://music.apple.com/us/album/cigarette-burns/6770690867</v>
       </c>
       <c r="L178" t="str">
-        <v>Starless - A Perfect Circle</v>
+        <v>Cigarette Burns - Corey Kent</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Looking For You</v>
+        <v>Let You Down</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/looking-for-you/6768355609</v>
+        <v>https://music.apple.com/us/song/let-you-down/6773362320</v>
       </c>
       <c r="D179" t="str">
         <v>2026-06-01</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Looking For You - Single</v>
+        <v>El Relevo</v>
       </c>
       <c r="G179" t="str">
-        <v>3:19</v>
+        <v>4:14</v>
       </c>
       <c r="H179" t="str">
-        <v>Gable Price and Friends</v>
+        <v>Luis Figueroa</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/gable-price-and-friends/1441378212</v>
+        <v>https://music.apple.com/us/artist/luis-figueroa/395266944</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/looking-for-you/6768355596</v>
+        <v>https://music.apple.com/us/album/let-you-down/6773362108</v>
       </c>
       <c r="L179" t="str">
-        <v>Looking For You - Gable Price and Friends</v>
+        <v>Let You Down - Luis Figueroa</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>FOCUSED</v>
+        <v>Starless</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/focused/1887909237</v>
+        <v>https://music.apple.com/us/song/starless/6770568779</v>
       </c>
       <c r="D180" t="str">
         <v>2026-06-01</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>FOCUSED - Single</v>
+        <v>Starless - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>2:23</v>
+        <v>4:32</v>
       </c>
       <c r="H180" t="str">
-        <v>Shepherd</v>
+        <v>A Perfect Circle</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/shepherd/1192803216</v>
+        <v>https://music.apple.com/us/artist/a-perfect-circle/652503</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/focused/1887909236</v>
+        <v>https://music.apple.com/us/album/starless/6770568776</v>
       </c>
       <c r="L180" t="str">
-        <v>FOCUSED - Shepherd</v>
+        <v>Starless - A Perfect Circle</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Tú Ni En Cuenta</v>
+        <v>Looking For You</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/tu-ni-en-cuenta/6767701804</v>
+        <v>https://music.apple.com/us/song/looking-for-you/6768355609</v>
       </c>
       <c r="D181" t="str">
         <v>2026-06-01</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Tú Ni En Cuenta - Single</v>
+        <v>Looking For You - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>3:23</v>
+        <v>3:19</v>
       </c>
       <c r="H181" t="str">
-        <v>Banda MS de Sergio Lizárraga</v>
+        <v>Gable Price and Friends</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/banda-ms-de-sergio-liz%C3%A1rraga/413048014</v>
+        <v>https://music.apple.com/us/artist/gable-price-and-friends/1441378212</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/tu-ni-en-cuenta/6767701803</v>
+        <v>https://music.apple.com/us/album/looking-for-you/6768355596</v>
       </c>
       <c r="L181" t="str">
-        <v>Tú Ni En Cuenta - Banda MS de Sergio Lizárraga</v>
+        <v>Looking For You - Gable Price and Friends</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>dream state</v>
+        <v>FOCUSED</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/dream-state/6765596009</v>
+        <v>https://music.apple.com/us/song/focused/1887909237</v>
       </c>
       <c r="D182" t="str">
         <v>2026-06-01</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>dream state - Single</v>
+        <v>FOCUSED - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>4:01</v>
+        <v>2:23</v>
       </c>
       <c r="H182" t="str">
-        <v>Martin Luke Brown</v>
+        <v>Shepherd</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/martin-luke-brown/883292185</v>
+        <v>https://music.apple.com/us/artist/shepherd/1192803216</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/dream-state/1896004790</v>
+        <v>https://music.apple.com/us/album/focused/1887909236</v>
       </c>
       <c r="L182" t="str">
-        <v>dream state - Martin Luke Brown</v>
+        <v>FOCUSED - Shepherd</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Needle (feat. Spencer Cullum)</v>
+        <v>Tú Ni En Cuenta</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/needle-feat-spencer-cullum/6767618217</v>
+        <v>https://music.apple.com/us/song/tu-ni-en-cuenta/6767701804</v>
       </c>
       <c r="D183" t="str">
         <v>2026-06-01</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Needle (feat. Spencer Cullum) - Single</v>
+        <v>Tú Ni En Cuenta - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>3:39</v>
+        <v>3:23</v>
       </c>
       <c r="H183" t="str">
-        <v>Mynolia</v>
+        <v>Banda MS de Sergio Lizárraga</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/mynolia/1444347510</v>
+        <v>https://music.apple.com/us/artist/banda-ms-de-sergio-liz%C3%A1rraga/413048014</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/needle-feat-spencer-cullum/6767618203</v>
+        <v>https://music.apple.com/us/album/tu-ni-en-cuenta/6767701803</v>
       </c>
       <c r="L183" t="str">
-        <v>Needle (feat. Spencer Cullum) - Mynolia</v>
+        <v>Tú Ni En Cuenta - Banda MS de Sergio Lizárraga</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>You Retreat In Time And Space</v>
+        <v>dream state</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/you-retreat-in-time-and-space/1890015660</v>
+        <v>https://music.apple.com/us/song/dream-state/6765596009</v>
       </c>
       <c r="D184" t="str">
         <v>2026-06-01</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Inferno</v>
+        <v>dream state - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>5:25</v>
+        <v>4:01</v>
       </c>
       <c r="H184" t="str">
-        <v>Boards of Canada</v>
+        <v>Martin Luke Brown</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/boards-of-canada/2989314</v>
+        <v>https://music.apple.com/us/artist/martin-luke-brown/883292185</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/you-retreat-in-time-and-space/1890015523</v>
+        <v>https://music.apple.com/us/album/dream-state/1896004790</v>
       </c>
       <c r="L184" t="str">
-        <v>You Retreat In Time And Space - Boards of Canada</v>
+        <v>dream state - Martin Luke Brown</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>It's Happening (To Me)</v>
+        <v>Needle (feat. Spencer Cullum)</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/its-happening-to-me/6764723461</v>
+        <v>https://music.apple.com/us/song/needle-feat-spencer-cullum/6767618217</v>
       </c>
       <c r="D185" t="str">
         <v>2026-06-01</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>It's Happening (To Me) - Single</v>
+        <v>Needle (feat. Spencer Cullum) - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>2:34</v>
+        <v>3:39</v>
       </c>
       <c r="H185" t="str">
-        <v>Delroy Edwards</v>
+        <v>Mynolia</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/delroy-edwards/591790909</v>
+        <v>https://music.apple.com/us/artist/mynolia/1444347510</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/its-happening-to-me/1895893472</v>
+        <v>https://music.apple.com/us/album/needle-feat-spencer-cullum/6767618203</v>
       </c>
       <c r="L185" t="str">
-        <v>It's Happening (To Me) - Delroy Edwards</v>
+        <v>Needle (feat. Spencer Cullum) - Mynolia</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>FCUK</v>
+        <v>You Retreat In Time And Space</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/fcuk/6769623577</v>
+        <v>https://music.apple.com/us/song/you-retreat-in-time-and-space/1890015660</v>
       </c>
       <c r="D186" t="str">
         <v>2026-06-01</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>FCUK - Single</v>
+        <v>Inferno</v>
       </c>
       <c r="G186" t="str">
-        <v>2:22</v>
+        <v>5:25</v>
       </c>
       <c r="H186" t="str">
-        <v>H.LLS</v>
+        <v>Boards of Canada</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/h-lls/1751287958</v>
+        <v>https://music.apple.com/us/artist/boards-of-canada/2989314</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/fcuk/6769623566</v>
+        <v>https://music.apple.com/us/album/you-retreat-in-time-and-space/1890015523</v>
       </c>
       <c r="L186" t="str">
-        <v>FCUK - H.LLS</v>
+        <v>You Retreat In Time And Space - Boards of Canada</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Higher</v>
+        <v>It's Happening (To Me)</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/higher/1880124200</v>
+        <v>https://music.apple.com/us/song/its-happening-to-me/6764723461</v>
       </c>
       <c r="D187" t="str">
         <v>2026-06-01</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Run, Run Pure Beauty</v>
+        <v>It's Happening (To Me) - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>4:06</v>
+        <v>2:34</v>
       </c>
       <c r="H187" t="str">
-        <v>Francis of Delirium</v>
+        <v>Delroy Edwards</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/francis-of-delirium/1485902996</v>
+        <v>https://music.apple.com/us/artist/delroy-edwards/591790909</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/higher/1880123731</v>
+        <v>https://music.apple.com/us/album/its-happening-to-me/1895893472</v>
       </c>
       <c r="L187" t="str">
-        <v>Higher - Francis of Delirium</v>
+        <v>It's Happening (To Me) - Delroy Edwards</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>B.U.N</v>
+        <v>FCUK</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/b-u-n/6763272338</v>
+        <v>https://music.apple.com/us/song/fcuk/6769623577</v>
       </c>
       <c r="D188" t="str">
         <v>2026-06-01</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>B.U.N - Single</v>
+        <v>FCUK - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>3:43</v>
+        <v>2:22</v>
       </c>
       <c r="H188" t="str">
-        <v>Roll Deep</v>
+        <v>H.LLS</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/roll-deep/3083873</v>
+        <v>https://music.apple.com/us/artist/h-lls/1751287958</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/b-u-n/1895242397</v>
+        <v>https://music.apple.com/us/album/fcuk/6769623566</v>
       </c>
       <c r="L188" t="str">
-        <v>B.U.N - Roll Deep</v>
+        <v>FCUK - H.LLS</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Only Love (feat. Pa Salieu)</v>
+        <v>Higher</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/only-love-feat-pa-salieu/6767014290</v>
+        <v>https://music.apple.com/us/song/higher/1880124200</v>
       </c>
       <c r="D189" t="str">
         <v>2026-06-01</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Here Because of Hope</v>
+        <v>Run, Run Pure Beauty</v>
       </c>
       <c r="G189" t="str">
-        <v>3:22</v>
+        <v>4:06</v>
       </c>
       <c r="H189" t="str">
-        <v>Ezra Collective</v>
+        <v>Francis of Delirium</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/ezra-collective/1103640281</v>
+        <v>https://music.apple.com/us/artist/francis-of-delirium/1485902996</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/only-love-feat-pa-salieu/6767014278</v>
+        <v>https://music.apple.com/us/album/higher/1880123731</v>
       </c>
       <c r="L189" t="str">
-        <v>Only Love (feat. Pa Salieu) - Ezra Collective</v>
+        <v>Higher - Francis of Delirium</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Beautiful Things 1st scene/audition</v>
+        <v>B.U.N</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/beautiful-things-1st-scene-audition/6771942631</v>
+        <v>https://music.apple.com/us/song/b-u-n/6763272338</v>
       </c>
       <c r="D190" t="str">
         <v>2026-06-01</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>UNDRA</v>
+        <v>B.U.N - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>2:49</v>
+        <v>3:43</v>
       </c>
       <c r="H190" t="str">
-        <v>reggie</v>
+        <v>Roll Deep</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/reggie/1526587068</v>
+        <v>https://music.apple.com/us/artist/roll-deep/3083873</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/beautiful-things-1st-scene-audition/6771942630</v>
+        <v>https://music.apple.com/us/album/b-u-n/1895242397</v>
       </c>
       <c r="L190" t="str">
-        <v>Beautiful Things 1st scene/audition - reggie</v>
+        <v>B.U.N - Roll Deep</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>HEAVEN'S ON FIRE</v>
+        <v>Only Love (feat. Pa Salieu)</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/heavens-on-fire/6771110730</v>
+        <v>https://music.apple.com/us/song/only-love-feat-pa-salieu/6767014290</v>
       </c>
       <c r="D191" t="str">
         <v>2026-06-01</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>HEAVEN'S ON FIRE</v>
+        <v>Here Because of Hope</v>
       </c>
       <c r="G191" t="str">
-        <v>2:54</v>
+        <v>3:22</v>
       </c>
       <c r="H191" t="str">
-        <v>Johnny Huynh</v>
+        <v>Ezra Collective</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/johnny-huynh/1708540956</v>
+        <v>https://music.apple.com/us/artist/ezra-collective/1103640281</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/heavens-on-fire/6771110729</v>
+        <v>https://music.apple.com/us/album/only-love-feat-pa-salieu/6767014278</v>
       </c>
       <c r="L191" t="str">
-        <v>HEAVEN'S ON FIRE - Johnny Huynh</v>
+        <v>Only Love (feat. Pa Salieu) - Ezra Collective</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Fallen Angel</v>
+        <v>Beautiful Things 1st scene/audition</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/fallen-angel/6771161222</v>
+        <v>https://music.apple.com/us/song/beautiful-things-1st-scene-audition/6771942631</v>
       </c>
       <c r="D192" t="str">
         <v>2026-06-01</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>You Don't Know My Name</v>
+        <v>UNDRA</v>
       </c>
       <c r="G192" t="str">
-        <v>3:05</v>
+        <v>2:49</v>
       </c>
       <c r="H192" t="str">
-        <v>Baby J</v>
+        <v>reggie</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/baby-j/1513690931</v>
+        <v>https://music.apple.com/us/artist/reggie/1526587068</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/fallen-angel/6771161180</v>
+        <v>https://music.apple.com/us/album/beautiful-things-1st-scene-audition/6771942630</v>
       </c>
       <c r="L192" t="str">
-        <v>Fallen Angel - Baby J</v>
+        <v>Beautiful Things 1st scene/audition - reggie</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>The Last Encounter</v>
+        <v>HEAVEN'S ON FIRE</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/the-last-encounter/6767395134</v>
+        <v>https://music.apple.com/us/song/heavens-on-fire/6771110730</v>
       </c>
       <c r="D193" t="str">
         <v>2026-06-01</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>The Last Encounter - Single</v>
+        <v>HEAVEN'S ON FIRE</v>
       </c>
       <c r="G193" t="str">
-        <v>3:04</v>
+        <v>2:54</v>
       </c>
       <c r="H193" t="str">
-        <v>Sofia Camara</v>
+        <v>Johnny Huynh</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/sofia-camara/1506432156</v>
+        <v>https://music.apple.com/us/artist/johnny-huynh/1708540956</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/the-last-encounter/6767395133</v>
+        <v>https://music.apple.com/us/album/heavens-on-fire/6771110729</v>
       </c>
       <c r="L193" t="str">
-        <v>The Last Encounter - Sofia Camara</v>
+        <v>HEAVEN'S ON FIRE - Johnny Huynh</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>We Fall</v>
+        <v>Fallen Angel</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/we-fall/6769218917</v>
+        <v>https://music.apple.com/us/song/fallen-angel/6771161222</v>
       </c>
       <c r="D194" t="str">
         <v>2026-06-01</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>We Fall - Single</v>
+        <v>You Don't Know My Name</v>
       </c>
       <c r="G194" t="str">
-        <v>4:01</v>
+        <v>3:05</v>
       </c>
       <c r="H194" t="str">
-        <v>MOIO</v>
+        <v>Baby J</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/moio/1664183608</v>
+        <v>https://music.apple.com/us/artist/baby-j/1513690931</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/we-fall/6769218915</v>
+        <v>https://music.apple.com/us/album/fallen-angel/6771161180</v>
       </c>
       <c r="L194" t="str">
-        <v>We Fall - MOIO</v>
+        <v>Fallen Angel - Baby J</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>You Don't Know Me</v>
+        <v>The Last Encounter</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/you-dont-know-me/6769214417</v>
+        <v>https://music.apple.com/us/song/the-last-encounter/6767395134</v>
       </c>
       <c r="D195" t="str">
         <v>2026-06-01</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>You Don’t Know Me - Single</v>
+        <v>The Last Encounter - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>3:50</v>
+        <v>3:04</v>
       </c>
       <c r="H195" t="str">
-        <v>Isabel Dumaa</v>
+        <v>Sofia Camara</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/isabel-dumaa/1631481156</v>
+        <v>https://music.apple.com/us/artist/sofia-camara/1506432156</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/you-dont-know-me/6769214410</v>
+        <v>https://music.apple.com/us/album/the-last-encounter/6767395133</v>
       </c>
       <c r="L195" t="str">
-        <v>You Don't Know Me - Isabel Dumaa</v>
+        <v>The Last Encounter - Sofia Camara</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Hold Up, Say What?</v>
+        <v>We Fall</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/hold-up-say-what/1879853511</v>
+        <v>https://music.apple.com/us/song/we-fall/6769218917</v>
       </c>
       <c r="D196" t="str">
         <v>2026-06-01</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>House Of Mirrors</v>
+        <v>We Fall - Single</v>
       </c>
       <c r="G196" t="str">
-        <v>4:04</v>
+        <v>4:01</v>
       </c>
       <c r="H196" t="str">
-        <v>All Them Witches</v>
+        <v>MOIO</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/all-them-witches/534924603</v>
+        <v>https://music.apple.com/us/artist/moio/1664183608</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/hold-up-say-what/1879853502</v>
+        <v>https://music.apple.com/us/album/we-fall/6769218915</v>
       </c>
       <c r="L196" t="str">
-        <v>Hold Up, Say What? - All Them Witches</v>
+        <v>We Fall - MOIO</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Iodine</v>
+        <v>You Don't Know Me</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/iodine/1871211805</v>
+        <v>https://music.apple.com/us/song/you-dont-know-me/6769214417</v>
       </c>
       <c r="D197" t="str">
         <v>2026-06-01</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Neverending</v>
+        <v>You Don’t Know Me - Single</v>
       </c>
       <c r="G197" t="str">
-        <v>3:40</v>
+        <v>3:50</v>
       </c>
       <c r="H197" t="str">
-        <v>Monolord</v>
+        <v>Isabel Dumaa</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/monolord/833749384</v>
+        <v>https://music.apple.com/us/artist/isabel-dumaa/1631481156</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/iodine/1871211801</v>
+        <v>https://music.apple.com/us/album/you-dont-know-me/6769214410</v>
       </c>
       <c r="L197" t="str">
-        <v>Iodine - Monolord</v>
+        <v>You Don't Know Me - Isabel Dumaa</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>I Speak Forgotten Voices</v>
+        <v>Hold Up, Say What?</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/i-speak-forgotten-voices/1878083625</v>
+        <v>https://music.apple.com/us/song/hold-up-say-what/1879853511</v>
       </c>
       <c r="D198" t="str">
         <v>2026-06-01</v>
@@ -7899,68 +7899,144 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>...By the Word...</v>
+        <v>House Of Mirrors</v>
       </c>
       <c r="G198" t="str">
-        <v>5:01</v>
+        <v>4:04</v>
       </c>
       <c r="H198" t="str">
-        <v>Trelldom</v>
+        <v>All Them Witches</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/trelldom/256586618</v>
+        <v>https://music.apple.com/us/artist/all-them-witches/534924603</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/i-speak-forgotten-voices/1878083622</v>
+        <v>https://music.apple.com/us/album/hold-up-say-what/1879853502</v>
       </c>
       <c r="L198" t="str">
-        <v>I Speak Forgotten Voices - Trelldom</v>
+        <v>Hold Up, Say What? - All Them Witches</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
+        <v>Iodine</v>
+      </c>
+      <c r="B199" t="str">
+        <v/>
+      </c>
+      <c r="C199" t="str">
+        <v>https://music.apple.com/us/song/iodine/1871211805</v>
+      </c>
+      <c r="D199" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="E199" t="str">
+        <v/>
+      </c>
+      <c r="F199" t="str">
+        <v>Neverending</v>
+      </c>
+      <c r="G199" t="str">
+        <v>3:40</v>
+      </c>
+      <c r="H199" t="str">
+        <v>Monolord</v>
+      </c>
+      <c r="I199" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J199" t="str">
+        <v>https://music.apple.com/us/artist/monolord/833749384</v>
+      </c>
+      <c r="K199" t="str">
+        <v>https://music.apple.com/us/album/iodine/1871211801</v>
+      </c>
+      <c r="L199" t="str">
+        <v>Iodine - Monolord</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
+        <v>I Speak Forgotten Voices</v>
+      </c>
+      <c r="B200" t="str">
+        <v/>
+      </c>
+      <c r="C200" t="str">
+        <v>https://music.apple.com/us/song/i-speak-forgotten-voices/1878083625</v>
+      </c>
+      <c r="D200" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="E200" t="str">
+        <v/>
+      </c>
+      <c r="F200" t="str">
+        <v>...By the Word...</v>
+      </c>
+      <c r="G200" t="str">
+        <v>5:01</v>
+      </c>
+      <c r="H200" t="str">
+        <v>Trelldom</v>
+      </c>
+      <c r="I200" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J200" t="str">
+        <v>https://music.apple.com/us/artist/trelldom/256586618</v>
+      </c>
+      <c r="K200" t="str">
+        <v>https://music.apple.com/us/album/i-speak-forgotten-voices/1878083622</v>
+      </c>
+      <c r="L200" t="str">
+        <v>I Speak Forgotten Voices - Trelldom</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="str">
         <v>Rats in the Temple</v>
       </c>
-      <c r="B199" t="str">
-        <v/>
-      </c>
-      <c r="C199" t="str">
+      <c r="B201" t="str">
+        <v/>
+      </c>
+      <c r="C201" t="str">
         <v>https://music.apple.com/us/song/rats-in-the-temple/6764627559</v>
       </c>
-      <c r="D199" t="str">
-        <v>2026-06-01</v>
-      </c>
-      <c r="E199" t="str">
-        <v/>
-      </c>
-      <c r="F199" t="str">
+      <c r="D201" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="E201" t="str">
+        <v/>
+      </c>
+      <c r="F201" t="str">
         <v>Rats in the Temple</v>
       </c>
-      <c r="G199" t="str">
+      <c r="G201" t="str">
         <v>4:45</v>
       </c>
-      <c r="H199" t="str">
+      <c r="H201" t="str">
         <v>Flotsam and Jetsam</v>
       </c>
-      <c r="I199" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J199" t="str">
+      <c r="I201" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J201" t="str">
         <v>https://music.apple.com/us/artist/flotsam-and-jetsam/162270</v>
       </c>
-      <c r="K199" t="str">
+      <c r="K201" t="str">
         <v>https://music.apple.com/us/album/rats-in-the-temple/1895855647</v>
       </c>
-      <c r="L199" t="str">
+      <c r="L201" t="str">
         <v>Rats in the Temple - Flotsam and Jetsam</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L199"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L201"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-06-week01/titles.xlsx
+++ b/data/global/2026-06-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L201"/>
+  <dimension ref="A1:L210"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אלירן בוזגלו - מחרוזת והלב 2026</v>
+        <v>שמעון בוסקילה - עולם יפה</v>
       </c>
       <c r="B2" t="str">
         <v>2026-06-01</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411150&amp;sid=db79b057e91704f5824c4dbc912b8a71</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411160&amp;sid=025af64e8b5ae176cc6981dfe7da5d26</v>
       </c>
       <c r="D2" t="str">
         <v>2026-06-01</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אלירן בוזגלו - מחרוזת והלב 2026</v>
+        <v>שמעון בוסקילה - עולם יפה</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>אביחי אוחנה - נתת לי חיים</v>
+        <v>קובי בוקעי - האהבה שלך</v>
       </c>
       <c r="B3" t="str">
         <v>2026-06-01</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411149&amp;sid=db79b057e91704f5824c4dbc912b8a71</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411159&amp;sid=025af64e8b5ae176cc6981dfe7da5d26</v>
       </c>
       <c r="D3" t="str">
         <v>2026-06-01</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>אביחי אוחנה - נתת לי חיים</v>
+        <v>קובי בוקעי - האהבה שלך</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>אבי בר - מחרוזת שקטים 2026</v>
+        <v>נהוראי אריאלי &amp; שי וינר - אתה טוב</v>
       </c>
       <c r="B4" t="str">
         <v>2026-06-01</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411148&amp;sid=db79b057e91704f5824c4dbc912b8a71</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411158&amp;sid=025af64e8b5ae176cc6981dfe7da5d26</v>
       </c>
       <c r="D4" t="str">
         <v>2026-06-01</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>אבי בר - מחרוזת שקטים 2026</v>
+        <v>נהוראי אריאלי &amp; שי וינר - אתה טוב</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Dua Lipa - Physical (Live From Mexico)</v>
+        <v>מיכל בן חיים - איזה עולם</v>
       </c>
       <c r="B5" t="str">
-        <v>3 days ago</v>
+        <v>2026-06-01</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=xZAe-d3bXTs</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411157&amp;sid=025af64e8b5ae176cc6981dfe7da5d26</v>
       </c>
       <c r="D5" t="str">
         <v>2026-06-01</v>
@@ -565,16 +565,16 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>3 days ago</v>
+        <v/>
       </c>
       <c r="G5" t="str">
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>Dua Lipa</v>
+        <v/>
       </c>
       <c r="I5" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Dua Lipa - Physical (Live From Mexico) - Dua Lipa</v>
+        <v>מיכל בן חיים - איזה עולם</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Dagny - Rain (Lyric Video)</v>
+        <v>מורן מצליח - מאז שהלכת</v>
       </c>
       <c r="B6" t="str">
-        <v>3 days ago</v>
+        <v>2026-06-01</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=j3ZJwczZoUQ</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411156&amp;sid=025af64e8b5ae176cc6981dfe7da5d26</v>
       </c>
       <c r="D6" t="str">
         <v>2026-06-01</v>
@@ -603,16 +603,16 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>3 days ago</v>
+        <v/>
       </c>
       <c r="G6" t="str">
         <v/>
       </c>
       <c r="H6" t="str">
-        <v>Dagny</v>
+        <v/>
       </c>
       <c r="I6" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Dagny - Rain (Lyric Video) - Dagny</v>
+        <v>מורן מצליח - מאז שהלכת</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Modern Talking - Cheri Cheri Lady (Auf los geht's los, 14.09.1985)</v>
+        <v>מורן מצליח - חשבתי שאתה לתמיד</v>
       </c>
       <c r="B7" t="str">
-        <v>3 days ago</v>
+        <v>2026-06-01</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=c0LtTVKNwNA</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411155&amp;sid=025af64e8b5ae176cc6981dfe7da5d26</v>
       </c>
       <c r="D7" t="str">
         <v>2026-06-01</v>
@@ -641,16 +641,16 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>3 days ago</v>
+        <v/>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>Modern Talking Offiziell</v>
+        <v/>
       </c>
       <c r="I7" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J7" t="str">
         <v/>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Modern Talking - Cheri Cheri Lady (Auf los geht's los, 14.09.1985) - Modern Talking Offiziell</v>
+        <v>מורן מצליח - חשבתי שאתה לתמיד</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Jonas Blue - Girl (Official Lyric Video)</v>
+        <v>איה - באתי לרקוד</v>
       </c>
       <c r="B8" t="str">
-        <v>3 days ago</v>
+        <v>2026-06-01</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=FTUe3jzUqXU</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411154&amp;sid=025af64e8b5ae176cc6981dfe7da5d26</v>
       </c>
       <c r="D8" t="str">
         <v>2026-06-01</v>
@@ -679,16 +679,16 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>3 days ago</v>
+        <v/>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>Defected Records and Jonas Blue</v>
+        <v/>
       </c>
       <c r="I8" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Jonas Blue - Girl (Official Lyric Video) - Defected Records and Jonas Blue</v>
+        <v>איה - באתי לרקוד</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Dogpark - Don't Lie (Visualizer)</v>
+        <v>ישראל צוברי - אלוקיי</v>
       </c>
       <c r="B9" t="str">
-        <v>3 days ago</v>
+        <v>2026-06-01</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=is7qKBRycJI</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411153&amp;sid=025af64e8b5ae176cc6981dfe7da5d26</v>
       </c>
       <c r="D9" t="str">
         <v>2026-06-01</v>
@@ -717,16 +717,16 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>3 days ago</v>
+        <v/>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>Dogpark</v>
+        <v/>
       </c>
       <c r="I9" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J9" t="str">
         <v/>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Dogpark - Don't Lie (Visualizer) - Dogpark</v>
+        <v>ישראל צוברי - אלוקיי</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>elijah woods - L-O-V-E (Treehouse Sessions)</v>
+        <v>ירין יפת &amp; אפסילון - לא נמצאת</v>
       </c>
       <c r="B10" t="str">
-        <v>3 days ago</v>
+        <v>2026-06-01</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=q5kN7eH6rgo</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411152&amp;sid=025af64e8b5ae176cc6981dfe7da5d26</v>
       </c>
       <c r="D10" t="str">
         <v>2026-06-01</v>
@@ -755,16 +755,16 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>3 days ago</v>
+        <v/>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>elijah woods</v>
+        <v/>
       </c>
       <c r="I10" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J10" t="str">
         <v/>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>elijah woods - L-O-V-E (Treehouse Sessions) - elijah woods</v>
+        <v>ירין יפת &amp; אפסילון - לא נמצאת</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Lauren Alaina - Better Off (Official Audio)</v>
+        <v>אנה זק - ילד שמנת - גרסת הפילאטיס</v>
       </c>
       <c r="B11" t="str">
-        <v>3 days ago</v>
+        <v>2026-06-01</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=Vj-ong3XNHM</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411151&amp;sid=025af64e8b5ae176cc6981dfe7da5d26</v>
       </c>
       <c r="D11" t="str">
         <v>2026-06-01</v>
@@ -793,16 +793,16 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>3 days ago</v>
+        <v/>
       </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>Lauren Alaina</v>
+        <v/>
       </c>
       <c r="I11" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J11" t="str">
         <v/>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Lauren Alaina - Better Off (Official Audio) - Lauren Alaina</v>
+        <v>אנה זק - ילד שמנת - גרסת הפילאטיס</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Lauren Sanderson - ARE YOU REALLY HERE? (Lyric Video)</v>
+        <v>Dua Lipa - Physical (Live From Mexico)</v>
       </c>
       <c r="B12" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=u7Et_hbMZUA</v>
+        <v>https://www.youtube.com/watch?v=xZAe-d3bXTs</v>
       </c>
       <c r="D12" t="str">
         <v>2026-06-01</v>
@@ -837,7 +837,7 @@
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>Lauren Sanderson</v>
+        <v>Dua Lipa</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Lauren Sanderson - ARE YOU REALLY HERE? (Lyric Video) - Lauren Sanderson</v>
+        <v>Dua Lipa - Physical (Live From Mexico) - Dua Lipa</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Nightly – blue jeans (Official Lyric Video)</v>
+        <v>Dagny - Rain (Lyric Video)</v>
       </c>
       <c r="B13" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=LnA3xkXUwaM</v>
+        <v>https://www.youtube.com/watch?v=j3ZJwczZoUQ</v>
       </c>
       <c r="D13" t="str">
         <v>2026-06-01</v>
@@ -875,7 +875,7 @@
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>NIGHTLY</v>
+        <v>Dagny</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Nightly – blue jeans (Official Lyric Video) - NIGHTLY</v>
+        <v>Dagny - Rain (Lyric Video) - Dagny</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Dasha - Mad About It (Official Visualizer)</v>
+        <v>Modern Talking - Cheri Cheri Lady (Auf los geht's los, 14.09.1985)</v>
       </c>
       <c r="B14" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=Ae1gf_7p3H8</v>
+        <v>https://www.youtube.com/watch?v=c0LtTVKNwNA</v>
       </c>
       <c r="D14" t="str">
         <v>2026-06-01</v>
@@ -913,7 +913,7 @@
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>Dasha</v>
+        <v>Modern Talking Offiziell</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Dasha - Mad About It (Official Visualizer) - Dasha</v>
+        <v>Modern Talking - Cheri Cheri Lady (Auf los geht's los, 14.09.1985) - Modern Talking Offiziell</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Ariana Grande - hate that i made you love me (official lyric video)</v>
+        <v>Jonas Blue - Girl (Official Lyric Video)</v>
       </c>
       <c r="B15" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=v1t4MTqdfyI</v>
+        <v>https://www.youtube.com/watch?v=FTUe3jzUqXU</v>
       </c>
       <c r="D15" t="str">
         <v>2026-06-01</v>
@@ -951,7 +951,7 @@
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>Ariana Grande</v>
+        <v>Defected Records and Jonas Blue</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Ariana Grande - hate that i made you love me (official lyric video) - Ariana Grande</v>
+        <v>Jonas Blue - Girl (Official Lyric Video) - Defected Records and Jonas Blue</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Max McNown - Something To Someone (Performance Video)</v>
+        <v>Dogpark - Don't Lie (Visualizer)</v>
       </c>
       <c r="B16" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=4Ki4ejT86YM</v>
+        <v>https://www.youtube.com/watch?v=is7qKBRycJI</v>
       </c>
       <c r="D16" t="str">
         <v>2026-06-01</v>
@@ -989,7 +989,7 @@
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>Max McNown</v>
+        <v>Dogpark</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Max McNown - Something To Someone (Performance Video) - Max McNown</v>
+        <v>Dogpark - Don't Lie (Visualizer) - Dogpark</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Bebe Rexha &amp; David Guetta - Sad Girls (Official Visual)</v>
+        <v>elijah woods - L-O-V-E (Treehouse Sessions)</v>
       </c>
       <c r="B17" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=P8UqZ5IF-QE</v>
+        <v>https://www.youtube.com/watch?v=q5kN7eH6rgo</v>
       </c>
       <c r="D17" t="str">
         <v>2026-06-01</v>
@@ -1027,7 +1027,7 @@
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>Bebe Rexha</v>
+        <v>elijah woods</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Bebe Rexha &amp; David Guetta - Sad Girls (Official Visual) - Bebe Rexha</v>
+        <v>elijah woods - L-O-V-E (Treehouse Sessions) - elijah woods</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Knox - Long Story Short (Official Video)</v>
+        <v>Lauren Alaina - Better Off (Official Audio)</v>
       </c>
       <c r="B18" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=5OGY6hCELfg</v>
+        <v>https://www.youtube.com/watch?v=Vj-ong3XNHM</v>
       </c>
       <c r="D18" t="str">
         <v>2026-06-01</v>
@@ -1065,7 +1065,7 @@
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>Knox</v>
+        <v>Lauren Alaina</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Knox - Long Story Short (Official Video) - Knox</v>
+        <v>Lauren Alaina - Better Off (Official Audio) - Lauren Alaina</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Sofia Camara - The Last Encounter</v>
+        <v>Lauren Sanderson - ARE YOU REALLY HERE? (Lyric Video)</v>
       </c>
       <c r="B19" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=E9kN4HLGG1c</v>
+        <v>https://www.youtube.com/watch?v=u7Et_hbMZUA</v>
       </c>
       <c r="D19" t="str">
         <v>2026-06-01</v>
@@ -1103,7 +1103,7 @@
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>Sofia Camara</v>
+        <v>Lauren Sanderson</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Sofia Camara - The Last Encounter - Sofia Camara</v>
+        <v>Lauren Sanderson - ARE YOU REALLY HERE? (Lyric Video) - Lauren Sanderson</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Official Music Video: "Flowers" -- Alexander James</v>
+        <v>Nightly – blue jeans (Official Lyric Video)</v>
       </c>
       <c r="B20" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=aZ4WP0P92tM</v>
+        <v>https://www.youtube.com/watch?v=LnA3xkXUwaM</v>
       </c>
       <c r="D20" t="str">
         <v>2026-06-01</v>
@@ -1141,7 +1141,7 @@
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>Alexander James</v>
+        <v>NIGHTLY</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Official Music Video: "Flowers" -- Alexander James - Alexander James</v>
+        <v>Nightly – blue jeans (Official Lyric Video) - NIGHTLY</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>almost monday - skinny dip (official video)</v>
+        <v>Dasha - Mad About It (Official Visualizer)</v>
       </c>
       <c r="B21" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=hOxZDoaIzKQ</v>
+        <v>https://www.youtube.com/watch?v=Ae1gf_7p3H8</v>
       </c>
       <c r="D21" t="str">
         <v>2026-06-01</v>
@@ -1179,7 +1179,7 @@
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>almost monday</v>
+        <v>Dasha</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>almost monday - skinny dip (official video) - almost monday</v>
+        <v>Dasha - Mad About It (Official Visualizer) - Dasha</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Kip Moore - The Darkness (Official)</v>
+        <v>Ariana Grande - hate that i made you love me (official lyric video)</v>
       </c>
       <c r="B22" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=lTqqixCt5Mk</v>
+        <v>https://www.youtube.com/watch?v=v1t4MTqdfyI</v>
       </c>
       <c r="D22" t="str">
         <v>2026-06-01</v>
@@ -1217,7 +1217,7 @@
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>Kip Moore</v>
+        <v>Ariana Grande</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Kip Moore - The Darkness (Official) - Kip Moore</v>
+        <v>Ariana Grande - hate that i made you love me (official lyric video) - Ariana Grande</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Paul McCartney - Come Inside (Lyric Video)</v>
+        <v>Max McNown - Something To Someone (Performance Video)</v>
       </c>
       <c r="B23" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=C8Zw_Cbm2V0</v>
+        <v>https://www.youtube.com/watch?v=4Ki4ejT86YM</v>
       </c>
       <c r="D23" t="str">
         <v>2026-06-01</v>
@@ -1255,7 +1255,7 @@
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>PAUL McCARTNEY</v>
+        <v>Max McNown</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Paul McCartney - Come Inside (Lyric Video) - PAUL McCARTNEY</v>
+        <v>Max McNown - Something To Someone (Performance Video) - Max McNown</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Santana, Becky G - Mi Gran Amor (Official Lyric Video)</v>
+        <v>Bebe Rexha &amp; David Guetta - Sad Girls (Official Visual)</v>
       </c>
       <c r="B24" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=btdBd_Yee8E</v>
+        <v>https://www.youtube.com/watch?v=P8UqZ5IF-QE</v>
       </c>
       <c r="D24" t="str">
         <v>2026-06-01</v>
@@ -1293,7 +1293,7 @@
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>Santana</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Santana, Becky G - Mi Gran Amor (Official Lyric Video) - Santana</v>
+        <v>Bebe Rexha &amp; David Guetta - Sad Girls (Official Visual) - Bebe Rexha</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Dua Lipa - Training Season (Live From Mexico)</v>
+        <v>Knox - Long Story Short (Official Video)</v>
       </c>
       <c r="B25" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=Va8Udsvqigs</v>
+        <v>https://www.youtube.com/watch?v=5OGY6hCELfg</v>
       </c>
       <c r="D25" t="str">
         <v>2026-06-01</v>
@@ -1331,7 +1331,7 @@
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>Dua Lipa</v>
+        <v>Knox</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Dua Lipa - Training Season (Live From Mexico) - Dua Lipa</v>
+        <v>Knox - Long Story Short (Official Video) - Knox</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Charley - Liar</v>
+        <v>Sofia Camara - The Last Encounter</v>
       </c>
       <c r="B26" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=3Erfj2Eecgw</v>
+        <v>https://www.youtube.com/watch?v=E9kN4HLGG1c</v>
       </c>
       <c r="D26" t="str">
         <v>2026-06-01</v>
@@ -1369,7 +1369,7 @@
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>Charley</v>
+        <v>Sofia Camara</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Charley - Liar - Charley</v>
+        <v>Sofia Camara - The Last Encounter - Sofia Camara</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (ft Gabito Ballesteros) [Visualizer]</v>
+        <v>Official Music Video: "Flowers" -- Alexander James</v>
       </c>
       <c r="B27" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=em5ryETDkAo</v>
+        <v>https://www.youtube.com/watch?v=aZ4WP0P92tM</v>
       </c>
       <c r="D27" t="str">
         <v>2026-06-01</v>
@@ -1407,7 +1407,7 @@
         <v/>
       </c>
       <c r="H27" t="str">
-        <v>David Guetta and Jennifer Lopez</v>
+        <v>Alexander James</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (ft Gabito Ballesteros) [Visualizer] - David Guetta and Jennifer Lopez</v>
+        <v>Official Music Video: "Flowers" -- Alexander James - Alexander James</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Jordana Bryant - Too Little Too Late (Official Audio)</v>
+        <v>almost monday - skinny dip (official video)</v>
       </c>
       <c r="B28" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=AmwNx9qlOpA</v>
+        <v>https://www.youtube.com/watch?v=hOxZDoaIzKQ</v>
       </c>
       <c r="D28" t="str">
         <v>2026-06-01</v>
@@ -1445,7 +1445,7 @@
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>Jordana Bryant</v>
+        <v>almost monday</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Jordana Bryant - Too Little Too Late (Official Audio) - Jordana Bryant</v>
+        <v>almost monday - skinny dip (official video) - almost monday</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Lewis Capaldi - Stay Love</v>
+        <v>Kip Moore - The Darkness (Official)</v>
       </c>
       <c r="B29" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=9Pud3BqPpq0</v>
+        <v>https://www.youtube.com/watch?v=lTqqixCt5Mk</v>
       </c>
       <c r="D29" t="str">
         <v>2026-06-01</v>
@@ -1483,7 +1483,7 @@
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>Lewis Capaldi</v>
+        <v>Kip Moore</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Lewis Capaldi - Stay Love - Lewis Capaldi</v>
+        <v>Kip Moore - The Darkness (Official) - Kip Moore</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Surreal World of Oddities - Pulling At My Strings - Official Music Video | 4K</v>
+        <v>Paul McCartney - Come Inside (Lyric Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>5 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=fMt-f2aUW3c</v>
+        <v>https://www.youtube.com/watch?v=C8Zw_Cbm2V0</v>
       </c>
       <c r="D30" t="str">
         <v>2026-06-01</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>5 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>Kelly Boesch AI Art</v>
+        <v>PAUL McCARTNEY</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Surreal World of Oddities - Pulling At My Strings - Official Music Video | 4K - Kelly Boesch AI Art</v>
+        <v>Paul McCartney - Come Inside (Lyric Video) - PAUL McCARTNEY</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Julia Cole - Love You to Death (Official Video)</v>
+        <v>Santana, Becky G - Mi Gran Amor (Official Lyric Video)</v>
       </c>
       <c r="B31" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=dWgmFc2QuLY</v>
+        <v>https://www.youtube.com/watch?v=btdBd_Yee8E</v>
       </c>
       <c r="D31" t="str">
         <v>2026-06-01</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>Julia Cole Music</v>
+        <v>Santana</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Julia Cole - Love You to Death (Official Video) - Julia Cole Music</v>
+        <v>Santana, Becky G - Mi Gran Amor (Official Lyric Video) - Santana</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Victor Biliac - De-ai fi tu salcie la mal ( Cover Edit )</v>
+        <v>Dua Lipa - Training Season (Live From Mexico)</v>
       </c>
       <c r="B32" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=v3c0kG-V2zk</v>
+        <v>https://www.youtube.com/watch?v=Va8Udsvqigs</v>
       </c>
       <c r="D32" t="str">
         <v>2026-06-01</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
       </c>
       <c r="H32" t="str">
-        <v>VictorBiliac</v>
+        <v>Dua Lipa</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Victor Biliac - De-ai fi tu salcie la mal ( Cover Edit ) - VictorBiliac</v>
+        <v>Dua Lipa - Training Season (Live From Mexico) - Dua Lipa</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Lolo Zouaï - Coquelicot (feat. disiz) (Official Video)</v>
+        <v>Charley - Liar</v>
       </c>
       <c r="B33" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=-4p6FkrOGT4</v>
+        <v>https://www.youtube.com/watch?v=3Erfj2Eecgw</v>
       </c>
       <c r="D33" t="str">
         <v>2026-06-01</v>
@@ -1635,7 +1635,7 @@
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>Lolo Zouaï and disiz</v>
+        <v>Charley</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Lolo Zouaï - Coquelicot (feat. disiz) (Official Video) - Lolo Zouaï and disiz</v>
+        <v>Charley - Liar - Charley</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Jungle - The Wave (Official Video)</v>
+        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (ft Gabito Ballesteros) [Visualizer]</v>
       </c>
       <c r="B34" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=DW1vUkqNvqQ</v>
+        <v>https://www.youtube.com/watch?v=em5ryETDkAo</v>
       </c>
       <c r="D34" t="str">
         <v>2026-06-01</v>
@@ -1673,7 +1673,7 @@
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>Jungle4eva</v>
+        <v>David Guetta and Jennifer Lopez</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Jungle - The Wave (Official Video) - Jungle4eva</v>
+        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (ft Gabito Ballesteros) [Visualizer] - David Guetta and Jennifer Lopez</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Daytime TV – Sun (Official Music Video)</v>
+        <v>Jordana Bryant - Too Little Too Late (Official Audio)</v>
       </c>
       <c r="B35" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=Jqo4ra_ch-M</v>
+        <v>https://www.youtube.com/watch?v=AmwNx9qlOpA</v>
       </c>
       <c r="D35" t="str">
         <v>2026-06-01</v>
@@ -1711,7 +1711,7 @@
         <v/>
       </c>
       <c r="H35" t="str">
-        <v>DAYTIME TV</v>
+        <v>Jordana Bryant</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Daytime TV – Sun (Official Music Video) - DAYTIME TV</v>
+        <v>Jordana Bryant - Too Little Too Late (Official Audio) - Jordana Bryant</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Surreal and Strange AI Video | Not Made For The Cage | Kelly Boesch - 4K</v>
+        <v>Lewis Capaldi - Stay Love</v>
       </c>
       <c r="B36" t="str">
-        <v>2 weeks ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=ACNj3L2bzV8</v>
+        <v>https://www.youtube.com/watch?v=9Pud3BqPpq0</v>
       </c>
       <c r="D36" t="str">
         <v>2026-06-01</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>2 weeks ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>Kelly Boesch AI Art</v>
+        <v>Lewis Capaldi</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Surreal and Strange AI Video | Not Made For The Cage | Kelly Boesch - 4K - Kelly Boesch AI Art</v>
+        <v>Lewis Capaldi - Stay Love - Lewis Capaldi</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Bruno Mars - Risk It All [Live From The Romantic Tour]</v>
+        <v>Surreal World of Oddities - Pulling At My Strings - Official Music Video | 4K</v>
       </c>
       <c r="B37" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=aFbueod4reQ</v>
+        <v>https://www.youtube.com/watch?v=fMt-f2aUW3c</v>
       </c>
       <c r="D37" t="str">
         <v>2026-06-01</v>
@@ -1787,7 +1787,7 @@
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>Bruno Mars</v>
+        <v>Kelly Boesch AI Art</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Bruno Mars - Risk It All [Live From The Romantic Tour] - Bruno Mars</v>
+        <v>Surreal World of Oddities - Pulling At My Strings - Official Music Video | 4K - Kelly Boesch AI Art</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Keith Urban - Summer Breeze (52nd American Music Awards)</v>
+        <v>Julia Cole - Love You to Death (Official Video)</v>
       </c>
       <c r="B38" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=zn-4eVoqofQ</v>
+        <v>https://www.youtube.com/watch?v=dWgmFc2QuLY</v>
       </c>
       <c r="D38" t="str">
         <v>2026-06-01</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
       </c>
       <c r="H38" t="str">
-        <v>Keith Urban</v>
+        <v>Julia Cole Music</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Keith Urban - Summer Breeze (52nd American Music Awards) - Keith Urban</v>
+        <v>Julia Cole - Love You to Death (Official Video) - Julia Cole Music</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Nelly Furtado, Boi-1Da, Canada Soccer - ELECTRIC CIRCUS (Official Music Video)</v>
+        <v>Victor Biliac - De-ai fi tu salcie la mal ( Cover Edit )</v>
       </c>
       <c r="B39" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=lHYEMWFuErM</v>
+        <v>https://www.youtube.com/watch?v=v3c0kG-V2zk</v>
       </c>
       <c r="D39" t="str">
         <v>2026-06-01</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
       </c>
       <c r="H39" t="str">
-        <v>Nelly Furtado</v>
+        <v>VictorBiliac</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Nelly Furtado, Boi-1Da, Canada Soccer - ELECTRIC CIRCUS (Official Music Video) - Nelly Furtado</v>
+        <v>Victor Biliac - De-ai fi tu salcie la mal ( Cover Edit ) - VictorBiliac</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Teddy Swims - Mr. Know It All (Live from the AMAs)</v>
+        <v>Lolo Zouaï - Coquelicot (feat. disiz) (Official Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=ttM4gWkhZBk</v>
+        <v>https://www.youtube.com/watch?v=-4p6FkrOGT4</v>
       </c>
       <c r="D40" t="str">
         <v>2026-06-01</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
       </c>
       <c r="H40" t="str">
-        <v>Teddy Swims and American Music Awards</v>
+        <v>Lolo Zouaï and disiz</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Teddy Swims - Mr. Know It All (Live from the AMAs) - Teddy Swims and American Music Awards</v>
+        <v>Lolo Zouaï - Coquelicot (feat. disiz) (Official Video) - Lolo Zouaï and disiz</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Shakira, Burna Boy - Dai Dai (Official Video)</v>
+        <v>Jungle - The Wave (Official Video)</v>
       </c>
       <c r="B41" t="str">
-        <v>8 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=fcnDmrtj6Sk</v>
+        <v>https://www.youtube.com/watch?v=DW1vUkqNvqQ</v>
       </c>
       <c r="D41" t="str">
         <v>2026-06-01</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>8 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
       </c>
       <c r="H41" t="str">
-        <v>Shakira and 2 more</v>
+        <v>Jungle4eva</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Shakira, Burna Boy - Dai Dai (Official Video) - Shakira and 2 more</v>
+        <v>Jungle - The Wave (Official Video) - Jungle4eva</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards)</v>
+        <v>Daytime TV – Sun (Official Music Video)</v>
       </c>
       <c r="B42" t="str">
-        <v>8 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=wacpnp83cJg</v>
+        <v>https://www.youtube.com/watch?v=Jqo4ra_ch-M</v>
       </c>
       <c r="D42" t="str">
         <v>2026-06-01</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>8 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
       </c>
       <c r="H42" t="str">
-        <v>Lainey Wilson</v>
+        <v>DAYTIME TV</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards) - Lainey Wilson</v>
+        <v>Daytime TV – Sun (Official Music Video) - DAYTIME TV</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ]</v>
+        <v>Surreal and Strange AI Video | Not Made For The Cage | Kelly Boesch - 4K</v>
       </c>
       <c r="B43" t="str">
-        <v>9 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=w8FTnkNVmq0</v>
+        <v>https://www.youtube.com/watch?v=ACNj3L2bzV8</v>
       </c>
       <c r="D43" t="str">
         <v>2026-06-01</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>9 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
       </c>
       <c r="H43" t="str">
-        <v>Duran Duran</v>
+        <v>Kelly Boesch AI Art</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ] - Duran Duran</v>
+        <v>Surreal and Strange AI Video | Not Made For The Cage | Kelly Boesch - 4K - Kelly Boesch AI Art</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Nico Santos - Optimist</v>
+        <v>Bruno Mars - Risk It All [Live From The Romantic Tour]</v>
       </c>
       <c r="B44" t="str">
-        <v>11 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=JA6PIcBeKZ0</v>
+        <v>https://www.youtube.com/watch?v=aFbueod4reQ</v>
       </c>
       <c r="D44" t="str">
         <v>2026-06-01</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>11 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
       </c>
       <c r="H44" t="str">
-        <v>Nico Santos</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Nico Santos - Optimist - Nico Santos</v>
+        <v>Bruno Mars - Risk It All [Live From The Romantic Tour] - Bruno Mars</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Def Leppard - Personal Jesus (Live at Caesars Palace)</v>
+        <v>Keith Urban - Summer Breeze (52nd American Music Awards)</v>
       </c>
       <c r="B45" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=k5SRMgdG4L4</v>
+        <v>https://www.youtube.com/watch?v=zn-4eVoqofQ</v>
       </c>
       <c r="D45" t="str">
         <v>2026-06-01</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
       </c>
       <c r="H45" t="str">
-        <v>DEF LEPPARD</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Def Leppard - Personal Jesus (Live at Caesars Palace) - DEF LEPPARD</v>
+        <v>Keith Urban - Summer Breeze (52nd American Music Awards) - Keith Urban</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer)</v>
+        <v>Nelly Furtado, Boi-1Da, Canada Soccer - ELECTRIC CIRCUS (Official Music Video)</v>
       </c>
       <c r="B46" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=eWSwy9GU2L8</v>
+        <v>https://www.youtube.com/watch?v=lHYEMWFuErM</v>
       </c>
       <c r="D46" t="str">
         <v>2026-06-01</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>Will Linley</v>
+        <v>Nelly Furtado</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer) - Will Linley</v>
+        <v>Nelly Furtado, Boi-1Da, Canada Soccer - ELECTRIC CIRCUS (Official Music Video) - Nelly Furtado</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Kylie Minogue - Story (Official Lyric Video)</v>
+        <v>Teddy Swims - Mr. Know It All (Live from the AMAs)</v>
       </c>
       <c r="B47" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=fv7_1qKo8mg</v>
+        <v>https://www.youtube.com/watch?v=ttM4gWkhZBk</v>
       </c>
       <c r="D47" t="str">
         <v>2026-06-01</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>Kylie Minogue</v>
+        <v>Teddy Swims and American Music Awards</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Kylie Minogue - Story (Official Lyric Video) - Kylie Minogue</v>
+        <v>Teddy Swims - Mr. Know It All (Live from the AMAs) - Teddy Swims and American Music Awards</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video)</v>
+        <v>Shakira, Burna Boy - Dai Dai (Official Video)</v>
       </c>
       <c r="B48" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=3KUQx2s1fQc</v>
+        <v>https://www.youtube.com/watch?v=fcnDmrtj6Sk</v>
       </c>
       <c r="D48" t="str">
         <v>2026-06-01</v>
@@ -2205,7 +2205,7 @@
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>Billy Raffoul</v>
+        <v>Shakira and 2 more</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video) - Billy Raffoul</v>
+        <v>Shakira, Burna Boy - Dai Dai (Official Video) - Shakira and 2 more</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025)</v>
+        <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards)</v>
       </c>
       <c r="B49" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=vWf4uiLvwF8</v>
+        <v>https://www.youtube.com/watch?v=wacpnp83cJg</v>
       </c>
       <c r="D49" t="str">
         <v>2026-06-01</v>
@@ -2243,7 +2243,7 @@
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>The Offspring</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025) - The Offspring</v>
+        <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards) - Lainey Wilson</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024)</v>
+        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ]</v>
       </c>
       <c r="B50" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=9xjMaXegmWM</v>
+        <v>https://www.youtube.com/watch?v=w8FTnkNVmq0</v>
       </c>
       <c r="D50" t="str">
         <v>2026-06-01</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>David Gilmour</v>
+        <v>Duran Duran</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024) - David Gilmour</v>
+        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ] - Duran Duran</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Scorpions - Delicate Dance (Madison Square Garden 2022)</v>
+        <v>Nico Santos - Optimist</v>
       </c>
       <c r="B51" t="str">
-        <v>9 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=yAjEr9WLTnU</v>
+        <v>https://www.youtube.com/watch?v=JA6PIcBeKZ0</v>
       </c>
       <c r="D51" t="str">
         <v>2026-06-01</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>9 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>Scorpions</v>
+        <v>Nico Santos</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Scorpions - Delicate Dance (Madison Square Garden 2022) - Scorpions</v>
+        <v>Nico Santos - Optimist - Nico Santos</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston)</v>
+        <v>Def Leppard - Personal Jesus (Live at Caesars Palace)</v>
       </c>
       <c r="B52" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=oRw4PqBzGc0</v>
+        <v>https://www.youtube.com/watch?v=k5SRMgdG4L4</v>
       </c>
       <c r="D52" t="str">
         <v>2026-06-01</v>
@@ -2357,7 +2357,7 @@
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>Brandon Lake and NICK JONAS</v>
+        <v>DEF LEPPARD</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston) - Brandon Lake and NICK JONAS</v>
+        <v>Def Leppard - Personal Jesus (Live at Caesars Palace) - DEF LEPPARD</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video)</v>
+        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer)</v>
       </c>
       <c r="B53" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=OKf_IOGxFQo</v>
+        <v>https://www.youtube.com/watch?v=eWSwy9GU2L8</v>
       </c>
       <c r="D53" t="str">
         <v>2026-06-01</v>
@@ -2395,7 +2395,7 @@
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>Kygo and Dan Tyminski</v>
+        <v>Will Linley</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video) - Kygo and Dan Tyminski</v>
+        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer) - Will Linley</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>The Warning - Ego (Official Video)</v>
+        <v>Kylie Minogue - Story (Official Lyric Video)</v>
       </c>
       <c r="B54" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=CG6Q5i75bR4</v>
+        <v>https://www.youtube.com/watch?v=fv7_1qKo8mg</v>
       </c>
       <c r="D54" t="str">
         <v>2026-06-01</v>
@@ -2433,7 +2433,7 @@
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>The Warning</v>
+        <v>Kylie Minogue</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>The Warning - Ego (Official Video) - The Warning</v>
+        <v>Kylie Minogue - Story (Official Lyric Video) - Kylie Minogue</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>paris jackson - teenage drama (official lyric video)</v>
+        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video)</v>
       </c>
       <c r="B55" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=kVfDArNljos</v>
+        <v>https://www.youtube.com/watch?v=3KUQx2s1fQc</v>
       </c>
       <c r="D55" t="str">
         <v>2026-06-01</v>
@@ -2471,7 +2471,7 @@
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>paris jackson</v>
+        <v>Billy Raffoul</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>paris jackson - teenage drama (official lyric video) - paris jackson</v>
+        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video) - Billy Raffoul</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Minelli - Sun Goes Down | Official Visualizer</v>
+        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025)</v>
       </c>
       <c r="B56" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=xOsjm-AwN5I</v>
+        <v>https://www.youtube.com/watch?v=vWf4uiLvwF8</v>
       </c>
       <c r="D56" t="str">
         <v>2026-06-01</v>
@@ -2509,7 +2509,7 @@
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>Minelli</v>
+        <v>The Offspring</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Minelli - Sun Goes Down | Official Visualizer - Minelli</v>
+        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025) - The Offspring</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Maggie Rose - Gentle Man (Official Studio Video)</v>
+        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024)</v>
       </c>
       <c r="B57" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=aWNK-vWrN60</v>
+        <v>https://www.youtube.com/watch?v=9xjMaXegmWM</v>
       </c>
       <c r="D57" t="str">
         <v>2026-06-01</v>
@@ -2547,7 +2547,7 @@
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>Maggie Rose</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Maggie Rose - Gentle Man (Official Studio Video) - Maggie Rose</v>
+        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024) - David Gilmour</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer]</v>
+        <v>Scorpions - Delicate Dance (Madison Square Garden 2022)</v>
       </c>
       <c r="B58" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=mN5AZBrVq9I</v>
+        <v>https://www.youtube.com/watch?v=yAjEr9WLTnU</v>
       </c>
       <c r="D58" t="str">
         <v>2026-06-01</v>
@@ -2585,7 +2585,7 @@
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>David Guetta</v>
+        <v>Scorpions</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer] - David Guetta</v>
+        <v>Scorpions - Delicate Dance (Madison Square Garden 2022) - Scorpions</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video)</v>
+        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston)</v>
       </c>
       <c r="B59" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=0PTufEGRAVQ</v>
+        <v>https://www.youtube.com/watch?v=oRw4PqBzGc0</v>
       </c>
       <c r="D59" t="str">
         <v>2026-06-01</v>
@@ -2623,7 +2623,7 @@
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>Chris Young and Shaylen</v>
+        <v>Brandon Lake and NICK JONAS</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video) - Chris Young and Shaylen</v>
+        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston) - Brandon Lake and NICK JONAS</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Lauv - Pretty Little Things</v>
+        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B60" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=_JBfanFvHnA</v>
+        <v>https://www.youtube.com/watch?v=OKf_IOGxFQo</v>
       </c>
       <c r="D60" t="str">
         <v>2026-06-01</v>
@@ -2661,7 +2661,7 @@
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>Lauv</v>
+        <v>Kygo and Dan Tyminski</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Lauv - Pretty Little Things - Lauv</v>
+        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video) - Kygo and Dan Tyminski</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Icona Pop - Butterfly Feelings (Official Audio)</v>
+        <v>The Warning - Ego (Official Video)</v>
       </c>
       <c r="B61" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=bXA_Q75QZTs</v>
+        <v>https://www.youtube.com/watch?v=CG6Q5i75bR4</v>
       </c>
       <c r="D61" t="str">
         <v>2026-06-01</v>
@@ -2699,7 +2699,7 @@
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>Icona Pop</v>
+        <v>The Warning</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Icona Pop - Butterfly Feelings (Official Audio) - Icona Pop</v>
+        <v>The Warning - Ego (Official Video) - The Warning</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Will Swinton - Only One (Official Video)</v>
+        <v>paris jackson - teenage drama (official lyric video)</v>
       </c>
       <c r="B62" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=A0KzP-zm9hA</v>
+        <v>https://www.youtube.com/watch?v=kVfDArNljos</v>
       </c>
       <c r="D62" t="str">
         <v>2026-06-01</v>
@@ -2737,7 +2737,7 @@
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>Will Swinton</v>
+        <v>paris jackson</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Will Swinton - Only One (Official Video) - Will Swinton</v>
+        <v>paris jackson - teenage drama (official lyric video) - paris jackson</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Dean Lewis - Escape (Official Video)</v>
+        <v>Minelli - Sun Goes Down | Official Visualizer</v>
       </c>
       <c r="B63" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=BZRaTXCkhcg</v>
+        <v>https://www.youtube.com/watch?v=xOsjm-AwN5I</v>
       </c>
       <c r="D63" t="str">
         <v>2026-06-01</v>
@@ -2775,7 +2775,7 @@
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>Dean Lewis</v>
+        <v>Minelli</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Dean Lewis - Escape (Official Video) - Dean Lewis</v>
+        <v>Minelli - Sun Goes Down | Official Visualizer - Minelli</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico]</v>
+        <v>Maggie Rose - Gentle Man (Official Studio Video)</v>
       </c>
       <c r="B64" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=PNm0hf_zZJY</v>
+        <v>https://www.youtube.com/watch?v=aWNK-vWrN60</v>
       </c>
       <c r="D64" t="str">
         <v>2026-06-01</v>
@@ -2813,7 +2813,7 @@
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>Dua Lipa and OficialMana</v>
+        <v>Maggie Rose</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico] - Dua Lipa and OficialMana</v>
+        <v>Maggie Rose - Gentle Man (Official Studio Video) - Maggie Rose</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Niall Horan - End of an Era (Lyric Video)</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer]</v>
       </c>
       <c r="B65" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=EUNNmAAe5gQ</v>
+        <v>https://www.youtube.com/watch?v=mN5AZBrVq9I</v>
       </c>
       <c r="D65" t="str">
         <v>2026-06-01</v>
@@ -2851,7 +2851,7 @@
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>Niall Horan</v>
+        <v>David Guetta</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Niall Horan - End of an Era (Lyric Video) - Niall Horan</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer] - David Guetta</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Olivia Rodrigo - the cure (Official Music Video)</v>
+        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video)</v>
       </c>
       <c r="B66" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=B402rKl4bUg</v>
+        <v>https://www.youtube.com/watch?v=0PTufEGRAVQ</v>
       </c>
       <c r="D66" t="str">
         <v>2026-06-01</v>
@@ -2889,7 +2889,7 @@
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>Olivia Rodrigo</v>
+        <v>Chris Young and Shaylen</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Olivia Rodrigo - the cure (Official Music Video) - Olivia Rodrigo</v>
+        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video) - Chris Young and Shaylen</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Ruel - Debbie Don't Cry (Official Music Video)</v>
+        <v>Lauv - Pretty Little Things</v>
       </c>
       <c r="B67" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=iz7wuk0GOwI</v>
+        <v>https://www.youtube.com/watch?v=_JBfanFvHnA</v>
       </c>
       <c r="D67" t="str">
         <v>2026-06-01</v>
@@ -2927,7 +2927,7 @@
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>RUEL</v>
+        <v>Lauv</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Ruel - Debbie Don't Cry (Official Music Video) - RUEL</v>
+        <v>Lauv - Pretty Little Things - Lauv</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>TINI - Down (LIVE)</v>
+        <v>Icona Pop - Butterfly Feelings (Official Audio)</v>
       </c>
       <c r="B68" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=ADbFeQUPTrk</v>
+        <v>https://www.youtube.com/watch?v=bXA_Q75QZTs</v>
       </c>
       <c r="D68" t="str">
         <v>2026-06-01</v>
@@ -2965,7 +2965,7 @@
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>TINI</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>TINI - Down (LIVE) - TINI</v>
+        <v>Icona Pop - Butterfly Feelings (Official Audio) - Icona Pop</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Charli xcx - SS26 (Official Video)</v>
+        <v>Will Swinton - Only One (Official Video)</v>
       </c>
       <c r="B69" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=twLhSqabby0</v>
+        <v>https://www.youtube.com/watch?v=A0KzP-zm9hA</v>
       </c>
       <c r="D69" t="str">
         <v>2026-06-01</v>
@@ -3003,7 +3003,7 @@
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>Charli xcx</v>
+        <v>Will Swinton</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Charli xcx - SS26 (Official Video) - Charli xcx</v>
+        <v>Will Swinton - Only One (Official Video) - Will Swinton</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Dua Lipa - Live From Mexico</v>
+        <v>Dean Lewis - Escape (Official Video)</v>
       </c>
       <c r="B70" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=vZYVkitGXBU</v>
+        <v>https://www.youtube.com/watch?v=BZRaTXCkhcg</v>
       </c>
       <c r="D70" t="str">
         <v>2026-06-01</v>
@@ -3041,7 +3041,7 @@
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>Dua Lipa</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Dua Lipa - Live From Mexico - Dua Lipa</v>
+        <v>Dean Lewis - Escape (Official Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Matilda Mann - 'The Fig Tree' (Official Video)</v>
+        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico]</v>
       </c>
       <c r="B71" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=XPyubkkkw44</v>
+        <v>https://www.youtube.com/watch?v=PNm0hf_zZJY</v>
       </c>
       <c r="D71" t="str">
         <v>2026-06-01</v>
@@ -3073,13 +3073,13 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>Matilda Mann</v>
+        <v>Dua Lipa and OficialMana</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Matilda Mann - 'The Fig Tree' (Official Video) - Matilda Mann</v>
+        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico] - Dua Lipa and OficialMana</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Ella Langley - Be Her (61st Academy of Country Music Awards)</v>
+        <v>Niall Horan - End of an Era (Lyric Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=4KbYfH7EAm8</v>
+        <v>https://www.youtube.com/watch?v=EUNNmAAe5gQ</v>
       </c>
       <c r="D72" t="str">
         <v>2026-06-01</v>
@@ -3111,13 +3111,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>Ella Langley</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Ella Langley - Be Her (61st Academy of Country Music Awards) - Ella Langley</v>
+        <v>Niall Horan - End of an Era (Lyric Video) - Niall Horan</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Nothing But Thieves - Evolution (Official Audio)</v>
+        <v>Olivia Rodrigo - the cure (Official Music Video)</v>
       </c>
       <c r="B73" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=Kcs-4EZSUW0</v>
+        <v>https://www.youtube.com/watch?v=B402rKl4bUg</v>
       </c>
       <c r="D73" t="str">
         <v>2026-06-01</v>
@@ -3149,13 +3149,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Nothing But Thieves - Evolution (Official Audio) - Nothing But Thieves</v>
+        <v>Olivia Rodrigo - the cure (Official Music Video) - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO)</v>
+        <v>Ruel - Debbie Don't Cry (Official Music Video)</v>
       </c>
       <c r="B74" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=HiLT1jzDZb4</v>
+        <v>https://www.youtube.com/watch?v=iz7wuk0GOwI</v>
       </c>
       <c r="D74" t="str">
         <v>2026-06-01</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>kesha</v>
+        <v>RUEL</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO) - kesha</v>
+        <v>Ruel - Debbie Don't Cry (Official Music Video) - RUEL</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify</v>
+        <v>TINI - Down (LIVE)</v>
       </c>
       <c r="B75" t="str">
-        <v>12 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=_WGsJYCCfU8</v>
+        <v>https://www.youtube.com/watch?v=ADbFeQUPTrk</v>
       </c>
       <c r="D75" t="str">
         <v>2026-06-01</v>
@@ -3225,13 +3225,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>12 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>Holly Humberstone</v>
+        <v>TINI</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify - Holly Humberstone</v>
+        <v>TINI - Down (LIVE) - TINI</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Foo Fighters - Of All People (Official Video)</v>
+        <v>Charli xcx - SS26 (Official Video)</v>
       </c>
       <c r="B76" t="str">
-        <v>12 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=r_iMzMrCQs0</v>
+        <v>https://www.youtube.com/watch?v=twLhSqabby0</v>
       </c>
       <c r="D76" t="str">
         <v>2026-06-01</v>
@@ -3263,13 +3263,13 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>12 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>Foo Fighters</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Foo Fighters - Of All People (Official Video) - Foo Fighters</v>
+        <v>Charli xcx - SS26 (Official Video) - Charli xcx</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>'From Me To You' by The Beatles, performed by The Young Analogues</v>
+        <v>Dua Lipa - Live From Mexico</v>
       </c>
       <c r="B77" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=cLiyO2t3xd0</v>
+        <v>https://www.youtube.com/watch?v=vZYVkitGXBU</v>
       </c>
       <c r="D77" t="str">
         <v>2026-06-01</v>
@@ -3301,13 +3301,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>The Analogues</v>
+        <v>Dua Lipa</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>'From Me To You' by The Beatles, performed by The Young Analogues - The Analogues</v>
+        <v>Dua Lipa - Live From Mexico - Dua Lipa</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video]</v>
+        <v>Matilda Mann - 'The Fig Tree' (Official Video)</v>
       </c>
       <c r="B78" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=O67Q25sMhyU</v>
+        <v>https://www.youtube.com/watch?v=XPyubkkkw44</v>
       </c>
       <c r="D78" t="str">
         <v>2026-06-01</v>
@@ -3339,13 +3339,13 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>Rod Stewart</v>
+        <v>Matilda Mann</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video] - Rod Stewart</v>
+        <v>Matilda Mann - 'The Fig Tree' (Official Video) - Matilda Mann</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Blue October - 18th Floor Balcony (Official Music Video)</v>
+        <v>Ella Langley - Be Her (61st Academy of Country Music Awards)</v>
       </c>
       <c r="B79" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=tPfbOjz-hRs</v>
+        <v>https://www.youtube.com/watch?v=4KbYfH7EAm8</v>
       </c>
       <c r="D79" t="str">
         <v>2026-06-01</v>
@@ -3383,7 +3383,7 @@
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>Blue October</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Blue October - 18th Floor Balcony (Official Music Video) - Blue October</v>
+        <v>Ella Langley - Be Her (61st Academy of Country Music Awards) - Ella Langley</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Far Caspian - hum (Official Video)</v>
+        <v>Nothing But Thieves - Evolution (Official Audio)</v>
       </c>
       <c r="B80" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=qqXrLDhGJRk</v>
+        <v>https://www.youtube.com/watch?v=Kcs-4EZSUW0</v>
       </c>
       <c r="D80" t="str">
         <v>2026-06-01</v>
@@ -3421,7 +3421,7 @@
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>Far Caspian</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Far Caspian - hum (Official Video) - Far Caspian</v>
+        <v>Nothing But Thieves - Evolution (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Kenia Os - Love Bombing</v>
+        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO)</v>
       </c>
       <c r="B81" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=ZuWA3pAyriQ</v>
+        <v>https://www.youtube.com/watch?v=HiLT1jzDZb4</v>
       </c>
       <c r="D81" t="str">
         <v>2026-06-01</v>
@@ -3459,7 +3459,7 @@
         <v/>
       </c>
       <c r="H81" t="str">
-        <v>Kenia Os</v>
+        <v>kesha</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Kenia Os - Love Bombing - Kenia Os</v>
+        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO) - kesha</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026</v>
+        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify</v>
       </c>
       <c r="B82" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=ftJR_CrRsig</v>
+        <v>https://www.youtube.com/watch?v=_WGsJYCCfU8</v>
       </c>
       <c r="D82" t="str">
         <v>2026-06-01</v>
@@ -3497,7 +3497,7 @@
         <v/>
       </c>
       <c r="H82" t="str">
-        <v>Purple Disco Machine</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026 - Purple Disco Machine</v>
+        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify - Holly Humberstone</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026</v>
+        <v>Foo Fighters - Of All People (Official Video)</v>
       </c>
       <c r="B83" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=EltgrumKJfk</v>
+        <v>https://www.youtube.com/watch?v=r_iMzMrCQs0</v>
       </c>
       <c r="D83" t="str">
         <v>2026-06-01</v>
@@ -3529,13 +3529,13 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
       </c>
       <c r="H83" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Foo Fighters - Of All People (Official Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹</v>
+        <v>'From Me To You' by The Beatles, performed by The Young Analogues</v>
       </c>
       <c r="B84" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=EykAYQj99GU</v>
+        <v>https://www.youtube.com/watch?v=cLiyO2t3xd0</v>
       </c>
       <c r="D84" t="str">
         <v>2026-06-01</v>
@@ -3567,13 +3567,13 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
       </c>
       <c r="H84" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>The Analogues</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹 - Eurovision Song Contest</v>
+        <v>'From Me To You' by The Beatles, performed by The Young Analogues - The Analogues</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026</v>
+        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video]</v>
       </c>
       <c r="B85" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=doGkDemPcFE</v>
+        <v>https://www.youtube.com/watch?v=O67Q25sMhyU</v>
       </c>
       <c r="D85" t="str">
         <v>2026-06-01</v>
@@ -3605,13 +3605,13 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
       </c>
       <c r="H85" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Rod Stewart</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video] - Rod Stewart</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026</v>
+        <v>Blue October - 18th Floor Balcony (Official Music Video)</v>
       </c>
       <c r="B86" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=rNpFNJLhSfA</v>
+        <v>https://www.youtube.com/watch?v=tPfbOjz-hRs</v>
       </c>
       <c r="D86" t="str">
         <v>2026-06-01</v>
@@ -3643,13 +3643,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Blue October</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Blue October - 18th Floor Balcony (Official Music Video) - Blue October</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026</v>
+        <v>Far Caspian - hum (Official Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=TpMQ6dhcvvE</v>
+        <v>https://www.youtube.com/watch?v=qqXrLDhGJRk</v>
       </c>
       <c r="D87" t="str">
         <v>2026-06-01</v>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Far Caspian</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Far Caspian - hum (Official Video) - Far Caspian</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​</v>
+        <v>Kenia Os - Love Bombing</v>
       </c>
       <c r="B88" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=ppCyj5DxO8s</v>
+        <v>https://www.youtube.com/watch?v=ZuWA3pAyriQ</v>
       </c>
       <c r="D88" t="str">
         <v>2026-06-01</v>
@@ -3719,13 +3719,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Kenia Os</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​ - Eurovision Song Contest</v>
+        <v>Kenia Os - Love Bombing - Kenia Os</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Evanescence – Who Will You Follow (Official Music Video)</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026</v>
       </c>
       <c r="B89" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=ak4Ti54Y6rY</v>
+        <v>https://www.youtube.com/watch?v=ftJR_CrRsig</v>
       </c>
       <c r="D89" t="str">
         <v>2026-06-01</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>Evanescence</v>
+        <v>Purple Disco Machine</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Evanescence – Who Will You Follow (Official Music Video) - Evanescence</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026 - Purple Disco Machine</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>DEEP PURPLE – ARROGANT BOY (Official Video)</v>
+        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026</v>
       </c>
       <c r="B90" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=SoSr0sStFaE</v>
+        <v>https://www.youtube.com/watch?v=EltgrumKJfk</v>
       </c>
       <c r="D90" t="str">
         <v>2026-06-01</v>
@@ -3801,7 +3801,7 @@
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>earMUSIC and Deep Purple Official</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>DEEP PURPLE – ARROGANT BOY (Official Video) - earMUSIC and Deep Purple Official</v>
+        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video]</v>
+        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹</v>
       </c>
       <c r="B91" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=9iCw89UajaQ</v>
+        <v>https://www.youtube.com/watch?v=EykAYQj99GU</v>
       </c>
       <c r="D91" t="str">
         <v>2026-06-01</v>
@@ -3839,7 +3839,7 @@
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>Armin van Buuren</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Madison Cunningham - "Take Two" (Live in Chicago)</v>
+        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B92" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=bUBLlJXtjqE</v>
+        <v>https://www.youtube.com/watch?v=doGkDemPcFE</v>
       </c>
       <c r="D92" t="str">
         <v>2026-06-01</v>
@@ -3877,7 +3877,7 @@
         <v/>
       </c>
       <c r="H92" t="str">
-        <v>Madison Cunningham</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Madison Cunningham - "Take Two" (Live in Chicago) - Madison Cunningham</v>
+        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Johnny Orlando - Heads Up (Official Video)</v>
+        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B93" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=s5mClhWsajE</v>
+        <v>https://www.youtube.com/watch?v=rNpFNJLhSfA</v>
       </c>
       <c r="D93" t="str">
         <v>2026-06-01</v>
@@ -3915,7 +3915,7 @@
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>Johnny Orlando</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Johnny Orlando - Heads Up (Official Video) - Johnny Orlando</v>
+        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Carver Jones - BEST FRIEND (Official Video)</v>
+        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B94" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=96xxxpZ5uxI</v>
+        <v>https://www.youtube.com/watch?v=TpMQ6dhcvvE</v>
       </c>
       <c r="D94" t="str">
         <v>2026-06-01</v>
@@ -3953,7 +3953,7 @@
         <v/>
       </c>
       <c r="H94" t="str">
-        <v>Carver Jones</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Carver Jones - BEST FRIEND (Official Video) - Carver Jones</v>
+        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Jazmin Bean - Darling (Official Music Video)</v>
+        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​</v>
       </c>
       <c r="B95" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=N4uW3ZcowBM</v>
+        <v>https://www.youtube.com/watch?v=ppCyj5DxO8s</v>
       </c>
       <c r="D95" t="str">
         <v>2026-06-01</v>
@@ -3991,7 +3991,7 @@
         <v/>
       </c>
       <c r="H95" t="str">
-        <v>Jazmin bean</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Jazmin Bean - Darling (Official Music Video) - Jazmin bean</v>
+        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​ - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Baby Queen - Word Vomit (Official Visualiser)</v>
+        <v>Evanescence – Who Will You Follow (Official Music Video)</v>
       </c>
       <c r="B96" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=T-bo4Klq_js</v>
+        <v>https://www.youtube.com/watch?v=ak4Ti54Y6rY</v>
       </c>
       <c r="D96" t="str">
         <v>2026-06-01</v>
@@ -4029,7 +4029,7 @@
         <v/>
       </c>
       <c r="H96" t="str">
-        <v>Baby Queen</v>
+        <v>Evanescence</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Baby Queen - Word Vomit (Official Visualiser) - Baby Queen</v>
+        <v>Evanescence – Who Will You Follow (Official Music Video) - Evanescence</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Switchfoot - Absolution (Official Audio)</v>
+        <v>DEEP PURPLE – ARROGANT BOY (Official Video)</v>
       </c>
       <c r="B97" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=nCOSfMdKq9k</v>
+        <v>https://www.youtube.com/watch?v=SoSr0sStFaE</v>
       </c>
       <c r="D97" t="str">
         <v>2026-06-01</v>
@@ -4067,7 +4067,7 @@
         <v/>
       </c>
       <c r="H97" t="str">
-        <v>Switchfoot</v>
+        <v>earMUSIC and Deep Purple Official</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Switchfoot - Absolution (Official Audio) - Switchfoot</v>
+        <v>DEEP PURPLE – ARROGANT BOY (Official Video) - earMUSIC and Deep Purple Official</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Grace Potter - Love Me Not (Official Audio)</v>
+        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B98" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=W3v0HAxDTUY</v>
+        <v>https://www.youtube.com/watch?v=9iCw89UajaQ</v>
       </c>
       <c r="D98" t="str">
         <v>2026-06-01</v>
@@ -4105,7 +4105,7 @@
         <v/>
       </c>
       <c r="H98" t="str">
-        <v>Grace Potter</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Grace Potter - Love Me Not (Official Audio) - Grace Potter</v>
+        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.08.1986)</v>
+        <v>Madison Cunningham - "Take Two" (Live in Chicago)</v>
       </c>
       <c r="B99" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=Dhy4xH662vE</v>
+        <v>https://www.youtube.com/watch?v=bUBLlJXtjqE</v>
       </c>
       <c r="D99" t="str">
         <v>2026-06-01</v>
@@ -4143,7 +4143,7 @@
         <v/>
       </c>
       <c r="H99" t="str">
-        <v>Modern Talking Offiziell</v>
+        <v>Madison Cunningham</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.08.1986) - Modern Talking Offiziell</v>
+        <v>Madison Cunningham - "Take Two" (Live in Chicago) - Madison Cunningham</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>The All-American Rejects - Clothesline (Official Lyric Video)</v>
+        <v>Johnny Orlando - Heads Up (Official Video)</v>
       </c>
       <c r="B100" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=y9axmk3NjrA</v>
+        <v>https://www.youtube.com/watch?v=s5mClhWsajE</v>
       </c>
       <c r="D100" t="str">
         <v>2026-06-01</v>
@@ -4181,7 +4181,7 @@
         <v/>
       </c>
       <c r="H100" t="str">
-        <v>The All-American Rejects</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>The All-American Rejects - Clothesline (Official Lyric Video) - The All-American Rejects</v>
+        <v>Johnny Orlando - Heads Up (Official Video) - Johnny Orlando</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Henry Moodie - MISS U (Official Visualiser)</v>
+        <v>Carver Jones - BEST FRIEND (Official Video)</v>
       </c>
       <c r="B101" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=l_lroRlSmTE</v>
+        <v>https://www.youtube.com/watch?v=96xxxpZ5uxI</v>
       </c>
       <c r="D101" t="str">
         <v>2026-06-01</v>
@@ -4219,7 +4219,7 @@
         <v/>
       </c>
       <c r="H101" t="str">
-        <v>Henry Moodie</v>
+        <v>Carver Jones</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Henry Moodie - MISS U (Official Visualiser) - Henry Moodie</v>
+        <v>Carver Jones - BEST FRIEND (Official Video) - Carver Jones</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Spacey Jane - I Never See Her (Official Music Video)</v>
+        <v>Jazmin Bean - Darling (Official Music Video)</v>
       </c>
       <c r="B102" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=q6tyEMN5haA</v>
+        <v>https://www.youtube.com/watch?v=N4uW3ZcowBM</v>
       </c>
       <c r="D102" t="str">
         <v>2026-06-01</v>
@@ -4257,7 +4257,7 @@
         <v/>
       </c>
       <c r="H102" t="str">
-        <v>Spacey Jane</v>
+        <v>Jazmin bean</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4269,18 +4269,18 @@
         <v/>
       </c>
       <c r="L102" t="str">
-        <v>Spacey Jane - I Never See Her (Official Music Video) - Spacey Jane</v>
+        <v>Jazmin Bean - Darling (Official Music Video) - Jazmin bean</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video)</v>
+        <v>Baby Queen - Word Vomit (Official Visualiser)</v>
       </c>
       <c r="B103" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C103" t="str">
-        <v>https://www.youtube.com/watch?v=qacdvCqOZGc</v>
+        <v>https://www.youtube.com/watch?v=T-bo4Klq_js</v>
       </c>
       <c r="D103" t="str">
         <v>2026-06-01</v>
@@ -4295,7 +4295,7 @@
         <v/>
       </c>
       <c r="H103" t="str">
-        <v>Megan Moroney</v>
+        <v>Baby Queen</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4307,18 +4307,18 @@
         <v/>
       </c>
       <c r="L103" t="str">
-        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video) - Megan Moroney</v>
+        <v>Baby Queen - Word Vomit (Official Visualiser) - Baby Queen</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Matt Hansen - Orchid (Official Visualiser)</v>
+        <v>Switchfoot - Absolution (Official Audio)</v>
       </c>
       <c r="B104" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C104" t="str">
-        <v>https://www.youtube.com/watch?v=otVYamnbOhY</v>
+        <v>https://www.youtube.com/watch?v=nCOSfMdKq9k</v>
       </c>
       <c r="D104" t="str">
         <v>2026-06-01</v>
@@ -4333,7 +4333,7 @@
         <v/>
       </c>
       <c r="H104" t="str">
-        <v>Matt Hansen</v>
+        <v>Switchfoot</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4345,18 +4345,18 @@
         <v/>
       </c>
       <c r="L104" t="str">
-        <v>Matt Hansen - Orchid (Official Visualiser) - Matt Hansen</v>
+        <v>Switchfoot - Absolution (Official Audio) - Switchfoot</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>hate that i made you love me</v>
+        <v>Grace Potter - Love Me Not (Official Audio)</v>
       </c>
       <c r="B105" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/hate-that-i-made-you-love-me/6763656876</v>
+        <v>https://www.youtube.com/watch?v=W3v0HAxDTUY</v>
       </c>
       <c r="D105" t="str">
         <v>2026-06-01</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>petal</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G105" t="str">
-        <v>3:17</v>
+        <v/>
       </c>
       <c r="H105" t="str">
-        <v>Ariana Grande</v>
+        <v>Grace Potter</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/ariana-grande/412778295</v>
+        <v/>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/hate-that-i-made-you-love-me/1895420989</v>
+        <v/>
       </c>
       <c r="L105" t="str">
-        <v>hate that i made you love me - Ariana Grande</v>
+        <v>Grace Potter - Love Me Not (Official Audio) - Grace Potter</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Come Inside</v>
+        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.08.1986)</v>
       </c>
       <c r="B106" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/come-inside/1887403093</v>
+        <v>https://www.youtube.com/watch?v=Dhy4xH662vE</v>
       </c>
       <c r="D106" t="str">
         <v>2026-06-01</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>The Boys of Dungeon Lane</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G106" t="str">
-        <v>3:13</v>
+        <v/>
       </c>
       <c r="H106" t="str">
-        <v>Paul McCartney</v>
+        <v>Modern Talking Offiziell</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/paul-mccartney/12224</v>
+        <v/>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/come-inside/1887402919</v>
+        <v/>
       </c>
       <c r="L106" t="str">
-        <v>Come Inside - Paul McCartney</v>
+        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.08.1986) - Modern Talking Offiziell</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Game Time</v>
+        <v>The All-American Rejects - Clothesline (Official Lyric Video)</v>
       </c>
       <c r="B107" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/game-time/6771157200</v>
+        <v>https://www.youtube.com/watch?v=y9axmk3NjrA</v>
       </c>
       <c r="D107" t="str">
         <v>2026-06-01</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>Game Time (FIFA World Cup 2026™) - Single</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G107" t="str">
-        <v>3:26</v>
+        <v/>
       </c>
       <c r="H107" t="str">
-        <v>Future</v>
+        <v>The All-American Rejects</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/future/128050210</v>
+        <v/>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/game-time/6771157186</v>
+        <v/>
       </c>
       <c r="L107" t="str">
-        <v>Game Time - Future</v>
+        <v>The All-American Rejects - Clothesline (Official Lyric Video) - The All-American Rejects</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Motion Party (Remix)</v>
+        <v>Henry Moodie - MISS U (Official Visualiser)</v>
       </c>
       <c r="B108" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/motion-party-remix/6773413965</v>
+        <v>https://www.youtube.com/watch?v=l_lroRlSmTE</v>
       </c>
       <c r="D108" t="str">
         <v>2026-06-01</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Motion Party (Remix) - Single</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G108" t="str">
-        <v>2:36</v>
+        <v/>
       </c>
       <c r="H108" t="str">
-        <v>Bossman Dlow</v>
+        <v>Henry Moodie</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/bossman-dlow/1474308236</v>
+        <v/>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/motion-party-remix/6773413953</v>
+        <v/>
       </c>
       <c r="L108" t="str">
-        <v>Motion Party (Remix) - Bossman Dlow</v>
+        <v>Henry Moodie - MISS U (Official Visualiser) - Henry Moodie</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Aquel diciembre</v>
+        <v>Spacey Jane - I Never See Her (Official Music Video)</v>
       </c>
       <c r="B109" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/aquel-diciembre/6769580010</v>
+        <v>https://www.youtube.com/watch?v=q6tyEMN5haA</v>
       </c>
       <c r="D109" t="str">
         <v>2026-06-01</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>Do Not Disturb: Late Checkout</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G109" t="str">
-        <v>3:22</v>
+        <v/>
       </c>
       <c r="H109" t="str">
-        <v>Young Miko</v>
+        <v>Spacey Jane</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/young-miko/1576521417</v>
+        <v/>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/aquel-diciembre/6769579992</v>
+        <v/>
       </c>
       <c r="L109" t="str">
-        <v>Aquel diciembre - Young Miko</v>
+        <v>Spacey Jane - I Never See Her (Official Music Video) - Spacey Jane</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Handle</v>
+        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video)</v>
       </c>
       <c r="B110" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/handle/6771922623</v>
+        <v>https://www.youtube.com/watch?v=qacdvCqOZGc</v>
       </c>
       <c r="D110" t="str">
         <v>2026-06-01</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Blue Island</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G110" t="str">
-        <v>3:06</v>
+        <v/>
       </c>
       <c r="H110" t="str">
-        <v>Ravyn Lenae</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/ravyn-lenae/1044417443</v>
+        <v/>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/handle/6771922622</v>
+        <v/>
       </c>
       <c r="L110" t="str">
-        <v>Handle - Ravyn Lenae</v>
+        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>The Wave</v>
+        <v>Matt Hansen - Orchid (Official Visualiser)</v>
       </c>
       <c r="B111" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/the-wave/1886730541</v>
+        <v>https://www.youtube.com/watch?v=otVYamnbOhY</v>
       </c>
       <c r="D111" t="str">
         <v>2026-06-01</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Sunshine</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G111" t="str">
-        <v>3:22</v>
+        <v/>
       </c>
       <c r="H111" t="str">
-        <v>Jungle</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/jungle/825833522</v>
+        <v/>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/the-wave/1886730527</v>
+        <v/>
       </c>
       <c r="L111" t="str">
-        <v>The Wave - Jungle</v>
+        <v>Matt Hansen - Orchid (Official Visualiser) - Matt Hansen</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>STOP</v>
+        <v>Every Single Weekend (feat. Jamie xx)</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/stop/6771161771</v>
+        <v>https://music.apple.com/us/song/every-single-weekend-feat-jamie-xx/6770445933</v>
       </c>
       <c r="D112" t="str">
         <v>2026-06-01</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>are you mad at me? - Single</v>
+        <v>Every Single Weekend (feat. Jamie xx) - Single</v>
       </c>
       <c r="G112" t="str">
-        <v>2:56</v>
+        <v>2:10</v>
       </c>
       <c r="H112" t="str">
-        <v>Bella Kay</v>
+        <v>The Avalanches</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
+        <v>https://music.apple.com/us/artist/the-avalanches/27524431</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/stop/6771161760</v>
+        <v>https://music.apple.com/us/album/every-single-weekend-feat-jamie-xx/6770445752</v>
       </c>
       <c r="L112" t="str">
-        <v>STOP - Bella Kay</v>
+        <v>Every Single Weekend (feat. Jamie xx) - The Avalanches</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Here (Apple Music Sessions)</v>
+        <v>hate that i made you love me</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/here-apple-music-sessions/1878235516</v>
+        <v>https://music.apple.com/us/song/hate-that-i-made-you-love-me/6763656876</v>
       </c>
       <c r="D113" t="str">
         <v>2026-06-01</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Apple Music Sessions</v>
+        <v>petal</v>
       </c>
       <c r="G113" t="str">
-        <v>3:08</v>
+        <v>3:17</v>
       </c>
       <c r="H113" t="str">
-        <v>Mumford &amp; Sons</v>
+        <v>Ariana Grande</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/mumford-sons/307699986</v>
+        <v>https://music.apple.com/us/artist/ariana-grande/412778295</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/here-apple-music-sessions/1878235330</v>
+        <v>https://music.apple.com/us/album/hate-that-i-made-you-love-me/1895420989</v>
       </c>
       <c r="L113" t="str">
-        <v>Here (Apple Music Sessions) - Mumford &amp; Sons</v>
+        <v>hate that i made you love me - Ariana Grande</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Talk On The Hill</v>
+        <v>Come Inside</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/talk-on-the-hill/6769524458</v>
+        <v>https://music.apple.com/us/song/come-inside/1887403093</v>
       </c>
       <c r="D114" t="str">
         <v>2026-06-01</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>The Thread</v>
+        <v>The Boys of Dungeon Lane</v>
       </c>
       <c r="G114" t="str">
-        <v>3:27</v>
+        <v>3:13</v>
       </c>
       <c r="H114" t="str">
-        <v>WILLOW</v>
+        <v>Paul McCartney</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/willow/400531893</v>
+        <v>https://music.apple.com/us/artist/paul-mccartney/12224</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/talk-on-the-hill/6769524450</v>
+        <v>https://music.apple.com/us/album/come-inside/1887402919</v>
       </c>
       <c r="L114" t="str">
-        <v>Talk On The Hill - WILLOW</v>
+        <v>Come Inside - Paul McCartney</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>No Fear</v>
+        <v>Game Time</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/no-fear/1880484493</v>
+        <v>https://music.apple.com/us/song/game-time/6771157200</v>
       </c>
       <c r="D115" t="str">
         <v>2026-06-01</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>For Love of Grace &amp; the Hereafter</v>
+        <v>Game Time (FIFA World Cup 2026™) - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>3:38</v>
+        <v>3:26</v>
       </c>
       <c r="H115" t="str">
-        <v>Iceage</v>
+        <v>Future</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/iceage/406846711</v>
+        <v>https://music.apple.com/us/artist/future/128050210</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/no-fear/1880484160</v>
+        <v>https://music.apple.com/us/album/game-time/6771157186</v>
       </c>
       <c r="L115" t="str">
-        <v>No Fear - Iceage</v>
+        <v>Game Time - Future</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Hostage</v>
+        <v>Motion Party (Remix)</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/hostage/6774372288</v>
+        <v>https://music.apple.com/us/song/motion-party-remix/6773413965</v>
       </c>
       <c r="D116" t="str">
         <v>2026-06-01</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Big Mama</v>
+        <v>Motion Party (Remix) - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>3:11</v>
+        <v>2:36</v>
       </c>
       <c r="H116" t="str">
-        <v>Latto</v>
+        <v>Bossman Dlow</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/latto/419799506</v>
+        <v>https://music.apple.com/us/artist/bossman-dlow/1474308236</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/hostage/6774372200</v>
+        <v>https://music.apple.com/us/album/motion-party-remix/6773413953</v>
       </c>
       <c r="L116" t="str">
-        <v>Hostage - Latto</v>
+        <v>Motion Party (Remix) - Bossman Dlow</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Sad Girls</v>
+        <v>Aquel diciembre</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/sad-girls/6768814374</v>
+        <v>https://music.apple.com/us/song/aquel-diciembre/6769580010</v>
       </c>
       <c r="D117" t="str">
         <v>2026-06-01</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Sad Girls - Single</v>
+        <v>Do Not Disturb: Late Checkout</v>
       </c>
       <c r="G117" t="str">
-        <v>2:48</v>
+        <v>3:22</v>
       </c>
       <c r="H117" t="str">
-        <v>Bebe Rexha</v>
+        <v>Young Miko</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/bebe-rexha/466059563</v>
+        <v>https://music.apple.com/us/artist/young-miko/1576521417</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/sad-girls/6768814373</v>
+        <v>https://music.apple.com/us/album/aquel-diciembre/6769579992</v>
       </c>
       <c r="L117" t="str">
-        <v>Sad Girls - Bebe Rexha</v>
+        <v>Aquel diciembre - Young Miko</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Salvame Hoy (feat. Gabito Ballesteros)</v>
+        <v>Handle</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/salvame-hoy-feat-gabito-ballesteros/6765697019</v>
+        <v>https://music.apple.com/us/song/handle/6771922623</v>
       </c>
       <c r="D118" t="str">
         <v>2026-06-01</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Salvame Hoy (feat. Gabito Ballesteros) - Single</v>
+        <v>Blue Island</v>
       </c>
       <c r="G118" t="str">
-        <v>3:35</v>
+        <v>3:06</v>
       </c>
       <c r="H118" t="str">
-        <v>Jennifer Lopez</v>
+        <v>Ravyn Lenae</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/jennifer-lopez/463009</v>
+        <v>https://music.apple.com/us/artist/ravyn-lenae/1044417443</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/salvame-hoy-feat-gabito-ballesteros/1896041010</v>
+        <v>https://music.apple.com/us/album/handle/6771922622</v>
       </c>
       <c r="L118" t="str">
-        <v>Salvame Hoy (feat. Gabito Ballesteros) - Jennifer Lopez</v>
+        <v>Handle - Ravyn Lenae</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Rubio</v>
+        <v>The Wave</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/rubio/6770655339</v>
+        <v>https://music.apple.com/us/song/the-wave/1886730541</v>
       </c>
       <c r="D119" t="str">
         <v>2026-06-01</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>La Voz Favorita</v>
+        <v>Sunshine</v>
       </c>
       <c r="G119" t="str">
-        <v>4:42</v>
+        <v>3:22</v>
       </c>
       <c r="H119" t="str">
-        <v>Jay Wheeler</v>
+        <v>Jungle</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/jay-wheeler/164376380</v>
+        <v>https://music.apple.com/us/artist/jungle/825833522</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/rubio/6770654729</v>
+        <v>https://music.apple.com/us/album/the-wave/1886730527</v>
       </c>
       <c r="L119" t="str">
-        <v>Rubio - Jay Wheeler</v>
+        <v>The Wave - Jungle</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Pary</v>
+        <v>STOP</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/pary/6767367748</v>
+        <v>https://music.apple.com/us/song/stop/6771161771</v>
       </c>
       <c r="D120" t="str">
         <v>2026-06-01</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Con dolor - EP</v>
+        <v>are you mad at me? - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>2:52</v>
+        <v>2:56</v>
       </c>
       <c r="H120" t="str">
-        <v>Grupo Frontera</v>
+        <v>Bella Kay</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
+        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/pary/6767367501</v>
+        <v>https://music.apple.com/us/album/stop/6771161760</v>
       </c>
       <c r="L120" t="str">
-        <v>Pary - Grupo Frontera</v>
+        <v>STOP - Bella Kay</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Think As You Drunk</v>
+        <v>Here (Apple Music Sessions)</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/think-as-you-drunk/6770725979</v>
+        <v>https://music.apple.com/us/song/here-apple-music-sessions/1878235516</v>
       </c>
       <c r="D121" t="str">
         <v>2026-06-01</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>That's Just Me</v>
+        <v>Apple Music Sessions</v>
       </c>
       <c r="G121" t="str">
-        <v>3:48</v>
+        <v>3:08</v>
       </c>
       <c r="H121" t="str">
-        <v>Riley Green</v>
+        <v>Mumford &amp; Sons</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/riley-green/662432971</v>
+        <v>https://music.apple.com/us/artist/mumford-sons/307699986</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/think-as-you-drunk/6770725355</v>
+        <v>https://music.apple.com/us/album/here-apple-music-sessions/1878235330</v>
       </c>
       <c r="L121" t="str">
-        <v>Think As You Drunk - Riley Green</v>
+        <v>Here (Apple Music Sessions) - Mumford &amp; Sons</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Play Your Games</v>
+        <v>Talk On The Hill</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/play-your-games/6772932837</v>
+        <v>https://music.apple.com/us/song/talk-on-the-hill/6769524458</v>
       </c>
       <c r="D122" t="str">
         <v>2026-06-01</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Play Your Games - Single</v>
+        <v>The Thread</v>
       </c>
       <c r="G122" t="str">
-        <v>3:15</v>
+        <v>3:27</v>
       </c>
       <c r="H122" t="str">
-        <v>Greta Van Fleet</v>
+        <v>WILLOW</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/greta-van-fleet/646178956</v>
+        <v>https://music.apple.com/us/artist/willow/400531893</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/play-your-games/6772932835</v>
+        <v>https://music.apple.com/us/album/talk-on-the-hill/6769524450</v>
       </c>
       <c r="L122" t="str">
-        <v>Play Your Games - Greta Van Fleet</v>
+        <v>Talk On The Hill - WILLOW</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello)</v>
+        <v>No Fear</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/adjourn-it-feat-serj-tankian-roman-morello/6769340216</v>
+        <v>https://music.apple.com/us/song/no-fear/1880484493</v>
       </c>
       <c r="D123" t="str">
         <v>2026-06-01</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello) - Single</v>
+        <v>For Love of Grace &amp; the Hereafter</v>
       </c>
       <c r="G123" t="str">
-        <v>2:47</v>
+        <v>3:38</v>
       </c>
       <c r="H123" t="str">
-        <v>Tom Morello</v>
+        <v>Iceage</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/tom-morello/466357</v>
+        <v>https://music.apple.com/us/artist/iceage/406846711</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/adjourn-it-feat-serj-tankian-roman-morello/6769340214</v>
+        <v>https://music.apple.com/us/album/no-fear/1880484160</v>
       </c>
       <c r="L123" t="str">
-        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello) - Tom Morello</v>
+        <v>No Fear - Iceage</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Essex_Honey.mp3</v>
+        <v>Hostage</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/essex-honey-mp3/6771169447</v>
+        <v>https://music.apple.com/us/song/hostage/6774372288</v>
       </c>
       <c r="D124" t="str">
         <v>2026-06-01</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Essex_Honey.mp3 - Single</v>
+        <v>Big Mama</v>
       </c>
       <c r="G124" t="str">
-        <v>4:49</v>
+        <v>3:11</v>
       </c>
       <c r="H124" t="str">
-        <v>Blood Orange</v>
+        <v>Latto</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/blood-orange/440698865</v>
+        <v>https://music.apple.com/us/artist/latto/419799506</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/essex-honey-mp3/6771169151</v>
+        <v>https://music.apple.com/us/album/hostage/6774372200</v>
       </c>
       <c r="L124" t="str">
-        <v>Essex_Honey.mp3 - Blood Orange</v>
+        <v>Hostage - Latto</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>minute</v>
+        <v>Sad Girls</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/minute/1875303122</v>
+        <v>https://music.apple.com/us/song/sad-girls/6768814374</v>
       </c>
       <c r="D125" t="str">
         <v>2026-06-01</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>ghosted - EP</v>
+        <v>Sad Girls - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>2:59</v>
+        <v>2:48</v>
       </c>
       <c r="H125" t="str">
-        <v>Saint Harison</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/saint-harison/1639595302</v>
+        <v>https://music.apple.com/us/artist/bebe-rexha/466059563</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/minute/1875302904</v>
+        <v>https://music.apple.com/us/album/sad-girls/6768814373</v>
       </c>
       <c r="L125" t="str">
-        <v>minute - Saint Harison</v>
+        <v>Sad Girls - Bebe Rexha</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>THE LIVING</v>
+        <v>Salvame Hoy (feat. Gabito Ballesteros)</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/the-living/1894092345</v>
+        <v>https://music.apple.com/us/song/salvame-hoy-feat-gabito-ballesteros/6765697019</v>
       </c>
       <c r="D126" t="str">
         <v>2026-06-01</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>COSMIC OPERA ACT II</v>
+        <v>Salvame Hoy (feat. Gabito Ballesteros) - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>2:48</v>
+        <v>3:35</v>
       </c>
       <c r="H126" t="str">
-        <v>Labrinth</v>
+        <v>Jennifer Lopez</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
+        <v>https://music.apple.com/us/artist/jennifer-lopez/463009</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/the-living/1894092339</v>
+        <v>https://music.apple.com/us/album/salvame-hoy-feat-gabito-ballesteros/1896041010</v>
       </c>
       <c r="L126" t="str">
-        <v>THE LIVING - Labrinth</v>
+        <v>Salvame Hoy (feat. Gabito Ballesteros) - Jennifer Lopez</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Thug</v>
+        <v>Rubio</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/thug/6769289966</v>
+        <v>https://music.apple.com/us/song/rubio/6770655339</v>
       </c>
       <c r="D127" t="str">
         <v>2026-06-01</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Thug - Single</v>
+        <v>La Voz Favorita</v>
       </c>
       <c r="G127" t="str">
-        <v>2:25</v>
+        <v>4:42</v>
       </c>
       <c r="H127" t="str">
-        <v>G Herbo</v>
+        <v>Jay Wheeler</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/g-herbo/1036753321</v>
+        <v>https://music.apple.com/us/artist/jay-wheeler/164376380</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/thug/6769289953</v>
+        <v>https://music.apple.com/us/album/rubio/6770654729</v>
       </c>
       <c r="L127" t="str">
-        <v>Thug - G Herbo</v>
+        <v>Rubio - Jay Wheeler</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Clap</v>
+        <v>Pary</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/clap/6769903711</v>
+        <v>https://music.apple.com/us/song/pary/6767367748</v>
       </c>
       <c r="D128" t="str">
         <v>2026-06-01</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Clap - Single</v>
+        <v>Con dolor - EP</v>
       </c>
       <c r="G128" t="str">
-        <v>2:04</v>
+        <v>2:52</v>
       </c>
       <c r="H128" t="str">
-        <v>Polo G</v>
+        <v>Grupo Frontera</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/polo-g/1159371412</v>
+        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/clap/6769903710</v>
+        <v>https://music.apple.com/us/album/pary/6767367501</v>
       </c>
       <c r="L128" t="str">
-        <v>Clap - Polo G</v>
+        <v>Pary - Grupo Frontera</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>GANG BIZNESS</v>
+        <v>Think As You Drunk</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/gang-bizness/6772383809</v>
+        <v>https://music.apple.com/us/song/think-as-you-drunk/6770725979</v>
       </c>
       <c r="D129" t="str">
         <v>2026-06-01</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>THE GENTLEMEN'S CLUB</v>
+        <v>That's Just Me</v>
       </c>
       <c r="G129" t="str">
-        <v>2:47</v>
+        <v>3:48</v>
       </c>
       <c r="H129" t="str">
-        <v>YG</v>
+        <v>Riley Green</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/yg/189792075</v>
+        <v>https://music.apple.com/us/artist/riley-green/662432971</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/gang-bizness/6772383681</v>
+        <v>https://music.apple.com/us/album/think-as-you-drunk/6770725355</v>
       </c>
       <c r="L129" t="str">
-        <v>GANG BIZNESS - YG</v>
+        <v>Think As You Drunk - Riley Green</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>UR HEARTBEAT (WHO DO U THINK ABOUT AT 2AM?)</v>
+        <v>Play Your Games</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/ur-heartbeat-who-do-u-think-about-at-2am/6765534140</v>
+        <v>https://music.apple.com/us/song/play-your-games/6772932837</v>
       </c>
       <c r="D130" t="str">
         <v>2026-06-01</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>A LITTLE VENGEANCE</v>
+        <v>Play Your Games - Single</v>
       </c>
       <c r="G130" t="str">
-        <v>2:50</v>
+        <v>3:15</v>
       </c>
       <c r="H130" t="str">
-        <v>Jessie Reyez</v>
+        <v>Greta Van Fleet</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
+        <v>https://music.apple.com/us/artist/greta-van-fleet/646178956</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/ur-heartbeat-who-do-u-think-about-at-2am/1895983502</v>
+        <v>https://music.apple.com/us/album/play-your-games/6772932835</v>
       </c>
       <c r="L130" t="str">
-        <v>UR HEARTBEAT (WHO DO U THINK ABOUT AT 2AM?) - Jessie Reyez</v>
+        <v>Play Your Games - Greta Van Fleet</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Joshua Tree</v>
+        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello)</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/joshua-tree/6771859148</v>
+        <v>https://music.apple.com/us/song/adjourn-it-feat-serj-tankian-roman-morello/6769340216</v>
       </c>
       <c r="D131" t="str">
         <v>2026-06-01</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Euphoria: Season 3 (HBO Original Series Soundtrack)</v>
+        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello) - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>2:50</v>
+        <v>2:47</v>
       </c>
       <c r="H131" t="str">
-        <v>Hans Zimmer</v>
+        <v>Tom Morello</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/hans-zimmer/454295032</v>
+        <v>https://music.apple.com/us/artist/tom-morello/466357</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/joshua-tree/6771858464</v>
+        <v>https://music.apple.com/us/album/adjourn-it-feat-serj-tankian-roman-morello/6769340214</v>
       </c>
       <c r="L131" t="str">
-        <v>Joshua Tree - Hans Zimmer</v>
+        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello) - Tom Morello</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Mi Gran Amor</v>
+        <v>Essex_Honey.mp3</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/mi-gran-amor/6773365775</v>
+        <v>https://music.apple.com/us/song/essex-honey-mp3/6771169447</v>
       </c>
       <c r="D132" t="str">
         <v>2026-06-01</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Mi Gran Amor - Single</v>
+        <v>Essex_Honey.mp3 - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>3:37</v>
+        <v>4:49</v>
       </c>
       <c r="H132" t="str">
-        <v>Santana</v>
+        <v>Blood Orange</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/santana/217174</v>
+        <v>https://music.apple.com/us/artist/blood-orange/440698865</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/mi-gran-amor/6773365236</v>
+        <v>https://music.apple.com/us/album/essex-honey-mp3/6771169151</v>
       </c>
       <c r="L132" t="str">
-        <v>Mi Gran Amor - Santana</v>
+        <v>Essex_Honey.mp3 - Blood Orange</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>london</v>
+        <v>minute</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/london/6770745672</v>
+        <v>https://music.apple.com/us/song/minute/1875303122</v>
       </c>
       <c r="D133" t="str">
         <v>2026-06-01</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>stardust - EP</v>
+        <v>ghosted - EP</v>
       </c>
       <c r="G133" t="str">
-        <v>3:23</v>
+        <v>2:59</v>
       </c>
       <c r="H133" t="str">
-        <v>Freya Skye</v>
+        <v>Saint Harison</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/freya-skye/1541643053</v>
+        <v>https://music.apple.com/us/artist/saint-harison/1639595302</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/london/6770745662</v>
+        <v>https://music.apple.com/us/album/minute/1875302904</v>
       </c>
       <c r="L133" t="str">
-        <v>london - Freya Skye</v>
+        <v>minute - Saint Harison</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Caution</v>
+        <v>THE LIVING</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/caution/6768487482</v>
+        <v>https://music.apple.com/us/song/the-living/1894092345</v>
       </c>
       <c r="D134" t="str">
         <v>2026-06-01</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>K-POPS! (Music from and inspired by K-POPS! Motion Picture)</v>
+        <v>COSMIC OPERA ACT II</v>
       </c>
       <c r="G134" t="str">
-        <v>2:43</v>
+        <v>2:48</v>
       </c>
       <c r="H134" t="str">
-        <v>NMIXX</v>
+        <v>Labrinth</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/nmixx/1600411676</v>
+        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/caution/6768487478</v>
+        <v>https://music.apple.com/us/album/the-living/1894092339</v>
       </c>
       <c r="L134" t="str">
-        <v>Caution - NMIXX</v>
+        <v>THE LIVING - Labrinth</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>LEMONADE (feat. Becky G)</v>
+        <v>Thug</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/lemonade-feat-becky-g/1893742425</v>
+        <v>https://music.apple.com/us/song/thug/6769289966</v>
       </c>
       <c r="D135" t="str">
         <v>2026-06-01</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>LEMONADE - The 2nd Album</v>
+        <v>Thug - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>3:07</v>
+        <v>2:25</v>
       </c>
       <c r="H135" t="str">
-        <v>aespa</v>
+        <v>G Herbo</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
+        <v>https://music.apple.com/us/artist/g-herbo/1036753321</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/lemonade-feat-becky-g/1893742002</v>
+        <v>https://music.apple.com/us/album/thug/6769289953</v>
       </c>
       <c r="L135" t="str">
-        <v>LEMONADE (feat. Becky G) - aespa</v>
+        <v>Thug - G Herbo</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Take Me Back (Leave Me There)</v>
+        <v>Clap</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/take-me-back-leave-me-there/1892466278</v>
+        <v>https://music.apple.com/us/song/clap/6769903711</v>
       </c>
       <c r="D136" t="str">
         <v>2026-06-01</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Banks Of The Trinity</v>
+        <v>Clap - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>2:58</v>
+        <v>2:04</v>
       </c>
       <c r="H136" t="str">
-        <v>Cody Johnson</v>
+        <v>Polo G</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
+        <v>https://music.apple.com/us/artist/polo-g/1159371412</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/take-me-back-leave-me-there/1892465981</v>
+        <v>https://music.apple.com/us/album/clap/6769903710</v>
       </c>
       <c r="L136" t="str">
-        <v>Take Me Back (Leave Me There) - Cody Johnson</v>
+        <v>Clap - Polo G</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Cheap Thrills</v>
+        <v>GANG BIZNESS</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/cheap-thrills/6771156732</v>
+        <v>https://music.apple.com/us/song/gang-bizness/6772383809</v>
       </c>
       <c r="D137" t="str">
         <v>2026-06-01</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Cheap Thrills - Single</v>
+        <v>THE GENTLEMEN'S CLUB</v>
       </c>
       <c r="G137" t="str">
-        <v>2:42</v>
+        <v>2:47</v>
       </c>
       <c r="H137" t="str">
-        <v>Gavin Adcock</v>
+        <v>YG</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/gavin-adcock/1580645019</v>
+        <v>https://music.apple.com/us/artist/yg/189792075</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/cheap-thrills/6771156723</v>
+        <v>https://music.apple.com/us/album/gang-bizness/6772383681</v>
       </c>
       <c r="L137" t="str">
-        <v>Cheap Thrills - Gavin Adcock</v>
+        <v>GANG BIZNESS - YG</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>ME VALE V</v>
+        <v>UR HEARTBEAT (WHO DO U THINK ABOUT AT 2AM?)</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/me-vale-v/6769567844</v>
+        <v>https://music.apple.com/us/song/ur-heartbeat-who-do-u-think-about-at-2am/6765534140</v>
       </c>
       <c r="D138" t="str">
         <v>2026-06-01</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>ACOMODO</v>
+        <v>A LITTLE VENGEANCE</v>
       </c>
       <c r="G138" t="str">
-        <v>3:06</v>
+        <v>2:50</v>
       </c>
       <c r="H138" t="str">
-        <v>Tito Double P</v>
+        <v>Jessie Reyez</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/tito-double-p/1690905306</v>
+        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/me-vale-v/6769567568</v>
+        <v>https://music.apple.com/us/album/ur-heartbeat-who-do-u-think-about-at-2am/1895983502</v>
       </c>
       <c r="L138" t="str">
-        <v>ME VALE V - Tito Double P</v>
+        <v>UR HEARTBEAT (WHO DO U THINK ABOUT AT 2AM?) - Jessie Reyez</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Bug In The Cake</v>
+        <v>Joshua Tree</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/bug-in-the-cake/1880470542</v>
+        <v>https://music.apple.com/us/song/joshua-tree/6771859148</v>
       </c>
       <c r="D139" t="str">
         <v>2026-06-01</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Be Sweet To Me</v>
+        <v>Euphoria: Season 3 (HBO Original Series Soundtrack)</v>
       </c>
       <c r="G139" t="str">
-        <v>2:48</v>
+        <v>2:50</v>
       </c>
       <c r="H139" t="str">
-        <v>Violet Grohl</v>
+        <v>Hans Zimmer</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
+        <v>https://music.apple.com/us/artist/hans-zimmer/454295032</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/bug-in-the-cake/1880470537</v>
+        <v>https://music.apple.com/us/album/joshua-tree/6771858464</v>
       </c>
       <c r="L139" t="str">
-        <v>Bug In The Cake - Violet Grohl</v>
+        <v>Joshua Tree - Hans Zimmer</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Coil</v>
+        <v>Mi Gran Amor</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/coil/6766858354</v>
+        <v>https://music.apple.com/us/song/mi-gran-amor/6773365775</v>
       </c>
       <c r="D140" t="str">
         <v>2026-06-01</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Rumspringa</v>
+        <v>Mi Gran Amor - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>3:54</v>
+        <v>3:37</v>
       </c>
       <c r="H140" t="str">
-        <v>ear</v>
+        <v>Santana</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/ear/1829661500</v>
+        <v>https://music.apple.com/us/artist/santana/217174</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/coil/6766858352</v>
+        <v>https://music.apple.com/us/album/mi-gran-amor/6773365236</v>
       </c>
       <c r="L140" t="str">
-        <v>Coil - ear</v>
+        <v>Mi Gran Amor - Santana</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Smugglers &amp; Scholars (feat. Killer Mike)</v>
+        <v>london</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/smugglers-scholars-feat-killer-mike/6769424017</v>
+        <v>https://music.apple.com/us/song/london/6770745672</v>
       </c>
       <c r="D141" t="str">
         <v>2026-06-01</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Smugglers &amp; Scholars (feat. Killer Mike) - Single</v>
+        <v>stardust - EP</v>
       </c>
       <c r="G141" t="str">
-        <v>3:30</v>
+        <v>3:23</v>
       </c>
       <c r="H141" t="str">
-        <v>Kneecap</v>
+        <v>Freya Skye</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
+        <v>https://music.apple.com/us/artist/freya-skye/1541643053</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/smugglers-scholars-feat-killer-mike/6769423676</v>
+        <v>https://music.apple.com/us/album/london/6770745662</v>
       </c>
       <c r="L141" t="str">
-        <v>Smugglers &amp; Scholars (feat. Killer Mike) - Kneecap</v>
+        <v>london - Freya Skye</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Out of my Head</v>
+        <v>Caution</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/out-of-my-head/6767725166</v>
+        <v>https://music.apple.com/us/song/caution/6768487482</v>
       </c>
       <c r="D142" t="str">
         <v>2026-06-01</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>I Forgot / Out of my Head - Single</v>
+        <v>K-POPS! (Music from and inspired by K-POPS! Motion Picture)</v>
       </c>
       <c r="G142" t="str">
-        <v>3:04</v>
+        <v>2:43</v>
       </c>
       <c r="H142" t="str">
-        <v>Cara Delevingne</v>
+        <v>NMIXX</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/cara-delevingne/1204798982</v>
+        <v>https://music.apple.com/us/artist/nmixx/1600411676</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/out-of-my-head/6767725156</v>
+        <v>https://music.apple.com/us/album/caution/6768487478</v>
       </c>
       <c r="L142" t="str">
-        <v>Out of my Head - Cara Delevingne</v>
+        <v>Caution - NMIXX</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Passenger Princess</v>
+        <v>LEMONADE (feat. Becky G)</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/passenger-princess/6771012228</v>
+        <v>https://music.apple.com/us/song/lemonade-feat-becky-g/1893742425</v>
       </c>
       <c r="D143" t="str">
         <v>2026-06-01</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Passenger Princess - Single</v>
+        <v>LEMONADE - The 2nd Album</v>
       </c>
       <c r="G143" t="str">
-        <v>3:18</v>
+        <v>3:07</v>
       </c>
       <c r="H143" t="str">
-        <v>Perrie</v>
+        <v>aespa</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/perrie/1729865272</v>
+        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/passenger-princess/6771012223</v>
+        <v>https://music.apple.com/us/album/lemonade-feat-becky-g/1893742002</v>
       </c>
       <c r="L143" t="str">
-        <v>Passenger Princess - Perrie</v>
+        <v>LEMONADE (feat. Becky G) - aespa</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Man of the House</v>
+        <v>Take Me Back (Leave Me There)</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/man-of-the-house/1893733057</v>
+        <v>https://music.apple.com/us/song/take-me-back-leave-me-there/1892466278</v>
       </c>
       <c r="D144" t="str">
         <v>2026-06-01</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>SE9</v>
+        <v>Banks Of The Trinity</v>
       </c>
       <c r="G144" t="str">
-        <v>2:35</v>
+        <v>2:58</v>
       </c>
       <c r="H144" t="str">
-        <v>Skye Newman</v>
+        <v>Cody Johnson</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/skye-newman/1799174381</v>
+        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/man-of-the-house/1893733056</v>
+        <v>https://music.apple.com/us/album/take-me-back-leave-me-there/1892465981</v>
       </c>
       <c r="L144" t="str">
-        <v>Man of the House - Skye Newman</v>
+        <v>Take Me Back (Leave Me There) - Cody Johnson</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Beautiful Freeks</v>
+        <v>Cheap Thrills</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/beautiful-freeks/6764602396</v>
+        <v>https://music.apple.com/us/song/cheap-thrills/6771156732</v>
       </c>
       <c r="D145" t="str">
         <v>2026-06-01</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Beautiful Freeks - Single</v>
+        <v>Cheap Thrills - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>2:37</v>
+        <v>2:42</v>
       </c>
       <c r="H145" t="str">
-        <v>MEEK</v>
+        <v>Gavin Adcock</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/meek/1784432868</v>
+        <v>https://music.apple.com/us/artist/gavin-adcock/1580645019</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/beautiful-freeks/6764602393</v>
+        <v>https://music.apple.com/us/album/cheap-thrills/6771156723</v>
       </c>
       <c r="L145" t="str">
-        <v>Beautiful Freeks - MEEK</v>
+        <v>Cheap Thrills - Gavin Adcock</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Slave to the Rithm (feat. Bring Me The Horizon) [I Hate Models Never Alone Remix]</v>
+        <v>ME VALE V</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/slave-to-the-rithm-feat-bring-me-the-horizon-i/6771972616</v>
+        <v>https://music.apple.com/us/song/me-vale-v/6769567844</v>
       </c>
       <c r="D146" t="str">
         <v>2026-06-01</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Slave to the Rithm (I Hate Models Never Alone Remix) [feat. Bring Me The Horizon] - Single</v>
+        <v>ACOMODO</v>
       </c>
       <c r="G146" t="str">
-        <v>4:34</v>
+        <v>3:06</v>
       </c>
       <c r="H146" t="str">
-        <v>ILLENIUM</v>
+        <v>Tito Double P</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/illenium/645420096</v>
+        <v>https://music.apple.com/us/artist/tito-double-p/1690905306</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/slave-to-the-rithm-feat-bring-me-the-horizon-i/6771972613</v>
+        <v>https://music.apple.com/us/album/me-vale-v/6769567568</v>
       </c>
       <c r="L146" t="str">
-        <v>Slave to the Rithm (feat. Bring Me The Horizon) [I Hate Models Never Alone Remix] - ILLENIUM</v>
+        <v>ME VALE V - Tito Double P</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Beg For Me (JADE Remix)</v>
+        <v>Bug In The Cake</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/beg-for-me-jade-remix/6771474203</v>
+        <v>https://music.apple.com/us/song/bug-in-the-cake/1880470542</v>
       </c>
       <c r="D147" t="str">
         <v>2026-06-01</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Beg For Me (Remix) - Single</v>
+        <v>Be Sweet To Me</v>
       </c>
       <c r="G147" t="str">
-        <v>2:50</v>
+        <v>2:48</v>
       </c>
       <c r="H147" t="str">
-        <v>Lily Allen</v>
+        <v>Violet Grohl</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/lily-allen/157063999</v>
+        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/beg-for-me-jade-remix/6771474201</v>
+        <v>https://music.apple.com/us/album/bug-in-the-cake/1880470537</v>
       </c>
       <c r="L147" t="str">
-        <v>Beg For Me (JADE Remix) - Lily Allen</v>
+        <v>Bug In The Cake - Violet Grohl</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>ABOVE IT</v>
+        <v>Coil</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/above-it/6766248703</v>
+        <v>https://music.apple.com/us/song/coil/6766858354</v>
       </c>
       <c r="D148" t="str">
         <v>2026-06-01</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>GET THE TABLES - Single</v>
+        <v>Rumspringa</v>
       </c>
       <c r="G148" t="str">
-        <v>1:45</v>
+        <v>3:54</v>
       </c>
       <c r="H148" t="str">
-        <v>Andy Mineo</v>
+        <v>ear</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/andy-mineo/257538441</v>
+        <v>https://music.apple.com/us/artist/ear/1829661500</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/above-it/6766248699</v>
+        <v>https://music.apple.com/us/album/coil/6766858352</v>
       </c>
       <c r="L148" t="str">
-        <v>ABOVE IT - Andy Mineo</v>
+        <v>Coil - ear</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>THE JESUS GENERATION</v>
+        <v>Smugglers &amp; Scholars (feat. Killer Mike)</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/the-jesus-generation/6773948895</v>
+        <v>https://music.apple.com/us/song/smugglers-scholars-feat-killer-mike/6769424017</v>
       </c>
       <c r="D149" t="str">
         <v>2026-06-01</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>THE JESUS GENERATION - Single</v>
+        <v>Smugglers &amp; Scholars (feat. Killer Mike) - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>4:15</v>
+        <v>3:30</v>
       </c>
       <c r="H149" t="str">
-        <v>Forrest Frank</v>
+        <v>Kneecap</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/forrest-frank/1436657314</v>
+        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/the-jesus-generation/6773948742</v>
+        <v>https://music.apple.com/us/album/smugglers-scholars-feat-killer-mike/6769423676</v>
       </c>
       <c r="L149" t="str">
-        <v>THE JESUS GENERATION - Forrest Frank</v>
+        <v>Smugglers &amp; Scholars (feat. Killer Mike) - Kneecap</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Is It Over Now?</v>
+        <v>Out of my Head</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/is-it-over-now/6767564750</v>
+        <v>https://music.apple.com/us/song/out-of-my-head/6767725166</v>
       </c>
       <c r="D150" t="str">
         <v>2026-06-01</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Is It Over Now? - Single</v>
+        <v>I Forgot / Out of my Head - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>3:39</v>
+        <v>3:04</v>
       </c>
       <c r="H150" t="str">
-        <v>Elderbrook</v>
+        <v>Cara Delevingne</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/elderbrook/736829657</v>
+        <v>https://music.apple.com/us/artist/cara-delevingne/1204798982</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/is-it-over-now/6767564746</v>
+        <v>https://music.apple.com/us/album/out-of-my-head/6767725156</v>
       </c>
       <c r="L150" t="str">
-        <v>Is It Over Now? - Elderbrook</v>
+        <v>Out of my Head - Cara Delevingne</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>12 Steps</v>
+        <v>Passenger Princess</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/12-steps/6769559623</v>
+        <v>https://music.apple.com/us/song/passenger-princess/6771012228</v>
       </c>
       <c r="D151" t="str">
         <v>2026-06-01</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>12 Steps - Single</v>
+        <v>Passenger Princess - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>3:11</v>
+        <v>3:18</v>
       </c>
       <c r="H151" t="str">
-        <v>Dexter and The Moonrocks</v>
+        <v>Perrie</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/dexter-and-the-moonrocks/1581657500</v>
+        <v>https://music.apple.com/us/artist/perrie/1729865272</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/12-steps/6769559618</v>
+        <v>https://music.apple.com/us/album/passenger-princess/6771012223</v>
       </c>
       <c r="L151" t="str">
-        <v>12 Steps - Dexter and The Moonrocks</v>
+        <v>Passenger Princess - Perrie</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Over And Over</v>
+        <v>Man of the House</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/over-and-over/6771585908</v>
+        <v>https://music.apple.com/us/song/man-of-the-house/1893733057</v>
       </c>
       <c r="D152" t="str">
         <v>2026-06-01</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>It's A Dying Art</v>
+        <v>SE9</v>
       </c>
       <c r="G152" t="str">
-        <v>4:38</v>
+        <v>2:35</v>
       </c>
       <c r="H152" t="str">
-        <v>Little Big Town</v>
+        <v>Skye Newman</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/little-big-town/513770</v>
+        <v>https://music.apple.com/us/artist/skye-newman/1799174381</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/over-and-over/6771585889</v>
+        <v>https://music.apple.com/us/album/man-of-the-house/1893733056</v>
       </c>
       <c r="L152" t="str">
-        <v>Over And Over - Little Big Town</v>
+        <v>Man of the House - Skye Newman</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>AMAPOLA</v>
+        <v>Beautiful Freeks</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/amapola/6769560428</v>
+        <v>https://music.apple.com/us/song/beautiful-freeks/6764602396</v>
       </c>
       <c r="D153" t="str">
         <v>2026-06-01</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Ricky y Mau</v>
+        <v>Beautiful Freeks - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>2:22</v>
+        <v>2:37</v>
       </c>
       <c r="H153" t="str">
-        <v>Mau y Ricky</v>
+        <v>MEEK</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/mau-y-ricky/1096068683</v>
+        <v>https://music.apple.com/us/artist/meek/1784432868</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/amapola/6769559985</v>
+        <v>https://music.apple.com/us/album/beautiful-freeks/6764602393</v>
       </c>
       <c r="L153" t="str">
-        <v>AMAPOLA - Mau y Ricky</v>
+        <v>Beautiful Freeks - MEEK</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Mad About It</v>
+        <v>Slave to the Rithm (feat. Bring Me The Horizon) [I Hate Models Never Alone Remix]</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/mad-about-it/6767425272</v>
+        <v>https://music.apple.com/us/song/slave-to-the-rithm-feat-bring-me-the-horizon-i/6771972616</v>
       </c>
       <c r="D154" t="str">
         <v>2026-06-01</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Mad About It - Single</v>
+        <v>Slave to the Rithm (I Hate Models Never Alone Remix) [feat. Bring Me The Horizon] - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>2:37</v>
+        <v>4:34</v>
       </c>
       <c r="H154" t="str">
-        <v>Dasha</v>
+        <v>ILLENIUM</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/dasha/1462663731</v>
+        <v>https://music.apple.com/us/artist/illenium/645420096</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/mad-about-it/6767425271</v>
+        <v>https://music.apple.com/us/album/slave-to-the-rithm-feat-bring-me-the-horizon-i/6771972613</v>
       </c>
       <c r="L154" t="str">
-        <v>Mad About It - Dasha</v>
+        <v>Slave to the Rithm (feat. Bring Me The Horizon) [I Hate Models Never Alone Remix] - ILLENIUM</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Love’s a Gun</v>
+        <v>Beg For Me (JADE Remix)</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/loves-a-gun/6771898253</v>
+        <v>https://music.apple.com/us/song/beg-for-me-jade-remix/6771474203</v>
       </c>
       <c r="D155" t="str">
         <v>2026-06-01</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Love’s a Gun - Single</v>
+        <v>Beg For Me (Remix) - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>2:59</v>
+        <v>2:50</v>
       </c>
       <c r="H155" t="str">
-        <v>Daniel Seavey</v>
+        <v>Lily Allen</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/daniel-seavey/1646124302</v>
+        <v>https://music.apple.com/us/artist/lily-allen/157063999</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/loves-a-gun/6771897951</v>
+        <v>https://music.apple.com/us/album/beg-for-me-jade-remix/6771474201</v>
       </c>
       <c r="L155" t="str">
-        <v>Love’s a Gun - Daniel Seavey</v>
+        <v>Beg For Me (JADE Remix) - Lily Allen</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Long Story Short</v>
+        <v>ABOVE IT</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/long-story-short/6770700866</v>
+        <v>https://music.apple.com/us/song/above-it/6766248703</v>
       </c>
       <c r="D156" t="str">
         <v>2026-06-01</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Long Story Short - Single</v>
+        <v>GET THE TABLES - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>2:48</v>
+        <v>1:45</v>
       </c>
       <c r="H156" t="str">
-        <v>Knox</v>
+        <v>Andy Mineo</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/knox/1547519433</v>
+        <v>https://music.apple.com/us/artist/andy-mineo/257538441</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/long-story-short/6770700853</v>
+        <v>https://music.apple.com/us/album/above-it/6766248699</v>
       </c>
       <c r="L156" t="str">
-        <v>Long Story Short - Knox</v>
+        <v>ABOVE IT - Andy Mineo</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>blue jeans</v>
+        <v>THE JESUS GENERATION</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/blue-jeans/6770529591</v>
+        <v>https://music.apple.com/us/song/the-jesus-generation/6773948895</v>
       </c>
       <c r="D157" t="str">
         <v>2026-06-01</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>blue jeans - Single</v>
+        <v>THE JESUS GENERATION - Single</v>
       </c>
       <c r="G157" t="str">
-        <v>2:37</v>
+        <v>4:15</v>
       </c>
       <c r="H157" t="str">
-        <v>Nightly</v>
+        <v>Forrest Frank</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/nightly/352310972</v>
+        <v>https://music.apple.com/us/artist/forrest-frank/1436657314</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/blue-jeans/6770529589</v>
+        <v>https://music.apple.com/us/album/the-jesus-generation/6773948742</v>
       </c>
       <c r="L157" t="str">
-        <v>blue jeans - Nightly</v>
+        <v>THE JESUS GENERATION - Forrest Frank</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Que Gacho</v>
+        <v>Is It Over Now?</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/que-gacho/6770628420</v>
+        <v>https://music.apple.com/us/song/is-it-over-now/6767564750</v>
       </c>
       <c r="D158" t="str">
         <v>2026-06-01</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Que Gacho - Single</v>
+        <v>Is It Over Now? - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>3:13</v>
+        <v>3:39</v>
       </c>
       <c r="H158" t="str">
-        <v>Luis R Conriquez</v>
+        <v>Elderbrook</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
+        <v>https://music.apple.com/us/artist/elderbrook/736829657</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/que-gacho/6770628419</v>
+        <v>https://music.apple.com/us/album/is-it-over-now/6767564746</v>
       </c>
       <c r="L158" t="str">
-        <v>Que Gacho - Luis R Conriquez</v>
+        <v>Is It Over Now? - Elderbrook</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>same God</v>
+        <v>12 Steps</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/same-god/1878232616</v>
+        <v>https://music.apple.com/us/song/12-steps/6769559623</v>
       </c>
       <c r="D159" t="str">
         <v>2026-06-01</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>I HOPE THIS HELPS</v>
+        <v>12 Steps - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>3:34</v>
+        <v>3:11</v>
       </c>
       <c r="H159" t="str">
-        <v>Alana Springsteen</v>
+        <v>Dexter and The Moonrocks</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/alana-springsteen/1309335606</v>
+        <v>https://music.apple.com/us/artist/dexter-and-the-moonrocks/1581657500</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/same-god/1878232194</v>
+        <v>https://music.apple.com/us/album/12-steps/6769559618</v>
       </c>
       <c r="L159" t="str">
-        <v>same God - Alana Springsteen</v>
+        <v>12 Steps - Dexter and The Moonrocks</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>emotional swaggage</v>
+        <v>Over And Over</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/emotional-swaggage/6767397453</v>
+        <v>https://music.apple.com/us/song/over-and-over/6771585908</v>
       </c>
       <c r="D160" t="str">
         <v>2026-06-01</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>IDCASH</v>
+        <v>It's A Dying Art</v>
       </c>
       <c r="G160" t="str">
-        <v>2:12</v>
+        <v>4:38</v>
       </c>
       <c r="H160" t="str">
-        <v>IDK</v>
+        <v>Little Big Town</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/idk/1578186947</v>
+        <v>https://music.apple.com/us/artist/little-big-town/513770</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/emotional-swaggage/6767397348</v>
+        <v>https://music.apple.com/us/album/over-and-over/6771585889</v>
       </c>
       <c r="L160" t="str">
-        <v>emotional swaggage - IDK</v>
+        <v>Over And Over - Little Big Town</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Baby Driver</v>
+        <v>AMAPOLA</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/baby-driver/6769152279</v>
+        <v>https://music.apple.com/us/song/amapola/6769560428</v>
       </c>
       <c r="D161" t="str">
         <v>2026-06-01</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Baby Driver - Single</v>
+        <v>Ricky y Mau</v>
       </c>
       <c r="G161" t="str">
-        <v>3:36</v>
+        <v>2:22</v>
       </c>
       <c r="H161" t="str">
-        <v>070 Shake</v>
+        <v>Mau y Ricky</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/070-shake/1097177293</v>
+        <v>https://music.apple.com/us/artist/mau-y-ricky/1096068683</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/baby-driver/6769152273</v>
+        <v>https://music.apple.com/us/album/amapola/6769559985</v>
       </c>
       <c r="L161" t="str">
-        <v>Baby Driver - 070 Shake</v>
+        <v>AMAPOLA - Mau y Ricky</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>More! More! More!</v>
+        <v>Mad About It</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/more-more-more/6770600105</v>
+        <v>https://music.apple.com/us/song/mad-about-it/6767425272</v>
       </c>
       <c r="D162" t="str">
         <v>2026-06-01</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>REBECCA</v>
+        <v>Mad About It - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>2:55</v>
+        <v>2:37</v>
       </c>
       <c r="H162" t="str">
-        <v>Becky Hill</v>
+        <v>Dasha</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/becky-hill/533839517</v>
+        <v>https://music.apple.com/us/artist/dasha/1462663731</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/more-more-more/6770600098</v>
+        <v>https://music.apple.com/us/album/mad-about-it/6767425271</v>
       </c>
       <c r="L162" t="str">
-        <v>More! More! More! - Becky Hill</v>
+        <v>Mad About It - Dasha</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Young Again</v>
+        <v>Love’s a Gun</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/young-again/1877229743</v>
+        <v>https://music.apple.com/us/song/loves-a-gun/6771898253</v>
       </c>
       <c r="D163" t="str">
         <v>2026-06-01</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>EI8HT</v>
+        <v>Love’s a Gun - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>3:36</v>
+        <v>2:59</v>
       </c>
       <c r="H163" t="str">
-        <v>Shinedown</v>
+        <v>Daniel Seavey</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/shinedown/1883858</v>
+        <v>https://music.apple.com/us/artist/daniel-seavey/1646124302</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/young-again/1877229738</v>
+        <v>https://music.apple.com/us/album/loves-a-gun/6771897951</v>
       </c>
       <c r="L163" t="str">
-        <v>Young Again - Shinedown</v>
+        <v>Love’s a Gun - Daniel Seavey</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>skinny dip</v>
+        <v>Long Story Short</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/skinny-dip/6769856281</v>
+        <v>https://music.apple.com/us/song/long-story-short/6770700866</v>
       </c>
       <c r="D164" t="str">
         <v>2026-06-01</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>skinny dip - Single</v>
+        <v>Long Story Short - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>3:12</v>
+        <v>2:48</v>
       </c>
       <c r="H164" t="str">
-        <v>almost monday</v>
+        <v>Knox</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/almost-monday/1300723925</v>
+        <v>https://music.apple.com/us/artist/knox/1547519433</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/skinny-dip/6769855907</v>
+        <v>https://music.apple.com/us/album/long-story-short/6770700853</v>
       </c>
       <c r="L164" t="str">
-        <v>skinny dip - almost monday</v>
+        <v>Long Story Short - Knox</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>girls like girls (from the motion picture)</v>
+        <v>Dior</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/girls-like-girls-from-the-motion-picture/1893704575</v>
+        <v>https://music.apple.com/us/song/dior/1892136721</v>
       </c>
       <c r="D165" t="str">
         <v>2026-06-01</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>girls like girls the album</v>
+        <v>bitknot</v>
       </c>
       <c r="G165" t="str">
-        <v>4:14</v>
+        <v>3:32</v>
       </c>
       <c r="H165" t="str">
-        <v>Hayley Kiyoko</v>
+        <v>feeble little horse</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/hayley-kiyoko/325569584</v>
+        <v>https://music.apple.com/us/artist/feeble-little-horse/1564273208</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/girls-like-girls-from-the-motion-picture/1893704396</v>
+        <v>https://music.apple.com/us/album/dior/1892136714</v>
       </c>
       <c r="L165" t="str">
-        <v>girls like girls (from the motion picture) - Hayley Kiyoko</v>
+        <v>Dior - feeble little horse</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Better Off</v>
+        <v>blue jeans</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/better-off/6772045367</v>
+        <v>https://music.apple.com/us/song/blue-jeans/6770529591</v>
       </c>
       <c r="D166" t="str">
         <v>2026-06-01</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Stages</v>
+        <v>blue jeans - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>3:16</v>
+        <v>2:37</v>
       </c>
       <c r="H166" t="str">
-        <v>Lauren Alaina</v>
+        <v>Nightly</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/lauren-alaina/425028816</v>
+        <v>https://music.apple.com/us/artist/nightly/352310972</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/better-off/6772044978</v>
+        <v>https://music.apple.com/us/album/blue-jeans/6770529589</v>
       </c>
       <c r="L166" t="str">
-        <v>Better Off - Lauren Alaina</v>
+        <v>blue jeans - Nightly</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Everythang Pinka (feat. Teezo Touchdown)</v>
+        <v>Que Gacho</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/everythang-pinka-feat-teezo-touchdown/6772026590</v>
+        <v>https://music.apple.com/us/song/que-gacho/6770628420</v>
       </c>
       <c r="D167" t="str">
         <v>2026-06-01</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Everythang Pinka (feat. Teezo Touchdown) - Single</v>
+        <v>Que Gacho - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>2:48</v>
+        <v>3:13</v>
       </c>
       <c r="H167" t="str">
-        <v>Monaleo</v>
+        <v>Luis R Conriquez</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/monaleo/1495603374</v>
+        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/everythang-pinka-feat-teezo-touchdown/6772026586</v>
+        <v>https://music.apple.com/us/album/que-gacho/6770628419</v>
       </c>
       <c r="L167" t="str">
-        <v>Everythang Pinka (feat. Teezo Touchdown) - Monaleo</v>
+        <v>Que Gacho - Luis R Conriquez</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Lost in translation...</v>
+        <v>same God</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/lost-in-translation/1870971556</v>
+        <v>https://music.apple.com/us/song/same-god/1878232616</v>
       </c>
       <c r="D168" t="str">
         <v>2026-06-01</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Dream inside a dream…</v>
+        <v>I HOPE THIS HELPS</v>
       </c>
       <c r="G168" t="str">
-        <v>3:30</v>
+        <v>3:34</v>
       </c>
       <c r="H168" t="str">
-        <v>R3HAB</v>
+        <v>Alana Springsteen</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/r3hab/331900515</v>
+        <v>https://music.apple.com/us/artist/alana-springsteen/1309335606</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/lost-in-translation/1870971550</v>
+        <v>https://music.apple.com/us/album/same-god/1878232194</v>
       </c>
       <c r="L168" t="str">
-        <v>Lost in translation... - R3HAB</v>
+        <v>same God - Alana Springsteen</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Call Security</v>
+        <v>emotional swaggage</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/call-security/6769296603</v>
+        <v>https://music.apple.com/us/song/emotional-swaggage/6767397453</v>
       </c>
       <c r="D169" t="str">
         <v>2026-06-01</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>U, Me &amp; My Ego</v>
+        <v>IDCASH</v>
       </c>
       <c r="G169" t="str">
-        <v>3:22</v>
+        <v>2:12</v>
       </c>
       <c r="H169" t="str">
-        <v>Chxrry</v>
+        <v>IDK</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/chxrry/1520135642</v>
+        <v>https://music.apple.com/us/artist/idk/1578186947</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/call-security/6769296591</v>
+        <v>https://music.apple.com/us/album/emotional-swaggage/6767397348</v>
       </c>
       <c r="L169" t="str">
-        <v>Call Security - Chxrry</v>
+        <v>emotional swaggage - IDK</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>chaotic</v>
+        <v>Baby Driver</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/chaotic/6767629281</v>
+        <v>https://music.apple.com/us/song/baby-driver/6769152279</v>
       </c>
       <c r="D170" t="str">
         <v>2026-06-01</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>scars to prove it</v>
+        <v>Baby Driver - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>3:14</v>
+        <v>3:36</v>
       </c>
       <c r="H170" t="str">
-        <v>Hailey Picardi</v>
+        <v>070 Shake</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
+        <v>https://music.apple.com/us/artist/070-shake/1097177293</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/chaotic/6767626506</v>
+        <v>https://music.apple.com/us/album/baby-driver/6769152273</v>
       </c>
       <c r="L170" t="str">
-        <v>chaotic - Hailey Picardi</v>
+        <v>Baby Driver - 070 Shake</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Keep It To Yourself</v>
+        <v>More! More! More!</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/keep-it-to-yourself/6771099675</v>
+        <v>https://music.apple.com/us/song/more-more-more/6770600105</v>
       </c>
       <c r="D171" t="str">
         <v>2026-06-01</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>LOVE IS THE LAW</v>
+        <v>REBECCA</v>
       </c>
       <c r="G171" t="str">
-        <v>4:17</v>
+        <v>2:55</v>
       </c>
       <c r="H171" t="str">
-        <v>Love Spells</v>
+        <v>Becky Hill</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/love-spells/1597025563</v>
+        <v>https://music.apple.com/us/artist/becky-hill/533839517</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/keep-it-to-yourself/6771099661</v>
+        <v>https://music.apple.com/us/album/more-more-more/6770600098</v>
       </c>
       <c r="L171" t="str">
-        <v>Keep It To Yourself - Love Spells</v>
+        <v>More! More! More! - Becky Hill</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Something to Someone</v>
+        <v>Young Again</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/something-to-someone/6767255424</v>
+        <v>https://music.apple.com/us/song/young-again/1877229743</v>
       </c>
       <c r="D172" t="str">
         <v>2026-06-01</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Something to Someone - Single</v>
+        <v>EI8HT</v>
       </c>
       <c r="G172" t="str">
-        <v>3:55</v>
+        <v>3:36</v>
       </c>
       <c r="H172" t="str">
-        <v>Max McNown</v>
+        <v>Shinedown</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
+        <v>https://music.apple.com/us/artist/shinedown/1883858</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/something-to-someone/1896445136</v>
+        <v>https://music.apple.com/us/album/young-again/1877229738</v>
       </c>
       <c r="L172" t="str">
-        <v>Something to Someone - Max McNown</v>
+        <v>Young Again - Shinedown</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Green Screen (1pm)</v>
+        <v>skinny dip</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/green-screen-1pm/6766279426</v>
+        <v>https://music.apple.com/us/song/skinny-dip/6769856281</v>
       </c>
       <c r="D173" t="str">
         <v>2026-06-01</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>The Hours: High Noon</v>
+        <v>skinny dip - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>2:10</v>
+        <v>3:12</v>
       </c>
       <c r="H173" t="str">
-        <v>Cautious Clay</v>
+        <v>almost monday</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/cautious-clay/1064628701</v>
+        <v>https://music.apple.com/us/artist/almost-monday/1300723925</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/green-screen-1pm/1896264236</v>
+        <v>https://music.apple.com/us/album/skinny-dip/6769855907</v>
       </c>
       <c r="L173" t="str">
-        <v>Green Screen (1pm) - Cautious Clay</v>
+        <v>skinny dip - almost monday</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Scoreboard</v>
+        <v>girls like girls (from the motion picture)</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/scoreboard/6767255746</v>
+        <v>https://music.apple.com/us/song/girls-like-girls-from-the-motion-picture/1893704575</v>
       </c>
       <c r="D174" t="str">
         <v>2026-06-01</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>I Just Wanna Be Loved</v>
+        <v>girls like girls the album</v>
       </c>
       <c r="G174" t="str">
-        <v>3:24</v>
+        <v>4:14</v>
       </c>
       <c r="H174" t="str">
-        <v>Gabriella Rose</v>
+        <v>Hayley Kiyoko</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/gabriella-rose/645706232</v>
+        <v>https://music.apple.com/us/artist/hayley-kiyoko/325569584</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/scoreboard/1896445371</v>
+        <v>https://music.apple.com/us/album/girls-like-girls-from-the-motion-picture/1893704396</v>
       </c>
       <c r="L174" t="str">
-        <v>Scoreboard - Gabriella Rose</v>
+        <v>girls like girls (from the motion picture) - Hayley Kiyoko</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>High</v>
+        <v>Better Off</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/high/6773775211</v>
+        <v>https://music.apple.com/us/song/better-off/6772045367</v>
       </c>
       <c r="D175" t="str">
         <v>2026-06-01</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Payback Is A Dog (EP)</v>
+        <v>Stages</v>
       </c>
       <c r="G175" t="str">
-        <v>2:55</v>
+        <v>3:16</v>
       </c>
       <c r="H175" t="str">
-        <v>Nia Smith</v>
+        <v>Lauren Alaina</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/nia-smith/1755576018</v>
+        <v>https://music.apple.com/us/artist/lauren-alaina/425028816</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/high/6773775203</v>
+        <v>https://music.apple.com/us/album/better-off/6772044978</v>
       </c>
       <c r="L175" t="str">
-        <v>High - Nia Smith</v>
+        <v>Better Off - Lauren Alaina</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Ay Gyal</v>
+        <v>Everythang Pinka (feat. Teezo Touchdown)</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/ay-gyal/6771885805</v>
+        <v>https://music.apple.com/us/song/everythang-pinka-feat-teezo-touchdown/6772026590</v>
       </c>
       <c r="D176" t="str">
         <v>2026-06-01</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Ay Gyal - Single</v>
+        <v>Everythang Pinka (feat. Teezo Touchdown) - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>2:12</v>
+        <v>2:48</v>
       </c>
       <c r="H176" t="str">
-        <v>1Ski OG</v>
+        <v>Monaleo</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
+        <v>https://music.apple.com/us/artist/monaleo/1495603374</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/ay-gyal/6771885803</v>
+        <v>https://music.apple.com/us/album/everythang-pinka-feat-teezo-touchdown/6772026586</v>
       </c>
       <c r="L176" t="str">
-        <v>Ay Gyal - 1Ski OG</v>
+        <v>Everythang Pinka (feat. Teezo Touchdown) - Monaleo</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>always knew</v>
+        <v>Lost in translation...</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/always-knew/6762864274</v>
+        <v>https://music.apple.com/us/song/lost-in-translation/1870971556</v>
       </c>
       <c r="D177" t="str">
         <v>2026-06-01</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>always knew - Single</v>
+        <v>Dream inside a dream…</v>
       </c>
       <c r="G177" t="str">
-        <v>3:25</v>
+        <v>3:30</v>
       </c>
       <c r="H177" t="str">
-        <v>Biscits</v>
+        <v>R3HAB</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/biscits/1185553226</v>
+        <v>https://music.apple.com/us/artist/r3hab/331900515</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/always-knew/1895047928</v>
+        <v>https://music.apple.com/us/album/lost-in-translation/1870971550</v>
       </c>
       <c r="L177" t="str">
-        <v>always knew - Biscits</v>
+        <v>Lost in translation... - R3HAB</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Cigarette Burns</v>
+        <v>Call Security</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/cigarette-burns/6770691000</v>
+        <v>https://music.apple.com/us/song/call-security/6769296603</v>
       </c>
       <c r="D178" t="str">
         <v>2026-06-01</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Heartland Rock and Roll</v>
+        <v>U, Me &amp; My Ego</v>
       </c>
       <c r="G178" t="str">
-        <v>2:41</v>
+        <v>3:22</v>
       </c>
       <c r="H178" t="str">
-        <v>Corey Kent</v>
+        <v>Chxrry</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/corey-kent/1171544097</v>
+        <v>https://music.apple.com/us/artist/chxrry/1520135642</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/cigarette-burns/6770690867</v>
+        <v>https://music.apple.com/us/album/call-security/6769296591</v>
       </c>
       <c r="L178" t="str">
-        <v>Cigarette Burns - Corey Kent</v>
+        <v>Call Security - Chxrry</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Let You Down</v>
+        <v>chaotic</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/let-you-down/6773362320</v>
+        <v>https://music.apple.com/us/song/chaotic/6767629281</v>
       </c>
       <c r="D179" t="str">
         <v>2026-06-01</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>El Relevo</v>
+        <v>scars to prove it</v>
       </c>
       <c r="G179" t="str">
-        <v>4:14</v>
+        <v>3:14</v>
       </c>
       <c r="H179" t="str">
-        <v>Luis Figueroa</v>
+        <v>Hailey Picardi</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/luis-figueroa/395266944</v>
+        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/let-you-down/6773362108</v>
+        <v>https://music.apple.com/us/album/chaotic/6767626506</v>
       </c>
       <c r="L179" t="str">
-        <v>Let You Down - Luis Figueroa</v>
+        <v>chaotic - Hailey Picardi</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Starless</v>
+        <v>Keep It To Yourself</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/starless/6770568779</v>
+        <v>https://music.apple.com/us/song/keep-it-to-yourself/6771099675</v>
       </c>
       <c r="D180" t="str">
         <v>2026-06-01</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Starless - Single</v>
+        <v>LOVE IS THE LAW</v>
       </c>
       <c r="G180" t="str">
-        <v>4:32</v>
+        <v>4:17</v>
       </c>
       <c r="H180" t="str">
-        <v>A Perfect Circle</v>
+        <v>Love Spells</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/a-perfect-circle/652503</v>
+        <v>https://music.apple.com/us/artist/love-spells/1597025563</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/starless/6770568776</v>
+        <v>https://music.apple.com/us/album/keep-it-to-yourself/6771099661</v>
       </c>
       <c r="L180" t="str">
-        <v>Starless - A Perfect Circle</v>
+        <v>Keep It To Yourself - Love Spells</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Looking For You</v>
+        <v>Something to Someone</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/looking-for-you/6768355609</v>
+        <v>https://music.apple.com/us/song/something-to-someone/6767255424</v>
       </c>
       <c r="D181" t="str">
         <v>2026-06-01</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Looking For You - Single</v>
+        <v>Something to Someone - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>3:19</v>
+        <v>3:55</v>
       </c>
       <c r="H181" t="str">
-        <v>Gable Price and Friends</v>
+        <v>Max McNown</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/gable-price-and-friends/1441378212</v>
+        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/looking-for-you/6768355596</v>
+        <v>https://music.apple.com/us/album/something-to-someone/1896445136</v>
       </c>
       <c r="L181" t="str">
-        <v>Looking For You - Gable Price and Friends</v>
+        <v>Something to Someone - Max McNown</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>FOCUSED</v>
+        <v>Green Screen (1pm)</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/focused/1887909237</v>
+        <v>https://music.apple.com/us/song/green-screen-1pm/6766279426</v>
       </c>
       <c r="D182" t="str">
         <v>2026-06-01</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>FOCUSED - Single</v>
+        <v>The Hours: High Noon</v>
       </c>
       <c r="G182" t="str">
-        <v>2:23</v>
+        <v>2:10</v>
       </c>
       <c r="H182" t="str">
-        <v>Shepherd</v>
+        <v>Cautious Clay</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/shepherd/1192803216</v>
+        <v>https://music.apple.com/us/artist/cautious-clay/1064628701</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/focused/1887909236</v>
+        <v>https://music.apple.com/us/album/green-screen-1pm/1896264236</v>
       </c>
       <c r="L182" t="str">
-        <v>FOCUSED - Shepherd</v>
+        <v>Green Screen (1pm) - Cautious Clay</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Tú Ni En Cuenta</v>
+        <v>Scoreboard</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/tu-ni-en-cuenta/6767701804</v>
+        <v>https://music.apple.com/us/song/scoreboard/6767255746</v>
       </c>
       <c r="D183" t="str">
         <v>2026-06-01</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Tú Ni En Cuenta - Single</v>
+        <v>I Just Wanna Be Loved</v>
       </c>
       <c r="G183" t="str">
-        <v>3:23</v>
+        <v>3:24</v>
       </c>
       <c r="H183" t="str">
-        <v>Banda MS de Sergio Lizárraga</v>
+        <v>Gabriella Rose</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/banda-ms-de-sergio-liz%C3%A1rraga/413048014</v>
+        <v>https://music.apple.com/us/artist/gabriella-rose/645706232</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/tu-ni-en-cuenta/6767701803</v>
+        <v>https://music.apple.com/us/album/scoreboard/1896445371</v>
       </c>
       <c r="L183" t="str">
-        <v>Tú Ni En Cuenta - Banda MS de Sergio Lizárraga</v>
+        <v>Scoreboard - Gabriella Rose</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>dream state</v>
+        <v>High</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/dream-state/6765596009</v>
+        <v>https://music.apple.com/us/song/high/6773775211</v>
       </c>
       <c r="D184" t="str">
         <v>2026-06-01</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>dream state - Single</v>
+        <v>Payback Is A Dog (EP)</v>
       </c>
       <c r="G184" t="str">
-        <v>4:01</v>
+        <v>2:55</v>
       </c>
       <c r="H184" t="str">
-        <v>Martin Luke Brown</v>
+        <v>Nia Smith</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/martin-luke-brown/883292185</v>
+        <v>https://music.apple.com/us/artist/nia-smith/1755576018</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/dream-state/1896004790</v>
+        <v>https://music.apple.com/us/album/high/6773775203</v>
       </c>
       <c r="L184" t="str">
-        <v>dream state - Martin Luke Brown</v>
+        <v>High - Nia Smith</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Needle (feat. Spencer Cullum)</v>
+        <v>Ay Gyal</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/needle-feat-spencer-cullum/6767618217</v>
+        <v>https://music.apple.com/us/song/ay-gyal/6771885805</v>
       </c>
       <c r="D185" t="str">
         <v>2026-06-01</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Needle (feat. Spencer Cullum) - Single</v>
+        <v>Ay Gyal - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>3:39</v>
+        <v>2:12</v>
       </c>
       <c r="H185" t="str">
-        <v>Mynolia</v>
+        <v>1Ski OG</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/mynolia/1444347510</v>
+        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/needle-feat-spencer-cullum/6767618203</v>
+        <v>https://music.apple.com/us/album/ay-gyal/6771885803</v>
       </c>
       <c r="L185" t="str">
-        <v>Needle (feat. Spencer Cullum) - Mynolia</v>
+        <v>Ay Gyal - 1Ski OG</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>You Retreat In Time And Space</v>
+        <v>always knew</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/you-retreat-in-time-and-space/1890015660</v>
+        <v>https://music.apple.com/us/song/always-knew/6762864274</v>
       </c>
       <c r="D186" t="str">
         <v>2026-06-01</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Inferno</v>
+        <v>always knew - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>5:25</v>
+        <v>3:25</v>
       </c>
       <c r="H186" t="str">
-        <v>Boards of Canada</v>
+        <v>Biscits</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/boards-of-canada/2989314</v>
+        <v>https://music.apple.com/us/artist/biscits/1185553226</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/you-retreat-in-time-and-space/1890015523</v>
+        <v>https://music.apple.com/us/album/always-knew/1895047928</v>
       </c>
       <c r="L186" t="str">
-        <v>You Retreat In Time And Space - Boards of Canada</v>
+        <v>always knew - Biscits</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>It's Happening (To Me)</v>
+        <v>Cigarette Burns</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/its-happening-to-me/6764723461</v>
+        <v>https://music.apple.com/us/song/cigarette-burns/6770691000</v>
       </c>
       <c r="D187" t="str">
         <v>2026-06-01</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>It's Happening (To Me) - Single</v>
+        <v>Heartland Rock and Roll</v>
       </c>
       <c r="G187" t="str">
-        <v>2:34</v>
+        <v>2:41</v>
       </c>
       <c r="H187" t="str">
-        <v>Delroy Edwards</v>
+        <v>Corey Kent</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/delroy-edwards/591790909</v>
+        <v>https://music.apple.com/us/artist/corey-kent/1171544097</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/its-happening-to-me/1895893472</v>
+        <v>https://music.apple.com/us/album/cigarette-burns/6770690867</v>
       </c>
       <c r="L187" t="str">
-        <v>It's Happening (To Me) - Delroy Edwards</v>
+        <v>Cigarette Burns - Corey Kent</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>FCUK</v>
+        <v>Let You Down</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/fcuk/6769623577</v>
+        <v>https://music.apple.com/us/song/let-you-down/6773362320</v>
       </c>
       <c r="D188" t="str">
         <v>2026-06-01</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>FCUK - Single</v>
+        <v>El Relevo</v>
       </c>
       <c r="G188" t="str">
-        <v>2:22</v>
+        <v>4:14</v>
       </c>
       <c r="H188" t="str">
-        <v>H.LLS</v>
+        <v>Luis Figueroa</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/h-lls/1751287958</v>
+        <v>https://music.apple.com/us/artist/luis-figueroa/395266944</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/fcuk/6769623566</v>
+        <v>https://music.apple.com/us/album/let-you-down/6773362108</v>
       </c>
       <c r="L188" t="str">
-        <v>FCUK - H.LLS</v>
+        <v>Let You Down - Luis Figueroa</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Higher</v>
+        <v>Starless</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/higher/1880124200</v>
+        <v>https://music.apple.com/us/song/starless/6770568779</v>
       </c>
       <c r="D189" t="str">
         <v>2026-06-01</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Run, Run Pure Beauty</v>
+        <v>Starless - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>4:06</v>
+        <v>4:32</v>
       </c>
       <c r="H189" t="str">
-        <v>Francis of Delirium</v>
+        <v>A Perfect Circle</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/francis-of-delirium/1485902996</v>
+        <v>https://music.apple.com/us/artist/a-perfect-circle/652503</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/higher/1880123731</v>
+        <v>https://music.apple.com/us/album/starless/6770568776</v>
       </c>
       <c r="L189" t="str">
-        <v>Higher - Francis of Delirium</v>
+        <v>Starless - A Perfect Circle</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>B.U.N</v>
+        <v>Looking For You</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/b-u-n/6763272338</v>
+        <v>https://music.apple.com/us/song/looking-for-you/6768355609</v>
       </c>
       <c r="D190" t="str">
         <v>2026-06-01</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>B.U.N - Single</v>
+        <v>Looking For You - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>3:43</v>
+        <v>3:19</v>
       </c>
       <c r="H190" t="str">
-        <v>Roll Deep</v>
+        <v>Gable Price and Friends</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/roll-deep/3083873</v>
+        <v>https://music.apple.com/us/artist/gable-price-and-friends/1441378212</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/b-u-n/1895242397</v>
+        <v>https://music.apple.com/us/album/looking-for-you/6768355596</v>
       </c>
       <c r="L190" t="str">
-        <v>B.U.N - Roll Deep</v>
+        <v>Looking For You - Gable Price and Friends</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Only Love (feat. Pa Salieu)</v>
+        <v>FOCUSED</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/only-love-feat-pa-salieu/6767014290</v>
+        <v>https://music.apple.com/us/song/focused/1887909237</v>
       </c>
       <c r="D191" t="str">
         <v>2026-06-01</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Here Because of Hope</v>
+        <v>FOCUSED - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>3:22</v>
+        <v>2:23</v>
       </c>
       <c r="H191" t="str">
-        <v>Ezra Collective</v>
+        <v>Shepherd</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/ezra-collective/1103640281</v>
+        <v>https://music.apple.com/us/artist/shepherd/1192803216</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/only-love-feat-pa-salieu/6767014278</v>
+        <v>https://music.apple.com/us/album/focused/1887909236</v>
       </c>
       <c r="L191" t="str">
-        <v>Only Love (feat. Pa Salieu) - Ezra Collective</v>
+        <v>FOCUSED - Shepherd</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Beautiful Things 1st scene/audition</v>
+        <v>Tú Ni En Cuenta</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/beautiful-things-1st-scene-audition/6771942631</v>
+        <v>https://music.apple.com/us/song/tu-ni-en-cuenta/6767701804</v>
       </c>
       <c r="D192" t="str">
         <v>2026-06-01</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>UNDRA</v>
+        <v>Tú Ni En Cuenta - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>2:49</v>
+        <v>3:23</v>
       </c>
       <c r="H192" t="str">
-        <v>reggie</v>
+        <v>Banda MS de Sergio Lizárraga</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/reggie/1526587068</v>
+        <v>https://music.apple.com/us/artist/banda-ms-de-sergio-liz%C3%A1rraga/413048014</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/beautiful-things-1st-scene-audition/6771942630</v>
+        <v>https://music.apple.com/us/album/tu-ni-en-cuenta/6767701803</v>
       </c>
       <c r="L192" t="str">
-        <v>Beautiful Things 1st scene/audition - reggie</v>
+        <v>Tú Ni En Cuenta - Banda MS de Sergio Lizárraga</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>HEAVEN'S ON FIRE</v>
+        <v>dream state</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/heavens-on-fire/6771110730</v>
+        <v>https://music.apple.com/us/song/dream-state/6765596009</v>
       </c>
       <c r="D193" t="str">
         <v>2026-06-01</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>HEAVEN'S ON FIRE</v>
+        <v>dream state - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>2:54</v>
+        <v>4:01</v>
       </c>
       <c r="H193" t="str">
-        <v>Johnny Huynh</v>
+        <v>Martin Luke Brown</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/johnny-huynh/1708540956</v>
+        <v>https://music.apple.com/us/artist/martin-luke-brown/883292185</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/heavens-on-fire/6771110729</v>
+        <v>https://music.apple.com/us/album/dream-state/1896004790</v>
       </c>
       <c r="L193" t="str">
-        <v>HEAVEN'S ON FIRE - Johnny Huynh</v>
+        <v>dream state - Martin Luke Brown</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Fallen Angel</v>
+        <v>Needle (feat. Spencer Cullum)</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/fallen-angel/6771161222</v>
+        <v>https://music.apple.com/us/song/needle-feat-spencer-cullum/6767618217</v>
       </c>
       <c r="D194" t="str">
         <v>2026-06-01</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>You Don't Know My Name</v>
+        <v>Needle (feat. Spencer Cullum) - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>3:05</v>
+        <v>3:39</v>
       </c>
       <c r="H194" t="str">
-        <v>Baby J</v>
+        <v>Mynolia</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/baby-j/1513690931</v>
+        <v>https://music.apple.com/us/artist/mynolia/1444347510</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/fallen-angel/6771161180</v>
+        <v>https://music.apple.com/us/album/needle-feat-spencer-cullum/6767618203</v>
       </c>
       <c r="L194" t="str">
-        <v>Fallen Angel - Baby J</v>
+        <v>Needle (feat. Spencer Cullum) - Mynolia</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>The Last Encounter</v>
+        <v>You Retreat In Time And Space</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/the-last-encounter/6767395134</v>
+        <v>https://music.apple.com/us/song/you-retreat-in-time-and-space/1890015660</v>
       </c>
       <c r="D195" t="str">
         <v>2026-06-01</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>The Last Encounter - Single</v>
+        <v>Inferno</v>
       </c>
       <c r="G195" t="str">
-        <v>3:04</v>
+        <v>5:25</v>
       </c>
       <c r="H195" t="str">
-        <v>Sofia Camara</v>
+        <v>Boards of Canada</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/sofia-camara/1506432156</v>
+        <v>https://music.apple.com/us/artist/boards-of-canada/2989314</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/the-last-encounter/6767395133</v>
+        <v>https://music.apple.com/us/album/you-retreat-in-time-and-space/1890015523</v>
       </c>
       <c r="L195" t="str">
-        <v>The Last Encounter - Sofia Camara</v>
+        <v>You Retreat In Time And Space - Boards of Canada</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>We Fall</v>
+        <v>It's Happening (To Me)</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/we-fall/6769218917</v>
+        <v>https://music.apple.com/us/song/its-happening-to-me/6764723461</v>
       </c>
       <c r="D196" t="str">
         <v>2026-06-01</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>We Fall - Single</v>
+        <v>It's Happening (To Me) - Single</v>
       </c>
       <c r="G196" t="str">
-        <v>4:01</v>
+        <v>2:34</v>
       </c>
       <c r="H196" t="str">
-        <v>MOIO</v>
+        <v>Delroy Edwards</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/moio/1664183608</v>
+        <v>https://music.apple.com/us/artist/delroy-edwards/591790909</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/we-fall/6769218915</v>
+        <v>https://music.apple.com/us/album/its-happening-to-me/1895893472</v>
       </c>
       <c r="L196" t="str">
-        <v>We Fall - MOIO</v>
+        <v>It's Happening (To Me) - Delroy Edwards</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>You Don't Know Me</v>
+        <v>FCUK</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/you-dont-know-me/6769214417</v>
+        <v>https://music.apple.com/us/song/fcuk/6769623577</v>
       </c>
       <c r="D197" t="str">
         <v>2026-06-01</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>You Don’t Know Me - Single</v>
+        <v>FCUK - Single</v>
       </c>
       <c r="G197" t="str">
-        <v>3:50</v>
+        <v>2:22</v>
       </c>
       <c r="H197" t="str">
-        <v>Isabel Dumaa</v>
+        <v>H.LLS</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/isabel-dumaa/1631481156</v>
+        <v>https://music.apple.com/us/artist/h-lls/1751287958</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/you-dont-know-me/6769214410</v>
+        <v>https://music.apple.com/us/album/fcuk/6769623566</v>
       </c>
       <c r="L197" t="str">
-        <v>You Don't Know Me - Isabel Dumaa</v>
+        <v>FCUK - H.LLS</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Hold Up, Say What?</v>
+        <v>Higher</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/hold-up-say-what/1879853511</v>
+        <v>https://music.apple.com/us/song/higher/1880124200</v>
       </c>
       <c r="D198" t="str">
         <v>2026-06-01</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>House Of Mirrors</v>
+        <v>Run, Run Pure Beauty</v>
       </c>
       <c r="G198" t="str">
-        <v>4:04</v>
+        <v>4:06</v>
       </c>
       <c r="H198" t="str">
-        <v>All Them Witches</v>
+        <v>Francis of Delirium</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/all-them-witches/534924603</v>
+        <v>https://music.apple.com/us/artist/francis-of-delirium/1485902996</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/hold-up-say-what/1879853502</v>
+        <v>https://music.apple.com/us/album/higher/1880123731</v>
       </c>
       <c r="L198" t="str">
-        <v>Hold Up, Say What? - All Them Witches</v>
+        <v>Higher - Francis of Delirium</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Iodine</v>
+        <v>B.U.N</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/iodine/1871211805</v>
+        <v>https://music.apple.com/us/song/b-u-n/6763272338</v>
       </c>
       <c r="D199" t="str">
         <v>2026-06-01</v>
@@ -7937,36 +7937,36 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>Neverending</v>
+        <v>B.U.N - Single</v>
       </c>
       <c r="G199" t="str">
-        <v>3:40</v>
+        <v>3:43</v>
       </c>
       <c r="H199" t="str">
-        <v>Monolord</v>
+        <v>Roll Deep</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/monolord/833749384</v>
+        <v>https://music.apple.com/us/artist/roll-deep/3083873</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/iodine/1871211801</v>
+        <v>https://music.apple.com/us/album/b-u-n/1895242397</v>
       </c>
       <c r="L199" t="str">
-        <v>Iodine - Monolord</v>
+        <v>B.U.N - Roll Deep</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>I Speak Forgotten Voices</v>
+        <v>Only Love (feat. Pa Salieu)</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/i-speak-forgotten-voices/1878083625</v>
+        <v>https://music.apple.com/us/song/only-love-feat-pa-salieu/6767014290</v>
       </c>
       <c r="D200" t="str">
         <v>2026-06-01</v>
@@ -7975,68 +7975,410 @@
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>...By the Word...</v>
+        <v>Here Because of Hope</v>
       </c>
       <c r="G200" t="str">
-        <v>5:01</v>
+        <v>3:22</v>
       </c>
       <c r="H200" t="str">
-        <v>Trelldom</v>
+        <v>Ezra Collective</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/trelldom/256586618</v>
+        <v>https://music.apple.com/us/artist/ezra-collective/1103640281</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/i-speak-forgotten-voices/1878083622</v>
+        <v>https://music.apple.com/us/album/only-love-feat-pa-salieu/6767014278</v>
       </c>
       <c r="L200" t="str">
-        <v>I Speak Forgotten Voices - Trelldom</v>
+        <v>Only Love (feat. Pa Salieu) - Ezra Collective</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
+        <v>Beautiful Things 1st scene/audition</v>
+      </c>
+      <c r="B201" t="str">
+        <v/>
+      </c>
+      <c r="C201" t="str">
+        <v>https://music.apple.com/us/song/beautiful-things-1st-scene-audition/6771942631</v>
+      </c>
+      <c r="D201" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="E201" t="str">
+        <v/>
+      </c>
+      <c r="F201" t="str">
+        <v>UNDRA</v>
+      </c>
+      <c r="G201" t="str">
+        <v>2:49</v>
+      </c>
+      <c r="H201" t="str">
+        <v>reggie</v>
+      </c>
+      <c r="I201" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J201" t="str">
+        <v>https://music.apple.com/us/artist/reggie/1526587068</v>
+      </c>
+      <c r="K201" t="str">
+        <v>https://music.apple.com/us/album/beautiful-things-1st-scene-audition/6771942630</v>
+      </c>
+      <c r="L201" t="str">
+        <v>Beautiful Things 1st scene/audition - reggie</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
+        <v>HEAVEN'S ON FIRE</v>
+      </c>
+      <c r="B202" t="str">
+        <v/>
+      </c>
+      <c r="C202" t="str">
+        <v>https://music.apple.com/us/song/heavens-on-fire/6771110730</v>
+      </c>
+      <c r="D202" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="E202" t="str">
+        <v/>
+      </c>
+      <c r="F202" t="str">
+        <v>HEAVEN'S ON FIRE</v>
+      </c>
+      <c r="G202" t="str">
+        <v>2:54</v>
+      </c>
+      <c r="H202" t="str">
+        <v>Johnny Huynh</v>
+      </c>
+      <c r="I202" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J202" t="str">
+        <v>https://music.apple.com/us/artist/johnny-huynh/1708540956</v>
+      </c>
+      <c r="K202" t="str">
+        <v>https://music.apple.com/us/album/heavens-on-fire/6771110729</v>
+      </c>
+      <c r="L202" t="str">
+        <v>HEAVEN'S ON FIRE - Johnny Huynh</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
+        <v>Fallen Angel</v>
+      </c>
+      <c r="B203" t="str">
+        <v/>
+      </c>
+      <c r="C203" t="str">
+        <v>https://music.apple.com/us/song/fallen-angel/6771161222</v>
+      </c>
+      <c r="D203" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="E203" t="str">
+        <v/>
+      </c>
+      <c r="F203" t="str">
+        <v>You Don't Know My Name</v>
+      </c>
+      <c r="G203" t="str">
+        <v>3:05</v>
+      </c>
+      <c r="H203" t="str">
+        <v>Baby J</v>
+      </c>
+      <c r="I203" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J203" t="str">
+        <v>https://music.apple.com/us/artist/baby-j/1513690931</v>
+      </c>
+      <c r="K203" t="str">
+        <v>https://music.apple.com/us/album/fallen-angel/6771161180</v>
+      </c>
+      <c r="L203" t="str">
+        <v>Fallen Angel - Baby J</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
+        <v>The Last Encounter</v>
+      </c>
+      <c r="B204" t="str">
+        <v/>
+      </c>
+      <c r="C204" t="str">
+        <v>https://music.apple.com/us/song/the-last-encounter/6767395134</v>
+      </c>
+      <c r="D204" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="E204" t="str">
+        <v/>
+      </c>
+      <c r="F204" t="str">
+        <v>The Last Encounter - Single</v>
+      </c>
+      <c r="G204" t="str">
+        <v>3:04</v>
+      </c>
+      <c r="H204" t="str">
+        <v>Sofia Camara</v>
+      </c>
+      <c r="I204" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J204" t="str">
+        <v>https://music.apple.com/us/artist/sofia-camara/1506432156</v>
+      </c>
+      <c r="K204" t="str">
+        <v>https://music.apple.com/us/album/the-last-encounter/6767395133</v>
+      </c>
+      <c r="L204" t="str">
+        <v>The Last Encounter - Sofia Camara</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v>we fall</v>
+      </c>
+      <c r="B205" t="str">
+        <v/>
+      </c>
+      <c r="C205" t="str">
+        <v>https://music.apple.com/us/song/we-fall/6769218917</v>
+      </c>
+      <c r="D205" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="E205" t="str">
+        <v/>
+      </c>
+      <c r="F205" t="str">
+        <v>we fall - Single</v>
+      </c>
+      <c r="G205" t="str">
+        <v>4:01</v>
+      </c>
+      <c r="H205" t="str">
+        <v>MOIO</v>
+      </c>
+      <c r="I205" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J205" t="str">
+        <v>https://music.apple.com/us/artist/moio/1664183608</v>
+      </c>
+      <c r="K205" t="str">
+        <v>https://music.apple.com/us/album/we-fall/6769218915</v>
+      </c>
+      <c r="L205" t="str">
+        <v>we fall - MOIO</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="str">
+        <v>You Don't Know Me</v>
+      </c>
+      <c r="B206" t="str">
+        <v/>
+      </c>
+      <c r="C206" t="str">
+        <v>https://music.apple.com/us/song/you-dont-know-me/6769214417</v>
+      </c>
+      <c r="D206" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="E206" t="str">
+        <v/>
+      </c>
+      <c r="F206" t="str">
+        <v>You Don’t Know Me - Single</v>
+      </c>
+      <c r="G206" t="str">
+        <v>3:50</v>
+      </c>
+      <c r="H206" t="str">
+        <v>Isabel Dumaa</v>
+      </c>
+      <c r="I206" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J206" t="str">
+        <v>https://music.apple.com/us/artist/isabel-dumaa/1631481156</v>
+      </c>
+      <c r="K206" t="str">
+        <v>https://music.apple.com/us/album/you-dont-know-me/6769214410</v>
+      </c>
+      <c r="L206" t="str">
+        <v>You Don't Know Me - Isabel Dumaa</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
+        <v>Hold Up, Say What?</v>
+      </c>
+      <c r="B207" t="str">
+        <v/>
+      </c>
+      <c r="C207" t="str">
+        <v>https://music.apple.com/us/song/hold-up-say-what/1879853511</v>
+      </c>
+      <c r="D207" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="E207" t="str">
+        <v/>
+      </c>
+      <c r="F207" t="str">
+        <v>House Of Mirrors</v>
+      </c>
+      <c r="G207" t="str">
+        <v>4:04</v>
+      </c>
+      <c r="H207" t="str">
+        <v>All Them Witches</v>
+      </c>
+      <c r="I207" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J207" t="str">
+        <v>https://music.apple.com/us/artist/all-them-witches/534924603</v>
+      </c>
+      <c r="K207" t="str">
+        <v>https://music.apple.com/us/album/hold-up-say-what/1879853502</v>
+      </c>
+      <c r="L207" t="str">
+        <v>Hold Up, Say What? - All Them Witches</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="str">
+        <v>Iodine</v>
+      </c>
+      <c r="B208" t="str">
+        <v/>
+      </c>
+      <c r="C208" t="str">
+        <v>https://music.apple.com/us/song/iodine/1871211805</v>
+      </c>
+      <c r="D208" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="E208" t="str">
+        <v/>
+      </c>
+      <c r="F208" t="str">
+        <v>Neverending</v>
+      </c>
+      <c r="G208" t="str">
+        <v>3:40</v>
+      </c>
+      <c r="H208" t="str">
+        <v>Monolord</v>
+      </c>
+      <c r="I208" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J208" t="str">
+        <v>https://music.apple.com/us/artist/monolord/833749384</v>
+      </c>
+      <c r="K208" t="str">
+        <v>https://music.apple.com/us/album/iodine/1871211801</v>
+      </c>
+      <c r="L208" t="str">
+        <v>Iodine - Monolord</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="str">
+        <v>I Speak Forgotten Voices</v>
+      </c>
+      <c r="B209" t="str">
+        <v/>
+      </c>
+      <c r="C209" t="str">
+        <v>https://music.apple.com/us/song/i-speak-forgotten-voices/1878083625</v>
+      </c>
+      <c r="D209" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="E209" t="str">
+        <v/>
+      </c>
+      <c r="F209" t="str">
+        <v>...By the Word...</v>
+      </c>
+      <c r="G209" t="str">
+        <v>5:01</v>
+      </c>
+      <c r="H209" t="str">
+        <v>Trelldom</v>
+      </c>
+      <c r="I209" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J209" t="str">
+        <v>https://music.apple.com/us/artist/trelldom/256586618</v>
+      </c>
+      <c r="K209" t="str">
+        <v>https://music.apple.com/us/album/i-speak-forgotten-voices/1878083622</v>
+      </c>
+      <c r="L209" t="str">
+        <v>I Speak Forgotten Voices - Trelldom</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="str">
         <v>Rats in the Temple</v>
       </c>
-      <c r="B201" t="str">
-        <v/>
-      </c>
-      <c r="C201" t="str">
+      <c r="B210" t="str">
+        <v/>
+      </c>
+      <c r="C210" t="str">
         <v>https://music.apple.com/us/song/rats-in-the-temple/6764627559</v>
       </c>
-      <c r="D201" t="str">
-        <v>2026-06-01</v>
-      </c>
-      <c r="E201" t="str">
-        <v/>
-      </c>
-      <c r="F201" t="str">
+      <c r="D210" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="E210" t="str">
+        <v/>
+      </c>
+      <c r="F210" t="str">
         <v>Rats in the Temple</v>
       </c>
-      <c r="G201" t="str">
+      <c r="G210" t="str">
         <v>4:45</v>
       </c>
-      <c r="H201" t="str">
+      <c r="H210" t="str">
         <v>Flotsam and Jetsam</v>
       </c>
-      <c r="I201" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J201" t="str">
+      <c r="I210" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J210" t="str">
         <v>https://music.apple.com/us/artist/flotsam-and-jetsam/162270</v>
       </c>
-      <c r="K201" t="str">
+      <c r="K210" t="str">
         <v>https://music.apple.com/us/album/rats-in-the-temple/1895855647</v>
       </c>
-      <c r="L201" t="str">
+      <c r="L210" t="str">
         <v>Rats in the Temple - Flotsam and Jetsam</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L201"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L210"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-06-week01/titles.xlsx
+++ b/data/global/2026-06-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L210"/>
+  <dimension ref="A1:L202"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שמעון בוסקילה - עולם יפה</v>
+        <v>שמעון בוסקילה – עולם יפה</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411160&amp;sid=025af64e8b5ae176cc6981dfe7da5d26</v>
+        <v>https://yosmusic.com/%d7%a9%d7%9e%d7%a2%d7%95%d7%9f-%d7%91%d7%95%d7%a1%d7%a7%d7%99%d7%9c%d7%94-%d7%a2%d7%95%d7%9c%d7%9d-%d7%99%d7%a4%d7%94/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>"עולם יפה" של שמעון בוסקילה מצליח לחבר בין כאב קולקטיבי לבין פופ נגיש מאוד. לכאורה מדובר בשיר פשוט למדי, אבל הפשטות היא חלק מרכזי מהאפקט שלו. השיר בנוי על שני צירים מנוגדים: כאב, געגוע ושבר, ומנגד תקווה, התמדה ובחירה בחיים.</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,27 +469,27 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שמעון בוסקילה - עולם יפה</v>
+        <v>שמעון בוסקילה – עולם יפה</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>קובי בוקעי - האהבה שלך</v>
+        <v>מירי מסיקה שרה את "לב לבן" של שולי רנד</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411159&amp;sid=025af64e8b5ae176cc6981dfe7da5d26</v>
+        <v>https://yosmusic.com/%d7%9e%d7%99%d7%a8%d7%99-%d7%9e%d7%a1%d7%99%d7%a7%d7%94-%d7%a9%d7%a8%d7%94-%d7%90%d7%aa-%d7%9c%d7%91-%d7%9c%d7%91%d7%9f-%d7%a9%d7%9c-%d7%a9%d7%95%d7%9c%d7%99-%d7%a8%d7%a0%d7%93/</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v/>
+        <v>שיאה של עונת החתונות בפתח. זה הזמן לקדם ללב הפלייליסט של שירי החתונה  את "לב לבן" של שולי רנד. את היוזמה ה"מסחרית" הזו לקחה לידיה מירי מסיקה בגרסה לשיר בעיבוד אורי זך. השיר "לב לבן" של  הפך תוך חודשים ספורים</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -507,36 +507,36 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>קובי בוקעי - האהבה שלך</v>
+        <v>מירי מסיקה שרה את "לב לבן" של שולי רנד</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>נהוראי אריאלי &amp; שי וינר - אתה טוב</v>
+        <v>Dua Lipa - Physical (Live From Mexico)</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-06-01</v>
+        <v>4d ago</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411158&amp;sid=025af64e8b5ae176cc6981dfe7da5d26</v>
+        <v>https://www.youtube.com/watch?v=xZAe-d3bXTs</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v/>
+        <v>4d ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
       </c>
       <c r="H4" t="str">
-        <v/>
+        <v>Dua Lipa</v>
       </c>
       <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -545,36 +545,36 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>נהוראי אריאלי &amp; שי וינר - אתה טוב</v>
+        <v>Dua Lipa - Physical (Live From Mexico) - Dua Lipa</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>מיכל בן חיים - איזה עולם</v>
+        <v>Dagny - Rain (Lyric Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-06-01</v>
+        <v>4d ago</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411157&amp;sid=025af64e8b5ae176cc6981dfe7da5d26</v>
+        <v>https://www.youtube.com/watch?v=j3ZJwczZoUQ</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E5" t="str">
         <v/>
       </c>
       <c r="F5" t="str">
-        <v/>
+        <v>4d ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
       </c>
       <c r="H5" t="str">
-        <v/>
+        <v>Dagny</v>
       </c>
       <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -583,36 +583,36 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>מיכל בן חיים - איזה עולם</v>
+        <v>Dagny - Rain (Lyric Video) - Dagny</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>מורן מצליח - מאז שהלכת</v>
+        <v>Modern Talking - Cheri Cheri Lady (Auf los geht's los, 14.09.1985)</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-06-01</v>
+        <v>4d ago</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411156&amp;sid=025af64e8b5ae176cc6981dfe7da5d26</v>
+        <v>https://www.youtube.com/watch?v=c0LtTVKNwNA</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E6" t="str">
         <v/>
       </c>
       <c r="F6" t="str">
-        <v/>
+        <v>4d ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
       </c>
       <c r="H6" t="str">
-        <v/>
+        <v>Modern Talking Offiziell</v>
       </c>
       <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -621,36 +621,36 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>מורן מצליח - מאז שהלכת</v>
+        <v>Modern Talking - Cheri Cheri Lady (Auf los geht's los, 14.09.1985) - Modern Talking Offiziell</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>מורן מצליח - חשבתי שאתה לתמיד</v>
+        <v>The Chemical Brothers - Go (Live Show Visual)</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-06-01</v>
+        <v>4d ago</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411155&amp;sid=025af64e8b5ae176cc6981dfe7da5d26</v>
+        <v>https://www.youtube.com/watch?v=fHCIchBq8CM</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E7" t="str">
         <v/>
       </c>
       <c r="F7" t="str">
-        <v/>
+        <v>4d ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v/>
+        <v>The Chemical Brothers</v>
       </c>
       <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J7" t="str">
         <v/>
@@ -659,36 +659,36 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>מורן מצליח - חשבתי שאתה לתמיד</v>
+        <v>The Chemical Brothers - Go (Live Show Visual) - The Chemical Brothers</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>איה - באתי לרקוד</v>
+        <v>Jonas Blue - Girl (Official Lyric Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-06-01</v>
+        <v>4d ago</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411154&amp;sid=025af64e8b5ae176cc6981dfe7da5d26</v>
+        <v>https://www.youtube.com/watch?v=FTUe3jzUqXU</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E8" t="str">
         <v/>
       </c>
       <c r="F8" t="str">
-        <v/>
+        <v>4d ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8" t="str">
-        <v/>
+        <v>Defected Records and Jonas Blue</v>
       </c>
       <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -697,36 +697,36 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>איה - באתי לרקוד</v>
+        <v>Jonas Blue - Girl (Official Lyric Video) - Defected Records and Jonas Blue</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>ישראל צוברי - אלוקיי</v>
+        <v>Dogpark - Don't Lie (Visualizer)</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-06-01</v>
+        <v>4d ago</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411153&amp;sid=025af64e8b5ae176cc6981dfe7da5d26</v>
+        <v>https://www.youtube.com/watch?v=is7qKBRycJI</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E9" t="str">
         <v/>
       </c>
       <c r="F9" t="str">
-        <v/>
+        <v>4d ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v/>
+        <v>Dogpark</v>
       </c>
       <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J9" t="str">
         <v/>
@@ -735,36 +735,36 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>ישראל צוברי - אלוקיי</v>
+        <v>Dogpark - Don't Lie (Visualizer) - Dogpark</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>ירין יפת &amp; אפסילון - לא נמצאת</v>
+        <v>elijah woods - L-O-V-E (Treehouse Sessions)</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-06-01</v>
+        <v>4d ago</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411152&amp;sid=025af64e8b5ae176cc6981dfe7da5d26</v>
+        <v>https://www.youtube.com/watch?v=q5kN7eH6rgo</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E10" t="str">
         <v/>
       </c>
       <c r="F10" t="str">
-        <v/>
+        <v>4d ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v/>
+        <v>elijah woods</v>
       </c>
       <c r="I10" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J10" t="str">
         <v/>
@@ -773,36 +773,36 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>ירין יפת &amp; אפסילון - לא נמצאת</v>
+        <v>elijah woods - L-O-V-E (Treehouse Sessions) - elijah woods</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>אנה זק - ילד שמנת - גרסת הפילאטיס</v>
+        <v>Lauren Alaina - Better Off (Official Audio)</v>
       </c>
       <c r="B11" t="str">
-        <v>2026-06-01</v>
+        <v>4d ago</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411151&amp;sid=025af64e8b5ae176cc6981dfe7da5d26</v>
+        <v>https://www.youtube.com/watch?v=Vj-ong3XNHM</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E11" t="str">
         <v/>
       </c>
       <c r="F11" t="str">
-        <v/>
+        <v>4d ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v/>
+        <v>Lauren Alaina</v>
       </c>
       <c r="I11" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J11" t="str">
         <v/>
@@ -811,33 +811,33 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>אנה זק - ילד שמנת - גרסת הפילאטיס</v>
+        <v>Lauren Alaina - Better Off (Official Audio) - Lauren Alaina</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Dua Lipa - Physical (Live From Mexico)</v>
+        <v>Lauren Sanderson - ARE YOU REALLY HERE? (Lyric Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=xZAe-d3bXTs</v>
+        <v>https://www.youtube.com/watch?v=u7Et_hbMZUA</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E12" t="str">
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>Dua Lipa</v>
+        <v>Lauren Sanderson</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,33 +849,33 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Dua Lipa - Physical (Live From Mexico) - Dua Lipa</v>
+        <v>Lauren Sanderson - ARE YOU REALLY HERE? (Lyric Video) - Lauren Sanderson</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Dagny - Rain (Lyric Video)</v>
+        <v>Nightly – blue jeans (Official Lyric Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=j3ZJwczZoUQ</v>
+        <v>https://www.youtube.com/watch?v=LnA3xkXUwaM</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E13" t="str">
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>Dagny</v>
+        <v>NIGHTLY</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,33 +887,33 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Dagny - Rain (Lyric Video) - Dagny</v>
+        <v>Nightly – blue jeans (Official Lyric Video) - NIGHTLY</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Modern Talking - Cheri Cheri Lady (Auf los geht's los, 14.09.1985)</v>
+        <v>Dasha - Mad About It (Official Visualizer)</v>
       </c>
       <c r="B14" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=c0LtTVKNwNA</v>
+        <v>https://www.youtube.com/watch?v=Ae1gf_7p3H8</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E14" t="str">
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>Modern Talking Offiziell</v>
+        <v>Dasha</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,33 +925,33 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Modern Talking - Cheri Cheri Lady (Auf los geht's los, 14.09.1985) - Modern Talking Offiziell</v>
+        <v>Dasha - Mad About It (Official Visualizer) - Dasha</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Jonas Blue - Girl (Official Lyric Video)</v>
+        <v>Ariana Grande - hate that i made you love me (official lyric video)</v>
       </c>
       <c r="B15" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=FTUe3jzUqXU</v>
+        <v>https://www.youtube.com/watch?v=v1t4MTqdfyI</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E15" t="str">
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>Defected Records and Jonas Blue</v>
+        <v>Ariana Grande</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,33 +963,33 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Jonas Blue - Girl (Official Lyric Video) - Defected Records and Jonas Blue</v>
+        <v>Ariana Grande - hate that i made you love me (official lyric video) - Ariana Grande</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Dogpark - Don't Lie (Visualizer)</v>
+        <v>Max McNown - Something To Someone (Performance Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=is7qKBRycJI</v>
+        <v>https://www.youtube.com/watch?v=4Ki4ejT86YM</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E16" t="str">
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>Dogpark</v>
+        <v>Max McNown</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,33 +1001,33 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Dogpark - Don't Lie (Visualizer) - Dogpark</v>
+        <v>Max McNown - Something To Someone (Performance Video) - Max McNown</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>elijah woods - L-O-V-E (Treehouse Sessions)</v>
+        <v>Bebe Rexha &amp; David Guetta - Sad Girls (Official Visual)</v>
       </c>
       <c r="B17" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=q5kN7eH6rgo</v>
+        <v>https://www.youtube.com/watch?v=P8UqZ5IF-QE</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E17" t="str">
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>elijah woods</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,33 +1039,33 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>elijah woods - L-O-V-E (Treehouse Sessions) - elijah woods</v>
+        <v>Bebe Rexha &amp; David Guetta - Sad Girls (Official Visual) - Bebe Rexha</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Lauren Alaina - Better Off (Official Audio)</v>
+        <v>Knox - Long Story Short (Official Video)</v>
       </c>
       <c r="B18" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=Vj-ong3XNHM</v>
+        <v>https://www.youtube.com/watch?v=5OGY6hCELfg</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E18" t="str">
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>Lauren Alaina</v>
+        <v>Knox</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,33 +1077,33 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Lauren Alaina - Better Off (Official Audio) - Lauren Alaina</v>
+        <v>Knox - Long Story Short (Official Video) - Knox</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Lauren Sanderson - ARE YOU REALLY HERE? (Lyric Video)</v>
+        <v>Sofia Camara - The Last Encounter</v>
       </c>
       <c r="B19" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=u7Et_hbMZUA</v>
+        <v>https://www.youtube.com/watch?v=E9kN4HLGG1c</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E19" t="str">
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>Lauren Sanderson</v>
+        <v>Sofia Camara</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,33 +1115,33 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Lauren Sanderson - ARE YOU REALLY HERE? (Lyric Video) - Lauren Sanderson</v>
+        <v>Sofia Camara - The Last Encounter - Sofia Camara</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Nightly – blue jeans (Official Lyric Video)</v>
+        <v>Official Music Video: "Flowers" -- Alexander James</v>
       </c>
       <c r="B20" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=LnA3xkXUwaM</v>
+        <v>https://www.youtube.com/watch?v=aZ4WP0P92tM</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E20" t="str">
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>NIGHTLY</v>
+        <v>Alexander James</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,33 +1153,33 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Nightly – blue jeans (Official Lyric Video) - NIGHTLY</v>
+        <v>Official Music Video: "Flowers" -- Alexander James - Alexander James</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Dasha - Mad About It (Official Visualizer)</v>
+        <v>almost monday - skinny dip (official video)</v>
       </c>
       <c r="B21" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=Ae1gf_7p3H8</v>
+        <v>https://www.youtube.com/watch?v=hOxZDoaIzKQ</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E21" t="str">
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>Dasha</v>
+        <v>almost monday</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,33 +1191,33 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Dasha - Mad About It (Official Visualizer) - Dasha</v>
+        <v>almost monday - skinny dip (official video) - almost monday</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Ariana Grande - hate that i made you love me (official lyric video)</v>
+        <v>Kip Moore - The Darkness (Official)</v>
       </c>
       <c r="B22" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=v1t4MTqdfyI</v>
+        <v>https://www.youtube.com/watch?v=lTqqixCt5Mk</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E22" t="str">
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>Ariana Grande</v>
+        <v>Kip Moore</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,33 +1229,33 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Ariana Grande - hate that i made you love me (official lyric video) - Ariana Grande</v>
+        <v>Kip Moore - The Darkness (Official) - Kip Moore</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Max McNown - Something To Someone (Performance Video)</v>
+        <v>Paul McCartney - Come Inside (Lyric Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=4Ki4ejT86YM</v>
+        <v>https://www.youtube.com/watch?v=C8Zw_Cbm2V0</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E23" t="str">
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>Max McNown</v>
+        <v>PAUL McCARTNEY</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,33 +1267,33 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Max McNown - Something To Someone (Performance Video) - Max McNown</v>
+        <v>Paul McCartney - Come Inside (Lyric Video) - PAUL McCARTNEY</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Bebe Rexha &amp; David Guetta - Sad Girls (Official Visual)</v>
+        <v>Santana, Becky G - Mi Gran Amor (Official Lyric Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=P8UqZ5IF-QE</v>
+        <v>https://www.youtube.com/watch?v=btdBd_Yee8E</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E24" t="str">
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>Bebe Rexha</v>
+        <v>Santana</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,33 +1305,33 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Bebe Rexha &amp; David Guetta - Sad Girls (Official Visual) - Bebe Rexha</v>
+        <v>Santana, Becky G - Mi Gran Amor (Official Lyric Video) - Santana</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Knox - Long Story Short (Official Video)</v>
+        <v>Dua Lipa - Training Season (Live From Mexico)</v>
       </c>
       <c r="B25" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=5OGY6hCELfg</v>
+        <v>https://www.youtube.com/watch?v=Va8Udsvqigs</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E25" t="str">
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>Knox</v>
+        <v>Dua Lipa</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,33 +1343,33 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Knox - Long Story Short (Official Video) - Knox</v>
+        <v>Dua Lipa - Training Season (Live From Mexico) - Dua Lipa</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Sofia Camara - The Last Encounter</v>
+        <v>Charley - Liar</v>
       </c>
       <c r="B26" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=E9kN4HLGG1c</v>
+        <v>https://www.youtube.com/watch?v=3Erfj2Eecgw</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E26" t="str">
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>Sofia Camara</v>
+        <v>Charley</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,33 +1381,33 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Sofia Camara - The Last Encounter - Sofia Camara</v>
+        <v>Charley - Liar - Charley</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Official Music Video: "Flowers" -- Alexander James</v>
+        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (ft Gabito Ballesteros) [Visualizer]</v>
       </c>
       <c r="B27" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=aZ4WP0P92tM</v>
+        <v>https://www.youtube.com/watch?v=em5ryETDkAo</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E27" t="str">
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
       </c>
       <c r="H27" t="str">
-        <v>Alexander James</v>
+        <v>David Guetta and Jennifer Lopez</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,33 +1419,33 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Official Music Video: "Flowers" -- Alexander James - Alexander James</v>
+        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (ft Gabito Ballesteros) [Visualizer] - David Guetta and Jennifer Lopez</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>almost monday - skinny dip (official video)</v>
+        <v>Jordana Bryant - Too Little Too Late (Official Audio)</v>
       </c>
       <c r="B28" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=hOxZDoaIzKQ</v>
+        <v>https://www.youtube.com/watch?v=AmwNx9qlOpA</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E28" t="str">
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>almost monday</v>
+        <v>Jordana Bryant</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,33 +1457,33 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>almost monday - skinny dip (official video) - almost monday</v>
+        <v>Jordana Bryant - Too Little Too Late (Official Audio) - Jordana Bryant</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Kip Moore - The Darkness (Official)</v>
+        <v>Lewis Capaldi - Stay Love (Official Video)</v>
       </c>
       <c r="B29" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=lTqqixCt5Mk</v>
+        <v>https://www.youtube.com/watch?v=9Pud3BqPpq0</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E29" t="str">
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>Kip Moore</v>
+        <v>Lewis Capaldi</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,33 +1495,33 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Kip Moore - The Darkness (Official) - Kip Moore</v>
+        <v>Lewis Capaldi - Stay Love (Official Video) - Lewis Capaldi</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Paul McCartney - Come Inside (Lyric Video)</v>
+        <v>Surreal World of Oddities - Pulling At My Strings - Official Music Video | 4K</v>
       </c>
       <c r="B30" t="str">
-        <v>3 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=C8Zw_Cbm2V0</v>
+        <v>https://www.youtube.com/watch?v=fMt-f2aUW3c</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E30" t="str">
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>3 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>PAUL McCARTNEY</v>
+        <v>Kelly Boesch AI Art</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,33 +1533,33 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Paul McCartney - Come Inside (Lyric Video) - PAUL McCARTNEY</v>
+        <v>Surreal World of Oddities - Pulling At My Strings - Official Music Video | 4K - Kelly Boesch AI Art</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Santana, Becky G - Mi Gran Amor (Official Lyric Video)</v>
+        <v>Julia Cole - Love You to Death (Official Video)</v>
       </c>
       <c r="B31" t="str">
-        <v>3 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=btdBd_Yee8E</v>
+        <v>https://www.youtube.com/watch?v=dWgmFc2QuLY</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E31" t="str">
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>3 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>Santana</v>
+        <v>Julia Cole Music</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,33 +1571,33 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Santana, Becky G - Mi Gran Amor (Official Lyric Video) - Santana</v>
+        <v>Julia Cole - Love You to Death (Official Video) - Julia Cole Music</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Dua Lipa - Training Season (Live From Mexico)</v>
+        <v>Victor Biliac - De-ai fi tu salcie la mal ( Cover Edit )</v>
       </c>
       <c r="B32" t="str">
-        <v>3 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=Va8Udsvqigs</v>
+        <v>https://www.youtube.com/watch?v=v3c0kG-V2zk</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E32" t="str">
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>3 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
       </c>
       <c r="H32" t="str">
-        <v>Dua Lipa</v>
+        <v>VictorBiliac</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,33 +1609,33 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Dua Lipa - Training Season (Live From Mexico) - Dua Lipa</v>
+        <v>Victor Biliac - De-ai fi tu salcie la mal ( Cover Edit ) - VictorBiliac</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Charley - Liar</v>
+        <v>Lolo Zouaï - Coquelicot (feat. disiz) (Official Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>4 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=3Erfj2Eecgw</v>
+        <v>https://www.youtube.com/watch?v=-4p6FkrOGT4</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E33" t="str">
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>4 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>Charley</v>
+        <v>Lolo Zouaï and disiz</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,33 +1647,33 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Charley - Liar - Charley</v>
+        <v>Lolo Zouaï - Coquelicot (feat. disiz) (Official Video) - Lolo Zouaï and disiz</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (ft Gabito Ballesteros) [Visualizer]</v>
+        <v>Jungle - The Wave (Official Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>4 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=em5ryETDkAo</v>
+        <v>https://www.youtube.com/watch?v=DW1vUkqNvqQ</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E34" t="str">
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>4 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>David Guetta and Jennifer Lopez</v>
+        <v>Jungle4eva</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,33 +1685,33 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (ft Gabito Ballesteros) [Visualizer] - David Guetta and Jennifer Lopez</v>
+        <v>Jungle - The Wave (Official Video) - Jungle4eva</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Jordana Bryant - Too Little Too Late (Official Audio)</v>
+        <v>Daytime TV – Sun (Official Music Video)</v>
       </c>
       <c r="B35" t="str">
-        <v>4 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=AmwNx9qlOpA</v>
+        <v>https://www.youtube.com/watch?v=Jqo4ra_ch-M</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E35" t="str">
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>4 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
       </c>
       <c r="H35" t="str">
-        <v>Jordana Bryant</v>
+        <v>DAYTIME TV</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,33 +1723,33 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Jordana Bryant - Too Little Too Late (Official Audio) - Jordana Bryant</v>
+        <v>Daytime TV – Sun (Official Music Video) - DAYTIME TV</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Lewis Capaldi - Stay Love</v>
+        <v>Surreal and Strange AI Video | Not Made For The Cage | Kelly Boesch - 4K</v>
       </c>
       <c r="B36" t="str">
-        <v>4 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=9Pud3BqPpq0</v>
+        <v>https://www.youtube.com/watch?v=ACNj3L2bzV8</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E36" t="str">
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>4 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>Lewis Capaldi</v>
+        <v>Kelly Boesch AI Art</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,33 +1761,33 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Lewis Capaldi - Stay Love - Lewis Capaldi</v>
+        <v>Surreal and Strange AI Video | Not Made For The Cage | Kelly Boesch - 4K - Kelly Boesch AI Art</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Surreal World of Oddities - Pulling At My Strings - Official Music Video | 4K</v>
+        <v>Bruno Mars - Risk It All [Live From The Romantic Tour]</v>
       </c>
       <c r="B37" t="str">
-        <v>5 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=fMt-f2aUW3c</v>
+        <v>https://www.youtube.com/watch?v=aFbueod4reQ</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E37" t="str">
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>5 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>Kelly Boesch AI Art</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,33 +1799,33 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Surreal World of Oddities - Pulling At My Strings - Official Music Video | 4K - Kelly Boesch AI Art</v>
+        <v>Bruno Mars - Risk It All [Live From The Romantic Tour] - Bruno Mars</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Julia Cole - Love You to Death (Official Video)</v>
+        <v>Keith Urban - Summer Breeze (52nd American Music Awards)</v>
       </c>
       <c r="B38" t="str">
-        <v>4 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=dWgmFc2QuLY</v>
+        <v>https://www.youtube.com/watch?v=zn-4eVoqofQ</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E38" t="str">
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>4 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
       </c>
       <c r="H38" t="str">
-        <v>Julia Cole Music</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,33 +1837,33 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Julia Cole - Love You to Death (Official Video) - Julia Cole Music</v>
+        <v>Keith Urban - Summer Breeze (52nd American Music Awards) - Keith Urban</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Victor Biliac - De-ai fi tu salcie la mal ( Cover Edit )</v>
+        <v>Nelly Furtado, Boi-1Da, Canada Soccer - ELECTRIC CIRCUS (Official Music Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>5 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=v3c0kG-V2zk</v>
+        <v>https://www.youtube.com/watch?v=lHYEMWFuErM</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E39" t="str">
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>5 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
       </c>
       <c r="H39" t="str">
-        <v>VictorBiliac</v>
+        <v>Nelly Furtado</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,33 +1875,33 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Victor Biliac - De-ai fi tu salcie la mal ( Cover Edit ) - VictorBiliac</v>
+        <v>Nelly Furtado, Boi-1Da, Canada Soccer - ELECTRIC CIRCUS (Official Music Video) - Nelly Furtado</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Lolo Zouaï - Coquelicot (feat. disiz) (Official Video)</v>
+        <v>Teddy Swims - Mr. Know It All (Live from the AMAs)</v>
       </c>
       <c r="B40" t="str">
-        <v>5 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=-4p6FkrOGT4</v>
+        <v>https://www.youtube.com/watch?v=ttM4gWkhZBk</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E40" t="str">
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>5 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
       </c>
       <c r="H40" t="str">
-        <v>Lolo Zouaï and disiz</v>
+        <v>Teddy Swims and American Music Awards</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,33 +1913,33 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Lolo Zouaï - Coquelicot (feat. disiz) (Official Video) - Lolo Zouaï and disiz</v>
+        <v>Teddy Swims - Mr. Know It All (Live from the AMAs) - Teddy Swims and American Music Awards</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Jungle - The Wave (Official Video)</v>
+        <v>Shakira, Burna Boy - Dai Dai (Official Video)</v>
       </c>
       <c r="B41" t="str">
-        <v>5 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=DW1vUkqNvqQ</v>
+        <v>https://www.youtube.com/watch?v=fcnDmrtj6Sk</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E41" t="str">
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>5 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
       </c>
       <c r="H41" t="str">
-        <v>Jungle4eva</v>
+        <v>Shakira and 2 more</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,33 +1951,33 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Jungle - The Wave (Official Video) - Jungle4eva</v>
+        <v>Shakira, Burna Boy - Dai Dai (Official Video) - Shakira and 2 more</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Daytime TV – Sun (Official Music Video)</v>
+        <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards)</v>
       </c>
       <c r="B42" t="str">
-        <v>5 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=Jqo4ra_ch-M</v>
+        <v>https://www.youtube.com/watch?v=wacpnp83cJg</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E42" t="str">
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>5 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
       </c>
       <c r="H42" t="str">
-        <v>DAYTIME TV</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,33 +1989,33 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Daytime TV – Sun (Official Music Video) - DAYTIME TV</v>
+        <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards) - Lainey Wilson</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Surreal and Strange AI Video | Not Made For The Cage | Kelly Boesch - 4K</v>
+        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ]</v>
       </c>
       <c r="B43" t="str">
-        <v>2 weeks ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=ACNj3L2bzV8</v>
+        <v>https://www.youtube.com/watch?v=w8FTnkNVmq0</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E43" t="str">
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>2 weeks ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
       </c>
       <c r="H43" t="str">
-        <v>Kelly Boesch AI Art</v>
+        <v>Duran Duran</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,33 +2027,33 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Surreal and Strange AI Video | Not Made For The Cage | Kelly Boesch - 4K - Kelly Boesch AI Art</v>
+        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ] - Duran Duran</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Bruno Mars - Risk It All [Live From The Romantic Tour]</v>
+        <v>Nico Santos - Optimist</v>
       </c>
       <c r="B44" t="str">
-        <v>6 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=aFbueod4reQ</v>
+        <v>https://www.youtube.com/watch?v=JA6PIcBeKZ0</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E44" t="str">
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>6 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
       </c>
       <c r="H44" t="str">
-        <v>Bruno Mars</v>
+        <v>Nico Santos</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,33 +2065,33 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Bruno Mars - Risk It All [Live From The Romantic Tour] - Bruno Mars</v>
+        <v>Nico Santos - Optimist - Nico Santos</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Keith Urban - Summer Breeze (52nd American Music Awards)</v>
+        <v>Def Leppard - Personal Jesus (Live at Caesars Palace)</v>
       </c>
       <c r="B45" t="str">
-        <v>6 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=zn-4eVoqofQ</v>
+        <v>https://www.youtube.com/watch?v=k5SRMgdG4L4</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E45" t="str">
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>6 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
       </c>
       <c r="H45" t="str">
-        <v>Keith Urban</v>
+        <v>DEF LEPPARD</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,33 +2103,33 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Keith Urban - Summer Breeze (52nd American Music Awards) - Keith Urban</v>
+        <v>Def Leppard - Personal Jesus (Live at Caesars Palace) - DEF LEPPARD</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Nelly Furtado, Boi-1Da, Canada Soccer - ELECTRIC CIRCUS (Official Music Video)</v>
+        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer)</v>
       </c>
       <c r="B46" t="str">
-        <v>6 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=lHYEMWFuErM</v>
+        <v>https://www.youtube.com/watch?v=eWSwy9GU2L8</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E46" t="str">
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>6 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>Nelly Furtado</v>
+        <v>Will Linley</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,33 +2141,33 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Nelly Furtado, Boi-1Da, Canada Soccer - ELECTRIC CIRCUS (Official Music Video) - Nelly Furtado</v>
+        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer) - Will Linley</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Teddy Swims - Mr. Know It All (Live from the AMAs)</v>
+        <v>Kylie Minogue - Story (Official Lyric Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>6 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=ttM4gWkhZBk</v>
+        <v>https://www.youtube.com/watch?v=fv7_1qKo8mg</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E47" t="str">
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>6 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>Teddy Swims and American Music Awards</v>
+        <v>Kylie Minogue</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,33 +2179,33 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Teddy Swims - Mr. Know It All (Live from the AMAs) - Teddy Swims and American Music Awards</v>
+        <v>Kylie Minogue - Story (Official Lyric Video) - Kylie Minogue</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Shakira, Burna Boy - Dai Dai (Official Video)</v>
+        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=fcnDmrtj6Sk</v>
+        <v>https://www.youtube.com/watch?v=3KUQx2s1fQc</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E48" t="str">
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>Shakira and 2 more</v>
+        <v>Billy Raffoul</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,33 +2217,33 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Shakira, Burna Boy - Dai Dai (Official Video) - Shakira and 2 more</v>
+        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video) - Billy Raffoul</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards)</v>
+        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025)</v>
       </c>
       <c r="B49" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=wacpnp83cJg</v>
+        <v>https://www.youtube.com/watch?v=vWf4uiLvwF8</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E49" t="str">
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>Lainey Wilson</v>
+        <v>The Offspring</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,33 +2255,33 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards) - Lainey Wilson</v>
+        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025) - The Offspring</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ]</v>
+        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024)</v>
       </c>
       <c r="B50" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=w8FTnkNVmq0</v>
+        <v>https://www.youtube.com/watch?v=9xjMaXegmWM</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E50" t="str">
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>Duran Duran</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,33 +2293,33 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ] - Duran Duran</v>
+        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024) - David Gilmour</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Nico Santos - Optimist</v>
+        <v>Scorpions - Delicate Dance (Madison Square Garden 2022)</v>
       </c>
       <c r="B51" t="str">
-        <v>12 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=JA6PIcBeKZ0</v>
+        <v>https://www.youtube.com/watch?v=yAjEr9WLTnU</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E51" t="str">
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>12 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>Nico Santos</v>
+        <v>Scorpions</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,33 +2331,33 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Nico Santos - Optimist - Nico Santos</v>
+        <v>Scorpions - Delicate Dance (Madison Square Garden 2022) - Scorpions</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Def Leppard - Personal Jesus (Live at Caesars Palace)</v>
+        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston)</v>
       </c>
       <c r="B52" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=k5SRMgdG4L4</v>
+        <v>https://www.youtube.com/watch?v=oRw4PqBzGc0</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E52" t="str">
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>DEF LEPPARD</v>
+        <v>Brandon Lake and NICK JONAS</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,33 +2369,33 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Def Leppard - Personal Jesus (Live at Caesars Palace) - DEF LEPPARD</v>
+        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston) - Brandon Lake and NICK JONAS</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer)</v>
+        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B53" t="str">
-        <v>10 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=eWSwy9GU2L8</v>
+        <v>https://www.youtube.com/watch?v=OKf_IOGxFQo</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E53" t="str">
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>10 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>Will Linley</v>
+        <v>Kygo and Dan Tyminski</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,33 +2407,33 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer) - Will Linley</v>
+        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video) - Kygo and Dan Tyminski</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Kylie Minogue - Story (Official Lyric Video)</v>
+        <v>The Warning - Ego (Official Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>10 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=fv7_1qKo8mg</v>
+        <v>https://www.youtube.com/watch?v=CG6Q5i75bR4</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E54" t="str">
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>10 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>Kylie Minogue</v>
+        <v>The Warning</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,33 +2445,33 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Kylie Minogue - Story (Official Lyric Video) - Kylie Minogue</v>
+        <v>The Warning - Ego (Official Video) - The Warning</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video)</v>
+        <v>paris jackson - teenage drama (official lyric video)</v>
       </c>
       <c r="B55" t="str">
-        <v>10 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=3KUQx2s1fQc</v>
+        <v>https://www.youtube.com/watch?v=kVfDArNljos</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E55" t="str">
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>10 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>Billy Raffoul</v>
+        <v>paris jackson</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,33 +2483,33 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video) - Billy Raffoul</v>
+        <v>paris jackson - teenage drama (official lyric video) - paris jackson</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025)</v>
+        <v>Minelli - Sun Goes Down | Official Visualizer</v>
       </c>
       <c r="B56" t="str">
-        <v>10 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=vWf4uiLvwF8</v>
+        <v>https://www.youtube.com/watch?v=xOsjm-AwN5I</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E56" t="str">
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>10 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>The Offspring</v>
+        <v>Minelli</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,33 +2521,33 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025) - The Offspring</v>
+        <v>Minelli - Sun Goes Down | Official Visualizer - Minelli</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024)</v>
+        <v>Maggie Rose - Gentle Man (Official Studio Video)</v>
       </c>
       <c r="B57" t="str">
-        <v>10 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=9xjMaXegmWM</v>
+        <v>https://www.youtube.com/watch?v=aWNK-vWrN60</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E57" t="str">
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>10 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>David Gilmour</v>
+        <v>Maggie Rose</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,33 +2559,33 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024) - David Gilmour</v>
+        <v>Maggie Rose - Gentle Man (Official Studio Video) - Maggie Rose</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Scorpions - Delicate Dance (Madison Square Garden 2022)</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer]</v>
       </c>
       <c r="B58" t="str">
-        <v>10 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=yAjEr9WLTnU</v>
+        <v>https://www.youtube.com/watch?v=mN5AZBrVq9I</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E58" t="str">
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>10 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>Scorpions</v>
+        <v>David Guetta</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,33 +2597,33 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Scorpions - Delicate Dance (Madison Square Garden 2022) - Scorpions</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer] - David Guetta</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston)</v>
+        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>10 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=oRw4PqBzGc0</v>
+        <v>https://www.youtube.com/watch?v=0PTufEGRAVQ</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E59" t="str">
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>10 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>Brandon Lake and NICK JONAS</v>
+        <v>Chris Young and Shaylen</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,33 +2635,33 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston) - Brandon Lake and NICK JONAS</v>
+        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video) - Chris Young and Shaylen</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video)</v>
+        <v>Lauv - Pretty Little Things</v>
       </c>
       <c r="B60" t="str">
-        <v>10 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=OKf_IOGxFQo</v>
+        <v>https://www.youtube.com/watch?v=_JBfanFvHnA</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E60" t="str">
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>10 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>Kygo and Dan Tyminski</v>
+        <v>Lauv</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,33 +2673,33 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video) - Kygo and Dan Tyminski</v>
+        <v>Lauv - Pretty Little Things - Lauv</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>The Warning - Ego (Official Video)</v>
+        <v>Icona Pop - Butterfly Feelings (Official Audio)</v>
       </c>
       <c r="B61" t="str">
-        <v>10 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=CG6Q5i75bR4</v>
+        <v>https://www.youtube.com/watch?v=bXA_Q75QZTs</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E61" t="str">
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>10 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>The Warning</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,33 +2711,33 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>The Warning - Ego (Official Video) - The Warning</v>
+        <v>Icona Pop - Butterfly Feelings (Official Audio) - Icona Pop</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>paris jackson - teenage drama (official lyric video)</v>
+        <v>Will Swinton - Only One (Official Video)</v>
       </c>
       <c r="B62" t="str">
-        <v>10 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=kVfDArNljos</v>
+        <v>https://www.youtube.com/watch?v=A0KzP-zm9hA</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E62" t="str">
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>10 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>paris jackson</v>
+        <v>Will Swinton</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,33 +2749,33 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>paris jackson - teenage drama (official lyric video) - paris jackson</v>
+        <v>Will Swinton - Only One (Official Video) - Will Swinton</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Minelli - Sun Goes Down | Official Visualizer</v>
+        <v>Dean Lewis - Escape (Official Video)</v>
       </c>
       <c r="B63" t="str">
-        <v>10 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=xOsjm-AwN5I</v>
+        <v>https://www.youtube.com/watch?v=BZRaTXCkhcg</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E63" t="str">
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>10 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>Minelli</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,33 +2787,33 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Minelli - Sun Goes Down | Official Visualizer - Minelli</v>
+        <v>Dean Lewis - Escape (Official Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Maggie Rose - Gentle Man (Official Studio Video)</v>
+        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico]</v>
       </c>
       <c r="B64" t="str">
-        <v>10 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=aWNK-vWrN60</v>
+        <v>https://www.youtube.com/watch?v=PNm0hf_zZJY</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E64" t="str">
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>10 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>Maggie Rose</v>
+        <v>Dua Lipa and OficialMana</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,33 +2825,33 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Maggie Rose - Gentle Man (Official Studio Video) - Maggie Rose</v>
+        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico] - Dua Lipa and OficialMana</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer]</v>
+        <v>Niall Horan - End of an Era (Lyric Video)</v>
       </c>
       <c r="B65" t="str">
-        <v>10 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=mN5AZBrVq9I</v>
+        <v>https://www.youtube.com/watch?v=EUNNmAAe5gQ</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E65" t="str">
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>10 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>David Guetta</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,33 +2863,33 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer] - David Guetta</v>
+        <v>Niall Horan - End of an Era (Lyric Video) - Niall Horan</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video)</v>
+        <v>Olivia Rodrigo - the cure (Official Music Video)</v>
       </c>
       <c r="B66" t="str">
-        <v>10 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=0PTufEGRAVQ</v>
+        <v>https://www.youtube.com/watch?v=B402rKl4bUg</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E66" t="str">
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>10 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>Chris Young and Shaylen</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,33 +2901,33 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video) - Chris Young and Shaylen</v>
+        <v>Olivia Rodrigo - the cure (Official Music Video) - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Lauv - Pretty Little Things</v>
+        <v>Ruel - Debbie Don't Cry (Official Music Video)</v>
       </c>
       <c r="B67" t="str">
-        <v>10 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=_JBfanFvHnA</v>
+        <v>https://www.youtube.com/watch?v=iz7wuk0GOwI</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E67" t="str">
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>10 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>Lauv</v>
+        <v>RUEL</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,33 +2939,33 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Lauv - Pretty Little Things - Lauv</v>
+        <v>Ruel - Debbie Don't Cry (Official Music Video) - RUEL</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Icona Pop - Butterfly Feelings (Official Audio)</v>
+        <v>TINI - Down (LIVE)</v>
       </c>
       <c r="B68" t="str">
-        <v>10 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=bXA_Q75QZTs</v>
+        <v>https://www.youtube.com/watch?v=ADbFeQUPTrk</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E68" t="str">
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>10 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>Icona Pop</v>
+        <v>TINI</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,33 +2977,33 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Icona Pop - Butterfly Feelings (Official Audio) - Icona Pop</v>
+        <v>TINI - Down (LIVE) - TINI</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Will Swinton - Only One (Official Video)</v>
+        <v>Charli xcx - SS26 (Official Video)</v>
       </c>
       <c r="B69" t="str">
-        <v>10 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=A0KzP-zm9hA</v>
+        <v>https://www.youtube.com/watch?v=twLhSqabby0</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E69" t="str">
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>10 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>Will Swinton</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,33 +3015,33 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Will Swinton - Only One (Official Video) - Will Swinton</v>
+        <v>Charli xcx - SS26 (Official Video) - Charli xcx</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Dean Lewis - Escape (Official Video)</v>
+        <v>Dua Lipa - Live From Mexico</v>
       </c>
       <c r="B70" t="str">
-        <v>10 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=BZRaTXCkhcg</v>
+        <v>https://www.youtube.com/watch?v=vZYVkitGXBU</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E70" t="str">
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>10 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>Dean Lewis</v>
+        <v>Dua Lipa</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,33 +3053,33 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Dean Lewis - Escape (Official Video) - Dean Lewis</v>
+        <v>Dua Lipa - Live From Mexico - Dua Lipa</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico]</v>
+        <v>Matilda Mann - 'The Fig Tree' (Official Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>10 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=PNm0hf_zZJY</v>
+        <v>https://www.youtube.com/watch?v=XPyubkkkw44</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E71" t="str">
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>10 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>Dua Lipa and OficialMana</v>
+        <v>Matilda Mann</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,33 +3091,33 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico] - Dua Lipa and OficialMana</v>
+        <v>Matilda Mann - 'The Fig Tree' (Official Video) - Matilda Mann</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Niall Horan - End of an Era (Lyric Video)</v>
+        <v>Ella Langley - Be Her (61st Academy of Country Music Awards)</v>
       </c>
       <c r="B72" t="str">
-        <v>10 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=EUNNmAAe5gQ</v>
+        <v>https://www.youtube.com/watch?v=4KbYfH7EAm8</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E72" t="str">
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>10 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>Niall Horan</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,33 +3129,33 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Niall Horan - End of an Era (Lyric Video) - Niall Horan</v>
+        <v>Ella Langley - Be Her (61st Academy of Country Music Awards) - Ella Langley</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Olivia Rodrigo - the cure (Official Music Video)</v>
+        <v>Nothing But Thieves - Evolution (Official Audio)</v>
       </c>
       <c r="B73" t="str">
-        <v>10 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=B402rKl4bUg</v>
+        <v>https://www.youtube.com/watch?v=Kcs-4EZSUW0</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E73" t="str">
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>10 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>Olivia Rodrigo</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,33 +3167,33 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Olivia Rodrigo - the cure (Official Music Video) - Olivia Rodrigo</v>
+        <v>Nothing But Thieves - Evolution (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Ruel - Debbie Don't Cry (Official Music Video)</v>
+        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO)</v>
       </c>
       <c r="B74" t="str">
-        <v>10 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=iz7wuk0GOwI</v>
+        <v>https://www.youtube.com/watch?v=HiLT1jzDZb4</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E74" t="str">
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>10 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>RUEL</v>
+        <v>kesha</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,33 +3205,33 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Ruel - Debbie Don't Cry (Official Music Video) - RUEL</v>
+        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO) - kesha</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>TINI - Down (LIVE)</v>
+        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify</v>
       </c>
       <c r="B75" t="str">
-        <v>10 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=ADbFeQUPTrk</v>
+        <v>https://www.youtube.com/watch?v=_WGsJYCCfU8</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E75" t="str">
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>10 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>TINI</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,33 +3243,33 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>TINI - Down (LIVE) - TINI</v>
+        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify - Holly Humberstone</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Charli xcx - SS26 (Official Video)</v>
+        <v>Foo Fighters - Of All People (Official Video)</v>
       </c>
       <c r="B76" t="str">
-        <v>10 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=twLhSqabby0</v>
+        <v>https://www.youtube.com/watch?v=r_iMzMrCQs0</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E76" t="str">
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>10 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>Charli xcx</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,33 +3281,33 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Charli xcx - SS26 (Official Video) - Charli xcx</v>
+        <v>Foo Fighters - Of All People (Official Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Dua Lipa - Live From Mexico</v>
+        <v>'From Me To You' by The Beatles, performed by The Young Analogues</v>
       </c>
       <c r="B77" t="str">
-        <v>11 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=vZYVkitGXBU</v>
+        <v>https://www.youtube.com/watch?v=cLiyO2t3xd0</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E77" t="str">
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>11 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>Dua Lipa</v>
+        <v>The Analogues</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,33 +3319,33 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Dua Lipa - Live From Mexico - Dua Lipa</v>
+        <v>'From Me To You' by The Beatles, performed by The Young Analogues - The Analogues</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Matilda Mann - 'The Fig Tree' (Official Video)</v>
+        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video]</v>
       </c>
       <c r="B78" t="str">
-        <v>11 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=XPyubkkkw44</v>
+        <v>https://www.youtube.com/watch?v=O67Q25sMhyU</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E78" t="str">
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>11 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>Matilda Mann</v>
+        <v>Rod Stewart</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,33 +3357,33 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Matilda Mann - 'The Fig Tree' (Official Video) - Matilda Mann</v>
+        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video] - Rod Stewart</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Ella Langley - Be Her (61st Academy of Country Music Awards)</v>
+        <v>Blue October - 18th Floor Balcony (Official Music Video)</v>
       </c>
       <c r="B79" t="str">
-        <v>12 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=4KbYfH7EAm8</v>
+        <v>https://www.youtube.com/watch?v=tPfbOjz-hRs</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E79" t="str">
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>12 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>Ella Langley</v>
+        <v>Blue October</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,33 +3395,33 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Ella Langley - Be Her (61st Academy of Country Music Awards) - Ella Langley</v>
+        <v>Blue October - 18th Floor Balcony (Official Music Video) - Blue October</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Nothing But Thieves - Evolution (Official Audio)</v>
+        <v>Far Caspian - hum (Official Video)</v>
       </c>
       <c r="B80" t="str">
-        <v>12 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=Kcs-4EZSUW0</v>
+        <v>https://www.youtube.com/watch?v=qqXrLDhGJRk</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E80" t="str">
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>12 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Far Caspian</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,33 +3433,33 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Nothing But Thieves - Evolution (Official Audio) - Nothing But Thieves</v>
+        <v>Far Caspian - hum (Official Video) - Far Caspian</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO)</v>
+        <v>Kenia Os - Love Bombing</v>
       </c>
       <c r="B81" t="str">
-        <v>12 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=HiLT1jzDZb4</v>
+        <v>https://www.youtube.com/watch?v=ZuWA3pAyriQ</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E81" t="str">
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>12 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
       </c>
       <c r="H81" t="str">
-        <v>kesha</v>
+        <v>Kenia Os</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,33 +3471,33 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO) - kesha</v>
+        <v>Kenia Os - Love Bombing - Kenia Os</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026</v>
       </c>
       <c r="B82" t="str">
-        <v>12 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=_WGsJYCCfU8</v>
+        <v>https://www.youtube.com/watch?v=ftJR_CrRsig</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E82" t="str">
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>12 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
       </c>
       <c r="H82" t="str">
-        <v>Holly Humberstone</v>
+        <v>Purple Disco Machine</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,33 +3509,33 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify - Holly Humberstone</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026 - Purple Disco Machine</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Foo Fighters - Of All People (Official Video)</v>
+        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026</v>
       </c>
       <c r="B83" t="str">
-        <v>12 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=r_iMzMrCQs0</v>
+        <v>https://www.youtube.com/watch?v=EltgrumKJfk</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E83" t="str">
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>12 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
       </c>
       <c r="H83" t="str">
-        <v>Foo Fighters</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,33 +3547,33 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Foo Fighters - Of All People (Official Video) - Foo Fighters</v>
+        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>'From Me To You' by The Beatles, performed by The Young Analogues</v>
+        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹</v>
       </c>
       <c r="B84" t="str">
-        <v>12 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=cLiyO2t3xd0</v>
+        <v>https://www.youtube.com/watch?v=EykAYQj99GU</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E84" t="str">
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>12 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
       </c>
       <c r="H84" t="str">
-        <v>The Analogues</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,33 +3585,33 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>'From Me To You' by The Beatles, performed by The Young Analogues - The Analogues</v>
+        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video]</v>
+        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B85" t="str">
-        <v>12 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=O67Q25sMhyU</v>
+        <v>https://www.youtube.com/watch?v=doGkDemPcFE</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E85" t="str">
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>12 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
       </c>
       <c r="H85" t="str">
-        <v>Rod Stewart</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,33 +3623,33 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video] - Rod Stewart</v>
+        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Blue October - 18th Floor Balcony (Official Music Video)</v>
+        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B86" t="str">
-        <v>12 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=tPfbOjz-hRs</v>
+        <v>https://www.youtube.com/watch?v=rNpFNJLhSfA</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E86" t="str">
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>12 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>Blue October</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,33 +3661,33 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Blue October - 18th Floor Balcony (Official Music Video) - Blue October</v>
+        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Far Caspian - hum (Official Video)</v>
+        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B87" t="str">
-        <v>12 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=qqXrLDhGJRk</v>
+        <v>https://www.youtube.com/watch?v=TpMQ6dhcvvE</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E87" t="str">
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>12 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>Far Caspian</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,33 +3699,33 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Far Caspian - hum (Official Video) - Far Caspian</v>
+        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Kenia Os - Love Bombing</v>
+        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​</v>
       </c>
       <c r="B88" t="str">
-        <v>12 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=ZuWA3pAyriQ</v>
+        <v>https://www.youtube.com/watch?v=ppCyj5DxO8s</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E88" t="str">
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>12 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>Kenia Os</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,33 +3737,33 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Kenia Os - Love Bombing - Kenia Os</v>
+        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​ - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026</v>
+        <v>Evanescence – Who Will You Follow (Official Music Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=ftJR_CrRsig</v>
+        <v>https://www.youtube.com/watch?v=ak4Ti54Y6rY</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E89" t="str">
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>Purple Disco Machine</v>
+        <v>Evanescence</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,33 +3775,33 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026 - Purple Disco Machine</v>
+        <v>Evanescence – Who Will You Follow (Official Music Video) - Evanescence</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026</v>
+        <v>DEEP PURPLE – ARROGANT BOY (Official Video)</v>
       </c>
       <c r="B90" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=EltgrumKJfk</v>
+        <v>https://www.youtube.com/watch?v=SoSr0sStFaE</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E90" t="str">
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>earMUSIC and Deep Purple Official</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,33 +3813,33 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026 - Eurovision Song Contest</v>
+        <v>DEEP PURPLE – ARROGANT BOY (Official Video) - earMUSIC and Deep Purple Official</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹</v>
+        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B91" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=EykAYQj99GU</v>
+        <v>https://www.youtube.com/watch?v=9iCw89UajaQ</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E91" t="str">
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,33 +3851,33 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹 - Eurovision Song Contest</v>
+        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026</v>
+        <v>Madison Cunningham - "Take Two" (Live in Chicago)</v>
       </c>
       <c r="B92" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=doGkDemPcFE</v>
+        <v>https://www.youtube.com/watch?v=bUBLlJXtjqE</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E92" t="str">
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
       </c>
       <c r="H92" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Madison Cunningham</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,33 +3889,33 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Madison Cunningham - "Take Two" (Live in Chicago) - Madison Cunningham</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026</v>
+        <v>Johnny Orlando - Heads Up (Official Video)</v>
       </c>
       <c r="B93" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=rNpFNJLhSfA</v>
+        <v>https://www.youtube.com/watch?v=s5mClhWsajE</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E93" t="str">
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,33 +3927,33 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Johnny Orlando - Heads Up (Official Video) - Johnny Orlando</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026</v>
+        <v>Carver Jones - BEST FRIEND (Official Video)</v>
       </c>
       <c r="B94" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=TpMQ6dhcvvE</v>
+        <v>https://www.youtube.com/watch?v=96xxxpZ5uxI</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E94" t="str">
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
       </c>
       <c r="H94" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Carver Jones</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,33 +3965,33 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Carver Jones - BEST FRIEND (Official Video) - Carver Jones</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​</v>
+        <v>Jazmin Bean - Darling (Official Music Video)</v>
       </c>
       <c r="B95" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=ppCyj5DxO8s</v>
+        <v>https://www.youtube.com/watch?v=N4uW3ZcowBM</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E95" t="str">
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
       </c>
       <c r="H95" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Jazmin bean</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,33 +4003,33 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​ - Eurovision Song Contest</v>
+        <v>Jazmin Bean - Darling (Official Music Video) - Jazmin bean</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Evanescence – Who Will You Follow (Official Music Video)</v>
+        <v>Baby Queen - Word Vomit (Official Visualiser)</v>
       </c>
       <c r="B96" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=ak4Ti54Y6rY</v>
+        <v>https://www.youtube.com/watch?v=T-bo4Klq_js</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E96" t="str">
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
       </c>
       <c r="H96" t="str">
-        <v>Evanescence</v>
+        <v>Baby Queen</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,33 +4041,33 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Evanescence – Who Will You Follow (Official Music Video) - Evanescence</v>
+        <v>Baby Queen - Word Vomit (Official Visualiser) - Baby Queen</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>DEEP PURPLE – ARROGANT BOY (Official Video)</v>
+        <v>Switchfoot - Absolution (Official Audio)</v>
       </c>
       <c r="B97" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=SoSr0sStFaE</v>
+        <v>https://www.youtube.com/watch?v=nCOSfMdKq9k</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E97" t="str">
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
       </c>
       <c r="H97" t="str">
-        <v>earMUSIC and Deep Purple Official</v>
+        <v>Switchfoot</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,33 +4079,33 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>DEEP PURPLE – ARROGANT BOY (Official Video) - earMUSIC and Deep Purple Official</v>
+        <v>Switchfoot - Absolution (Official Audio) - Switchfoot</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video]</v>
+        <v>Grace Potter - Love Me Not (Official Audio)</v>
       </c>
       <c r="B98" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=9iCw89UajaQ</v>
+        <v>https://www.youtube.com/watch?v=W3v0HAxDTUY</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E98" t="str">
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
       </c>
       <c r="H98" t="str">
-        <v>Armin van Buuren</v>
+        <v>Grace Potter</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,33 +4117,33 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Grace Potter - Love Me Not (Official Audio) - Grace Potter</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Madison Cunningham - "Take Two" (Live in Chicago)</v>
+        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.08.1986)</v>
       </c>
       <c r="B99" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=bUBLlJXtjqE</v>
+        <v>https://www.youtube.com/watch?v=Dhy4xH662vE</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E99" t="str">
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
       </c>
       <c r="H99" t="str">
-        <v>Madison Cunningham</v>
+        <v>Modern Talking Offiziell</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,33 +4155,33 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Madison Cunningham - "Take Two" (Live in Chicago) - Madison Cunningham</v>
+        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.08.1986) - Modern Talking Offiziell</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Johnny Orlando - Heads Up (Official Video)</v>
+        <v>The All-American Rejects - Clothesline (Official Lyric Video)</v>
       </c>
       <c r="B100" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=s5mClhWsajE</v>
+        <v>https://www.youtube.com/watch?v=y9axmk3NjrA</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E100" t="str">
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
       </c>
       <c r="H100" t="str">
-        <v>Johnny Orlando</v>
+        <v>The All-American Rejects</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,33 +4193,33 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Johnny Orlando - Heads Up (Official Video) - Johnny Orlando</v>
+        <v>The All-American Rejects - Clothesline (Official Lyric Video) - The All-American Rejects</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Carver Jones - BEST FRIEND (Official Video)</v>
+        <v>Henry Moodie - MISS U (Official Visualiser)</v>
       </c>
       <c r="B101" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=96xxxpZ5uxI</v>
+        <v>https://www.youtube.com/watch?v=l_lroRlSmTE</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E101" t="str">
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G101" t="str">
         <v/>
       </c>
       <c r="H101" t="str">
-        <v>Carver Jones</v>
+        <v>Henry Moodie</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,33 +4231,33 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Carver Jones - BEST FRIEND (Official Video) - Carver Jones</v>
+        <v>Henry Moodie - MISS U (Official Visualiser) - Henry Moodie</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Jazmin Bean - Darling (Official Music Video)</v>
+        <v>Spacey Jane - I Never See Her (Official Music Video)</v>
       </c>
       <c r="B102" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=N4uW3ZcowBM</v>
+        <v>https://www.youtube.com/watch?v=q6tyEMN5haA</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E102" t="str">
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G102" t="str">
         <v/>
       </c>
       <c r="H102" t="str">
-        <v>Jazmin bean</v>
+        <v>Spacey Jane</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4269,33 +4269,33 @@
         <v/>
       </c>
       <c r="L102" t="str">
-        <v>Jazmin Bean - Darling (Official Music Video) - Jazmin bean</v>
+        <v>Spacey Jane - I Never See Her (Official Music Video) - Spacey Jane</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Baby Queen - Word Vomit (Official Visualiser)</v>
+        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video)</v>
       </c>
       <c r="B103" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C103" t="str">
-        <v>https://www.youtube.com/watch?v=T-bo4Klq_js</v>
+        <v>https://www.youtube.com/watch?v=qacdvCqOZGc</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E103" t="str">
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G103" t="str">
         <v/>
       </c>
       <c r="H103" t="str">
-        <v>Baby Queen</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4307,4078 +4307,3774 @@
         <v/>
       </c>
       <c r="L103" t="str">
-        <v>Baby Queen - Word Vomit (Official Visualiser) - Baby Queen</v>
+        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Switchfoot - Absolution (Official Audio)</v>
+        <v>Every Single Weekend (feat. Jamie xx)</v>
       </c>
       <c r="B104" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://www.youtube.com/watch?v=nCOSfMdKq9k</v>
+        <v>https://music.apple.com/us/song/every-single-weekend-feat-jamie-xx/6770445933</v>
       </c>
       <c r="D104" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E104" t="str">
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>2 weeks ago</v>
+        <v>Every Single Weekend (feat. Jamie xx) - Single</v>
       </c>
       <c r="G104" t="str">
-        <v/>
+        <v>2:10</v>
       </c>
       <c r="H104" t="str">
-        <v>Switchfoot</v>
+        <v>The Avalanches</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/the-avalanches/27524431</v>
       </c>
       <c r="K104" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/every-single-weekend-feat-jamie-xx/6770445752</v>
       </c>
       <c r="L104" t="str">
-        <v>Switchfoot - Absolution (Official Audio) - Switchfoot</v>
+        <v>Every Single Weekend (feat. Jamie xx) - The Avalanches</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Grace Potter - Love Me Not (Official Audio)</v>
+        <v>hate that i made you love me</v>
       </c>
       <c r="B105" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://www.youtube.com/watch?v=W3v0HAxDTUY</v>
+        <v>https://music.apple.com/us/song/hate-that-i-made-you-love-me/6763656876</v>
       </c>
       <c r="D105" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E105" t="str">
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>2 weeks ago</v>
+        <v>petal</v>
       </c>
       <c r="G105" t="str">
-        <v/>
+        <v>3:17</v>
       </c>
       <c r="H105" t="str">
-        <v>Grace Potter</v>
+        <v>Ariana Grande</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/ariana-grande/412778295</v>
       </c>
       <c r="K105" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/hate-that-i-made-you-love-me/1895420989</v>
       </c>
       <c r="L105" t="str">
-        <v>Grace Potter - Love Me Not (Official Audio) - Grace Potter</v>
+        <v>hate that i made you love me - Ariana Grande</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.08.1986)</v>
+        <v>Come Inside</v>
       </c>
       <c r="B106" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://www.youtube.com/watch?v=Dhy4xH662vE</v>
+        <v>https://music.apple.com/us/song/come-inside/1887403093</v>
       </c>
       <c r="D106" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E106" t="str">
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>2 weeks ago</v>
+        <v>The Boys of Dungeon Lane</v>
       </c>
       <c r="G106" t="str">
-        <v/>
+        <v>3:13</v>
       </c>
       <c r="H106" t="str">
-        <v>Modern Talking Offiziell</v>
+        <v>Paul McCartney</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/paul-mccartney/12224</v>
       </c>
       <c r="K106" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/come-inside/1887402919</v>
       </c>
       <c r="L106" t="str">
-        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.08.1986) - Modern Talking Offiziell</v>
+        <v>Come Inside - Paul McCartney</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>The All-American Rejects - Clothesline (Official Lyric Video)</v>
+        <v>Game Time</v>
       </c>
       <c r="B107" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://www.youtube.com/watch?v=y9axmk3NjrA</v>
+        <v>https://music.apple.com/us/song/game-time/6771157200</v>
       </c>
       <c r="D107" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E107" t="str">
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>2 weeks ago</v>
+        <v>Game Time (FIFA World Cup 2026™) - Single</v>
       </c>
       <c r="G107" t="str">
-        <v/>
+        <v>3:26</v>
       </c>
       <c r="H107" t="str">
-        <v>The All-American Rejects</v>
+        <v>Future</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/future/128050210</v>
       </c>
       <c r="K107" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/game-time/6771157186</v>
       </c>
       <c r="L107" t="str">
-        <v>The All-American Rejects - Clothesline (Official Lyric Video) - The All-American Rejects</v>
+        <v>Game Time - Future</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Henry Moodie - MISS U (Official Visualiser)</v>
+        <v>Motion Party (Remix)</v>
       </c>
       <c r="B108" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://www.youtube.com/watch?v=l_lroRlSmTE</v>
+        <v>https://music.apple.com/us/song/motion-party-remix/6773413965</v>
       </c>
       <c r="D108" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E108" t="str">
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>2 weeks ago</v>
+        <v>Motion Party (Remix) - Single</v>
       </c>
       <c r="G108" t="str">
-        <v/>
+        <v>2:36</v>
       </c>
       <c r="H108" t="str">
-        <v>Henry Moodie</v>
+        <v>Bossman Dlow</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/bossman-dlow/1474308236</v>
       </c>
       <c r="K108" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/motion-party-remix/6773413953</v>
       </c>
       <c r="L108" t="str">
-        <v>Henry Moodie - MISS U (Official Visualiser) - Henry Moodie</v>
+        <v>Motion Party (Remix) - Bossman Dlow</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Spacey Jane - I Never See Her (Official Music Video)</v>
+        <v>Aquel diciembre</v>
       </c>
       <c r="B109" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://www.youtube.com/watch?v=q6tyEMN5haA</v>
+        <v>https://music.apple.com/us/song/aquel-diciembre/6769580010</v>
       </c>
       <c r="D109" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E109" t="str">
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>2 weeks ago</v>
+        <v>Do Not Disturb: Late Checkout</v>
       </c>
       <c r="G109" t="str">
-        <v/>
+        <v>3:22</v>
       </c>
       <c r="H109" t="str">
-        <v>Spacey Jane</v>
+        <v>Young Miko</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/young-miko/1576521417</v>
       </c>
       <c r="K109" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/aquel-diciembre/6769579992</v>
       </c>
       <c r="L109" t="str">
-        <v>Spacey Jane - I Never See Her (Official Music Video) - Spacey Jane</v>
+        <v>Aquel diciembre - Young Miko</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video)</v>
+        <v>Handle</v>
       </c>
       <c r="B110" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://www.youtube.com/watch?v=qacdvCqOZGc</v>
+        <v>https://music.apple.com/us/song/handle/6771922623</v>
       </c>
       <c r="D110" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E110" t="str">
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>2 weeks ago</v>
+        <v>Blue Island</v>
       </c>
       <c r="G110" t="str">
-        <v/>
+        <v>3:06</v>
       </c>
       <c r="H110" t="str">
-        <v>Megan Moroney</v>
+        <v>Ravyn Lenae</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/ravyn-lenae/1044417443</v>
       </c>
       <c r="K110" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/handle/6771922622</v>
       </c>
       <c r="L110" t="str">
-        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video) - Megan Moroney</v>
+        <v>Handle - Ravyn Lenae</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Matt Hansen - Orchid (Official Visualiser)</v>
+        <v>The Wave</v>
       </c>
       <c r="B111" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://www.youtube.com/watch?v=otVYamnbOhY</v>
+        <v>https://music.apple.com/us/song/the-wave/1886730541</v>
       </c>
       <c r="D111" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E111" t="str">
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>2 weeks ago</v>
+        <v>Sunshine</v>
       </c>
       <c r="G111" t="str">
-        <v/>
+        <v>3:22</v>
       </c>
       <c r="H111" t="str">
-        <v>Matt Hansen</v>
+        <v>Jungle</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/jungle/825833522</v>
       </c>
       <c r="K111" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/the-wave/1886730527</v>
       </c>
       <c r="L111" t="str">
-        <v>Matt Hansen - Orchid (Official Visualiser) - Matt Hansen</v>
+        <v>The Wave - Jungle</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Every Single Weekend (feat. Jamie xx)</v>
+        <v>STOP</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/every-single-weekend-feat-jamie-xx/6770445933</v>
+        <v>https://music.apple.com/us/song/stop/6771161771</v>
       </c>
       <c r="D112" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E112" t="str">
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Every Single Weekend (feat. Jamie xx) - Single</v>
+        <v>are you mad at me? - Single</v>
       </c>
       <c r="G112" t="str">
-        <v>2:10</v>
+        <v>2:56</v>
       </c>
       <c r="H112" t="str">
-        <v>The Avalanches</v>
+        <v>Bella Kay</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/the-avalanches/27524431</v>
+        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/every-single-weekend-feat-jamie-xx/6770445752</v>
+        <v>https://music.apple.com/us/album/stop/6771161760</v>
       </c>
       <c r="L112" t="str">
-        <v>Every Single Weekend (feat. Jamie xx) - The Avalanches</v>
+        <v>STOP - Bella Kay</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>hate that i made you love me</v>
+        <v>Here (Apple Music Sessions)</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/hate-that-i-made-you-love-me/6763656876</v>
+        <v>https://music.apple.com/us/song/here-apple-music-sessions/1878235516</v>
       </c>
       <c r="D113" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E113" t="str">
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>petal</v>
+        <v>Apple Music Sessions</v>
       </c>
       <c r="G113" t="str">
-        <v>3:17</v>
+        <v>3:08</v>
       </c>
       <c r="H113" t="str">
-        <v>Ariana Grande</v>
+        <v>Mumford &amp; Sons</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/ariana-grande/412778295</v>
+        <v>https://music.apple.com/us/artist/mumford-sons/307699986</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/hate-that-i-made-you-love-me/1895420989</v>
+        <v>https://music.apple.com/us/album/here-apple-music-sessions/1878235330</v>
       </c>
       <c r="L113" t="str">
-        <v>hate that i made you love me - Ariana Grande</v>
+        <v>Here (Apple Music Sessions) - Mumford &amp; Sons</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Come Inside</v>
+        <v>Talk On The Hill</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/come-inside/1887403093</v>
+        <v>https://music.apple.com/us/song/talk-on-the-hill/6769524458</v>
       </c>
       <c r="D114" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E114" t="str">
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>The Boys of Dungeon Lane</v>
+        <v>The Thread</v>
       </c>
       <c r="G114" t="str">
-        <v>3:13</v>
+        <v>3:27</v>
       </c>
       <c r="H114" t="str">
-        <v>Paul McCartney</v>
+        <v>WILLOW</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/paul-mccartney/12224</v>
+        <v>https://music.apple.com/us/artist/willow/400531893</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/come-inside/1887402919</v>
+        <v>https://music.apple.com/us/album/talk-on-the-hill/6769524450</v>
       </c>
       <c r="L114" t="str">
-        <v>Come Inside - Paul McCartney</v>
+        <v>Talk On The Hill - WILLOW</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Game Time</v>
+        <v>No Fear</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/game-time/6771157200</v>
+        <v>https://music.apple.com/us/song/no-fear/1880484493</v>
       </c>
       <c r="D115" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E115" t="str">
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Game Time (FIFA World Cup 2026™) - Single</v>
+        <v>For Love of Grace &amp; the Hereafter</v>
       </c>
       <c r="G115" t="str">
-        <v>3:26</v>
+        <v>3:38</v>
       </c>
       <c r="H115" t="str">
-        <v>Future</v>
+        <v>Iceage</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/future/128050210</v>
+        <v>https://music.apple.com/us/artist/iceage/406846711</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/game-time/6771157186</v>
+        <v>https://music.apple.com/us/album/no-fear/1880484160</v>
       </c>
       <c r="L115" t="str">
-        <v>Game Time - Future</v>
+        <v>No Fear - Iceage</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Motion Party (Remix)</v>
+        <v>Hostage</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/motion-party-remix/6773413965</v>
+        <v>https://music.apple.com/us/song/hostage/6774372288</v>
       </c>
       <c r="D116" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E116" t="str">
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Motion Party (Remix) - Single</v>
+        <v>Big Mama</v>
       </c>
       <c r="G116" t="str">
-        <v>2:36</v>
+        <v>3:11</v>
       </c>
       <c r="H116" t="str">
-        <v>Bossman Dlow</v>
+        <v>Latto</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/bossman-dlow/1474308236</v>
+        <v>https://music.apple.com/us/artist/latto/419799506</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/motion-party-remix/6773413953</v>
+        <v>https://music.apple.com/us/album/hostage/6774372200</v>
       </c>
       <c r="L116" t="str">
-        <v>Motion Party (Remix) - Bossman Dlow</v>
+        <v>Hostage - Latto</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Aquel diciembre</v>
+        <v>Sad Girls</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/aquel-diciembre/6769580010</v>
+        <v>https://music.apple.com/us/song/sad-girls/6768814374</v>
       </c>
       <c r="D117" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E117" t="str">
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Do Not Disturb: Late Checkout</v>
+        <v>Sad Girls - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>3:22</v>
+        <v>2:48</v>
       </c>
       <c r="H117" t="str">
-        <v>Young Miko</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/young-miko/1576521417</v>
+        <v>https://music.apple.com/us/artist/bebe-rexha/466059563</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/aquel-diciembre/6769579992</v>
+        <v>https://music.apple.com/us/album/sad-girls/6768814373</v>
       </c>
       <c r="L117" t="str">
-        <v>Aquel diciembre - Young Miko</v>
+        <v>Sad Girls - Bebe Rexha</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Handle</v>
+        <v>Salvame Hoy (feat. Gabito Ballesteros)</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/handle/6771922623</v>
+        <v>https://music.apple.com/us/song/salvame-hoy-feat-gabito-ballesteros/6765697019</v>
       </c>
       <c r="D118" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E118" t="str">
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Blue Island</v>
+        <v>Salvame Hoy (feat. Gabito Ballesteros) - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>3:06</v>
+        <v>3:35</v>
       </c>
       <c r="H118" t="str">
-        <v>Ravyn Lenae</v>
+        <v>Jennifer Lopez</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/ravyn-lenae/1044417443</v>
+        <v>https://music.apple.com/us/artist/jennifer-lopez/463009</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/handle/6771922622</v>
+        <v>https://music.apple.com/us/album/salvame-hoy-feat-gabito-ballesteros/1896041010</v>
       </c>
       <c r="L118" t="str">
-        <v>Handle - Ravyn Lenae</v>
+        <v>Salvame Hoy (feat. Gabito Ballesteros) - Jennifer Lopez</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>The Wave</v>
+        <v>Rubio</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/the-wave/1886730541</v>
+        <v>https://music.apple.com/us/song/rubio/6770655339</v>
       </c>
       <c r="D119" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E119" t="str">
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Sunshine</v>
+        <v>La Voz Favorita</v>
       </c>
       <c r="G119" t="str">
-        <v>3:22</v>
+        <v>4:42</v>
       </c>
       <c r="H119" t="str">
-        <v>Jungle</v>
+        <v>Jay Wheeler</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/jungle/825833522</v>
+        <v>https://music.apple.com/us/artist/jay-wheeler/164376380</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/the-wave/1886730527</v>
+        <v>https://music.apple.com/us/album/rubio/6770654729</v>
       </c>
       <c r="L119" t="str">
-        <v>The Wave - Jungle</v>
+        <v>Rubio - Jay Wheeler</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>STOP</v>
+        <v>Pary</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/stop/6771161771</v>
+        <v>https://music.apple.com/us/song/pary/6767367748</v>
       </c>
       <c r="D120" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E120" t="str">
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>are you mad at me? - Single</v>
+        <v>Con dolor - EP</v>
       </c>
       <c r="G120" t="str">
-        <v>2:56</v>
+        <v>2:52</v>
       </c>
       <c r="H120" t="str">
-        <v>Bella Kay</v>
+        <v>Grupo Frontera</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
+        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/stop/6771161760</v>
+        <v>https://music.apple.com/us/album/pary/6767367501</v>
       </c>
       <c r="L120" t="str">
-        <v>STOP - Bella Kay</v>
+        <v>Pary - Grupo Frontera</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Here (Apple Music Sessions)</v>
+        <v>Think As You Drunk</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/here-apple-music-sessions/1878235516</v>
+        <v>https://music.apple.com/us/song/think-as-you-drunk/6770725979</v>
       </c>
       <c r="D121" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E121" t="str">
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Apple Music Sessions</v>
+        <v>That's Just Me</v>
       </c>
       <c r="G121" t="str">
-        <v>3:08</v>
+        <v>3:48</v>
       </c>
       <c r="H121" t="str">
-        <v>Mumford &amp; Sons</v>
+        <v>Riley Green</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/mumford-sons/307699986</v>
+        <v>https://music.apple.com/us/artist/riley-green/662432971</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/here-apple-music-sessions/1878235330</v>
+        <v>https://music.apple.com/us/album/think-as-you-drunk/6770725355</v>
       </c>
       <c r="L121" t="str">
-        <v>Here (Apple Music Sessions) - Mumford &amp; Sons</v>
+        <v>Think As You Drunk - Riley Green</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Talk On The Hill</v>
+        <v>Play Your Games</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/talk-on-the-hill/6769524458</v>
+        <v>https://music.apple.com/us/song/play-your-games/6772932837</v>
       </c>
       <c r="D122" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E122" t="str">
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>The Thread</v>
+        <v>Play Your Games - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>3:27</v>
+        <v>3:15</v>
       </c>
       <c r="H122" t="str">
-        <v>WILLOW</v>
+        <v>Greta Van Fleet</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/willow/400531893</v>
+        <v>https://music.apple.com/us/artist/greta-van-fleet/646178956</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/talk-on-the-hill/6769524450</v>
+        <v>https://music.apple.com/us/album/play-your-games/6772932835</v>
       </c>
       <c r="L122" t="str">
-        <v>Talk On The Hill - WILLOW</v>
+        <v>Play Your Games - Greta Van Fleet</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>No Fear</v>
+        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello)</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/no-fear/1880484493</v>
+        <v>https://music.apple.com/us/song/adjourn-it-feat-serj-tankian-roman-morello/6769340216</v>
       </c>
       <c r="D123" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E123" t="str">
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>For Love of Grace &amp; the Hereafter</v>
+        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello) - Single</v>
       </c>
       <c r="G123" t="str">
-        <v>3:38</v>
+        <v>2:47</v>
       </c>
       <c r="H123" t="str">
-        <v>Iceage</v>
+        <v>Tom Morello</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/iceage/406846711</v>
+        <v>https://music.apple.com/us/artist/tom-morello/466357</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/no-fear/1880484160</v>
+        <v>https://music.apple.com/us/album/adjourn-it-feat-serj-tankian-roman-morello/6769340214</v>
       </c>
       <c r="L123" t="str">
-        <v>No Fear - Iceage</v>
+        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello) - Tom Morello</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Hostage</v>
+        <v>Essex_Honey.mp3</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/hostage/6774372288</v>
+        <v>https://music.apple.com/us/song/essex-honey-mp3/6771169447</v>
       </c>
       <c r="D124" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E124" t="str">
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Big Mama</v>
+        <v>Essex_Honey.mp3 - Single</v>
       </c>
       <c r="G124" t="str">
-        <v>3:11</v>
+        <v>4:49</v>
       </c>
       <c r="H124" t="str">
-        <v>Latto</v>
+        <v>Blood Orange</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/latto/419799506</v>
+        <v>https://music.apple.com/us/artist/blood-orange/440698865</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/hostage/6774372200</v>
+        <v>https://music.apple.com/us/album/essex-honey-mp3/6771169151</v>
       </c>
       <c r="L124" t="str">
-        <v>Hostage - Latto</v>
+        <v>Essex_Honey.mp3 - Blood Orange</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Sad Girls</v>
+        <v>minute</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/sad-girls/6768814374</v>
+        <v>https://music.apple.com/us/song/minute/1875303122</v>
       </c>
       <c r="D125" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E125" t="str">
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Sad Girls - Single</v>
+        <v>ghosted - EP</v>
       </c>
       <c r="G125" t="str">
-        <v>2:48</v>
+        <v>2:59</v>
       </c>
       <c r="H125" t="str">
-        <v>Bebe Rexha</v>
+        <v>Saint Harison</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/bebe-rexha/466059563</v>
+        <v>https://music.apple.com/us/artist/saint-harison/1639595302</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/sad-girls/6768814373</v>
+        <v>https://music.apple.com/us/album/minute/1875302904</v>
       </c>
       <c r="L125" t="str">
-        <v>Sad Girls - Bebe Rexha</v>
+        <v>minute - Saint Harison</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Salvame Hoy (feat. Gabito Ballesteros)</v>
+        <v>THE LIVING</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/salvame-hoy-feat-gabito-ballesteros/6765697019</v>
+        <v>https://music.apple.com/us/song/the-living/1894092345</v>
       </c>
       <c r="D126" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E126" t="str">
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Salvame Hoy (feat. Gabito Ballesteros) - Single</v>
+        <v>COSMIC OPERA ACT II</v>
       </c>
       <c r="G126" t="str">
-        <v>3:35</v>
+        <v>2:48</v>
       </c>
       <c r="H126" t="str">
-        <v>Jennifer Lopez</v>
+        <v>Labrinth</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/jennifer-lopez/463009</v>
+        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/salvame-hoy-feat-gabito-ballesteros/1896041010</v>
+        <v>https://music.apple.com/us/album/the-living/1894092339</v>
       </c>
       <c r="L126" t="str">
-        <v>Salvame Hoy (feat. Gabito Ballesteros) - Jennifer Lopez</v>
+        <v>THE LIVING - Labrinth</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Rubio</v>
+        <v>Thug</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/rubio/6770655339</v>
+        <v>https://music.apple.com/us/song/thug/6769289966</v>
       </c>
       <c r="D127" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E127" t="str">
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>La Voz Favorita</v>
+        <v>Thug - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>4:42</v>
+        <v>2:25</v>
       </c>
       <c r="H127" t="str">
-        <v>Jay Wheeler</v>
+        <v>G Herbo</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/jay-wheeler/164376380</v>
+        <v>https://music.apple.com/us/artist/g-herbo/1036753321</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/rubio/6770654729</v>
+        <v>https://music.apple.com/us/album/thug/6769289953</v>
       </c>
       <c r="L127" t="str">
-        <v>Rubio - Jay Wheeler</v>
+        <v>Thug - G Herbo</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Pary</v>
+        <v>Clap</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/pary/6767367748</v>
+        <v>https://music.apple.com/us/song/clap/6769903711</v>
       </c>
       <c r="D128" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E128" t="str">
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Con dolor - EP</v>
+        <v>Clap - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>2:52</v>
+        <v>2:04</v>
       </c>
       <c r="H128" t="str">
-        <v>Grupo Frontera</v>
+        <v>Polo G</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
+        <v>https://music.apple.com/us/artist/polo-g/1159371412</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/pary/6767367501</v>
+        <v>https://music.apple.com/us/album/clap/6769903710</v>
       </c>
       <c r="L128" t="str">
-        <v>Pary - Grupo Frontera</v>
+        <v>Clap - Polo G</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Think As You Drunk</v>
+        <v>GANG BIZNESS</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/think-as-you-drunk/6770725979</v>
+        <v>https://music.apple.com/us/song/gang-bizness/6772383809</v>
       </c>
       <c r="D129" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E129" t="str">
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>That's Just Me</v>
+        <v>THE GENTLEMEN'S CLUB</v>
       </c>
       <c r="G129" t="str">
-        <v>3:48</v>
+        <v>2:47</v>
       </c>
       <c r="H129" t="str">
-        <v>Riley Green</v>
+        <v>YG</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/riley-green/662432971</v>
+        <v>https://music.apple.com/us/artist/yg/189792075</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/think-as-you-drunk/6770725355</v>
+        <v>https://music.apple.com/us/album/gang-bizness/6772383681</v>
       </c>
       <c r="L129" t="str">
-        <v>Think As You Drunk - Riley Green</v>
+        <v>GANG BIZNESS - YG</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Play Your Games</v>
+        <v>UR HEARTBEAT (WHO DO U THINK ABOUT AT 2AM?)</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/play-your-games/6772932837</v>
+        <v>https://music.apple.com/us/song/ur-heartbeat-who-do-u-think-about-at-2am/6765534140</v>
       </c>
       <c r="D130" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E130" t="str">
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Play Your Games - Single</v>
+        <v>A LITTLE VENGEANCE</v>
       </c>
       <c r="G130" t="str">
-        <v>3:15</v>
+        <v>2:50</v>
       </c>
       <c r="H130" t="str">
-        <v>Greta Van Fleet</v>
+        <v>Jessie Reyez</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/greta-van-fleet/646178956</v>
+        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/play-your-games/6772932835</v>
+        <v>https://music.apple.com/us/album/ur-heartbeat-who-do-u-think-about-at-2am/1895983502</v>
       </c>
       <c r="L130" t="str">
-        <v>Play Your Games - Greta Van Fleet</v>
+        <v>UR HEARTBEAT (WHO DO U THINK ABOUT AT 2AM?) - Jessie Reyez</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello)</v>
+        <v>Joshua Tree</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/adjourn-it-feat-serj-tankian-roman-morello/6769340216</v>
+        <v>https://music.apple.com/us/song/joshua-tree/6771859148</v>
       </c>
       <c r="D131" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E131" t="str">
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello) - Single</v>
+        <v>Euphoria: Season 3 (HBO Original Series Soundtrack)</v>
       </c>
       <c r="G131" t="str">
-        <v>2:47</v>
+        <v>2:50</v>
       </c>
       <c r="H131" t="str">
-        <v>Tom Morello</v>
+        <v>Hans Zimmer</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/tom-morello/466357</v>
+        <v>https://music.apple.com/us/artist/hans-zimmer/454295032</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/adjourn-it-feat-serj-tankian-roman-morello/6769340214</v>
+        <v>https://music.apple.com/us/album/joshua-tree/6771858464</v>
       </c>
       <c r="L131" t="str">
-        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello) - Tom Morello</v>
+        <v>Joshua Tree - Hans Zimmer</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Essex_Honey.mp3</v>
+        <v>Mi Gran Amor</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/essex-honey-mp3/6771169447</v>
+        <v>https://music.apple.com/us/song/mi-gran-amor/6773365775</v>
       </c>
       <c r="D132" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E132" t="str">
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Essex_Honey.mp3 - Single</v>
+        <v>Mi Gran Amor - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>4:49</v>
+        <v>3:37</v>
       </c>
       <c r="H132" t="str">
-        <v>Blood Orange</v>
+        <v>Santana</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/blood-orange/440698865</v>
+        <v>https://music.apple.com/us/artist/santana/217174</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/essex-honey-mp3/6771169151</v>
+        <v>https://music.apple.com/us/album/mi-gran-amor/6773365236</v>
       </c>
       <c r="L132" t="str">
-        <v>Essex_Honey.mp3 - Blood Orange</v>
+        <v>Mi Gran Amor - Santana</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>minute</v>
+        <v>london</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/minute/1875303122</v>
+        <v>https://music.apple.com/us/song/london/6770745672</v>
       </c>
       <c r="D133" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E133" t="str">
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>ghosted - EP</v>
+        <v>stardust - EP</v>
       </c>
       <c r="G133" t="str">
-        <v>2:59</v>
+        <v>3:23</v>
       </c>
       <c r="H133" t="str">
-        <v>Saint Harison</v>
+        <v>Freya Skye</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/saint-harison/1639595302</v>
+        <v>https://music.apple.com/us/artist/freya-skye/1541643053</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/minute/1875302904</v>
+        <v>https://music.apple.com/us/album/london/6770745662</v>
       </c>
       <c r="L133" t="str">
-        <v>minute - Saint Harison</v>
+        <v>london - Freya Skye</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>THE LIVING</v>
+        <v>Caution</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/the-living/1894092345</v>
+        <v>https://music.apple.com/us/song/caution/6768487482</v>
       </c>
       <c r="D134" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E134" t="str">
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>COSMIC OPERA ACT II</v>
+        <v>K-POPS! (Music from and inspired by K-POPS! Motion Picture)</v>
       </c>
       <c r="G134" t="str">
-        <v>2:48</v>
+        <v>2:43</v>
       </c>
       <c r="H134" t="str">
-        <v>Labrinth</v>
+        <v>NMIXX</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
+        <v>https://music.apple.com/us/artist/nmixx/1600411676</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/the-living/1894092339</v>
+        <v>https://music.apple.com/us/album/caution/6768487478</v>
       </c>
       <c r="L134" t="str">
-        <v>THE LIVING - Labrinth</v>
+        <v>Caution - NMIXX</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Thug</v>
+        <v>LEMONADE (feat. Becky G)</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/thug/6769289966</v>
+        <v>https://music.apple.com/us/song/lemonade-feat-becky-g/1893742425</v>
       </c>
       <c r="D135" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E135" t="str">
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Thug - Single</v>
+        <v>LEMONADE - The 2nd Album</v>
       </c>
       <c r="G135" t="str">
-        <v>2:25</v>
+        <v>3:07</v>
       </c>
       <c r="H135" t="str">
-        <v>G Herbo</v>
+        <v>aespa</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/g-herbo/1036753321</v>
+        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/thug/6769289953</v>
+        <v>https://music.apple.com/us/album/lemonade-feat-becky-g/1893742002</v>
       </c>
       <c r="L135" t="str">
-        <v>Thug - G Herbo</v>
+        <v>LEMONADE (feat. Becky G) - aespa</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Clap</v>
+        <v>Take Me Back (Leave Me There)</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/clap/6769903711</v>
+        <v>https://music.apple.com/us/song/take-me-back-leave-me-there/1892466278</v>
       </c>
       <c r="D136" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E136" t="str">
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Clap - Single</v>
+        <v>Banks Of The Trinity</v>
       </c>
       <c r="G136" t="str">
-        <v>2:04</v>
+        <v>2:58</v>
       </c>
       <c r="H136" t="str">
-        <v>Polo G</v>
+        <v>Cody Johnson</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/polo-g/1159371412</v>
+        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/clap/6769903710</v>
+        <v>https://music.apple.com/us/album/take-me-back-leave-me-there/1892465981</v>
       </c>
       <c r="L136" t="str">
-        <v>Clap - Polo G</v>
+        <v>Take Me Back (Leave Me There) - Cody Johnson</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>GANG BIZNESS</v>
+        <v>Cheap Thrills</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/gang-bizness/6772383809</v>
+        <v>https://music.apple.com/us/song/cheap-thrills/6771156732</v>
       </c>
       <c r="D137" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E137" t="str">
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>THE GENTLEMEN'S CLUB</v>
+        <v>Cheap Thrills - Single</v>
       </c>
       <c r="G137" t="str">
-        <v>2:47</v>
+        <v>2:42</v>
       </c>
       <c r="H137" t="str">
-        <v>YG</v>
+        <v>Gavin Adcock</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/yg/189792075</v>
+        <v>https://music.apple.com/us/artist/gavin-adcock/1580645019</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/gang-bizness/6772383681</v>
+        <v>https://music.apple.com/us/album/cheap-thrills/6771156723</v>
       </c>
       <c r="L137" t="str">
-        <v>GANG BIZNESS - YG</v>
+        <v>Cheap Thrills - Gavin Adcock</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>UR HEARTBEAT (WHO DO U THINK ABOUT AT 2AM?)</v>
+        <v>ME VALE V</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/ur-heartbeat-who-do-u-think-about-at-2am/6765534140</v>
+        <v>https://music.apple.com/us/song/me-vale-v/6769567844</v>
       </c>
       <c r="D138" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E138" t="str">
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>A LITTLE VENGEANCE</v>
+        <v>ACOMODO</v>
       </c>
       <c r="G138" t="str">
-        <v>2:50</v>
+        <v>3:06</v>
       </c>
       <c r="H138" t="str">
-        <v>Jessie Reyez</v>
+        <v>Tito Double P</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
+        <v>https://music.apple.com/us/artist/tito-double-p/1690905306</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/ur-heartbeat-who-do-u-think-about-at-2am/1895983502</v>
+        <v>https://music.apple.com/us/album/me-vale-v/6769567568</v>
       </c>
       <c r="L138" t="str">
-        <v>UR HEARTBEAT (WHO DO U THINK ABOUT AT 2AM?) - Jessie Reyez</v>
+        <v>ME VALE V - Tito Double P</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Joshua Tree</v>
+        <v>Bug In The Cake</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/joshua-tree/6771859148</v>
+        <v>https://music.apple.com/us/song/bug-in-the-cake/1880470542</v>
       </c>
       <c r="D139" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E139" t="str">
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Euphoria: Season 3 (HBO Original Series Soundtrack)</v>
+        <v>Be Sweet To Me</v>
       </c>
       <c r="G139" t="str">
-        <v>2:50</v>
+        <v>2:48</v>
       </c>
       <c r="H139" t="str">
-        <v>Hans Zimmer</v>
+        <v>Violet Grohl</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/hans-zimmer/454295032</v>
+        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/joshua-tree/6771858464</v>
+        <v>https://music.apple.com/us/album/bug-in-the-cake/1880470537</v>
       </c>
       <c r="L139" t="str">
-        <v>Joshua Tree - Hans Zimmer</v>
+        <v>Bug In The Cake - Violet Grohl</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Mi Gran Amor</v>
+        <v>Coil</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/mi-gran-amor/6773365775</v>
+        <v>https://music.apple.com/us/song/coil/6766858354</v>
       </c>
       <c r="D140" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E140" t="str">
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Mi Gran Amor - Single</v>
+        <v>Rumspringa</v>
       </c>
       <c r="G140" t="str">
-        <v>3:37</v>
+        <v>3:54</v>
       </c>
       <c r="H140" t="str">
-        <v>Santana</v>
+        <v>ear</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/santana/217174</v>
+        <v>https://music.apple.com/us/artist/ear/1829661500</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/mi-gran-amor/6773365236</v>
+        <v>https://music.apple.com/us/album/coil/6766858352</v>
       </c>
       <c r="L140" t="str">
-        <v>Mi Gran Amor - Santana</v>
+        <v>Coil - ear</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>london</v>
+        <v>Smugglers &amp; Scholars (feat. Killer Mike)</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/london/6770745672</v>
+        <v>https://music.apple.com/us/song/smugglers-scholars-feat-killer-mike/6769424017</v>
       </c>
       <c r="D141" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E141" t="str">
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>stardust - EP</v>
+        <v>Smugglers &amp; Scholars (feat. Killer Mike) - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>3:23</v>
+        <v>3:30</v>
       </c>
       <c r="H141" t="str">
-        <v>Freya Skye</v>
+        <v>Kneecap</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/freya-skye/1541643053</v>
+        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/london/6770745662</v>
+        <v>https://music.apple.com/us/album/smugglers-scholars-feat-killer-mike/6769423676</v>
       </c>
       <c r="L141" t="str">
-        <v>london - Freya Skye</v>
+        <v>Smugglers &amp; Scholars (feat. Killer Mike) - Kneecap</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Caution</v>
+        <v>Out of my Head</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/caution/6768487482</v>
+        <v>https://music.apple.com/us/song/out-of-my-head/6767725166</v>
       </c>
       <c r="D142" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E142" t="str">
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>K-POPS! (Music from and inspired by K-POPS! Motion Picture)</v>
+        <v>I Forgot / Out of my Head - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>2:43</v>
+        <v>3:04</v>
       </c>
       <c r="H142" t="str">
-        <v>NMIXX</v>
+        <v>Cara Delevingne</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/nmixx/1600411676</v>
+        <v>https://music.apple.com/us/artist/cara-delevingne/1204798982</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/caution/6768487478</v>
+        <v>https://music.apple.com/us/album/out-of-my-head/6767725156</v>
       </c>
       <c r="L142" t="str">
-        <v>Caution - NMIXX</v>
+        <v>Out of my Head - Cara Delevingne</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>LEMONADE (feat. Becky G)</v>
+        <v>Passenger Princess</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/lemonade-feat-becky-g/1893742425</v>
+        <v>https://music.apple.com/us/song/passenger-princess/6771012228</v>
       </c>
       <c r="D143" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E143" t="str">
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>LEMONADE - The 2nd Album</v>
+        <v>Passenger Princess - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>3:07</v>
+        <v>3:18</v>
       </c>
       <c r="H143" t="str">
-        <v>aespa</v>
+        <v>Perrie</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
+        <v>https://music.apple.com/us/artist/perrie/1729865272</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/lemonade-feat-becky-g/1893742002</v>
+        <v>https://music.apple.com/us/album/passenger-princess/6771012223</v>
       </c>
       <c r="L143" t="str">
-        <v>LEMONADE (feat. Becky G) - aespa</v>
+        <v>Passenger Princess - Perrie</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Take Me Back (Leave Me There)</v>
+        <v>Man of the House</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/take-me-back-leave-me-there/1892466278</v>
+        <v>https://music.apple.com/us/song/man-of-the-house/1893733057</v>
       </c>
       <c r="D144" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E144" t="str">
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Banks Of The Trinity</v>
+        <v>SE9</v>
       </c>
       <c r="G144" t="str">
-        <v>2:58</v>
+        <v>2:35</v>
       </c>
       <c r="H144" t="str">
-        <v>Cody Johnson</v>
+        <v>Skye Newman</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
+        <v>https://music.apple.com/us/artist/skye-newman/1799174381</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/take-me-back-leave-me-there/1892465981</v>
+        <v>https://music.apple.com/us/album/man-of-the-house/1893733056</v>
       </c>
       <c r="L144" t="str">
-        <v>Take Me Back (Leave Me There) - Cody Johnson</v>
+        <v>Man of the House - Skye Newman</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Cheap Thrills</v>
+        <v>Beautiful Freeks</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/cheap-thrills/6771156732</v>
+        <v>https://music.apple.com/us/song/beautiful-freeks/6764602396</v>
       </c>
       <c r="D145" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E145" t="str">
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Cheap Thrills - Single</v>
+        <v>Beautiful Freeks - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>2:42</v>
+        <v>2:37</v>
       </c>
       <c r="H145" t="str">
-        <v>Gavin Adcock</v>
+        <v>MEEK</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/gavin-adcock/1580645019</v>
+        <v>https://music.apple.com/us/artist/meek/1784432868</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/cheap-thrills/6771156723</v>
+        <v>https://music.apple.com/us/album/beautiful-freeks/6764602393</v>
       </c>
       <c r="L145" t="str">
-        <v>Cheap Thrills - Gavin Adcock</v>
+        <v>Beautiful Freeks - MEEK</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>ME VALE V</v>
+        <v>Slave to the Rithm (feat. Bring Me The Horizon) [I Hate Models Never Alone Remix]</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/me-vale-v/6769567844</v>
+        <v>https://music.apple.com/us/song/slave-to-the-rithm-feat-bring-me-the-horizon-i/6771972616</v>
       </c>
       <c r="D146" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E146" t="str">
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>ACOMODO</v>
+        <v>Slave to the Rithm (I Hate Models Never Alone Remix) [feat. Bring Me The Horizon] - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>3:06</v>
+        <v>4:34</v>
       </c>
       <c r="H146" t="str">
-        <v>Tito Double P</v>
+        <v>ILLENIUM</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/tito-double-p/1690905306</v>
+        <v>https://music.apple.com/us/artist/illenium/645420096</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/me-vale-v/6769567568</v>
+        <v>https://music.apple.com/us/album/slave-to-the-rithm-feat-bring-me-the-horizon-i/6771972613</v>
       </c>
       <c r="L146" t="str">
-        <v>ME VALE V - Tito Double P</v>
+        <v>Slave to the Rithm (feat. Bring Me The Horizon) [I Hate Models Never Alone Remix] - ILLENIUM</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Bug In The Cake</v>
+        <v>Beg For Me (JADE Remix)</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/bug-in-the-cake/1880470542</v>
+        <v>https://music.apple.com/us/song/beg-for-me-jade-remix/6771474203</v>
       </c>
       <c r="D147" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E147" t="str">
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Be Sweet To Me</v>
+        <v>Beg For Me (Remix) - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>2:48</v>
+        <v>2:50</v>
       </c>
       <c r="H147" t="str">
-        <v>Violet Grohl</v>
+        <v>Lily Allen</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
+        <v>https://music.apple.com/us/artist/lily-allen/157063999</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/bug-in-the-cake/1880470537</v>
+        <v>https://music.apple.com/us/album/beg-for-me-jade-remix/6771474201</v>
       </c>
       <c r="L147" t="str">
-        <v>Bug In The Cake - Violet Grohl</v>
+        <v>Beg For Me (JADE Remix) - Lily Allen</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Coil</v>
+        <v>ABOVE IT</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/coil/6766858354</v>
+        <v>https://music.apple.com/us/song/above-it/6766248703</v>
       </c>
       <c r="D148" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E148" t="str">
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Rumspringa</v>
+        <v>GET THE TABLES - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>3:54</v>
+        <v>1:45</v>
       </c>
       <c r="H148" t="str">
-        <v>ear</v>
+        <v>Andy Mineo</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/ear/1829661500</v>
+        <v>https://music.apple.com/us/artist/andy-mineo/257538441</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/coil/6766858352</v>
+        <v>https://music.apple.com/us/album/above-it/6766248699</v>
       </c>
       <c r="L148" t="str">
-        <v>Coil - ear</v>
+        <v>ABOVE IT - Andy Mineo</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Smugglers &amp; Scholars (feat. Killer Mike)</v>
+        <v>THE JESUS GENERATION</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/smugglers-scholars-feat-killer-mike/6769424017</v>
+        <v>https://music.apple.com/us/song/the-jesus-generation/6773948895</v>
       </c>
       <c r="D149" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E149" t="str">
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Smugglers &amp; Scholars (feat. Killer Mike) - Single</v>
+        <v>THE JESUS GENERATION - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>3:30</v>
+        <v>4:15</v>
       </c>
       <c r="H149" t="str">
-        <v>Kneecap</v>
+        <v>Forrest Frank</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
+        <v>https://music.apple.com/us/artist/forrest-frank/1436657314</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/smugglers-scholars-feat-killer-mike/6769423676</v>
+        <v>https://music.apple.com/us/album/the-jesus-generation/6773948742</v>
       </c>
       <c r="L149" t="str">
-        <v>Smugglers &amp; Scholars (feat. Killer Mike) - Kneecap</v>
+        <v>THE JESUS GENERATION - Forrest Frank</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Out of my Head</v>
+        <v>Is It Over Now?</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/out-of-my-head/6767725166</v>
+        <v>https://music.apple.com/us/song/is-it-over-now/6767564750</v>
       </c>
       <c r="D150" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E150" t="str">
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>I Forgot / Out of my Head - Single</v>
+        <v>Is It Over Now? - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>3:04</v>
+        <v>3:39</v>
       </c>
       <c r="H150" t="str">
-        <v>Cara Delevingne</v>
+        <v>Elderbrook</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/cara-delevingne/1204798982</v>
+        <v>https://music.apple.com/us/artist/elderbrook/736829657</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/out-of-my-head/6767725156</v>
+        <v>https://music.apple.com/us/album/is-it-over-now/6767564746</v>
       </c>
       <c r="L150" t="str">
-        <v>Out of my Head - Cara Delevingne</v>
+        <v>Is It Over Now? - Elderbrook</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Passenger Princess</v>
+        <v>12 Steps</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/passenger-princess/6771012228</v>
+        <v>https://music.apple.com/us/song/12-steps/6769559623</v>
       </c>
       <c r="D151" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E151" t="str">
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Passenger Princess - Single</v>
+        <v>12 Steps - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>3:18</v>
+        <v>3:11</v>
       </c>
       <c r="H151" t="str">
-        <v>Perrie</v>
+        <v>Dexter and The Moonrocks</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/perrie/1729865272</v>
+        <v>https://music.apple.com/us/artist/dexter-and-the-moonrocks/1581657500</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/passenger-princess/6771012223</v>
+        <v>https://music.apple.com/us/album/12-steps/6769559618</v>
       </c>
       <c r="L151" t="str">
-        <v>Passenger Princess - Perrie</v>
+        <v>12 Steps - Dexter and The Moonrocks</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Man of the House</v>
+        <v>Over And Over</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/man-of-the-house/1893733057</v>
+        <v>https://music.apple.com/us/song/over-and-over/6771585908</v>
       </c>
       <c r="D152" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E152" t="str">
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>SE9</v>
+        <v>It's A Dying Art</v>
       </c>
       <c r="G152" t="str">
-        <v>2:35</v>
+        <v>4:38</v>
       </c>
       <c r="H152" t="str">
-        <v>Skye Newman</v>
+        <v>Little Big Town</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/skye-newman/1799174381</v>
+        <v>https://music.apple.com/us/artist/little-big-town/513770</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/man-of-the-house/1893733056</v>
+        <v>https://music.apple.com/us/album/over-and-over/6771585889</v>
       </c>
       <c r="L152" t="str">
-        <v>Man of the House - Skye Newman</v>
+        <v>Over And Over - Little Big Town</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Beautiful Freeks</v>
+        <v>AMAPOLA</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/beautiful-freeks/6764602396</v>
+        <v>https://music.apple.com/us/song/amapola/6769560428</v>
       </c>
       <c r="D153" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E153" t="str">
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Beautiful Freeks - Single</v>
+        <v>Ricky y Mau</v>
       </c>
       <c r="G153" t="str">
-        <v>2:37</v>
+        <v>2:22</v>
       </c>
       <c r="H153" t="str">
-        <v>MEEK</v>
+        <v>Mau y Ricky</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/meek/1784432868</v>
+        <v>https://music.apple.com/us/artist/mau-y-ricky/1096068683</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/beautiful-freeks/6764602393</v>
+        <v>https://music.apple.com/us/album/amapola/6769559985</v>
       </c>
       <c r="L153" t="str">
-        <v>Beautiful Freeks - MEEK</v>
+        <v>AMAPOLA - Mau y Ricky</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Slave to the Rithm (feat. Bring Me The Horizon) [I Hate Models Never Alone Remix]</v>
+        <v>Mad About It</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/slave-to-the-rithm-feat-bring-me-the-horizon-i/6771972616</v>
+        <v>https://music.apple.com/us/song/mad-about-it/6767425272</v>
       </c>
       <c r="D154" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E154" t="str">
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Slave to the Rithm (I Hate Models Never Alone Remix) [feat. Bring Me The Horizon] - Single</v>
+        <v>Mad About It - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>4:34</v>
+        <v>2:37</v>
       </c>
       <c r="H154" t="str">
-        <v>ILLENIUM</v>
+        <v>Dasha</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/illenium/645420096</v>
+        <v>https://music.apple.com/us/artist/dasha/1462663731</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/slave-to-the-rithm-feat-bring-me-the-horizon-i/6771972613</v>
+        <v>https://music.apple.com/us/album/mad-about-it/6767425271</v>
       </c>
       <c r="L154" t="str">
-        <v>Slave to the Rithm (feat. Bring Me The Horizon) [I Hate Models Never Alone Remix] - ILLENIUM</v>
+        <v>Mad About It - Dasha</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Beg For Me (JADE Remix)</v>
+        <v>Love’s a Gun</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/beg-for-me-jade-remix/6771474203</v>
+        <v>https://music.apple.com/us/song/loves-a-gun/6771898253</v>
       </c>
       <c r="D155" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E155" t="str">
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Beg For Me (Remix) - Single</v>
+        <v>Love’s a Gun - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>2:50</v>
+        <v>2:59</v>
       </c>
       <c r="H155" t="str">
-        <v>Lily Allen</v>
+        <v>Daniel Seavey</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/lily-allen/157063999</v>
+        <v>https://music.apple.com/us/artist/daniel-seavey/1646124302</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/beg-for-me-jade-remix/6771474201</v>
+        <v>https://music.apple.com/us/album/loves-a-gun/6771897951</v>
       </c>
       <c r="L155" t="str">
-        <v>Beg For Me (JADE Remix) - Lily Allen</v>
+        <v>Love’s a Gun - Daniel Seavey</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>ABOVE IT</v>
+        <v>Long Story Short</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/above-it/6766248703</v>
+        <v>https://music.apple.com/us/song/long-story-short/6770700866</v>
       </c>
       <c r="D156" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E156" t="str">
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>GET THE TABLES - Single</v>
+        <v>Long Story Short - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>1:45</v>
+        <v>2:48</v>
       </c>
       <c r="H156" t="str">
-        <v>Andy Mineo</v>
+        <v>Knox</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/andy-mineo/257538441</v>
+        <v>https://music.apple.com/us/artist/knox/1547519433</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/above-it/6766248699</v>
+        <v>https://music.apple.com/us/album/long-story-short/6770700853</v>
       </c>
       <c r="L156" t="str">
-        <v>ABOVE IT - Andy Mineo</v>
+        <v>Long Story Short - Knox</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>THE JESUS GENERATION</v>
+        <v>Dior</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/the-jesus-generation/6773948895</v>
+        <v>https://music.apple.com/us/song/dior/1892136721</v>
       </c>
       <c r="D157" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E157" t="str">
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>THE JESUS GENERATION - Single</v>
+        <v>bitknot</v>
       </c>
       <c r="G157" t="str">
-        <v>4:15</v>
+        <v>3:32</v>
       </c>
       <c r="H157" t="str">
-        <v>Forrest Frank</v>
+        <v>feeble little horse</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/forrest-frank/1436657314</v>
+        <v>https://music.apple.com/us/artist/feeble-little-horse/1564273208</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/the-jesus-generation/6773948742</v>
+        <v>https://music.apple.com/us/album/dior/1892136714</v>
       </c>
       <c r="L157" t="str">
-        <v>THE JESUS GENERATION - Forrest Frank</v>
+        <v>Dior - feeble little horse</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Is It Over Now?</v>
+        <v>blue jeans</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/is-it-over-now/6767564750</v>
+        <v>https://music.apple.com/us/song/blue-jeans/6770529591</v>
       </c>
       <c r="D158" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E158" t="str">
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Is It Over Now? - Single</v>
+        <v>blue jeans - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>3:39</v>
+        <v>2:37</v>
       </c>
       <c r="H158" t="str">
-        <v>Elderbrook</v>
+        <v>Nightly</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/elderbrook/736829657</v>
+        <v>https://music.apple.com/us/artist/nightly/352310972</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/is-it-over-now/6767564746</v>
+        <v>https://music.apple.com/us/album/blue-jeans/6770529589</v>
       </c>
       <c r="L158" t="str">
-        <v>Is It Over Now? - Elderbrook</v>
+        <v>blue jeans - Nightly</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>12 Steps</v>
+        <v>Que Gacho</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/12-steps/6769559623</v>
+        <v>https://music.apple.com/us/song/que-gacho/6770628420</v>
       </c>
       <c r="D159" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E159" t="str">
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>12 Steps - Single</v>
+        <v>Que Gacho - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>3:11</v>
+        <v>3:13</v>
       </c>
       <c r="H159" t="str">
-        <v>Dexter and The Moonrocks</v>
+        <v>Luis R Conriquez</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/dexter-and-the-moonrocks/1581657500</v>
+        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/12-steps/6769559618</v>
+        <v>https://music.apple.com/us/album/que-gacho/6770628419</v>
       </c>
       <c r="L159" t="str">
-        <v>12 Steps - Dexter and The Moonrocks</v>
+        <v>Que Gacho - Luis R Conriquez</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Over And Over</v>
+        <v>same God</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/over-and-over/6771585908</v>
+        <v>https://music.apple.com/us/song/same-god/1878232616</v>
       </c>
       <c r="D160" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E160" t="str">
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>It's A Dying Art</v>
+        <v>I HOPE THIS HELPS</v>
       </c>
       <c r="G160" t="str">
-        <v>4:38</v>
+        <v>3:34</v>
       </c>
       <c r="H160" t="str">
-        <v>Little Big Town</v>
+        <v>Alana Springsteen</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/little-big-town/513770</v>
+        <v>https://music.apple.com/us/artist/alana-springsteen/1309335606</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/over-and-over/6771585889</v>
+        <v>https://music.apple.com/us/album/same-god/1878232194</v>
       </c>
       <c r="L160" t="str">
-        <v>Over And Over - Little Big Town</v>
+        <v>same God - Alana Springsteen</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>AMAPOLA</v>
+        <v>emotional swaggage</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/amapola/6769560428</v>
+        <v>https://music.apple.com/us/song/emotional-swaggage/6767397453</v>
       </c>
       <c r="D161" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E161" t="str">
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Ricky y Mau</v>
+        <v>IDCASH</v>
       </c>
       <c r="G161" t="str">
-        <v>2:22</v>
+        <v>2:12</v>
       </c>
       <c r="H161" t="str">
-        <v>Mau y Ricky</v>
+        <v>IDK</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/mau-y-ricky/1096068683</v>
+        <v>https://music.apple.com/us/artist/idk/1578186947</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/amapola/6769559985</v>
+        <v>https://music.apple.com/us/album/emotional-swaggage/6767397348</v>
       </c>
       <c r="L161" t="str">
-        <v>AMAPOLA - Mau y Ricky</v>
+        <v>emotional swaggage - IDK</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Mad About It</v>
+        <v>Baby Driver</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/mad-about-it/6767425272</v>
+        <v>https://music.apple.com/us/song/baby-driver/6769152279</v>
       </c>
       <c r="D162" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E162" t="str">
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Mad About It - Single</v>
+        <v>Baby Driver - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>2:37</v>
+        <v>3:36</v>
       </c>
       <c r="H162" t="str">
-        <v>Dasha</v>
+        <v>070 Shake</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/dasha/1462663731</v>
+        <v>https://music.apple.com/us/artist/070-shake/1097177293</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/mad-about-it/6767425271</v>
+        <v>https://music.apple.com/us/album/baby-driver/6769152273</v>
       </c>
       <c r="L162" t="str">
-        <v>Mad About It - Dasha</v>
+        <v>Baby Driver - 070 Shake</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Love’s a Gun</v>
+        <v>More! More! More!</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/loves-a-gun/6771898253</v>
+        <v>https://music.apple.com/us/song/more-more-more/6770600105</v>
       </c>
       <c r="D163" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E163" t="str">
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Love’s a Gun - Single</v>
+        <v>REBECCA</v>
       </c>
       <c r="G163" t="str">
-        <v>2:59</v>
+        <v>2:55</v>
       </c>
       <c r="H163" t="str">
-        <v>Daniel Seavey</v>
+        <v>Becky Hill</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/daniel-seavey/1646124302</v>
+        <v>https://music.apple.com/us/artist/becky-hill/533839517</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/loves-a-gun/6771897951</v>
+        <v>https://music.apple.com/us/album/more-more-more/6770600098</v>
       </c>
       <c r="L163" t="str">
-        <v>Love’s a Gun - Daniel Seavey</v>
+        <v>More! More! More! - Becky Hill</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Long Story Short</v>
+        <v>Young Again</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/long-story-short/6770700866</v>
+        <v>https://music.apple.com/us/song/young-again/1877229743</v>
       </c>
       <c r="D164" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E164" t="str">
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Long Story Short - Single</v>
+        <v>EI8HT</v>
       </c>
       <c r="G164" t="str">
-        <v>2:48</v>
+        <v>3:36</v>
       </c>
       <c r="H164" t="str">
-        <v>Knox</v>
+        <v>Shinedown</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/knox/1547519433</v>
+        <v>https://music.apple.com/us/artist/shinedown/1883858</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/long-story-short/6770700853</v>
+        <v>https://music.apple.com/us/album/young-again/1877229738</v>
       </c>
       <c r="L164" t="str">
-        <v>Long Story Short - Knox</v>
+        <v>Young Again - Shinedown</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Dior</v>
+        <v>skinny dip</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/dior/1892136721</v>
+        <v>https://music.apple.com/us/song/skinny-dip/6769856281</v>
       </c>
       <c r="D165" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E165" t="str">
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>bitknot</v>
+        <v>skinny dip - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>3:32</v>
+        <v>3:12</v>
       </c>
       <c r="H165" t="str">
-        <v>feeble little horse</v>
+        <v>almost monday</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/feeble-little-horse/1564273208</v>
+        <v>https://music.apple.com/us/artist/almost-monday/1300723925</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/dior/1892136714</v>
+        <v>https://music.apple.com/us/album/skinny-dip/6769855907</v>
       </c>
       <c r="L165" t="str">
-        <v>Dior - feeble little horse</v>
+        <v>skinny dip - almost monday</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>blue jeans</v>
+        <v>girls like girls (from the motion picture)</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/blue-jeans/6770529591</v>
+        <v>https://music.apple.com/us/song/girls-like-girls-from-the-motion-picture/1893704575</v>
       </c>
       <c r="D166" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E166" t="str">
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>blue jeans - Single</v>
+        <v>girls like girls the album</v>
       </c>
       <c r="G166" t="str">
-        <v>2:37</v>
+        <v>4:14</v>
       </c>
       <c r="H166" t="str">
-        <v>Nightly</v>
+        <v>Hayley Kiyoko</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/nightly/352310972</v>
+        <v>https://music.apple.com/us/artist/hayley-kiyoko/325569584</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/blue-jeans/6770529589</v>
+        <v>https://music.apple.com/us/album/girls-like-girls-from-the-motion-picture/1893704396</v>
       </c>
       <c r="L166" t="str">
-        <v>blue jeans - Nightly</v>
+        <v>girls like girls (from the motion picture) - Hayley Kiyoko</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Que Gacho</v>
+        <v>Better Off</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/que-gacho/6770628420</v>
+        <v>https://music.apple.com/us/song/better-off/6772045367</v>
       </c>
       <c r="D167" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E167" t="str">
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Que Gacho - Single</v>
+        <v>Stages</v>
       </c>
       <c r="G167" t="str">
-        <v>3:13</v>
+        <v>3:16</v>
       </c>
       <c r="H167" t="str">
-        <v>Luis R Conriquez</v>
+        <v>Lauren Alaina</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
+        <v>https://music.apple.com/us/artist/lauren-alaina/425028816</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/que-gacho/6770628419</v>
+        <v>https://music.apple.com/us/album/better-off/6772044978</v>
       </c>
       <c r="L167" t="str">
-        <v>Que Gacho - Luis R Conriquez</v>
+        <v>Better Off - Lauren Alaina</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>same God</v>
+        <v>Everythang Pinka (feat. Teezo Touchdown)</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/same-god/1878232616</v>
+        <v>https://music.apple.com/us/song/everythang-pinka-feat-teezo-touchdown/6772026590</v>
       </c>
       <c r="D168" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E168" t="str">
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>I HOPE THIS HELPS</v>
+        <v>Everythang Pinka (feat. Teezo Touchdown) - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>3:34</v>
+        <v>2:48</v>
       </c>
       <c r="H168" t="str">
-        <v>Alana Springsteen</v>
+        <v>Monaleo</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/alana-springsteen/1309335606</v>
+        <v>https://music.apple.com/us/artist/monaleo/1495603374</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/same-god/1878232194</v>
+        <v>https://music.apple.com/us/album/everythang-pinka-feat-teezo-touchdown/6772026586</v>
       </c>
       <c r="L168" t="str">
-        <v>same God - Alana Springsteen</v>
+        <v>Everythang Pinka (feat. Teezo Touchdown) - Monaleo</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>emotional swaggage</v>
+        <v>Lost in translation...</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/emotional-swaggage/6767397453</v>
+        <v>https://music.apple.com/us/song/lost-in-translation/1870971556</v>
       </c>
       <c r="D169" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E169" t="str">
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>IDCASH</v>
+        <v>Dream inside a dream…</v>
       </c>
       <c r="G169" t="str">
-        <v>2:12</v>
+        <v>3:30</v>
       </c>
       <c r="H169" t="str">
-        <v>IDK</v>
+        <v>R3HAB</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/idk/1578186947</v>
+        <v>https://music.apple.com/us/artist/r3hab/331900515</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/emotional-swaggage/6767397348</v>
+        <v>https://music.apple.com/us/album/lost-in-translation/1870971550</v>
       </c>
       <c r="L169" t="str">
-        <v>emotional swaggage - IDK</v>
+        <v>Lost in translation... - R3HAB</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Baby Driver</v>
+        <v>Call Security</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/baby-driver/6769152279</v>
+        <v>https://music.apple.com/us/song/call-security/6769296603</v>
       </c>
       <c r="D170" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E170" t="str">
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Baby Driver - Single</v>
+        <v>U, Me &amp; My Ego</v>
       </c>
       <c r="G170" t="str">
-        <v>3:36</v>
+        <v>3:22</v>
       </c>
       <c r="H170" t="str">
-        <v>070 Shake</v>
+        <v>Chxrry</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/070-shake/1097177293</v>
+        <v>https://music.apple.com/us/artist/chxrry/1520135642</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/baby-driver/6769152273</v>
+        <v>https://music.apple.com/us/album/call-security/6769296591</v>
       </c>
       <c r="L170" t="str">
-        <v>Baby Driver - 070 Shake</v>
+        <v>Call Security - Chxrry</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>More! More! More!</v>
+        <v>chaotic</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/more-more-more/6770600105</v>
+        <v>https://music.apple.com/us/song/chaotic/6767629281</v>
       </c>
       <c r="D171" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E171" t="str">
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>REBECCA</v>
+        <v>scars to prove it</v>
       </c>
       <c r="G171" t="str">
-        <v>2:55</v>
+        <v>3:14</v>
       </c>
       <c r="H171" t="str">
-        <v>Becky Hill</v>
+        <v>Hailey Picardi</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/becky-hill/533839517</v>
+        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/more-more-more/6770600098</v>
+        <v>https://music.apple.com/us/album/chaotic/6767626506</v>
       </c>
       <c r="L171" t="str">
-        <v>More! More! More! - Becky Hill</v>
+        <v>chaotic - Hailey Picardi</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Young Again</v>
+        <v>Keep It To Yourself</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/young-again/1877229743</v>
+        <v>https://music.apple.com/us/song/keep-it-to-yourself/6771099675</v>
       </c>
       <c r="D172" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E172" t="str">
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>EI8HT</v>
+        <v>LOVE IS THE LAW</v>
       </c>
       <c r="G172" t="str">
-        <v>3:36</v>
+        <v>4:17</v>
       </c>
       <c r="H172" t="str">
-        <v>Shinedown</v>
+        <v>Love Spells</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/shinedown/1883858</v>
+        <v>https://music.apple.com/us/artist/love-spells/1597025563</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/young-again/1877229738</v>
+        <v>https://music.apple.com/us/album/keep-it-to-yourself/6771099661</v>
       </c>
       <c r="L172" t="str">
-        <v>Young Again - Shinedown</v>
+        <v>Keep It To Yourself - Love Spells</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>skinny dip</v>
+        <v>Something to Someone</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/skinny-dip/6769856281</v>
+        <v>https://music.apple.com/us/song/something-to-someone/6767255424</v>
       </c>
       <c r="D173" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E173" t="str">
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>skinny dip - Single</v>
+        <v>Something to Someone - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>3:12</v>
+        <v>3:55</v>
       </c>
       <c r="H173" t="str">
-        <v>almost monday</v>
+        <v>Max McNown</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/almost-monday/1300723925</v>
+        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/skinny-dip/6769855907</v>
+        <v>https://music.apple.com/us/album/something-to-someone/1896445136</v>
       </c>
       <c r="L173" t="str">
-        <v>skinny dip - almost monday</v>
+        <v>Something to Someone - Max McNown</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>girls like girls (from the motion picture)</v>
+        <v>Green Screen (1pm)</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/girls-like-girls-from-the-motion-picture/1893704575</v>
+        <v>https://music.apple.com/us/song/green-screen-1pm/6766279426</v>
       </c>
       <c r="D174" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E174" t="str">
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>girls like girls the album</v>
+        <v>The Hours: High Noon</v>
       </c>
       <c r="G174" t="str">
-        <v>4:14</v>
+        <v>2:10</v>
       </c>
       <c r="H174" t="str">
-        <v>Hayley Kiyoko</v>
+        <v>Cautious Clay</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/hayley-kiyoko/325569584</v>
+        <v>https://music.apple.com/us/artist/cautious-clay/1064628701</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/girls-like-girls-from-the-motion-picture/1893704396</v>
+        <v>https://music.apple.com/us/album/green-screen-1pm/1896264236</v>
       </c>
       <c r="L174" t="str">
-        <v>girls like girls (from the motion picture) - Hayley Kiyoko</v>
+        <v>Green Screen (1pm) - Cautious Clay</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Better Off</v>
+        <v>Scoreboard</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/better-off/6772045367</v>
+        <v>https://music.apple.com/us/song/scoreboard/6767255746</v>
       </c>
       <c r="D175" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E175" t="str">
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Stages</v>
+        <v>I Just Wanna Be Loved</v>
       </c>
       <c r="G175" t="str">
-        <v>3:16</v>
+        <v>3:24</v>
       </c>
       <c r="H175" t="str">
-        <v>Lauren Alaina</v>
+        <v>Gabriella Rose</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/lauren-alaina/425028816</v>
+        <v>https://music.apple.com/us/artist/gabriella-rose/645706232</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/better-off/6772044978</v>
+        <v>https://music.apple.com/us/album/scoreboard/1896445371</v>
       </c>
       <c r="L175" t="str">
-        <v>Better Off - Lauren Alaina</v>
+        <v>Scoreboard - Gabriella Rose</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Everythang Pinka (feat. Teezo Touchdown)</v>
+        <v>High</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/everythang-pinka-feat-teezo-touchdown/6772026590</v>
+        <v>https://music.apple.com/us/song/high/6773775211</v>
       </c>
       <c r="D176" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E176" t="str">
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Everythang Pinka (feat. Teezo Touchdown) - Single</v>
+        <v>Payback Is A Dog (EP)</v>
       </c>
       <c r="G176" t="str">
-        <v>2:48</v>
+        <v>2:55</v>
       </c>
       <c r="H176" t="str">
-        <v>Monaleo</v>
+        <v>Nia Smith</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/monaleo/1495603374</v>
+        <v>https://music.apple.com/us/artist/nia-smith/1755576018</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/everythang-pinka-feat-teezo-touchdown/6772026586</v>
+        <v>https://music.apple.com/us/album/high/6773775203</v>
       </c>
       <c r="L176" t="str">
-        <v>Everythang Pinka (feat. Teezo Touchdown) - Monaleo</v>
+        <v>High - Nia Smith</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Lost in translation...</v>
+        <v>Ay Gyal</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/lost-in-translation/1870971556</v>
+        <v>https://music.apple.com/us/song/ay-gyal/6771885805</v>
       </c>
       <c r="D177" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E177" t="str">
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Dream inside a dream…</v>
+        <v>Ay Gyal - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>3:30</v>
+        <v>2:12</v>
       </c>
       <c r="H177" t="str">
-        <v>R3HAB</v>
+        <v>1Ski OG</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/r3hab/331900515</v>
+        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/lost-in-translation/1870971550</v>
+        <v>https://music.apple.com/us/album/ay-gyal/6771885803</v>
       </c>
       <c r="L177" t="str">
-        <v>Lost in translation... - R3HAB</v>
+        <v>Ay Gyal - 1Ski OG</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Call Security</v>
+        <v>always knew</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/call-security/6769296603</v>
+        <v>https://music.apple.com/us/song/always-knew/6762864274</v>
       </c>
       <c r="D178" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E178" t="str">
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>U, Me &amp; My Ego</v>
+        <v>always knew - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>3:22</v>
+        <v>3:25</v>
       </c>
       <c r="H178" t="str">
-        <v>Chxrry</v>
+        <v>Biscits</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/chxrry/1520135642</v>
+        <v>https://music.apple.com/us/artist/biscits/1185553226</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/call-security/6769296591</v>
+        <v>https://music.apple.com/us/album/always-knew/1895047928</v>
       </c>
       <c r="L178" t="str">
-        <v>Call Security - Chxrry</v>
+        <v>always knew - Biscits</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>chaotic</v>
+        <v>Cigarette Burns</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/chaotic/6767629281</v>
+        <v>https://music.apple.com/us/song/cigarette-burns/6770691000</v>
       </c>
       <c r="D179" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E179" t="str">
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>scars to prove it</v>
+        <v>Heartland Rock and Roll</v>
       </c>
       <c r="G179" t="str">
-        <v>3:14</v>
+        <v>2:41</v>
       </c>
       <c r="H179" t="str">
-        <v>Hailey Picardi</v>
+        <v>Corey Kent</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
+        <v>https://music.apple.com/us/artist/corey-kent/1171544097</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/chaotic/6767626506</v>
+        <v>https://music.apple.com/us/album/cigarette-burns/6770690867</v>
       </c>
       <c r="L179" t="str">
-        <v>chaotic - Hailey Picardi</v>
+        <v>Cigarette Burns - Corey Kent</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Keep It To Yourself</v>
+        <v>Let You Down</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/keep-it-to-yourself/6771099675</v>
+        <v>https://music.apple.com/us/song/let-you-down/6773362320</v>
       </c>
       <c r="D180" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E180" t="str">
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>LOVE IS THE LAW</v>
+        <v>El Relevo</v>
       </c>
       <c r="G180" t="str">
-        <v>4:17</v>
+        <v>4:14</v>
       </c>
       <c r="H180" t="str">
-        <v>Love Spells</v>
+        <v>Luis Figueroa</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/love-spells/1597025563</v>
+        <v>https://music.apple.com/us/artist/luis-figueroa/395266944</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/keep-it-to-yourself/6771099661</v>
+        <v>https://music.apple.com/us/album/let-you-down/6773362108</v>
       </c>
       <c r="L180" t="str">
-        <v>Keep It To Yourself - Love Spells</v>
+        <v>Let You Down - Luis Figueroa</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Something to Someone</v>
+        <v>Starless</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/something-to-someone/6767255424</v>
+        <v>https://music.apple.com/us/song/starless/6770568779</v>
       </c>
       <c r="D181" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E181" t="str">
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Something to Someone - Single</v>
+        <v>Starless - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>3:55</v>
+        <v>4:32</v>
       </c>
       <c r="H181" t="str">
-        <v>Max McNown</v>
+        <v>A Perfect Circle</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
+        <v>https://music.apple.com/us/artist/a-perfect-circle/652503</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/something-to-someone/1896445136</v>
+        <v>https://music.apple.com/us/album/starless/6770568776</v>
       </c>
       <c r="L181" t="str">
-        <v>Something to Someone - Max McNown</v>
+        <v>Starless - A Perfect Circle</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Green Screen (1pm)</v>
+        <v>Looking For You</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/green-screen-1pm/6766279426</v>
+        <v>https://music.apple.com/us/song/looking-for-you/6768355609</v>
       </c>
       <c r="D182" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E182" t="str">
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>The Hours: High Noon</v>
+        <v>Looking For You - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>2:10</v>
+        <v>3:19</v>
       </c>
       <c r="H182" t="str">
-        <v>Cautious Clay</v>
+        <v>Gable Price and Friends</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/cautious-clay/1064628701</v>
+        <v>https://music.apple.com/us/artist/gable-price-and-friends/1441378212</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/green-screen-1pm/1896264236</v>
+        <v>https://music.apple.com/us/album/looking-for-you/6768355596</v>
       </c>
       <c r="L182" t="str">
-        <v>Green Screen (1pm) - Cautious Clay</v>
+        <v>Looking For You - Gable Price and Friends</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Scoreboard</v>
+        <v>FOCUSED</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/scoreboard/6767255746</v>
+        <v>https://music.apple.com/us/song/focused/1887909237</v>
       </c>
       <c r="D183" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E183" t="str">
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>I Just Wanna Be Loved</v>
+        <v>FOCUSED - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>3:24</v>
+        <v>2:23</v>
       </c>
       <c r="H183" t="str">
-        <v>Gabriella Rose</v>
+        <v>Shepherd</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/gabriella-rose/645706232</v>
+        <v>https://music.apple.com/us/artist/shepherd/1192803216</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/scoreboard/1896445371</v>
+        <v>https://music.apple.com/us/album/focused/1887909236</v>
       </c>
       <c r="L183" t="str">
-        <v>Scoreboard - Gabriella Rose</v>
+        <v>FOCUSED - Shepherd</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>High</v>
+        <v>Tú Ni En Cuenta</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/high/6773775211</v>
+        <v>https://music.apple.com/us/song/tu-ni-en-cuenta/6767701804</v>
       </c>
       <c r="D184" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E184" t="str">
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Payback Is A Dog (EP)</v>
+        <v>Tú Ni En Cuenta - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>2:55</v>
+        <v>3:23</v>
       </c>
       <c r="H184" t="str">
-        <v>Nia Smith</v>
+        <v>Banda MS de Sergio Lizárraga</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/nia-smith/1755576018</v>
+        <v>https://music.apple.com/us/artist/banda-ms-de-sergio-liz%C3%A1rraga/413048014</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/high/6773775203</v>
+        <v>https://music.apple.com/us/album/tu-ni-en-cuenta/6767701803</v>
       </c>
       <c r="L184" t="str">
-        <v>High - Nia Smith</v>
+        <v>Tú Ni En Cuenta - Banda MS de Sergio Lizárraga</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Ay Gyal</v>
+        <v>dream state</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/ay-gyal/6771885805</v>
+        <v>https://music.apple.com/us/song/dream-state/6765596009</v>
       </c>
       <c r="D185" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E185" t="str">
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Ay Gyal - Single</v>
+        <v>dream state - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>2:12</v>
+        <v>4:01</v>
       </c>
       <c r="H185" t="str">
-        <v>1Ski OG</v>
+        <v>Martin Luke Brown</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
+        <v>https://music.apple.com/us/artist/martin-luke-brown/883292185</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/ay-gyal/6771885803</v>
+        <v>https://music.apple.com/us/album/dream-state/1896004790</v>
       </c>
       <c r="L185" t="str">
-        <v>Ay Gyal - 1Ski OG</v>
+        <v>dream state - Martin Luke Brown</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>always knew</v>
+        <v>Needle (feat. Spencer Cullum)</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/always-knew/6762864274</v>
+        <v>https://music.apple.com/us/song/needle-feat-spencer-cullum/6767618217</v>
       </c>
       <c r="D186" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E186" t="str">
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>always knew - Single</v>
+        <v>Needle (feat. Spencer Cullum) - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>3:25</v>
+        <v>3:39</v>
       </c>
       <c r="H186" t="str">
-        <v>Biscits</v>
+        <v>Mynolia</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/biscits/1185553226</v>
+        <v>https://music.apple.com/us/artist/mynolia/1444347510</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/always-knew/1895047928</v>
+        <v>https://music.apple.com/us/album/needle-feat-spencer-cullum/6767618203</v>
       </c>
       <c r="L186" t="str">
-        <v>always knew - Biscits</v>
+        <v>Needle (feat. Spencer Cullum) - Mynolia</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Cigarette Burns</v>
+        <v>You Retreat In Time And Space</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/cigarette-burns/6770691000</v>
+        <v>https://music.apple.com/us/song/you-retreat-in-time-and-space/1890015660</v>
       </c>
       <c r="D187" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E187" t="str">
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Heartland Rock and Roll</v>
+        <v>Inferno</v>
       </c>
       <c r="G187" t="str">
-        <v>2:41</v>
+        <v>5:25</v>
       </c>
       <c r="H187" t="str">
-        <v>Corey Kent</v>
+        <v>Boards of Canada</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/corey-kent/1171544097</v>
+        <v>https://music.apple.com/us/artist/boards-of-canada/2989314</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/cigarette-burns/6770690867</v>
+        <v>https://music.apple.com/us/album/you-retreat-in-time-and-space/1890015523</v>
       </c>
       <c r="L187" t="str">
-        <v>Cigarette Burns - Corey Kent</v>
+        <v>You Retreat In Time And Space - Boards of Canada</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Let You Down</v>
+        <v>It's Happening (To Me)</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/let-you-down/6773362320</v>
+        <v>https://music.apple.com/us/song/its-happening-to-me/6764723461</v>
       </c>
       <c r="D188" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E188" t="str">
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>El Relevo</v>
+        <v>It's Happening (To Me) - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>4:14</v>
+        <v>2:34</v>
       </c>
       <c r="H188" t="str">
-        <v>Luis Figueroa</v>
+        <v>Delroy Edwards</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/luis-figueroa/395266944</v>
+        <v>https://music.apple.com/us/artist/delroy-edwards/591790909</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/let-you-down/6773362108</v>
+        <v>https://music.apple.com/us/album/its-happening-to-me/1895893472</v>
       </c>
       <c r="L188" t="str">
-        <v>Let You Down - Luis Figueroa</v>
+        <v>It's Happening (To Me) - Delroy Edwards</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Starless</v>
+        <v>FCUK</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/starless/6770568779</v>
+        <v>https://music.apple.com/us/song/fcuk/6769623577</v>
       </c>
       <c r="D189" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E189" t="str">
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Starless - Single</v>
+        <v>FCUK - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>4:32</v>
+        <v>2:22</v>
       </c>
       <c r="H189" t="str">
-        <v>A Perfect Circle</v>
+        <v>H.LLS</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/a-perfect-circle/652503</v>
+        <v>https://music.apple.com/us/artist/h-lls/1751287958</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/starless/6770568776</v>
+        <v>https://music.apple.com/us/album/fcuk/6769623566</v>
       </c>
       <c r="L189" t="str">
-        <v>Starless - A Perfect Circle</v>
+        <v>FCUK - H.LLS</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Looking For You</v>
+        <v>Higher</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/looking-for-you/6768355609</v>
+        <v>https://music.apple.com/us/song/higher/1880124200</v>
       </c>
       <c r="D190" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E190" t="str">
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Looking For You - Single</v>
+        <v>Run, Run Pure Beauty</v>
       </c>
       <c r="G190" t="str">
-        <v>3:19</v>
+        <v>4:06</v>
       </c>
       <c r="H190" t="str">
-        <v>Gable Price and Friends</v>
+        <v>Francis of Delirium</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/gable-price-and-friends/1441378212</v>
+        <v>https://music.apple.com/us/artist/francis-of-delirium/1485902996</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/looking-for-you/6768355596</v>
+        <v>https://music.apple.com/us/album/higher/1880123731</v>
       </c>
       <c r="L190" t="str">
-        <v>Looking For You - Gable Price and Friends</v>
+        <v>Higher - Francis of Delirium</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>FOCUSED</v>
+        <v>B.U.N</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/focused/1887909237</v>
+        <v>https://music.apple.com/us/song/b-u-n/6763272338</v>
       </c>
       <c r="D191" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E191" t="str">
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>FOCUSED - Single</v>
+        <v>B.U.N - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>2:23</v>
+        <v>3:43</v>
       </c>
       <c r="H191" t="str">
-        <v>Shepherd</v>
+        <v>Roll Deep</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/shepherd/1192803216</v>
+        <v>https://music.apple.com/us/artist/roll-deep/3083873</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/focused/1887909236</v>
+        <v>https://music.apple.com/us/album/b-u-n/1895242397</v>
       </c>
       <c r="L191" t="str">
-        <v>FOCUSED - Shepherd</v>
+        <v>B.U.N - Roll Deep</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Tú Ni En Cuenta</v>
+        <v>Only Love (feat. Pa Salieu)</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/tu-ni-en-cuenta/6767701804</v>
+        <v>https://music.apple.com/us/song/only-love-feat-pa-salieu/6767014290</v>
       </c>
       <c r="D192" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E192" t="str">
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Tú Ni En Cuenta - Single</v>
+        <v>Here Because of Hope</v>
       </c>
       <c r="G192" t="str">
-        <v>3:23</v>
+        <v>3:22</v>
       </c>
       <c r="H192" t="str">
-        <v>Banda MS de Sergio Lizárraga</v>
+        <v>Ezra Collective</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/banda-ms-de-sergio-liz%C3%A1rraga/413048014</v>
+        <v>https://music.apple.com/us/artist/ezra-collective/1103640281</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/tu-ni-en-cuenta/6767701803</v>
+        <v>https://music.apple.com/us/album/only-love-feat-pa-salieu/6767014278</v>
       </c>
       <c r="L192" t="str">
-        <v>Tú Ni En Cuenta - Banda MS de Sergio Lizárraga</v>
+        <v>Only Love (feat. Pa Salieu) - Ezra Collective</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>dream state</v>
+        <v>Beautiful Things 1st scene/audition</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/dream-state/6765596009</v>
+        <v>https://music.apple.com/us/song/beautiful-things-1st-scene-audition/6771942631</v>
       </c>
       <c r="D193" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E193" t="str">
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>dream state - Single</v>
+        <v>UNDRA</v>
       </c>
       <c r="G193" t="str">
-        <v>4:01</v>
+        <v>2:49</v>
       </c>
       <c r="H193" t="str">
-        <v>Martin Luke Brown</v>
+        <v>reggie</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/martin-luke-brown/883292185</v>
+        <v>https://music.apple.com/us/artist/reggie/1526587068</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/dream-state/1896004790</v>
+        <v>https://music.apple.com/us/album/beautiful-things-1st-scene-audition/6771942630</v>
       </c>
       <c r="L193" t="str">
-        <v>dream state - Martin Luke Brown</v>
+        <v>Beautiful Things 1st scene/audition - reggie</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Needle (feat. Spencer Cullum)</v>
+        <v>HEAVEN'S ON FIRE</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/needle-feat-spencer-cullum/6767618217</v>
+        <v>https://music.apple.com/us/song/heavens-on-fire/6771110730</v>
       </c>
       <c r="D194" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E194" t="str">
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Needle (feat. Spencer Cullum) - Single</v>
+        <v>HEAVEN'S ON FIRE</v>
       </c>
       <c r="G194" t="str">
-        <v>3:39</v>
+        <v>2:54</v>
       </c>
       <c r="H194" t="str">
-        <v>Mynolia</v>
+        <v>Johnny Huynh</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/mynolia/1444347510</v>
+        <v>https://music.apple.com/us/artist/johnny-huynh/1708540956</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/needle-feat-spencer-cullum/6767618203</v>
+        <v>https://music.apple.com/us/album/heavens-on-fire/6771110729</v>
       </c>
       <c r="L194" t="str">
-        <v>Needle (feat. Spencer Cullum) - Mynolia</v>
+        <v>HEAVEN'S ON FIRE - Johnny Huynh</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>You Retreat In Time And Space</v>
+        <v>Fallen Angel</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/you-retreat-in-time-and-space/1890015660</v>
+        <v>https://music.apple.com/us/song/fallen-angel/6771161222</v>
       </c>
       <c r="D195" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E195" t="str">
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Inferno</v>
+        <v>You Don't Know My Name</v>
       </c>
       <c r="G195" t="str">
-        <v>5:25</v>
+        <v>3:05</v>
       </c>
       <c r="H195" t="str">
-        <v>Boards of Canada</v>
+        <v>Baby J</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/boards-of-canada/2989314</v>
+        <v>https://music.apple.com/us/artist/baby-j/1513690931</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/you-retreat-in-time-and-space/1890015523</v>
+        <v>https://music.apple.com/us/album/fallen-angel/6771161180</v>
       </c>
       <c r="L195" t="str">
-        <v>You Retreat In Time And Space - Boards of Canada</v>
+        <v>Fallen Angel - Baby J</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>It's Happening (To Me)</v>
+        <v>The Last Encounter</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/its-happening-to-me/6764723461</v>
+        <v>https://music.apple.com/us/song/the-last-encounter/6767395134</v>
       </c>
       <c r="D196" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E196" t="str">
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>It's Happening (To Me) - Single</v>
+        <v>The Last Encounter - Single</v>
       </c>
       <c r="G196" t="str">
-        <v>2:34</v>
+        <v>3:04</v>
       </c>
       <c r="H196" t="str">
-        <v>Delroy Edwards</v>
+        <v>Sofia Camara</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/delroy-edwards/591790909</v>
+        <v>https://music.apple.com/us/artist/sofia-camara/1506432156</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/its-happening-to-me/1895893472</v>
+        <v>https://music.apple.com/us/album/the-last-encounter/6767395133</v>
       </c>
       <c r="L196" t="str">
-        <v>It's Happening (To Me) - Delroy Edwards</v>
+        <v>The Last Encounter - Sofia Camara</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>FCUK</v>
+        <v>we fall</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/fcuk/6769623577</v>
+        <v>https://music.apple.com/us/song/we-fall/6769218917</v>
       </c>
       <c r="D197" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E197" t="str">
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>FCUK - Single</v>
+        <v>we fall - Single</v>
       </c>
       <c r="G197" t="str">
-        <v>2:22</v>
+        <v>4:01</v>
       </c>
       <c r="H197" t="str">
-        <v>H.LLS</v>
+        <v>MOIO</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/h-lls/1751287958</v>
+        <v>https://music.apple.com/us/artist/moio/1664183608</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/fcuk/6769623566</v>
+        <v>https://music.apple.com/us/album/we-fall/6769218915</v>
       </c>
       <c r="L197" t="str">
-        <v>FCUK - H.LLS</v>
+        <v>we fall - MOIO</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Higher</v>
+        <v>You Don't Know Me</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/higher/1880124200</v>
+        <v>https://music.apple.com/us/song/you-dont-know-me/6769214417</v>
       </c>
       <c r="D198" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E198" t="str">
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Run, Run Pure Beauty</v>
+        <v>You Don’t Know Me - Single</v>
       </c>
       <c r="G198" t="str">
-        <v>4:06</v>
+        <v>3:50</v>
       </c>
       <c r="H198" t="str">
-        <v>Francis of Delirium</v>
+        <v>Isabel Dumaa</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/francis-of-delirium/1485902996</v>
+        <v>https://music.apple.com/us/artist/isabel-dumaa/1631481156</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/higher/1880123731</v>
+        <v>https://music.apple.com/us/album/you-dont-know-me/6769214410</v>
       </c>
       <c r="L198" t="str">
-        <v>Higher - Francis of Delirium</v>
+        <v>You Don't Know Me - Isabel Dumaa</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>B.U.N</v>
+        <v>Hold Up, Say What?</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/b-u-n/6763272338</v>
+        <v>https://music.apple.com/us/song/hold-up-say-what/1879853511</v>
       </c>
       <c r="D199" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E199" t="str">
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>B.U.N - Single</v>
+        <v>House Of Mirrors</v>
       </c>
       <c r="G199" t="str">
-        <v>3:43</v>
+        <v>4:04</v>
       </c>
       <c r="H199" t="str">
-        <v>Roll Deep</v>
+        <v>All Them Witches</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/roll-deep/3083873</v>
+        <v>https://music.apple.com/us/artist/all-them-witches/534924603</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/b-u-n/1895242397</v>
+        <v>https://music.apple.com/us/album/hold-up-say-what/1879853502</v>
       </c>
       <c r="L199" t="str">
-        <v>B.U.N - Roll Deep</v>
+        <v>Hold Up, Say What? - All Them Witches</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Only Love (feat. Pa Salieu)</v>
+        <v>Iodine</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/only-love-feat-pa-salieu/6767014290</v>
+        <v>https://music.apple.com/us/song/iodine/1871211805</v>
       </c>
       <c r="D200" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E200" t="str">
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>Here Because of Hope</v>
+        <v>Neverending</v>
       </c>
       <c r="G200" t="str">
-        <v>3:22</v>
+        <v>3:40</v>
       </c>
       <c r="H200" t="str">
-        <v>Ezra Collective</v>
+        <v>Monolord</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/ezra-collective/1103640281</v>
+        <v>https://music.apple.com/us/artist/monolord/833749384</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/only-love-feat-pa-salieu/6767014278</v>
+        <v>https://music.apple.com/us/album/iodine/1871211801</v>
       </c>
       <c r="L200" t="str">
-        <v>Only Love (feat. Pa Salieu) - Ezra Collective</v>
+        <v>Iodine - Monolord</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Beautiful Things 1st scene/audition</v>
+        <v>I Speak Forgotten Voices</v>
       </c>
       <c r="B201" t="str">
         <v/>
       </c>
       <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/beautiful-things-1st-scene-audition/6771942631</v>
+        <v>https://music.apple.com/us/song/i-speak-forgotten-voices/1878083625</v>
       </c>
       <c r="D201" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E201" t="str">
         <v/>
       </c>
       <c r="F201" t="str">
-        <v>UNDRA</v>
+        <v>...By the Word...</v>
       </c>
       <c r="G201" t="str">
-        <v>2:49</v>
+        <v>5:01</v>
       </c>
       <c r="H201" t="str">
-        <v>reggie</v>
+        <v>Trelldom</v>
       </c>
       <c r="I201" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/reggie/1526587068</v>
+        <v>https://music.apple.com/us/artist/trelldom/256586618</v>
       </c>
       <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/beautiful-things-1st-scene-audition/6771942630</v>
+        <v>https://music.apple.com/us/album/i-speak-forgotten-voices/1878083622</v>
       </c>
       <c r="L201" t="str">
-        <v>Beautiful Things 1st scene/audition - reggie</v>
+        <v>I Speak Forgotten Voices - Trelldom</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>HEAVEN'S ON FIRE</v>
+        <v>Rats in the Temple</v>
       </c>
       <c r="B202" t="str">
         <v/>
       </c>
       <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/heavens-on-fire/6771110730</v>
+        <v>https://music.apple.com/us/song/rats-in-the-temple/6764627559</v>
       </c>
       <c r="D202" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E202" t="str">
         <v/>
       </c>
       <c r="F202" t="str">
-        <v>HEAVEN'S ON FIRE</v>
+        <v>Rats in the Temple</v>
       </c>
       <c r="G202" t="str">
-        <v>2:54</v>
+        <v>4:45</v>
       </c>
       <c r="H202" t="str">
-        <v>Johnny Huynh</v>
+        <v>Flotsam and Jetsam</v>
       </c>
       <c r="I202" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/johnny-huynh/1708540956</v>
+        <v>https://music.apple.com/us/artist/flotsam-and-jetsam/162270</v>
       </c>
       <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/heavens-on-fire/6771110729</v>
+        <v>https://music.apple.com/us/album/rats-in-the-temple/1895855647</v>
       </c>
       <c r="L202" t="str">
-        <v>HEAVEN'S ON FIRE - Johnny Huynh</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="str">
-        <v>Fallen Angel</v>
-      </c>
-      <c r="B203" t="str">
-        <v/>
-      </c>
-      <c r="C203" t="str">
-        <v>https://music.apple.com/us/song/fallen-angel/6771161222</v>
-      </c>
-      <c r="D203" t="str">
-        <v>2026-06-01</v>
-      </c>
-      <c r="E203" t="str">
-        <v/>
-      </c>
-      <c r="F203" t="str">
-        <v>You Don't Know My Name</v>
-      </c>
-      <c r="G203" t="str">
-        <v>3:05</v>
-      </c>
-      <c r="H203" t="str">
-        <v>Baby J</v>
-      </c>
-      <c r="I203" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J203" t="str">
-        <v>https://music.apple.com/us/artist/baby-j/1513690931</v>
-      </c>
-      <c r="K203" t="str">
-        <v>https://music.apple.com/us/album/fallen-angel/6771161180</v>
-      </c>
-      <c r="L203" t="str">
-        <v>Fallen Angel - Baby J</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="str">
-        <v>The Last Encounter</v>
-      </c>
-      <c r="B204" t="str">
-        <v/>
-      </c>
-      <c r="C204" t="str">
-        <v>https://music.apple.com/us/song/the-last-encounter/6767395134</v>
-      </c>
-      <c r="D204" t="str">
-        <v>2026-06-01</v>
-      </c>
-      <c r="E204" t="str">
-        <v/>
-      </c>
-      <c r="F204" t="str">
-        <v>The Last Encounter - Single</v>
-      </c>
-      <c r="G204" t="str">
-        <v>3:04</v>
-      </c>
-      <c r="H204" t="str">
-        <v>Sofia Camara</v>
-      </c>
-      <c r="I204" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J204" t="str">
-        <v>https://music.apple.com/us/artist/sofia-camara/1506432156</v>
-      </c>
-      <c r="K204" t="str">
-        <v>https://music.apple.com/us/album/the-last-encounter/6767395133</v>
-      </c>
-      <c r="L204" t="str">
-        <v>The Last Encounter - Sofia Camara</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="str">
-        <v>we fall</v>
-      </c>
-      <c r="B205" t="str">
-        <v/>
-      </c>
-      <c r="C205" t="str">
-        <v>https://music.apple.com/us/song/we-fall/6769218917</v>
-      </c>
-      <c r="D205" t="str">
-        <v>2026-06-01</v>
-      </c>
-      <c r="E205" t="str">
-        <v/>
-      </c>
-      <c r="F205" t="str">
-        <v>we fall - Single</v>
-      </c>
-      <c r="G205" t="str">
-        <v>4:01</v>
-      </c>
-      <c r="H205" t="str">
-        <v>MOIO</v>
-      </c>
-      <c r="I205" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J205" t="str">
-        <v>https://music.apple.com/us/artist/moio/1664183608</v>
-      </c>
-      <c r="K205" t="str">
-        <v>https://music.apple.com/us/album/we-fall/6769218915</v>
-      </c>
-      <c r="L205" t="str">
-        <v>we fall - MOIO</v>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="str">
-        <v>You Don't Know Me</v>
-      </c>
-      <c r="B206" t="str">
-        <v/>
-      </c>
-      <c r="C206" t="str">
-        <v>https://music.apple.com/us/song/you-dont-know-me/6769214417</v>
-      </c>
-      <c r="D206" t="str">
-        <v>2026-06-01</v>
-      </c>
-      <c r="E206" t="str">
-        <v/>
-      </c>
-      <c r="F206" t="str">
-        <v>You Don’t Know Me - Single</v>
-      </c>
-      <c r="G206" t="str">
-        <v>3:50</v>
-      </c>
-      <c r="H206" t="str">
-        <v>Isabel Dumaa</v>
-      </c>
-      <c r="I206" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J206" t="str">
-        <v>https://music.apple.com/us/artist/isabel-dumaa/1631481156</v>
-      </c>
-      <c r="K206" t="str">
-        <v>https://music.apple.com/us/album/you-dont-know-me/6769214410</v>
-      </c>
-      <c r="L206" t="str">
-        <v>You Don't Know Me - Isabel Dumaa</v>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="str">
-        <v>Hold Up, Say What?</v>
-      </c>
-      <c r="B207" t="str">
-        <v/>
-      </c>
-      <c r="C207" t="str">
-        <v>https://music.apple.com/us/song/hold-up-say-what/1879853511</v>
-      </c>
-      <c r="D207" t="str">
-        <v>2026-06-01</v>
-      </c>
-      <c r="E207" t="str">
-        <v/>
-      </c>
-      <c r="F207" t="str">
-        <v>House Of Mirrors</v>
-      </c>
-      <c r="G207" t="str">
-        <v>4:04</v>
-      </c>
-      <c r="H207" t="str">
-        <v>All Them Witches</v>
-      </c>
-      <c r="I207" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J207" t="str">
-        <v>https://music.apple.com/us/artist/all-them-witches/534924603</v>
-      </c>
-      <c r="K207" t="str">
-        <v>https://music.apple.com/us/album/hold-up-say-what/1879853502</v>
-      </c>
-      <c r="L207" t="str">
-        <v>Hold Up, Say What? - All Them Witches</v>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="str">
-        <v>Iodine</v>
-      </c>
-      <c r="B208" t="str">
-        <v/>
-      </c>
-      <c r="C208" t="str">
-        <v>https://music.apple.com/us/song/iodine/1871211805</v>
-      </c>
-      <c r="D208" t="str">
-        <v>2026-06-01</v>
-      </c>
-      <c r="E208" t="str">
-        <v/>
-      </c>
-      <c r="F208" t="str">
-        <v>Neverending</v>
-      </c>
-      <c r="G208" t="str">
-        <v>3:40</v>
-      </c>
-      <c r="H208" t="str">
-        <v>Monolord</v>
-      </c>
-      <c r="I208" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J208" t="str">
-        <v>https://music.apple.com/us/artist/monolord/833749384</v>
-      </c>
-      <c r="K208" t="str">
-        <v>https://music.apple.com/us/album/iodine/1871211801</v>
-      </c>
-      <c r="L208" t="str">
-        <v>Iodine - Monolord</v>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="str">
-        <v>I Speak Forgotten Voices</v>
-      </c>
-      <c r="B209" t="str">
-        <v/>
-      </c>
-      <c r="C209" t="str">
-        <v>https://music.apple.com/us/song/i-speak-forgotten-voices/1878083625</v>
-      </c>
-      <c r="D209" t="str">
-        <v>2026-06-01</v>
-      </c>
-      <c r="E209" t="str">
-        <v/>
-      </c>
-      <c r="F209" t="str">
-        <v>...By the Word...</v>
-      </c>
-      <c r="G209" t="str">
-        <v>5:01</v>
-      </c>
-      <c r="H209" t="str">
-        <v>Trelldom</v>
-      </c>
-      <c r="I209" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J209" t="str">
-        <v>https://music.apple.com/us/artist/trelldom/256586618</v>
-      </c>
-      <c r="K209" t="str">
-        <v>https://music.apple.com/us/album/i-speak-forgotten-voices/1878083622</v>
-      </c>
-      <c r="L209" t="str">
-        <v>I Speak Forgotten Voices - Trelldom</v>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="str">
-        <v>Rats in the Temple</v>
-      </c>
-      <c r="B210" t="str">
-        <v/>
-      </c>
-      <c r="C210" t="str">
-        <v>https://music.apple.com/us/song/rats-in-the-temple/6764627559</v>
-      </c>
-      <c r="D210" t="str">
-        <v>2026-06-01</v>
-      </c>
-      <c r="E210" t="str">
-        <v/>
-      </c>
-      <c r="F210" t="str">
-        <v>Rats in the Temple</v>
-      </c>
-      <c r="G210" t="str">
-        <v>4:45</v>
-      </c>
-      <c r="H210" t="str">
-        <v>Flotsam and Jetsam</v>
-      </c>
-      <c r="I210" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J210" t="str">
-        <v>https://music.apple.com/us/artist/flotsam-and-jetsam/162270</v>
-      </c>
-      <c r="K210" t="str">
-        <v>https://music.apple.com/us/album/rats-in-the-temple/1895855647</v>
-      </c>
-      <c r="L210" t="str">
         <v>Rats in the Temple - Flotsam and Jetsam</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L210"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L202"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-06-week01/titles.xlsx
+++ b/data/global/2026-06-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L202"/>
+  <dimension ref="A1:L220"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שמעון בוסקילה – עולם יפה</v>
+        <v>סטטיק &amp; רינת בר - אקסטרה לארג'</v>
       </c>
       <c r="B2" t="str">
         <v>2026-06-02</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a9%d7%9e%d7%a2%d7%95%d7%9f-%d7%91%d7%95%d7%a1%d7%a7%d7%99%d7%9c%d7%94-%d7%a2%d7%95%d7%9c%d7%9d-%d7%99%d7%a4%d7%94/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411179&amp;sid=13e1d521681219f1f5cc74f85473f139</v>
       </c>
       <c r="D2" t="str">
         <v>2026-06-02</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>"עולם יפה" של שמעון בוסקילה מצליח לחבר בין כאב קולקטיבי לבין פופ נגיש מאוד. לכאורה מדובר בשיר פשוט למדי, אבל הפשטות היא חלק מרכזי מהאפקט שלו. השיר בנוי על שני צירים מנוגדים: כאב, געגוע ושבר, ומנגד תקווה, התמדה ובחירה בחיים.</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שמעון בוסקילה – עולם יפה</v>
+        <v>סטטיק &amp; רינת בר - אקסטרה לארג'</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>מירי מסיקה שרה את "לב לבן" של שולי רנד</v>
+        <v>רועי מזוז &amp; שילה בן אברהם - הסיפור של ג'וני</v>
       </c>
       <c r="B3" t="str">
         <v>2026-06-02</v>
       </c>
       <c r="C3" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%99%d7%a8%d7%99-%d7%9e%d7%a1%d7%99%d7%a7%d7%94-%d7%a9%d7%a8%d7%94-%d7%90%d7%aa-%d7%9c%d7%91-%d7%9c%d7%91%d7%9f-%d7%a9%d7%9c-%d7%a9%d7%95%d7%9c%d7%99-%d7%a8%d7%a0%d7%93/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411178&amp;sid=13e1d521681219f1f5cc74f85473f139</v>
       </c>
       <c r="D3" t="str">
         <v>2026-06-02</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>שיאה של עונת החתונות בפתח. זה הזמן לקדם ללב הפלייליסט של שירי החתונה  את "לב לבן" של שולי רנד. את היוזמה ה"מסחרית" הזו לקחה לידיה מירי מסיקה בגרסה לשיר בעיבוד אורי זך. השיר "לב לבן" של  הפך תוך חודשים ספורים</v>
+        <v/>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>מירי מסיקה שרה את "לב לבן" של שולי רנד</v>
+        <v>רועי מזוז &amp; שילה בן אברהם - הסיפור של ג'וני</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Dua Lipa - Physical (Live From Mexico)</v>
+        <v>עופר סופר - טוב ומטיב</v>
       </c>
       <c r="B4" t="str">
-        <v>4d ago</v>
+        <v>2026-06-02</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=xZAe-d3bXTs</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411177&amp;sid=13e1d521681219f1f5cc74f85473f139</v>
       </c>
       <c r="D4" t="str">
         <v>2026-06-02</v>
@@ -527,16 +527,16 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>4d ago</v>
+        <v/>
       </c>
       <c r="G4" t="str">
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>Dua Lipa</v>
+        <v/>
       </c>
       <c r="I4" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Dua Lipa - Physical (Live From Mexico) - Dua Lipa</v>
+        <v>עופר סופר - טוב ומטיב</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Dagny - Rain (Lyric Video)</v>
+        <v>משינה - כמעט וכאילו</v>
       </c>
       <c r="B5" t="str">
-        <v>4d ago</v>
+        <v>2026-06-02</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=j3ZJwczZoUQ</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411176&amp;sid=13e1d521681219f1f5cc74f85473f139</v>
       </c>
       <c r="D5" t="str">
         <v>2026-06-02</v>
@@ -565,16 +565,16 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>4d ago</v>
+        <v/>
       </c>
       <c r="G5" t="str">
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>Dagny</v>
+        <v/>
       </c>
       <c r="I5" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Dagny - Rain (Lyric Video) - Dagny</v>
+        <v>משינה - כמעט וכאילו</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Modern Talking - Cheri Cheri Lady (Auf los geht's los, 14.09.1985)</v>
+        <v>מיכאל כורש - שלוש בלילה</v>
       </c>
       <c r="B6" t="str">
-        <v>4d ago</v>
+        <v>2026-06-02</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=c0LtTVKNwNA</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411175&amp;sid=13e1d521681219f1f5cc74f85473f139</v>
       </c>
       <c r="D6" t="str">
         <v>2026-06-02</v>
@@ -603,16 +603,16 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>4d ago</v>
+        <v/>
       </c>
       <c r="G6" t="str">
         <v/>
       </c>
       <c r="H6" t="str">
-        <v>Modern Talking Offiziell</v>
+        <v/>
       </c>
       <c r="I6" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Modern Talking - Cheri Cheri Lady (Auf los geht's los, 14.09.1985) - Modern Talking Offiziell</v>
+        <v>מיכאל כורש - שלוש בלילה</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>The Chemical Brothers - Go (Live Show Visual)</v>
+        <v>יובל לוי מארחת את דין פרינס גבאי - פאקים</v>
       </c>
       <c r="B7" t="str">
-        <v>4d ago</v>
+        <v>2026-06-02</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=fHCIchBq8CM</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411174&amp;sid=13e1d521681219f1f5cc74f85473f139</v>
       </c>
       <c r="D7" t="str">
         <v>2026-06-02</v>
@@ -641,16 +641,16 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>4d ago</v>
+        <v/>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>The Chemical Brothers</v>
+        <v/>
       </c>
       <c r="I7" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J7" t="str">
         <v/>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>The Chemical Brothers - Go (Live Show Visual) - The Chemical Brothers</v>
+        <v>יובל לוי מארחת את דין פרינס גבאי - פאקים</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Jonas Blue - Girl (Official Lyric Video)</v>
+        <v>יובל לוי - החיה</v>
       </c>
       <c r="B8" t="str">
-        <v>4d ago</v>
+        <v>2026-06-02</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=FTUe3jzUqXU</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411173&amp;sid=13e1d521681219f1f5cc74f85473f139</v>
       </c>
       <c r="D8" t="str">
         <v>2026-06-02</v>
@@ -679,16 +679,16 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>4d ago</v>
+        <v/>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>Defected Records and Jonas Blue</v>
+        <v/>
       </c>
       <c r="I8" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Jonas Blue - Girl (Official Lyric Video) - Defected Records and Jonas Blue</v>
+        <v>יובל לוי - החיה</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Dogpark - Don't Lie (Visualizer)</v>
+        <v>שניאור אוראל - שערי שמים פתח</v>
       </c>
       <c r="B9" t="str">
-        <v>4d ago</v>
+        <v>2026-06-02</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=is7qKBRycJI</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411172&amp;sid=13e1d521681219f1f5cc74f85473f139</v>
       </c>
       <c r="D9" t="str">
         <v>2026-06-02</v>
@@ -717,16 +717,16 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>4d ago</v>
+        <v/>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>Dogpark</v>
+        <v/>
       </c>
       <c r="I9" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J9" t="str">
         <v/>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Dogpark - Don't Lie (Visualizer) - Dogpark</v>
+        <v>שניאור אוראל - שערי שמים פתח</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>elijah woods - L-O-V-E (Treehouse Sessions)</v>
+        <v>מתנאל אסייג - תדר</v>
       </c>
       <c r="B10" t="str">
-        <v>4d ago</v>
+        <v>2026-06-02</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=q5kN7eH6rgo</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411171&amp;sid=13e1d521681219f1f5cc74f85473f139</v>
       </c>
       <c r="D10" t="str">
         <v>2026-06-02</v>
@@ -755,16 +755,16 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>4d ago</v>
+        <v/>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>elijah woods</v>
+        <v/>
       </c>
       <c r="I10" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J10" t="str">
         <v/>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>elijah woods - L-O-V-E (Treehouse Sessions) - elijah woods</v>
+        <v>מתנאל אסייג - תדר</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Lauren Alaina - Better Off (Official Audio)</v>
+        <v>ליאל אוחיון - היית גבר</v>
       </c>
       <c r="B11" t="str">
-        <v>4d ago</v>
+        <v>2026-06-02</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=Vj-ong3XNHM</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411170&amp;sid=13e1d521681219f1f5cc74f85473f139</v>
       </c>
       <c r="D11" t="str">
         <v>2026-06-02</v>
@@ -793,16 +793,16 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>4d ago</v>
+        <v/>
       </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>Lauren Alaina</v>
+        <v/>
       </c>
       <c r="I11" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J11" t="str">
         <v/>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Lauren Alaina - Better Off (Official Audio) - Lauren Alaina</v>
+        <v>ליאל אוחיון - היית גבר</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Lauren Sanderson - ARE YOU REALLY HERE? (Lyric Video)</v>
+        <v>ישראל ברששת - מחרוזת מהנשמה 2026</v>
       </c>
       <c r="B12" t="str">
-        <v>4d ago</v>
+        <v>2026-06-02</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=u7Et_hbMZUA</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411169&amp;sid=13e1d521681219f1f5cc74f85473f139</v>
       </c>
       <c r="D12" t="str">
         <v>2026-06-02</v>
@@ -831,16 +831,16 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>4d ago</v>
+        <v/>
       </c>
       <c r="G12" t="str">
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>Lauren Sanderson</v>
+        <v/>
       </c>
       <c r="I12" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J12" t="str">
         <v/>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Lauren Sanderson - ARE YOU REALLY HERE? (Lyric Video) - Lauren Sanderson</v>
+        <v>ישראל ברששת - מחרוזת מהנשמה 2026</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Nightly – blue jeans (Official Lyric Video)</v>
+        <v>ישעיהו - תשמור חזק</v>
       </c>
       <c r="B13" t="str">
-        <v>4d ago</v>
+        <v>2026-06-02</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=LnA3xkXUwaM</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411168&amp;sid=13e1d521681219f1f5cc74f85473f139</v>
       </c>
       <c r="D13" t="str">
         <v>2026-06-02</v>
@@ -869,16 +869,16 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>4d ago</v>
+        <v/>
       </c>
       <c r="G13" t="str">
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>NIGHTLY</v>
+        <v/>
       </c>
       <c r="I13" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J13" t="str">
         <v/>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Nightly – blue jeans (Official Lyric Video) - NIGHTLY</v>
+        <v>ישעיהו - תשמור חזק</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Dasha - Mad About It (Official Visualizer)</v>
+        <v>יוסף חיים - איש שחולם געגוע</v>
       </c>
       <c r="B14" t="str">
-        <v>4d ago</v>
+        <v>2026-06-02</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=Ae1gf_7p3H8</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411167&amp;sid=13e1d521681219f1f5cc74f85473f139</v>
       </c>
       <c r="D14" t="str">
         <v>2026-06-02</v>
@@ -907,16 +907,16 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>4d ago</v>
+        <v/>
       </c>
       <c r="G14" t="str">
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>Dasha</v>
+        <v/>
       </c>
       <c r="I14" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J14" t="str">
         <v/>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Dasha - Mad About It (Official Visualizer) - Dasha</v>
+        <v>יוסף חיים - איש שחולם געגוע</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Ariana Grande - hate that i made you love me (official lyric video)</v>
+        <v>יהונתן ישראל - רק לעלות</v>
       </c>
       <c r="B15" t="str">
-        <v>4d ago</v>
+        <v>2026-06-02</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=v1t4MTqdfyI</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411166&amp;sid=13e1d521681219f1f5cc74f85473f139</v>
       </c>
       <c r="D15" t="str">
         <v>2026-06-02</v>
@@ -945,16 +945,16 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>4d ago</v>
+        <v/>
       </c>
       <c r="G15" t="str">
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>Ariana Grande</v>
+        <v/>
       </c>
       <c r="I15" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J15" t="str">
         <v/>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Ariana Grande - hate that i made you love me (official lyric video) - Ariana Grande</v>
+        <v>יהונתן ישראל - רק לעלות</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Max McNown - Something To Someone (Performance Video)</v>
+        <v>חן כהן - תל גיבורים</v>
       </c>
       <c r="B16" t="str">
-        <v>4d ago</v>
+        <v>2026-06-02</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=4Ki4ejT86YM</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411165&amp;sid=13e1d521681219f1f5cc74f85473f139</v>
       </c>
       <c r="D16" t="str">
         <v>2026-06-02</v>
@@ -983,16 +983,16 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>4d ago</v>
+        <v/>
       </c>
       <c r="G16" t="str">
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>Max McNown</v>
+        <v/>
       </c>
       <c r="I16" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J16" t="str">
         <v/>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Max McNown - Something To Someone (Performance Video) - Max McNown</v>
+        <v>חן כהן - תל גיבורים</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Bebe Rexha &amp; David Guetta - Sad Girls (Official Visual)</v>
+        <v>הייפ קרו - אהבה עיוורת</v>
       </c>
       <c r="B17" t="str">
-        <v>4d ago</v>
+        <v>2026-06-02</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=P8UqZ5IF-QE</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411164&amp;sid=13e1d521681219f1f5cc74f85473f139</v>
       </c>
       <c r="D17" t="str">
         <v>2026-06-02</v>
@@ -1021,16 +1021,16 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>4d ago</v>
+        <v/>
       </c>
       <c r="G17" t="str">
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>Bebe Rexha</v>
+        <v/>
       </c>
       <c r="I17" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J17" t="str">
         <v/>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Bebe Rexha &amp; David Guetta - Sad Girls (Official Visual) - Bebe Rexha</v>
+        <v>הייפ קרו - אהבה עיוורת</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Knox - Long Story Short (Official Video)</v>
+        <v>אלינור חלילוב - מחרוזת קיץ 2026</v>
       </c>
       <c r="B18" t="str">
-        <v>4d ago</v>
+        <v>2026-06-02</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=5OGY6hCELfg</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411163&amp;sid=13e1d521681219f1f5cc74f85473f139</v>
       </c>
       <c r="D18" t="str">
         <v>2026-06-02</v>
@@ -1059,16 +1059,16 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>4d ago</v>
+        <v/>
       </c>
       <c r="G18" t="str">
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>Knox</v>
+        <v/>
       </c>
       <c r="I18" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J18" t="str">
         <v/>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Knox - Long Story Short (Official Video) - Knox</v>
+        <v>אלינור חלילוב - מחרוזת קיץ 2026</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Sofia Camara - The Last Encounter</v>
+        <v>אברהם חתומה - כשהלב בקרשים</v>
       </c>
       <c r="B19" t="str">
-        <v>4d ago</v>
+        <v>2026-06-02</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=E9kN4HLGG1c</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411162&amp;sid=13e1d521681219f1f5cc74f85473f139</v>
       </c>
       <c r="D19" t="str">
         <v>2026-06-02</v>
@@ -1097,16 +1097,16 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>4d ago</v>
+        <v/>
       </c>
       <c r="G19" t="str">
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>Sofia Camara</v>
+        <v/>
       </c>
       <c r="I19" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J19" t="str">
         <v/>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Sofia Camara - The Last Encounter - Sofia Camara</v>
+        <v>אברהם חתומה - כשהלב בקרשים</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Official Music Video: "Flowers" -- Alexander James</v>
+        <v>אביאלי חדד - וויסקי בלילות</v>
       </c>
       <c r="B20" t="str">
-        <v>4d ago</v>
+        <v>2026-06-02</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=aZ4WP0P92tM</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411161&amp;sid=13e1d521681219f1f5cc74f85473f139</v>
       </c>
       <c r="D20" t="str">
         <v>2026-06-02</v>
@@ -1135,16 +1135,16 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>4d ago</v>
+        <v/>
       </c>
       <c r="G20" t="str">
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>Alexander James</v>
+        <v/>
       </c>
       <c r="I20" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J20" t="str">
         <v/>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Official Music Video: "Flowers" -- Alexander James - Alexander James</v>
+        <v>אביאלי חדד - וויסקי בלילות</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>almost monday - skinny dip (official video)</v>
+        <v>Billy Idol - John Wayne feat. Alison Mosshart (Official Music Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>4d ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=hOxZDoaIzKQ</v>
+        <v>https://www.youtube.com/watch?v=47LNk7oiTVI</v>
       </c>
       <c r="D21" t="str">
         <v>2026-06-02</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>4d ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>almost monday</v>
+        <v>Billy Idol</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>almost monday - skinny dip (official video) - almost monday</v>
+        <v>Billy Idol - John Wayne feat. Alison Mosshart (Official Music Video) - Billy Idol</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Kip Moore - The Darkness (Official)</v>
+        <v>'It's Unusual' Official Music Video - Kelly Boesch | 4K</v>
       </c>
       <c r="B22" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=lTqqixCt5Mk</v>
+        <v>https://www.youtube.com/watch?v=Ru3fB2l1RSo</v>
       </c>
       <c r="D22" t="str">
         <v>2026-06-02</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>Kip Moore</v>
+        <v>Kelly Boesch AI Art</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Kip Moore - The Darkness (Official) - Kip Moore</v>
+        <v>'It's Unusual' Official Music Video - Kelly Boesch | 4K - Kelly Boesch AI Art</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Paul McCartney - Come Inside (Lyric Video)</v>
+        <v>Icona Pop - Butterfly Feelings (Official Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>4d ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=C8Zw_Cbm2V0</v>
+        <v>https://www.youtube.com/watch?v=AMW1Zq9RbIU</v>
       </c>
       <c r="D23" t="str">
         <v>2026-06-02</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>4d ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>PAUL McCARTNEY</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Paul McCartney - Come Inside (Lyric Video) - PAUL McCARTNEY</v>
+        <v>Icona Pop - Butterfly Feelings (Official Video) - Icona Pop</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Santana, Becky G - Mi Gran Amor (Official Lyric Video)</v>
+        <v>Hippo Campus - South</v>
       </c>
       <c r="B24" t="str">
-        <v>4d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=btdBd_Yee8E</v>
+        <v>https://www.youtube.com/watch?v=FYOmFfV7Ojo</v>
       </c>
       <c r="D24" t="str">
         <v>2026-06-02</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>4d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>Santana</v>
+        <v>Hippo Campus</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Santana, Becky G - Mi Gran Amor (Official Lyric Video) - Santana</v>
+        <v>Hippo Campus - South - Hippo Campus</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Dua Lipa - Training Season (Live From Mexico)</v>
+        <v>elijah woods - Old (Treehouse Sessions)</v>
       </c>
       <c r="B25" t="str">
-        <v>4d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=Va8Udsvqigs</v>
+        <v>https://www.youtube.com/watch?v=yDlkPdR_6zM</v>
       </c>
       <c r="D25" t="str">
         <v>2026-06-02</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>4d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>Dua Lipa</v>
+        <v>elijah woods</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Dua Lipa - Training Season (Live From Mexico) - Dua Lipa</v>
+        <v>elijah woods - Old (Treehouse Sessions) - elijah woods</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Charley - Liar</v>
+        <v>Nothing But Thieves - Evolution (Official Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>4d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=3Erfj2Eecgw</v>
+        <v>https://www.youtube.com/watch?v=hmjfuuuRRYU</v>
       </c>
       <c r="D26" t="str">
         <v>2026-06-02</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>4d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>Charley</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Charley - Liar - Charley</v>
+        <v>Nothing But Thieves - Evolution (Official Video) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (ft Gabito Ballesteros) [Visualizer]</v>
+        <v>Ariana Grande - hate that i made you love me (official music video)</v>
       </c>
       <c r="B27" t="str">
-        <v>4d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=em5ryETDkAo</v>
+        <v>https://www.youtube.com/watch?v=82-jTNka3uc</v>
       </c>
       <c r="D27" t="str">
         <v>2026-06-02</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>4d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
       </c>
       <c r="H27" t="str">
-        <v>David Guetta and Jennifer Lopez</v>
+        <v>Ariana Grande</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (ft Gabito Ballesteros) [Visualizer] - David Guetta and Jennifer Lopez</v>
+        <v>Ariana Grande - hate that i made you love me (official music video) - Ariana Grande</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Jordana Bryant - Too Little Too Late (Official Audio)</v>
+        <v>LAUREL - Fire Breather</v>
       </c>
       <c r="B28" t="str">
-        <v>4d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=AmwNx9qlOpA</v>
+        <v>https://www.youtube.com/watch?v=rtyavLIJjy0</v>
       </c>
       <c r="D28" t="str">
         <v>2026-06-02</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>4d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>Jordana Bryant</v>
+        <v>LAUREL</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Jordana Bryant - Too Little Too Late (Official Audio) - Jordana Bryant</v>
+        <v>LAUREL - Fire Breather - LAUREL</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Lewis Capaldi - Stay Love (Official Video)</v>
+        <v>The Warning - Ego (Performance Video)</v>
       </c>
       <c r="B29" t="str">
-        <v>4d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=9Pud3BqPpq0</v>
+        <v>https://www.youtube.com/watch?v=7PApWObImjo</v>
       </c>
       <c r="D29" t="str">
         <v>2026-06-02</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>4d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>Lewis Capaldi</v>
+        <v>The Warning</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Lewis Capaldi - Stay Love (Official Video) - Lewis Capaldi</v>
+        <v>The Warning - Ego (Performance Video) - The Warning</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Surreal World of Oddities - Pulling At My Strings - Official Music Video | 4K</v>
+        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (feat. Gabito Ballesteros) [Official Lyric Video]</v>
       </c>
       <c r="B30" t="str">
-        <v>6d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=fMt-f2aUW3c</v>
+        <v>https://www.youtube.com/watch?v=vruZSAYJBe4</v>
       </c>
       <c r="D30" t="str">
         <v>2026-06-02</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>6d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>Kelly Boesch AI Art</v>
+        <v>David Guetta and Jennifer Lopez</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Surreal World of Oddities - Pulling At My Strings - Official Music Video | 4K - Kelly Boesch AI Art</v>
+        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (feat. Gabito Ballesteros) [Official Lyric Video] - David Guetta and Jennifer Lopez</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Julia Cole - Love You to Death (Official Video)</v>
+        <v>Armin van Buuren - Equanimity (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B31" t="str">
-        <v>5d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=dWgmFc2QuLY</v>
+        <v>https://www.youtube.com/watch?v=k93t10R-Qrg</v>
       </c>
       <c r="D31" t="str">
         <v>2026-06-02</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>5d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>Julia Cole Music</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Julia Cole - Love You to Death (Official Video) - Julia Cole Music</v>
+        <v>Armin van Buuren - Equanimity (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Victor Biliac - De-ai fi tu salcie la mal ( Cover Edit )</v>
+        <v>“I Didn’t Know What Time It Was” - Andrew Bird Jazz Trio (Live from The Green Mill)</v>
       </c>
       <c r="B32" t="str">
-        <v>5d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=v3c0kG-V2zk</v>
+        <v>https://www.youtube.com/watch?v=XyRgdfXo2nI</v>
       </c>
       <c r="D32" t="str">
         <v>2026-06-02</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>5d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
       </c>
       <c r="H32" t="str">
-        <v>VictorBiliac</v>
+        <v>Andrew Bird</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Victor Biliac - De-ai fi tu salcie la mal ( Cover Edit ) - VictorBiliac</v>
+        <v>“I Didn’t Know What Time It Was” - Andrew Bird Jazz Trio (Live from The Green Mill) - Andrew Bird</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Lolo Zouaï - Coquelicot (feat. disiz) (Official Video)</v>
+        <v>Freya Ridings - Mother Of Pearl (Official Lyric Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>5d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=-4p6FkrOGT4</v>
+        <v>https://www.youtube.com/watch?v=7SGzYAZ0oxM</v>
       </c>
       <c r="D33" t="str">
         <v>2026-06-02</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>5d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>Lolo Zouaï and disiz</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Lolo Zouaï - Coquelicot (feat. disiz) (Official Video) - Lolo Zouaï and disiz</v>
+        <v>Freya Ridings - Mother Of Pearl (Official Lyric Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Jungle - The Wave (Official Video)</v>
+        <v>Danny Gokey - God's Not (Official Music Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>5d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=DW1vUkqNvqQ</v>
+        <v>https://www.youtube.com/watch?v=oGpKqX6ftcU</v>
       </c>
       <c r="D34" t="str">
         <v>2026-06-02</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>5d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>Jungle4eva</v>
+        <v>Danny Gokey</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Jungle - The Wave (Official Video) - Jungle4eva</v>
+        <v>Danny Gokey - God's Not (Official Music Video) - Danny Gokey</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Daytime TV – Sun (Official Music Video)</v>
+        <v>Armik - Brisas (2026 Remaster/Remix) (Exciting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B35" t="str">
-        <v>5d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=Jqo4ra_ch-M</v>
+        <v>https://www.youtube.com/watch?v=51Zu2iU2z2Q</v>
       </c>
       <c r="D35" t="str">
         <v>2026-06-02</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>5d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
       </c>
       <c r="H35" t="str">
-        <v>DAYTIME TV</v>
+        <v>Armik</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Daytime TV – Sun (Official Music Video) - DAYTIME TV</v>
+        <v>Armik - Brisas (2026 Remaster/Remix) (Exciting Rumba Flamenco, Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Surreal and Strange AI Video | Not Made For The Cage | Kelly Boesch - 4K</v>
+        <v>Holly Humberstone - Lucy (Free People Sessions)</v>
       </c>
       <c r="B36" t="str">
-        <v>2w ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=ACNj3L2bzV8</v>
+        <v>https://www.youtube.com/watch?v=c1GR2TTs9W8</v>
       </c>
       <c r="D36" t="str">
         <v>2026-06-02</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>2w ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>Kelly Boesch AI Art</v>
+        <v>Holly Humberstone and Free People</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Surreal and Strange AI Video | Not Made For The Cage | Kelly Boesch - 4K - Kelly Boesch AI Art</v>
+        <v>Holly Humberstone - Lucy (Free People Sessions) - Holly Humberstone and Free People</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Bruno Mars - Risk It All [Live From The Romantic Tour]</v>
+        <v>The Offspring - Why Don’t You Get a Job? | Live at BeachLife Festival 2026</v>
       </c>
       <c r="B37" t="str">
-        <v>6d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=aFbueod4reQ</v>
+        <v>https://www.youtube.com/watch?v=zRJ2etb_rpI</v>
       </c>
       <c r="D37" t="str">
         <v>2026-06-02</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>6d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>Bruno Mars</v>
+        <v>The Offspring</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Bruno Mars - Risk It All [Live From The Romantic Tour] - Bruno Mars</v>
+        <v>The Offspring - Why Don’t You Get a Job? | Live at BeachLife Festival 2026 - The Offspring</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Keith Urban - Summer Breeze (52nd American Music Awards)</v>
+        <v>Jagwar Twin, sir lucius - bad feeling (oompa loompa) (Visualizer)</v>
       </c>
       <c r="B38" t="str">
-        <v>6d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=zn-4eVoqofQ</v>
+        <v>https://www.youtube.com/watch?v=XGgI5HvR-gg</v>
       </c>
       <c r="D38" t="str">
         <v>2026-06-02</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>6d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
       </c>
       <c r="H38" t="str">
-        <v>Keith Urban</v>
+        <v>Jagwar Twin</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Keith Urban - Summer Breeze (52nd American Music Awards) - Keith Urban</v>
+        <v>Jagwar Twin, sir lucius - bad feeling (oompa loompa) (Visualizer) - Jagwar Twin</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Nelly Furtado, Boi-1Da, Canada Soccer - ELECTRIC CIRCUS (Official Music Video)</v>
+        <v>Nathan Evans x SAINT PHNX - Home (World Cup 2026) (Official Music Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>7d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=lHYEMWFuErM</v>
+        <v>https://www.youtube.com/watch?v=lRBNYETENNg</v>
       </c>
       <c r="D39" t="str">
         <v>2026-06-02</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>7d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
       </c>
       <c r="H39" t="str">
-        <v>Nelly Furtado</v>
+        <v>NathanEvanss</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Nelly Furtado, Boi-1Da, Canada Soccer - ELECTRIC CIRCUS (Official Music Video) - Nelly Furtado</v>
+        <v>Nathan Evans x SAINT PHNX - Home (World Cup 2026) (Official Music Video) - NathanEvanss</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Teddy Swims - Mr. Know It All (Live from the AMAs)</v>
+        <v>Greta Van Fleet - Play Your Games (Official Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>7d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=ttM4gWkhZBk</v>
+        <v>https://www.youtube.com/watch?v=CJsfI1QVBEM</v>
       </c>
       <c r="D40" t="str">
         <v>2026-06-02</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>7d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
       </c>
       <c r="H40" t="str">
-        <v>Teddy Swims and American Music Awards</v>
+        <v>Greta Van Fleet</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Teddy Swims - Mr. Know It All (Live from the AMAs) - Teddy Swims and American Music Awards</v>
+        <v>Greta Van Fleet - Play Your Games (Official Video) - Greta Van Fleet</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Shakira, Burna Boy - Dai Dai (Official Video)</v>
+        <v>Lola Young – From Down Here (From a Living Room)</v>
       </c>
       <c r="B41" t="str">
-        <v>9d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=fcnDmrtj6Sk</v>
+        <v>https://www.youtube.com/watch?v=uF5HUfho2NU</v>
       </c>
       <c r="D41" t="str">
         <v>2026-06-02</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>9d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
       </c>
       <c r="H41" t="str">
-        <v>Shakira and 2 more</v>
+        <v>Lola Young</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Shakira, Burna Boy - Dai Dai (Official Video) - Shakira and 2 more</v>
+        <v>Lola Young – From Down Here (From a Living Room) - Lola Young</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards)</v>
+        <v>Lawrence - Rain Check ft. Quinn XCII (Lyric Video)</v>
       </c>
       <c r="B42" t="str">
-        <v>9d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=wacpnp83cJg</v>
+        <v>https://www.youtube.com/watch?v=xXeyznlIrFY</v>
       </c>
       <c r="D42" t="str">
         <v>2026-06-02</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>9d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
       </c>
       <c r="H42" t="str">
-        <v>Lainey Wilson</v>
+        <v>Lawrence and Quinn XCII</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards) - Lainey Wilson</v>
+        <v>Lawrence - Rain Check ft. Quinn XCII (Lyric Video) - Lawrence and Quinn XCII</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ]</v>
+        <v>ANTONIA - NO HATE | Official Music Video</v>
       </c>
       <c r="B43" t="str">
-        <v>10d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=w8FTnkNVmq0</v>
+        <v>https://www.youtube.com/watch?v=rhlONr1DTj0</v>
       </c>
       <c r="D43" t="str">
         <v>2026-06-02</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>10d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
       </c>
       <c r="H43" t="str">
-        <v>Duran Duran</v>
+        <v>ANTONIA</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ] - Duran Duran</v>
+        <v>ANTONIA - NO HATE | Official Music Video - ANTONIA</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Nico Santos - Optimist</v>
+        <v>R3HAB - "Lost in translation..." (Official Lyric Video)</v>
       </c>
       <c r="B44" t="str">
-        <v>12d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=JA6PIcBeKZ0</v>
+        <v>https://www.youtube.com/watch?v=TbJtz0oy2cI</v>
       </c>
       <c r="D44" t="str">
         <v>2026-06-02</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>12d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
       </c>
       <c r="H44" t="str">
-        <v>Nico Santos</v>
+        <v>R3HAB</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Nico Santos - Optimist - Nico Santos</v>
+        <v>R3HAB - "Lost in translation..." (Official Lyric Video) - R3HAB</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Def Leppard - Personal Jesus (Live at Caesars Palace)</v>
+        <v>Pink Floyd - Shine On You Crazy Diamond (Parts 1-5) - Live in Venice (Official Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>10d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=k5SRMgdG4L4</v>
+        <v>https://www.youtube.com/watch?v=kwiawhDk2TM</v>
       </c>
       <c r="D45" t="str">
         <v>2026-06-02</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>10d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
       </c>
       <c r="H45" t="str">
-        <v>DEF LEPPARD</v>
+        <v>Pink Floyd</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Def Leppard - Personal Jesus (Live at Caesars Palace) - DEF LEPPARD</v>
+        <v>Pink Floyd - Shine On You Crazy Diamond (Parts 1-5) - Live in Venice (Official Video) - Pink Floyd</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer)</v>
+        <v>SHADE - TOXIC</v>
       </c>
       <c r="B46" t="str">
-        <v>10d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=eWSwy9GU2L8</v>
+        <v>https://www.youtube.com/watch?v=A3km0zrBKSg</v>
       </c>
       <c r="D46" t="str">
         <v>2026-06-02</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>10d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>Will Linley</v>
+        <v>Shade Official Channel</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer) - Will Linley</v>
+        <v>SHADE - TOXIC - Shade Official Channel</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Kylie Minogue - Story (Official Lyric Video)</v>
+        <v>Dua Lipa - Physical (Live From Mexico)</v>
       </c>
       <c r="B47" t="str">
-        <v>10d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=fv7_1qKo8mg</v>
+        <v>https://www.youtube.com/watch?v=xZAe-d3bXTs</v>
       </c>
       <c r="D47" t="str">
         <v>2026-06-02</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>10d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>Kylie Minogue</v>
+        <v>Dua Lipa</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Kylie Minogue - Story (Official Lyric Video) - Kylie Minogue</v>
+        <v>Dua Lipa - Physical (Live From Mexico) - Dua Lipa</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video)</v>
+        <v>Dagny - Rain (Lyric Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>10d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=3KUQx2s1fQc</v>
+        <v>https://www.youtube.com/watch?v=j3ZJwczZoUQ</v>
       </c>
       <c r="D48" t="str">
         <v>2026-06-02</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>10d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>Billy Raffoul</v>
+        <v>Dagny</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video) - Billy Raffoul</v>
+        <v>Dagny - Rain (Lyric Video) - Dagny</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025)</v>
+        <v>Modern Talking - Cheri Cheri Lady (Auf los geht's los, 14.09.1985)</v>
       </c>
       <c r="B49" t="str">
-        <v>10d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=vWf4uiLvwF8</v>
+        <v>https://www.youtube.com/watch?v=c0LtTVKNwNA</v>
       </c>
       <c r="D49" t="str">
         <v>2026-06-02</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>10d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>The Offspring</v>
+        <v>Modern Talking Offiziell</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025) - The Offspring</v>
+        <v>Modern Talking - Cheri Cheri Lady (Auf los geht's los, 14.09.1985) - Modern Talking Offiziell</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024)</v>
+        <v>The Chemical Brothers - Go (Live Show Visual)</v>
       </c>
       <c r="B50" t="str">
-        <v>10d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=9xjMaXegmWM</v>
+        <v>https://www.youtube.com/watch?v=fHCIchBq8CM</v>
       </c>
       <c r="D50" t="str">
         <v>2026-06-02</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>10d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>David Gilmour</v>
+        <v>The Chemical Brothers</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024) - David Gilmour</v>
+        <v>The Chemical Brothers - Go (Live Show Visual) - The Chemical Brothers</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Scorpions - Delicate Dance (Madison Square Garden 2022)</v>
+        <v>Jonas Blue - Girl (Official Lyric Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>10d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=yAjEr9WLTnU</v>
+        <v>https://www.youtube.com/watch?v=FTUe3jzUqXU</v>
       </c>
       <c r="D51" t="str">
         <v>2026-06-02</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>10d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>Scorpions</v>
+        <v>Defected Records and Jonas Blue</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Scorpions - Delicate Dance (Madison Square Garden 2022) - Scorpions</v>
+        <v>Jonas Blue - Girl (Official Lyric Video) - Defected Records and Jonas Blue</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston)</v>
+        <v>Dogpark - Don't Lie (Visualizer)</v>
       </c>
       <c r="B52" t="str">
-        <v>10d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=oRw4PqBzGc0</v>
+        <v>https://www.youtube.com/watch?v=is7qKBRycJI</v>
       </c>
       <c r="D52" t="str">
         <v>2026-06-02</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>10d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>Brandon Lake and NICK JONAS</v>
+        <v>Dogpark</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston) - Brandon Lake and NICK JONAS</v>
+        <v>Dogpark - Don't Lie (Visualizer) - Dogpark</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video)</v>
+        <v>elijah woods - L-O-V-E (Treehouse Sessions)</v>
       </c>
       <c r="B53" t="str">
-        <v>11d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=OKf_IOGxFQo</v>
+        <v>https://www.youtube.com/watch?v=q5kN7eH6rgo</v>
       </c>
       <c r="D53" t="str">
         <v>2026-06-02</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>11d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>Kygo and Dan Tyminski</v>
+        <v>elijah woods</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video) - Kygo and Dan Tyminski</v>
+        <v>elijah woods - L-O-V-E (Treehouse Sessions) - elijah woods</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>The Warning - Ego (Official Video)</v>
+        <v>Lauren Alaina - Better Off (Official Audio)</v>
       </c>
       <c r="B54" t="str">
-        <v>11d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=CG6Q5i75bR4</v>
+        <v>https://www.youtube.com/watch?v=Vj-ong3XNHM</v>
       </c>
       <c r="D54" t="str">
         <v>2026-06-02</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>11d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>The Warning</v>
+        <v>Lauren Alaina</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>The Warning - Ego (Official Video) - The Warning</v>
+        <v>Lauren Alaina - Better Off (Official Audio) - Lauren Alaina</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>paris jackson - teenage drama (official lyric video)</v>
+        <v>Lauren Sanderson - ARE YOU REALLY HERE? (Lyric Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>11d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=kVfDArNljos</v>
+        <v>https://www.youtube.com/watch?v=u7Et_hbMZUA</v>
       </c>
       <c r="D55" t="str">
         <v>2026-06-02</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>11d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>paris jackson</v>
+        <v>Lauren Sanderson</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>paris jackson - teenage drama (official lyric video) - paris jackson</v>
+        <v>Lauren Sanderson - ARE YOU REALLY HERE? (Lyric Video) - Lauren Sanderson</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Minelli - Sun Goes Down | Official Visualizer</v>
+        <v>Nightly – blue jeans (Official Lyric Video)</v>
       </c>
       <c r="B56" t="str">
-        <v>11d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=xOsjm-AwN5I</v>
+        <v>https://www.youtube.com/watch?v=LnA3xkXUwaM</v>
       </c>
       <c r="D56" t="str">
         <v>2026-06-02</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>11d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>Minelli</v>
+        <v>NIGHTLY</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Minelli - Sun Goes Down | Official Visualizer - Minelli</v>
+        <v>Nightly – blue jeans (Official Lyric Video) - NIGHTLY</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Maggie Rose - Gentle Man (Official Studio Video)</v>
+        <v>Dasha - Mad About It (Official Visualizer)</v>
       </c>
       <c r="B57" t="str">
-        <v>11d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=aWNK-vWrN60</v>
+        <v>https://www.youtube.com/watch?v=Ae1gf_7p3H8</v>
       </c>
       <c r="D57" t="str">
         <v>2026-06-02</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>11d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>Maggie Rose</v>
+        <v>Dasha</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Maggie Rose - Gentle Man (Official Studio Video) - Maggie Rose</v>
+        <v>Dasha - Mad About It (Official Visualizer) - Dasha</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer]</v>
+        <v>Max McNown - Something To Someone (Performance Video)</v>
       </c>
       <c r="B58" t="str">
-        <v>11d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=mN5AZBrVq9I</v>
+        <v>https://www.youtube.com/watch?v=4Ki4ejT86YM</v>
       </c>
       <c r="D58" t="str">
         <v>2026-06-02</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>11d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>David Guetta</v>
+        <v>Max McNown</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer] - David Guetta</v>
+        <v>Max McNown - Something To Someone (Performance Video) - Max McNown</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video)</v>
+        <v>Bebe Rexha &amp; David Guetta - Sad Girls (Official Visual)</v>
       </c>
       <c r="B59" t="str">
-        <v>11d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=0PTufEGRAVQ</v>
+        <v>https://www.youtube.com/watch?v=P8UqZ5IF-QE</v>
       </c>
       <c r="D59" t="str">
         <v>2026-06-02</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>11d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>Chris Young and Shaylen</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video) - Chris Young and Shaylen</v>
+        <v>Bebe Rexha &amp; David Guetta - Sad Girls (Official Visual) - Bebe Rexha</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Lauv - Pretty Little Things</v>
+        <v>Knox - Long Story Short (Official Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>11d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=_JBfanFvHnA</v>
+        <v>https://www.youtube.com/watch?v=5OGY6hCELfg</v>
       </c>
       <c r="D60" t="str">
         <v>2026-06-02</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>11d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>Lauv</v>
+        <v>Knox</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Lauv - Pretty Little Things - Lauv</v>
+        <v>Knox - Long Story Short (Official Video) - Knox</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Icona Pop - Butterfly Feelings (Official Audio)</v>
+        <v>Sofia Camara - The Last Encounter</v>
       </c>
       <c r="B61" t="str">
-        <v>11d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=bXA_Q75QZTs</v>
+        <v>https://www.youtube.com/watch?v=E9kN4HLGG1c</v>
       </c>
       <c r="D61" t="str">
         <v>2026-06-02</v>
@@ -2693,13 +2693,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>11d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>Icona Pop</v>
+        <v>Sofia Camara</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Icona Pop - Butterfly Feelings (Official Audio) - Icona Pop</v>
+        <v>Sofia Camara - The Last Encounter - Sofia Camara</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Will Swinton - Only One (Official Video)</v>
+        <v>Official Music Video: "Flowers" -- Alexander James</v>
       </c>
       <c r="B62" t="str">
-        <v>11d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=A0KzP-zm9hA</v>
+        <v>https://www.youtube.com/watch?v=aZ4WP0P92tM</v>
       </c>
       <c r="D62" t="str">
         <v>2026-06-02</v>
@@ -2731,13 +2731,13 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>11d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>Will Swinton</v>
+        <v>Alexander James</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Will Swinton - Only One (Official Video) - Will Swinton</v>
+        <v>Official Music Video: "Flowers" -- Alexander James - Alexander James</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Dean Lewis - Escape (Official Video)</v>
+        <v>almost monday - skinny dip (official video)</v>
       </c>
       <c r="B63" t="str">
-        <v>11d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=BZRaTXCkhcg</v>
+        <v>https://www.youtube.com/watch?v=hOxZDoaIzKQ</v>
       </c>
       <c r="D63" t="str">
         <v>2026-06-02</v>
@@ -2769,13 +2769,13 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>11d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>Dean Lewis</v>
+        <v>almost monday</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Dean Lewis - Escape (Official Video) - Dean Lewis</v>
+        <v>almost monday - skinny dip (official video) - almost monday</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico]</v>
+        <v>Kip Moore - The Darkness (Official)</v>
       </c>
       <c r="B64" t="str">
-        <v>11d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=PNm0hf_zZJY</v>
+        <v>https://www.youtube.com/watch?v=lTqqixCt5Mk</v>
       </c>
       <c r="D64" t="str">
         <v>2026-06-02</v>
@@ -2807,13 +2807,13 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>11d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>Dua Lipa and OficialMana</v>
+        <v>Kip Moore</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico] - Dua Lipa and OficialMana</v>
+        <v>Kip Moore - The Darkness (Official) - Kip Moore</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Niall Horan - End of an Era (Lyric Video)</v>
+        <v>Paul McCartney - Come Inside (Lyric Video)</v>
       </c>
       <c r="B65" t="str">
-        <v>11d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=EUNNmAAe5gQ</v>
+        <v>https://www.youtube.com/watch?v=C8Zw_Cbm2V0</v>
       </c>
       <c r="D65" t="str">
         <v>2026-06-02</v>
@@ -2845,13 +2845,13 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>11d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>Niall Horan</v>
+        <v>PAUL McCARTNEY</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Niall Horan - End of an Era (Lyric Video) - Niall Horan</v>
+        <v>Paul McCartney - Come Inside (Lyric Video) - PAUL McCARTNEY</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Olivia Rodrigo - the cure (Official Music Video)</v>
+        <v>Santana, Becky G - Mi Gran Amor (Official Lyric Video)</v>
       </c>
       <c r="B66" t="str">
-        <v>11d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=B402rKl4bUg</v>
+        <v>https://www.youtube.com/watch?v=btdBd_Yee8E</v>
       </c>
       <c r="D66" t="str">
         <v>2026-06-02</v>
@@ -2883,13 +2883,13 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>11d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>Olivia Rodrigo</v>
+        <v>Santana</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Olivia Rodrigo - the cure (Official Music Video) - Olivia Rodrigo</v>
+        <v>Santana, Becky G - Mi Gran Amor (Official Lyric Video) - Santana</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Ruel - Debbie Don't Cry (Official Music Video)</v>
+        <v>Dua Lipa - Training Season (Live From Mexico)</v>
       </c>
       <c r="B67" t="str">
-        <v>11d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=iz7wuk0GOwI</v>
+        <v>https://www.youtube.com/watch?v=Va8Udsvqigs</v>
       </c>
       <c r="D67" t="str">
         <v>2026-06-02</v>
@@ -2921,13 +2921,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>11d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>RUEL</v>
+        <v>Dua Lipa</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Ruel - Debbie Don't Cry (Official Music Video) - RUEL</v>
+        <v>Dua Lipa - Training Season (Live From Mexico) - Dua Lipa</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>TINI - Down (LIVE)</v>
+        <v>Charley - Liar</v>
       </c>
       <c r="B68" t="str">
-        <v>11d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=ADbFeQUPTrk</v>
+        <v>https://www.youtube.com/watch?v=3Erfj2Eecgw</v>
       </c>
       <c r="D68" t="str">
         <v>2026-06-02</v>
@@ -2959,13 +2959,13 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>11d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>TINI</v>
+        <v>Charley</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>TINI - Down (LIVE) - TINI</v>
+        <v>Charley - Liar - Charley</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Charli xcx - SS26 (Official Video)</v>
+        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (ft Gabito Ballesteros) [Visualizer]</v>
       </c>
       <c r="B69" t="str">
-        <v>11d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=twLhSqabby0</v>
+        <v>https://www.youtube.com/watch?v=em5ryETDkAo</v>
       </c>
       <c r="D69" t="str">
         <v>2026-06-02</v>
@@ -2997,13 +2997,13 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>11d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>Charli xcx</v>
+        <v>David Guetta and Jennifer Lopez</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Charli xcx - SS26 (Official Video) - Charli xcx</v>
+        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (ft Gabito Ballesteros) [Visualizer] - David Guetta and Jennifer Lopez</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Dua Lipa - Live From Mexico</v>
+        <v>Jordana Bryant - Too Little Too Late (Official Audio)</v>
       </c>
       <c r="B70" t="str">
-        <v>11d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=vZYVkitGXBU</v>
+        <v>https://www.youtube.com/watch?v=AmwNx9qlOpA</v>
       </c>
       <c r="D70" t="str">
         <v>2026-06-02</v>
@@ -3035,13 +3035,13 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>11d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>Dua Lipa</v>
+        <v>Jordana Bryant</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Dua Lipa - Live From Mexico - Dua Lipa</v>
+        <v>Jordana Bryant - Too Little Too Late (Official Audio) - Jordana Bryant</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Matilda Mann - 'The Fig Tree' (Official Video)</v>
+        <v>Lewis Capaldi - Stay Love (Official Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>12d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=XPyubkkkw44</v>
+        <v>https://www.youtube.com/watch?v=9Pud3BqPpq0</v>
       </c>
       <c r="D71" t="str">
         <v>2026-06-02</v>
@@ -3073,13 +3073,13 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>12d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>Matilda Mann</v>
+        <v>Lewis Capaldi</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Matilda Mann - 'The Fig Tree' (Official Video) - Matilda Mann</v>
+        <v>Lewis Capaldi - Stay Love (Official Video) - Lewis Capaldi</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Ella Langley - Be Her (61st Academy of Country Music Awards)</v>
+        <v>Surreal World of Oddities - Pulling At My Strings - Official Music Video | 4K</v>
       </c>
       <c r="B72" t="str">
-        <v>12d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=4KbYfH7EAm8</v>
+        <v>https://www.youtube.com/watch?v=fMt-f2aUW3c</v>
       </c>
       <c r="D72" t="str">
         <v>2026-06-02</v>
@@ -3111,13 +3111,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>12d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>Ella Langley</v>
+        <v>Kelly Boesch AI Art</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Ella Langley - Be Her (61st Academy of Country Music Awards) - Ella Langley</v>
+        <v>Surreal World of Oddities - Pulling At My Strings - Official Music Video | 4K - Kelly Boesch AI Art</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Nothing But Thieves - Evolution (Official Audio)</v>
+        <v>Julia Cole - Love You to Death (Official Video)</v>
       </c>
       <c r="B73" t="str">
-        <v>12d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=Kcs-4EZSUW0</v>
+        <v>https://www.youtube.com/watch?v=dWgmFc2QuLY</v>
       </c>
       <c r="D73" t="str">
         <v>2026-06-02</v>
@@ -3149,13 +3149,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>12d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Julia Cole Music</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Nothing But Thieves - Evolution (Official Audio) - Nothing But Thieves</v>
+        <v>Julia Cole - Love You to Death (Official Video) - Julia Cole Music</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO)</v>
+        <v>Victor Biliac - De-ai fi tu salcie la mal ( Cover Edit )</v>
       </c>
       <c r="B74" t="str">
-        <v>12d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=HiLT1jzDZb4</v>
+        <v>https://www.youtube.com/watch?v=v3c0kG-V2zk</v>
       </c>
       <c r="D74" t="str">
         <v>2026-06-02</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>12d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>kesha</v>
+        <v>VictorBiliac</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO) - kesha</v>
+        <v>Victor Biliac - De-ai fi tu salcie la mal ( Cover Edit ) - VictorBiliac</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify</v>
+        <v>Lolo Zouaï - Coquelicot (feat. disiz) (Official Video)</v>
       </c>
       <c r="B75" t="str">
-        <v>13d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=_WGsJYCCfU8</v>
+        <v>https://www.youtube.com/watch?v=-4p6FkrOGT4</v>
       </c>
       <c r="D75" t="str">
         <v>2026-06-02</v>
@@ -3225,13 +3225,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>13d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>Holly Humberstone</v>
+        <v>Lolo Zouaï and disiz</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify - Holly Humberstone</v>
+        <v>Lolo Zouaï - Coquelicot (feat. disiz) (Official Video) - Lolo Zouaï and disiz</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Foo Fighters - Of All People (Official Video)</v>
+        <v>Jungle - The Wave (Official Video)</v>
       </c>
       <c r="B76" t="str">
-        <v>13d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=r_iMzMrCQs0</v>
+        <v>https://www.youtube.com/watch?v=DW1vUkqNvqQ</v>
       </c>
       <c r="D76" t="str">
         <v>2026-06-02</v>
@@ -3263,13 +3263,13 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>13d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>Foo Fighters</v>
+        <v>Jungle4eva</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Foo Fighters - Of All People (Official Video) - Foo Fighters</v>
+        <v>Jungle - The Wave (Official Video) - Jungle4eva</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>'From Me To You' by The Beatles, performed by The Young Analogues</v>
+        <v>Daytime TV – Sun (Official Music Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>13d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=cLiyO2t3xd0</v>
+        <v>https://www.youtube.com/watch?v=Jqo4ra_ch-M</v>
       </c>
       <c r="D77" t="str">
         <v>2026-06-02</v>
@@ -3301,13 +3301,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>13d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>The Analogues</v>
+        <v>DAYTIME TV</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>'From Me To You' by The Beatles, performed by The Young Analogues - The Analogues</v>
+        <v>Daytime TV – Sun (Official Music Video) - DAYTIME TV</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video]</v>
+        <v>Surreal and Strange AI Video | Not Made For The Cage | Kelly Boesch - 4K</v>
       </c>
       <c r="B78" t="str">
-        <v>13d ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=O67Q25sMhyU</v>
+        <v>https://www.youtube.com/watch?v=ACNj3L2bzV8</v>
       </c>
       <c r="D78" t="str">
         <v>2026-06-02</v>
@@ -3339,13 +3339,13 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>13d ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>Rod Stewart</v>
+        <v>Kelly Boesch AI Art</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video] - Rod Stewart</v>
+        <v>Surreal and Strange AI Video | Not Made For The Cage | Kelly Boesch - 4K - Kelly Boesch AI Art</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Blue October - 18th Floor Balcony (Official Music Video)</v>
+        <v>Bruno Mars - Risk It All [Live From The Romantic Tour]</v>
       </c>
       <c r="B79" t="str">
-        <v>13d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=tPfbOjz-hRs</v>
+        <v>https://www.youtube.com/watch?v=aFbueod4reQ</v>
       </c>
       <c r="D79" t="str">
         <v>2026-06-02</v>
@@ -3377,13 +3377,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>13d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>Blue October</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Blue October - 18th Floor Balcony (Official Music Video) - Blue October</v>
+        <v>Bruno Mars - Risk It All [Live From The Romantic Tour] - Bruno Mars</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Far Caspian - hum (Official Video)</v>
+        <v>Keith Urban - Summer Breeze (52nd American Music Awards)</v>
       </c>
       <c r="B80" t="str">
-        <v>13d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=qqXrLDhGJRk</v>
+        <v>https://www.youtube.com/watch?v=zn-4eVoqofQ</v>
       </c>
       <c r="D80" t="str">
         <v>2026-06-02</v>
@@ -3415,13 +3415,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>13d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>Far Caspian</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Far Caspian - hum (Official Video) - Far Caspian</v>
+        <v>Keith Urban - Summer Breeze (52nd American Music Awards) - Keith Urban</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Kenia Os - Love Bombing</v>
+        <v>Nelly Furtado, Boi-1Da, Canada Soccer - ELECTRIC CIRCUS (Official Music Video)</v>
       </c>
       <c r="B81" t="str">
-        <v>13d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=ZuWA3pAyriQ</v>
+        <v>https://www.youtube.com/watch?v=lHYEMWFuErM</v>
       </c>
       <c r="D81" t="str">
         <v>2026-06-02</v>
@@ -3453,13 +3453,13 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>13d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
       </c>
       <c r="H81" t="str">
-        <v>Kenia Os</v>
+        <v>Nelly Furtado</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Kenia Os - Love Bombing - Kenia Os</v>
+        <v>Nelly Furtado, Boi-1Da, Canada Soccer - ELECTRIC CIRCUS (Official Music Video) - Nelly Furtado</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026</v>
+        <v>Teddy Swims - Mr. Know It All (Live from the AMAs)</v>
       </c>
       <c r="B82" t="str">
-        <v>13d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=ftJR_CrRsig</v>
+        <v>https://www.youtube.com/watch?v=ttM4gWkhZBk</v>
       </c>
       <c r="D82" t="str">
         <v>2026-06-02</v>
@@ -3491,13 +3491,13 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>13d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
       </c>
       <c r="H82" t="str">
-        <v>Purple Disco Machine</v>
+        <v>Teddy Swims and American Music Awards</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026 - Purple Disco Machine</v>
+        <v>Teddy Swims - Mr. Know It All (Live from the AMAs) - Teddy Swims and American Music Awards</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026</v>
+        <v>Shakira, Burna Boy - Dai Dai (Official Video)</v>
       </c>
       <c r="B83" t="str">
-        <v>2w ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=EltgrumKJfk</v>
+        <v>https://www.youtube.com/watch?v=fcnDmrtj6Sk</v>
       </c>
       <c r="D83" t="str">
         <v>2026-06-02</v>
@@ -3529,13 +3529,13 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>2w ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
       </c>
       <c r="H83" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Shakira and 2 more</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Shakira, Burna Boy - Dai Dai (Official Video) - Shakira and 2 more</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹</v>
+        <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards)</v>
       </c>
       <c r="B84" t="str">
-        <v>2w ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=EykAYQj99GU</v>
+        <v>https://www.youtube.com/watch?v=wacpnp83cJg</v>
       </c>
       <c r="D84" t="str">
         <v>2026-06-02</v>
@@ -3567,13 +3567,13 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>2w ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
       </c>
       <c r="H84" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹 - Eurovision Song Contest</v>
+        <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards) - Lainey Wilson</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026</v>
+        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ]</v>
       </c>
       <c r="B85" t="str">
-        <v>2w ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=doGkDemPcFE</v>
+        <v>https://www.youtube.com/watch?v=w8FTnkNVmq0</v>
       </c>
       <c r="D85" t="str">
         <v>2026-06-02</v>
@@ -3605,13 +3605,13 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>2w ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
       </c>
       <c r="H85" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Duran Duran</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ] - Duran Duran</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026</v>
+        <v>Nico Santos - Optimist</v>
       </c>
       <c r="B86" t="str">
-        <v>2w ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=rNpFNJLhSfA</v>
+        <v>https://www.youtube.com/watch?v=JA6PIcBeKZ0</v>
       </c>
       <c r="D86" t="str">
         <v>2026-06-02</v>
@@ -3643,13 +3643,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>2w ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Nico Santos</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Nico Santos - Optimist - Nico Santos</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026</v>
+        <v>Def Leppard - Personal Jesus (Live at Caesars Palace)</v>
       </c>
       <c r="B87" t="str">
-        <v>2w ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=TpMQ6dhcvvE</v>
+        <v>https://www.youtube.com/watch?v=k5SRMgdG4L4</v>
       </c>
       <c r="D87" t="str">
         <v>2026-06-02</v>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>2w ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>DEF LEPPARD</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Def Leppard - Personal Jesus (Live at Caesars Palace) - DEF LEPPARD</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​</v>
+        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer)</v>
       </c>
       <c r="B88" t="str">
-        <v>2w ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=ppCyj5DxO8s</v>
+        <v>https://www.youtube.com/watch?v=eWSwy9GU2L8</v>
       </c>
       <c r="D88" t="str">
         <v>2026-06-02</v>
@@ -3719,13 +3719,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>2w ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Will Linley</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​ - Eurovision Song Contest</v>
+        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer) - Will Linley</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Evanescence – Who Will You Follow (Official Music Video)</v>
+        <v>Kylie Minogue - Story (Official Lyric Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>2w ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=ak4Ti54Y6rY</v>
+        <v>https://www.youtube.com/watch?v=fv7_1qKo8mg</v>
       </c>
       <c r="D89" t="str">
         <v>2026-06-02</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>2w ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>Evanescence</v>
+        <v>Kylie Minogue</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Evanescence – Who Will You Follow (Official Music Video) - Evanescence</v>
+        <v>Kylie Minogue - Story (Official Lyric Video) - Kylie Minogue</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>DEEP PURPLE – ARROGANT BOY (Official Video)</v>
+        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video)</v>
       </c>
       <c r="B90" t="str">
-        <v>2w ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=SoSr0sStFaE</v>
+        <v>https://www.youtube.com/watch?v=3KUQx2s1fQc</v>
       </c>
       <c r="D90" t="str">
         <v>2026-06-02</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>2w ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>earMUSIC and Deep Purple Official</v>
+        <v>Billy Raffoul</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>DEEP PURPLE – ARROGANT BOY (Official Video) - earMUSIC and Deep Purple Official</v>
+        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video) - Billy Raffoul</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video]</v>
+        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025)</v>
       </c>
       <c r="B91" t="str">
-        <v>2w ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=9iCw89UajaQ</v>
+        <v>https://www.youtube.com/watch?v=vWf4uiLvwF8</v>
       </c>
       <c r="D91" t="str">
         <v>2026-06-02</v>
@@ -3833,13 +3833,13 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>2w ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>Armin van Buuren</v>
+        <v>The Offspring</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025) - The Offspring</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Madison Cunningham - "Take Two" (Live in Chicago)</v>
+        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024)</v>
       </c>
       <c r="B92" t="str">
-        <v>2w ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=bUBLlJXtjqE</v>
+        <v>https://www.youtube.com/watch?v=9xjMaXegmWM</v>
       </c>
       <c r="D92" t="str">
         <v>2026-06-02</v>
@@ -3871,13 +3871,13 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>2w ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
       </c>
       <c r="H92" t="str">
-        <v>Madison Cunningham</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Madison Cunningham - "Take Two" (Live in Chicago) - Madison Cunningham</v>
+        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024) - David Gilmour</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Johnny Orlando - Heads Up (Official Video)</v>
+        <v>Scorpions - Delicate Dance (Madison Square Garden 2022)</v>
       </c>
       <c r="B93" t="str">
-        <v>2w ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=s5mClhWsajE</v>
+        <v>https://www.youtube.com/watch?v=yAjEr9WLTnU</v>
       </c>
       <c r="D93" t="str">
         <v>2026-06-02</v>
@@ -3909,13 +3909,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>2w ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>Johnny Orlando</v>
+        <v>Scorpions</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Johnny Orlando - Heads Up (Official Video) - Johnny Orlando</v>
+        <v>Scorpions - Delicate Dance (Madison Square Garden 2022) - Scorpions</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Carver Jones - BEST FRIEND (Official Video)</v>
+        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston)</v>
       </c>
       <c r="B94" t="str">
-        <v>2w ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=96xxxpZ5uxI</v>
+        <v>https://www.youtube.com/watch?v=oRw4PqBzGc0</v>
       </c>
       <c r="D94" t="str">
         <v>2026-06-02</v>
@@ -3947,13 +3947,13 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>2w ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
       </c>
       <c r="H94" t="str">
-        <v>Carver Jones</v>
+        <v>Brandon Lake and NICK JONAS</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Carver Jones - BEST FRIEND (Official Video) - Carver Jones</v>
+        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston) - Brandon Lake and NICK JONAS</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Jazmin Bean - Darling (Official Music Video)</v>
+        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B95" t="str">
-        <v>2w ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=N4uW3ZcowBM</v>
+        <v>https://www.youtube.com/watch?v=OKf_IOGxFQo</v>
       </c>
       <c r="D95" t="str">
         <v>2026-06-02</v>
@@ -3985,13 +3985,13 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>2w ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
       </c>
       <c r="H95" t="str">
-        <v>Jazmin bean</v>
+        <v>Kygo and Dan Tyminski</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Jazmin Bean - Darling (Official Music Video) - Jazmin bean</v>
+        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video) - Kygo and Dan Tyminski</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Baby Queen - Word Vomit (Official Visualiser)</v>
+        <v>The Warning - Ego (Official Video)</v>
       </c>
       <c r="B96" t="str">
-        <v>2w ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=T-bo4Klq_js</v>
+        <v>https://www.youtube.com/watch?v=CG6Q5i75bR4</v>
       </c>
       <c r="D96" t="str">
         <v>2026-06-02</v>
@@ -4023,13 +4023,13 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>2w ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
       </c>
       <c r="H96" t="str">
-        <v>Baby Queen</v>
+        <v>The Warning</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Baby Queen - Word Vomit (Official Visualiser) - Baby Queen</v>
+        <v>The Warning - Ego (Official Video) - The Warning</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Switchfoot - Absolution (Official Audio)</v>
+        <v>paris jackson - teenage drama (official lyric video)</v>
       </c>
       <c r="B97" t="str">
-        <v>2w ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=nCOSfMdKq9k</v>
+        <v>https://www.youtube.com/watch?v=kVfDArNljos</v>
       </c>
       <c r="D97" t="str">
         <v>2026-06-02</v>
@@ -4061,13 +4061,13 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>2w ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
       </c>
       <c r="H97" t="str">
-        <v>Switchfoot</v>
+        <v>paris jackson</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Switchfoot - Absolution (Official Audio) - Switchfoot</v>
+        <v>paris jackson - teenage drama (official lyric video) - paris jackson</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Grace Potter - Love Me Not (Official Audio)</v>
+        <v>Minelli - Sun Goes Down | Official Visualizer</v>
       </c>
       <c r="B98" t="str">
-        <v>2w ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=W3v0HAxDTUY</v>
+        <v>https://www.youtube.com/watch?v=xOsjm-AwN5I</v>
       </c>
       <c r="D98" t="str">
         <v>2026-06-02</v>
@@ -4099,13 +4099,13 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>2w ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
       </c>
       <c r="H98" t="str">
-        <v>Grace Potter</v>
+        <v>Minelli</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Grace Potter - Love Me Not (Official Audio) - Grace Potter</v>
+        <v>Minelli - Sun Goes Down | Official Visualizer - Minelli</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.08.1986)</v>
+        <v>Maggie Rose - Gentle Man (Official Studio Video)</v>
       </c>
       <c r="B99" t="str">
-        <v>2w ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=Dhy4xH662vE</v>
+        <v>https://www.youtube.com/watch?v=aWNK-vWrN60</v>
       </c>
       <c r="D99" t="str">
         <v>2026-06-02</v>
@@ -4137,13 +4137,13 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>2w ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
       </c>
       <c r="H99" t="str">
-        <v>Modern Talking Offiziell</v>
+        <v>Maggie Rose</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.08.1986) - Modern Talking Offiziell</v>
+        <v>Maggie Rose - Gentle Man (Official Studio Video) - Maggie Rose</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>The All-American Rejects - Clothesline (Official Lyric Video)</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer]</v>
       </c>
       <c r="B100" t="str">
-        <v>2w ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=y9axmk3NjrA</v>
+        <v>https://www.youtube.com/watch?v=mN5AZBrVq9I</v>
       </c>
       <c r="D100" t="str">
         <v>2026-06-02</v>
@@ -4175,13 +4175,13 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>2w ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
       </c>
       <c r="H100" t="str">
-        <v>The All-American Rejects</v>
+        <v>David Guetta</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>The All-American Rejects - Clothesline (Official Lyric Video) - The All-American Rejects</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer] - David Guetta</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Henry Moodie - MISS U (Official Visualiser)</v>
+        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video)</v>
       </c>
       <c r="B101" t="str">
-        <v>2w ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=l_lroRlSmTE</v>
+        <v>https://www.youtube.com/watch?v=0PTufEGRAVQ</v>
       </c>
       <c r="D101" t="str">
         <v>2026-06-02</v>
@@ -4213,13 +4213,13 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>2w ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G101" t="str">
         <v/>
       </c>
       <c r="H101" t="str">
-        <v>Henry Moodie</v>
+        <v>Chris Young and Shaylen</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Henry Moodie - MISS U (Official Visualiser) - Henry Moodie</v>
+        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video) - Chris Young and Shaylen</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Spacey Jane - I Never See Her (Official Music Video)</v>
+        <v>Lauv - Pretty Little Things</v>
       </c>
       <c r="B102" t="str">
-        <v>2w ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=q6tyEMN5haA</v>
+        <v>https://www.youtube.com/watch?v=_JBfanFvHnA</v>
       </c>
       <c r="D102" t="str">
         <v>2026-06-02</v>
@@ -4251,13 +4251,13 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>2w ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G102" t="str">
         <v/>
       </c>
       <c r="H102" t="str">
-        <v>Spacey Jane</v>
+        <v>Lauv</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4269,18 +4269,18 @@
         <v/>
       </c>
       <c r="L102" t="str">
-        <v>Spacey Jane - I Never See Her (Official Music Video) - Spacey Jane</v>
+        <v>Lauv - Pretty Little Things - Lauv</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video)</v>
+        <v>Icona Pop - Butterfly Feelings (Official Audio)</v>
       </c>
       <c r="B103" t="str">
-        <v>2w ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C103" t="str">
-        <v>https://www.youtube.com/watch?v=qacdvCqOZGc</v>
+        <v>https://www.youtube.com/watch?v=bXA_Q75QZTs</v>
       </c>
       <c r="D103" t="str">
         <v>2026-06-02</v>
@@ -4289,13 +4289,13 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>2w ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G103" t="str">
         <v/>
       </c>
       <c r="H103" t="str">
-        <v>Megan Moroney</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4307,18 +4307,18 @@
         <v/>
       </c>
       <c r="L103" t="str">
-        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video) - Megan Moroney</v>
+        <v>Icona Pop - Butterfly Feelings (Official Audio) - Icona Pop</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Every Single Weekend (feat. Jamie xx)</v>
+        <v>Will Swinton - Only One (Official Video)</v>
       </c>
       <c r="B104" t="str">
-        <v/>
+        <v>11 days ago</v>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/every-single-weekend-feat-jamie-xx/6770445933</v>
+        <v>https://www.youtube.com/watch?v=A0KzP-zm9hA</v>
       </c>
       <c r="D104" t="str">
         <v>2026-06-02</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>Every Single Weekend (feat. Jamie xx) - Single</v>
+        <v>11 days ago</v>
       </c>
       <c r="G104" t="str">
-        <v>2:10</v>
+        <v/>
       </c>
       <c r="H104" t="str">
-        <v>The Avalanches</v>
+        <v>Will Swinton</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/the-avalanches/27524431</v>
+        <v/>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/every-single-weekend-feat-jamie-xx/6770445752</v>
+        <v/>
       </c>
       <c r="L104" t="str">
-        <v>Every Single Weekend (feat. Jamie xx) - The Avalanches</v>
+        <v>Will Swinton - Only One (Official Video) - Will Swinton</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>hate that i made you love me</v>
+        <v>Dean Lewis - Escape (Official Video)</v>
       </c>
       <c r="B105" t="str">
-        <v/>
+        <v>11 days ago</v>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/hate-that-i-made-you-love-me/6763656876</v>
+        <v>https://www.youtube.com/watch?v=BZRaTXCkhcg</v>
       </c>
       <c r="D105" t="str">
         <v>2026-06-02</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>petal</v>
+        <v>11 days ago</v>
       </c>
       <c r="G105" t="str">
-        <v>3:17</v>
+        <v/>
       </c>
       <c r="H105" t="str">
-        <v>Ariana Grande</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/ariana-grande/412778295</v>
+        <v/>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/hate-that-i-made-you-love-me/1895420989</v>
+        <v/>
       </c>
       <c r="L105" t="str">
-        <v>hate that i made you love me - Ariana Grande</v>
+        <v>Dean Lewis - Escape (Official Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Come Inside</v>
+        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico]</v>
       </c>
       <c r="B106" t="str">
-        <v/>
+        <v>12 days ago</v>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/come-inside/1887403093</v>
+        <v>https://www.youtube.com/watch?v=PNm0hf_zZJY</v>
       </c>
       <c r="D106" t="str">
         <v>2026-06-02</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>The Boys of Dungeon Lane</v>
+        <v>12 days ago</v>
       </c>
       <c r="G106" t="str">
-        <v>3:13</v>
+        <v/>
       </c>
       <c r="H106" t="str">
-        <v>Paul McCartney</v>
+        <v>Dua Lipa and OficialMana</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/paul-mccartney/12224</v>
+        <v/>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/come-inside/1887402919</v>
+        <v/>
       </c>
       <c r="L106" t="str">
-        <v>Come Inside - Paul McCartney</v>
+        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico] - Dua Lipa and OficialMana</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Game Time</v>
+        <v>Niall Horan - End of an Era (Lyric Video)</v>
       </c>
       <c r="B107" t="str">
-        <v/>
+        <v>11 days ago</v>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/game-time/6771157200</v>
+        <v>https://www.youtube.com/watch?v=EUNNmAAe5gQ</v>
       </c>
       <c r="D107" t="str">
         <v>2026-06-02</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>Game Time (FIFA World Cup 2026™) - Single</v>
+        <v>11 days ago</v>
       </c>
       <c r="G107" t="str">
-        <v>3:26</v>
+        <v/>
       </c>
       <c r="H107" t="str">
-        <v>Future</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/future/128050210</v>
+        <v/>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/game-time/6771157186</v>
+        <v/>
       </c>
       <c r="L107" t="str">
-        <v>Game Time - Future</v>
+        <v>Niall Horan - End of an Era (Lyric Video) - Niall Horan</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Motion Party (Remix)</v>
+        <v>Olivia Rodrigo - the cure (Official Music Video)</v>
       </c>
       <c r="B108" t="str">
-        <v/>
+        <v>11 days ago</v>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/motion-party-remix/6773413965</v>
+        <v>https://www.youtube.com/watch?v=B402rKl4bUg</v>
       </c>
       <c r="D108" t="str">
         <v>2026-06-02</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Motion Party (Remix) - Single</v>
+        <v>11 days ago</v>
       </c>
       <c r="G108" t="str">
-        <v>2:36</v>
+        <v/>
       </c>
       <c r="H108" t="str">
-        <v>Bossman Dlow</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/bossman-dlow/1474308236</v>
+        <v/>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/motion-party-remix/6773413953</v>
+        <v/>
       </c>
       <c r="L108" t="str">
-        <v>Motion Party (Remix) - Bossman Dlow</v>
+        <v>Olivia Rodrigo - the cure (Official Music Video) - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Aquel diciembre</v>
+        <v>Ruel - Debbie Don't Cry (Official Music Video)</v>
       </c>
       <c r="B109" t="str">
-        <v/>
+        <v>11 days ago</v>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/aquel-diciembre/6769580010</v>
+        <v>https://www.youtube.com/watch?v=iz7wuk0GOwI</v>
       </c>
       <c r="D109" t="str">
         <v>2026-06-02</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>Do Not Disturb: Late Checkout</v>
+        <v>11 days ago</v>
       </c>
       <c r="G109" t="str">
-        <v>3:22</v>
+        <v/>
       </c>
       <c r="H109" t="str">
-        <v>Young Miko</v>
+        <v>RUEL</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/young-miko/1576521417</v>
+        <v/>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/aquel-diciembre/6769579992</v>
+        <v/>
       </c>
       <c r="L109" t="str">
-        <v>Aquel diciembre - Young Miko</v>
+        <v>Ruel - Debbie Don't Cry (Official Music Video) - RUEL</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Handle</v>
+        <v>TINI - Down (LIVE)</v>
       </c>
       <c r="B110" t="str">
-        <v/>
+        <v>11 days ago</v>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/handle/6771922623</v>
+        <v>https://www.youtube.com/watch?v=ADbFeQUPTrk</v>
       </c>
       <c r="D110" t="str">
         <v>2026-06-02</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Blue Island</v>
+        <v>11 days ago</v>
       </c>
       <c r="G110" t="str">
-        <v>3:06</v>
+        <v/>
       </c>
       <c r="H110" t="str">
-        <v>Ravyn Lenae</v>
+        <v>TINI</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/ravyn-lenae/1044417443</v>
+        <v/>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/handle/6771922622</v>
+        <v/>
       </c>
       <c r="L110" t="str">
-        <v>Handle - Ravyn Lenae</v>
+        <v>TINI - Down (LIVE) - TINI</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>The Wave</v>
+        <v>Charli xcx - SS26 (Official Video)</v>
       </c>
       <c r="B111" t="str">
-        <v/>
+        <v>12 days ago</v>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/the-wave/1886730541</v>
+        <v>https://www.youtube.com/watch?v=twLhSqabby0</v>
       </c>
       <c r="D111" t="str">
         <v>2026-06-02</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Sunshine</v>
+        <v>12 days ago</v>
       </c>
       <c r="G111" t="str">
-        <v>3:22</v>
+        <v/>
       </c>
       <c r="H111" t="str">
-        <v>Jungle</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/jungle/825833522</v>
+        <v/>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/the-wave/1886730527</v>
+        <v/>
       </c>
       <c r="L111" t="str">
-        <v>The Wave - Jungle</v>
+        <v>Charli xcx - SS26 (Official Video) - Charli xcx</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>STOP</v>
+        <v>Dua Lipa - Live From Mexico</v>
       </c>
       <c r="B112" t="str">
-        <v/>
+        <v>12 days ago</v>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/stop/6771161771</v>
+        <v>https://www.youtube.com/watch?v=vZYVkitGXBU</v>
       </c>
       <c r="D112" t="str">
         <v>2026-06-02</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>are you mad at me? - Single</v>
+        <v>12 days ago</v>
       </c>
       <c r="G112" t="str">
-        <v>2:56</v>
+        <v/>
       </c>
       <c r="H112" t="str">
-        <v>Bella Kay</v>
+        <v>Dua Lipa</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
+        <v/>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/stop/6771161760</v>
+        <v/>
       </c>
       <c r="L112" t="str">
-        <v>STOP - Bella Kay</v>
+        <v>Dua Lipa - Live From Mexico - Dua Lipa</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Here (Apple Music Sessions)</v>
+        <v>Matilda Mann - 'The Fig Tree' (Official Video)</v>
       </c>
       <c r="B113" t="str">
-        <v/>
+        <v>12 days ago</v>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/here-apple-music-sessions/1878235516</v>
+        <v>https://www.youtube.com/watch?v=XPyubkkkw44</v>
       </c>
       <c r="D113" t="str">
         <v>2026-06-02</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Apple Music Sessions</v>
+        <v>12 days ago</v>
       </c>
       <c r="G113" t="str">
-        <v>3:08</v>
+        <v/>
       </c>
       <c r="H113" t="str">
-        <v>Mumford &amp; Sons</v>
+        <v>Matilda Mann</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/mumford-sons/307699986</v>
+        <v/>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/here-apple-music-sessions/1878235330</v>
+        <v/>
       </c>
       <c r="L113" t="str">
-        <v>Here (Apple Music Sessions) - Mumford &amp; Sons</v>
+        <v>Matilda Mann - 'The Fig Tree' (Official Video) - Matilda Mann</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Talk On The Hill</v>
+        <v>Ella Langley - Be Her (61st Academy of Country Music Awards)</v>
       </c>
       <c r="B114" t="str">
-        <v/>
+        <v>13 days ago</v>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/talk-on-the-hill/6769524458</v>
+        <v>https://www.youtube.com/watch?v=4KbYfH7EAm8</v>
       </c>
       <c r="D114" t="str">
         <v>2026-06-02</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>The Thread</v>
+        <v>13 days ago</v>
       </c>
       <c r="G114" t="str">
-        <v>3:27</v>
+        <v/>
       </c>
       <c r="H114" t="str">
-        <v>WILLOW</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/willow/400531893</v>
+        <v/>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/talk-on-the-hill/6769524450</v>
+        <v/>
       </c>
       <c r="L114" t="str">
-        <v>Talk On The Hill - WILLOW</v>
+        <v>Ella Langley - Be Her (61st Academy of Country Music Awards) - Ella Langley</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>No Fear</v>
+        <v>Nothing But Thieves - Evolution (Official Audio)</v>
       </c>
       <c r="B115" t="str">
-        <v/>
+        <v>13 days ago</v>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/no-fear/1880484493</v>
+        <v>https://www.youtube.com/watch?v=Kcs-4EZSUW0</v>
       </c>
       <c r="D115" t="str">
         <v>2026-06-02</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>For Love of Grace &amp; the Hereafter</v>
+        <v>13 days ago</v>
       </c>
       <c r="G115" t="str">
-        <v>3:38</v>
+        <v/>
       </c>
       <c r="H115" t="str">
-        <v>Iceage</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/iceage/406846711</v>
+        <v/>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/no-fear/1880484160</v>
+        <v/>
       </c>
       <c r="L115" t="str">
-        <v>No Fear - Iceage</v>
+        <v>Nothing But Thieves - Evolution (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Hostage</v>
+        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO)</v>
       </c>
       <c r="B116" t="str">
-        <v/>
+        <v>13 days ago</v>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/hostage/6774372288</v>
+        <v>https://www.youtube.com/watch?v=HiLT1jzDZb4</v>
       </c>
       <c r="D116" t="str">
         <v>2026-06-02</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Big Mama</v>
+        <v>13 days ago</v>
       </c>
       <c r="G116" t="str">
-        <v>3:11</v>
+        <v/>
       </c>
       <c r="H116" t="str">
-        <v>Latto</v>
+        <v>kesha</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/latto/419799506</v>
+        <v/>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/hostage/6774372200</v>
+        <v/>
       </c>
       <c r="L116" t="str">
-        <v>Hostage - Latto</v>
+        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO) - kesha</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Sad Girls</v>
+        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify</v>
       </c>
       <c r="B117" t="str">
-        <v/>
+        <v>13 days ago</v>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/sad-girls/6768814374</v>
+        <v>https://www.youtube.com/watch?v=_WGsJYCCfU8</v>
       </c>
       <c r="D117" t="str">
         <v>2026-06-02</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Sad Girls - Single</v>
+        <v>13 days ago</v>
       </c>
       <c r="G117" t="str">
-        <v>2:48</v>
+        <v/>
       </c>
       <c r="H117" t="str">
-        <v>Bebe Rexha</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/bebe-rexha/466059563</v>
+        <v/>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/sad-girls/6768814373</v>
+        <v/>
       </c>
       <c r="L117" t="str">
-        <v>Sad Girls - Bebe Rexha</v>
+        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify - Holly Humberstone</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Salvame Hoy (feat. Gabito Ballesteros)</v>
+        <v>Foo Fighters - Of All People (Official Video)</v>
       </c>
       <c r="B118" t="str">
-        <v/>
+        <v>13 days ago</v>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/salvame-hoy-feat-gabito-ballesteros/6765697019</v>
+        <v>https://www.youtube.com/watch?v=r_iMzMrCQs0</v>
       </c>
       <c r="D118" t="str">
         <v>2026-06-02</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Salvame Hoy (feat. Gabito Ballesteros) - Single</v>
+        <v>13 days ago</v>
       </c>
       <c r="G118" t="str">
-        <v>3:35</v>
+        <v/>
       </c>
       <c r="H118" t="str">
-        <v>Jennifer Lopez</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/jennifer-lopez/463009</v>
+        <v/>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/salvame-hoy-feat-gabito-ballesteros/1896041010</v>
+        <v/>
       </c>
       <c r="L118" t="str">
-        <v>Salvame Hoy (feat. Gabito Ballesteros) - Jennifer Lopez</v>
+        <v>Foo Fighters - Of All People (Official Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Rubio</v>
+        <v>'From Me To You' by The Beatles, performed by The Young Analogues</v>
       </c>
       <c r="B119" t="str">
-        <v/>
+        <v>13 days ago</v>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/rubio/6770655339</v>
+        <v>https://www.youtube.com/watch?v=cLiyO2t3xd0</v>
       </c>
       <c r="D119" t="str">
         <v>2026-06-02</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>La Voz Favorita</v>
+        <v>13 days ago</v>
       </c>
       <c r="G119" t="str">
-        <v>4:42</v>
+        <v/>
       </c>
       <c r="H119" t="str">
-        <v>Jay Wheeler</v>
+        <v>The Analogues</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/jay-wheeler/164376380</v>
+        <v/>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/rubio/6770654729</v>
+        <v/>
       </c>
       <c r="L119" t="str">
-        <v>Rubio - Jay Wheeler</v>
+        <v>'From Me To You' by The Beatles, performed by The Young Analogues - The Analogues</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Pary</v>
+        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video]</v>
       </c>
       <c r="B120" t="str">
-        <v/>
+        <v>13 days ago</v>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/pary/6767367748</v>
+        <v>https://www.youtube.com/watch?v=O67Q25sMhyU</v>
       </c>
       <c r="D120" t="str">
         <v>2026-06-02</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Con dolor - EP</v>
+        <v>13 days ago</v>
       </c>
       <c r="G120" t="str">
-        <v>2:52</v>
+        <v/>
       </c>
       <c r="H120" t="str">
-        <v>Grupo Frontera</v>
+        <v>Rod Stewart</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
+        <v/>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/pary/6767367501</v>
+        <v/>
       </c>
       <c r="L120" t="str">
-        <v>Pary - Grupo Frontera</v>
+        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video] - Rod Stewart</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Think As You Drunk</v>
+        <v>snake the drain</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/think-as-you-drunk/6770725979</v>
+        <v>https://music.apple.com/us/song/snake-the-drain/6771506655</v>
       </c>
       <c r="D121" t="str">
         <v>2026-06-02</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>That's Just Me</v>
+        <v>this time it’s different / snake the drain - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>3:48</v>
+        <v>3:08</v>
       </c>
       <c r="H121" t="str">
-        <v>Riley Green</v>
+        <v>Devon Again</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/riley-green/662432971</v>
+        <v>https://music.apple.com/us/artist/devon-again/1574318250</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/think-as-you-drunk/6770725355</v>
+        <v>https://music.apple.com/us/album/snake-the-drain/6771506650</v>
       </c>
       <c r="L121" t="str">
-        <v>Think As You Drunk - Riley Green</v>
+        <v>snake the drain - Devon Again</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Play Your Games</v>
+        <v>hate that i made you love me</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/play-your-games/6772932837</v>
+        <v>https://music.apple.com/us/song/hate-that-i-made-you-love-me/6763656876</v>
       </c>
       <c r="D122" t="str">
         <v>2026-06-02</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Play Your Games - Single</v>
+        <v>petal</v>
       </c>
       <c r="G122" t="str">
-        <v>3:15</v>
+        <v>3:17</v>
       </c>
       <c r="H122" t="str">
-        <v>Greta Van Fleet</v>
+        <v>Ariana Grande</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/greta-van-fleet/646178956</v>
+        <v>https://music.apple.com/us/artist/ariana-grande/412778295</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/play-your-games/6772932835</v>
+        <v>https://music.apple.com/us/album/hate-that-i-made-you-love-me/1895420989</v>
       </c>
       <c r="L122" t="str">
-        <v>Play Your Games - Greta Van Fleet</v>
+        <v>hate that i made you love me - Ariana Grande</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello)</v>
+        <v>Come Inside</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/adjourn-it-feat-serj-tankian-roman-morello/6769340216</v>
+        <v>https://music.apple.com/us/song/come-inside/1887403093</v>
       </c>
       <c r="D123" t="str">
         <v>2026-06-02</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello) - Single</v>
+        <v>The Boys of Dungeon Lane</v>
       </c>
       <c r="G123" t="str">
-        <v>2:47</v>
+        <v>3:13</v>
       </c>
       <c r="H123" t="str">
-        <v>Tom Morello</v>
+        <v>Paul McCartney</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/tom-morello/466357</v>
+        <v>https://music.apple.com/us/artist/paul-mccartney/12224</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/adjourn-it-feat-serj-tankian-roman-morello/6769340214</v>
+        <v>https://music.apple.com/us/album/come-inside/1887402919</v>
       </c>
       <c r="L123" t="str">
-        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello) - Tom Morello</v>
+        <v>Come Inside - Paul McCartney</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Essex_Honey.mp3</v>
+        <v>Game Time</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/essex-honey-mp3/6771169447</v>
+        <v>https://music.apple.com/us/song/game-time/6771157200</v>
       </c>
       <c r="D124" t="str">
         <v>2026-06-02</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Essex_Honey.mp3 - Single</v>
+        <v>Game Time (FIFA World Cup 2026™) - Single</v>
       </c>
       <c r="G124" t="str">
-        <v>4:49</v>
+        <v>3:26</v>
       </c>
       <c r="H124" t="str">
-        <v>Blood Orange</v>
+        <v>Future</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/blood-orange/440698865</v>
+        <v>https://music.apple.com/us/artist/future/128050210</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/essex-honey-mp3/6771169151</v>
+        <v>https://music.apple.com/us/album/game-time/6771157186</v>
       </c>
       <c r="L124" t="str">
-        <v>Essex_Honey.mp3 - Blood Orange</v>
+        <v>Game Time - Future</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>minute</v>
+        <v>Motion Party (Remix)</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/minute/1875303122</v>
+        <v>https://music.apple.com/us/song/motion-party-remix/6773413965</v>
       </c>
       <c r="D125" t="str">
         <v>2026-06-02</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>ghosted - EP</v>
+        <v>Motion Party (Remix) - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>2:59</v>
+        <v>2:36</v>
       </c>
       <c r="H125" t="str">
-        <v>Saint Harison</v>
+        <v>Bossman Dlow</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/saint-harison/1639595302</v>
+        <v>https://music.apple.com/us/artist/bossman-dlow/1474308236</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/minute/1875302904</v>
+        <v>https://music.apple.com/us/album/motion-party-remix/6773413953</v>
       </c>
       <c r="L125" t="str">
-        <v>minute - Saint Harison</v>
+        <v>Motion Party (Remix) - Bossman Dlow</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>THE LIVING</v>
+        <v>Aquel diciembre</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/the-living/1894092345</v>
+        <v>https://music.apple.com/us/song/aquel-diciembre/6769580010</v>
       </c>
       <c r="D126" t="str">
         <v>2026-06-02</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>COSMIC OPERA ACT II</v>
+        <v>Do Not Disturb: Late Checkout</v>
       </c>
       <c r="G126" t="str">
-        <v>2:48</v>
+        <v>3:22</v>
       </c>
       <c r="H126" t="str">
-        <v>Labrinth</v>
+        <v>Young Miko</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
+        <v>https://music.apple.com/us/artist/young-miko/1576521417</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/the-living/1894092339</v>
+        <v>https://music.apple.com/us/album/aquel-diciembre/6769579992</v>
       </c>
       <c r="L126" t="str">
-        <v>THE LIVING - Labrinth</v>
+        <v>Aquel diciembre - Young Miko</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Thug</v>
+        <v>Handle</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/thug/6769289966</v>
+        <v>https://music.apple.com/us/song/handle/6771922623</v>
       </c>
       <c r="D127" t="str">
         <v>2026-06-02</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Thug - Single</v>
+        <v>Blue Island</v>
       </c>
       <c r="G127" t="str">
-        <v>2:25</v>
+        <v>3:06</v>
       </c>
       <c r="H127" t="str">
-        <v>G Herbo</v>
+        <v>Ravyn Lenae</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/g-herbo/1036753321</v>
+        <v>https://music.apple.com/us/artist/ravyn-lenae/1044417443</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/thug/6769289953</v>
+        <v>https://music.apple.com/us/album/handle/6771922622</v>
       </c>
       <c r="L127" t="str">
-        <v>Thug - G Herbo</v>
+        <v>Handle - Ravyn Lenae</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Clap</v>
+        <v>Every Single Weekend (feat. Jamie xx)</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/clap/6769903711</v>
+        <v>https://music.apple.com/us/song/every-single-weekend-feat-jamie-xx/6770445933</v>
       </c>
       <c r="D128" t="str">
         <v>2026-06-02</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Clap - Single</v>
+        <v>Every Single Weekend (feat. Jamie xx) - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>2:04</v>
+        <v>2:10</v>
       </c>
       <c r="H128" t="str">
-        <v>Polo G</v>
+        <v>The Avalanches</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/polo-g/1159371412</v>
+        <v>https://music.apple.com/us/artist/the-avalanches/27524431</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/clap/6769903710</v>
+        <v>https://music.apple.com/us/album/every-single-weekend-feat-jamie-xx/6770445752</v>
       </c>
       <c r="L128" t="str">
-        <v>Clap - Polo G</v>
+        <v>Every Single Weekend (feat. Jamie xx) - The Avalanches</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>GANG BIZNESS</v>
+        <v>The Wave</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/gang-bizness/6772383809</v>
+        <v>https://music.apple.com/us/song/the-wave/1886730541</v>
       </c>
       <c r="D129" t="str">
         <v>2026-06-02</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>THE GENTLEMEN'S CLUB</v>
+        <v>Sunshine</v>
       </c>
       <c r="G129" t="str">
-        <v>2:47</v>
+        <v>3:22</v>
       </c>
       <c r="H129" t="str">
-        <v>YG</v>
+        <v>Jungle</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/yg/189792075</v>
+        <v>https://music.apple.com/us/artist/jungle/825833522</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/gang-bizness/6772383681</v>
+        <v>https://music.apple.com/us/album/the-wave/1886730527</v>
       </c>
       <c r="L129" t="str">
-        <v>GANG BIZNESS - YG</v>
+        <v>The Wave - Jungle</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>UR HEARTBEAT (WHO DO U THINK ABOUT AT 2AM?)</v>
+        <v>STOP</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/ur-heartbeat-who-do-u-think-about-at-2am/6765534140</v>
+        <v>https://music.apple.com/us/song/stop/6771161771</v>
       </c>
       <c r="D130" t="str">
         <v>2026-06-02</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>A LITTLE VENGEANCE</v>
+        <v>are you mad at me? - Single</v>
       </c>
       <c r="G130" t="str">
-        <v>2:50</v>
+        <v>2:56</v>
       </c>
       <c r="H130" t="str">
-        <v>Jessie Reyez</v>
+        <v>Bella Kay</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
+        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/ur-heartbeat-who-do-u-think-about-at-2am/1895983502</v>
+        <v>https://music.apple.com/us/album/stop/6771161760</v>
       </c>
       <c r="L130" t="str">
-        <v>UR HEARTBEAT (WHO DO U THINK ABOUT AT 2AM?) - Jessie Reyez</v>
+        <v>STOP - Bella Kay</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Joshua Tree</v>
+        <v>Here (Apple Music Sessions)</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/joshua-tree/6771859148</v>
+        <v>https://music.apple.com/us/song/here-apple-music-sessions/1878235516</v>
       </c>
       <c r="D131" t="str">
         <v>2026-06-02</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Euphoria: Season 3 (HBO Original Series Soundtrack)</v>
+        <v>Apple Music Sessions</v>
       </c>
       <c r="G131" t="str">
-        <v>2:50</v>
+        <v>3:08</v>
       </c>
       <c r="H131" t="str">
-        <v>Hans Zimmer</v>
+        <v>Mumford &amp; Sons</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/hans-zimmer/454295032</v>
+        <v>https://music.apple.com/us/artist/mumford-sons/307699986</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/joshua-tree/6771858464</v>
+        <v>https://music.apple.com/us/album/here-apple-music-sessions/1878235330</v>
       </c>
       <c r="L131" t="str">
-        <v>Joshua Tree - Hans Zimmer</v>
+        <v>Here (Apple Music Sessions) - Mumford &amp; Sons</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Mi Gran Amor</v>
+        <v>Talk On The Hill</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/mi-gran-amor/6773365775</v>
+        <v>https://music.apple.com/us/song/talk-on-the-hill/6769524458</v>
       </c>
       <c r="D132" t="str">
         <v>2026-06-02</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Mi Gran Amor - Single</v>
+        <v>The Thread</v>
       </c>
       <c r="G132" t="str">
-        <v>3:37</v>
+        <v>3:27</v>
       </c>
       <c r="H132" t="str">
-        <v>Santana</v>
+        <v>WILLOW</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/santana/217174</v>
+        <v>https://music.apple.com/us/artist/willow/400531893</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/mi-gran-amor/6773365236</v>
+        <v>https://music.apple.com/us/album/talk-on-the-hill/6769524450</v>
       </c>
       <c r="L132" t="str">
-        <v>Mi Gran Amor - Santana</v>
+        <v>Talk On The Hill - WILLOW</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>london</v>
+        <v>No Fear</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/london/6770745672</v>
+        <v>https://music.apple.com/us/song/no-fear/1880484493</v>
       </c>
       <c r="D133" t="str">
         <v>2026-06-02</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>stardust - EP</v>
+        <v>For Love of Grace &amp; the Hereafter</v>
       </c>
       <c r="G133" t="str">
-        <v>3:23</v>
+        <v>3:38</v>
       </c>
       <c r="H133" t="str">
-        <v>Freya Skye</v>
+        <v>Iceage</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/freya-skye/1541643053</v>
+        <v>https://music.apple.com/us/artist/iceage/406846711</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/london/6770745662</v>
+        <v>https://music.apple.com/us/album/no-fear/1880484160</v>
       </c>
       <c r="L133" t="str">
-        <v>london - Freya Skye</v>
+        <v>No Fear - Iceage</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Caution</v>
+        <v>Hostage</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/caution/6768487482</v>
+        <v>https://music.apple.com/us/song/hostage/6774372288</v>
       </c>
       <c r="D134" t="str">
         <v>2026-06-02</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>K-POPS! (Music from and inspired by K-POPS! Motion Picture)</v>
+        <v>Big Mama</v>
       </c>
       <c r="G134" t="str">
-        <v>2:43</v>
+        <v>3:11</v>
       </c>
       <c r="H134" t="str">
-        <v>NMIXX</v>
+        <v>Latto</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/nmixx/1600411676</v>
+        <v>https://music.apple.com/us/artist/latto/419799506</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/caution/6768487478</v>
+        <v>https://music.apple.com/us/album/hostage/6774372200</v>
       </c>
       <c r="L134" t="str">
-        <v>Caution - NMIXX</v>
+        <v>Hostage - Latto</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>LEMONADE (feat. Becky G)</v>
+        <v>Sad Girls</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/lemonade-feat-becky-g/1893742425</v>
+        <v>https://music.apple.com/us/song/sad-girls/6768814374</v>
       </c>
       <c r="D135" t="str">
         <v>2026-06-02</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>LEMONADE - The 2nd Album</v>
+        <v>Sad Girls - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>3:07</v>
+        <v>2:48</v>
       </c>
       <c r="H135" t="str">
-        <v>aespa</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
+        <v>https://music.apple.com/us/artist/bebe-rexha/466059563</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/lemonade-feat-becky-g/1893742002</v>
+        <v>https://music.apple.com/us/album/sad-girls/6768814373</v>
       </c>
       <c r="L135" t="str">
-        <v>LEMONADE (feat. Becky G) - aespa</v>
+        <v>Sad Girls - Bebe Rexha</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Take Me Back (Leave Me There)</v>
+        <v>Salvame Hoy (feat. Gabito Ballesteros)</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/take-me-back-leave-me-there/1892466278</v>
+        <v>https://music.apple.com/us/song/salvame-hoy-feat-gabito-ballesteros/6765697019</v>
       </c>
       <c r="D136" t="str">
         <v>2026-06-02</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Banks Of The Trinity</v>
+        <v>Salvame Hoy (feat. Gabito Ballesteros) - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>2:58</v>
+        <v>3:35</v>
       </c>
       <c r="H136" t="str">
-        <v>Cody Johnson</v>
+        <v>Jennifer Lopez</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
+        <v>https://music.apple.com/us/artist/jennifer-lopez/463009</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/take-me-back-leave-me-there/1892465981</v>
+        <v>https://music.apple.com/us/album/salvame-hoy-feat-gabito-ballesteros/1896041010</v>
       </c>
       <c r="L136" t="str">
-        <v>Take Me Back (Leave Me There) - Cody Johnson</v>
+        <v>Salvame Hoy (feat. Gabito Ballesteros) - Jennifer Lopez</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Cheap Thrills</v>
+        <v>Rubio</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/cheap-thrills/6771156732</v>
+        <v>https://music.apple.com/us/song/rubio/6770655339</v>
       </c>
       <c r="D137" t="str">
         <v>2026-06-02</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Cheap Thrills - Single</v>
+        <v>La Voz Favorita</v>
       </c>
       <c r="G137" t="str">
-        <v>2:42</v>
+        <v>4:42</v>
       </c>
       <c r="H137" t="str">
-        <v>Gavin Adcock</v>
+        <v>Jay Wheeler</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/gavin-adcock/1580645019</v>
+        <v>https://music.apple.com/us/artist/jay-wheeler/164376380</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/cheap-thrills/6771156723</v>
+        <v>https://music.apple.com/us/album/rubio/6770654729</v>
       </c>
       <c r="L137" t="str">
-        <v>Cheap Thrills - Gavin Adcock</v>
+        <v>Rubio - Jay Wheeler</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>ME VALE V</v>
+        <v>Pary</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/me-vale-v/6769567844</v>
+        <v>https://music.apple.com/us/song/pary/6767367748</v>
       </c>
       <c r="D138" t="str">
         <v>2026-06-02</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>ACOMODO</v>
+        <v>Con dolor - EP</v>
       </c>
       <c r="G138" t="str">
-        <v>3:06</v>
+        <v>2:52</v>
       </c>
       <c r="H138" t="str">
-        <v>Tito Double P</v>
+        <v>Grupo Frontera</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/tito-double-p/1690905306</v>
+        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/me-vale-v/6769567568</v>
+        <v>https://music.apple.com/us/album/pary/6767367501</v>
       </c>
       <c r="L138" t="str">
-        <v>ME VALE V - Tito Double P</v>
+        <v>Pary - Grupo Frontera</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Bug In The Cake</v>
+        <v>Think As You Drunk</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/bug-in-the-cake/1880470542</v>
+        <v>https://music.apple.com/us/song/think-as-you-drunk/6770725979</v>
       </c>
       <c r="D139" t="str">
         <v>2026-06-02</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Be Sweet To Me</v>
+        <v>That's Just Me</v>
       </c>
       <c r="G139" t="str">
-        <v>2:48</v>
+        <v>3:48</v>
       </c>
       <c r="H139" t="str">
-        <v>Violet Grohl</v>
+        <v>Riley Green</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
+        <v>https://music.apple.com/us/artist/riley-green/662432971</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/bug-in-the-cake/1880470537</v>
+        <v>https://music.apple.com/us/album/think-as-you-drunk/6770725355</v>
       </c>
       <c r="L139" t="str">
-        <v>Bug In The Cake - Violet Grohl</v>
+        <v>Think As You Drunk - Riley Green</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Coil</v>
+        <v>Play Your Games</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/coil/6766858354</v>
+        <v>https://music.apple.com/us/song/play-your-games/6772932837</v>
       </c>
       <c r="D140" t="str">
         <v>2026-06-02</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Rumspringa</v>
+        <v>Play Your Games - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>3:54</v>
+        <v>3:15</v>
       </c>
       <c r="H140" t="str">
-        <v>ear</v>
+        <v>Greta Van Fleet</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/ear/1829661500</v>
+        <v>https://music.apple.com/us/artist/greta-van-fleet/646178956</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/coil/6766858352</v>
+        <v>https://music.apple.com/us/album/play-your-games/6772932835</v>
       </c>
       <c r="L140" t="str">
-        <v>Coil - ear</v>
+        <v>Play Your Games - Greta Van Fleet</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Smugglers &amp; Scholars (feat. Killer Mike)</v>
+        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello)</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/smugglers-scholars-feat-killer-mike/6769424017</v>
+        <v>https://music.apple.com/us/song/adjourn-it-feat-serj-tankian-roman-morello/6769340216</v>
       </c>
       <c r="D141" t="str">
         <v>2026-06-02</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Smugglers &amp; Scholars (feat. Killer Mike) - Single</v>
+        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello) - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>3:30</v>
+        <v>2:47</v>
       </c>
       <c r="H141" t="str">
-        <v>Kneecap</v>
+        <v>Tom Morello</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
+        <v>https://music.apple.com/us/artist/tom-morello/466357</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/smugglers-scholars-feat-killer-mike/6769423676</v>
+        <v>https://music.apple.com/us/album/adjourn-it-feat-serj-tankian-roman-morello/6769340214</v>
       </c>
       <c r="L141" t="str">
-        <v>Smugglers &amp; Scholars (feat. Killer Mike) - Kneecap</v>
+        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello) - Tom Morello</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Out of my Head</v>
+        <v>Essex_Honey.mp3</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/out-of-my-head/6767725166</v>
+        <v>https://music.apple.com/us/song/essex-honey-mp3/6771169447</v>
       </c>
       <c r="D142" t="str">
         <v>2026-06-02</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>I Forgot / Out of my Head - Single</v>
+        <v>Essex_Honey.mp3 - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>3:04</v>
+        <v>4:49</v>
       </c>
       <c r="H142" t="str">
-        <v>Cara Delevingne</v>
+        <v>Blood Orange</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/cara-delevingne/1204798982</v>
+        <v>https://music.apple.com/us/artist/blood-orange/440698865</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/out-of-my-head/6767725156</v>
+        <v>https://music.apple.com/us/album/essex-honey-mp3/6771169151</v>
       </c>
       <c r="L142" t="str">
-        <v>Out of my Head - Cara Delevingne</v>
+        <v>Essex_Honey.mp3 - Blood Orange</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Passenger Princess</v>
+        <v>minute</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/passenger-princess/6771012228</v>
+        <v>https://music.apple.com/us/song/minute/1875303122</v>
       </c>
       <c r="D143" t="str">
         <v>2026-06-02</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Passenger Princess - Single</v>
+        <v>ghosted - EP</v>
       </c>
       <c r="G143" t="str">
-        <v>3:18</v>
+        <v>2:59</v>
       </c>
       <c r="H143" t="str">
-        <v>Perrie</v>
+        <v>Saint Harison</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/perrie/1729865272</v>
+        <v>https://music.apple.com/us/artist/saint-harison/1639595302</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/passenger-princess/6771012223</v>
+        <v>https://music.apple.com/us/album/minute/1875302904</v>
       </c>
       <c r="L143" t="str">
-        <v>Passenger Princess - Perrie</v>
+        <v>minute - Saint Harison</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Man of the House</v>
+        <v>THE LIVING</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/man-of-the-house/1893733057</v>
+        <v>https://music.apple.com/us/song/the-living/1894092345</v>
       </c>
       <c r="D144" t="str">
         <v>2026-06-02</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>SE9</v>
+        <v>COSMIC OPERA ACT II</v>
       </c>
       <c r="G144" t="str">
-        <v>2:35</v>
+        <v>2:48</v>
       </c>
       <c r="H144" t="str">
-        <v>Skye Newman</v>
+        <v>Labrinth</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/skye-newman/1799174381</v>
+        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/man-of-the-house/1893733056</v>
+        <v>https://music.apple.com/us/album/the-living/1894092339</v>
       </c>
       <c r="L144" t="str">
-        <v>Man of the House - Skye Newman</v>
+        <v>THE LIVING - Labrinth</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Beautiful Freeks</v>
+        <v>Thug</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/beautiful-freeks/6764602396</v>
+        <v>https://music.apple.com/us/song/thug/6769289966</v>
       </c>
       <c r="D145" t="str">
         <v>2026-06-02</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Beautiful Freeks - Single</v>
+        <v>Thug - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>2:37</v>
+        <v>2:25</v>
       </c>
       <c r="H145" t="str">
-        <v>MEEK</v>
+        <v>G Herbo</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/meek/1784432868</v>
+        <v>https://music.apple.com/us/artist/g-herbo/1036753321</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/beautiful-freeks/6764602393</v>
+        <v>https://music.apple.com/us/album/thug/6769289953</v>
       </c>
       <c r="L145" t="str">
-        <v>Beautiful Freeks - MEEK</v>
+        <v>Thug - G Herbo</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Slave to the Rithm (feat. Bring Me The Horizon) [I Hate Models Never Alone Remix]</v>
+        <v>Clap</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/slave-to-the-rithm-feat-bring-me-the-horizon-i/6771972616</v>
+        <v>https://music.apple.com/us/song/clap/6769903711</v>
       </c>
       <c r="D146" t="str">
         <v>2026-06-02</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Slave to the Rithm (I Hate Models Never Alone Remix) [feat. Bring Me The Horizon] - Single</v>
+        <v>Clap - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>4:34</v>
+        <v>2:04</v>
       </c>
       <c r="H146" t="str">
-        <v>ILLENIUM</v>
+        <v>Polo G</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/illenium/645420096</v>
+        <v>https://music.apple.com/us/artist/polo-g/1159371412</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/slave-to-the-rithm-feat-bring-me-the-horizon-i/6771972613</v>
+        <v>https://music.apple.com/us/album/clap/6769903710</v>
       </c>
       <c r="L146" t="str">
-        <v>Slave to the Rithm (feat. Bring Me The Horizon) [I Hate Models Never Alone Remix] - ILLENIUM</v>
+        <v>Clap - Polo G</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Beg For Me (JADE Remix)</v>
+        <v>GANG BIZNESS</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/beg-for-me-jade-remix/6771474203</v>
+        <v>https://music.apple.com/us/song/gang-bizness/6772383809</v>
       </c>
       <c r="D147" t="str">
         <v>2026-06-02</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Beg For Me (Remix) - Single</v>
+        <v>THE GENTLEMEN'S CLUB</v>
       </c>
       <c r="G147" t="str">
-        <v>2:50</v>
+        <v>2:47</v>
       </c>
       <c r="H147" t="str">
-        <v>Lily Allen</v>
+        <v>YG</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/lily-allen/157063999</v>
+        <v>https://music.apple.com/us/artist/yg/189792075</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/beg-for-me-jade-remix/6771474201</v>
+        <v>https://music.apple.com/us/album/gang-bizness/6772383681</v>
       </c>
       <c r="L147" t="str">
-        <v>Beg For Me (JADE Remix) - Lily Allen</v>
+        <v>GANG BIZNESS - YG</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>ABOVE IT</v>
+        <v>UR HEARTBEAT (WHO DO U THINK ABOUT AT 2AM?)</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/above-it/6766248703</v>
+        <v>https://music.apple.com/us/song/ur-heartbeat-who-do-u-think-about-at-2am/6765534140</v>
       </c>
       <c r="D148" t="str">
         <v>2026-06-02</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>GET THE TABLES - Single</v>
+        <v>A LITTLE VENGEANCE</v>
       </c>
       <c r="G148" t="str">
-        <v>1:45</v>
+        <v>2:50</v>
       </c>
       <c r="H148" t="str">
-        <v>Andy Mineo</v>
+        <v>Jessie Reyez</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/andy-mineo/257538441</v>
+        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/above-it/6766248699</v>
+        <v>https://music.apple.com/us/album/ur-heartbeat-who-do-u-think-about-at-2am/1895983502</v>
       </c>
       <c r="L148" t="str">
-        <v>ABOVE IT - Andy Mineo</v>
+        <v>UR HEARTBEAT (WHO DO U THINK ABOUT AT 2AM?) - Jessie Reyez</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>THE JESUS GENERATION</v>
+        <v>Joshua Tree</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/the-jesus-generation/6773948895</v>
+        <v>https://music.apple.com/us/song/joshua-tree/6771859148</v>
       </c>
       <c r="D149" t="str">
         <v>2026-06-02</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>THE JESUS GENERATION - Single</v>
+        <v>Euphoria: Season 3 (HBO Original Series Soundtrack)</v>
       </c>
       <c r="G149" t="str">
-        <v>4:15</v>
+        <v>2:50</v>
       </c>
       <c r="H149" t="str">
-        <v>Forrest Frank</v>
+        <v>Hans Zimmer</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/forrest-frank/1436657314</v>
+        <v>https://music.apple.com/us/artist/hans-zimmer/454295032</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/the-jesus-generation/6773948742</v>
+        <v>https://music.apple.com/us/album/joshua-tree/6771858464</v>
       </c>
       <c r="L149" t="str">
-        <v>THE JESUS GENERATION - Forrest Frank</v>
+        <v>Joshua Tree - Hans Zimmer</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Is It Over Now?</v>
+        <v>Mi Gran Amor</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/is-it-over-now/6767564750</v>
+        <v>https://music.apple.com/us/song/mi-gran-amor/6773365775</v>
       </c>
       <c r="D150" t="str">
         <v>2026-06-02</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Is It Over Now? - Single</v>
+        <v>Mi Gran Amor - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>3:39</v>
+        <v>3:37</v>
       </c>
       <c r="H150" t="str">
-        <v>Elderbrook</v>
+        <v>Santana</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/elderbrook/736829657</v>
+        <v>https://music.apple.com/us/artist/santana/217174</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/is-it-over-now/6767564746</v>
+        <v>https://music.apple.com/us/album/mi-gran-amor/6773365236</v>
       </c>
       <c r="L150" t="str">
-        <v>Is It Over Now? - Elderbrook</v>
+        <v>Mi Gran Amor - Santana</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>12 Steps</v>
+        <v>london</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/12-steps/6769559623</v>
+        <v>https://music.apple.com/us/song/london/6770745672</v>
       </c>
       <c r="D151" t="str">
         <v>2026-06-02</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>12 Steps - Single</v>
+        <v>stardust - EP</v>
       </c>
       <c r="G151" t="str">
-        <v>3:11</v>
+        <v>3:23</v>
       </c>
       <c r="H151" t="str">
-        <v>Dexter and The Moonrocks</v>
+        <v>Freya Skye</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/dexter-and-the-moonrocks/1581657500</v>
+        <v>https://music.apple.com/us/artist/freya-skye/1541643053</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/12-steps/6769559618</v>
+        <v>https://music.apple.com/us/album/london/6770745662</v>
       </c>
       <c r="L151" t="str">
-        <v>12 Steps - Dexter and The Moonrocks</v>
+        <v>london - Freya Skye</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Over And Over</v>
+        <v>Caution</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/over-and-over/6771585908</v>
+        <v>https://music.apple.com/us/song/caution/6768487482</v>
       </c>
       <c r="D152" t="str">
         <v>2026-06-02</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>It's A Dying Art</v>
+        <v>K-POPS! (Music from and inspired by K-POPS! Motion Picture)</v>
       </c>
       <c r="G152" t="str">
-        <v>4:38</v>
+        <v>2:43</v>
       </c>
       <c r="H152" t="str">
-        <v>Little Big Town</v>
+        <v>NMIXX</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/little-big-town/513770</v>
+        <v>https://music.apple.com/us/artist/nmixx/1600411676</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/over-and-over/6771585889</v>
+        <v>https://music.apple.com/us/album/caution/6768487478</v>
       </c>
       <c r="L152" t="str">
-        <v>Over And Over - Little Big Town</v>
+        <v>Caution - NMIXX</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>AMAPOLA</v>
+        <v>LEMONADE (feat. Becky G)</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/amapola/6769560428</v>
+        <v>https://music.apple.com/us/song/lemonade-feat-becky-g/1893742425</v>
       </c>
       <c r="D153" t="str">
         <v>2026-06-02</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Ricky y Mau</v>
+        <v>LEMONADE - The 2nd Album</v>
       </c>
       <c r="G153" t="str">
-        <v>2:22</v>
+        <v>3:07</v>
       </c>
       <c r="H153" t="str">
-        <v>Mau y Ricky</v>
+        <v>aespa</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/mau-y-ricky/1096068683</v>
+        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/amapola/6769559985</v>
+        <v>https://music.apple.com/us/album/lemonade-feat-becky-g/1893742002</v>
       </c>
       <c r="L153" t="str">
-        <v>AMAPOLA - Mau y Ricky</v>
+        <v>LEMONADE (feat. Becky G) - aespa</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Mad About It</v>
+        <v>Take Me Back (Leave Me There)</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/mad-about-it/6767425272</v>
+        <v>https://music.apple.com/us/song/take-me-back-leave-me-there/1892466278</v>
       </c>
       <c r="D154" t="str">
         <v>2026-06-02</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Mad About It - Single</v>
+        <v>Banks Of The Trinity</v>
       </c>
       <c r="G154" t="str">
-        <v>2:37</v>
+        <v>2:58</v>
       </c>
       <c r="H154" t="str">
-        <v>Dasha</v>
+        <v>Cody Johnson</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/dasha/1462663731</v>
+        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/mad-about-it/6767425271</v>
+        <v>https://music.apple.com/us/album/take-me-back-leave-me-there/1892465981</v>
       </c>
       <c r="L154" t="str">
-        <v>Mad About It - Dasha</v>
+        <v>Take Me Back (Leave Me There) - Cody Johnson</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Love’s a Gun</v>
+        <v>Cheap Thrills</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/loves-a-gun/6771898253</v>
+        <v>https://music.apple.com/us/song/cheap-thrills/6771156732</v>
       </c>
       <c r="D155" t="str">
         <v>2026-06-02</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Love’s a Gun - Single</v>
+        <v>Cheap Thrills - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>2:59</v>
+        <v>2:42</v>
       </c>
       <c r="H155" t="str">
-        <v>Daniel Seavey</v>
+        <v>Gavin Adcock</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/daniel-seavey/1646124302</v>
+        <v>https://music.apple.com/us/artist/gavin-adcock/1580645019</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/loves-a-gun/6771897951</v>
+        <v>https://music.apple.com/us/album/cheap-thrills/6771156723</v>
       </c>
       <c r="L155" t="str">
-        <v>Love’s a Gun - Daniel Seavey</v>
+        <v>Cheap Thrills - Gavin Adcock</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Long Story Short</v>
+        <v>ME VALE V</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/long-story-short/6770700866</v>
+        <v>https://music.apple.com/us/song/me-vale-v/6769567844</v>
       </c>
       <c r="D156" t="str">
         <v>2026-06-02</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Long Story Short - Single</v>
+        <v>ACOMODO</v>
       </c>
       <c r="G156" t="str">
-        <v>2:48</v>
+        <v>3:06</v>
       </c>
       <c r="H156" t="str">
-        <v>Knox</v>
+        <v>Tito Double P</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/knox/1547519433</v>
+        <v>https://music.apple.com/us/artist/tito-double-p/1690905306</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/long-story-short/6770700853</v>
+        <v>https://music.apple.com/us/album/me-vale-v/6769567568</v>
       </c>
       <c r="L156" t="str">
-        <v>Long Story Short - Knox</v>
+        <v>ME VALE V - Tito Double P</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Dior</v>
+        <v>Bug In The Cake</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/dior/1892136721</v>
+        <v>https://music.apple.com/us/song/bug-in-the-cake/1880470542</v>
       </c>
       <c r="D157" t="str">
         <v>2026-06-02</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>bitknot</v>
+        <v>Be Sweet To Me</v>
       </c>
       <c r="G157" t="str">
-        <v>3:32</v>
+        <v>2:48</v>
       </c>
       <c r="H157" t="str">
-        <v>feeble little horse</v>
+        <v>Violet Grohl</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/feeble-little-horse/1564273208</v>
+        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/dior/1892136714</v>
+        <v>https://music.apple.com/us/album/bug-in-the-cake/1880470537</v>
       </c>
       <c r="L157" t="str">
-        <v>Dior - feeble little horse</v>
+        <v>Bug In The Cake - Violet Grohl</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>blue jeans</v>
+        <v>Coil</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/blue-jeans/6770529591</v>
+        <v>https://music.apple.com/us/song/coil/6766858354</v>
       </c>
       <c r="D158" t="str">
         <v>2026-06-02</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>blue jeans - Single</v>
+        <v>Rumspringa</v>
       </c>
       <c r="G158" t="str">
-        <v>2:37</v>
+        <v>3:54</v>
       </c>
       <c r="H158" t="str">
-        <v>Nightly</v>
+        <v>ear</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/nightly/352310972</v>
+        <v>https://music.apple.com/us/artist/ear/1829661500</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/blue-jeans/6770529589</v>
+        <v>https://music.apple.com/us/album/coil/6766858352</v>
       </c>
       <c r="L158" t="str">
-        <v>blue jeans - Nightly</v>
+        <v>Coil - ear</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Que Gacho</v>
+        <v>Smugglers &amp; Scholars (feat. Killer Mike)</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/que-gacho/6770628420</v>
+        <v>https://music.apple.com/us/song/smugglers-scholars-feat-killer-mike/6769424017</v>
       </c>
       <c r="D159" t="str">
         <v>2026-06-02</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Que Gacho - Single</v>
+        <v>Smugglers &amp; Scholars (feat. Killer Mike) - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>3:13</v>
+        <v>3:30</v>
       </c>
       <c r="H159" t="str">
-        <v>Luis R Conriquez</v>
+        <v>Kneecap</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
+        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/que-gacho/6770628419</v>
+        <v>https://music.apple.com/us/album/smugglers-scholars-feat-killer-mike/6769423676</v>
       </c>
       <c r="L159" t="str">
-        <v>Que Gacho - Luis R Conriquez</v>
+        <v>Smugglers &amp; Scholars (feat. Killer Mike) - Kneecap</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>same God</v>
+        <v>Out of my Head</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/same-god/1878232616</v>
+        <v>https://music.apple.com/us/song/out-of-my-head/6767725166</v>
       </c>
       <c r="D160" t="str">
         <v>2026-06-02</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>I HOPE THIS HELPS</v>
+        <v>I Forgot / Out of my Head - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>3:34</v>
+        <v>3:04</v>
       </c>
       <c r="H160" t="str">
-        <v>Alana Springsteen</v>
+        <v>Cara Delevingne</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/alana-springsteen/1309335606</v>
+        <v>https://music.apple.com/us/artist/cara-delevingne/1204798982</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/same-god/1878232194</v>
+        <v>https://music.apple.com/us/album/out-of-my-head/6767725156</v>
       </c>
       <c r="L160" t="str">
-        <v>same God - Alana Springsteen</v>
+        <v>Out of my Head - Cara Delevingne</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>emotional swaggage</v>
+        <v>Passenger Princess</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/emotional-swaggage/6767397453</v>
+        <v>https://music.apple.com/us/song/passenger-princess/6771012228</v>
       </c>
       <c r="D161" t="str">
         <v>2026-06-02</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>IDCASH</v>
+        <v>Passenger Princess - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>2:12</v>
+        <v>3:18</v>
       </c>
       <c r="H161" t="str">
-        <v>IDK</v>
+        <v>Perrie</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/idk/1578186947</v>
+        <v>https://music.apple.com/us/artist/perrie/1729865272</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/emotional-swaggage/6767397348</v>
+        <v>https://music.apple.com/us/album/passenger-princess/6771012223</v>
       </c>
       <c r="L161" t="str">
-        <v>emotional swaggage - IDK</v>
+        <v>Passenger Princess - Perrie</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Baby Driver</v>
+        <v>Man of the House</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/baby-driver/6769152279</v>
+        <v>https://music.apple.com/us/song/man-of-the-house/1893733057</v>
       </c>
       <c r="D162" t="str">
         <v>2026-06-02</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Baby Driver - Single</v>
+        <v>SE9</v>
       </c>
       <c r="G162" t="str">
-        <v>3:36</v>
+        <v>2:35</v>
       </c>
       <c r="H162" t="str">
-        <v>070 Shake</v>
+        <v>Skye Newman</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/070-shake/1097177293</v>
+        <v>https://music.apple.com/us/artist/skye-newman/1799174381</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/baby-driver/6769152273</v>
+        <v>https://music.apple.com/us/album/man-of-the-house/1893733056</v>
       </c>
       <c r="L162" t="str">
-        <v>Baby Driver - 070 Shake</v>
+        <v>Man of the House - Skye Newman</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>More! More! More!</v>
+        <v>Beautiful Freeks</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/more-more-more/6770600105</v>
+        <v>https://music.apple.com/us/song/beautiful-freeks/6764602396</v>
       </c>
       <c r="D163" t="str">
         <v>2026-06-02</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>REBECCA</v>
+        <v>Beautiful Freeks - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>2:55</v>
+        <v>2:37</v>
       </c>
       <c r="H163" t="str">
-        <v>Becky Hill</v>
+        <v>MEEK</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/becky-hill/533839517</v>
+        <v>https://music.apple.com/us/artist/meek/1784432868</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/more-more-more/6770600098</v>
+        <v>https://music.apple.com/us/album/beautiful-freeks/6764602393</v>
       </c>
       <c r="L163" t="str">
-        <v>More! More! More! - Becky Hill</v>
+        <v>Beautiful Freeks - MEEK</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Young Again</v>
+        <v>Slave to the Rithm (feat. Bring Me The Horizon) [I Hate Models Never Alone Remix]</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/young-again/1877229743</v>
+        <v>https://music.apple.com/us/song/slave-to-the-rithm-feat-bring-me-the-horizon-i/6771972616</v>
       </c>
       <c r="D164" t="str">
         <v>2026-06-02</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>EI8HT</v>
+        <v>Slave to the Rithm (I Hate Models Never Alone Remix) [feat. Bring Me The Horizon] - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>3:36</v>
+        <v>4:34</v>
       </c>
       <c r="H164" t="str">
-        <v>Shinedown</v>
+        <v>ILLENIUM</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/shinedown/1883858</v>
+        <v>https://music.apple.com/us/artist/illenium/645420096</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/young-again/1877229738</v>
+        <v>https://music.apple.com/us/album/slave-to-the-rithm-feat-bring-me-the-horizon-i/6771972613</v>
       </c>
       <c r="L164" t="str">
-        <v>Young Again - Shinedown</v>
+        <v>Slave to the Rithm (feat. Bring Me The Horizon) [I Hate Models Never Alone Remix] - ILLENIUM</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>skinny dip</v>
+        <v>Beg For Me (JADE Remix)</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/skinny-dip/6769856281</v>
+        <v>https://music.apple.com/us/song/beg-for-me-jade-remix/6771474203</v>
       </c>
       <c r="D165" t="str">
         <v>2026-06-02</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>skinny dip - Single</v>
+        <v>Beg For Me (Remix) - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>3:12</v>
+        <v>2:50</v>
       </c>
       <c r="H165" t="str">
-        <v>almost monday</v>
+        <v>Lily Allen</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/almost-monday/1300723925</v>
+        <v>https://music.apple.com/us/artist/lily-allen/157063999</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/skinny-dip/6769855907</v>
+        <v>https://music.apple.com/us/album/beg-for-me-jade-remix/6771474201</v>
       </c>
       <c r="L165" t="str">
-        <v>skinny dip - almost monday</v>
+        <v>Beg For Me (JADE Remix) - Lily Allen</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>girls like girls (from the motion picture)</v>
+        <v>ABOVE IT</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/girls-like-girls-from-the-motion-picture/1893704575</v>
+        <v>https://music.apple.com/us/song/above-it/6766248703</v>
       </c>
       <c r="D166" t="str">
         <v>2026-06-02</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>girls like girls the album</v>
+        <v>GET THE TABLES - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>4:14</v>
+        <v>1:45</v>
       </c>
       <c r="H166" t="str">
-        <v>Hayley Kiyoko</v>
+        <v>Andy Mineo</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/hayley-kiyoko/325569584</v>
+        <v>https://music.apple.com/us/artist/andy-mineo/257538441</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/girls-like-girls-from-the-motion-picture/1893704396</v>
+        <v>https://music.apple.com/us/album/above-it/6766248699</v>
       </c>
       <c r="L166" t="str">
-        <v>girls like girls (from the motion picture) - Hayley Kiyoko</v>
+        <v>ABOVE IT - Andy Mineo</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Better Off</v>
+        <v>THE JESUS GENERATION</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/better-off/6772045367</v>
+        <v>https://music.apple.com/us/song/the-jesus-generation/6773948895</v>
       </c>
       <c r="D167" t="str">
         <v>2026-06-02</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Stages</v>
+        <v>THE JESUS GENERATION - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>3:16</v>
+        <v>4:15</v>
       </c>
       <c r="H167" t="str">
-        <v>Lauren Alaina</v>
+        <v>Forrest Frank</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/lauren-alaina/425028816</v>
+        <v>https://music.apple.com/us/artist/forrest-frank/1436657314</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/better-off/6772044978</v>
+        <v>https://music.apple.com/us/album/the-jesus-generation/6773948742</v>
       </c>
       <c r="L167" t="str">
-        <v>Better Off - Lauren Alaina</v>
+        <v>THE JESUS GENERATION - Forrest Frank</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Everythang Pinka (feat. Teezo Touchdown)</v>
+        <v>Is It Over Now?</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/everythang-pinka-feat-teezo-touchdown/6772026590</v>
+        <v>https://music.apple.com/us/song/is-it-over-now/6767564750</v>
       </c>
       <c r="D168" t="str">
         <v>2026-06-02</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Everythang Pinka (feat. Teezo Touchdown) - Single</v>
+        <v>Is It Over Now? - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>2:48</v>
+        <v>3:39</v>
       </c>
       <c r="H168" t="str">
-        <v>Monaleo</v>
+        <v>Elderbrook</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/monaleo/1495603374</v>
+        <v>https://music.apple.com/us/artist/elderbrook/736829657</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/everythang-pinka-feat-teezo-touchdown/6772026586</v>
+        <v>https://music.apple.com/us/album/is-it-over-now/6767564746</v>
       </c>
       <c r="L168" t="str">
-        <v>Everythang Pinka (feat. Teezo Touchdown) - Monaleo</v>
+        <v>Is It Over Now? - Elderbrook</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Lost in translation...</v>
+        <v>12 Steps</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/lost-in-translation/1870971556</v>
+        <v>https://music.apple.com/us/song/12-steps/6769559623</v>
       </c>
       <c r="D169" t="str">
         <v>2026-06-02</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Dream inside a dream…</v>
+        <v>12 Steps - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>3:30</v>
+        <v>3:11</v>
       </c>
       <c r="H169" t="str">
-        <v>R3HAB</v>
+        <v>Dexter and The Moonrocks</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/r3hab/331900515</v>
+        <v>https://music.apple.com/us/artist/dexter-and-the-moonrocks/1581657500</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/lost-in-translation/1870971550</v>
+        <v>https://music.apple.com/us/album/12-steps/6769559618</v>
       </c>
       <c r="L169" t="str">
-        <v>Lost in translation... - R3HAB</v>
+        <v>12 Steps - Dexter and The Moonrocks</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Call Security</v>
+        <v>Over And Over</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/call-security/6769296603</v>
+        <v>https://music.apple.com/us/song/over-and-over/6771585908</v>
       </c>
       <c r="D170" t="str">
         <v>2026-06-02</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>U, Me &amp; My Ego</v>
+        <v>It's A Dying Art</v>
       </c>
       <c r="G170" t="str">
-        <v>3:22</v>
+        <v>4:38</v>
       </c>
       <c r="H170" t="str">
-        <v>Chxrry</v>
+        <v>Little Big Town</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/chxrry/1520135642</v>
+        <v>https://music.apple.com/us/artist/little-big-town/513770</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/call-security/6769296591</v>
+        <v>https://music.apple.com/us/album/over-and-over/6771585889</v>
       </c>
       <c r="L170" t="str">
-        <v>Call Security - Chxrry</v>
+        <v>Over And Over - Little Big Town</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>chaotic</v>
+        <v>AMAPOLA</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/chaotic/6767629281</v>
+        <v>https://music.apple.com/us/song/amapola/6769560428</v>
       </c>
       <c r="D171" t="str">
         <v>2026-06-02</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>scars to prove it</v>
+        <v>Ricky y Mau</v>
       </c>
       <c r="G171" t="str">
-        <v>3:14</v>
+        <v>2:22</v>
       </c>
       <c r="H171" t="str">
-        <v>Hailey Picardi</v>
+        <v>Mau y Ricky</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
+        <v>https://music.apple.com/us/artist/mau-y-ricky/1096068683</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/chaotic/6767626506</v>
+        <v>https://music.apple.com/us/album/amapola/6769559985</v>
       </c>
       <c r="L171" t="str">
-        <v>chaotic - Hailey Picardi</v>
+        <v>AMAPOLA - Mau y Ricky</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Keep It To Yourself</v>
+        <v>Mad About It</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/keep-it-to-yourself/6771099675</v>
+        <v>https://music.apple.com/us/song/mad-about-it/6767425272</v>
       </c>
       <c r="D172" t="str">
         <v>2026-06-02</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>LOVE IS THE LAW</v>
+        <v>Mad About It - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>4:17</v>
+        <v>2:37</v>
       </c>
       <c r="H172" t="str">
-        <v>Love Spells</v>
+        <v>Dasha</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/love-spells/1597025563</v>
+        <v>https://music.apple.com/us/artist/dasha/1462663731</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/keep-it-to-yourself/6771099661</v>
+        <v>https://music.apple.com/us/album/mad-about-it/6767425271</v>
       </c>
       <c r="L172" t="str">
-        <v>Keep It To Yourself - Love Spells</v>
+        <v>Mad About It - Dasha</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Something to Someone</v>
+        <v>Love’s a Gun</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/something-to-someone/6767255424</v>
+        <v>https://music.apple.com/us/song/loves-a-gun/6771898253</v>
       </c>
       <c r="D173" t="str">
         <v>2026-06-02</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Something to Someone - Single</v>
+        <v>Love’s a Gun - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>3:55</v>
+        <v>2:59</v>
       </c>
       <c r="H173" t="str">
-        <v>Max McNown</v>
+        <v>Daniel Seavey</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
+        <v>https://music.apple.com/us/artist/daniel-seavey/1646124302</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/something-to-someone/1896445136</v>
+        <v>https://music.apple.com/us/album/loves-a-gun/6771897951</v>
       </c>
       <c r="L173" t="str">
-        <v>Something to Someone - Max McNown</v>
+        <v>Love’s a Gun - Daniel Seavey</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Green Screen (1pm)</v>
+        <v>Long Story Short</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/green-screen-1pm/6766279426</v>
+        <v>https://music.apple.com/us/song/long-story-short/6770700866</v>
       </c>
       <c r="D174" t="str">
         <v>2026-06-02</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>The Hours: High Noon</v>
+        <v>Long Story Short - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>2:10</v>
+        <v>2:48</v>
       </c>
       <c r="H174" t="str">
-        <v>Cautious Clay</v>
+        <v>Knox</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/cautious-clay/1064628701</v>
+        <v>https://music.apple.com/us/artist/knox/1547519433</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/green-screen-1pm/1896264236</v>
+        <v>https://music.apple.com/us/album/long-story-short/6770700853</v>
       </c>
       <c r="L174" t="str">
-        <v>Green Screen (1pm) - Cautious Clay</v>
+        <v>Long Story Short - Knox</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Scoreboard</v>
+        <v>Dior</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/scoreboard/6767255746</v>
+        <v>https://music.apple.com/us/song/dior/1892136721</v>
       </c>
       <c r="D175" t="str">
         <v>2026-06-02</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>I Just Wanna Be Loved</v>
+        <v>bitknot</v>
       </c>
       <c r="G175" t="str">
-        <v>3:24</v>
+        <v>3:32</v>
       </c>
       <c r="H175" t="str">
-        <v>Gabriella Rose</v>
+        <v>feeble little horse</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/gabriella-rose/645706232</v>
+        <v>https://music.apple.com/us/artist/feeble-little-horse/1564273208</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/scoreboard/1896445371</v>
+        <v>https://music.apple.com/us/album/dior/1892136714</v>
       </c>
       <c r="L175" t="str">
-        <v>Scoreboard - Gabriella Rose</v>
+        <v>Dior - feeble little horse</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>High</v>
+        <v>blue jeans</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/high/6773775211</v>
+        <v>https://music.apple.com/us/song/blue-jeans/6770529591</v>
       </c>
       <c r="D176" t="str">
         <v>2026-06-02</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Payback Is A Dog (EP)</v>
+        <v>blue jeans - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>2:55</v>
+        <v>2:37</v>
       </c>
       <c r="H176" t="str">
-        <v>Nia Smith</v>
+        <v>Nightly</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/nia-smith/1755576018</v>
+        <v>https://music.apple.com/us/artist/nightly/352310972</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/high/6773775203</v>
+        <v>https://music.apple.com/us/album/blue-jeans/6770529589</v>
       </c>
       <c r="L176" t="str">
-        <v>High - Nia Smith</v>
+        <v>blue jeans - Nightly</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Ay Gyal</v>
+        <v>Que Gacho</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/ay-gyal/6771885805</v>
+        <v>https://music.apple.com/us/song/que-gacho/6770628420</v>
       </c>
       <c r="D177" t="str">
         <v>2026-06-02</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Ay Gyal - Single</v>
+        <v>Que Gacho - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>2:12</v>
+        <v>3:13</v>
       </c>
       <c r="H177" t="str">
-        <v>1Ski OG</v>
+        <v>Luis R Conriquez</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
+        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/ay-gyal/6771885803</v>
+        <v>https://music.apple.com/us/album/que-gacho/6770628419</v>
       </c>
       <c r="L177" t="str">
-        <v>Ay Gyal - 1Ski OG</v>
+        <v>Que Gacho - Luis R Conriquez</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>always knew</v>
+        <v>same God</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/always-knew/6762864274</v>
+        <v>https://music.apple.com/us/song/same-god/1878232616</v>
       </c>
       <c r="D178" t="str">
         <v>2026-06-02</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>always knew - Single</v>
+        <v>I HOPE THIS HELPS</v>
       </c>
       <c r="G178" t="str">
-        <v>3:25</v>
+        <v>3:34</v>
       </c>
       <c r="H178" t="str">
-        <v>Biscits</v>
+        <v>Alana Springsteen</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/biscits/1185553226</v>
+        <v>https://music.apple.com/us/artist/alana-springsteen/1309335606</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/always-knew/1895047928</v>
+        <v>https://music.apple.com/us/album/same-god/1878232194</v>
       </c>
       <c r="L178" t="str">
-        <v>always knew - Biscits</v>
+        <v>same God - Alana Springsteen</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Cigarette Burns</v>
+        <v>emotional swaggage</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/cigarette-burns/6770691000</v>
+        <v>https://music.apple.com/us/song/emotional-swaggage/6767397453</v>
       </c>
       <c r="D179" t="str">
         <v>2026-06-02</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Heartland Rock and Roll</v>
+        <v>IDCASH</v>
       </c>
       <c r="G179" t="str">
-        <v>2:41</v>
+        <v>2:12</v>
       </c>
       <c r="H179" t="str">
-        <v>Corey Kent</v>
+        <v>IDK</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/corey-kent/1171544097</v>
+        <v>https://music.apple.com/us/artist/idk/1578186947</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/cigarette-burns/6770690867</v>
+        <v>https://music.apple.com/us/album/emotional-swaggage/6767397348</v>
       </c>
       <c r="L179" t="str">
-        <v>Cigarette Burns - Corey Kent</v>
+        <v>emotional swaggage - IDK</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Let You Down</v>
+        <v>Baby Driver</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/let-you-down/6773362320</v>
+        <v>https://music.apple.com/us/song/baby-driver/6769152279</v>
       </c>
       <c r="D180" t="str">
         <v>2026-06-02</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>El Relevo</v>
+        <v>Baby Driver - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>4:14</v>
+        <v>3:36</v>
       </c>
       <c r="H180" t="str">
-        <v>Luis Figueroa</v>
+        <v>070 Shake</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/luis-figueroa/395266944</v>
+        <v>https://music.apple.com/us/artist/070-shake/1097177293</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/let-you-down/6773362108</v>
+        <v>https://music.apple.com/us/album/baby-driver/6769152273</v>
       </c>
       <c r="L180" t="str">
-        <v>Let You Down - Luis Figueroa</v>
+        <v>Baby Driver - 070 Shake</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Starless</v>
+        <v>More! More! More!</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/starless/6770568779</v>
+        <v>https://music.apple.com/us/song/more-more-more/6770600105</v>
       </c>
       <c r="D181" t="str">
         <v>2026-06-02</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Starless - Single</v>
+        <v>REBECCA</v>
       </c>
       <c r="G181" t="str">
-        <v>4:32</v>
+        <v>2:55</v>
       </c>
       <c r="H181" t="str">
-        <v>A Perfect Circle</v>
+        <v>Becky Hill</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/a-perfect-circle/652503</v>
+        <v>https://music.apple.com/us/artist/becky-hill/533839517</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/starless/6770568776</v>
+        <v>https://music.apple.com/us/album/more-more-more/6770600098</v>
       </c>
       <c r="L181" t="str">
-        <v>Starless - A Perfect Circle</v>
+        <v>More! More! More! - Becky Hill</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Looking For You</v>
+        <v>Young Again</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/looking-for-you/6768355609</v>
+        <v>https://music.apple.com/us/song/young-again/1877229743</v>
       </c>
       <c r="D182" t="str">
         <v>2026-06-02</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Looking For You - Single</v>
+        <v>EI8HT</v>
       </c>
       <c r="G182" t="str">
-        <v>3:19</v>
+        <v>3:36</v>
       </c>
       <c r="H182" t="str">
-        <v>Gable Price and Friends</v>
+        <v>Shinedown</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/gable-price-and-friends/1441378212</v>
+        <v>https://music.apple.com/us/artist/shinedown/1883858</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/looking-for-you/6768355596</v>
+        <v>https://music.apple.com/us/album/young-again/1877229738</v>
       </c>
       <c r="L182" t="str">
-        <v>Looking For You - Gable Price and Friends</v>
+        <v>Young Again - Shinedown</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>FOCUSED</v>
+        <v>skinny dip</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/focused/1887909237</v>
+        <v>https://music.apple.com/us/song/skinny-dip/6769856281</v>
       </c>
       <c r="D183" t="str">
         <v>2026-06-02</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>FOCUSED - Single</v>
+        <v>skinny dip - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>2:23</v>
+        <v>3:12</v>
       </c>
       <c r="H183" t="str">
-        <v>Shepherd</v>
+        <v>almost monday</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/shepherd/1192803216</v>
+        <v>https://music.apple.com/us/artist/almost-monday/1300723925</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/focused/1887909236</v>
+        <v>https://music.apple.com/us/album/skinny-dip/6769855907</v>
       </c>
       <c r="L183" t="str">
-        <v>FOCUSED - Shepherd</v>
+        <v>skinny dip - almost monday</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Tú Ni En Cuenta</v>
+        <v>girls like girls (from the motion picture)</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/tu-ni-en-cuenta/6767701804</v>
+        <v>https://music.apple.com/us/song/girls-like-girls-from-the-motion-picture/1893704575</v>
       </c>
       <c r="D184" t="str">
         <v>2026-06-02</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Tú Ni En Cuenta - Single</v>
+        <v>girls like girls the album</v>
       </c>
       <c r="G184" t="str">
-        <v>3:23</v>
+        <v>4:14</v>
       </c>
       <c r="H184" t="str">
-        <v>Banda MS de Sergio Lizárraga</v>
+        <v>Hayley Kiyoko</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/banda-ms-de-sergio-liz%C3%A1rraga/413048014</v>
+        <v>https://music.apple.com/us/artist/hayley-kiyoko/325569584</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/tu-ni-en-cuenta/6767701803</v>
+        <v>https://music.apple.com/us/album/girls-like-girls-from-the-motion-picture/1893704396</v>
       </c>
       <c r="L184" t="str">
-        <v>Tú Ni En Cuenta - Banda MS de Sergio Lizárraga</v>
+        <v>girls like girls (from the motion picture) - Hayley Kiyoko</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>dream state</v>
+        <v>Better Off</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/dream-state/6765596009</v>
+        <v>https://music.apple.com/us/song/better-off/6772045367</v>
       </c>
       <c r="D185" t="str">
         <v>2026-06-02</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>dream state - Single</v>
+        <v>Stages</v>
       </c>
       <c r="G185" t="str">
-        <v>4:01</v>
+        <v>3:16</v>
       </c>
       <c r="H185" t="str">
-        <v>Martin Luke Brown</v>
+        <v>Lauren Alaina</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/martin-luke-brown/883292185</v>
+        <v>https://music.apple.com/us/artist/lauren-alaina/425028816</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/dream-state/1896004790</v>
+        <v>https://music.apple.com/us/album/better-off/6772044978</v>
       </c>
       <c r="L185" t="str">
-        <v>dream state - Martin Luke Brown</v>
+        <v>Better Off - Lauren Alaina</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Needle (feat. Spencer Cullum)</v>
+        <v>Everythang Pinka (feat. Teezo Touchdown)</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/needle-feat-spencer-cullum/6767618217</v>
+        <v>https://music.apple.com/us/song/everythang-pinka-feat-teezo-touchdown/6772026590</v>
       </c>
       <c r="D186" t="str">
         <v>2026-06-02</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Needle (feat. Spencer Cullum) - Single</v>
+        <v>Everythang Pinka (feat. Teezo Touchdown) - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>3:39</v>
+        <v>2:48</v>
       </c>
       <c r="H186" t="str">
-        <v>Mynolia</v>
+        <v>Monaleo</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/mynolia/1444347510</v>
+        <v>https://music.apple.com/us/artist/monaleo/1495603374</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/needle-feat-spencer-cullum/6767618203</v>
+        <v>https://music.apple.com/us/album/everythang-pinka-feat-teezo-touchdown/6772026586</v>
       </c>
       <c r="L186" t="str">
-        <v>Needle (feat. Spencer Cullum) - Mynolia</v>
+        <v>Everythang Pinka (feat. Teezo Touchdown) - Monaleo</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>You Retreat In Time And Space</v>
+        <v>Lost in translation...</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/you-retreat-in-time-and-space/1890015660</v>
+        <v>https://music.apple.com/us/song/lost-in-translation/1870971556</v>
       </c>
       <c r="D187" t="str">
         <v>2026-06-02</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Inferno</v>
+        <v>Dream inside a dream…</v>
       </c>
       <c r="G187" t="str">
-        <v>5:25</v>
+        <v>3:30</v>
       </c>
       <c r="H187" t="str">
-        <v>Boards of Canada</v>
+        <v>R3HAB</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/boards-of-canada/2989314</v>
+        <v>https://music.apple.com/us/artist/r3hab/331900515</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/you-retreat-in-time-and-space/1890015523</v>
+        <v>https://music.apple.com/us/album/lost-in-translation/1870971550</v>
       </c>
       <c r="L187" t="str">
-        <v>You Retreat In Time And Space - Boards of Canada</v>
+        <v>Lost in translation... - R3HAB</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>It's Happening (To Me)</v>
+        <v>Call Security</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/its-happening-to-me/6764723461</v>
+        <v>https://music.apple.com/us/song/call-security/6769296603</v>
       </c>
       <c r="D188" t="str">
         <v>2026-06-02</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>It's Happening (To Me) - Single</v>
+        <v>U, Me &amp; My Ego</v>
       </c>
       <c r="G188" t="str">
-        <v>2:34</v>
+        <v>3:22</v>
       </c>
       <c r="H188" t="str">
-        <v>Delroy Edwards</v>
+        <v>Chxrry</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/delroy-edwards/591790909</v>
+        <v>https://music.apple.com/us/artist/chxrry/1520135642</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/its-happening-to-me/1895893472</v>
+        <v>https://music.apple.com/us/album/call-security/6769296591</v>
       </c>
       <c r="L188" t="str">
-        <v>It's Happening (To Me) - Delroy Edwards</v>
+        <v>Call Security - Chxrry</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>FCUK</v>
+        <v>chaotic</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/fcuk/6769623577</v>
+        <v>https://music.apple.com/us/song/chaotic/6767629281</v>
       </c>
       <c r="D189" t="str">
         <v>2026-06-02</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>FCUK - Single</v>
+        <v>scars to prove it</v>
       </c>
       <c r="G189" t="str">
-        <v>2:22</v>
+        <v>3:14</v>
       </c>
       <c r="H189" t="str">
-        <v>H.LLS</v>
+        <v>Hailey Picardi</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/h-lls/1751287958</v>
+        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/fcuk/6769623566</v>
+        <v>https://music.apple.com/us/album/chaotic/6767626506</v>
       </c>
       <c r="L189" t="str">
-        <v>FCUK - H.LLS</v>
+        <v>chaotic - Hailey Picardi</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Higher</v>
+        <v>Keep It To Yourself</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/higher/1880124200</v>
+        <v>https://music.apple.com/us/song/keep-it-to-yourself/6771099675</v>
       </c>
       <c r="D190" t="str">
         <v>2026-06-02</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Run, Run Pure Beauty</v>
+        <v>LOVE IS THE LAW</v>
       </c>
       <c r="G190" t="str">
-        <v>4:06</v>
+        <v>4:17</v>
       </c>
       <c r="H190" t="str">
-        <v>Francis of Delirium</v>
+        <v>Love Spells</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/francis-of-delirium/1485902996</v>
+        <v>https://music.apple.com/us/artist/love-spells/1597025563</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/higher/1880123731</v>
+        <v>https://music.apple.com/us/album/keep-it-to-yourself/6771099661</v>
       </c>
       <c r="L190" t="str">
-        <v>Higher - Francis of Delirium</v>
+        <v>Keep It To Yourself - Love Spells</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>B.U.N</v>
+        <v>Something to Someone</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/b-u-n/6763272338</v>
+        <v>https://music.apple.com/us/song/something-to-someone/6767255424</v>
       </c>
       <c r="D191" t="str">
         <v>2026-06-02</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>B.U.N - Single</v>
+        <v>Something to Someone - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>3:43</v>
+        <v>3:55</v>
       </c>
       <c r="H191" t="str">
-        <v>Roll Deep</v>
+        <v>Max McNown</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/roll-deep/3083873</v>
+        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/b-u-n/1895242397</v>
+        <v>https://music.apple.com/us/album/something-to-someone/1896445136</v>
       </c>
       <c r="L191" t="str">
-        <v>B.U.N - Roll Deep</v>
+        <v>Something to Someone - Max McNown</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Only Love (feat. Pa Salieu)</v>
+        <v>Green Screen (1pm)</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/only-love-feat-pa-salieu/6767014290</v>
+        <v>https://music.apple.com/us/song/green-screen-1pm/6766279426</v>
       </c>
       <c r="D192" t="str">
         <v>2026-06-02</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Here Because of Hope</v>
+        <v>The Hours: High Noon</v>
       </c>
       <c r="G192" t="str">
-        <v>3:22</v>
+        <v>2:10</v>
       </c>
       <c r="H192" t="str">
-        <v>Ezra Collective</v>
+        <v>Cautious Clay</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/ezra-collective/1103640281</v>
+        <v>https://music.apple.com/us/artist/cautious-clay/1064628701</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/only-love-feat-pa-salieu/6767014278</v>
+        <v>https://music.apple.com/us/album/green-screen-1pm/1896264236</v>
       </c>
       <c r="L192" t="str">
-        <v>Only Love (feat. Pa Salieu) - Ezra Collective</v>
+        <v>Green Screen (1pm) - Cautious Clay</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Beautiful Things 1st scene/audition</v>
+        <v>Scoreboard</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/beautiful-things-1st-scene-audition/6771942631</v>
+        <v>https://music.apple.com/us/song/scoreboard/6767255746</v>
       </c>
       <c r="D193" t="str">
         <v>2026-06-02</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>UNDRA</v>
+        <v>I Just Wanna Be Loved</v>
       </c>
       <c r="G193" t="str">
-        <v>2:49</v>
+        <v>3:24</v>
       </c>
       <c r="H193" t="str">
-        <v>reggie</v>
+        <v>Gabriella Rose</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/reggie/1526587068</v>
+        <v>https://music.apple.com/us/artist/gabriella-rose/645706232</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/beautiful-things-1st-scene-audition/6771942630</v>
+        <v>https://music.apple.com/us/album/scoreboard/1896445371</v>
       </c>
       <c r="L193" t="str">
-        <v>Beautiful Things 1st scene/audition - reggie</v>
+        <v>Scoreboard - Gabriella Rose</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>HEAVEN'S ON FIRE</v>
+        <v>High</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/heavens-on-fire/6771110730</v>
+        <v>https://music.apple.com/us/song/high/6773775211</v>
       </c>
       <c r="D194" t="str">
         <v>2026-06-02</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>HEAVEN'S ON FIRE</v>
+        <v>Payback Is A Dog (EP)</v>
       </c>
       <c r="G194" t="str">
-        <v>2:54</v>
+        <v>2:55</v>
       </c>
       <c r="H194" t="str">
-        <v>Johnny Huynh</v>
+        <v>Nia Smith</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/johnny-huynh/1708540956</v>
+        <v>https://music.apple.com/us/artist/nia-smith/1755576018</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/heavens-on-fire/6771110729</v>
+        <v>https://music.apple.com/us/album/high/6773775203</v>
       </c>
       <c r="L194" t="str">
-        <v>HEAVEN'S ON FIRE - Johnny Huynh</v>
+        <v>High - Nia Smith</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Fallen Angel</v>
+        <v>Ay Gyal</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/fallen-angel/6771161222</v>
+        <v>https://music.apple.com/us/song/ay-gyal/6771885805</v>
       </c>
       <c r="D195" t="str">
         <v>2026-06-02</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>You Don't Know My Name</v>
+        <v>Ay Gyal - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>3:05</v>
+        <v>2:12</v>
       </c>
       <c r="H195" t="str">
-        <v>Baby J</v>
+        <v>1Ski OG</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/baby-j/1513690931</v>
+        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/fallen-angel/6771161180</v>
+        <v>https://music.apple.com/us/album/ay-gyal/6771885803</v>
       </c>
       <c r="L195" t="str">
-        <v>Fallen Angel - Baby J</v>
+        <v>Ay Gyal - 1Ski OG</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>The Last Encounter</v>
+        <v>always knew</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/the-last-encounter/6767395134</v>
+        <v>https://music.apple.com/us/song/always-knew/6762864274</v>
       </c>
       <c r="D196" t="str">
         <v>2026-06-02</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>The Last Encounter - Single</v>
+        <v>always knew - Single</v>
       </c>
       <c r="G196" t="str">
-        <v>3:04</v>
+        <v>3:25</v>
       </c>
       <c r="H196" t="str">
-        <v>Sofia Camara</v>
+        <v>Biscits</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/sofia-camara/1506432156</v>
+        <v>https://music.apple.com/us/artist/biscits/1185553226</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/the-last-encounter/6767395133</v>
+        <v>https://music.apple.com/us/album/always-knew/1895047928</v>
       </c>
       <c r="L196" t="str">
-        <v>The Last Encounter - Sofia Camara</v>
+        <v>always knew - Biscits</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>we fall</v>
+        <v>Cigarette Burns</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/we-fall/6769218917</v>
+        <v>https://music.apple.com/us/song/cigarette-burns/6770691000</v>
       </c>
       <c r="D197" t="str">
         <v>2026-06-02</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>we fall - Single</v>
+        <v>Heartland Rock and Roll</v>
       </c>
       <c r="G197" t="str">
-        <v>4:01</v>
+        <v>2:41</v>
       </c>
       <c r="H197" t="str">
-        <v>MOIO</v>
+        <v>Corey Kent</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/moio/1664183608</v>
+        <v>https://music.apple.com/us/artist/corey-kent/1171544097</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/we-fall/6769218915</v>
+        <v>https://music.apple.com/us/album/cigarette-burns/6770690867</v>
       </c>
       <c r="L197" t="str">
-        <v>we fall - MOIO</v>
+        <v>Cigarette Burns - Corey Kent</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>You Don't Know Me</v>
+        <v>Let You Down</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/you-dont-know-me/6769214417</v>
+        <v>https://music.apple.com/us/song/let-you-down/6773362320</v>
       </c>
       <c r="D198" t="str">
         <v>2026-06-02</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>You Don’t Know Me - Single</v>
+        <v>El Relevo</v>
       </c>
       <c r="G198" t="str">
-        <v>3:50</v>
+        <v>4:14</v>
       </c>
       <c r="H198" t="str">
-        <v>Isabel Dumaa</v>
+        <v>Luis Figueroa</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/isabel-dumaa/1631481156</v>
+        <v>https://music.apple.com/us/artist/luis-figueroa/395266944</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/you-dont-know-me/6769214410</v>
+        <v>https://music.apple.com/us/album/let-you-down/6773362108</v>
       </c>
       <c r="L198" t="str">
-        <v>You Don't Know Me - Isabel Dumaa</v>
+        <v>Let You Down - Luis Figueroa</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Hold Up, Say What?</v>
+        <v>Starless</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/hold-up-say-what/1879853511</v>
+        <v>https://music.apple.com/us/song/starless/6770568779</v>
       </c>
       <c r="D199" t="str">
         <v>2026-06-02</v>
@@ -7937,36 +7937,36 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>House Of Mirrors</v>
+        <v>Starless - Single</v>
       </c>
       <c r="G199" t="str">
-        <v>4:04</v>
+        <v>4:32</v>
       </c>
       <c r="H199" t="str">
-        <v>All Them Witches</v>
+        <v>A Perfect Circle</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/all-them-witches/534924603</v>
+        <v>https://music.apple.com/us/artist/a-perfect-circle/652503</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/hold-up-say-what/1879853502</v>
+        <v>https://music.apple.com/us/album/starless/6770568776</v>
       </c>
       <c r="L199" t="str">
-        <v>Hold Up, Say What? - All Them Witches</v>
+        <v>Starless - A Perfect Circle</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Iodine</v>
+        <v>Looking For You</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/iodine/1871211805</v>
+        <v>https://music.apple.com/us/song/looking-for-you/6768355609</v>
       </c>
       <c r="D200" t="str">
         <v>2026-06-02</v>
@@ -7975,36 +7975,36 @@
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>Neverending</v>
+        <v>Looking For You - Single</v>
       </c>
       <c r="G200" t="str">
-        <v>3:40</v>
+        <v>3:19</v>
       </c>
       <c r="H200" t="str">
-        <v>Monolord</v>
+        <v>Gable Price and Friends</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/monolord/833749384</v>
+        <v>https://music.apple.com/us/artist/gable-price-and-friends/1441378212</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/iodine/1871211801</v>
+        <v>https://music.apple.com/us/album/looking-for-you/6768355596</v>
       </c>
       <c r="L200" t="str">
-        <v>Iodine - Monolord</v>
+        <v>Looking For You - Gable Price and Friends</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>I Speak Forgotten Voices</v>
+        <v>FOCUSED</v>
       </c>
       <c r="B201" t="str">
         <v/>
       </c>
       <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/i-speak-forgotten-voices/1878083625</v>
+        <v>https://music.apple.com/us/song/focused/1887909237</v>
       </c>
       <c r="D201" t="str">
         <v>2026-06-02</v>
@@ -8013,68 +8013,752 @@
         <v/>
       </c>
       <c r="F201" t="str">
-        <v>...By the Word...</v>
+        <v>FOCUSED - Single</v>
       </c>
       <c r="G201" t="str">
-        <v>5:01</v>
+        <v>2:23</v>
       </c>
       <c r="H201" t="str">
-        <v>Trelldom</v>
+        <v>Shepherd</v>
       </c>
       <c r="I201" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/trelldom/256586618</v>
+        <v>https://music.apple.com/us/artist/shepherd/1192803216</v>
       </c>
       <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/i-speak-forgotten-voices/1878083622</v>
+        <v>https://music.apple.com/us/album/focused/1887909236</v>
       </c>
       <c r="L201" t="str">
-        <v>I Speak Forgotten Voices - Trelldom</v>
+        <v>FOCUSED - Shepherd</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
+        <v>Tú Ni En Cuenta</v>
+      </c>
+      <c r="B202" t="str">
+        <v/>
+      </c>
+      <c r="C202" t="str">
+        <v>https://music.apple.com/us/song/tu-ni-en-cuenta/6767701804</v>
+      </c>
+      <c r="D202" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="E202" t="str">
+        <v/>
+      </c>
+      <c r="F202" t="str">
+        <v>Tú Ni En Cuenta - Single</v>
+      </c>
+      <c r="G202" t="str">
+        <v>3:23</v>
+      </c>
+      <c r="H202" t="str">
+        <v>Banda MS de Sergio Lizárraga</v>
+      </c>
+      <c r="I202" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J202" t="str">
+        <v>https://music.apple.com/us/artist/banda-ms-de-sergio-liz%C3%A1rraga/413048014</v>
+      </c>
+      <c r="K202" t="str">
+        <v>https://music.apple.com/us/album/tu-ni-en-cuenta/6767701803</v>
+      </c>
+      <c r="L202" t="str">
+        <v>Tú Ni En Cuenta - Banda MS de Sergio Lizárraga</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
+        <v>dream state</v>
+      </c>
+      <c r="B203" t="str">
+        <v/>
+      </c>
+      <c r="C203" t="str">
+        <v>https://music.apple.com/us/song/dream-state/6765596009</v>
+      </c>
+      <c r="D203" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="E203" t="str">
+        <v/>
+      </c>
+      <c r="F203" t="str">
+        <v>dream state - Single</v>
+      </c>
+      <c r="G203" t="str">
+        <v>4:01</v>
+      </c>
+      <c r="H203" t="str">
+        <v>Martin Luke Brown</v>
+      </c>
+      <c r="I203" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J203" t="str">
+        <v>https://music.apple.com/us/artist/martin-luke-brown/883292185</v>
+      </c>
+      <c r="K203" t="str">
+        <v>https://music.apple.com/us/album/dream-state/1896004790</v>
+      </c>
+      <c r="L203" t="str">
+        <v>dream state - Martin Luke Brown</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
+        <v>Needle (feat. Spencer Cullum)</v>
+      </c>
+      <c r="B204" t="str">
+        <v/>
+      </c>
+      <c r="C204" t="str">
+        <v>https://music.apple.com/us/song/needle-feat-spencer-cullum/6767618217</v>
+      </c>
+      <c r="D204" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="E204" t="str">
+        <v/>
+      </c>
+      <c r="F204" t="str">
+        <v>Needle (feat. Spencer Cullum) - Single</v>
+      </c>
+      <c r="G204" t="str">
+        <v>3:39</v>
+      </c>
+      <c r="H204" t="str">
+        <v>Mynolia</v>
+      </c>
+      <c r="I204" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J204" t="str">
+        <v>https://music.apple.com/us/artist/mynolia/1444347510</v>
+      </c>
+      <c r="K204" t="str">
+        <v>https://music.apple.com/us/album/needle-feat-spencer-cullum/6767618203</v>
+      </c>
+      <c r="L204" t="str">
+        <v>Needle (feat. Spencer Cullum) - Mynolia</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v>You Retreat In Time And Space</v>
+      </c>
+      <c r="B205" t="str">
+        <v/>
+      </c>
+      <c r="C205" t="str">
+        <v>https://music.apple.com/us/song/you-retreat-in-time-and-space/1890015660</v>
+      </c>
+      <c r="D205" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="E205" t="str">
+        <v/>
+      </c>
+      <c r="F205" t="str">
+        <v>Inferno</v>
+      </c>
+      <c r="G205" t="str">
+        <v>5:25</v>
+      </c>
+      <c r="H205" t="str">
+        <v>Boards of Canada</v>
+      </c>
+      <c r="I205" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J205" t="str">
+        <v>https://music.apple.com/us/artist/boards-of-canada/2989314</v>
+      </c>
+      <c r="K205" t="str">
+        <v>https://music.apple.com/us/album/you-retreat-in-time-and-space/1890015523</v>
+      </c>
+      <c r="L205" t="str">
+        <v>You Retreat In Time And Space - Boards of Canada</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="str">
+        <v>It's Happening (To Me)</v>
+      </c>
+      <c r="B206" t="str">
+        <v/>
+      </c>
+      <c r="C206" t="str">
+        <v>https://music.apple.com/us/song/its-happening-to-me/6764723461</v>
+      </c>
+      <c r="D206" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="E206" t="str">
+        <v/>
+      </c>
+      <c r="F206" t="str">
+        <v>It's Happening (To Me) - Single</v>
+      </c>
+      <c r="G206" t="str">
+        <v>2:34</v>
+      </c>
+      <c r="H206" t="str">
+        <v>Delroy Edwards</v>
+      </c>
+      <c r="I206" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J206" t="str">
+        <v>https://music.apple.com/us/artist/delroy-edwards/591790909</v>
+      </c>
+      <c r="K206" t="str">
+        <v>https://music.apple.com/us/album/its-happening-to-me/1895893472</v>
+      </c>
+      <c r="L206" t="str">
+        <v>It's Happening (To Me) - Delroy Edwards</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
+        <v>FCUK</v>
+      </c>
+      <c r="B207" t="str">
+        <v/>
+      </c>
+      <c r="C207" t="str">
+        <v>https://music.apple.com/us/song/fcuk/6769623577</v>
+      </c>
+      <c r="D207" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="E207" t="str">
+        <v/>
+      </c>
+      <c r="F207" t="str">
+        <v>FCUK - Single</v>
+      </c>
+      <c r="G207" t="str">
+        <v>2:22</v>
+      </c>
+      <c r="H207" t="str">
+        <v>H.LLS</v>
+      </c>
+      <c r="I207" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J207" t="str">
+        <v>https://music.apple.com/us/artist/h-lls/1751287958</v>
+      </c>
+      <c r="K207" t="str">
+        <v>https://music.apple.com/us/album/fcuk/6769623566</v>
+      </c>
+      <c r="L207" t="str">
+        <v>FCUK - H.LLS</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="str">
+        <v>Higher</v>
+      </c>
+      <c r="B208" t="str">
+        <v/>
+      </c>
+      <c r="C208" t="str">
+        <v>https://music.apple.com/us/song/higher/1880124200</v>
+      </c>
+      <c r="D208" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="E208" t="str">
+        <v/>
+      </c>
+      <c r="F208" t="str">
+        <v>Run, Run Pure Beauty</v>
+      </c>
+      <c r="G208" t="str">
+        <v>4:06</v>
+      </c>
+      <c r="H208" t="str">
+        <v>Francis of Delirium</v>
+      </c>
+      <c r="I208" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J208" t="str">
+        <v>https://music.apple.com/us/artist/francis-of-delirium/1485902996</v>
+      </c>
+      <c r="K208" t="str">
+        <v>https://music.apple.com/us/album/higher/1880123731</v>
+      </c>
+      <c r="L208" t="str">
+        <v>Higher - Francis of Delirium</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="str">
+        <v>B.U.N</v>
+      </c>
+      <c r="B209" t="str">
+        <v/>
+      </c>
+      <c r="C209" t="str">
+        <v>https://music.apple.com/us/song/b-u-n/6763272338</v>
+      </c>
+      <c r="D209" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="E209" t="str">
+        <v/>
+      </c>
+      <c r="F209" t="str">
+        <v>B.U.N - Single</v>
+      </c>
+      <c r="G209" t="str">
+        <v>3:43</v>
+      </c>
+      <c r="H209" t="str">
+        <v>Roll Deep</v>
+      </c>
+      <c r="I209" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J209" t="str">
+        <v>https://music.apple.com/us/artist/roll-deep/3083873</v>
+      </c>
+      <c r="K209" t="str">
+        <v>https://music.apple.com/us/album/b-u-n/1895242397</v>
+      </c>
+      <c r="L209" t="str">
+        <v>B.U.N - Roll Deep</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="str">
+        <v>Only Love (feat. Pa Salieu)</v>
+      </c>
+      <c r="B210" t="str">
+        <v/>
+      </c>
+      <c r="C210" t="str">
+        <v>https://music.apple.com/us/song/only-love-feat-pa-salieu/6767014290</v>
+      </c>
+      <c r="D210" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="E210" t="str">
+        <v/>
+      </c>
+      <c r="F210" t="str">
+        <v>Here Because of Hope</v>
+      </c>
+      <c r="G210" t="str">
+        <v>3:22</v>
+      </c>
+      <c r="H210" t="str">
+        <v>Ezra Collective</v>
+      </c>
+      <c r="I210" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J210" t="str">
+        <v>https://music.apple.com/us/artist/ezra-collective/1103640281</v>
+      </c>
+      <c r="K210" t="str">
+        <v>https://music.apple.com/us/album/only-love-feat-pa-salieu/6767014278</v>
+      </c>
+      <c r="L210" t="str">
+        <v>Only Love (feat. Pa Salieu) - Ezra Collective</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="str">
+        <v>Beautiful Things 1st scene/audition</v>
+      </c>
+      <c r="B211" t="str">
+        <v/>
+      </c>
+      <c r="C211" t="str">
+        <v>https://music.apple.com/us/song/beautiful-things-1st-scene-audition/6771942631</v>
+      </c>
+      <c r="D211" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="E211" t="str">
+        <v/>
+      </c>
+      <c r="F211" t="str">
+        <v>UNDRA</v>
+      </c>
+      <c r="G211" t="str">
+        <v>2:49</v>
+      </c>
+      <c r="H211" t="str">
+        <v>reggie</v>
+      </c>
+      <c r="I211" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J211" t="str">
+        <v>https://music.apple.com/us/artist/reggie/1526587068</v>
+      </c>
+      <c r="K211" t="str">
+        <v>https://music.apple.com/us/album/beautiful-things-1st-scene-audition/6771942630</v>
+      </c>
+      <c r="L211" t="str">
+        <v>Beautiful Things 1st scene/audition - reggie</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="str">
+        <v>HEAVEN'S ON FIRE</v>
+      </c>
+      <c r="B212" t="str">
+        <v/>
+      </c>
+      <c r="C212" t="str">
+        <v>https://music.apple.com/us/song/heavens-on-fire/6771110730</v>
+      </c>
+      <c r="D212" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="E212" t="str">
+        <v/>
+      </c>
+      <c r="F212" t="str">
+        <v>HEAVEN'S ON FIRE</v>
+      </c>
+      <c r="G212" t="str">
+        <v>2:54</v>
+      </c>
+      <c r="H212" t="str">
+        <v>Johnny Huynh</v>
+      </c>
+      <c r="I212" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J212" t="str">
+        <v>https://music.apple.com/us/artist/johnny-huynh/1708540956</v>
+      </c>
+      <c r="K212" t="str">
+        <v>https://music.apple.com/us/album/heavens-on-fire/6771110729</v>
+      </c>
+      <c r="L212" t="str">
+        <v>HEAVEN'S ON FIRE - Johnny Huynh</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="str">
+        <v>Fallen Angel</v>
+      </c>
+      <c r="B213" t="str">
+        <v/>
+      </c>
+      <c r="C213" t="str">
+        <v>https://music.apple.com/us/song/fallen-angel/6771161222</v>
+      </c>
+      <c r="D213" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="E213" t="str">
+        <v/>
+      </c>
+      <c r="F213" t="str">
+        <v>You Don't Know My Name</v>
+      </c>
+      <c r="G213" t="str">
+        <v>3:05</v>
+      </c>
+      <c r="H213" t="str">
+        <v>Baby J</v>
+      </c>
+      <c r="I213" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J213" t="str">
+        <v>https://music.apple.com/us/artist/baby-j/1513690931</v>
+      </c>
+      <c r="K213" t="str">
+        <v>https://music.apple.com/us/album/fallen-angel/6771161180</v>
+      </c>
+      <c r="L213" t="str">
+        <v>Fallen Angel - Baby J</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="str">
+        <v>The Last Encounter</v>
+      </c>
+      <c r="B214" t="str">
+        <v/>
+      </c>
+      <c r="C214" t="str">
+        <v>https://music.apple.com/us/song/the-last-encounter/6767395134</v>
+      </c>
+      <c r="D214" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="E214" t="str">
+        <v/>
+      </c>
+      <c r="F214" t="str">
+        <v>The Last Encounter - Single</v>
+      </c>
+      <c r="G214" t="str">
+        <v>3:04</v>
+      </c>
+      <c r="H214" t="str">
+        <v>Sofia Camara</v>
+      </c>
+      <c r="I214" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J214" t="str">
+        <v>https://music.apple.com/us/artist/sofia-camara/1506432156</v>
+      </c>
+      <c r="K214" t="str">
+        <v>https://music.apple.com/us/album/the-last-encounter/6767395133</v>
+      </c>
+      <c r="L214" t="str">
+        <v>The Last Encounter - Sofia Camara</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="str">
+        <v>we fall</v>
+      </c>
+      <c r="B215" t="str">
+        <v/>
+      </c>
+      <c r="C215" t="str">
+        <v>https://music.apple.com/us/song/we-fall/6769218917</v>
+      </c>
+      <c r="D215" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="E215" t="str">
+        <v/>
+      </c>
+      <c r="F215" t="str">
+        <v>we fall - Single</v>
+      </c>
+      <c r="G215" t="str">
+        <v>4:01</v>
+      </c>
+      <c r="H215" t="str">
+        <v>MOIO</v>
+      </c>
+      <c r="I215" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J215" t="str">
+        <v>https://music.apple.com/us/artist/moio/1664183608</v>
+      </c>
+      <c r="K215" t="str">
+        <v>https://music.apple.com/us/album/we-fall/6769218915</v>
+      </c>
+      <c r="L215" t="str">
+        <v>we fall - MOIO</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="str">
+        <v>You Don't Know Me</v>
+      </c>
+      <c r="B216" t="str">
+        <v/>
+      </c>
+      <c r="C216" t="str">
+        <v>https://music.apple.com/us/song/you-dont-know-me/6769214417</v>
+      </c>
+      <c r="D216" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="E216" t="str">
+        <v/>
+      </c>
+      <c r="F216" t="str">
+        <v>You Don’t Know Me - Single</v>
+      </c>
+      <c r="G216" t="str">
+        <v>3:50</v>
+      </c>
+      <c r="H216" t="str">
+        <v>Isabel Dumaa</v>
+      </c>
+      <c r="I216" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J216" t="str">
+        <v>https://music.apple.com/us/artist/isabel-dumaa/1631481156</v>
+      </c>
+      <c r="K216" t="str">
+        <v>https://music.apple.com/us/album/you-dont-know-me/6769214410</v>
+      </c>
+      <c r="L216" t="str">
+        <v>You Don't Know Me - Isabel Dumaa</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="str">
+        <v>Hold Up, Say What?</v>
+      </c>
+      <c r="B217" t="str">
+        <v/>
+      </c>
+      <c r="C217" t="str">
+        <v>https://music.apple.com/us/song/hold-up-say-what/1879853511</v>
+      </c>
+      <c r="D217" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="E217" t="str">
+        <v/>
+      </c>
+      <c r="F217" t="str">
+        <v>House Of Mirrors</v>
+      </c>
+      <c r="G217" t="str">
+        <v>4:04</v>
+      </c>
+      <c r="H217" t="str">
+        <v>All Them Witches</v>
+      </c>
+      <c r="I217" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J217" t="str">
+        <v>https://music.apple.com/us/artist/all-them-witches/534924603</v>
+      </c>
+      <c r="K217" t="str">
+        <v>https://music.apple.com/us/album/hold-up-say-what/1879853502</v>
+      </c>
+      <c r="L217" t="str">
+        <v>Hold Up, Say What? - All Them Witches</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="str">
+        <v>Iodine</v>
+      </c>
+      <c r="B218" t="str">
+        <v/>
+      </c>
+      <c r="C218" t="str">
+        <v>https://music.apple.com/us/song/iodine/1871211805</v>
+      </c>
+      <c r="D218" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="E218" t="str">
+        <v/>
+      </c>
+      <c r="F218" t="str">
+        <v>Neverending</v>
+      </c>
+      <c r="G218" t="str">
+        <v>3:40</v>
+      </c>
+      <c r="H218" t="str">
+        <v>Monolord</v>
+      </c>
+      <c r="I218" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J218" t="str">
+        <v>https://music.apple.com/us/artist/monolord/833749384</v>
+      </c>
+      <c r="K218" t="str">
+        <v>https://music.apple.com/us/album/iodine/1871211801</v>
+      </c>
+      <c r="L218" t="str">
+        <v>Iodine - Monolord</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="str">
+        <v>I Speak Forgotten Voices</v>
+      </c>
+      <c r="B219" t="str">
+        <v/>
+      </c>
+      <c r="C219" t="str">
+        <v>https://music.apple.com/us/song/i-speak-forgotten-voices/1878083625</v>
+      </c>
+      <c r="D219" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="E219" t="str">
+        <v/>
+      </c>
+      <c r="F219" t="str">
+        <v>...By the Word...</v>
+      </c>
+      <c r="G219" t="str">
+        <v>5:01</v>
+      </c>
+      <c r="H219" t="str">
+        <v>Trelldom</v>
+      </c>
+      <c r="I219" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J219" t="str">
+        <v>https://music.apple.com/us/artist/trelldom/256586618</v>
+      </c>
+      <c r="K219" t="str">
+        <v>https://music.apple.com/us/album/i-speak-forgotten-voices/1878083622</v>
+      </c>
+      <c r="L219" t="str">
+        <v>I Speak Forgotten Voices - Trelldom</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="str">
         <v>Rats in the Temple</v>
       </c>
-      <c r="B202" t="str">
-        <v/>
-      </c>
-      <c r="C202" t="str">
+      <c r="B220" t="str">
+        <v/>
+      </c>
+      <c r="C220" t="str">
         <v>https://music.apple.com/us/song/rats-in-the-temple/6764627559</v>
       </c>
-      <c r="D202" t="str">
-        <v>2026-06-02</v>
-      </c>
-      <c r="E202" t="str">
-        <v/>
-      </c>
-      <c r="F202" t="str">
+      <c r="D220" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="E220" t="str">
+        <v/>
+      </c>
+      <c r="F220" t="str">
         <v>Rats in the Temple</v>
       </c>
-      <c r="G202" t="str">
+      <c r="G220" t="str">
         <v>4:45</v>
       </c>
-      <c r="H202" t="str">
+      <c r="H220" t="str">
         <v>Flotsam and Jetsam</v>
       </c>
-      <c r="I202" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J202" t="str">
+      <c r="I220" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J220" t="str">
         <v>https://music.apple.com/us/artist/flotsam-and-jetsam/162270</v>
       </c>
-      <c r="K202" t="str">
+      <c r="K220" t="str">
         <v>https://music.apple.com/us/album/rats-in-the-temple/1895855647</v>
       </c>
-      <c r="L202" t="str">
+      <c r="L220" t="str">
         <v>Rats in the Temple - Flotsam and Jetsam</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L202"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L220"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-06-week01/titles.xlsx
+++ b/data/global/2026-06-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L220"/>
+  <dimension ref="A1:L203"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>סטטיק &amp; רינת בר - אקסטרה לארג'</v>
+        <v>משינה – כמעט וכאילו</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411179&amp;sid=13e1d521681219f1f5cc74f85473f139</v>
+        <v>https://yosmusic.com/%d7%9e%d7%a9%d7%99%d7%a0%d7%94-%d7%9b%d7%9e%d7%a2%d7%98-%d7%95%d7%9b%d7%90%d7%99%d7%9c%d7%95/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>"כמעט כאילו" של משינה  מגיע אחרי יותר מארבעה עשורים של יצירה. במקום להציג הצהרה חגיגית או נוסטלגית על 40 שנות קריירה, משינה בוחרת לכתוב שיר על בלבול, ספק, מציאות מתעתעת וחוסר יכולת להכריע. במובן הזה, הוא נשמע מאוד עכשווי למרות</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,27 +469,27 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>סטטיק &amp; רינת בר - אקסטרה לארג'</v>
+        <v>משינה – כמעט וכאילו</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>רועי מזוז &amp; שילה בן אברהם - הסיפור של ג'וני</v>
+        <v>מייזי פיטרס Florescence</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411178&amp;sid=13e1d521681219f1f5cc74f85473f139</v>
+        <v>https://yosmusic.com/%d7%9e%d7%99%d7%99%d7%96%d7%99-%d7%a4%d7%99%d7%98%d7%a8%d7%a1-florescence/</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v/>
+        <v>החיים נראים מעט אחרת עבור מייזי פיטרס. מאז יציאת  אלבומה השני, "The Good Witch" מ-2023.  באלבומה השלישי, כוכבת הפופ הבריטית משחררת את הכאב ומוצאת שלווה באהבת אמת. בדיוק כשהקריירה שלה צברה תאוצה לקראת סוף 2024, הזמרת שנבחרה לחמם את ההופעות</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -498,7 +498,7 @@
         <v/>
       </c>
       <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -507,36 +507,36 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>רועי מזוז &amp; שילה בן אברהם - הסיפור של ג'וני</v>
+        <v>מייזי פיטרס Florescence</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>עופר סופר - טוב ומטיב</v>
+        <v>Billy Idol - John Wayne feat. Alison Mosshart (Official Music Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-06-02</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411177&amp;sid=13e1d521681219f1f5cc74f85473f139</v>
+        <v>https://www.youtube.com/watch?v=47LNk7oiTVI</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v/>
+        <v>16 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
       </c>
       <c r="H4" t="str">
-        <v/>
+        <v>Billy Idol</v>
       </c>
       <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -545,36 +545,36 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>עופר סופר - טוב ומטיב</v>
+        <v>Billy Idol - John Wayne feat. Alison Mosshart (Official Music Video) - Billy Idol</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>משינה - כמעט וכאילו</v>
+        <v>'It's Unusual' Official Music Video - Kelly Boesch | 4K</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-06-02</v>
+        <v>4 days ago</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411176&amp;sid=13e1d521681219f1f5cc74f85473f139</v>
+        <v>https://www.youtube.com/watch?v=Ru3fB2l1RSo</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E5" t="str">
         <v/>
       </c>
       <c r="F5" t="str">
-        <v/>
+        <v>4 days ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
       </c>
       <c r="H5" t="str">
-        <v/>
+        <v>Kelly Boesch AI Art</v>
       </c>
       <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -583,36 +583,36 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>משינה - כמעט וכאילו</v>
+        <v>'It's Unusual' Official Music Video - Kelly Boesch | 4K - Kelly Boesch AI Art</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>מיכאל כורש - שלוש בלילה</v>
+        <v>Icona Pop - Butterfly Feelings (Official Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-06-02</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411175&amp;sid=13e1d521681219f1f5cc74f85473f139</v>
+        <v>https://www.youtube.com/watch?v=AMW1Zq9RbIU</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E6" t="str">
         <v/>
       </c>
       <c r="F6" t="str">
-        <v/>
+        <v>18 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
       </c>
       <c r="H6" t="str">
-        <v/>
+        <v>Icona Pop</v>
       </c>
       <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -621,36 +621,36 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>מיכאל כורש - שלוש בלילה</v>
+        <v>Icona Pop - Butterfly Feelings (Official Video) - Icona Pop</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>יובל לוי מארחת את דין פרינס גבאי - פאקים</v>
+        <v>Hippo Campus - South</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-06-02</v>
+        <v>1 day ago</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411174&amp;sid=13e1d521681219f1f5cc74f85473f139</v>
+        <v>https://www.youtube.com/watch?v=FYOmFfV7Ojo</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E7" t="str">
         <v/>
       </c>
       <c r="F7" t="str">
-        <v/>
+        <v>1 day ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v/>
+        <v>Hippo Campus</v>
       </c>
       <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J7" t="str">
         <v/>
@@ -659,36 +659,36 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>יובל לוי מארחת את דין פרינס גבאי - פאקים</v>
+        <v>Hippo Campus - South - Hippo Campus</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>יובל לוי - החיה</v>
+        <v>elijah woods - Old (Treehouse Sessions)</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-06-02</v>
+        <v>1 day ago</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411173&amp;sid=13e1d521681219f1f5cc74f85473f139</v>
+        <v>https://www.youtube.com/watch?v=yDlkPdR_6zM</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E8" t="str">
         <v/>
       </c>
       <c r="F8" t="str">
-        <v/>
+        <v>1 day ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8" t="str">
-        <v/>
+        <v>elijah woods</v>
       </c>
       <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -697,36 +697,36 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>יובל לוי - החיה</v>
+        <v>elijah woods - Old (Treehouse Sessions) - elijah woods</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>שניאור אוראל - שערי שמים פתח</v>
+        <v>Nothing But Thieves - Evolution (Official Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-06-02</v>
+        <v>1 day ago</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411172&amp;sid=13e1d521681219f1f5cc74f85473f139</v>
+        <v>https://www.youtube.com/watch?v=hmjfuuuRRYU</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E9" t="str">
         <v/>
       </c>
       <c r="F9" t="str">
-        <v/>
+        <v>1 day ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v/>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J9" t="str">
         <v/>
@@ -735,36 +735,36 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>שניאור אוראל - שערי שמים פתח</v>
+        <v>Nothing But Thieves - Evolution (Official Video) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>מתנאל אסייג - תדר</v>
+        <v>Ariana Grande - hate that i made you love me (official music video)</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-06-02</v>
+        <v>1 day ago</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411171&amp;sid=13e1d521681219f1f5cc74f85473f139</v>
+        <v>https://www.youtube.com/watch?v=82-jTNka3uc</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E10" t="str">
         <v/>
       </c>
       <c r="F10" t="str">
-        <v/>
+        <v>1 day ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v/>
+        <v>Ariana Grande</v>
       </c>
       <c r="I10" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J10" t="str">
         <v/>
@@ -773,36 +773,36 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>מתנאל אסייג - תדר</v>
+        <v>Ariana Grande - hate that i made you love me (official music video) - Ariana Grande</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>ליאל אוחיון - היית גבר</v>
+        <v>LAUREL - Fire Breather</v>
       </c>
       <c r="B11" t="str">
-        <v>2026-06-02</v>
+        <v>1 day ago</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411170&amp;sid=13e1d521681219f1f5cc74f85473f139</v>
+        <v>https://www.youtube.com/watch?v=rtyavLIJjy0</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E11" t="str">
         <v/>
       </c>
       <c r="F11" t="str">
-        <v/>
+        <v>1 day ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v/>
+        <v>LAUREL</v>
       </c>
       <c r="I11" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J11" t="str">
         <v/>
@@ -811,36 +811,36 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>ליאל אוחיון - היית גבר</v>
+        <v>LAUREL - Fire Breather - LAUREL</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ישראל ברששת - מחרוזת מהנשמה 2026</v>
+        <v>The Warning - Ego (Performance Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>2026-06-02</v>
+        <v>3 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411169&amp;sid=13e1d521681219f1f5cc74f85473f139</v>
+        <v>https://www.youtube.com/watch?v=7PApWObImjo</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E12" t="str">
         <v/>
       </c>
       <c r="F12" t="str">
-        <v/>
+        <v>3 days ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
       </c>
       <c r="H12" t="str">
-        <v/>
+        <v>The Warning</v>
       </c>
       <c r="I12" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J12" t="str">
         <v/>
@@ -849,36 +849,36 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>ישראל ברששת - מחרוזת מהנשמה 2026</v>
+        <v>The Warning - Ego (Performance Video) - The Warning</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>ישעיהו - תשמור חזק</v>
+        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (feat. Gabito Ballesteros) [Official Lyric Video]</v>
       </c>
       <c r="B13" t="str">
-        <v>2026-06-02</v>
+        <v>3 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411168&amp;sid=13e1d521681219f1f5cc74f85473f139</v>
+        <v>https://www.youtube.com/watch?v=vruZSAYJBe4</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E13" t="str">
         <v/>
       </c>
       <c r="F13" t="str">
-        <v/>
+        <v>3 days ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
       </c>
       <c r="H13" t="str">
-        <v/>
+        <v>David Guetta and Jennifer Lopez</v>
       </c>
       <c r="I13" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J13" t="str">
         <v/>
@@ -887,36 +887,36 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>ישעיהו - תשמור חזק</v>
+        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (feat. Gabito Ballesteros) [Official Lyric Video] - David Guetta and Jennifer Lopez</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>יוסף חיים - איש שחולם געגוע</v>
+        <v>Armin van Buuren - Equanimity (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B14" t="str">
-        <v>2026-06-02</v>
+        <v>3 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411167&amp;sid=13e1d521681219f1f5cc74f85473f139</v>
+        <v>https://www.youtube.com/watch?v=k93t10R-Qrg</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E14" t="str">
         <v/>
       </c>
       <c r="F14" t="str">
-        <v/>
+        <v>3 days ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
       </c>
       <c r="H14" t="str">
-        <v/>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I14" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J14" t="str">
         <v/>
@@ -925,36 +925,36 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>יוסף חיים - איש שחולם געגוע</v>
+        <v>Armin van Buuren - Equanimity (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>יהונתן ישראל - רק לעלות</v>
+        <v>“I Didn’t Know What Time It Was” - Andrew Bird Jazz Trio (Live from The Green Mill)</v>
       </c>
       <c r="B15" t="str">
-        <v>2026-06-02</v>
+        <v>4 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411166&amp;sid=13e1d521681219f1f5cc74f85473f139</v>
+        <v>https://www.youtube.com/watch?v=XyRgdfXo2nI</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E15" t="str">
         <v/>
       </c>
       <c r="F15" t="str">
-        <v/>
+        <v>4 days ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
       </c>
       <c r="H15" t="str">
-        <v/>
+        <v>Andrew Bird</v>
       </c>
       <c r="I15" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J15" t="str">
         <v/>
@@ -963,36 +963,36 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>יהונתן ישראל - רק לעלות</v>
+        <v>“I Didn’t Know What Time It Was” - Andrew Bird Jazz Trio (Live from The Green Mill) - Andrew Bird</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>חן כהן - תל גיבורים</v>
+        <v>Freya Ridings - Mother Of Pearl (Official Lyric Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>2026-06-02</v>
+        <v>4 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411165&amp;sid=13e1d521681219f1f5cc74f85473f139</v>
+        <v>https://www.youtube.com/watch?v=7SGzYAZ0oxM</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E16" t="str">
         <v/>
       </c>
       <c r="F16" t="str">
-        <v/>
+        <v>4 days ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
       </c>
       <c r="H16" t="str">
-        <v/>
+        <v>Freya Ridings</v>
       </c>
       <c r="I16" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J16" t="str">
         <v/>
@@ -1001,36 +1001,36 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>חן כהן - תל גיבורים</v>
+        <v>Freya Ridings - Mother Of Pearl (Official Lyric Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>הייפ קרו - אהבה עיוורת</v>
+        <v>Danny Gokey - God's Not (Official Music Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>2026-06-02</v>
+        <v>4 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411164&amp;sid=13e1d521681219f1f5cc74f85473f139</v>
+        <v>https://www.youtube.com/watch?v=oGpKqX6ftcU</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E17" t="str">
         <v/>
       </c>
       <c r="F17" t="str">
-        <v/>
+        <v>4 days ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
       </c>
       <c r="H17" t="str">
-        <v/>
+        <v>Danny Gokey</v>
       </c>
       <c r="I17" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J17" t="str">
         <v/>
@@ -1039,36 +1039,36 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>הייפ קרו - אהבה עיוורת</v>
+        <v>Danny Gokey - God's Not (Official Music Video) - Danny Gokey</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>אלינור חלילוב - מחרוזת קיץ 2026</v>
+        <v>Armik - Brisas (2026 Remaster/Remix) (Exciting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B18" t="str">
-        <v>2026-06-02</v>
+        <v>4 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411163&amp;sid=13e1d521681219f1f5cc74f85473f139</v>
+        <v>https://www.youtube.com/watch?v=51Zu2iU2z2Q</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E18" t="str">
         <v/>
       </c>
       <c r="F18" t="str">
-        <v/>
+        <v>4 days ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
       </c>
       <c r="H18" t="str">
-        <v/>
+        <v>Armik</v>
       </c>
       <c r="I18" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J18" t="str">
         <v/>
@@ -1077,36 +1077,36 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>אלינור חלילוב - מחרוזת קיץ 2026</v>
+        <v>Armik - Brisas (2026 Remaster/Remix) (Exciting Rumba Flamenco, Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>אברהם חתומה - כשהלב בקרשים</v>
+        <v>Holly Humberstone - Lucy (Free People Sessions)</v>
       </c>
       <c r="B19" t="str">
-        <v>2026-06-02</v>
+        <v>4 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411162&amp;sid=13e1d521681219f1f5cc74f85473f139</v>
+        <v>https://www.youtube.com/watch?v=c1GR2TTs9W8</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E19" t="str">
         <v/>
       </c>
       <c r="F19" t="str">
-        <v/>
+        <v>4 days ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
       </c>
       <c r="H19" t="str">
-        <v/>
+        <v>Holly Humberstone and Free People</v>
       </c>
       <c r="I19" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J19" t="str">
         <v/>
@@ -1115,36 +1115,36 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>אברהם חתומה - כשהלב בקרשים</v>
+        <v>Holly Humberstone - Lucy (Free People Sessions) - Holly Humberstone and Free People</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>אביאלי חדד - וויסקי בלילות</v>
+        <v>The Offspring - Why Don’t You Get a Job? | Live at BeachLife Festival 2026</v>
       </c>
       <c r="B20" t="str">
-        <v>2026-06-02</v>
+        <v>4 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411161&amp;sid=13e1d521681219f1f5cc74f85473f139</v>
+        <v>https://www.youtube.com/watch?v=zRJ2etb_rpI</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E20" t="str">
         <v/>
       </c>
       <c r="F20" t="str">
-        <v/>
+        <v>4 days ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
       </c>
       <c r="H20" t="str">
-        <v/>
+        <v>The Offspring</v>
       </c>
       <c r="I20" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J20" t="str">
         <v/>
@@ -1153,33 +1153,33 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>אביאלי חדד - וויסקי בלילות</v>
+        <v>The Offspring - Why Don’t You Get a Job? | Live at BeachLife Festival 2026 - The Offspring</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Billy Idol - John Wayne feat. Alison Mosshart (Official Music Video)</v>
+        <v>Jagwar Twin, sir lucius - bad feeling (oompa loompa) (Visualizer)</v>
       </c>
       <c r="B21" t="str">
-        <v>7 hours ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=47LNk7oiTVI</v>
+        <v>https://www.youtube.com/watch?v=XGgI5HvR-gg</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E21" t="str">
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>7 hours ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>Billy Idol</v>
+        <v>Jagwar Twin</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,21 +1191,21 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Billy Idol - John Wayne feat. Alison Mosshart (Official Music Video) - Billy Idol</v>
+        <v>Jagwar Twin, sir lucius - bad feeling (oompa loompa) (Visualizer) - Jagwar Twin</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>'It's Unusual' Official Music Video - Kelly Boesch | 4K</v>
+        <v>Nathan Evans x SAINT PHNX - Home (World Cup 2026) (Official Music Video)</v>
       </c>
       <c r="B22" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=Ru3fB2l1RSo</v>
+        <v>https://www.youtube.com/watch?v=lRBNYETENNg</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1217,7 +1217,7 @@
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>Kelly Boesch AI Art</v>
+        <v>NathanEvanss</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,33 +1229,33 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>'It's Unusual' Official Music Video - Kelly Boesch | 4K - Kelly Boesch AI Art</v>
+        <v>Nathan Evans x SAINT PHNX - Home (World Cup 2026) (Official Music Video) - NathanEvanss</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Icona Pop - Butterfly Feelings (Official Video)</v>
+        <v>Greta Van Fleet - Play Your Games (Official Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>9 hours ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=AMW1Zq9RbIU</v>
+        <v>https://www.youtube.com/watch?v=CJsfI1QVBEM</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E23" t="str">
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>9 hours ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>Icona Pop</v>
+        <v>Greta Van Fleet</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,33 +1267,33 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Icona Pop - Butterfly Feelings (Official Video) - Icona Pop</v>
+        <v>Greta Van Fleet - Play Your Games (Official Video) - Greta Van Fleet</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Hippo Campus - South</v>
+        <v>Lola Young – From Down Here (From a Living Room)</v>
       </c>
       <c r="B24" t="str">
-        <v>1 day ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=FYOmFfV7Ojo</v>
+        <v>https://www.youtube.com/watch?v=uF5HUfho2NU</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E24" t="str">
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>1 day ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>Hippo Campus</v>
+        <v>Lola Young</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,33 +1305,33 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Hippo Campus - South - Hippo Campus</v>
+        <v>Lola Young – From Down Here (From a Living Room) - Lola Young</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>elijah woods - Old (Treehouse Sessions)</v>
+        <v>Lawrence - Rain Check ft. Quinn XCII (Lyric Video)</v>
       </c>
       <c r="B25" t="str">
-        <v>1 day ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=yDlkPdR_6zM</v>
+        <v>https://www.youtube.com/watch?v=xXeyznlIrFY</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E25" t="str">
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>1 day ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>elijah woods</v>
+        <v>Lawrence and Quinn XCII</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,33 +1343,33 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>elijah woods - Old (Treehouse Sessions) - elijah woods</v>
+        <v>Lawrence - Rain Check ft. Quinn XCII (Lyric Video) - Lawrence and Quinn XCII</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Nothing But Thieves - Evolution (Official Video)</v>
+        <v>ANTONIA - NO HATE | Official Music Video</v>
       </c>
       <c r="B26" t="str">
-        <v>1 day ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=hmjfuuuRRYU</v>
+        <v>https://www.youtube.com/watch?v=rhlONr1DTj0</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E26" t="str">
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>1 day ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>Nothing But Thieves</v>
+        <v>ANTONIA</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,33 +1381,33 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Nothing But Thieves - Evolution (Official Video) - Nothing But Thieves</v>
+        <v>ANTONIA - NO HATE | Official Music Video - ANTONIA</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Ariana Grande - hate that i made you love me (official music video)</v>
+        <v>R3HAB - "Lost in translation..." (Official Lyric Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>1 day ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=82-jTNka3uc</v>
+        <v>https://www.youtube.com/watch?v=TbJtz0oy2cI</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E27" t="str">
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>1 day ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
       </c>
       <c r="H27" t="str">
-        <v>Ariana Grande</v>
+        <v>R3HAB</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,33 +1419,33 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Ariana Grande - hate that i made you love me (official music video) - Ariana Grande</v>
+        <v>R3HAB - "Lost in translation..." (Official Lyric Video) - R3HAB</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>LAUREL - Fire Breather</v>
+        <v>Pink Floyd - Shine On You Crazy Diamond (Parts 1-5) - Live in Venice (Official Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>1 day ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=rtyavLIJjy0</v>
+        <v>https://www.youtube.com/watch?v=kwiawhDk2TM</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E28" t="str">
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>1 day ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>LAUREL</v>
+        <v>Pink Floyd</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,33 +1457,33 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>LAUREL - Fire Breather - LAUREL</v>
+        <v>Pink Floyd - Shine On You Crazy Diamond (Parts 1-5) - Live in Venice (Official Video) - Pink Floyd</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>The Warning - Ego (Performance Video)</v>
+        <v>SHADE - TOXIC</v>
       </c>
       <c r="B29" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=7PApWObImjo</v>
+        <v>https://www.youtube.com/watch?v=A3km0zrBKSg</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E29" t="str">
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>The Warning</v>
+        <v>Shade Official Channel</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,33 +1495,33 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>The Warning - Ego (Performance Video) - The Warning</v>
+        <v>SHADE - TOXIC - Shade Official Channel</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (feat. Gabito Ballesteros) [Official Lyric Video]</v>
+        <v>Dua Lipa - Physical (Live From Mexico)</v>
       </c>
       <c r="B30" t="str">
-        <v>3 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=vruZSAYJBe4</v>
+        <v>https://www.youtube.com/watch?v=xZAe-d3bXTs</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E30" t="str">
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>3 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>David Guetta and Jennifer Lopez</v>
+        <v>Dua Lipa</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,33 +1533,33 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (feat. Gabito Ballesteros) [Official Lyric Video] - David Guetta and Jennifer Lopez</v>
+        <v>Dua Lipa - Physical (Live From Mexico) - Dua Lipa</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Armin van Buuren - Equanimity (from 'Piano' album) [Official Video]</v>
+        <v>Dagny - Rain (Lyric Video)</v>
       </c>
       <c r="B31" t="str">
-        <v>3 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=k93t10R-Qrg</v>
+        <v>https://www.youtube.com/watch?v=j3ZJwczZoUQ</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E31" t="str">
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>3 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>Armin van Buuren</v>
+        <v>Dagny</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,33 +1571,33 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Armin van Buuren - Equanimity (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Dagny - Rain (Lyric Video) - Dagny</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>“I Didn’t Know What Time It Was” - Andrew Bird Jazz Trio (Live from The Green Mill)</v>
+        <v>Modern Talking - Cheri Cheri Lady (Auf los geht's los, 14.09.1985)</v>
       </c>
       <c r="B32" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=XyRgdfXo2nI</v>
+        <v>https://www.youtube.com/watch?v=c0LtTVKNwNA</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E32" t="str">
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
       </c>
       <c r="H32" t="str">
-        <v>Andrew Bird</v>
+        <v>Modern Talking Offiziell</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,33 +1609,33 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>“I Didn’t Know What Time It Was” - Andrew Bird Jazz Trio (Live from The Green Mill) - Andrew Bird</v>
+        <v>Modern Talking - Cheri Cheri Lady (Auf los geht's los, 14.09.1985) - Modern Talking Offiziell</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Freya Ridings - Mother Of Pearl (Official Lyric Video)</v>
+        <v>The Chemical Brothers - Go (Live Show Visual)</v>
       </c>
       <c r="B33" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=7SGzYAZ0oxM</v>
+        <v>https://www.youtube.com/watch?v=fHCIchBq8CM</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E33" t="str">
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>Freya Ridings</v>
+        <v>The Chemical Brothers</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,33 +1647,33 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Freya Ridings - Mother Of Pearl (Official Lyric Video) - Freya Ridings</v>
+        <v>The Chemical Brothers - Go (Live Show Visual) - The Chemical Brothers</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Danny Gokey - God's Not (Official Music Video)</v>
+        <v>Jonas Blue - Girl (Official Lyric Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=oGpKqX6ftcU</v>
+        <v>https://www.youtube.com/watch?v=FTUe3jzUqXU</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E34" t="str">
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>Danny Gokey</v>
+        <v>Defected Records and Jonas Blue</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,33 +1685,33 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Danny Gokey - God's Not (Official Music Video) - Danny Gokey</v>
+        <v>Jonas Blue - Girl (Official Lyric Video) - Defected Records and Jonas Blue</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Armik - Brisas (2026 Remaster/Remix) (Exciting Rumba Flamenco, Spanish Guitar)</v>
+        <v>Dogpark - Don't Lie (Visualizer)</v>
       </c>
       <c r="B35" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=51Zu2iU2z2Q</v>
+        <v>https://www.youtube.com/watch?v=is7qKBRycJI</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E35" t="str">
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
       </c>
       <c r="H35" t="str">
-        <v>Armik</v>
+        <v>Dogpark</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,33 +1723,33 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Armik - Brisas (2026 Remaster/Remix) (Exciting Rumba Flamenco, Spanish Guitar) - Armik</v>
+        <v>Dogpark - Don't Lie (Visualizer) - Dogpark</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Holly Humberstone - Lucy (Free People Sessions)</v>
+        <v>elijah woods - L-O-V-E (Treehouse Sessions)</v>
       </c>
       <c r="B36" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=c1GR2TTs9W8</v>
+        <v>https://www.youtube.com/watch?v=q5kN7eH6rgo</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E36" t="str">
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>Holly Humberstone and Free People</v>
+        <v>elijah woods</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,33 +1761,33 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Holly Humberstone - Lucy (Free People Sessions) - Holly Humberstone and Free People</v>
+        <v>elijah woods - L-O-V-E (Treehouse Sessions) - elijah woods</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>The Offspring - Why Don’t You Get a Job? | Live at BeachLife Festival 2026</v>
+        <v>Lauren Alaina - Better Off (Official Audio)</v>
       </c>
       <c r="B37" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=zRJ2etb_rpI</v>
+        <v>https://www.youtube.com/watch?v=Vj-ong3XNHM</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E37" t="str">
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>The Offspring</v>
+        <v>Lauren Alaina</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,33 +1799,33 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>The Offspring - Why Don’t You Get a Job? | Live at BeachLife Festival 2026 - The Offspring</v>
+        <v>Lauren Alaina - Better Off (Official Audio) - Lauren Alaina</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Jagwar Twin, sir lucius - bad feeling (oompa loompa) (Visualizer)</v>
+        <v>Lauren Sanderson - ARE YOU REALLY HERE? (Lyric Video)</v>
       </c>
       <c r="B38" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=XGgI5HvR-gg</v>
+        <v>https://www.youtube.com/watch?v=u7Et_hbMZUA</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E38" t="str">
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
       </c>
       <c r="H38" t="str">
-        <v>Jagwar Twin</v>
+        <v>Lauren Sanderson</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,33 +1837,33 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Jagwar Twin, sir lucius - bad feeling (oompa loompa) (Visualizer) - Jagwar Twin</v>
+        <v>Lauren Sanderson - ARE YOU REALLY HERE? (Lyric Video) - Lauren Sanderson</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Nathan Evans x SAINT PHNX - Home (World Cup 2026) (Official Music Video)</v>
+        <v>Nightly – blue jeans (Official Lyric Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=lRBNYETENNg</v>
+        <v>https://www.youtube.com/watch?v=LnA3xkXUwaM</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E39" t="str">
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
       </c>
       <c r="H39" t="str">
-        <v>NathanEvanss</v>
+        <v>NIGHTLY</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,33 +1875,33 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Nathan Evans x SAINT PHNX - Home (World Cup 2026) (Official Music Video) - NathanEvanss</v>
+        <v>Nightly – blue jeans (Official Lyric Video) - NIGHTLY</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Greta Van Fleet - Play Your Games (Official Video)</v>
+        <v>Dasha - Mad About It (Official Visualizer)</v>
       </c>
       <c r="B40" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=CJsfI1QVBEM</v>
+        <v>https://www.youtube.com/watch?v=Ae1gf_7p3H8</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E40" t="str">
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
       </c>
       <c r="H40" t="str">
-        <v>Greta Van Fleet</v>
+        <v>Dasha</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,33 +1913,33 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Greta Van Fleet - Play Your Games (Official Video) - Greta Van Fleet</v>
+        <v>Dasha - Mad About It (Official Visualizer) - Dasha</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Lola Young – From Down Here (From a Living Room)</v>
+        <v>Max McNown - Something To Someone (Performance Video)</v>
       </c>
       <c r="B41" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=uF5HUfho2NU</v>
+        <v>https://www.youtube.com/watch?v=4Ki4ejT86YM</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E41" t="str">
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
       </c>
       <c r="H41" t="str">
-        <v>Lola Young</v>
+        <v>Max McNown</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,33 +1951,33 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Lola Young – From Down Here (From a Living Room) - Lola Young</v>
+        <v>Max McNown - Something To Someone (Performance Video) - Max McNown</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Lawrence - Rain Check ft. Quinn XCII (Lyric Video)</v>
+        <v>Bebe Rexha &amp; David Guetta - Sad Girls (Official Visual)</v>
       </c>
       <c r="B42" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=xXeyznlIrFY</v>
+        <v>https://www.youtube.com/watch?v=P8UqZ5IF-QE</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E42" t="str">
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
       </c>
       <c r="H42" t="str">
-        <v>Lawrence and Quinn XCII</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,33 +1989,33 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Lawrence - Rain Check ft. Quinn XCII (Lyric Video) - Lawrence and Quinn XCII</v>
+        <v>Bebe Rexha &amp; David Guetta - Sad Girls (Official Visual) - Bebe Rexha</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>ANTONIA - NO HATE | Official Music Video</v>
+        <v>Knox - Long Story Short (Official Video)</v>
       </c>
       <c r="B43" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=rhlONr1DTj0</v>
+        <v>https://www.youtube.com/watch?v=5OGY6hCELfg</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E43" t="str">
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
       </c>
       <c r="H43" t="str">
-        <v>ANTONIA</v>
+        <v>Knox</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,33 +2027,33 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>ANTONIA - NO HATE | Official Music Video - ANTONIA</v>
+        <v>Knox - Long Story Short (Official Video) - Knox</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>R3HAB - "Lost in translation..." (Official Lyric Video)</v>
+        <v>Sofia Camara - The Last Encounter</v>
       </c>
       <c r="B44" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=TbJtz0oy2cI</v>
+        <v>https://www.youtube.com/watch?v=E9kN4HLGG1c</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E44" t="str">
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
       </c>
       <c r="H44" t="str">
-        <v>R3HAB</v>
+        <v>Sofia Camara</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,33 +2065,33 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>R3HAB - "Lost in translation..." (Official Lyric Video) - R3HAB</v>
+        <v>Sofia Camara - The Last Encounter - Sofia Camara</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Pink Floyd - Shine On You Crazy Diamond (Parts 1-5) - Live in Venice (Official Video)</v>
+        <v>Official Music Video: "Flowers" -- Alexander James</v>
       </c>
       <c r="B45" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=kwiawhDk2TM</v>
+        <v>https://www.youtube.com/watch?v=aZ4WP0P92tM</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E45" t="str">
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
       </c>
       <c r="H45" t="str">
-        <v>Pink Floyd</v>
+        <v>Alexander James</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,33 +2103,33 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Pink Floyd - Shine On You Crazy Diamond (Parts 1-5) - Live in Venice (Official Video) - Pink Floyd</v>
+        <v>Official Music Video: "Flowers" -- Alexander James - Alexander James</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>SHADE - TOXIC</v>
+        <v>almost monday - skinny dip (official video)</v>
       </c>
       <c r="B46" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=A3km0zrBKSg</v>
+        <v>https://www.youtube.com/watch?v=hOxZDoaIzKQ</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E46" t="str">
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>Shade Official Channel</v>
+        <v>almost monday</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,21 +2141,21 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>SHADE - TOXIC - Shade Official Channel</v>
+        <v>almost monday - skinny dip (official video) - almost monday</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Dua Lipa - Physical (Live From Mexico)</v>
+        <v>Kip Moore - The Darkness (Official)</v>
       </c>
       <c r="B47" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=xZAe-d3bXTs</v>
+        <v>https://www.youtube.com/watch?v=lTqqixCt5Mk</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2167,7 +2167,7 @@
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>Dua Lipa</v>
+        <v>Kip Moore</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,33 +2179,33 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Dua Lipa - Physical (Live From Mexico) - Dua Lipa</v>
+        <v>Kip Moore - The Darkness (Official) - Kip Moore</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Dagny - Rain (Lyric Video)</v>
+        <v>Paul McCartney - Come Inside (Lyric Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=j3ZJwczZoUQ</v>
+        <v>https://www.youtube.com/watch?v=C8Zw_Cbm2V0</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E48" t="str">
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>Dagny</v>
+        <v>PAUL McCARTNEY</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,33 +2217,33 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Dagny - Rain (Lyric Video) - Dagny</v>
+        <v>Paul McCartney - Come Inside (Lyric Video) - PAUL McCARTNEY</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Modern Talking - Cheri Cheri Lady (Auf los geht's los, 14.09.1985)</v>
+        <v>Santana, Becky G - Mi Gran Amor (Official Lyric Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=c0LtTVKNwNA</v>
+        <v>https://www.youtube.com/watch?v=btdBd_Yee8E</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E49" t="str">
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>Modern Talking Offiziell</v>
+        <v>Santana</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,33 +2255,33 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Modern Talking - Cheri Cheri Lady (Auf los geht's los, 14.09.1985) - Modern Talking Offiziell</v>
+        <v>Santana, Becky G - Mi Gran Amor (Official Lyric Video) - Santana</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>The Chemical Brothers - Go (Live Show Visual)</v>
+        <v>Dua Lipa - Training Season (Live From Mexico)</v>
       </c>
       <c r="B50" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=fHCIchBq8CM</v>
+        <v>https://www.youtube.com/watch?v=Va8Udsvqigs</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E50" t="str">
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>The Chemical Brothers</v>
+        <v>Dua Lipa</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,33 +2293,33 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>The Chemical Brothers - Go (Live Show Visual) - The Chemical Brothers</v>
+        <v>Dua Lipa - Training Season (Live From Mexico) - Dua Lipa</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Jonas Blue - Girl (Official Lyric Video)</v>
+        <v>Charley - Liar</v>
       </c>
       <c r="B51" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=FTUe3jzUqXU</v>
+        <v>https://www.youtube.com/watch?v=3Erfj2Eecgw</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E51" t="str">
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>Defected Records and Jonas Blue</v>
+        <v>Charley</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,33 +2331,33 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Jonas Blue - Girl (Official Lyric Video) - Defected Records and Jonas Blue</v>
+        <v>Charley - Liar - Charley</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Dogpark - Don't Lie (Visualizer)</v>
+        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (ft Gabito Ballesteros) [Visualizer]</v>
       </c>
       <c r="B52" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=is7qKBRycJI</v>
+        <v>https://www.youtube.com/watch?v=em5ryETDkAo</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E52" t="str">
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>Dogpark</v>
+        <v>David Guetta and Jennifer Lopez</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,33 +2369,33 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Dogpark - Don't Lie (Visualizer) - Dogpark</v>
+        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (ft Gabito Ballesteros) [Visualizer] - David Guetta and Jennifer Lopez</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>elijah woods - L-O-V-E (Treehouse Sessions)</v>
+        <v>Jordana Bryant - Too Little Too Late (Official Audio)</v>
       </c>
       <c r="B53" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=q5kN7eH6rgo</v>
+        <v>https://www.youtube.com/watch?v=AmwNx9qlOpA</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E53" t="str">
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>elijah woods</v>
+        <v>Jordana Bryant</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,33 +2407,33 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>elijah woods - L-O-V-E (Treehouse Sessions) - elijah woods</v>
+        <v>Jordana Bryant - Too Little Too Late (Official Audio) - Jordana Bryant</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Lauren Alaina - Better Off (Official Audio)</v>
+        <v>Lewis Capaldi - Stay Love (Official Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=Vj-ong3XNHM</v>
+        <v>https://www.youtube.com/watch?v=9Pud3BqPpq0</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E54" t="str">
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>Lauren Alaina</v>
+        <v>Lewis Capaldi</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,33 +2445,33 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Lauren Alaina - Better Off (Official Audio) - Lauren Alaina</v>
+        <v>Lewis Capaldi - Stay Love (Official Video) - Lewis Capaldi</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Lauren Sanderson - ARE YOU REALLY HERE? (Lyric Video)</v>
+        <v>Surreal World of Oddities - Pulling At My Strings - Official Music Video | 4K</v>
       </c>
       <c r="B55" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=u7Et_hbMZUA</v>
+        <v>https://www.youtube.com/watch?v=fMt-f2aUW3c</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E55" t="str">
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>Lauren Sanderson</v>
+        <v>Kelly Boesch AI Art</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,33 +2483,33 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Lauren Sanderson - ARE YOU REALLY HERE? (Lyric Video) - Lauren Sanderson</v>
+        <v>Surreal World of Oddities - Pulling At My Strings - Official Music Video | 4K - Kelly Boesch AI Art</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Nightly – blue jeans (Official Lyric Video)</v>
+        <v>Julia Cole - Love You to Death (Official Video)</v>
       </c>
       <c r="B56" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=LnA3xkXUwaM</v>
+        <v>https://www.youtube.com/watch?v=dWgmFc2QuLY</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E56" t="str">
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>NIGHTLY</v>
+        <v>Julia Cole Music</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,33 +2521,33 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Nightly – blue jeans (Official Lyric Video) - NIGHTLY</v>
+        <v>Julia Cole - Love You to Death (Official Video) - Julia Cole Music</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Dasha - Mad About It (Official Visualizer)</v>
+        <v>Victor Biliac - De-ai fi tu salcie la mal ( Cover Edit )</v>
       </c>
       <c r="B57" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=Ae1gf_7p3H8</v>
+        <v>https://www.youtube.com/watch?v=v3c0kG-V2zk</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E57" t="str">
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>Dasha</v>
+        <v>VictorBiliac</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,33 +2559,33 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Dasha - Mad About It (Official Visualizer) - Dasha</v>
+        <v>Victor Biliac - De-ai fi tu salcie la mal ( Cover Edit ) - VictorBiliac</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Max McNown - Something To Someone (Performance Video)</v>
+        <v>Lolo Zouaï - Coquelicot (feat. disiz) (Official Video)</v>
       </c>
       <c r="B58" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=4Ki4ejT86YM</v>
+        <v>https://www.youtube.com/watch?v=-4p6FkrOGT4</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E58" t="str">
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>Max McNown</v>
+        <v>Lolo Zouaï and disiz</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,33 +2597,33 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Max McNown - Something To Someone (Performance Video) - Max McNown</v>
+        <v>Lolo Zouaï - Coquelicot (feat. disiz) (Official Video) - Lolo Zouaï and disiz</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Bebe Rexha &amp; David Guetta - Sad Girls (Official Visual)</v>
+        <v>Jungle - The Wave (Official Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=P8UqZ5IF-QE</v>
+        <v>https://www.youtube.com/watch?v=DW1vUkqNvqQ</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E59" t="str">
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>Bebe Rexha</v>
+        <v>Jungle4eva</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,33 +2635,33 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Bebe Rexha &amp; David Guetta - Sad Girls (Official Visual) - Bebe Rexha</v>
+        <v>Jungle - The Wave (Official Video) - Jungle4eva</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Knox - Long Story Short (Official Video)</v>
+        <v>Daytime TV – Sun (Official Music Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=5OGY6hCELfg</v>
+        <v>https://www.youtube.com/watch?v=Jqo4ra_ch-M</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E60" t="str">
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>Knox</v>
+        <v>DAYTIME TV</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,33 +2673,33 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Knox - Long Story Short (Official Video) - Knox</v>
+        <v>Daytime TV – Sun (Official Music Video) - DAYTIME TV</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Sofia Camara - The Last Encounter</v>
+        <v>Surreal and Strange AI Video | Not Made For The Cage | Kelly Boesch - 4K</v>
       </c>
       <c r="B61" t="str">
-        <v>4 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=E9kN4HLGG1c</v>
+        <v>https://www.youtube.com/watch?v=ACNj3L2bzV8</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E61" t="str">
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>4 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>Sofia Camara</v>
+        <v>Kelly Boesch AI Art</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,33 +2711,33 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Sofia Camara - The Last Encounter - Sofia Camara</v>
+        <v>Surreal and Strange AI Video | Not Made For The Cage | Kelly Boesch - 4K - Kelly Boesch AI Art</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Official Music Video: "Flowers" -- Alexander James</v>
+        <v>Bruno Mars - Risk It All [Live From The Romantic Tour]</v>
       </c>
       <c r="B62" t="str">
-        <v>4 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=aZ4WP0P92tM</v>
+        <v>https://www.youtube.com/watch?v=aFbueod4reQ</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E62" t="str">
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>4 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>Alexander James</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,33 +2749,33 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Official Music Video: "Flowers" -- Alexander James - Alexander James</v>
+        <v>Bruno Mars - Risk It All [Live From The Romantic Tour] - Bruno Mars</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>almost monday - skinny dip (official video)</v>
+        <v>Keith Urban - Summer Breeze (52nd American Music Awards)</v>
       </c>
       <c r="B63" t="str">
-        <v>4 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=hOxZDoaIzKQ</v>
+        <v>https://www.youtube.com/watch?v=zn-4eVoqofQ</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E63" t="str">
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>4 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>almost monday</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,33 +2787,33 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>almost monday - skinny dip (official video) - almost monday</v>
+        <v>Keith Urban - Summer Breeze (52nd American Music Awards) - Keith Urban</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Kip Moore - The Darkness (Official)</v>
+        <v>Nelly Furtado, Boi-1Da, Canada Soccer - ELECTRIC CIRCUS (Official Music Video)</v>
       </c>
       <c r="B64" t="str">
-        <v>4 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=lTqqixCt5Mk</v>
+        <v>https://www.youtube.com/watch?v=lHYEMWFuErM</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E64" t="str">
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>4 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>Kip Moore</v>
+        <v>Nelly Furtado</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,33 +2825,33 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Kip Moore - The Darkness (Official) - Kip Moore</v>
+        <v>Nelly Furtado, Boi-1Da, Canada Soccer - ELECTRIC CIRCUS (Official Music Video) - Nelly Furtado</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Paul McCartney - Come Inside (Lyric Video)</v>
+        <v>Teddy Swims - Mr. Know It All (Live from the AMAs)</v>
       </c>
       <c r="B65" t="str">
-        <v>4 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=C8Zw_Cbm2V0</v>
+        <v>https://www.youtube.com/watch?v=ttM4gWkhZBk</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E65" t="str">
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>4 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>PAUL McCARTNEY</v>
+        <v>Teddy Swims and American Music Awards</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,33 +2863,33 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Paul McCartney - Come Inside (Lyric Video) - PAUL McCARTNEY</v>
+        <v>Teddy Swims - Mr. Know It All (Live from the AMAs) - Teddy Swims and American Music Awards</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Santana, Becky G - Mi Gran Amor (Official Lyric Video)</v>
+        <v>Shakira, Burna Boy - Dai Dai (Official Video)</v>
       </c>
       <c r="B66" t="str">
-        <v>4 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=btdBd_Yee8E</v>
+        <v>https://www.youtube.com/watch?v=fcnDmrtj6Sk</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E66" t="str">
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>4 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>Santana</v>
+        <v>Shakira and 2 more</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,33 +2901,33 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Santana, Becky G - Mi Gran Amor (Official Lyric Video) - Santana</v>
+        <v>Shakira, Burna Boy - Dai Dai (Official Video) - Shakira and 2 more</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Dua Lipa - Training Season (Live From Mexico)</v>
+        <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards)</v>
       </c>
       <c r="B67" t="str">
-        <v>5 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=Va8Udsvqigs</v>
+        <v>https://www.youtube.com/watch?v=wacpnp83cJg</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E67" t="str">
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>5 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>Dua Lipa</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,33 +2939,33 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Dua Lipa - Training Season (Live From Mexico) - Dua Lipa</v>
+        <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards) - Lainey Wilson</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Charley - Liar</v>
+        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ]</v>
       </c>
       <c r="B68" t="str">
-        <v>5 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=3Erfj2Eecgw</v>
+        <v>https://www.youtube.com/watch?v=w8FTnkNVmq0</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E68" t="str">
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>5 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>Charley</v>
+        <v>Duran Duran</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,33 +2977,33 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Charley - Liar - Charley</v>
+        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ] - Duran Duran</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (ft Gabito Ballesteros) [Visualizer]</v>
+        <v>Nico Santos - Optimist</v>
       </c>
       <c r="B69" t="str">
-        <v>5 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=em5ryETDkAo</v>
+        <v>https://www.youtube.com/watch?v=JA6PIcBeKZ0</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E69" t="str">
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>5 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>David Guetta and Jennifer Lopez</v>
+        <v>Nico Santos</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,33 +3015,33 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (ft Gabito Ballesteros) [Visualizer] - David Guetta and Jennifer Lopez</v>
+        <v>Nico Santos - Optimist - Nico Santos</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Jordana Bryant - Too Little Too Late (Official Audio)</v>
+        <v>Def Leppard - Personal Jesus (Live at Caesars Palace)</v>
       </c>
       <c r="B70" t="str">
-        <v>5 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=AmwNx9qlOpA</v>
+        <v>https://www.youtube.com/watch?v=k5SRMgdG4L4</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E70" t="str">
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>5 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>Jordana Bryant</v>
+        <v>DEF LEPPARD</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,33 +3053,33 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Jordana Bryant - Too Little Too Late (Official Audio) - Jordana Bryant</v>
+        <v>Def Leppard - Personal Jesus (Live at Caesars Palace) - DEF LEPPARD</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Lewis Capaldi - Stay Love (Official Video)</v>
+        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer)</v>
       </c>
       <c r="B71" t="str">
-        <v>5 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=9Pud3BqPpq0</v>
+        <v>https://www.youtube.com/watch?v=eWSwy9GU2L8</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E71" t="str">
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>5 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>Lewis Capaldi</v>
+        <v>Will Linley</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,33 +3091,33 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Lewis Capaldi - Stay Love (Official Video) - Lewis Capaldi</v>
+        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer) - Will Linley</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Surreal World of Oddities - Pulling At My Strings - Official Music Video | 4K</v>
+        <v>Kylie Minogue - Story (Official Lyric Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>6 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=fMt-f2aUW3c</v>
+        <v>https://www.youtube.com/watch?v=fv7_1qKo8mg</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E72" t="str">
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>6 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>Kelly Boesch AI Art</v>
+        <v>Kylie Minogue</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,33 +3129,33 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Surreal World of Oddities - Pulling At My Strings - Official Music Video | 4K - Kelly Boesch AI Art</v>
+        <v>Kylie Minogue - Story (Official Lyric Video) - Kylie Minogue</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Julia Cole - Love You to Death (Official Video)</v>
+        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video)</v>
       </c>
       <c r="B73" t="str">
-        <v>6 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=dWgmFc2QuLY</v>
+        <v>https://www.youtube.com/watch?v=3KUQx2s1fQc</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E73" t="str">
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>6 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>Julia Cole Music</v>
+        <v>Billy Raffoul</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,33 +3167,33 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Julia Cole - Love You to Death (Official Video) - Julia Cole Music</v>
+        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video) - Billy Raffoul</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Victor Biliac - De-ai fi tu salcie la mal ( Cover Edit )</v>
+        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025)</v>
       </c>
       <c r="B74" t="str">
-        <v>6 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=v3c0kG-V2zk</v>
+        <v>https://www.youtube.com/watch?v=vWf4uiLvwF8</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E74" t="str">
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>6 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>VictorBiliac</v>
+        <v>The Offspring</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,33 +3205,33 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Victor Biliac - De-ai fi tu salcie la mal ( Cover Edit ) - VictorBiliac</v>
+        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025) - The Offspring</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Lolo Zouaï - Coquelicot (feat. disiz) (Official Video)</v>
+        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024)</v>
       </c>
       <c r="B75" t="str">
-        <v>6 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=-4p6FkrOGT4</v>
+        <v>https://www.youtube.com/watch?v=9xjMaXegmWM</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E75" t="str">
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>6 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>Lolo Zouaï and disiz</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,33 +3243,33 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Lolo Zouaï - Coquelicot (feat. disiz) (Official Video) - Lolo Zouaï and disiz</v>
+        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024) - David Gilmour</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Jungle - The Wave (Official Video)</v>
+        <v>Scorpions - Delicate Dance (Madison Square Garden 2022)</v>
       </c>
       <c r="B76" t="str">
-        <v>6 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=DW1vUkqNvqQ</v>
+        <v>https://www.youtube.com/watch?v=yAjEr9WLTnU</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E76" t="str">
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>6 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>Jungle4eva</v>
+        <v>Scorpions</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,33 +3281,33 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Jungle - The Wave (Official Video) - Jungle4eva</v>
+        <v>Scorpions - Delicate Dance (Madison Square Garden 2022) - Scorpions</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Daytime TV – Sun (Official Music Video)</v>
+        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston)</v>
       </c>
       <c r="B77" t="str">
-        <v>6 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=Jqo4ra_ch-M</v>
+        <v>https://www.youtube.com/watch?v=oRw4PqBzGc0</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E77" t="str">
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>6 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>DAYTIME TV</v>
+        <v>Brandon Lake and NICK JONAS</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,33 +3319,33 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Daytime TV – Sun (Official Music Video) - DAYTIME TV</v>
+        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston) - Brandon Lake and NICK JONAS</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Surreal and Strange AI Video | Not Made For The Cage | Kelly Boesch - 4K</v>
+        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B78" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=ACNj3L2bzV8</v>
+        <v>https://www.youtube.com/watch?v=OKf_IOGxFQo</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E78" t="str">
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>Kelly Boesch AI Art</v>
+        <v>Kygo and Dan Tyminski</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,33 +3357,33 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Surreal and Strange AI Video | Not Made For The Cage | Kelly Boesch - 4K - Kelly Boesch AI Art</v>
+        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video) - Kygo and Dan Tyminski</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Bruno Mars - Risk It All [Live From The Romantic Tour]</v>
+        <v>The Warning - Ego (Official Video)</v>
       </c>
       <c r="B79" t="str">
-        <v>7 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=aFbueod4reQ</v>
+        <v>https://www.youtube.com/watch?v=CG6Q5i75bR4</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E79" t="str">
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>7 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>Bruno Mars</v>
+        <v>The Warning</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,33 +3395,33 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Bruno Mars - Risk It All [Live From The Romantic Tour] - Bruno Mars</v>
+        <v>The Warning - Ego (Official Video) - The Warning</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Keith Urban - Summer Breeze (52nd American Music Awards)</v>
+        <v>paris jackson - teenage drama (official lyric video)</v>
       </c>
       <c r="B80" t="str">
-        <v>7 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=zn-4eVoqofQ</v>
+        <v>https://www.youtube.com/watch?v=kVfDArNljos</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E80" t="str">
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>7 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>Keith Urban</v>
+        <v>paris jackson</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,33 +3433,33 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Keith Urban - Summer Breeze (52nd American Music Awards) - Keith Urban</v>
+        <v>paris jackson - teenage drama (official lyric video) - paris jackson</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Nelly Furtado, Boi-1Da, Canada Soccer - ELECTRIC CIRCUS (Official Music Video)</v>
+        <v>Minelli - Sun Goes Down | Official Visualizer</v>
       </c>
       <c r="B81" t="str">
-        <v>7 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=lHYEMWFuErM</v>
+        <v>https://www.youtube.com/watch?v=xOsjm-AwN5I</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E81" t="str">
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>7 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
       </c>
       <c r="H81" t="str">
-        <v>Nelly Furtado</v>
+        <v>Minelli</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,33 +3471,33 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Nelly Furtado, Boi-1Da, Canada Soccer - ELECTRIC CIRCUS (Official Music Video) - Nelly Furtado</v>
+        <v>Minelli - Sun Goes Down | Official Visualizer - Minelli</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Teddy Swims - Mr. Know It All (Live from the AMAs)</v>
+        <v>Maggie Rose - Gentle Man (Official Studio Video)</v>
       </c>
       <c r="B82" t="str">
-        <v>7 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=ttM4gWkhZBk</v>
+        <v>https://www.youtube.com/watch?v=aWNK-vWrN60</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E82" t="str">
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>7 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
       </c>
       <c r="H82" t="str">
-        <v>Teddy Swims and American Music Awards</v>
+        <v>Maggie Rose</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,33 +3509,33 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Teddy Swims - Mr. Know It All (Live from the AMAs) - Teddy Swims and American Music Awards</v>
+        <v>Maggie Rose - Gentle Man (Official Studio Video) - Maggie Rose</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Shakira, Burna Boy - Dai Dai (Official Video)</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer]</v>
       </c>
       <c r="B83" t="str">
-        <v>10 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=fcnDmrtj6Sk</v>
+        <v>https://www.youtube.com/watch?v=mN5AZBrVq9I</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E83" t="str">
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>10 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
       </c>
       <c r="H83" t="str">
-        <v>Shakira and 2 more</v>
+        <v>David Guetta</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,33 +3547,33 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Shakira, Burna Boy - Dai Dai (Official Video) - Shakira and 2 more</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer] - David Guetta</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards)</v>
+        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video)</v>
       </c>
       <c r="B84" t="str">
-        <v>10 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=wacpnp83cJg</v>
+        <v>https://www.youtube.com/watch?v=0PTufEGRAVQ</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E84" t="str">
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>10 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
       </c>
       <c r="H84" t="str">
-        <v>Lainey Wilson</v>
+        <v>Chris Young and Shaylen</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,33 +3585,33 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards) - Lainey Wilson</v>
+        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video) - Chris Young and Shaylen</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ]</v>
+        <v>Lauv - Pretty Little Things</v>
       </c>
       <c r="B85" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=w8FTnkNVmq0</v>
+        <v>https://www.youtube.com/watch?v=_JBfanFvHnA</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E85" t="str">
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
       </c>
       <c r="H85" t="str">
-        <v>Duran Duran</v>
+        <v>Lauv</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,33 +3623,33 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ] - Duran Duran</v>
+        <v>Lauv - Pretty Little Things - Lauv</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Nico Santos - Optimist</v>
+        <v>Icona Pop - Butterfly Feelings (Official Audio)</v>
       </c>
       <c r="B86" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=JA6PIcBeKZ0</v>
+        <v>https://www.youtube.com/watch?v=bXA_Q75QZTs</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E86" t="str">
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>Nico Santos</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,33 +3661,33 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Nico Santos - Optimist - Nico Santos</v>
+        <v>Icona Pop - Butterfly Feelings (Official Audio) - Icona Pop</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Def Leppard - Personal Jesus (Live at Caesars Palace)</v>
+        <v>Will Swinton - Only One (Official Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>10 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=k5SRMgdG4L4</v>
+        <v>https://www.youtube.com/watch?v=A0KzP-zm9hA</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E87" t="str">
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>10 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>DEF LEPPARD</v>
+        <v>Will Swinton</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,33 +3699,33 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Def Leppard - Personal Jesus (Live at Caesars Palace) - DEF LEPPARD</v>
+        <v>Will Swinton - Only One (Official Video) - Will Swinton</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer)</v>
+        <v>Dean Lewis - Escape (Official Video)</v>
       </c>
       <c r="B88" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=eWSwy9GU2L8</v>
+        <v>https://www.youtube.com/watch?v=BZRaTXCkhcg</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E88" t="str">
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>Will Linley</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,33 +3737,33 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer) - Will Linley</v>
+        <v>Dean Lewis - Escape (Official Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Kylie Minogue - Story (Official Lyric Video)</v>
+        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico]</v>
       </c>
       <c r="B89" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=fv7_1qKo8mg</v>
+        <v>https://www.youtube.com/watch?v=PNm0hf_zZJY</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E89" t="str">
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>Kylie Minogue</v>
+        <v>Dua Lipa and OficialMana</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,33 +3775,33 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Kylie Minogue - Story (Official Lyric Video) - Kylie Minogue</v>
+        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico] - Dua Lipa and OficialMana</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video)</v>
+        <v>Niall Horan - End of an Era (Lyric Video)</v>
       </c>
       <c r="B90" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=3KUQx2s1fQc</v>
+        <v>https://www.youtube.com/watch?v=EUNNmAAe5gQ</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E90" t="str">
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>Billy Raffoul</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,33 +3813,33 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video) - Billy Raffoul</v>
+        <v>Niall Horan - End of an Era (Lyric Video) - Niall Horan</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025)</v>
+        <v>Olivia Rodrigo - the cure (Official Music Video)</v>
       </c>
       <c r="B91" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=vWf4uiLvwF8</v>
+        <v>https://www.youtube.com/watch?v=B402rKl4bUg</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E91" t="str">
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>The Offspring</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,33 +3851,33 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025) - The Offspring</v>
+        <v>Olivia Rodrigo - the cure (Official Music Video) - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024)</v>
+        <v>Ruel - Debbie Don't Cry (Official Music Video)</v>
       </c>
       <c r="B92" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=9xjMaXegmWM</v>
+        <v>https://www.youtube.com/watch?v=iz7wuk0GOwI</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E92" t="str">
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
       </c>
       <c r="H92" t="str">
-        <v>David Gilmour</v>
+        <v>RUEL</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,33 +3889,33 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024) - David Gilmour</v>
+        <v>Ruel - Debbie Don't Cry (Official Music Video) - RUEL</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Scorpions - Delicate Dance (Madison Square Garden 2022)</v>
+        <v>TINI - Down (LIVE)</v>
       </c>
       <c r="B93" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=yAjEr9WLTnU</v>
+        <v>https://www.youtube.com/watch?v=ADbFeQUPTrk</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E93" t="str">
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>Scorpions</v>
+        <v>TINI</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,33 +3927,33 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Scorpions - Delicate Dance (Madison Square Garden 2022) - Scorpions</v>
+        <v>TINI - Down (LIVE) - TINI</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston)</v>
+        <v>Charli xcx - SS26 (Official Video)</v>
       </c>
       <c r="B94" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=oRw4PqBzGc0</v>
+        <v>https://www.youtube.com/watch?v=twLhSqabby0</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E94" t="str">
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
       </c>
       <c r="H94" t="str">
-        <v>Brandon Lake and NICK JONAS</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,33 +3965,33 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston) - Brandon Lake and NICK JONAS</v>
+        <v>Charli xcx - SS26 (Official Video) - Charli xcx</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video)</v>
+        <v>Dua Lipa - Live From Mexico</v>
       </c>
       <c r="B95" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=OKf_IOGxFQo</v>
+        <v>https://www.youtube.com/watch?v=vZYVkitGXBU</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E95" t="str">
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
       </c>
       <c r="H95" t="str">
-        <v>Kygo and Dan Tyminski</v>
+        <v>Dua Lipa</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,33 +4003,33 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video) - Kygo and Dan Tyminski</v>
+        <v>Dua Lipa - Live From Mexico - Dua Lipa</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>The Warning - Ego (Official Video)</v>
+        <v>Matilda Mann - 'The Fig Tree' (Official Video)</v>
       </c>
       <c r="B96" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=CG6Q5i75bR4</v>
+        <v>https://www.youtube.com/watch?v=XPyubkkkw44</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E96" t="str">
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
       </c>
       <c r="H96" t="str">
-        <v>The Warning</v>
+        <v>Matilda Mann</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,33 +4041,33 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>The Warning - Ego (Official Video) - The Warning</v>
+        <v>Matilda Mann - 'The Fig Tree' (Official Video) - Matilda Mann</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>paris jackson - teenage drama (official lyric video)</v>
+        <v>Ella Langley - Be Her (61st Academy of Country Music Awards)</v>
       </c>
       <c r="B97" t="str">
-        <v>11 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=kVfDArNljos</v>
+        <v>https://www.youtube.com/watch?v=4KbYfH7EAm8</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E97" t="str">
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>11 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
       </c>
       <c r="H97" t="str">
-        <v>paris jackson</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,33 +4079,33 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>paris jackson - teenage drama (official lyric video) - paris jackson</v>
+        <v>Ella Langley - Be Her (61st Academy of Country Music Awards) - Ella Langley</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Minelli - Sun Goes Down | Official Visualizer</v>
+        <v>Nothing But Thieves - Evolution (Official Audio)</v>
       </c>
       <c r="B98" t="str">
-        <v>11 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=xOsjm-AwN5I</v>
+        <v>https://www.youtube.com/watch?v=Kcs-4EZSUW0</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E98" t="str">
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>11 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
       </c>
       <c r="H98" t="str">
-        <v>Minelli</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,33 +4117,33 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Minelli - Sun Goes Down | Official Visualizer - Minelli</v>
+        <v>Nothing But Thieves - Evolution (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Maggie Rose - Gentle Man (Official Studio Video)</v>
+        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO)</v>
       </c>
       <c r="B99" t="str">
-        <v>11 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=aWNK-vWrN60</v>
+        <v>https://www.youtube.com/watch?v=HiLT1jzDZb4</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E99" t="str">
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>11 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
       </c>
       <c r="H99" t="str">
-        <v>Maggie Rose</v>
+        <v>kesha</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,33 +4155,33 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Maggie Rose - Gentle Man (Official Studio Video) - Maggie Rose</v>
+        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO) - kesha</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer]</v>
+        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify</v>
       </c>
       <c r="B100" t="str">
-        <v>11 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=mN5AZBrVq9I</v>
+        <v>https://www.youtube.com/watch?v=_WGsJYCCfU8</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E100" t="str">
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>11 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
       </c>
       <c r="H100" t="str">
-        <v>David Guetta</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,33 +4193,33 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer] - David Guetta</v>
+        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify - Holly Humberstone</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video)</v>
+        <v>Foo Fighters - Of All People (Official Video)</v>
       </c>
       <c r="B101" t="str">
-        <v>11 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=0PTufEGRAVQ</v>
+        <v>https://www.youtube.com/watch?v=r_iMzMrCQs0</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E101" t="str">
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>11 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G101" t="str">
         <v/>
       </c>
       <c r="H101" t="str">
-        <v>Chris Young and Shaylen</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,33 +4231,33 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video) - Chris Young and Shaylen</v>
+        <v>Foo Fighters - Of All People (Official Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Lauv - Pretty Little Things</v>
+        <v>'From Me To You' by The Beatles, performed by The Young Analogues</v>
       </c>
       <c r="B102" t="str">
-        <v>11 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=_JBfanFvHnA</v>
+        <v>https://www.youtube.com/watch?v=cLiyO2t3xd0</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E102" t="str">
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>11 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G102" t="str">
         <v/>
       </c>
       <c r="H102" t="str">
-        <v>Lauv</v>
+        <v>The Analogues</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4269,33 +4269,33 @@
         <v/>
       </c>
       <c r="L102" t="str">
-        <v>Lauv - Pretty Little Things - Lauv</v>
+        <v>'From Me To You' by The Beatles, performed by The Young Analogues - The Analogues</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Icona Pop - Butterfly Feelings (Official Audio)</v>
+        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video]</v>
       </c>
       <c r="B103" t="str">
-        <v>11 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C103" t="str">
-        <v>https://www.youtube.com/watch?v=bXA_Q75QZTs</v>
+        <v>https://www.youtube.com/watch?v=O67Q25sMhyU</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E103" t="str">
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>11 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G103" t="str">
         <v/>
       </c>
       <c r="H103" t="str">
-        <v>Icona Pop</v>
+        <v>Rod Stewart</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4307,4458 +4307,3812 @@
         <v/>
       </c>
       <c r="L103" t="str">
-        <v>Icona Pop - Butterfly Feelings (Official Audio) - Icona Pop</v>
+        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video] - Rod Stewart</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Will Swinton - Only One (Official Video)</v>
+        <v>snake the drain</v>
       </c>
       <c r="B104" t="str">
-        <v>11 days ago</v>
+        <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://www.youtube.com/watch?v=A0KzP-zm9hA</v>
+        <v>https://music.apple.com/us/song/snake-the-drain/6771506655</v>
       </c>
       <c r="D104" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E104" t="str">
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>11 days ago</v>
+        <v>this time it’s different / snake the drain - Single</v>
       </c>
       <c r="G104" t="str">
-        <v/>
+        <v>3:08</v>
       </c>
       <c r="H104" t="str">
-        <v>Will Swinton</v>
+        <v>Devon Again</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/devon-again/1574318250</v>
       </c>
       <c r="K104" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/snake-the-drain/6771506650</v>
       </c>
       <c r="L104" t="str">
-        <v>Will Swinton - Only One (Official Video) - Will Swinton</v>
+        <v>snake the drain - Devon Again</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Dean Lewis - Escape (Official Video)</v>
+        <v>hate that i made you love me</v>
       </c>
       <c r="B105" t="str">
-        <v>11 days ago</v>
+        <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://www.youtube.com/watch?v=BZRaTXCkhcg</v>
+        <v>https://music.apple.com/us/song/hate-that-i-made-you-love-me/6763656876</v>
       </c>
       <c r="D105" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E105" t="str">
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>11 days ago</v>
+        <v>petal</v>
       </c>
       <c r="G105" t="str">
-        <v/>
+        <v>3:17</v>
       </c>
       <c r="H105" t="str">
-        <v>Dean Lewis</v>
+        <v>Ariana Grande</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/ariana-grande/412778295</v>
       </c>
       <c r="K105" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/hate-that-i-made-you-love-me/1895420989</v>
       </c>
       <c r="L105" t="str">
-        <v>Dean Lewis - Escape (Official Video) - Dean Lewis</v>
+        <v>hate that i made you love me - Ariana Grande</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico]</v>
+        <v>Come Inside</v>
       </c>
       <c r="B106" t="str">
-        <v>12 days ago</v>
+        <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://www.youtube.com/watch?v=PNm0hf_zZJY</v>
+        <v>https://music.apple.com/us/song/come-inside/1887403093</v>
       </c>
       <c r="D106" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E106" t="str">
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>12 days ago</v>
+        <v>The Boys of Dungeon Lane</v>
       </c>
       <c r="G106" t="str">
-        <v/>
+        <v>3:13</v>
       </c>
       <c r="H106" t="str">
-        <v>Dua Lipa and OficialMana</v>
+        <v>Paul McCartney</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/paul-mccartney/12224</v>
       </c>
       <c r="K106" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/come-inside/1887402919</v>
       </c>
       <c r="L106" t="str">
-        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico] - Dua Lipa and OficialMana</v>
+        <v>Come Inside - Paul McCartney</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Niall Horan - End of an Era (Lyric Video)</v>
+        <v>Game Time</v>
       </c>
       <c r="B107" t="str">
-        <v>11 days ago</v>
+        <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://www.youtube.com/watch?v=EUNNmAAe5gQ</v>
+        <v>https://music.apple.com/us/song/game-time/6771157200</v>
       </c>
       <c r="D107" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E107" t="str">
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>11 days ago</v>
+        <v>Game Time (FIFA World Cup 2026™) - Single</v>
       </c>
       <c r="G107" t="str">
-        <v/>
+        <v>3:26</v>
       </c>
       <c r="H107" t="str">
-        <v>Niall Horan</v>
+        <v>Future</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/future/128050210</v>
       </c>
       <c r="K107" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/game-time/6771157186</v>
       </c>
       <c r="L107" t="str">
-        <v>Niall Horan - End of an Era (Lyric Video) - Niall Horan</v>
+        <v>Game Time - Future</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Olivia Rodrigo - the cure (Official Music Video)</v>
+        <v>Motion Party (Remix)</v>
       </c>
       <c r="B108" t="str">
-        <v>11 days ago</v>
+        <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://www.youtube.com/watch?v=B402rKl4bUg</v>
+        <v>https://music.apple.com/us/song/motion-party-remix/6773413965</v>
       </c>
       <c r="D108" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E108" t="str">
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>11 days ago</v>
+        <v>Motion Party (Remix) - Single</v>
       </c>
       <c r="G108" t="str">
-        <v/>
+        <v>2:36</v>
       </c>
       <c r="H108" t="str">
-        <v>Olivia Rodrigo</v>
+        <v>Bossman Dlow</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/bossman-dlow/1474308236</v>
       </c>
       <c r="K108" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/motion-party-remix/6773413953</v>
       </c>
       <c r="L108" t="str">
-        <v>Olivia Rodrigo - the cure (Official Music Video) - Olivia Rodrigo</v>
+        <v>Motion Party (Remix) - Bossman Dlow</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Ruel - Debbie Don't Cry (Official Music Video)</v>
+        <v>Aquel diciembre</v>
       </c>
       <c r="B109" t="str">
-        <v>11 days ago</v>
+        <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://www.youtube.com/watch?v=iz7wuk0GOwI</v>
+        <v>https://music.apple.com/us/song/aquel-diciembre/6769580010</v>
       </c>
       <c r="D109" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E109" t="str">
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>11 days ago</v>
+        <v>Do Not Disturb: Late Checkout</v>
       </c>
       <c r="G109" t="str">
-        <v/>
+        <v>3:22</v>
       </c>
       <c r="H109" t="str">
-        <v>RUEL</v>
+        <v>Young Miko</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/young-miko/1576521417</v>
       </c>
       <c r="K109" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/aquel-diciembre/6769579992</v>
       </c>
       <c r="L109" t="str">
-        <v>Ruel - Debbie Don't Cry (Official Music Video) - RUEL</v>
+        <v>Aquel diciembre - Young Miko</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>TINI - Down (LIVE)</v>
+        <v>Handle</v>
       </c>
       <c r="B110" t="str">
-        <v>11 days ago</v>
+        <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://www.youtube.com/watch?v=ADbFeQUPTrk</v>
+        <v>https://music.apple.com/us/song/handle/6771922623</v>
       </c>
       <c r="D110" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E110" t="str">
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>11 days ago</v>
+        <v>Blue Island</v>
       </c>
       <c r="G110" t="str">
-        <v/>
+        <v>3:06</v>
       </c>
       <c r="H110" t="str">
-        <v>TINI</v>
+        <v>Ravyn Lenae</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/ravyn-lenae/1044417443</v>
       </c>
       <c r="K110" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/handle/6771922622</v>
       </c>
       <c r="L110" t="str">
-        <v>TINI - Down (LIVE) - TINI</v>
+        <v>Handle - Ravyn Lenae</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Charli xcx - SS26 (Official Video)</v>
+        <v>Every Single Weekend (feat. Jamie xx)</v>
       </c>
       <c r="B111" t="str">
-        <v>12 days ago</v>
+        <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://www.youtube.com/watch?v=twLhSqabby0</v>
+        <v>https://music.apple.com/us/song/every-single-weekend-feat-jamie-xx/6770445933</v>
       </c>
       <c r="D111" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E111" t="str">
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>12 days ago</v>
+        <v>Every Single Weekend (feat. Jamie xx) - Single</v>
       </c>
       <c r="G111" t="str">
-        <v/>
+        <v>2:10</v>
       </c>
       <c r="H111" t="str">
-        <v>Charli xcx</v>
+        <v>The Avalanches</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/the-avalanches/27524431</v>
       </c>
       <c r="K111" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/every-single-weekend-feat-jamie-xx/6770445752</v>
       </c>
       <c r="L111" t="str">
-        <v>Charli xcx - SS26 (Official Video) - Charli xcx</v>
+        <v>Every Single Weekend (feat. Jamie xx) - The Avalanches</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Dua Lipa - Live From Mexico</v>
+        <v>The Wave</v>
       </c>
       <c r="B112" t="str">
-        <v>12 days ago</v>
+        <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://www.youtube.com/watch?v=vZYVkitGXBU</v>
+        <v>https://music.apple.com/us/song/the-wave/1886730541</v>
       </c>
       <c r="D112" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E112" t="str">
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>12 days ago</v>
+        <v>Sunshine</v>
       </c>
       <c r="G112" t="str">
-        <v/>
+        <v>3:22</v>
       </c>
       <c r="H112" t="str">
-        <v>Dua Lipa</v>
+        <v>Jungle</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/jungle/825833522</v>
       </c>
       <c r="K112" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/the-wave/1886730527</v>
       </c>
       <c r="L112" t="str">
-        <v>Dua Lipa - Live From Mexico - Dua Lipa</v>
+        <v>The Wave - Jungle</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Matilda Mann - 'The Fig Tree' (Official Video)</v>
+        <v>STOP</v>
       </c>
       <c r="B113" t="str">
-        <v>12 days ago</v>
+        <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://www.youtube.com/watch?v=XPyubkkkw44</v>
+        <v>https://music.apple.com/us/song/stop/6771161771</v>
       </c>
       <c r="D113" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E113" t="str">
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>12 days ago</v>
+        <v>are you mad at me? - Single</v>
       </c>
       <c r="G113" t="str">
-        <v/>
+        <v>2:56</v>
       </c>
       <c r="H113" t="str">
-        <v>Matilda Mann</v>
+        <v>Bella Kay</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
       </c>
       <c r="K113" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/stop/6771161760</v>
       </c>
       <c r="L113" t="str">
-        <v>Matilda Mann - 'The Fig Tree' (Official Video) - Matilda Mann</v>
+        <v>STOP - Bella Kay</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Ella Langley - Be Her (61st Academy of Country Music Awards)</v>
+        <v>Here (Apple Music Sessions)</v>
       </c>
       <c r="B114" t="str">
-        <v>13 days ago</v>
+        <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://www.youtube.com/watch?v=4KbYfH7EAm8</v>
+        <v>https://music.apple.com/us/song/here-apple-music-sessions/1878235516</v>
       </c>
       <c r="D114" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E114" t="str">
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>13 days ago</v>
+        <v>Apple Music Sessions</v>
       </c>
       <c r="G114" t="str">
-        <v/>
+        <v>3:08</v>
       </c>
       <c r="H114" t="str">
-        <v>Ella Langley</v>
+        <v>Mumford &amp; Sons</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/mumford-sons/307699986</v>
       </c>
       <c r="K114" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/here-apple-music-sessions/1878235330</v>
       </c>
       <c r="L114" t="str">
-        <v>Ella Langley - Be Her (61st Academy of Country Music Awards) - Ella Langley</v>
+        <v>Here (Apple Music Sessions) - Mumford &amp; Sons</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Nothing But Thieves - Evolution (Official Audio)</v>
+        <v>Talk On The Hill</v>
       </c>
       <c r="B115" t="str">
-        <v>13 days ago</v>
+        <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://www.youtube.com/watch?v=Kcs-4EZSUW0</v>
+        <v>https://music.apple.com/us/song/talk-on-the-hill/6769524458</v>
       </c>
       <c r="D115" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E115" t="str">
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>13 days ago</v>
+        <v>The Thread</v>
       </c>
       <c r="G115" t="str">
-        <v/>
+        <v>3:27</v>
       </c>
       <c r="H115" t="str">
-        <v>Nothing But Thieves</v>
+        <v>WILLOW</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/willow/400531893</v>
       </c>
       <c r="K115" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/talk-on-the-hill/6769524450</v>
       </c>
       <c r="L115" t="str">
-        <v>Nothing But Thieves - Evolution (Official Audio) - Nothing But Thieves</v>
+        <v>Talk On The Hill - WILLOW</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO)</v>
+        <v>No Fear</v>
       </c>
       <c r="B116" t="str">
-        <v>13 days ago</v>
+        <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://www.youtube.com/watch?v=HiLT1jzDZb4</v>
+        <v>https://music.apple.com/us/song/no-fear/1880484493</v>
       </c>
       <c r="D116" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E116" t="str">
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>13 days ago</v>
+        <v>For Love of Grace &amp; the Hereafter</v>
       </c>
       <c r="G116" t="str">
-        <v/>
+        <v>3:38</v>
       </c>
       <c r="H116" t="str">
-        <v>kesha</v>
+        <v>Iceage</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/iceage/406846711</v>
       </c>
       <c r="K116" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/no-fear/1880484160</v>
       </c>
       <c r="L116" t="str">
-        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO) - kesha</v>
+        <v>No Fear - Iceage</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify</v>
+        <v>Hostage</v>
       </c>
       <c r="B117" t="str">
-        <v>13 days ago</v>
+        <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://www.youtube.com/watch?v=_WGsJYCCfU8</v>
+        <v>https://music.apple.com/us/song/hostage/6774372288</v>
       </c>
       <c r="D117" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E117" t="str">
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>13 days ago</v>
+        <v>Big Mama</v>
       </c>
       <c r="G117" t="str">
-        <v/>
+        <v>3:11</v>
       </c>
       <c r="H117" t="str">
-        <v>Holly Humberstone</v>
+        <v>Latto</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/latto/419799506</v>
       </c>
       <c r="K117" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/hostage/6774372200</v>
       </c>
       <c r="L117" t="str">
-        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify - Holly Humberstone</v>
+        <v>Hostage - Latto</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Foo Fighters - Of All People (Official Video)</v>
+        <v>Sad Girls</v>
       </c>
       <c r="B118" t="str">
-        <v>13 days ago</v>
+        <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://www.youtube.com/watch?v=r_iMzMrCQs0</v>
+        <v>https://music.apple.com/us/song/sad-girls/6768814374</v>
       </c>
       <c r="D118" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E118" t="str">
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>13 days ago</v>
+        <v>Sad Girls - Single</v>
       </c>
       <c r="G118" t="str">
-        <v/>
+        <v>2:48</v>
       </c>
       <c r="H118" t="str">
-        <v>Foo Fighters</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/bebe-rexha/466059563</v>
       </c>
       <c r="K118" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/sad-girls/6768814373</v>
       </c>
       <c r="L118" t="str">
-        <v>Foo Fighters - Of All People (Official Video) - Foo Fighters</v>
+        <v>Sad Girls - Bebe Rexha</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>'From Me To You' by The Beatles, performed by The Young Analogues</v>
+        <v>Salvame Hoy (feat. Gabito Ballesteros)</v>
       </c>
       <c r="B119" t="str">
-        <v>13 days ago</v>
+        <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://www.youtube.com/watch?v=cLiyO2t3xd0</v>
+        <v>https://music.apple.com/us/song/salvame-hoy-feat-gabito-ballesteros/6765697019</v>
       </c>
       <c r="D119" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E119" t="str">
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>13 days ago</v>
+        <v>Salvame Hoy (feat. Gabito Ballesteros) - Single</v>
       </c>
       <c r="G119" t="str">
-        <v/>
+        <v>3:35</v>
       </c>
       <c r="H119" t="str">
-        <v>The Analogues</v>
+        <v>Jennifer Lopez</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/jennifer-lopez/463009</v>
       </c>
       <c r="K119" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/salvame-hoy-feat-gabito-ballesteros/1896041010</v>
       </c>
       <c r="L119" t="str">
-        <v>'From Me To You' by The Beatles, performed by The Young Analogues - The Analogues</v>
+        <v>Salvame Hoy (feat. Gabito Ballesteros) - Jennifer Lopez</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video]</v>
+        <v>Rubio</v>
       </c>
       <c r="B120" t="str">
-        <v>13 days ago</v>
+        <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://www.youtube.com/watch?v=O67Q25sMhyU</v>
+        <v>https://music.apple.com/us/song/rubio/6770655339</v>
       </c>
       <c r="D120" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E120" t="str">
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>13 days ago</v>
+        <v>La Voz Favorita</v>
       </c>
       <c r="G120" t="str">
-        <v/>
+        <v>4:42</v>
       </c>
       <c r="H120" t="str">
-        <v>Rod Stewart</v>
+        <v>Jay Wheeler</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/jay-wheeler/164376380</v>
       </c>
       <c r="K120" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/rubio/6770654729</v>
       </c>
       <c r="L120" t="str">
-        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video] - Rod Stewart</v>
+        <v>Rubio - Jay Wheeler</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>snake the drain</v>
+        <v>Pary</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/snake-the-drain/6771506655</v>
+        <v>https://music.apple.com/us/song/pary/6767367748</v>
       </c>
       <c r="D121" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E121" t="str">
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>this time it’s different / snake the drain - Single</v>
+        <v>Con dolor - EP</v>
       </c>
       <c r="G121" t="str">
-        <v>3:08</v>
+        <v>2:52</v>
       </c>
       <c r="H121" t="str">
-        <v>Devon Again</v>
+        <v>Grupo Frontera</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/devon-again/1574318250</v>
+        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/snake-the-drain/6771506650</v>
+        <v>https://music.apple.com/us/album/pary/6767367501</v>
       </c>
       <c r="L121" t="str">
-        <v>snake the drain - Devon Again</v>
+        <v>Pary - Grupo Frontera</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>hate that i made you love me</v>
+        <v>Think As You Drunk</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/hate-that-i-made-you-love-me/6763656876</v>
+        <v>https://music.apple.com/us/song/think-as-you-drunk/6770725979</v>
       </c>
       <c r="D122" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E122" t="str">
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>petal</v>
+        <v>That's Just Me</v>
       </c>
       <c r="G122" t="str">
-        <v>3:17</v>
+        <v>3:48</v>
       </c>
       <c r="H122" t="str">
-        <v>Ariana Grande</v>
+        <v>Riley Green</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/ariana-grande/412778295</v>
+        <v>https://music.apple.com/us/artist/riley-green/662432971</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/hate-that-i-made-you-love-me/1895420989</v>
+        <v>https://music.apple.com/us/album/think-as-you-drunk/6770725355</v>
       </c>
       <c r="L122" t="str">
-        <v>hate that i made you love me - Ariana Grande</v>
+        <v>Think As You Drunk - Riley Green</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Come Inside</v>
+        <v>Play Your Games</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/come-inside/1887403093</v>
+        <v>https://music.apple.com/us/song/play-your-games/6772932837</v>
       </c>
       <c r="D123" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E123" t="str">
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>The Boys of Dungeon Lane</v>
+        <v>Play Your Games - Single</v>
       </c>
       <c r="G123" t="str">
-        <v>3:13</v>
+        <v>3:15</v>
       </c>
       <c r="H123" t="str">
-        <v>Paul McCartney</v>
+        <v>Greta Van Fleet</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/paul-mccartney/12224</v>
+        <v>https://music.apple.com/us/artist/greta-van-fleet/646178956</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/come-inside/1887402919</v>
+        <v>https://music.apple.com/us/album/play-your-games/6772932835</v>
       </c>
       <c r="L123" t="str">
-        <v>Come Inside - Paul McCartney</v>
+        <v>Play Your Games - Greta Van Fleet</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Game Time</v>
+        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello)</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/game-time/6771157200</v>
+        <v>https://music.apple.com/us/song/adjourn-it-feat-serj-tankian-roman-morello/6769340216</v>
       </c>
       <c r="D124" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E124" t="str">
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Game Time (FIFA World Cup 2026™) - Single</v>
+        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello) - Single</v>
       </c>
       <c r="G124" t="str">
-        <v>3:26</v>
+        <v>2:47</v>
       </c>
       <c r="H124" t="str">
-        <v>Future</v>
+        <v>Tom Morello</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/future/128050210</v>
+        <v>https://music.apple.com/us/artist/tom-morello/466357</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/game-time/6771157186</v>
+        <v>https://music.apple.com/us/album/adjourn-it-feat-serj-tankian-roman-morello/6769340214</v>
       </c>
       <c r="L124" t="str">
-        <v>Game Time - Future</v>
+        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello) - Tom Morello</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Motion Party (Remix)</v>
+        <v>Essex_Honey.mp3</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/motion-party-remix/6773413965</v>
+        <v>https://music.apple.com/us/song/essex-honey-mp3/6771169447</v>
       </c>
       <c r="D125" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E125" t="str">
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Motion Party (Remix) - Single</v>
+        <v>Essex_Honey.mp3 - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>2:36</v>
+        <v>4:49</v>
       </c>
       <c r="H125" t="str">
-        <v>Bossman Dlow</v>
+        <v>Blood Orange</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/bossman-dlow/1474308236</v>
+        <v>https://music.apple.com/us/artist/blood-orange/440698865</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/motion-party-remix/6773413953</v>
+        <v>https://music.apple.com/us/album/essex-honey-mp3/6771169151</v>
       </c>
       <c r="L125" t="str">
-        <v>Motion Party (Remix) - Bossman Dlow</v>
+        <v>Essex_Honey.mp3 - Blood Orange</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Aquel diciembre</v>
+        <v>minute</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/aquel-diciembre/6769580010</v>
+        <v>https://music.apple.com/us/song/minute/1875303122</v>
       </c>
       <c r="D126" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E126" t="str">
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Do Not Disturb: Late Checkout</v>
+        <v>ghosted - EP</v>
       </c>
       <c r="G126" t="str">
-        <v>3:22</v>
+        <v>2:59</v>
       </c>
       <c r="H126" t="str">
-        <v>Young Miko</v>
+        <v>Saint Harison</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/young-miko/1576521417</v>
+        <v>https://music.apple.com/us/artist/saint-harison/1639595302</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/aquel-diciembre/6769579992</v>
+        <v>https://music.apple.com/us/album/minute/1875302904</v>
       </c>
       <c r="L126" t="str">
-        <v>Aquel diciembre - Young Miko</v>
+        <v>minute - Saint Harison</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Handle</v>
+        <v>THE LIVING</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/handle/6771922623</v>
+        <v>https://music.apple.com/us/song/the-living/1894092345</v>
       </c>
       <c r="D127" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E127" t="str">
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Blue Island</v>
+        <v>COSMIC OPERA ACT II</v>
       </c>
       <c r="G127" t="str">
-        <v>3:06</v>
+        <v>2:48</v>
       </c>
       <c r="H127" t="str">
-        <v>Ravyn Lenae</v>
+        <v>Labrinth</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/ravyn-lenae/1044417443</v>
+        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/handle/6771922622</v>
+        <v>https://music.apple.com/us/album/the-living/1894092339</v>
       </c>
       <c r="L127" t="str">
-        <v>Handle - Ravyn Lenae</v>
+        <v>THE LIVING - Labrinth</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Every Single Weekend (feat. Jamie xx)</v>
+        <v>Thug</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/every-single-weekend-feat-jamie-xx/6770445933</v>
+        <v>https://music.apple.com/us/song/thug/6769289966</v>
       </c>
       <c r="D128" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E128" t="str">
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Every Single Weekend (feat. Jamie xx) - Single</v>
+        <v>Thug - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>2:10</v>
+        <v>2:25</v>
       </c>
       <c r="H128" t="str">
-        <v>The Avalanches</v>
+        <v>G Herbo</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/the-avalanches/27524431</v>
+        <v>https://music.apple.com/us/artist/g-herbo/1036753321</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/every-single-weekend-feat-jamie-xx/6770445752</v>
+        <v>https://music.apple.com/us/album/thug/6769289953</v>
       </c>
       <c r="L128" t="str">
-        <v>Every Single Weekend (feat. Jamie xx) - The Avalanches</v>
+        <v>Thug - G Herbo</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>The Wave</v>
+        <v>Clap</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/the-wave/1886730541</v>
+        <v>https://music.apple.com/us/song/clap/6769903711</v>
       </c>
       <c r="D129" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E129" t="str">
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Sunshine</v>
+        <v>Clap - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>3:22</v>
+        <v>2:04</v>
       </c>
       <c r="H129" t="str">
-        <v>Jungle</v>
+        <v>Polo G</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/jungle/825833522</v>
+        <v>https://music.apple.com/us/artist/polo-g/1159371412</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/the-wave/1886730527</v>
+        <v>https://music.apple.com/us/album/clap/6769903710</v>
       </c>
       <c r="L129" t="str">
-        <v>The Wave - Jungle</v>
+        <v>Clap - Polo G</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>STOP</v>
+        <v>GANG BIZNESS</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/stop/6771161771</v>
+        <v>https://music.apple.com/us/song/gang-bizness/6772383809</v>
       </c>
       <c r="D130" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E130" t="str">
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>are you mad at me? - Single</v>
+        <v>THE GENTLEMEN'S CLUB</v>
       </c>
       <c r="G130" t="str">
-        <v>2:56</v>
+        <v>2:47</v>
       </c>
       <c r="H130" t="str">
-        <v>Bella Kay</v>
+        <v>YG</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
+        <v>https://music.apple.com/us/artist/yg/189792075</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/stop/6771161760</v>
+        <v>https://music.apple.com/us/album/gang-bizness/6772383681</v>
       </c>
       <c r="L130" t="str">
-        <v>STOP - Bella Kay</v>
+        <v>GANG BIZNESS - YG</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Here (Apple Music Sessions)</v>
+        <v>UR HEARTBEAT (WHO DO U THINK ABOUT AT 2AM?)</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/here-apple-music-sessions/1878235516</v>
+        <v>https://music.apple.com/us/song/ur-heartbeat-who-do-u-think-about-at-2am/6765534140</v>
       </c>
       <c r="D131" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E131" t="str">
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Apple Music Sessions</v>
+        <v>A LITTLE VENGEANCE</v>
       </c>
       <c r="G131" t="str">
-        <v>3:08</v>
+        <v>2:50</v>
       </c>
       <c r="H131" t="str">
-        <v>Mumford &amp; Sons</v>
+        <v>Jessie Reyez</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/mumford-sons/307699986</v>
+        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/here-apple-music-sessions/1878235330</v>
+        <v>https://music.apple.com/us/album/ur-heartbeat-who-do-u-think-about-at-2am/1895983502</v>
       </c>
       <c r="L131" t="str">
-        <v>Here (Apple Music Sessions) - Mumford &amp; Sons</v>
+        <v>UR HEARTBEAT (WHO DO U THINK ABOUT AT 2AM?) - Jessie Reyez</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Talk On The Hill</v>
+        <v>Joshua Tree</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/talk-on-the-hill/6769524458</v>
+        <v>https://music.apple.com/us/song/joshua-tree/6771859148</v>
       </c>
       <c r="D132" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E132" t="str">
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>The Thread</v>
+        <v>Euphoria: Season 3 (HBO Original Series Soundtrack)</v>
       </c>
       <c r="G132" t="str">
-        <v>3:27</v>
+        <v>2:50</v>
       </c>
       <c r="H132" t="str">
-        <v>WILLOW</v>
+        <v>Hans Zimmer</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/willow/400531893</v>
+        <v>https://music.apple.com/us/artist/hans-zimmer/454295032</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/talk-on-the-hill/6769524450</v>
+        <v>https://music.apple.com/us/album/joshua-tree/6771858464</v>
       </c>
       <c r="L132" t="str">
-        <v>Talk On The Hill - WILLOW</v>
+        <v>Joshua Tree - Hans Zimmer</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>No Fear</v>
+        <v>Mi Gran Amor</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/no-fear/1880484493</v>
+        <v>https://music.apple.com/us/song/mi-gran-amor/6773365775</v>
       </c>
       <c r="D133" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E133" t="str">
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>For Love of Grace &amp; the Hereafter</v>
+        <v>Mi Gran Amor - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>3:38</v>
+        <v>3:37</v>
       </c>
       <c r="H133" t="str">
-        <v>Iceage</v>
+        <v>Santana</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/iceage/406846711</v>
+        <v>https://music.apple.com/us/artist/santana/217174</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/no-fear/1880484160</v>
+        <v>https://music.apple.com/us/album/mi-gran-amor/6773365236</v>
       </c>
       <c r="L133" t="str">
-        <v>No Fear - Iceage</v>
+        <v>Mi Gran Amor - Santana</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Hostage</v>
+        <v>london</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/hostage/6774372288</v>
+        <v>https://music.apple.com/us/song/london/6770745672</v>
       </c>
       <c r="D134" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E134" t="str">
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Big Mama</v>
+        <v>stardust - EP</v>
       </c>
       <c r="G134" t="str">
-        <v>3:11</v>
+        <v>3:23</v>
       </c>
       <c r="H134" t="str">
-        <v>Latto</v>
+        <v>Freya Skye</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/latto/419799506</v>
+        <v>https://music.apple.com/us/artist/freya-skye/1541643053</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/hostage/6774372200</v>
+        <v>https://music.apple.com/us/album/london/6770745662</v>
       </c>
       <c r="L134" t="str">
-        <v>Hostage - Latto</v>
+        <v>london - Freya Skye</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Sad Girls</v>
+        <v>Caution</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/sad-girls/6768814374</v>
+        <v>https://music.apple.com/us/song/caution/6768487482</v>
       </c>
       <c r="D135" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E135" t="str">
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Sad Girls - Single</v>
+        <v>K-POPS! (Music from and inspired by K-POPS! Motion Picture)</v>
       </c>
       <c r="G135" t="str">
-        <v>2:48</v>
+        <v>2:43</v>
       </c>
       <c r="H135" t="str">
-        <v>Bebe Rexha</v>
+        <v>NMIXX</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/bebe-rexha/466059563</v>
+        <v>https://music.apple.com/us/artist/nmixx/1600411676</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/sad-girls/6768814373</v>
+        <v>https://music.apple.com/us/album/caution/6768487478</v>
       </c>
       <c r="L135" t="str">
-        <v>Sad Girls - Bebe Rexha</v>
+        <v>Caution - NMIXX</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Salvame Hoy (feat. Gabito Ballesteros)</v>
+        <v>LEMONADE (feat. Becky G)</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/salvame-hoy-feat-gabito-ballesteros/6765697019</v>
+        <v>https://music.apple.com/us/song/lemonade-feat-becky-g/1893742425</v>
       </c>
       <c r="D136" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E136" t="str">
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Salvame Hoy (feat. Gabito Ballesteros) - Single</v>
+        <v>LEMONADE - The 2nd Album</v>
       </c>
       <c r="G136" t="str">
-        <v>3:35</v>
+        <v>3:07</v>
       </c>
       <c r="H136" t="str">
-        <v>Jennifer Lopez</v>
+        <v>aespa</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/jennifer-lopez/463009</v>
+        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/salvame-hoy-feat-gabito-ballesteros/1896041010</v>
+        <v>https://music.apple.com/us/album/lemonade-feat-becky-g/1893742002</v>
       </c>
       <c r="L136" t="str">
-        <v>Salvame Hoy (feat. Gabito Ballesteros) - Jennifer Lopez</v>
+        <v>LEMONADE (feat. Becky G) - aespa</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Rubio</v>
+        <v>Take Me Back (Leave Me There)</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/rubio/6770655339</v>
+        <v>https://music.apple.com/us/song/take-me-back-leave-me-there/1892466278</v>
       </c>
       <c r="D137" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E137" t="str">
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>La Voz Favorita</v>
+        <v>Banks Of The Trinity</v>
       </c>
       <c r="G137" t="str">
-        <v>4:42</v>
+        <v>2:58</v>
       </c>
       <c r="H137" t="str">
-        <v>Jay Wheeler</v>
+        <v>Cody Johnson</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/jay-wheeler/164376380</v>
+        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/rubio/6770654729</v>
+        <v>https://music.apple.com/us/album/take-me-back-leave-me-there/1892465981</v>
       </c>
       <c r="L137" t="str">
-        <v>Rubio - Jay Wheeler</v>
+        <v>Take Me Back (Leave Me There) - Cody Johnson</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Pary</v>
+        <v>Cheap Thrills</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/pary/6767367748</v>
+        <v>https://music.apple.com/us/song/cheap-thrills/6771156732</v>
       </c>
       <c r="D138" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E138" t="str">
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Con dolor - EP</v>
+        <v>Cheap Thrills - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>2:52</v>
+        <v>2:42</v>
       </c>
       <c r="H138" t="str">
-        <v>Grupo Frontera</v>
+        <v>Gavin Adcock</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
+        <v>https://music.apple.com/us/artist/gavin-adcock/1580645019</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/pary/6767367501</v>
+        <v>https://music.apple.com/us/album/cheap-thrills/6771156723</v>
       </c>
       <c r="L138" t="str">
-        <v>Pary - Grupo Frontera</v>
+        <v>Cheap Thrills - Gavin Adcock</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Think As You Drunk</v>
+        <v>ME VALE V</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/think-as-you-drunk/6770725979</v>
+        <v>https://music.apple.com/us/song/me-vale-v/6769567844</v>
       </c>
       <c r="D139" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E139" t="str">
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>That's Just Me</v>
+        <v>ACOMODO</v>
       </c>
       <c r="G139" t="str">
-        <v>3:48</v>
+        <v>3:06</v>
       </c>
       <c r="H139" t="str">
-        <v>Riley Green</v>
+        <v>Tito Double P</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/riley-green/662432971</v>
+        <v>https://music.apple.com/us/artist/tito-double-p/1690905306</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/think-as-you-drunk/6770725355</v>
+        <v>https://music.apple.com/us/album/me-vale-v/6769567568</v>
       </c>
       <c r="L139" t="str">
-        <v>Think As You Drunk - Riley Green</v>
+        <v>ME VALE V - Tito Double P</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Play Your Games</v>
+        <v>Bug In The Cake</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/play-your-games/6772932837</v>
+        <v>https://music.apple.com/us/song/bug-in-the-cake/1880470542</v>
       </c>
       <c r="D140" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E140" t="str">
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Play Your Games - Single</v>
+        <v>Be Sweet To Me</v>
       </c>
       <c r="G140" t="str">
-        <v>3:15</v>
+        <v>2:48</v>
       </c>
       <c r="H140" t="str">
-        <v>Greta Van Fleet</v>
+        <v>Violet Grohl</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/greta-van-fleet/646178956</v>
+        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/play-your-games/6772932835</v>
+        <v>https://music.apple.com/us/album/bug-in-the-cake/1880470537</v>
       </c>
       <c r="L140" t="str">
-        <v>Play Your Games - Greta Van Fleet</v>
+        <v>Bug In The Cake - Violet Grohl</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello)</v>
+        <v>Coil</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/adjourn-it-feat-serj-tankian-roman-morello/6769340216</v>
+        <v>https://music.apple.com/us/song/coil/6766858354</v>
       </c>
       <c r="D141" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E141" t="str">
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello) - Single</v>
+        <v>Rumspringa</v>
       </c>
       <c r="G141" t="str">
-        <v>2:47</v>
+        <v>3:54</v>
       </c>
       <c r="H141" t="str">
-        <v>Tom Morello</v>
+        <v>ear</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/tom-morello/466357</v>
+        <v>https://music.apple.com/us/artist/ear/1829661500</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/adjourn-it-feat-serj-tankian-roman-morello/6769340214</v>
+        <v>https://music.apple.com/us/album/coil/6766858352</v>
       </c>
       <c r="L141" t="str">
-        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello) - Tom Morello</v>
+        <v>Coil - ear</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Essex_Honey.mp3</v>
+        <v>Smugglers &amp; Scholars (feat. Killer Mike)</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/essex-honey-mp3/6771169447</v>
+        <v>https://music.apple.com/us/song/smugglers-scholars-feat-killer-mike/6769424017</v>
       </c>
       <c r="D142" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E142" t="str">
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Essex_Honey.mp3 - Single</v>
+        <v>Smugglers &amp; Scholars (feat. Killer Mike) - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>4:49</v>
+        <v>3:30</v>
       </c>
       <c r="H142" t="str">
-        <v>Blood Orange</v>
+        <v>Kneecap</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/blood-orange/440698865</v>
+        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/essex-honey-mp3/6771169151</v>
+        <v>https://music.apple.com/us/album/smugglers-scholars-feat-killer-mike/6769423676</v>
       </c>
       <c r="L142" t="str">
-        <v>Essex_Honey.mp3 - Blood Orange</v>
+        <v>Smugglers &amp; Scholars (feat. Killer Mike) - Kneecap</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>minute</v>
+        <v>Out of my Head</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/minute/1875303122</v>
+        <v>https://music.apple.com/us/song/out-of-my-head/6767725166</v>
       </c>
       <c r="D143" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E143" t="str">
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>ghosted - EP</v>
+        <v>I Forgot / Out of my Head - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>2:59</v>
+        <v>3:04</v>
       </c>
       <c r="H143" t="str">
-        <v>Saint Harison</v>
+        <v>Cara Delevingne</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/saint-harison/1639595302</v>
+        <v>https://music.apple.com/us/artist/cara-delevingne/1204798982</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/minute/1875302904</v>
+        <v>https://music.apple.com/us/album/out-of-my-head/6767725156</v>
       </c>
       <c r="L143" t="str">
-        <v>minute - Saint Harison</v>
+        <v>Out of my Head - Cara Delevingne</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>THE LIVING</v>
+        <v>Passenger Princess</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/the-living/1894092345</v>
+        <v>https://music.apple.com/us/song/passenger-princess/6771012228</v>
       </c>
       <c r="D144" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E144" t="str">
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>COSMIC OPERA ACT II</v>
+        <v>Passenger Princess - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>2:48</v>
+        <v>3:18</v>
       </c>
       <c r="H144" t="str">
-        <v>Labrinth</v>
+        <v>Perrie</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
+        <v>https://music.apple.com/us/artist/perrie/1729865272</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/the-living/1894092339</v>
+        <v>https://music.apple.com/us/album/passenger-princess/6771012223</v>
       </c>
       <c r="L144" t="str">
-        <v>THE LIVING - Labrinth</v>
+        <v>Passenger Princess - Perrie</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Thug</v>
+        <v>Man of the House</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/thug/6769289966</v>
+        <v>https://music.apple.com/us/song/man-of-the-house/1893733057</v>
       </c>
       <c r="D145" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E145" t="str">
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Thug - Single</v>
+        <v>SE9</v>
       </c>
       <c r="G145" t="str">
-        <v>2:25</v>
+        <v>2:35</v>
       </c>
       <c r="H145" t="str">
-        <v>G Herbo</v>
+        <v>Skye Newman</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/g-herbo/1036753321</v>
+        <v>https://music.apple.com/us/artist/skye-newman/1799174381</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/thug/6769289953</v>
+        <v>https://music.apple.com/us/album/man-of-the-house/1893733056</v>
       </c>
       <c r="L145" t="str">
-        <v>Thug - G Herbo</v>
+        <v>Man of the House - Skye Newman</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Clap</v>
+        <v>Beautiful Freeks</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/clap/6769903711</v>
+        <v>https://music.apple.com/us/song/beautiful-freeks/6764602396</v>
       </c>
       <c r="D146" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E146" t="str">
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Clap - Single</v>
+        <v>Beautiful Freeks - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>2:04</v>
+        <v>2:37</v>
       </c>
       <c r="H146" t="str">
-        <v>Polo G</v>
+        <v>MEEK</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/polo-g/1159371412</v>
+        <v>https://music.apple.com/us/artist/meek/1784432868</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/clap/6769903710</v>
+        <v>https://music.apple.com/us/album/beautiful-freeks/6764602393</v>
       </c>
       <c r="L146" t="str">
-        <v>Clap - Polo G</v>
+        <v>Beautiful Freeks - MEEK</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>GANG BIZNESS</v>
+        <v>Slave to the Rithm (feat. Bring Me The Horizon) [I Hate Models Never Alone Remix]</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/gang-bizness/6772383809</v>
+        <v>https://music.apple.com/us/song/slave-to-the-rithm-feat-bring-me-the-horizon-i/6771972616</v>
       </c>
       <c r="D147" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E147" t="str">
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>THE GENTLEMEN'S CLUB</v>
+        <v>Slave to the Rithm (I Hate Models Never Alone Remix) [feat. Bring Me The Horizon] - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>2:47</v>
+        <v>4:34</v>
       </c>
       <c r="H147" t="str">
-        <v>YG</v>
+        <v>ILLENIUM</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/yg/189792075</v>
+        <v>https://music.apple.com/us/artist/illenium/645420096</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/gang-bizness/6772383681</v>
+        <v>https://music.apple.com/us/album/slave-to-the-rithm-feat-bring-me-the-horizon-i/6771972613</v>
       </c>
       <c r="L147" t="str">
-        <v>GANG BIZNESS - YG</v>
+        <v>Slave to the Rithm (feat. Bring Me The Horizon) [I Hate Models Never Alone Remix] - ILLENIUM</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>UR HEARTBEAT (WHO DO U THINK ABOUT AT 2AM?)</v>
+        <v>Beg For Me (JADE Remix)</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/ur-heartbeat-who-do-u-think-about-at-2am/6765534140</v>
+        <v>https://music.apple.com/us/song/beg-for-me-jade-remix/6771474203</v>
       </c>
       <c r="D148" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E148" t="str">
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>A LITTLE VENGEANCE</v>
+        <v>Beg For Me (Remix) - Single</v>
       </c>
       <c r="G148" t="str">
         <v>2:50</v>
       </c>
       <c r="H148" t="str">
-        <v>Jessie Reyez</v>
+        <v>Lily Allen</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
+        <v>https://music.apple.com/us/artist/lily-allen/157063999</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/ur-heartbeat-who-do-u-think-about-at-2am/1895983502</v>
+        <v>https://music.apple.com/us/album/beg-for-me-jade-remix/6771474201</v>
       </c>
       <c r="L148" t="str">
-        <v>UR HEARTBEAT (WHO DO U THINK ABOUT AT 2AM?) - Jessie Reyez</v>
+        <v>Beg For Me (JADE Remix) - Lily Allen</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Joshua Tree</v>
+        <v>ABOVE IT</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/joshua-tree/6771859148</v>
+        <v>https://music.apple.com/us/song/above-it/6766248703</v>
       </c>
       <c r="D149" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E149" t="str">
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Euphoria: Season 3 (HBO Original Series Soundtrack)</v>
+        <v>GET THE TABLES - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>2:50</v>
+        <v>1:45</v>
       </c>
       <c r="H149" t="str">
-        <v>Hans Zimmer</v>
+        <v>Andy Mineo</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/hans-zimmer/454295032</v>
+        <v>https://music.apple.com/us/artist/andy-mineo/257538441</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/joshua-tree/6771858464</v>
+        <v>https://music.apple.com/us/album/above-it/6766248699</v>
       </c>
       <c r="L149" t="str">
-        <v>Joshua Tree - Hans Zimmer</v>
+        <v>ABOVE IT - Andy Mineo</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Mi Gran Amor</v>
+        <v>THE JESUS GENERATION</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/mi-gran-amor/6773365775</v>
+        <v>https://music.apple.com/us/song/the-jesus-generation/6773948895</v>
       </c>
       <c r="D150" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E150" t="str">
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Mi Gran Amor - Single</v>
+        <v>THE JESUS GENERATION - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>3:37</v>
+        <v>4:15</v>
       </c>
       <c r="H150" t="str">
-        <v>Santana</v>
+        <v>Forrest Frank</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/santana/217174</v>
+        <v>https://music.apple.com/us/artist/forrest-frank/1436657314</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/mi-gran-amor/6773365236</v>
+        <v>https://music.apple.com/us/album/the-jesus-generation/6773948742</v>
       </c>
       <c r="L150" t="str">
-        <v>Mi Gran Amor - Santana</v>
+        <v>THE JESUS GENERATION - Forrest Frank</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>london</v>
+        <v>Is It Over Now?</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/london/6770745672</v>
+        <v>https://music.apple.com/us/song/is-it-over-now/6767564750</v>
       </c>
       <c r="D151" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E151" t="str">
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>stardust - EP</v>
+        <v>Is It Over Now? - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>3:23</v>
+        <v>3:39</v>
       </c>
       <c r="H151" t="str">
-        <v>Freya Skye</v>
+        <v>Elderbrook</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/freya-skye/1541643053</v>
+        <v>https://music.apple.com/us/artist/elderbrook/736829657</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/london/6770745662</v>
+        <v>https://music.apple.com/us/album/is-it-over-now/6767564746</v>
       </c>
       <c r="L151" t="str">
-        <v>london - Freya Skye</v>
+        <v>Is It Over Now? - Elderbrook</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Caution</v>
+        <v>12 Steps</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/caution/6768487482</v>
+        <v>https://music.apple.com/us/song/12-steps/6769559623</v>
       </c>
       <c r="D152" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E152" t="str">
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>K-POPS! (Music from and inspired by K-POPS! Motion Picture)</v>
+        <v>12 Steps - Single</v>
       </c>
       <c r="G152" t="str">
-        <v>2:43</v>
+        <v>3:11</v>
       </c>
       <c r="H152" t="str">
-        <v>NMIXX</v>
+        <v>Dexter and The Moonrocks</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/nmixx/1600411676</v>
+        <v>https://music.apple.com/us/artist/dexter-and-the-moonrocks/1581657500</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/caution/6768487478</v>
+        <v>https://music.apple.com/us/album/12-steps/6769559618</v>
       </c>
       <c r="L152" t="str">
-        <v>Caution - NMIXX</v>
+        <v>12 Steps - Dexter and The Moonrocks</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>LEMONADE (feat. Becky G)</v>
+        <v>Over And Over</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/lemonade-feat-becky-g/1893742425</v>
+        <v>https://music.apple.com/us/song/over-and-over/6771585908</v>
       </c>
       <c r="D153" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E153" t="str">
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>LEMONADE - The 2nd Album</v>
+        <v>It's A Dying Art</v>
       </c>
       <c r="G153" t="str">
-        <v>3:07</v>
+        <v>4:38</v>
       </c>
       <c r="H153" t="str">
-        <v>aespa</v>
+        <v>Little Big Town</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
+        <v>https://music.apple.com/us/artist/little-big-town/513770</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/lemonade-feat-becky-g/1893742002</v>
+        <v>https://music.apple.com/us/album/over-and-over/6771585889</v>
       </c>
       <c r="L153" t="str">
-        <v>LEMONADE (feat. Becky G) - aespa</v>
+        <v>Over And Over - Little Big Town</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Take Me Back (Leave Me There)</v>
+        <v>AMAPOLA</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/take-me-back-leave-me-there/1892466278</v>
+        <v>https://music.apple.com/us/song/amapola/6769560428</v>
       </c>
       <c r="D154" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E154" t="str">
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Banks Of The Trinity</v>
+        <v>Ricky y Mau</v>
       </c>
       <c r="G154" t="str">
-        <v>2:58</v>
+        <v>2:22</v>
       </c>
       <c r="H154" t="str">
-        <v>Cody Johnson</v>
+        <v>Mau y Ricky</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
+        <v>https://music.apple.com/us/artist/mau-y-ricky/1096068683</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/take-me-back-leave-me-there/1892465981</v>
+        <v>https://music.apple.com/us/album/amapola/6769559985</v>
       </c>
       <c r="L154" t="str">
-        <v>Take Me Back (Leave Me There) - Cody Johnson</v>
+        <v>AMAPOLA - Mau y Ricky</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Cheap Thrills</v>
+        <v>Mad About It</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/cheap-thrills/6771156732</v>
+        <v>https://music.apple.com/us/song/mad-about-it/6767425272</v>
       </c>
       <c r="D155" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E155" t="str">
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Cheap Thrills - Single</v>
+        <v>Mad About It - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>2:42</v>
+        <v>2:37</v>
       </c>
       <c r="H155" t="str">
-        <v>Gavin Adcock</v>
+        <v>Dasha</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/gavin-adcock/1580645019</v>
+        <v>https://music.apple.com/us/artist/dasha/1462663731</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/cheap-thrills/6771156723</v>
+        <v>https://music.apple.com/us/album/mad-about-it/6767425271</v>
       </c>
       <c r="L155" t="str">
-        <v>Cheap Thrills - Gavin Adcock</v>
+        <v>Mad About It - Dasha</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>ME VALE V</v>
+        <v>Love’s a Gun</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/me-vale-v/6769567844</v>
+        <v>https://music.apple.com/us/song/loves-a-gun/6771898253</v>
       </c>
       <c r="D156" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E156" t="str">
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>ACOMODO</v>
+        <v>Love’s a Gun - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>3:06</v>
+        <v>2:59</v>
       </c>
       <c r="H156" t="str">
-        <v>Tito Double P</v>
+        <v>Daniel Seavey</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/tito-double-p/1690905306</v>
+        <v>https://music.apple.com/us/artist/daniel-seavey/1646124302</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/me-vale-v/6769567568</v>
+        <v>https://music.apple.com/us/album/loves-a-gun/6771897951</v>
       </c>
       <c r="L156" t="str">
-        <v>ME VALE V - Tito Double P</v>
+        <v>Love’s a Gun - Daniel Seavey</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Bug In The Cake</v>
+        <v>Long Story Short</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/bug-in-the-cake/1880470542</v>
+        <v>https://music.apple.com/us/song/long-story-short/6770700866</v>
       </c>
       <c r="D157" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E157" t="str">
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Be Sweet To Me</v>
+        <v>Long Story Short - Single</v>
       </c>
       <c r="G157" t="str">
         <v>2:48</v>
       </c>
       <c r="H157" t="str">
-        <v>Violet Grohl</v>
+        <v>Knox</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
+        <v>https://music.apple.com/us/artist/knox/1547519433</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/bug-in-the-cake/1880470537</v>
+        <v>https://music.apple.com/us/album/long-story-short/6770700853</v>
       </c>
       <c r="L157" t="str">
-        <v>Bug In The Cake - Violet Grohl</v>
+        <v>Long Story Short - Knox</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Coil</v>
+        <v>Dior</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/coil/6766858354</v>
+        <v>https://music.apple.com/us/song/dior/1892136721</v>
       </c>
       <c r="D158" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E158" t="str">
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Rumspringa</v>
+        <v>bitknot</v>
       </c>
       <c r="G158" t="str">
-        <v>3:54</v>
+        <v>3:32</v>
       </c>
       <c r="H158" t="str">
-        <v>ear</v>
+        <v>feeble little horse</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/ear/1829661500</v>
+        <v>https://music.apple.com/us/artist/feeble-little-horse/1564273208</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/coil/6766858352</v>
+        <v>https://music.apple.com/us/album/dior/1892136714</v>
       </c>
       <c r="L158" t="str">
-        <v>Coil - ear</v>
+        <v>Dior - feeble little horse</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Smugglers &amp; Scholars (feat. Killer Mike)</v>
+        <v>blue jeans</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/smugglers-scholars-feat-killer-mike/6769424017</v>
+        <v>https://music.apple.com/us/song/blue-jeans/6770529591</v>
       </c>
       <c r="D159" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E159" t="str">
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Smugglers &amp; Scholars (feat. Killer Mike) - Single</v>
+        <v>blue jeans - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>3:30</v>
+        <v>2:37</v>
       </c>
       <c r="H159" t="str">
-        <v>Kneecap</v>
+        <v>Nightly</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
+        <v>https://music.apple.com/us/artist/nightly/352310972</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/smugglers-scholars-feat-killer-mike/6769423676</v>
+        <v>https://music.apple.com/us/album/blue-jeans/6770529589</v>
       </c>
       <c r="L159" t="str">
-        <v>Smugglers &amp; Scholars (feat. Killer Mike) - Kneecap</v>
+        <v>blue jeans - Nightly</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Out of my Head</v>
+        <v>Que Gacho</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/out-of-my-head/6767725166</v>
+        <v>https://music.apple.com/us/song/que-gacho/6770628420</v>
       </c>
       <c r="D160" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E160" t="str">
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>I Forgot / Out of my Head - Single</v>
+        <v>Que Gacho - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>3:04</v>
+        <v>3:13</v>
       </c>
       <c r="H160" t="str">
-        <v>Cara Delevingne</v>
+        <v>Luis R Conriquez</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/cara-delevingne/1204798982</v>
+        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/out-of-my-head/6767725156</v>
+        <v>https://music.apple.com/us/album/que-gacho/6770628419</v>
       </c>
       <c r="L160" t="str">
-        <v>Out of my Head - Cara Delevingne</v>
+        <v>Que Gacho - Luis R Conriquez</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Passenger Princess</v>
+        <v>same God</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/passenger-princess/6771012228</v>
+        <v>https://music.apple.com/us/song/same-god/1878232616</v>
       </c>
       <c r="D161" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E161" t="str">
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Passenger Princess - Single</v>
+        <v>I HOPE THIS HELPS</v>
       </c>
       <c r="G161" t="str">
-        <v>3:18</v>
+        <v>3:34</v>
       </c>
       <c r="H161" t="str">
-        <v>Perrie</v>
+        <v>Alana Springsteen</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/perrie/1729865272</v>
+        <v>https://music.apple.com/us/artist/alana-springsteen/1309335606</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/passenger-princess/6771012223</v>
+        <v>https://music.apple.com/us/album/same-god/1878232194</v>
       </c>
       <c r="L161" t="str">
-        <v>Passenger Princess - Perrie</v>
+        <v>same God - Alana Springsteen</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Man of the House</v>
+        <v>emotional swaggage</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/man-of-the-house/1893733057</v>
+        <v>https://music.apple.com/us/song/emotional-swaggage/6767397453</v>
       </c>
       <c r="D162" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E162" t="str">
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>SE9</v>
+        <v>IDCASH</v>
       </c>
       <c r="G162" t="str">
-        <v>2:35</v>
+        <v>2:12</v>
       </c>
       <c r="H162" t="str">
-        <v>Skye Newman</v>
+        <v>IDK</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/skye-newman/1799174381</v>
+        <v>https://music.apple.com/us/artist/idk/1578186947</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/man-of-the-house/1893733056</v>
+        <v>https://music.apple.com/us/album/emotional-swaggage/6767397348</v>
       </c>
       <c r="L162" t="str">
-        <v>Man of the House - Skye Newman</v>
+        <v>emotional swaggage - IDK</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Beautiful Freeks</v>
+        <v>Baby Driver</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/beautiful-freeks/6764602396</v>
+        <v>https://music.apple.com/us/song/baby-driver/6769152279</v>
       </c>
       <c r="D163" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E163" t="str">
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Beautiful Freeks - Single</v>
+        <v>Baby Driver - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>2:37</v>
+        <v>3:36</v>
       </c>
       <c r="H163" t="str">
-        <v>MEEK</v>
+        <v>070 Shake</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/meek/1784432868</v>
+        <v>https://music.apple.com/us/artist/070-shake/1097177293</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/beautiful-freeks/6764602393</v>
+        <v>https://music.apple.com/us/album/baby-driver/6769152273</v>
       </c>
       <c r="L163" t="str">
-        <v>Beautiful Freeks - MEEK</v>
+        <v>Baby Driver - 070 Shake</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Slave to the Rithm (feat. Bring Me The Horizon) [I Hate Models Never Alone Remix]</v>
+        <v>More! More! More!</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/slave-to-the-rithm-feat-bring-me-the-horizon-i/6771972616</v>
+        <v>https://music.apple.com/us/song/more-more-more/6770600105</v>
       </c>
       <c r="D164" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E164" t="str">
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Slave to the Rithm (I Hate Models Never Alone Remix) [feat. Bring Me The Horizon] - Single</v>
+        <v>REBECCA</v>
       </c>
       <c r="G164" t="str">
-        <v>4:34</v>
+        <v>2:55</v>
       </c>
       <c r="H164" t="str">
-        <v>ILLENIUM</v>
+        <v>Becky Hill</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/illenium/645420096</v>
+        <v>https://music.apple.com/us/artist/becky-hill/533839517</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/slave-to-the-rithm-feat-bring-me-the-horizon-i/6771972613</v>
+        <v>https://music.apple.com/us/album/more-more-more/6770600098</v>
       </c>
       <c r="L164" t="str">
-        <v>Slave to the Rithm (feat. Bring Me The Horizon) [I Hate Models Never Alone Remix] - ILLENIUM</v>
+        <v>More! More! More! - Becky Hill</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Beg For Me (JADE Remix)</v>
+        <v>Young Again</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/beg-for-me-jade-remix/6771474203</v>
+        <v>https://music.apple.com/us/song/young-again/1877229743</v>
       </c>
       <c r="D165" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E165" t="str">
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Beg For Me (Remix) - Single</v>
+        <v>EI8HT</v>
       </c>
       <c r="G165" t="str">
-        <v>2:50</v>
+        <v>3:36</v>
       </c>
       <c r="H165" t="str">
-        <v>Lily Allen</v>
+        <v>Shinedown</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/lily-allen/157063999</v>
+        <v>https://music.apple.com/us/artist/shinedown/1883858</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/beg-for-me-jade-remix/6771474201</v>
+        <v>https://music.apple.com/us/album/young-again/1877229738</v>
       </c>
       <c r="L165" t="str">
-        <v>Beg For Me (JADE Remix) - Lily Allen</v>
+        <v>Young Again - Shinedown</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>ABOVE IT</v>
+        <v>skinny dip</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/above-it/6766248703</v>
+        <v>https://music.apple.com/us/song/skinny-dip/6769856281</v>
       </c>
       <c r="D166" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E166" t="str">
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>GET THE TABLES - Single</v>
+        <v>skinny dip - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>1:45</v>
+        <v>3:12</v>
       </c>
       <c r="H166" t="str">
-        <v>Andy Mineo</v>
+        <v>almost monday</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/andy-mineo/257538441</v>
+        <v>https://music.apple.com/us/artist/almost-monday/1300723925</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/above-it/6766248699</v>
+        <v>https://music.apple.com/us/album/skinny-dip/6769855907</v>
       </c>
       <c r="L166" t="str">
-        <v>ABOVE IT - Andy Mineo</v>
+        <v>skinny dip - almost monday</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>THE JESUS GENERATION</v>
+        <v>girls like girls (from the motion picture)</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/the-jesus-generation/6773948895</v>
+        <v>https://music.apple.com/us/song/girls-like-girls-from-the-motion-picture/1893704575</v>
       </c>
       <c r="D167" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E167" t="str">
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>THE JESUS GENERATION - Single</v>
+        <v>girls like girls the album</v>
       </c>
       <c r="G167" t="str">
-        <v>4:15</v>
+        <v>4:14</v>
       </c>
       <c r="H167" t="str">
-        <v>Forrest Frank</v>
+        <v>Hayley Kiyoko</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/forrest-frank/1436657314</v>
+        <v>https://music.apple.com/us/artist/hayley-kiyoko/325569584</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/the-jesus-generation/6773948742</v>
+        <v>https://music.apple.com/us/album/girls-like-girls-from-the-motion-picture/1893704396</v>
       </c>
       <c r="L167" t="str">
-        <v>THE JESUS GENERATION - Forrest Frank</v>
+        <v>girls like girls (from the motion picture) - Hayley Kiyoko</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Is It Over Now?</v>
+        <v>Better Off</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/is-it-over-now/6767564750</v>
+        <v>https://music.apple.com/us/song/better-off/6772045367</v>
       </c>
       <c r="D168" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E168" t="str">
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Is It Over Now? - Single</v>
+        <v>Stages</v>
       </c>
       <c r="G168" t="str">
-        <v>3:39</v>
+        <v>3:16</v>
       </c>
       <c r="H168" t="str">
-        <v>Elderbrook</v>
+        <v>Lauren Alaina</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/elderbrook/736829657</v>
+        <v>https://music.apple.com/us/artist/lauren-alaina/425028816</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/is-it-over-now/6767564746</v>
+        <v>https://music.apple.com/us/album/better-off/6772044978</v>
       </c>
       <c r="L168" t="str">
-        <v>Is It Over Now? - Elderbrook</v>
+        <v>Better Off - Lauren Alaina</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>12 Steps</v>
+        <v>Everythang Pinka (feat. Teezo Touchdown)</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/12-steps/6769559623</v>
+        <v>https://music.apple.com/us/song/everythang-pinka-feat-teezo-touchdown/6772026590</v>
       </c>
       <c r="D169" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E169" t="str">
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>12 Steps - Single</v>
+        <v>Everythang Pinka (feat. Teezo Touchdown) - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>3:11</v>
+        <v>2:48</v>
       </c>
       <c r="H169" t="str">
-        <v>Dexter and The Moonrocks</v>
+        <v>Monaleo</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/dexter-and-the-moonrocks/1581657500</v>
+        <v>https://music.apple.com/us/artist/monaleo/1495603374</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/12-steps/6769559618</v>
+        <v>https://music.apple.com/us/album/everythang-pinka-feat-teezo-touchdown/6772026586</v>
       </c>
       <c r="L169" t="str">
-        <v>12 Steps - Dexter and The Moonrocks</v>
+        <v>Everythang Pinka (feat. Teezo Touchdown) - Monaleo</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Over And Over</v>
+        <v>Lost in translation...</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/over-and-over/6771585908</v>
+        <v>https://music.apple.com/us/song/lost-in-translation/1870971556</v>
       </c>
       <c r="D170" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E170" t="str">
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>It's A Dying Art</v>
+        <v>Dream inside a dream…</v>
       </c>
       <c r="G170" t="str">
-        <v>4:38</v>
+        <v>3:30</v>
       </c>
       <c r="H170" t="str">
-        <v>Little Big Town</v>
+        <v>R3HAB</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/little-big-town/513770</v>
+        <v>https://music.apple.com/us/artist/r3hab/331900515</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/over-and-over/6771585889</v>
+        <v>https://music.apple.com/us/album/lost-in-translation/1870971550</v>
       </c>
       <c r="L170" t="str">
-        <v>Over And Over - Little Big Town</v>
+        <v>Lost in translation... - R3HAB</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>AMAPOLA</v>
+        <v>Call Security</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/amapola/6769560428</v>
+        <v>https://music.apple.com/us/song/call-security/6769296603</v>
       </c>
       <c r="D171" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E171" t="str">
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Ricky y Mau</v>
+        <v>U, Me &amp; My Ego</v>
       </c>
       <c r="G171" t="str">
-        <v>2:22</v>
+        <v>3:22</v>
       </c>
       <c r="H171" t="str">
-        <v>Mau y Ricky</v>
+        <v>Chxrry</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/mau-y-ricky/1096068683</v>
+        <v>https://music.apple.com/us/artist/chxrry/1520135642</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/amapola/6769559985</v>
+        <v>https://music.apple.com/us/album/call-security/6769296591</v>
       </c>
       <c r="L171" t="str">
-        <v>AMAPOLA - Mau y Ricky</v>
+        <v>Call Security - Chxrry</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Mad About It</v>
+        <v>chaotic</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/mad-about-it/6767425272</v>
+        <v>https://music.apple.com/us/song/chaotic/6767629281</v>
       </c>
       <c r="D172" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E172" t="str">
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Mad About It - Single</v>
+        <v>scars to prove it</v>
       </c>
       <c r="G172" t="str">
-        <v>2:37</v>
+        <v>3:14</v>
       </c>
       <c r="H172" t="str">
-        <v>Dasha</v>
+        <v>Hailey Picardi</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/dasha/1462663731</v>
+        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/mad-about-it/6767425271</v>
+        <v>https://music.apple.com/us/album/chaotic/6767626506</v>
       </c>
       <c r="L172" t="str">
-        <v>Mad About It - Dasha</v>
+        <v>chaotic - Hailey Picardi</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Love’s a Gun</v>
+        <v>Keep It To Yourself</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/loves-a-gun/6771898253</v>
+        <v>https://music.apple.com/us/song/keep-it-to-yourself/6771099675</v>
       </c>
       <c r="D173" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E173" t="str">
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Love’s a Gun - Single</v>
+        <v>LOVE IS THE LAW</v>
       </c>
       <c r="G173" t="str">
-        <v>2:59</v>
+        <v>4:17</v>
       </c>
       <c r="H173" t="str">
-        <v>Daniel Seavey</v>
+        <v>Love Spells</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/daniel-seavey/1646124302</v>
+        <v>https://music.apple.com/us/artist/love-spells/1597025563</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/loves-a-gun/6771897951</v>
+        <v>https://music.apple.com/us/album/keep-it-to-yourself/6771099661</v>
       </c>
       <c r="L173" t="str">
-        <v>Love’s a Gun - Daniel Seavey</v>
+        <v>Keep It To Yourself - Love Spells</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Long Story Short</v>
+        <v>Something to Someone</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/long-story-short/6770700866</v>
+        <v>https://music.apple.com/us/song/something-to-someone/6767255424</v>
       </c>
       <c r="D174" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E174" t="str">
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Long Story Short - Single</v>
+        <v>Something to Someone - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>2:48</v>
+        <v>3:55</v>
       </c>
       <c r="H174" t="str">
-        <v>Knox</v>
+        <v>Max McNown</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/knox/1547519433</v>
+        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/long-story-short/6770700853</v>
+        <v>https://music.apple.com/us/album/something-to-someone/1896445136</v>
       </c>
       <c r="L174" t="str">
-        <v>Long Story Short - Knox</v>
+        <v>Something to Someone - Max McNown</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Dior</v>
+        <v>Green Screen (1pm)</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/dior/1892136721</v>
+        <v>https://music.apple.com/us/song/green-screen-1pm/6766279426</v>
       </c>
       <c r="D175" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E175" t="str">
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>bitknot</v>
+        <v>The Hours: High Noon</v>
       </c>
       <c r="G175" t="str">
-        <v>3:32</v>
+        <v>2:10</v>
       </c>
       <c r="H175" t="str">
-        <v>feeble little horse</v>
+        <v>Cautious Clay</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/feeble-little-horse/1564273208</v>
+        <v>https://music.apple.com/us/artist/cautious-clay/1064628701</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/dior/1892136714</v>
+        <v>https://music.apple.com/us/album/green-screen-1pm/1896264236</v>
       </c>
       <c r="L175" t="str">
-        <v>Dior - feeble little horse</v>
+        <v>Green Screen (1pm) - Cautious Clay</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>blue jeans</v>
+        <v>Scoreboard</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/blue-jeans/6770529591</v>
+        <v>https://music.apple.com/us/song/scoreboard/6767255746</v>
       </c>
       <c r="D176" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E176" t="str">
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>blue jeans - Single</v>
+        <v>I Just Wanna Be Loved</v>
       </c>
       <c r="G176" t="str">
-        <v>2:37</v>
+        <v>3:24</v>
       </c>
       <c r="H176" t="str">
-        <v>Nightly</v>
+        <v>Gabriella Rose</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/nightly/352310972</v>
+        <v>https://music.apple.com/us/artist/gabriella-rose/645706232</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/blue-jeans/6770529589</v>
+        <v>https://music.apple.com/us/album/scoreboard/1896445371</v>
       </c>
       <c r="L176" t="str">
-        <v>blue jeans - Nightly</v>
+        <v>Scoreboard - Gabriella Rose</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Que Gacho</v>
+        <v>High</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/que-gacho/6770628420</v>
+        <v>https://music.apple.com/us/song/high/6773775211</v>
       </c>
       <c r="D177" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E177" t="str">
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Que Gacho - Single</v>
+        <v>Payback Is A Dog (EP)</v>
       </c>
       <c r="G177" t="str">
-        <v>3:13</v>
+        <v>2:55</v>
       </c>
       <c r="H177" t="str">
-        <v>Luis R Conriquez</v>
+        <v>Nia Smith</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
+        <v>https://music.apple.com/us/artist/nia-smith/1755576018</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/que-gacho/6770628419</v>
+        <v>https://music.apple.com/us/album/high/6773775203</v>
       </c>
       <c r="L177" t="str">
-        <v>Que Gacho - Luis R Conriquez</v>
+        <v>High - Nia Smith</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>same God</v>
+        <v>Ay Gyal</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/same-god/1878232616</v>
+        <v>https://music.apple.com/us/song/ay-gyal/6771885805</v>
       </c>
       <c r="D178" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E178" t="str">
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>I HOPE THIS HELPS</v>
+        <v>Ay Gyal - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>3:34</v>
+        <v>2:12</v>
       </c>
       <c r="H178" t="str">
-        <v>Alana Springsteen</v>
+        <v>1Ski OG</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/alana-springsteen/1309335606</v>
+        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/same-god/1878232194</v>
+        <v>https://music.apple.com/us/album/ay-gyal/6771885803</v>
       </c>
       <c r="L178" t="str">
-        <v>same God - Alana Springsteen</v>
+        <v>Ay Gyal - 1Ski OG</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>emotional swaggage</v>
+        <v>always knew</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/emotional-swaggage/6767397453</v>
+        <v>https://music.apple.com/us/song/always-knew/6762864274</v>
       </c>
       <c r="D179" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E179" t="str">
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>IDCASH</v>
+        <v>always knew - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>2:12</v>
+        <v>3:25</v>
       </c>
       <c r="H179" t="str">
-        <v>IDK</v>
+        <v>Biscits</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/idk/1578186947</v>
+        <v>https://music.apple.com/us/artist/biscits/1185553226</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/emotional-swaggage/6767397348</v>
+        <v>https://music.apple.com/us/album/always-knew/1895047928</v>
       </c>
       <c r="L179" t="str">
-        <v>emotional swaggage - IDK</v>
+        <v>always knew - Biscits</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Baby Driver</v>
+        <v>Cigarette Burns</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/baby-driver/6769152279</v>
+        <v>https://music.apple.com/us/song/cigarette-burns/6770691000</v>
       </c>
       <c r="D180" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E180" t="str">
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Baby Driver - Single</v>
+        <v>Heartland Rock and Roll</v>
       </c>
       <c r="G180" t="str">
-        <v>3:36</v>
+        <v>2:41</v>
       </c>
       <c r="H180" t="str">
-        <v>070 Shake</v>
+        <v>Corey Kent</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/070-shake/1097177293</v>
+        <v>https://music.apple.com/us/artist/corey-kent/1171544097</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/baby-driver/6769152273</v>
+        <v>https://music.apple.com/us/album/cigarette-burns/6770690867</v>
       </c>
       <c r="L180" t="str">
-        <v>Baby Driver - 070 Shake</v>
+        <v>Cigarette Burns - Corey Kent</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>More! More! More!</v>
+        <v>Let You Down</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/more-more-more/6770600105</v>
+        <v>https://music.apple.com/us/song/let-you-down/6773362320</v>
       </c>
       <c r="D181" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E181" t="str">
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>REBECCA</v>
+        <v>El Relevo</v>
       </c>
       <c r="G181" t="str">
-        <v>2:55</v>
+        <v>4:14</v>
       </c>
       <c r="H181" t="str">
-        <v>Becky Hill</v>
+        <v>Luis Figueroa</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/becky-hill/533839517</v>
+        <v>https://music.apple.com/us/artist/luis-figueroa/395266944</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/more-more-more/6770600098</v>
+        <v>https://music.apple.com/us/album/let-you-down/6773362108</v>
       </c>
       <c r="L181" t="str">
-        <v>More! More! More! - Becky Hill</v>
+        <v>Let You Down - Luis Figueroa</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Young Again</v>
+        <v>Starless</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/young-again/1877229743</v>
+        <v>https://music.apple.com/us/song/starless/6770568779</v>
       </c>
       <c r="D182" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E182" t="str">
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>EI8HT</v>
+        <v>Starless - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>3:36</v>
+        <v>4:32</v>
       </c>
       <c r="H182" t="str">
-        <v>Shinedown</v>
+        <v>A Perfect Circle</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/shinedown/1883858</v>
+        <v>https://music.apple.com/us/artist/a-perfect-circle/652503</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/young-again/1877229738</v>
+        <v>https://music.apple.com/us/album/starless/6770568776</v>
       </c>
       <c r="L182" t="str">
-        <v>Young Again - Shinedown</v>
+        <v>Starless - A Perfect Circle</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>skinny dip</v>
+        <v>Looking For You</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/skinny-dip/6769856281</v>
+        <v>https://music.apple.com/us/song/looking-for-you/6768355609</v>
       </c>
       <c r="D183" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E183" t="str">
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>skinny dip - Single</v>
+        <v>Looking For You - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>3:12</v>
+        <v>3:19</v>
       </c>
       <c r="H183" t="str">
-        <v>almost monday</v>
+        <v>Gable Price and Friends</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/almost-monday/1300723925</v>
+        <v>https://music.apple.com/us/artist/gable-price-and-friends/1441378212</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/skinny-dip/6769855907</v>
+        <v>https://music.apple.com/us/album/looking-for-you/6768355596</v>
       </c>
       <c r="L183" t="str">
-        <v>skinny dip - almost monday</v>
+        <v>Looking For You - Gable Price and Friends</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>girls like girls (from the motion picture)</v>
+        <v>FOCUSED</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/girls-like-girls-from-the-motion-picture/1893704575</v>
+        <v>https://music.apple.com/us/song/focused/1887909237</v>
       </c>
       <c r="D184" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E184" t="str">
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>girls like girls the album</v>
+        <v>FOCUSED - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>4:14</v>
+        <v>2:23</v>
       </c>
       <c r="H184" t="str">
-        <v>Hayley Kiyoko</v>
+        <v>Shepherd</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/hayley-kiyoko/325569584</v>
+        <v>https://music.apple.com/us/artist/shepherd/1192803216</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/girls-like-girls-from-the-motion-picture/1893704396</v>
+        <v>https://music.apple.com/us/album/focused/1887909236</v>
       </c>
       <c r="L184" t="str">
-        <v>girls like girls (from the motion picture) - Hayley Kiyoko</v>
+        <v>FOCUSED - Shepherd</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Better Off</v>
+        <v>Tú Ni En Cuenta</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/better-off/6772045367</v>
+        <v>https://music.apple.com/us/song/tu-ni-en-cuenta/6767701804</v>
       </c>
       <c r="D185" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E185" t="str">
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Stages</v>
+        <v>Tú Ni En Cuenta - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>3:16</v>
+        <v>3:23</v>
       </c>
       <c r="H185" t="str">
-        <v>Lauren Alaina</v>
+        <v>Banda MS de Sergio Lizárraga</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/lauren-alaina/425028816</v>
+        <v>https://music.apple.com/us/artist/banda-ms-de-sergio-liz%C3%A1rraga/413048014</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/better-off/6772044978</v>
+        <v>https://music.apple.com/us/album/tu-ni-en-cuenta/6767701803</v>
       </c>
       <c r="L185" t="str">
-        <v>Better Off - Lauren Alaina</v>
+        <v>Tú Ni En Cuenta - Banda MS de Sergio Lizárraga</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Everythang Pinka (feat. Teezo Touchdown)</v>
+        <v>dream state</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/everythang-pinka-feat-teezo-touchdown/6772026590</v>
+        <v>https://music.apple.com/us/song/dream-state/6765596009</v>
       </c>
       <c r="D186" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E186" t="str">
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Everythang Pinka (feat. Teezo Touchdown) - Single</v>
+        <v>dream state - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>2:48</v>
+        <v>4:01</v>
       </c>
       <c r="H186" t="str">
-        <v>Monaleo</v>
+        <v>Martin Luke Brown</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/monaleo/1495603374</v>
+        <v>https://music.apple.com/us/artist/martin-luke-brown/883292185</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/everythang-pinka-feat-teezo-touchdown/6772026586</v>
+        <v>https://music.apple.com/us/album/dream-state/1896004790</v>
       </c>
       <c r="L186" t="str">
-        <v>Everythang Pinka (feat. Teezo Touchdown) - Monaleo</v>
+        <v>dream state - Martin Luke Brown</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Lost in translation...</v>
+        <v>Needle (feat. Spencer Cullum)</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/lost-in-translation/1870971556</v>
+        <v>https://music.apple.com/us/song/needle-feat-spencer-cullum/6767618217</v>
       </c>
       <c r="D187" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E187" t="str">
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Dream inside a dream…</v>
+        <v>Needle (feat. Spencer Cullum) - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>3:30</v>
+        <v>3:39</v>
       </c>
       <c r="H187" t="str">
-        <v>R3HAB</v>
+        <v>Mynolia</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/r3hab/331900515</v>
+        <v>https://music.apple.com/us/artist/mynolia/1444347510</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/lost-in-translation/1870971550</v>
+        <v>https://music.apple.com/us/album/needle-feat-spencer-cullum/6767618203</v>
       </c>
       <c r="L187" t="str">
-        <v>Lost in translation... - R3HAB</v>
+        <v>Needle (feat. Spencer Cullum) - Mynolia</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Call Security</v>
+        <v>You Retreat In Time And Space</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/call-security/6769296603</v>
+        <v>https://music.apple.com/us/song/you-retreat-in-time-and-space/1890015660</v>
       </c>
       <c r="D188" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E188" t="str">
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>U, Me &amp; My Ego</v>
+        <v>Inferno</v>
       </c>
       <c r="G188" t="str">
-        <v>3:22</v>
+        <v>5:25</v>
       </c>
       <c r="H188" t="str">
-        <v>Chxrry</v>
+        <v>Boards of Canada</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/chxrry/1520135642</v>
+        <v>https://music.apple.com/us/artist/boards-of-canada/2989314</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/call-security/6769296591</v>
+        <v>https://music.apple.com/us/album/you-retreat-in-time-and-space/1890015523</v>
       </c>
       <c r="L188" t="str">
-        <v>Call Security - Chxrry</v>
+        <v>You Retreat In Time And Space - Boards of Canada</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>chaotic</v>
+        <v>It's Happening (To Me)</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/chaotic/6767629281</v>
+        <v>https://music.apple.com/us/song/its-happening-to-me/6764723461</v>
       </c>
       <c r="D189" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E189" t="str">
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>scars to prove it</v>
+        <v>It's Happening (To Me) - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>3:14</v>
+        <v>2:34</v>
       </c>
       <c r="H189" t="str">
-        <v>Hailey Picardi</v>
+        <v>Delroy Edwards</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
+        <v>https://music.apple.com/us/artist/delroy-edwards/591790909</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/chaotic/6767626506</v>
+        <v>https://music.apple.com/us/album/its-happening-to-me/1895893472</v>
       </c>
       <c r="L189" t="str">
-        <v>chaotic - Hailey Picardi</v>
+        <v>It's Happening (To Me) - Delroy Edwards</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Keep It To Yourself</v>
+        <v>FCUK</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/keep-it-to-yourself/6771099675</v>
+        <v>https://music.apple.com/us/song/fcuk/6769623577</v>
       </c>
       <c r="D190" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E190" t="str">
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>LOVE IS THE LAW</v>
+        <v>FCUK - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>4:17</v>
+        <v>2:22</v>
       </c>
       <c r="H190" t="str">
-        <v>Love Spells</v>
+        <v>H.LLS</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/love-spells/1597025563</v>
+        <v>https://music.apple.com/us/artist/h-lls/1751287958</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/keep-it-to-yourself/6771099661</v>
+        <v>https://music.apple.com/us/album/fcuk/6769623566</v>
       </c>
       <c r="L190" t="str">
-        <v>Keep It To Yourself - Love Spells</v>
+        <v>FCUK - H.LLS</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Something to Someone</v>
+        <v>Higher</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/something-to-someone/6767255424</v>
+        <v>https://music.apple.com/us/song/higher/1880124200</v>
       </c>
       <c r="D191" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E191" t="str">
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Something to Someone - Single</v>
+        <v>Run, Run Pure Beauty</v>
       </c>
       <c r="G191" t="str">
-        <v>3:55</v>
+        <v>4:06</v>
       </c>
       <c r="H191" t="str">
-        <v>Max McNown</v>
+        <v>Francis of Delirium</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
+        <v>https://music.apple.com/us/artist/francis-of-delirium/1485902996</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/something-to-someone/1896445136</v>
+        <v>https://music.apple.com/us/album/higher/1880123731</v>
       </c>
       <c r="L191" t="str">
-        <v>Something to Someone - Max McNown</v>
+        <v>Higher - Francis of Delirium</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Green Screen (1pm)</v>
+        <v>B.U.N</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/green-screen-1pm/6766279426</v>
+        <v>https://music.apple.com/us/song/b-u-n/6763272338</v>
       </c>
       <c r="D192" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E192" t="str">
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>The Hours: High Noon</v>
+        <v>B.U.N - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>2:10</v>
+        <v>3:43</v>
       </c>
       <c r="H192" t="str">
-        <v>Cautious Clay</v>
+        <v>Roll Deep</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/cautious-clay/1064628701</v>
+        <v>https://music.apple.com/us/artist/roll-deep/3083873</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/green-screen-1pm/1896264236</v>
+        <v>https://music.apple.com/us/album/b-u-n/1895242397</v>
       </c>
       <c r="L192" t="str">
-        <v>Green Screen (1pm) - Cautious Clay</v>
+        <v>B.U.N - Roll Deep</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Scoreboard</v>
+        <v>Only Love (feat. Pa Salieu)</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/scoreboard/6767255746</v>
+        <v>https://music.apple.com/us/song/only-love-feat-pa-salieu/6767014290</v>
       </c>
       <c r="D193" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E193" t="str">
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>I Just Wanna Be Loved</v>
+        <v>Here Because of Hope</v>
       </c>
       <c r="G193" t="str">
-        <v>3:24</v>
+        <v>3:22</v>
       </c>
       <c r="H193" t="str">
-        <v>Gabriella Rose</v>
+        <v>Ezra Collective</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/gabriella-rose/645706232</v>
+        <v>https://music.apple.com/us/artist/ezra-collective/1103640281</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/scoreboard/1896445371</v>
+        <v>https://music.apple.com/us/album/only-love-feat-pa-salieu/6767014278</v>
       </c>
       <c r="L193" t="str">
-        <v>Scoreboard - Gabriella Rose</v>
+        <v>Only Love (feat. Pa Salieu) - Ezra Collective</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>High</v>
+        <v>Beautiful Things 1st scene/audition</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/high/6773775211</v>
+        <v>https://music.apple.com/us/song/beautiful-things-1st-scene-audition/6771942631</v>
       </c>
       <c r="D194" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E194" t="str">
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Payback Is A Dog (EP)</v>
+        <v>UNDRA</v>
       </c>
       <c r="G194" t="str">
-        <v>2:55</v>
+        <v>2:49</v>
       </c>
       <c r="H194" t="str">
-        <v>Nia Smith</v>
+        <v>reggie</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/nia-smith/1755576018</v>
+        <v>https://music.apple.com/us/artist/reggie/1526587068</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/high/6773775203</v>
+        <v>https://music.apple.com/us/album/beautiful-things-1st-scene-audition/6771942630</v>
       </c>
       <c r="L194" t="str">
-        <v>High - Nia Smith</v>
+        <v>Beautiful Things 1st scene/audition - reggie</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Ay Gyal</v>
+        <v>HEAVEN'S ON FIRE</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/ay-gyal/6771885805</v>
+        <v>https://music.apple.com/us/song/heavens-on-fire/6771110730</v>
       </c>
       <c r="D195" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E195" t="str">
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Ay Gyal - Single</v>
+        <v>HEAVEN'S ON FIRE</v>
       </c>
       <c r="G195" t="str">
-        <v>2:12</v>
+        <v>2:54</v>
       </c>
       <c r="H195" t="str">
-        <v>1Ski OG</v>
+        <v>Johnny Huynh</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
+        <v>https://music.apple.com/us/artist/johnny-huynh/1708540956</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/ay-gyal/6771885803</v>
+        <v>https://music.apple.com/us/album/heavens-on-fire/6771110729</v>
       </c>
       <c r="L195" t="str">
-        <v>Ay Gyal - 1Ski OG</v>
+        <v>HEAVEN'S ON FIRE - Johnny Huynh</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>always knew</v>
+        <v>Fallen Angel</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/always-knew/6762864274</v>
+        <v>https://music.apple.com/us/song/fallen-angel/6771161222</v>
       </c>
       <c r="D196" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E196" t="str">
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>always knew - Single</v>
+        <v>You Don't Know My Name</v>
       </c>
       <c r="G196" t="str">
-        <v>3:25</v>
+        <v>3:05</v>
       </c>
       <c r="H196" t="str">
-        <v>Biscits</v>
+        <v>Baby J</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/biscits/1185553226</v>
+        <v>https://music.apple.com/us/artist/baby-j/1513690931</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/always-knew/1895047928</v>
+        <v>https://music.apple.com/us/album/fallen-angel/6771161180</v>
       </c>
       <c r="L196" t="str">
-        <v>always knew - Biscits</v>
+        <v>Fallen Angel - Baby J</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Cigarette Burns</v>
+        <v>The Last Encounter</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/cigarette-burns/6770691000</v>
+        <v>https://music.apple.com/us/song/the-last-encounter/6767395134</v>
       </c>
       <c r="D197" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E197" t="str">
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Heartland Rock and Roll</v>
+        <v>The Last Encounter - Single</v>
       </c>
       <c r="G197" t="str">
-        <v>2:41</v>
+        <v>3:04</v>
       </c>
       <c r="H197" t="str">
-        <v>Corey Kent</v>
+        <v>Sofia Camara</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/corey-kent/1171544097</v>
+        <v>https://music.apple.com/us/artist/sofia-camara/1506432156</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/cigarette-burns/6770690867</v>
+        <v>https://music.apple.com/us/album/the-last-encounter/6767395133</v>
       </c>
       <c r="L197" t="str">
-        <v>Cigarette Burns - Corey Kent</v>
+        <v>The Last Encounter - Sofia Camara</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Let You Down</v>
+        <v>we fall</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/let-you-down/6773362320</v>
+        <v>https://music.apple.com/us/song/we-fall/6769218917</v>
       </c>
       <c r="D198" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E198" t="str">
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>El Relevo</v>
+        <v>we fall - Single</v>
       </c>
       <c r="G198" t="str">
-        <v>4:14</v>
+        <v>4:01</v>
       </c>
       <c r="H198" t="str">
-        <v>Luis Figueroa</v>
+        <v>MOIO</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/luis-figueroa/395266944</v>
+        <v>https://music.apple.com/us/artist/moio/1664183608</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/let-you-down/6773362108</v>
+        <v>https://music.apple.com/us/album/we-fall/6769218915</v>
       </c>
       <c r="L198" t="str">
-        <v>Let You Down - Luis Figueroa</v>
+        <v>we fall - MOIO</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Starless</v>
+        <v>You Don't Know Me</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/starless/6770568779</v>
+        <v>https://music.apple.com/us/song/you-dont-know-me/6769214417</v>
       </c>
       <c r="D199" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E199" t="str">
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>Starless - Single</v>
+        <v>You Don’t Know Me - Single</v>
       </c>
       <c r="G199" t="str">
-        <v>4:32</v>
+        <v>3:50</v>
       </c>
       <c r="H199" t="str">
-        <v>A Perfect Circle</v>
+        <v>Isabel Dumaa</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/a-perfect-circle/652503</v>
+        <v>https://music.apple.com/us/artist/isabel-dumaa/1631481156</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/starless/6770568776</v>
+        <v>https://music.apple.com/us/album/you-dont-know-me/6769214410</v>
       </c>
       <c r="L199" t="str">
-        <v>Starless - A Perfect Circle</v>
+        <v>You Don't Know Me - Isabel Dumaa</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Looking For You</v>
+        <v>Hold Up, Say What?</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/looking-for-you/6768355609</v>
+        <v>https://music.apple.com/us/song/hold-up-say-what/1879853511</v>
       </c>
       <c r="D200" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E200" t="str">
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>Looking For You - Single</v>
+        <v>House Of Mirrors</v>
       </c>
       <c r="G200" t="str">
-        <v>3:19</v>
+        <v>4:04</v>
       </c>
       <c r="H200" t="str">
-        <v>Gable Price and Friends</v>
+        <v>All Them Witches</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/gable-price-and-friends/1441378212</v>
+        <v>https://music.apple.com/us/artist/all-them-witches/534924603</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/looking-for-you/6768355596</v>
+        <v>https://music.apple.com/us/album/hold-up-say-what/1879853502</v>
       </c>
       <c r="L200" t="str">
-        <v>Looking For You - Gable Price and Friends</v>
+        <v>Hold Up, Say What? - All Them Witches</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>FOCUSED</v>
+        <v>Iodine</v>
       </c>
       <c r="B201" t="str">
         <v/>
       </c>
       <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/focused/1887909237</v>
+        <v>https://music.apple.com/us/song/iodine/1871211805</v>
       </c>
       <c r="D201" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E201" t="str">
         <v/>
       </c>
       <c r="F201" t="str">
-        <v>FOCUSED - Single</v>
+        <v>Neverending</v>
       </c>
       <c r="G201" t="str">
-        <v>2:23</v>
+        <v>3:40</v>
       </c>
       <c r="H201" t="str">
-        <v>Shepherd</v>
+        <v>Monolord</v>
       </c>
       <c r="I201" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/shepherd/1192803216</v>
+        <v>https://music.apple.com/us/artist/monolord/833749384</v>
       </c>
       <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/focused/1887909236</v>
+        <v>https://music.apple.com/us/album/iodine/1871211801</v>
       </c>
       <c r="L201" t="str">
-        <v>FOCUSED - Shepherd</v>
+        <v>Iodine - Monolord</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Tú Ni En Cuenta</v>
+        <v>I Speak Forgotten Voices</v>
       </c>
       <c r="B202" t="str">
         <v/>
       </c>
       <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/tu-ni-en-cuenta/6767701804</v>
+        <v>https://music.apple.com/us/song/i-speak-forgotten-voices/1878083625</v>
       </c>
       <c r="D202" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E202" t="str">
         <v/>
       </c>
       <c r="F202" t="str">
-        <v>Tú Ni En Cuenta - Single</v>
+        <v>...By the Word...</v>
       </c>
       <c r="G202" t="str">
-        <v>3:23</v>
+        <v>5:01</v>
       </c>
       <c r="H202" t="str">
-        <v>Banda MS de Sergio Lizárraga</v>
+        <v>Trelldom</v>
       </c>
       <c r="I202" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/banda-ms-de-sergio-liz%C3%A1rraga/413048014</v>
+        <v>https://music.apple.com/us/artist/trelldom/256586618</v>
       </c>
       <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/tu-ni-en-cuenta/6767701803</v>
+        <v>https://music.apple.com/us/album/i-speak-forgotten-voices/1878083622</v>
       </c>
       <c r="L202" t="str">
-        <v>Tú Ni En Cuenta - Banda MS de Sergio Lizárraga</v>
+        <v>I Speak Forgotten Voices - Trelldom</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>dream state</v>
+        <v>Rats in the Temple</v>
       </c>
       <c r="B203" t="str">
         <v/>
       </c>
       <c r="C203" t="str">
-        <v>https://music.apple.com/us/song/dream-state/6765596009</v>
+        <v>https://music.apple.com/us/song/rats-in-the-temple/6764627559</v>
       </c>
       <c r="D203" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E203" t="str">
         <v/>
       </c>
       <c r="F203" t="str">
-        <v>dream state - Single</v>
+        <v>Rats in the Temple</v>
       </c>
       <c r="G203" t="str">
-        <v>4:01</v>
+        <v>4:45</v>
       </c>
       <c r="H203" t="str">
-        <v>Martin Luke Brown</v>
+        <v>Flotsam and Jetsam</v>
       </c>
       <c r="I203" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J203" t="str">
-        <v>https://music.apple.com/us/artist/martin-luke-brown/883292185</v>
+        <v>https://music.apple.com/us/artist/flotsam-and-jetsam/162270</v>
       </c>
       <c r="K203" t="str">
-        <v>https://music.apple.com/us/album/dream-state/1896004790</v>
+        <v>https://music.apple.com/us/album/rats-in-the-temple/1895855647</v>
       </c>
       <c r="L203" t="str">
-        <v>dream state - Martin Luke Brown</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="str">
-        <v>Needle (feat. Spencer Cullum)</v>
-      </c>
-      <c r="B204" t="str">
-        <v/>
-      </c>
-      <c r="C204" t="str">
-        <v>https://music.apple.com/us/song/needle-feat-spencer-cullum/6767618217</v>
-      </c>
-      <c r="D204" t="str">
-        <v>2026-06-02</v>
-      </c>
-      <c r="E204" t="str">
-        <v/>
-      </c>
-      <c r="F204" t="str">
-        <v>Needle (feat. Spencer Cullum) - Single</v>
-      </c>
-      <c r="G204" t="str">
-        <v>3:39</v>
-      </c>
-      <c r="H204" t="str">
-        <v>Mynolia</v>
-      </c>
-      <c r="I204" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J204" t="str">
-        <v>https://music.apple.com/us/artist/mynolia/1444347510</v>
-      </c>
-      <c r="K204" t="str">
-        <v>https://music.apple.com/us/album/needle-feat-spencer-cullum/6767618203</v>
-      </c>
-      <c r="L204" t="str">
-        <v>Needle (feat. Spencer Cullum) - Mynolia</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="str">
-        <v>You Retreat In Time And Space</v>
-      </c>
-      <c r="B205" t="str">
-        <v/>
-      </c>
-      <c r="C205" t="str">
-        <v>https://music.apple.com/us/song/you-retreat-in-time-and-space/1890015660</v>
-      </c>
-      <c r="D205" t="str">
-        <v>2026-06-02</v>
-      </c>
-      <c r="E205" t="str">
-        <v/>
-      </c>
-      <c r="F205" t="str">
-        <v>Inferno</v>
-      </c>
-      <c r="G205" t="str">
-        <v>5:25</v>
-      </c>
-      <c r="H205" t="str">
-        <v>Boards of Canada</v>
-      </c>
-      <c r="I205" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J205" t="str">
-        <v>https://music.apple.com/us/artist/boards-of-canada/2989314</v>
-      </c>
-      <c r="K205" t="str">
-        <v>https://music.apple.com/us/album/you-retreat-in-time-and-space/1890015523</v>
-      </c>
-      <c r="L205" t="str">
-        <v>You Retreat In Time And Space - Boards of Canada</v>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="str">
-        <v>It's Happening (To Me)</v>
-      </c>
-      <c r="B206" t="str">
-        <v/>
-      </c>
-      <c r="C206" t="str">
-        <v>https://music.apple.com/us/song/its-happening-to-me/6764723461</v>
-      </c>
-      <c r="D206" t="str">
-        <v>2026-06-02</v>
-      </c>
-      <c r="E206" t="str">
-        <v/>
-      </c>
-      <c r="F206" t="str">
-        <v>It's Happening (To Me) - Single</v>
-      </c>
-      <c r="G206" t="str">
-        <v>2:34</v>
-      </c>
-      <c r="H206" t="str">
-        <v>Delroy Edwards</v>
-      </c>
-      <c r="I206" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J206" t="str">
-        <v>https://music.apple.com/us/artist/delroy-edwards/591790909</v>
-      </c>
-      <c r="K206" t="str">
-        <v>https://music.apple.com/us/album/its-happening-to-me/1895893472</v>
-      </c>
-      <c r="L206" t="str">
-        <v>It's Happening (To Me) - Delroy Edwards</v>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="str">
-        <v>FCUK</v>
-      </c>
-      <c r="B207" t="str">
-        <v/>
-      </c>
-      <c r="C207" t="str">
-        <v>https://music.apple.com/us/song/fcuk/6769623577</v>
-      </c>
-      <c r="D207" t="str">
-        <v>2026-06-02</v>
-      </c>
-      <c r="E207" t="str">
-        <v/>
-      </c>
-      <c r="F207" t="str">
-        <v>FCUK - Single</v>
-      </c>
-      <c r="G207" t="str">
-        <v>2:22</v>
-      </c>
-      <c r="H207" t="str">
-        <v>H.LLS</v>
-      </c>
-      <c r="I207" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J207" t="str">
-        <v>https://music.apple.com/us/artist/h-lls/1751287958</v>
-      </c>
-      <c r="K207" t="str">
-        <v>https://music.apple.com/us/album/fcuk/6769623566</v>
-      </c>
-      <c r="L207" t="str">
-        <v>FCUK - H.LLS</v>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="str">
-        <v>Higher</v>
-      </c>
-      <c r="B208" t="str">
-        <v/>
-      </c>
-      <c r="C208" t="str">
-        <v>https://music.apple.com/us/song/higher/1880124200</v>
-      </c>
-      <c r="D208" t="str">
-        <v>2026-06-02</v>
-      </c>
-      <c r="E208" t="str">
-        <v/>
-      </c>
-      <c r="F208" t="str">
-        <v>Run, Run Pure Beauty</v>
-      </c>
-      <c r="G208" t="str">
-        <v>4:06</v>
-      </c>
-      <c r="H208" t="str">
-        <v>Francis of Delirium</v>
-      </c>
-      <c r="I208" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J208" t="str">
-        <v>https://music.apple.com/us/artist/francis-of-delirium/1485902996</v>
-      </c>
-      <c r="K208" t="str">
-        <v>https://music.apple.com/us/album/higher/1880123731</v>
-      </c>
-      <c r="L208" t="str">
-        <v>Higher - Francis of Delirium</v>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="str">
-        <v>B.U.N</v>
-      </c>
-      <c r="B209" t="str">
-        <v/>
-      </c>
-      <c r="C209" t="str">
-        <v>https://music.apple.com/us/song/b-u-n/6763272338</v>
-      </c>
-      <c r="D209" t="str">
-        <v>2026-06-02</v>
-      </c>
-      <c r="E209" t="str">
-        <v/>
-      </c>
-      <c r="F209" t="str">
-        <v>B.U.N - Single</v>
-      </c>
-      <c r="G209" t="str">
-        <v>3:43</v>
-      </c>
-      <c r="H209" t="str">
-        <v>Roll Deep</v>
-      </c>
-      <c r="I209" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J209" t="str">
-        <v>https://music.apple.com/us/artist/roll-deep/3083873</v>
-      </c>
-      <c r="K209" t="str">
-        <v>https://music.apple.com/us/album/b-u-n/1895242397</v>
-      </c>
-      <c r="L209" t="str">
-        <v>B.U.N - Roll Deep</v>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="str">
-        <v>Only Love (feat. Pa Salieu)</v>
-      </c>
-      <c r="B210" t="str">
-        <v/>
-      </c>
-      <c r="C210" t="str">
-        <v>https://music.apple.com/us/song/only-love-feat-pa-salieu/6767014290</v>
-      </c>
-      <c r="D210" t="str">
-        <v>2026-06-02</v>
-      </c>
-      <c r="E210" t="str">
-        <v/>
-      </c>
-      <c r="F210" t="str">
-        <v>Here Because of Hope</v>
-      </c>
-      <c r="G210" t="str">
-        <v>3:22</v>
-      </c>
-      <c r="H210" t="str">
-        <v>Ezra Collective</v>
-      </c>
-      <c r="I210" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J210" t="str">
-        <v>https://music.apple.com/us/artist/ezra-collective/1103640281</v>
-      </c>
-      <c r="K210" t="str">
-        <v>https://music.apple.com/us/album/only-love-feat-pa-salieu/6767014278</v>
-      </c>
-      <c r="L210" t="str">
-        <v>Only Love (feat. Pa Salieu) - Ezra Collective</v>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="str">
-        <v>Beautiful Things 1st scene/audition</v>
-      </c>
-      <c r="B211" t="str">
-        <v/>
-      </c>
-      <c r="C211" t="str">
-        <v>https://music.apple.com/us/song/beautiful-things-1st-scene-audition/6771942631</v>
-      </c>
-      <c r="D211" t="str">
-        <v>2026-06-02</v>
-      </c>
-      <c r="E211" t="str">
-        <v/>
-      </c>
-      <c r="F211" t="str">
-        <v>UNDRA</v>
-      </c>
-      <c r="G211" t="str">
-        <v>2:49</v>
-      </c>
-      <c r="H211" t="str">
-        <v>reggie</v>
-      </c>
-      <c r="I211" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J211" t="str">
-        <v>https://music.apple.com/us/artist/reggie/1526587068</v>
-      </c>
-      <c r="K211" t="str">
-        <v>https://music.apple.com/us/album/beautiful-things-1st-scene-audition/6771942630</v>
-      </c>
-      <c r="L211" t="str">
-        <v>Beautiful Things 1st scene/audition - reggie</v>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="str">
-        <v>HEAVEN'S ON FIRE</v>
-      </c>
-      <c r="B212" t="str">
-        <v/>
-      </c>
-      <c r="C212" t="str">
-        <v>https://music.apple.com/us/song/heavens-on-fire/6771110730</v>
-      </c>
-      <c r="D212" t="str">
-        <v>2026-06-02</v>
-      </c>
-      <c r="E212" t="str">
-        <v/>
-      </c>
-      <c r="F212" t="str">
-        <v>HEAVEN'S ON FIRE</v>
-      </c>
-      <c r="G212" t="str">
-        <v>2:54</v>
-      </c>
-      <c r="H212" t="str">
-        <v>Johnny Huynh</v>
-      </c>
-      <c r="I212" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J212" t="str">
-        <v>https://music.apple.com/us/artist/johnny-huynh/1708540956</v>
-      </c>
-      <c r="K212" t="str">
-        <v>https://music.apple.com/us/album/heavens-on-fire/6771110729</v>
-      </c>
-      <c r="L212" t="str">
-        <v>HEAVEN'S ON FIRE - Johnny Huynh</v>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="str">
-        <v>Fallen Angel</v>
-      </c>
-      <c r="B213" t="str">
-        <v/>
-      </c>
-      <c r="C213" t="str">
-        <v>https://music.apple.com/us/song/fallen-angel/6771161222</v>
-      </c>
-      <c r="D213" t="str">
-        <v>2026-06-02</v>
-      </c>
-      <c r="E213" t="str">
-        <v/>
-      </c>
-      <c r="F213" t="str">
-        <v>You Don't Know My Name</v>
-      </c>
-      <c r="G213" t="str">
-        <v>3:05</v>
-      </c>
-      <c r="H213" t="str">
-        <v>Baby J</v>
-      </c>
-      <c r="I213" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J213" t="str">
-        <v>https://music.apple.com/us/artist/baby-j/1513690931</v>
-      </c>
-      <c r="K213" t="str">
-        <v>https://music.apple.com/us/album/fallen-angel/6771161180</v>
-      </c>
-      <c r="L213" t="str">
-        <v>Fallen Angel - Baby J</v>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="str">
-        <v>The Last Encounter</v>
-      </c>
-      <c r="B214" t="str">
-        <v/>
-      </c>
-      <c r="C214" t="str">
-        <v>https://music.apple.com/us/song/the-last-encounter/6767395134</v>
-      </c>
-      <c r="D214" t="str">
-        <v>2026-06-02</v>
-      </c>
-      <c r="E214" t="str">
-        <v/>
-      </c>
-      <c r="F214" t="str">
-        <v>The Last Encounter - Single</v>
-      </c>
-      <c r="G214" t="str">
-        <v>3:04</v>
-      </c>
-      <c r="H214" t="str">
-        <v>Sofia Camara</v>
-      </c>
-      <c r="I214" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J214" t="str">
-        <v>https://music.apple.com/us/artist/sofia-camara/1506432156</v>
-      </c>
-      <c r="K214" t="str">
-        <v>https://music.apple.com/us/album/the-last-encounter/6767395133</v>
-      </c>
-      <c r="L214" t="str">
-        <v>The Last Encounter - Sofia Camara</v>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="str">
-        <v>we fall</v>
-      </c>
-      <c r="B215" t="str">
-        <v/>
-      </c>
-      <c r="C215" t="str">
-        <v>https://music.apple.com/us/song/we-fall/6769218917</v>
-      </c>
-      <c r="D215" t="str">
-        <v>2026-06-02</v>
-      </c>
-      <c r="E215" t="str">
-        <v/>
-      </c>
-      <c r="F215" t="str">
-        <v>we fall - Single</v>
-      </c>
-      <c r="G215" t="str">
-        <v>4:01</v>
-      </c>
-      <c r="H215" t="str">
-        <v>MOIO</v>
-      </c>
-      <c r="I215" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J215" t="str">
-        <v>https://music.apple.com/us/artist/moio/1664183608</v>
-      </c>
-      <c r="K215" t="str">
-        <v>https://music.apple.com/us/album/we-fall/6769218915</v>
-      </c>
-      <c r="L215" t="str">
-        <v>we fall - MOIO</v>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="str">
-        <v>You Don't Know Me</v>
-      </c>
-      <c r="B216" t="str">
-        <v/>
-      </c>
-      <c r="C216" t="str">
-        <v>https://music.apple.com/us/song/you-dont-know-me/6769214417</v>
-      </c>
-      <c r="D216" t="str">
-        <v>2026-06-02</v>
-      </c>
-      <c r="E216" t="str">
-        <v/>
-      </c>
-      <c r="F216" t="str">
-        <v>You Don’t Know Me - Single</v>
-      </c>
-      <c r="G216" t="str">
-        <v>3:50</v>
-      </c>
-      <c r="H216" t="str">
-        <v>Isabel Dumaa</v>
-      </c>
-      <c r="I216" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J216" t="str">
-        <v>https://music.apple.com/us/artist/isabel-dumaa/1631481156</v>
-      </c>
-      <c r="K216" t="str">
-        <v>https://music.apple.com/us/album/you-dont-know-me/6769214410</v>
-      </c>
-      <c r="L216" t="str">
-        <v>You Don't Know Me - Isabel Dumaa</v>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="str">
-        <v>Hold Up, Say What?</v>
-      </c>
-      <c r="B217" t="str">
-        <v/>
-      </c>
-      <c r="C217" t="str">
-        <v>https://music.apple.com/us/song/hold-up-say-what/1879853511</v>
-      </c>
-      <c r="D217" t="str">
-        <v>2026-06-02</v>
-      </c>
-      <c r="E217" t="str">
-        <v/>
-      </c>
-      <c r="F217" t="str">
-        <v>House Of Mirrors</v>
-      </c>
-      <c r="G217" t="str">
-        <v>4:04</v>
-      </c>
-      <c r="H217" t="str">
-        <v>All Them Witches</v>
-      </c>
-      <c r="I217" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J217" t="str">
-        <v>https://music.apple.com/us/artist/all-them-witches/534924603</v>
-      </c>
-      <c r="K217" t="str">
-        <v>https://music.apple.com/us/album/hold-up-say-what/1879853502</v>
-      </c>
-      <c r="L217" t="str">
-        <v>Hold Up, Say What? - All Them Witches</v>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="str">
-        <v>Iodine</v>
-      </c>
-      <c r="B218" t="str">
-        <v/>
-      </c>
-      <c r="C218" t="str">
-        <v>https://music.apple.com/us/song/iodine/1871211805</v>
-      </c>
-      <c r="D218" t="str">
-        <v>2026-06-02</v>
-      </c>
-      <c r="E218" t="str">
-        <v/>
-      </c>
-      <c r="F218" t="str">
-        <v>Neverending</v>
-      </c>
-      <c r="G218" t="str">
-        <v>3:40</v>
-      </c>
-      <c r="H218" t="str">
-        <v>Monolord</v>
-      </c>
-      <c r="I218" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J218" t="str">
-        <v>https://music.apple.com/us/artist/monolord/833749384</v>
-      </c>
-      <c r="K218" t="str">
-        <v>https://music.apple.com/us/album/iodine/1871211801</v>
-      </c>
-      <c r="L218" t="str">
-        <v>Iodine - Monolord</v>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="str">
-        <v>I Speak Forgotten Voices</v>
-      </c>
-      <c r="B219" t="str">
-        <v/>
-      </c>
-      <c r="C219" t="str">
-        <v>https://music.apple.com/us/song/i-speak-forgotten-voices/1878083625</v>
-      </c>
-      <c r="D219" t="str">
-        <v>2026-06-02</v>
-      </c>
-      <c r="E219" t="str">
-        <v/>
-      </c>
-      <c r="F219" t="str">
-        <v>...By the Word...</v>
-      </c>
-      <c r="G219" t="str">
-        <v>5:01</v>
-      </c>
-      <c r="H219" t="str">
-        <v>Trelldom</v>
-      </c>
-      <c r="I219" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J219" t="str">
-        <v>https://music.apple.com/us/artist/trelldom/256586618</v>
-      </c>
-      <c r="K219" t="str">
-        <v>https://music.apple.com/us/album/i-speak-forgotten-voices/1878083622</v>
-      </c>
-      <c r="L219" t="str">
-        <v>I Speak Forgotten Voices - Trelldom</v>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="str">
-        <v>Rats in the Temple</v>
-      </c>
-      <c r="B220" t="str">
-        <v/>
-      </c>
-      <c r="C220" t="str">
-        <v>https://music.apple.com/us/song/rats-in-the-temple/6764627559</v>
-      </c>
-      <c r="D220" t="str">
-        <v>2026-06-02</v>
-      </c>
-      <c r="E220" t="str">
-        <v/>
-      </c>
-      <c r="F220" t="str">
-        <v>Rats in the Temple</v>
-      </c>
-      <c r="G220" t="str">
-        <v>4:45</v>
-      </c>
-      <c r="H220" t="str">
-        <v>Flotsam and Jetsam</v>
-      </c>
-      <c r="I220" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J220" t="str">
-        <v>https://music.apple.com/us/artist/flotsam-and-jetsam/162270</v>
-      </c>
-      <c r="K220" t="str">
-        <v>https://music.apple.com/us/album/rats-in-the-temple/1895855647</v>
-      </c>
-      <c r="L220" t="str">
         <v>Rats in the Temple - Flotsam and Jetsam</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L220"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L203"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-06-week01/titles.xlsx
+++ b/data/global/2026-06-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L203"/>
+  <dimension ref="A1:L221"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>משינה – כמעט וכאילו</v>
+        <v>מירי מסיקה - לב לבן קאבר</v>
       </c>
       <c r="B2" t="str">
         <v>2026-06-03</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%a9%d7%99%d7%a0%d7%94-%d7%9b%d7%9e%d7%a2%d7%98-%d7%95%d7%9b%d7%90%d7%99%d7%9c%d7%95/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411187&amp;sid=8c32dea66695624c346eddfe12cc9153</v>
       </c>
       <c r="D2" t="str">
         <v>2026-06-03</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>"כמעט כאילו" של משינה  מגיע אחרי יותר מארבעה עשורים של יצירה. במקום להציג הצהרה חגיגית או נוסטלגית על 40 שנות קריירה, משינה בוחרת לכתוב שיר על בלבול, ספק, מציאות מתעתעת וחוסר יכולת להכריע. במובן הזה, הוא נשמע מאוד עכשווי למרות</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>משינה – כמעט וכאילו</v>
+        <v>מירי מסיקה - לב לבן קאבר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>מייזי פיטרס Florescence</v>
+        <v>אמיר אליהו - כסף הכסף קאבר</v>
       </c>
       <c r="B3" t="str">
         <v>2026-06-03</v>
       </c>
       <c r="C3" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%99%d7%99%d7%96%d7%99-%d7%a4%d7%99%d7%98%d7%a8%d7%a1-florescence/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411182&amp;sid=8c32dea66695624c346eddfe12cc9153</v>
       </c>
       <c r="D3" t="str">
         <v>2026-06-03</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>החיים נראים מעט אחרת עבור מייזי פיטרס. מאז יציאת  אלבומה השני, "The Good Witch" מ-2023.  באלבומה השלישי, כוכבת הפופ הבריטית משחררת את הכאב ומוצאת שלווה באהבת אמת. בדיוק כשהקריירה שלה צברה תאוצה לקראת סוף 2024, הזמרת שנבחרה לחמם את ההופעות</v>
+        <v/>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -498,7 +498,7 @@
         <v/>
       </c>
       <c r="I3" t="str">
-        <v>אלבומים חדשים</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>מייזי פיטרס Florescence</v>
+        <v>אמיר אליהו - כסף הכסף קאבר</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Billy Idol - John Wayne feat. Alison Mosshart (Official Music Video)</v>
+        <v>שלומי הלימי - נווה הדרים קאבר</v>
       </c>
       <c r="B4" t="str">
-        <v>16 hours ago</v>
+        <v>2026-06-03</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=47LNk7oiTVI</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411199&amp;sid=a85ca8ef30bfde649d428d952bc8fa37</v>
       </c>
       <c r="D4" t="str">
         <v>2026-06-03</v>
@@ -527,16 +527,16 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>16 hours ago</v>
+        <v/>
       </c>
       <c r="G4" t="str">
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>Billy Idol</v>
+        <v/>
       </c>
       <c r="I4" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Billy Idol - John Wayne feat. Alison Mosshart (Official Music Video) - Billy Idol</v>
+        <v>שלומי הלימי - נווה הדרים קאבר</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>'It's Unusual' Official Music Video - Kelly Boesch | 4K</v>
+        <v>שיר לוי - פרחים מנייר קאבר</v>
       </c>
       <c r="B5" t="str">
-        <v>4 days ago</v>
+        <v>2026-06-03</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=Ru3fB2l1RSo</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411198&amp;sid=a85ca8ef30bfde649d428d952bc8fa37</v>
       </c>
       <c r="D5" t="str">
         <v>2026-06-03</v>
@@ -565,16 +565,16 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>4 days ago</v>
+        <v/>
       </c>
       <c r="G5" t="str">
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>Kelly Boesch AI Art</v>
+        <v/>
       </c>
       <c r="I5" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>'It's Unusual' Official Music Video - Kelly Boesch | 4K - Kelly Boesch AI Art</v>
+        <v>שיר לוי - פרחים מנייר קאבר</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Icona Pop - Butterfly Feelings (Official Video)</v>
+        <v>שילת סופר - נווה הדרים קאבר</v>
       </c>
       <c r="B6" t="str">
-        <v>18 hours ago</v>
+        <v>2026-06-03</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=AMW1Zq9RbIU</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411197&amp;sid=a85ca8ef30bfde649d428d952bc8fa37</v>
       </c>
       <c r="D6" t="str">
         <v>2026-06-03</v>
@@ -603,16 +603,16 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>18 hours ago</v>
+        <v/>
       </c>
       <c r="G6" t="str">
         <v/>
       </c>
       <c r="H6" t="str">
-        <v>Icona Pop</v>
+        <v/>
       </c>
       <c r="I6" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Icona Pop - Butterfly Feelings (Official Video) - Icona Pop</v>
+        <v>שילת סופר - נווה הדרים קאבר</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Hippo Campus - South</v>
+        <v>שי עמר - את יפה קאבר</v>
       </c>
       <c r="B7" t="str">
-        <v>1 day ago</v>
+        <v>2026-06-03</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=FYOmFfV7Ojo</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411196&amp;sid=a85ca8ef30bfde649d428d952bc8fa37</v>
       </c>
       <c r="D7" t="str">
         <v>2026-06-03</v>
@@ -641,16 +641,16 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>1 day ago</v>
+        <v/>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>Hippo Campus</v>
+        <v/>
       </c>
       <c r="I7" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J7" t="str">
         <v/>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Hippo Campus - South - Hippo Campus</v>
+        <v>שי עמר - את יפה קאבר</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>elijah woods - Old (Treehouse Sessions)</v>
+        <v>רפא' - מאשאפ בואי &amp; ציון</v>
       </c>
       <c r="B8" t="str">
-        <v>1 day ago</v>
+        <v>2026-06-03</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=yDlkPdR_6zM</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411195&amp;sid=a85ca8ef30bfde649d428d952bc8fa37</v>
       </c>
       <c r="D8" t="str">
         <v>2026-06-03</v>
@@ -679,16 +679,16 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>1 day ago</v>
+        <v/>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>elijah woods</v>
+        <v/>
       </c>
       <c r="I8" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>elijah woods - Old (Treehouse Sessions) - elijah woods</v>
+        <v>רפא' - מאשאפ בואי &amp; ציון</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Nothing But Thieves - Evolution (Official Video)</v>
+        <v>בנימין עזר &amp; דוד עזר - קולות קאבר</v>
       </c>
       <c r="B9" t="str">
-        <v>1 day ago</v>
+        <v>2026-06-03</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=hmjfuuuRRYU</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411194&amp;sid=a85ca8ef30bfde649d428d952bc8fa37</v>
       </c>
       <c r="D9" t="str">
         <v>2026-06-03</v>
@@ -717,16 +717,16 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>1 day ago</v>
+        <v/>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>Nothing But Thieves</v>
+        <v/>
       </c>
       <c r="I9" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J9" t="str">
         <v/>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Nothing But Thieves - Evolution (Official Video) - Nothing But Thieves</v>
+        <v>בנימין עזר &amp; דוד עזר - קולות קאבר</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Ariana Grande - hate that i made you love me (official music video)</v>
+        <v>רזיאל עורקבי - נווה הדרים קאבר</v>
       </c>
       <c r="B10" t="str">
-        <v>1 day ago</v>
+        <v>2026-06-03</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=82-jTNka3uc</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411193&amp;sid=a85ca8ef30bfde649d428d952bc8fa37</v>
       </c>
       <c r="D10" t="str">
         <v>2026-06-03</v>
@@ -755,16 +755,16 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>1 day ago</v>
+        <v/>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>Ariana Grande</v>
+        <v/>
       </c>
       <c r="I10" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J10" t="str">
         <v/>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Ariana Grande - hate that i made you love me (official music video) - Ariana Grande</v>
+        <v>רזיאל עורקבי - נווה הדרים קאבר</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>LAUREL - Fire Breather</v>
+        <v>רביד שלו - גן עדן קאבר</v>
       </c>
       <c r="B11" t="str">
-        <v>1 day ago</v>
+        <v>2026-06-03</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=rtyavLIJjy0</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411192&amp;sid=a85ca8ef30bfde649d428d952bc8fa37</v>
       </c>
       <c r="D11" t="str">
         <v>2026-06-03</v>
@@ -793,16 +793,16 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>1 day ago</v>
+        <v/>
       </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>LAUREL</v>
+        <v/>
       </c>
       <c r="I11" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J11" t="str">
         <v/>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>LAUREL - Fire Breather - LAUREL</v>
+        <v>רביד שלו - גן עדן קאבר</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>The Warning - Ego (Performance Video)</v>
+        <v>עומר יונה - לא תשבור אותי קאבר</v>
       </c>
       <c r="B12" t="str">
-        <v>3 days ago</v>
+        <v>2026-06-03</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=7PApWObImjo</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411191&amp;sid=a85ca8ef30bfde649d428d952bc8fa37</v>
       </c>
       <c r="D12" t="str">
         <v>2026-06-03</v>
@@ -831,16 +831,16 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>3 days ago</v>
+        <v/>
       </c>
       <c r="G12" t="str">
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>The Warning</v>
+        <v/>
       </c>
       <c r="I12" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J12" t="str">
         <v/>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>The Warning - Ego (Performance Video) - The Warning</v>
+        <v>עומר יונה - לא תשבור אותי קאבר</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (feat. Gabito Ballesteros) [Official Lyric Video]</v>
+        <v>נתנאל ואנונו - נווה הדרים קאבר</v>
       </c>
       <c r="B13" t="str">
-        <v>3 days ago</v>
+        <v>2026-06-03</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=vruZSAYJBe4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411190&amp;sid=a85ca8ef30bfde649d428d952bc8fa37</v>
       </c>
       <c r="D13" t="str">
         <v>2026-06-03</v>
@@ -869,16 +869,16 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>3 days ago</v>
+        <v/>
       </c>
       <c r="G13" t="str">
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>David Guetta and Jennifer Lopez</v>
+        <v/>
       </c>
       <c r="I13" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J13" t="str">
         <v/>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (feat. Gabito Ballesteros) [Official Lyric Video] - David Guetta and Jennifer Lopez</v>
+        <v>נתנאל ואנונו - נווה הדרים קאבר</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Armin van Buuren - Equanimity (from 'Piano' album) [Official Video]</v>
+        <v>נתי כהן - בראשית עולם קאבר</v>
       </c>
       <c r="B14" t="str">
-        <v>3 days ago</v>
+        <v>2026-06-03</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=k93t10R-Qrg</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411189&amp;sid=a85ca8ef30bfde649d428d952bc8fa37</v>
       </c>
       <c r="D14" t="str">
         <v>2026-06-03</v>
@@ -907,16 +907,16 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>3 days ago</v>
+        <v/>
       </c>
       <c r="G14" t="str">
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>Armin van Buuren</v>
+        <v/>
       </c>
       <c r="I14" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J14" t="str">
         <v/>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Armin van Buuren - Equanimity (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>נתי כהן - בראשית עולם קאבר</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>“I Didn’t Know What Time It Was” - Andrew Bird Jazz Trio (Live from The Green Mill)</v>
+        <v>נועם דדון - שיר לערב חג קאבר</v>
       </c>
       <c r="B15" t="str">
-        <v>4 days ago</v>
+        <v>2026-06-03</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=XyRgdfXo2nI</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411188&amp;sid=a85ca8ef30bfde649d428d952bc8fa37</v>
       </c>
       <c r="D15" t="str">
         <v>2026-06-03</v>
@@ -945,16 +945,16 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>4 days ago</v>
+        <v/>
       </c>
       <c r="G15" t="str">
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>Andrew Bird</v>
+        <v/>
       </c>
       <c r="I15" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J15" t="str">
         <v/>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>“I Didn’t Know What Time It Was” - Andrew Bird Jazz Trio (Live from The Green Mill) - Andrew Bird</v>
+        <v>נועם דדון - שיר לערב חג קאבר</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Freya Ridings - Mother Of Pearl (Official Lyric Video)</v>
+        <v>לינוי הגג - הכל שתיקות קאבר</v>
       </c>
       <c r="B16" t="str">
-        <v>4 days ago</v>
+        <v>2026-06-03</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=7SGzYAZ0oxM</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411186&amp;sid=a85ca8ef30bfde649d428d952bc8fa37</v>
       </c>
       <c r="D16" t="str">
         <v>2026-06-03</v>
@@ -983,16 +983,16 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>4 days ago</v>
+        <v/>
       </c>
       <c r="G16" t="str">
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>Freya Ridings</v>
+        <v/>
       </c>
       <c r="I16" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J16" t="str">
         <v/>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Freya Ridings - Mother Of Pearl (Official Lyric Video) - Freya Ridings</v>
+        <v>לינוי הגג - הכל שתיקות קאבר</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Danny Gokey - God's Not (Official Music Video)</v>
+        <v>לביא לוי - נווה הדרים קאבר</v>
       </c>
       <c r="B17" t="str">
-        <v>4 days ago</v>
+        <v>2026-06-03</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=oGpKqX6ftcU</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411184&amp;sid=a85ca8ef30bfde649d428d952bc8fa37</v>
       </c>
       <c r="D17" t="str">
         <v>2026-06-03</v>
@@ -1021,16 +1021,16 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>4 days ago</v>
+        <v/>
       </c>
       <c r="G17" t="str">
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>Danny Gokey</v>
+        <v/>
       </c>
       <c r="I17" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J17" t="str">
         <v/>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Danny Gokey - God's Not (Official Music Video) - Danny Gokey</v>
+        <v>לביא לוי - נווה הדרים קאבר</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Armik - Brisas (2026 Remaster/Remix) (Exciting Rumba Flamenco, Spanish Guitar)</v>
+        <v>יאיר ברוך - נווה הדרים קאבר</v>
       </c>
       <c r="B18" t="str">
-        <v>4 days ago</v>
+        <v>2026-06-03</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=51Zu2iU2z2Q</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411183&amp;sid=a85ca8ef30bfde649d428d952bc8fa37</v>
       </c>
       <c r="D18" t="str">
         <v>2026-06-03</v>
@@ -1059,16 +1059,16 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>4 days ago</v>
+        <v/>
       </c>
       <c r="G18" t="str">
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>Armik</v>
+        <v/>
       </c>
       <c r="I18" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J18" t="str">
         <v/>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Armik - Brisas (2026 Remaster/Remix) (Exciting Rumba Flamenco, Spanish Guitar) - Armik</v>
+        <v>יאיר ברוך - נווה הדרים קאבר</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Holly Humberstone - Lucy (Free People Sessions)</v>
+        <v>אילון לוי - עוד ישמע קאבר</v>
       </c>
       <c r="B19" t="str">
-        <v>4 days ago</v>
+        <v>2026-06-03</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=c1GR2TTs9W8</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411181&amp;sid=a85ca8ef30bfde649d428d952bc8fa37</v>
       </c>
       <c r="D19" t="str">
         <v>2026-06-03</v>
@@ -1097,16 +1097,16 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>4 days ago</v>
+        <v/>
       </c>
       <c r="G19" t="str">
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>Holly Humberstone and Free People</v>
+        <v/>
       </c>
       <c r="I19" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J19" t="str">
         <v/>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Holly Humberstone - Lucy (Free People Sessions) - Holly Humberstone and Free People</v>
+        <v>אילון לוי - עוד ישמע קאבר</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>The Offspring - Why Don’t You Get a Job? | Live at BeachLife Festival 2026</v>
+        <v>אבישי עוזיאל - מחזיק לך תיד קאבר</v>
       </c>
       <c r="B20" t="str">
-        <v>4 days ago</v>
+        <v>2026-06-03</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=zRJ2etb_rpI</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411180&amp;sid=a85ca8ef30bfde649d428d952bc8fa37</v>
       </c>
       <c r="D20" t="str">
         <v>2026-06-03</v>
@@ -1135,16 +1135,16 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>4 days ago</v>
+        <v/>
       </c>
       <c r="G20" t="str">
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>The Offspring</v>
+        <v/>
       </c>
       <c r="I20" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J20" t="str">
         <v/>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>The Offspring - Why Don’t You Get a Job? | Live at BeachLife Festival 2026 - The Offspring</v>
+        <v>אבישי עוזיאל - מחזיק לך תיד קאבר</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Jagwar Twin, sir lucius - bad feeling (oompa loompa) (Visualizer)</v>
+        <v>Just Slide Official Music Video | Kelly Boesch | 4K</v>
       </c>
       <c r="B21" t="str">
-        <v>4 days ago</v>
+        <v>8h ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=XGgI5HvR-gg</v>
+        <v>https://www.youtube.com/watch?v=lC14fuU8aPc</v>
       </c>
       <c r="D21" t="str">
         <v>2026-06-03</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>4 days ago</v>
+        <v>8h ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>Jagwar Twin</v>
+        <v>Kelly Boesch AI Art</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Jagwar Twin, sir lucius - bad feeling (oompa loompa) (Visualizer) - Jagwar Twin</v>
+        <v>Just Slide Official Music Video | Kelly Boesch | 4K - Kelly Boesch AI Art</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Nathan Evans x SAINT PHNX - Home (World Cup 2026) (Official Music Video)</v>
+        <v>Europe - The Cult of Ignorance (Official Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>4 days ago</v>
+        <v>10h ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=lRBNYETENNg</v>
+        <v>https://www.youtube.com/watch?v=p-IOsjOJpnA</v>
       </c>
       <c r="D22" t="str">
         <v>2026-06-03</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>4 days ago</v>
+        <v>10h ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>NathanEvanss</v>
+        <v>Europe</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Nathan Evans x SAINT PHNX - Home (World Cup 2026) (Official Music Video) - NathanEvanss</v>
+        <v>Europe - The Cult of Ignorance (Official Video) - Europe</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Greta Van Fleet - Play Your Games (Official Video)</v>
+        <v>Air Supply - Sweet Dreams (Official Lyric Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>4 days ago</v>
+        <v>14h ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=CJsfI1QVBEM</v>
+        <v>https://www.youtube.com/watch?v=axiK2vYjXio</v>
       </c>
       <c r="D23" t="str">
         <v>2026-06-03</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>4 days ago</v>
+        <v>14h ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>Greta Van Fleet</v>
+        <v>Air Supply</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Greta Van Fleet - Play Your Games (Official Video) - Greta Van Fleet</v>
+        <v>Air Supply - Sweet Dreams (Official Lyric Video) - Air Supply</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Lola Young – From Down Here (From a Living Room)</v>
+        <v>Culture Club - Cold Shoulder</v>
       </c>
       <c r="B24" t="str">
-        <v>4 days ago</v>
+        <v>22h ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=uF5HUfho2NU</v>
+        <v>https://www.youtube.com/watch?v=-YV4SCXFNyg</v>
       </c>
       <c r="D24" t="str">
         <v>2026-06-03</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>4 days ago</v>
+        <v>22h ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>Lola Young</v>
+        <v>Culture Club</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Lola Young – From Down Here (From a Living Room) - Lola Young</v>
+        <v>Culture Club - Cold Shoulder - Culture Club</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Lawrence - Rain Check ft. Quinn XCII (Lyric Video)</v>
+        <v>Julia Cole - Treat Me Like Dirt (Official Lyric Video)</v>
       </c>
       <c r="B25" t="str">
-        <v>4 days ago</v>
+        <v>22h ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=xXeyznlIrFY</v>
+        <v>https://www.youtube.com/watch?v=TS2Mgp5F0cs</v>
       </c>
       <c r="D25" t="str">
         <v>2026-06-03</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>4 days ago</v>
+        <v>22h ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>Lawrence and Quinn XCII</v>
+        <v>Julia Cole Music</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Lawrence - Rain Check ft. Quinn XCII (Lyric Video) - Lawrence and Quinn XCII</v>
+        <v>Julia Cole - Treat Me Like Dirt (Official Lyric Video) - Julia Cole Music</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>ANTONIA - NO HATE | Official Music Video</v>
+        <v>Allen Stone - A Fathers Song - Placeholder Sessions</v>
       </c>
       <c r="B26" t="str">
-        <v>4 days ago</v>
+        <v>23h ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=rhlONr1DTj0</v>
+        <v>https://www.youtube.com/watch?v=JPetpt4QMPE</v>
       </c>
       <c r="D26" t="str">
         <v>2026-06-03</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>4 days ago</v>
+        <v>23h ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>ANTONIA</v>
+        <v>Allen Stone and Placeholder Sessions</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>ANTONIA - NO HATE | Official Music Video - ANTONIA</v>
+        <v>Allen Stone - A Fathers Song - Placeholder Sessions - Allen Stone and Placeholder Sessions</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>R3HAB - "Lost in translation..." (Official Lyric Video)</v>
+        <v>Morgan Wallen - Don't We (Live From Tuscaloosa)</v>
       </c>
       <c r="B27" t="str">
-        <v>4 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=TbJtz0oy2cI</v>
+        <v>https://www.youtube.com/watch?v=qhmWM3uXPAU</v>
       </c>
       <c r="D27" t="str">
         <v>2026-06-03</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>4 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
       </c>
       <c r="H27" t="str">
-        <v>R3HAB</v>
+        <v>Morgan Wallen</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>R3HAB - "Lost in translation..." (Official Lyric Video) - R3HAB</v>
+        <v>Morgan Wallen - Don't We (Live From Tuscaloosa) - Morgan Wallen</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Pink Floyd - Shine On You Crazy Diamond (Parts 1-5) - Live in Venice (Official Video)</v>
+        <v>Billy Idol - John Wayne feat. Alison Mosshart (Official Music Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>4 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=kwiawhDk2TM</v>
+        <v>https://www.youtube.com/watch?v=47LNk7oiTVI</v>
       </c>
       <c r="D28" t="str">
         <v>2026-06-03</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>4 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>Pink Floyd</v>
+        <v>Billy Idol</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Pink Floyd - Shine On You Crazy Diamond (Parts 1-5) - Live in Venice (Official Video) - Pink Floyd</v>
+        <v>Billy Idol - John Wayne feat. Alison Mosshart (Official Music Video) - Billy Idol</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>SHADE - TOXIC</v>
+        <v>'It's Unusual' Official Music Video - Kelly Boesch | 4K</v>
       </c>
       <c r="B29" t="str">
-        <v>4 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=A3km0zrBKSg</v>
+        <v>https://www.youtube.com/watch?v=Ru3fB2l1RSo</v>
       </c>
       <c r="D29" t="str">
         <v>2026-06-03</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>4 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>Shade Official Channel</v>
+        <v>Kelly Boesch AI Art</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>SHADE - TOXIC - Shade Official Channel</v>
+        <v>'It's Unusual' Official Music Video - Kelly Boesch | 4K - Kelly Boesch AI Art</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Dua Lipa - Physical (Live From Mexico)</v>
+        <v>Icona Pop - Butterfly Feelings (Official Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>5 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=xZAe-d3bXTs</v>
+        <v>https://www.youtube.com/watch?v=AMW1Zq9RbIU</v>
       </c>
       <c r="D30" t="str">
         <v>2026-06-03</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>5 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>Dua Lipa</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Dua Lipa - Physical (Live From Mexico) - Dua Lipa</v>
+        <v>Icona Pop - Butterfly Feelings (Official Video) - Icona Pop</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Dagny - Rain (Lyric Video)</v>
+        <v>Hippo Campus - South</v>
       </c>
       <c r="B31" t="str">
-        <v>5 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=j3ZJwczZoUQ</v>
+        <v>https://www.youtube.com/watch?v=FYOmFfV7Ojo</v>
       </c>
       <c r="D31" t="str">
         <v>2026-06-03</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>5 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>Dagny</v>
+        <v>Hippo Campus</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Dagny - Rain (Lyric Video) - Dagny</v>
+        <v>Hippo Campus - South - Hippo Campus</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Modern Talking - Cheri Cheri Lady (Auf los geht's los, 14.09.1985)</v>
+        <v>elijah woods - Old (Treehouse Sessions)</v>
       </c>
       <c r="B32" t="str">
-        <v>5 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=c0LtTVKNwNA</v>
+        <v>https://www.youtube.com/watch?v=yDlkPdR_6zM</v>
       </c>
       <c r="D32" t="str">
         <v>2026-06-03</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>5 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
       </c>
       <c r="H32" t="str">
-        <v>Modern Talking Offiziell</v>
+        <v>elijah woods</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Modern Talking - Cheri Cheri Lady (Auf los geht's los, 14.09.1985) - Modern Talking Offiziell</v>
+        <v>elijah woods - Old (Treehouse Sessions) - elijah woods</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>The Chemical Brothers - Go (Live Show Visual)</v>
+        <v>Nothing But Thieves - Evolution (Official Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>5 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=fHCIchBq8CM</v>
+        <v>https://www.youtube.com/watch?v=hmjfuuuRRYU</v>
       </c>
       <c r="D33" t="str">
         <v>2026-06-03</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>5 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>The Chemical Brothers</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>The Chemical Brothers - Go (Live Show Visual) - The Chemical Brothers</v>
+        <v>Nothing But Thieves - Evolution (Official Video) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Jonas Blue - Girl (Official Lyric Video)</v>
+        <v>Ariana Grande - hate that i made you love me</v>
       </c>
       <c r="B34" t="str">
-        <v>5 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=FTUe3jzUqXU</v>
+        <v>https://www.youtube.com/watch?v=82-jTNka3uc</v>
       </c>
       <c r="D34" t="str">
         <v>2026-06-03</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>5 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>Defected Records and Jonas Blue</v>
+        <v>Ariana Grande</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Jonas Blue - Girl (Official Lyric Video) - Defected Records and Jonas Blue</v>
+        <v>Ariana Grande - hate that i made you love me - Ariana Grande</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Dogpark - Don't Lie (Visualizer)</v>
+        <v>LAUREL - Fire Breather</v>
       </c>
       <c r="B35" t="str">
-        <v>5 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=is7qKBRycJI</v>
+        <v>https://www.youtube.com/watch?v=rtyavLIJjy0</v>
       </c>
       <c r="D35" t="str">
         <v>2026-06-03</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>5 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
       </c>
       <c r="H35" t="str">
-        <v>Dogpark</v>
+        <v>LAUREL</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Dogpark - Don't Lie (Visualizer) - Dogpark</v>
+        <v>LAUREL - Fire Breather - LAUREL</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>elijah woods - L-O-V-E (Treehouse Sessions)</v>
+        <v>The Warning - Ego (Performance Video)</v>
       </c>
       <c r="B36" t="str">
-        <v>5 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=q5kN7eH6rgo</v>
+        <v>https://www.youtube.com/watch?v=7PApWObImjo</v>
       </c>
       <c r="D36" t="str">
         <v>2026-06-03</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>5 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>elijah woods</v>
+        <v>The Warning</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>elijah woods - L-O-V-E (Treehouse Sessions) - elijah woods</v>
+        <v>The Warning - Ego (Performance Video) - The Warning</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Lauren Alaina - Better Off (Official Audio)</v>
+        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (feat. Gabito Ballesteros) [Official Lyric Video]</v>
       </c>
       <c r="B37" t="str">
-        <v>5 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=Vj-ong3XNHM</v>
+        <v>https://www.youtube.com/watch?v=vruZSAYJBe4</v>
       </c>
       <c r="D37" t="str">
         <v>2026-06-03</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>5 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>Lauren Alaina</v>
+        <v>David Guetta and Jennifer Lopez</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Lauren Alaina - Better Off (Official Audio) - Lauren Alaina</v>
+        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (feat. Gabito Ballesteros) [Official Lyric Video] - David Guetta and Jennifer Lopez</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Lauren Sanderson - ARE YOU REALLY HERE? (Lyric Video)</v>
+        <v>Armin van Buuren - Equanimity (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B38" t="str">
-        <v>5 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=u7Et_hbMZUA</v>
+        <v>https://www.youtube.com/watch?v=k93t10R-Qrg</v>
       </c>
       <c r="D38" t="str">
         <v>2026-06-03</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>5 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
       </c>
       <c r="H38" t="str">
-        <v>Lauren Sanderson</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Lauren Sanderson - ARE YOU REALLY HERE? (Lyric Video) - Lauren Sanderson</v>
+        <v>Armin van Buuren - Equanimity (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Nightly – blue jeans (Official Lyric Video)</v>
+        <v>“I Didn’t Know What Time It Was” - Andrew Bird Jazz Trio (Live from The Green Mill)</v>
       </c>
       <c r="B39" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=LnA3xkXUwaM</v>
+        <v>https://www.youtube.com/watch?v=XyRgdfXo2nI</v>
       </c>
       <c r="D39" t="str">
         <v>2026-06-03</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
       </c>
       <c r="H39" t="str">
-        <v>NIGHTLY</v>
+        <v>Andrew Bird</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Nightly – blue jeans (Official Lyric Video) - NIGHTLY</v>
+        <v>“I Didn’t Know What Time It Was” - Andrew Bird Jazz Trio (Live from The Green Mill) - Andrew Bird</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Dasha - Mad About It (Official Visualizer)</v>
+        <v>Freya Ridings - Mother Of Pearl (Official Lyric Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=Ae1gf_7p3H8</v>
+        <v>https://www.youtube.com/watch?v=7SGzYAZ0oxM</v>
       </c>
       <c r="D40" t="str">
         <v>2026-06-03</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
       </c>
       <c r="H40" t="str">
-        <v>Dasha</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Dasha - Mad About It (Official Visualizer) - Dasha</v>
+        <v>Freya Ridings - Mother Of Pearl (Official Lyric Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Max McNown - Something To Someone (Performance Video)</v>
+        <v>Danny Gokey - God's Not (Official Music Video)</v>
       </c>
       <c r="B41" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=4Ki4ejT86YM</v>
+        <v>https://www.youtube.com/watch?v=oGpKqX6ftcU</v>
       </c>
       <c r="D41" t="str">
         <v>2026-06-03</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
       </c>
       <c r="H41" t="str">
-        <v>Max McNown</v>
+        <v>Danny Gokey</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Max McNown - Something To Someone (Performance Video) - Max McNown</v>
+        <v>Danny Gokey - God's Not (Official Music Video) - Danny Gokey</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Bebe Rexha &amp; David Guetta - Sad Girls (Official Visual)</v>
+        <v>Armik - Brisas (2026 Remaster/Remix) (Exciting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B42" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=P8UqZ5IF-QE</v>
+        <v>https://www.youtube.com/watch?v=51Zu2iU2z2Q</v>
       </c>
       <c r="D42" t="str">
         <v>2026-06-03</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
       </c>
       <c r="H42" t="str">
-        <v>Bebe Rexha</v>
+        <v>Armik</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Bebe Rexha &amp; David Guetta - Sad Girls (Official Visual) - Bebe Rexha</v>
+        <v>Armik - Brisas (2026 Remaster/Remix) (Exciting Rumba Flamenco, Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Knox - Long Story Short (Official Video)</v>
+        <v>Holly Humberstone - Lucy (Free People Sessions)</v>
       </c>
       <c r="B43" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=5OGY6hCELfg</v>
+        <v>https://www.youtube.com/watch?v=c1GR2TTs9W8</v>
       </c>
       <c r="D43" t="str">
         <v>2026-06-03</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
       </c>
       <c r="H43" t="str">
-        <v>Knox</v>
+        <v>Holly Humberstone and Free People</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Knox - Long Story Short (Official Video) - Knox</v>
+        <v>Holly Humberstone - Lucy (Free People Sessions) - Holly Humberstone and Free People</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Sofia Camara - The Last Encounter</v>
+        <v>The Offspring - Why Don’t You Get a Job? | Live at BeachLife Festival 2026</v>
       </c>
       <c r="B44" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=E9kN4HLGG1c</v>
+        <v>https://www.youtube.com/watch?v=zRJ2etb_rpI</v>
       </c>
       <c r="D44" t="str">
         <v>2026-06-03</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
       </c>
       <c r="H44" t="str">
-        <v>Sofia Camara</v>
+        <v>The Offspring</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Sofia Camara - The Last Encounter - Sofia Camara</v>
+        <v>The Offspring - Why Don’t You Get a Job? | Live at BeachLife Festival 2026 - The Offspring</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Official Music Video: "Flowers" -- Alexander James</v>
+        <v>Jagwar Twin, sir lucius - bad feeling (oompa loompa) (Visualizer)</v>
       </c>
       <c r="B45" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=aZ4WP0P92tM</v>
+        <v>https://www.youtube.com/watch?v=XGgI5HvR-gg</v>
       </c>
       <c r="D45" t="str">
         <v>2026-06-03</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
       </c>
       <c r="H45" t="str">
-        <v>Alexander James</v>
+        <v>Jagwar Twin</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Official Music Video: "Flowers" -- Alexander James - Alexander James</v>
+        <v>Jagwar Twin, sir lucius - bad feeling (oompa loompa) (Visualizer) - Jagwar Twin</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>almost monday - skinny dip (official video)</v>
+        <v>Nathan Evans x SAINT PHNX - Home (World Cup 2026) (Official Music Video)</v>
       </c>
       <c r="B46" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=hOxZDoaIzKQ</v>
+        <v>https://www.youtube.com/watch?v=lRBNYETENNg</v>
       </c>
       <c r="D46" t="str">
         <v>2026-06-03</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>almost monday</v>
+        <v>NathanEvanss</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>almost monday - skinny dip (official video) - almost monday</v>
+        <v>Nathan Evans x SAINT PHNX - Home (World Cup 2026) (Official Music Video) - NathanEvanss</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Kip Moore - The Darkness (Official)</v>
+        <v>Greta Van Fleet - Play Your Games (Official Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=lTqqixCt5Mk</v>
+        <v>https://www.youtube.com/watch?v=CJsfI1QVBEM</v>
       </c>
       <c r="D47" t="str">
         <v>2026-06-03</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>Kip Moore</v>
+        <v>Greta Van Fleet</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Kip Moore - The Darkness (Official) - Kip Moore</v>
+        <v>Greta Van Fleet - Play Your Games (Official Video) - Greta Van Fleet</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Paul McCartney - Come Inside (Lyric Video)</v>
+        <v>Lola Young – From Down Here (From a Living Room)</v>
       </c>
       <c r="B48" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=C8Zw_Cbm2V0</v>
+        <v>https://www.youtube.com/watch?v=uF5HUfho2NU</v>
       </c>
       <c r="D48" t="str">
         <v>2026-06-03</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>PAUL McCARTNEY</v>
+        <v>Lola Young</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Paul McCartney - Come Inside (Lyric Video) - PAUL McCARTNEY</v>
+        <v>Lola Young – From Down Here (From a Living Room) - Lola Young</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Santana, Becky G - Mi Gran Amor (Official Lyric Video)</v>
+        <v>Lawrence - Rain Check ft. Quinn XCII (Lyric Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=btdBd_Yee8E</v>
+        <v>https://www.youtube.com/watch?v=xXeyznlIrFY</v>
       </c>
       <c r="D49" t="str">
         <v>2026-06-03</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>Santana</v>
+        <v>Lawrence and Quinn XCII</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Santana, Becky G - Mi Gran Amor (Official Lyric Video) - Santana</v>
+        <v>Lawrence - Rain Check ft. Quinn XCII (Lyric Video) - Lawrence and Quinn XCII</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Dua Lipa - Training Season (Live From Mexico)</v>
+        <v>ANTONIA - NO HATE | Official Music Video</v>
       </c>
       <c r="B50" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=Va8Udsvqigs</v>
+        <v>https://www.youtube.com/watch?v=rhlONr1DTj0</v>
       </c>
       <c r="D50" t="str">
         <v>2026-06-03</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>Dua Lipa</v>
+        <v>ANTONIA</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Dua Lipa - Training Season (Live From Mexico) - Dua Lipa</v>
+        <v>ANTONIA - NO HATE | Official Music Video - ANTONIA</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Charley - Liar</v>
+        <v>R3HAB - "Lost in translation..." (Official Lyric Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=3Erfj2Eecgw</v>
+        <v>https://www.youtube.com/watch?v=TbJtz0oy2cI</v>
       </c>
       <c r="D51" t="str">
         <v>2026-06-03</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>Charley</v>
+        <v>R3HAB</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Charley - Liar - Charley</v>
+        <v>R3HAB - "Lost in translation..." (Official Lyric Video) - R3HAB</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (ft Gabito Ballesteros) [Visualizer]</v>
+        <v>Pink Floyd - Shine On You Crazy Diamond (Parts 1-5) - Live in Venice (Official Video)</v>
       </c>
       <c r="B52" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=em5ryETDkAo</v>
+        <v>https://www.youtube.com/watch?v=kwiawhDk2TM</v>
       </c>
       <c r="D52" t="str">
         <v>2026-06-03</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>David Guetta and Jennifer Lopez</v>
+        <v>Pink Floyd</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (ft Gabito Ballesteros) [Visualizer] - David Guetta and Jennifer Lopez</v>
+        <v>Pink Floyd - Shine On You Crazy Diamond (Parts 1-5) - Live in Venice (Official Video) - Pink Floyd</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Jordana Bryant - Too Little Too Late (Official Audio)</v>
+        <v>SHADE - TOXIC</v>
       </c>
       <c r="B53" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=AmwNx9qlOpA</v>
+        <v>https://www.youtube.com/watch?v=A3km0zrBKSg</v>
       </c>
       <c r="D53" t="str">
         <v>2026-06-03</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>Jordana Bryant</v>
+        <v>Shade Official Channel</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Jordana Bryant - Too Little Too Late (Official Audio) - Jordana Bryant</v>
+        <v>SHADE - TOXIC - Shade Official Channel</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Lewis Capaldi - Stay Love (Official Video)</v>
+        <v>Dua Lipa - Physical (Live From Mexico)</v>
       </c>
       <c r="B54" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=9Pud3BqPpq0</v>
+        <v>https://www.youtube.com/watch?v=xZAe-d3bXTs</v>
       </c>
       <c r="D54" t="str">
         <v>2026-06-03</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>Lewis Capaldi</v>
+        <v>Dua Lipa</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Lewis Capaldi - Stay Love (Official Video) - Lewis Capaldi</v>
+        <v>Dua Lipa - Physical (Live From Mexico) - Dua Lipa</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Surreal World of Oddities - Pulling At My Strings - Official Music Video | 4K</v>
+        <v>Dagny - Rain (Lyric Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>6 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=fMt-f2aUW3c</v>
+        <v>https://www.youtube.com/watch?v=j3ZJwczZoUQ</v>
       </c>
       <c r="D55" t="str">
         <v>2026-06-03</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>6 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>Kelly Boesch AI Art</v>
+        <v>Dagny</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Surreal World of Oddities - Pulling At My Strings - Official Music Video | 4K - Kelly Boesch AI Art</v>
+        <v>Dagny - Rain (Lyric Video) - Dagny</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Julia Cole - Love You to Death (Official Video)</v>
+        <v>Modern Talking - Cheri Cheri Lady (Auf los geht's los, 14.09.1985)</v>
       </c>
       <c r="B56" t="str">
-        <v>6 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=dWgmFc2QuLY</v>
+        <v>https://www.youtube.com/watch?v=c0LtTVKNwNA</v>
       </c>
       <c r="D56" t="str">
         <v>2026-06-03</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>6 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>Julia Cole Music</v>
+        <v>Modern Talking Offiziell</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Julia Cole - Love You to Death (Official Video) - Julia Cole Music</v>
+        <v>Modern Talking - Cheri Cheri Lady (Auf los geht's los, 14.09.1985) - Modern Talking Offiziell</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Victor Biliac - De-ai fi tu salcie la mal ( Cover Edit )</v>
+        <v>The Chemical Brothers - Go (Live Show Visual)</v>
       </c>
       <c r="B57" t="str">
-        <v>6 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=v3c0kG-V2zk</v>
+        <v>https://www.youtube.com/watch?v=fHCIchBq8CM</v>
       </c>
       <c r="D57" t="str">
         <v>2026-06-03</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>6 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>VictorBiliac</v>
+        <v>The Chemical Brothers</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Victor Biliac - De-ai fi tu salcie la mal ( Cover Edit ) - VictorBiliac</v>
+        <v>The Chemical Brothers - Go (Live Show Visual) - The Chemical Brothers</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Lolo Zouaï - Coquelicot (feat. disiz) (Official Video)</v>
+        <v>Jonas Blue - Girl (Official Lyric Video)</v>
       </c>
       <c r="B58" t="str">
-        <v>6 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=-4p6FkrOGT4</v>
+        <v>https://www.youtube.com/watch?v=FTUe3jzUqXU</v>
       </c>
       <c r="D58" t="str">
         <v>2026-06-03</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>6 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>Lolo Zouaï and disiz</v>
+        <v>Defected Records and Jonas Blue</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Lolo Zouaï - Coquelicot (feat. disiz) (Official Video) - Lolo Zouaï and disiz</v>
+        <v>Jonas Blue - Girl (Official Lyric Video) - Defected Records and Jonas Blue</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Jungle - The Wave (Official Video)</v>
+        <v>Dogpark - Don't Lie (Visualizer)</v>
       </c>
       <c r="B59" t="str">
-        <v>6 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=DW1vUkqNvqQ</v>
+        <v>https://www.youtube.com/watch?v=is7qKBRycJI</v>
       </c>
       <c r="D59" t="str">
         <v>2026-06-03</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>6 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>Jungle4eva</v>
+        <v>Dogpark</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Jungle - The Wave (Official Video) - Jungle4eva</v>
+        <v>Dogpark - Don't Lie (Visualizer) - Dogpark</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Daytime TV – Sun (Official Music Video)</v>
+        <v>elijah woods - L-O-V-E (Treehouse Sessions)</v>
       </c>
       <c r="B60" t="str">
-        <v>6 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=Jqo4ra_ch-M</v>
+        <v>https://www.youtube.com/watch?v=q5kN7eH6rgo</v>
       </c>
       <c r="D60" t="str">
         <v>2026-06-03</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>6 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>DAYTIME TV</v>
+        <v>elijah woods</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Daytime TV – Sun (Official Music Video) - DAYTIME TV</v>
+        <v>elijah woods - L-O-V-E (Treehouse Sessions) - elijah woods</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Surreal and Strange AI Video | Not Made For The Cage | Kelly Boesch - 4K</v>
+        <v>Lauren Alaina - Better Off (Official Audio)</v>
       </c>
       <c r="B61" t="str">
-        <v>2 weeks ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=ACNj3L2bzV8</v>
+        <v>https://www.youtube.com/watch?v=Vj-ong3XNHM</v>
       </c>
       <c r="D61" t="str">
         <v>2026-06-03</v>
@@ -2693,13 +2693,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>2 weeks ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>Kelly Boesch AI Art</v>
+        <v>Lauren Alaina</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Surreal and Strange AI Video | Not Made For The Cage | Kelly Boesch - 4K - Kelly Boesch AI Art</v>
+        <v>Lauren Alaina - Better Off (Official Audio) - Lauren Alaina</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Bruno Mars - Risk It All [Live From The Romantic Tour]</v>
+        <v>Lauren Sanderson - ARE YOU REALLY HERE? (Lyric Video)</v>
       </c>
       <c r="B62" t="str">
-        <v>7 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=aFbueod4reQ</v>
+        <v>https://www.youtube.com/watch?v=u7Et_hbMZUA</v>
       </c>
       <c r="D62" t="str">
         <v>2026-06-03</v>
@@ -2731,13 +2731,13 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>7 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>Bruno Mars</v>
+        <v>Lauren Sanderson</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Bruno Mars - Risk It All [Live From The Romantic Tour] - Bruno Mars</v>
+        <v>Lauren Sanderson - ARE YOU REALLY HERE? (Lyric Video) - Lauren Sanderson</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Keith Urban - Summer Breeze (52nd American Music Awards)</v>
+        <v>Nightly – blue jeans (Official Lyric Video)</v>
       </c>
       <c r="B63" t="str">
-        <v>7 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=zn-4eVoqofQ</v>
+        <v>https://www.youtube.com/watch?v=LnA3xkXUwaM</v>
       </c>
       <c r="D63" t="str">
         <v>2026-06-03</v>
@@ -2769,13 +2769,13 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>7 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>Keith Urban</v>
+        <v>NIGHTLY</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Keith Urban - Summer Breeze (52nd American Music Awards) - Keith Urban</v>
+        <v>Nightly – blue jeans (Official Lyric Video) - NIGHTLY</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Nelly Furtado, Boi-1Da, Canada Soccer - ELECTRIC CIRCUS (Official Music Video)</v>
+        <v>Dasha - Mad About It (Official Visualizer)</v>
       </c>
       <c r="B64" t="str">
-        <v>8 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=lHYEMWFuErM</v>
+        <v>https://www.youtube.com/watch?v=Ae1gf_7p3H8</v>
       </c>
       <c r="D64" t="str">
         <v>2026-06-03</v>
@@ -2807,13 +2807,13 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>8 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>Nelly Furtado</v>
+        <v>Dasha</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Nelly Furtado, Boi-1Da, Canada Soccer - ELECTRIC CIRCUS (Official Music Video) - Nelly Furtado</v>
+        <v>Dasha - Mad About It (Official Visualizer) - Dasha</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Teddy Swims - Mr. Know It All (Live from the AMAs)</v>
+        <v>Max McNown - Something To Someone (Performance Video)</v>
       </c>
       <c r="B65" t="str">
-        <v>8 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=ttM4gWkhZBk</v>
+        <v>https://www.youtube.com/watch?v=4Ki4ejT86YM</v>
       </c>
       <c r="D65" t="str">
         <v>2026-06-03</v>
@@ -2845,13 +2845,13 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>8 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>Teddy Swims and American Music Awards</v>
+        <v>Max McNown</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Teddy Swims - Mr. Know It All (Live from the AMAs) - Teddy Swims and American Music Awards</v>
+        <v>Max McNown - Something To Someone (Performance Video) - Max McNown</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Shakira, Burna Boy - Dai Dai (Official Video)</v>
+        <v>Bebe Rexha &amp; David Guetta - Sad Girls (Official Visual)</v>
       </c>
       <c r="B66" t="str">
-        <v>10 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=fcnDmrtj6Sk</v>
+        <v>https://www.youtube.com/watch?v=P8UqZ5IF-QE</v>
       </c>
       <c r="D66" t="str">
         <v>2026-06-03</v>
@@ -2883,13 +2883,13 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>10 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>Shakira and 2 more</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Shakira, Burna Boy - Dai Dai (Official Video) - Shakira and 2 more</v>
+        <v>Bebe Rexha &amp; David Guetta - Sad Girls (Official Visual) - Bebe Rexha</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards)</v>
+        <v>Knox - Long Story Short (Official Video)</v>
       </c>
       <c r="B67" t="str">
-        <v>10 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=wacpnp83cJg</v>
+        <v>https://www.youtube.com/watch?v=5OGY6hCELfg</v>
       </c>
       <c r="D67" t="str">
         <v>2026-06-03</v>
@@ -2921,13 +2921,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>10 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>Lainey Wilson</v>
+        <v>Knox</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards) - Lainey Wilson</v>
+        <v>Knox - Long Story Short (Official Video) - Knox</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ]</v>
+        <v>Sofia Camara - The Last Encounter</v>
       </c>
       <c r="B68" t="str">
-        <v>11 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=w8FTnkNVmq0</v>
+        <v>https://www.youtube.com/watch?v=E9kN4HLGG1c</v>
       </c>
       <c r="D68" t="str">
         <v>2026-06-03</v>
@@ -2959,13 +2959,13 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>11 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>Duran Duran</v>
+        <v>Sofia Camara</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ] - Duran Duran</v>
+        <v>Sofia Camara - The Last Encounter - Sofia Camara</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Nico Santos - Optimist</v>
+        <v>Official Music Video: "Flowers" -- Alexander James</v>
       </c>
       <c r="B69" t="str">
-        <v>13 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=JA6PIcBeKZ0</v>
+        <v>https://www.youtube.com/watch?v=aZ4WP0P92tM</v>
       </c>
       <c r="D69" t="str">
         <v>2026-06-03</v>
@@ -2997,13 +2997,13 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>13 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>Nico Santos</v>
+        <v>Alexander James</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Nico Santos - Optimist - Nico Santos</v>
+        <v>Official Music Video: "Flowers" -- Alexander James - Alexander James</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Def Leppard - Personal Jesus (Live at Caesars Palace)</v>
+        <v>almost monday - skinny dip (official video)</v>
       </c>
       <c r="B70" t="str">
-        <v>10 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=k5SRMgdG4L4</v>
+        <v>https://www.youtube.com/watch?v=hOxZDoaIzKQ</v>
       </c>
       <c r="D70" t="str">
         <v>2026-06-03</v>
@@ -3035,13 +3035,13 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>10 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>DEF LEPPARD</v>
+        <v>almost monday</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Def Leppard - Personal Jesus (Live at Caesars Palace) - DEF LEPPARD</v>
+        <v>almost monday - skinny dip (official video) - almost monday</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer)</v>
+        <v>Kip Moore - The Darkness (Official)</v>
       </c>
       <c r="B71" t="str">
-        <v>11 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=eWSwy9GU2L8</v>
+        <v>https://www.youtube.com/watch?v=lTqqixCt5Mk</v>
       </c>
       <c r="D71" t="str">
         <v>2026-06-03</v>
@@ -3073,13 +3073,13 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>11 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>Will Linley</v>
+        <v>Kip Moore</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer) - Will Linley</v>
+        <v>Kip Moore - The Darkness (Official) - Kip Moore</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Kylie Minogue - Story (Official Lyric Video)</v>
+        <v>Paul McCartney - Come Inside (Lyric Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>11 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=fv7_1qKo8mg</v>
+        <v>https://www.youtube.com/watch?v=C8Zw_Cbm2V0</v>
       </c>
       <c r="D72" t="str">
         <v>2026-06-03</v>
@@ -3111,13 +3111,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>11 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>Kylie Minogue</v>
+        <v>PAUL McCARTNEY</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Kylie Minogue - Story (Official Lyric Video) - Kylie Minogue</v>
+        <v>Paul McCartney - Come Inside (Lyric Video) - PAUL McCARTNEY</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video)</v>
+        <v>Santana, Becky G - Mi Gran Amor (Official Lyric Video)</v>
       </c>
       <c r="B73" t="str">
-        <v>11 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=3KUQx2s1fQc</v>
+        <v>https://www.youtube.com/watch?v=btdBd_Yee8E</v>
       </c>
       <c r="D73" t="str">
         <v>2026-06-03</v>
@@ -3149,13 +3149,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>11 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>Billy Raffoul</v>
+        <v>Santana</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video) - Billy Raffoul</v>
+        <v>Santana, Becky G - Mi Gran Amor (Official Lyric Video) - Santana</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025)</v>
+        <v>Dua Lipa - Training Season (Live From Mexico)</v>
       </c>
       <c r="B74" t="str">
-        <v>11 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=vWf4uiLvwF8</v>
+        <v>https://www.youtube.com/watch?v=Va8Udsvqigs</v>
       </c>
       <c r="D74" t="str">
         <v>2026-06-03</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>11 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>The Offspring</v>
+        <v>Dua Lipa</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025) - The Offspring</v>
+        <v>Dua Lipa - Training Season (Live From Mexico) - Dua Lipa</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024)</v>
+        <v>Charley - Liar</v>
       </c>
       <c r="B75" t="str">
-        <v>11 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=9xjMaXegmWM</v>
+        <v>https://www.youtube.com/watch?v=3Erfj2Eecgw</v>
       </c>
       <c r="D75" t="str">
         <v>2026-06-03</v>
@@ -3225,13 +3225,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>11 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>David Gilmour</v>
+        <v>Charley</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024) - David Gilmour</v>
+        <v>Charley - Liar - Charley</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Scorpions - Delicate Dance (Madison Square Garden 2022)</v>
+        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (ft Gabito Ballesteros) [Visualizer]</v>
       </c>
       <c r="B76" t="str">
-        <v>11 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=yAjEr9WLTnU</v>
+        <v>https://www.youtube.com/watch?v=em5ryETDkAo</v>
       </c>
       <c r="D76" t="str">
         <v>2026-06-03</v>
@@ -3263,13 +3263,13 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>11 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>Scorpions</v>
+        <v>David Guetta and Jennifer Lopez</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Scorpions - Delicate Dance (Madison Square Garden 2022) - Scorpions</v>
+        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (ft Gabito Ballesteros) [Visualizer] - David Guetta and Jennifer Lopez</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston)</v>
+        <v>Jordana Bryant - Too Little Too Late (Official Audio)</v>
       </c>
       <c r="B77" t="str">
-        <v>11 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=oRw4PqBzGc0</v>
+        <v>https://www.youtube.com/watch?v=AmwNx9qlOpA</v>
       </c>
       <c r="D77" t="str">
         <v>2026-06-03</v>
@@ -3301,13 +3301,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>11 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>Brandon Lake and NICK JONAS</v>
+        <v>Jordana Bryant</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston) - Brandon Lake and NICK JONAS</v>
+        <v>Jordana Bryant - Too Little Too Late (Official Audio) - Jordana Bryant</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video)</v>
+        <v>Lewis Capaldi - Stay Love (Official Video)</v>
       </c>
       <c r="B78" t="str">
-        <v>11 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=OKf_IOGxFQo</v>
+        <v>https://www.youtube.com/watch?v=9Pud3BqPpq0</v>
       </c>
       <c r="D78" t="str">
         <v>2026-06-03</v>
@@ -3339,13 +3339,13 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>11 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>Kygo and Dan Tyminski</v>
+        <v>Lewis Capaldi</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video) - Kygo and Dan Tyminski</v>
+        <v>Lewis Capaldi - Stay Love (Official Video) - Lewis Capaldi</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>The Warning - Ego (Official Video)</v>
+        <v>Surreal World of Oddities - Pulling At My Strings - Official Music Video | 4K</v>
       </c>
       <c r="B79" t="str">
-        <v>11 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=CG6Q5i75bR4</v>
+        <v>https://www.youtube.com/watch?v=fMt-f2aUW3c</v>
       </c>
       <c r="D79" t="str">
         <v>2026-06-03</v>
@@ -3377,13 +3377,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>11 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>The Warning</v>
+        <v>Kelly Boesch AI Art</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>The Warning - Ego (Official Video) - The Warning</v>
+        <v>Surreal World of Oddities - Pulling At My Strings - Official Music Video | 4K - Kelly Boesch AI Art</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>paris jackson - teenage drama (official lyric video)</v>
+        <v>Julia Cole - Love You to Death (Official Video)</v>
       </c>
       <c r="B80" t="str">
-        <v>11 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=kVfDArNljos</v>
+        <v>https://www.youtube.com/watch?v=dWgmFc2QuLY</v>
       </c>
       <c r="D80" t="str">
         <v>2026-06-03</v>
@@ -3415,13 +3415,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>11 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>paris jackson</v>
+        <v>Julia Cole Music</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>paris jackson - teenage drama (official lyric video) - paris jackson</v>
+        <v>Julia Cole - Love You to Death (Official Video) - Julia Cole Music</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Minelli - Sun Goes Down | Official Visualizer</v>
+        <v>Victor Biliac - De-ai fi tu salcie la mal ( Cover Edit )</v>
       </c>
       <c r="B81" t="str">
-        <v>11 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=xOsjm-AwN5I</v>
+        <v>https://www.youtube.com/watch?v=v3c0kG-V2zk</v>
       </c>
       <c r="D81" t="str">
         <v>2026-06-03</v>
@@ -3453,13 +3453,13 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>11 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
       </c>
       <c r="H81" t="str">
-        <v>Minelli</v>
+        <v>VictorBiliac</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Minelli - Sun Goes Down | Official Visualizer - Minelli</v>
+        <v>Victor Biliac - De-ai fi tu salcie la mal ( Cover Edit ) - VictorBiliac</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Maggie Rose - Gentle Man (Official Studio Video)</v>
+        <v>Lolo Zouaï - Coquelicot (feat. disiz) (Official Video)</v>
       </c>
       <c r="B82" t="str">
-        <v>11 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=aWNK-vWrN60</v>
+        <v>https://www.youtube.com/watch?v=-4p6FkrOGT4</v>
       </c>
       <c r="D82" t="str">
         <v>2026-06-03</v>
@@ -3491,13 +3491,13 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>11 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
       </c>
       <c r="H82" t="str">
-        <v>Maggie Rose</v>
+        <v>Lolo Zouaï and disiz</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Maggie Rose - Gentle Man (Official Studio Video) - Maggie Rose</v>
+        <v>Lolo Zouaï - Coquelicot (feat. disiz) (Official Video) - Lolo Zouaï and disiz</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer]</v>
+        <v>Jungle - The Wave (Official Video)</v>
       </c>
       <c r="B83" t="str">
-        <v>12 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=mN5AZBrVq9I</v>
+        <v>https://www.youtube.com/watch?v=DW1vUkqNvqQ</v>
       </c>
       <c r="D83" t="str">
         <v>2026-06-03</v>
@@ -3529,13 +3529,13 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>12 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
       </c>
       <c r="H83" t="str">
-        <v>David Guetta</v>
+        <v>Jungle4eva</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer] - David Guetta</v>
+        <v>Jungle - The Wave (Official Video) - Jungle4eva</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video)</v>
+        <v>Daytime TV – Sun (Official Music Video)</v>
       </c>
       <c r="B84" t="str">
-        <v>12 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=0PTufEGRAVQ</v>
+        <v>https://www.youtube.com/watch?v=Jqo4ra_ch-M</v>
       </c>
       <c r="D84" t="str">
         <v>2026-06-03</v>
@@ -3567,13 +3567,13 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>12 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
       </c>
       <c r="H84" t="str">
-        <v>Chris Young and Shaylen</v>
+        <v>DAYTIME TV</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video) - Chris Young and Shaylen</v>
+        <v>Daytime TV – Sun (Official Music Video) - DAYTIME TV</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Lauv - Pretty Little Things</v>
+        <v>Surreal and Strange AI Video | Not Made For The Cage | Kelly Boesch - 4K</v>
       </c>
       <c r="B85" t="str">
-        <v>12 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=_JBfanFvHnA</v>
+        <v>https://www.youtube.com/watch?v=ACNj3L2bzV8</v>
       </c>
       <c r="D85" t="str">
         <v>2026-06-03</v>
@@ -3605,13 +3605,13 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>12 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
       </c>
       <c r="H85" t="str">
-        <v>Lauv</v>
+        <v>Kelly Boesch AI Art</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Lauv - Pretty Little Things - Lauv</v>
+        <v>Surreal and Strange AI Video | Not Made For The Cage | Kelly Boesch - 4K - Kelly Boesch AI Art</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Icona Pop - Butterfly Feelings (Official Audio)</v>
+        <v>Bruno Mars - Risk It All [Live From The Romantic Tour]</v>
       </c>
       <c r="B86" t="str">
-        <v>12 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=bXA_Q75QZTs</v>
+        <v>https://www.youtube.com/watch?v=aFbueod4reQ</v>
       </c>
       <c r="D86" t="str">
         <v>2026-06-03</v>
@@ -3643,13 +3643,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>12 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>Icona Pop</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Icona Pop - Butterfly Feelings (Official Audio) - Icona Pop</v>
+        <v>Bruno Mars - Risk It All [Live From The Romantic Tour] - Bruno Mars</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Will Swinton - Only One (Official Video)</v>
+        <v>Keith Urban - Summer Breeze (52nd American Music Awards)</v>
       </c>
       <c r="B87" t="str">
-        <v>12 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=A0KzP-zm9hA</v>
+        <v>https://www.youtube.com/watch?v=zn-4eVoqofQ</v>
       </c>
       <c r="D87" t="str">
         <v>2026-06-03</v>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>12 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>Will Swinton</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Will Swinton - Only One (Official Video) - Will Swinton</v>
+        <v>Keith Urban - Summer Breeze (52nd American Music Awards) - Keith Urban</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Dean Lewis - Escape (Official Video)</v>
+        <v>Nelly Furtado, Boi-1Da, Canada Soccer - ELECTRIC CIRCUS (Official Music Video)</v>
       </c>
       <c r="B88" t="str">
-        <v>12 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=BZRaTXCkhcg</v>
+        <v>https://www.youtube.com/watch?v=lHYEMWFuErM</v>
       </c>
       <c r="D88" t="str">
         <v>2026-06-03</v>
@@ -3719,13 +3719,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>12 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>Dean Lewis</v>
+        <v>Nelly Furtado</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Dean Lewis - Escape (Official Video) - Dean Lewis</v>
+        <v>Nelly Furtado, Boi-1Da, Canada Soccer - ELECTRIC CIRCUS (Official Music Video) - Nelly Furtado</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico]</v>
+        <v>Teddy Swims - Mr. Know It All (Live from the AMAs)</v>
       </c>
       <c r="B89" t="str">
-        <v>12 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=PNm0hf_zZJY</v>
+        <v>https://www.youtube.com/watch?v=ttM4gWkhZBk</v>
       </c>
       <c r="D89" t="str">
         <v>2026-06-03</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>12 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>Dua Lipa and OficialMana</v>
+        <v>Teddy Swims and American Music Awards</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico] - Dua Lipa and OficialMana</v>
+        <v>Teddy Swims - Mr. Know It All (Live from the AMAs) - Teddy Swims and American Music Awards</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Niall Horan - End of an Era (Lyric Video)</v>
+        <v>Shakira, Burna Boy - Dai Dai (Official Video)</v>
       </c>
       <c r="B90" t="str">
-        <v>12 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=EUNNmAAe5gQ</v>
+        <v>https://www.youtube.com/watch?v=fcnDmrtj6Sk</v>
       </c>
       <c r="D90" t="str">
         <v>2026-06-03</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>12 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>Niall Horan</v>
+        <v>Shakira and 2 more</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Niall Horan - End of an Era (Lyric Video) - Niall Horan</v>
+        <v>Shakira, Burna Boy - Dai Dai (Official Video) - Shakira and 2 more</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Olivia Rodrigo - the cure (Official Music Video)</v>
+        <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards)</v>
       </c>
       <c r="B91" t="str">
-        <v>12 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=B402rKl4bUg</v>
+        <v>https://www.youtube.com/watch?v=wacpnp83cJg</v>
       </c>
       <c r="D91" t="str">
         <v>2026-06-03</v>
@@ -3833,13 +3833,13 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>12 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>Olivia Rodrigo</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Olivia Rodrigo - the cure (Official Music Video) - Olivia Rodrigo</v>
+        <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards) - Lainey Wilson</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Ruel - Debbie Don't Cry (Official Music Video)</v>
+        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ]</v>
       </c>
       <c r="B92" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=iz7wuk0GOwI</v>
+        <v>https://www.youtube.com/watch?v=w8FTnkNVmq0</v>
       </c>
       <c r="D92" t="str">
         <v>2026-06-03</v>
@@ -3871,13 +3871,13 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
       </c>
       <c r="H92" t="str">
-        <v>RUEL</v>
+        <v>Duran Duran</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Ruel - Debbie Don't Cry (Official Music Video) - RUEL</v>
+        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ] - Duran Duran</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>TINI - Down (LIVE)</v>
+        <v>Nico Santos - Optimist</v>
       </c>
       <c r="B93" t="str">
-        <v>12 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=ADbFeQUPTrk</v>
+        <v>https://www.youtube.com/watch?v=JA6PIcBeKZ0</v>
       </c>
       <c r="D93" t="str">
         <v>2026-06-03</v>
@@ -3909,13 +3909,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>12 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>TINI</v>
+        <v>Nico Santos</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>TINI - Down (LIVE) - TINI</v>
+        <v>Nico Santos - Optimist - Nico Santos</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Charli xcx - SS26 (Official Video)</v>
+        <v>Def Leppard - Personal Jesus (Live at Caesars Palace)</v>
       </c>
       <c r="B94" t="str">
-        <v>12 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=twLhSqabby0</v>
+        <v>https://www.youtube.com/watch?v=k5SRMgdG4L4</v>
       </c>
       <c r="D94" t="str">
         <v>2026-06-03</v>
@@ -3947,13 +3947,13 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>12 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
       </c>
       <c r="H94" t="str">
-        <v>Charli xcx</v>
+        <v>DEF LEPPARD</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Charli xcx - SS26 (Official Video) - Charli xcx</v>
+        <v>Def Leppard - Personal Jesus (Live at Caesars Palace) - DEF LEPPARD</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Dua Lipa - Live From Mexico</v>
+        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer)</v>
       </c>
       <c r="B95" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=vZYVkitGXBU</v>
+        <v>https://www.youtube.com/watch?v=eWSwy9GU2L8</v>
       </c>
       <c r="D95" t="str">
         <v>2026-06-03</v>
@@ -3985,13 +3985,13 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
       </c>
       <c r="H95" t="str">
-        <v>Dua Lipa</v>
+        <v>Will Linley</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Dua Lipa - Live From Mexico - Dua Lipa</v>
+        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer) - Will Linley</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Matilda Mann - 'The Fig Tree' (Official Video)</v>
+        <v>Kylie Minogue - Story (Official Lyric Video)</v>
       </c>
       <c r="B96" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=XPyubkkkw44</v>
+        <v>https://www.youtube.com/watch?v=fv7_1qKo8mg</v>
       </c>
       <c r="D96" t="str">
         <v>2026-06-03</v>
@@ -4023,13 +4023,13 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
       </c>
       <c r="H96" t="str">
-        <v>Matilda Mann</v>
+        <v>Kylie Minogue</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Matilda Mann - 'The Fig Tree' (Official Video) - Matilda Mann</v>
+        <v>Kylie Minogue - Story (Official Lyric Video) - Kylie Minogue</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Ella Langley - Be Her (61st Academy of Country Music Awards)</v>
+        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video)</v>
       </c>
       <c r="B97" t="str">
-        <v>13 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=4KbYfH7EAm8</v>
+        <v>https://www.youtube.com/watch?v=3KUQx2s1fQc</v>
       </c>
       <c r="D97" t="str">
         <v>2026-06-03</v>
@@ -4061,13 +4061,13 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>13 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
       </c>
       <c r="H97" t="str">
-        <v>Ella Langley</v>
+        <v>Billy Raffoul</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Ella Langley - Be Her (61st Academy of Country Music Awards) - Ella Langley</v>
+        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video) - Billy Raffoul</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Nothing But Thieves - Evolution (Official Audio)</v>
+        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025)</v>
       </c>
       <c r="B98" t="str">
-        <v>13 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=Kcs-4EZSUW0</v>
+        <v>https://www.youtube.com/watch?v=vWf4uiLvwF8</v>
       </c>
       <c r="D98" t="str">
         <v>2026-06-03</v>
@@ -4099,13 +4099,13 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>13 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
       </c>
       <c r="H98" t="str">
-        <v>Nothing But Thieves</v>
+        <v>The Offspring</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Nothing But Thieves - Evolution (Official Audio) - Nothing But Thieves</v>
+        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025) - The Offspring</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO)</v>
+        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024)</v>
       </c>
       <c r="B99" t="str">
-        <v>13 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=HiLT1jzDZb4</v>
+        <v>https://www.youtube.com/watch?v=9xjMaXegmWM</v>
       </c>
       <c r="D99" t="str">
         <v>2026-06-03</v>
@@ -4137,13 +4137,13 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>13 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
       </c>
       <c r="H99" t="str">
-        <v>kesha</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO) - kesha</v>
+        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024) - David Gilmour</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify</v>
+        <v>Scorpions - Delicate Dance (Madison Square Garden 2022)</v>
       </c>
       <c r="B100" t="str">
-        <v>13 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=_WGsJYCCfU8</v>
+        <v>https://www.youtube.com/watch?v=yAjEr9WLTnU</v>
       </c>
       <c r="D100" t="str">
         <v>2026-06-03</v>
@@ -4175,13 +4175,13 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>13 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
       </c>
       <c r="H100" t="str">
-        <v>Holly Humberstone</v>
+        <v>Scorpions</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify - Holly Humberstone</v>
+        <v>Scorpions - Delicate Dance (Madison Square Garden 2022) - Scorpions</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Foo Fighters - Of All People (Official Video)</v>
+        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston)</v>
       </c>
       <c r="B101" t="str">
-        <v>13 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=r_iMzMrCQs0</v>
+        <v>https://www.youtube.com/watch?v=oRw4PqBzGc0</v>
       </c>
       <c r="D101" t="str">
         <v>2026-06-03</v>
@@ -4213,13 +4213,13 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>13 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G101" t="str">
         <v/>
       </c>
       <c r="H101" t="str">
-        <v>Foo Fighters</v>
+        <v>Brandon Lake and NICK JONAS</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Foo Fighters - Of All People (Official Video) - Foo Fighters</v>
+        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston) - Brandon Lake and NICK JONAS</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>'From Me To You' by The Beatles, performed by The Young Analogues</v>
+        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B102" t="str">
-        <v>13 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=cLiyO2t3xd0</v>
+        <v>https://www.youtube.com/watch?v=OKf_IOGxFQo</v>
       </c>
       <c r="D102" t="str">
         <v>2026-06-03</v>
@@ -4251,13 +4251,13 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>13 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G102" t="str">
         <v/>
       </c>
       <c r="H102" t="str">
-        <v>The Analogues</v>
+        <v>Kygo and Dan Tyminski</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4269,18 +4269,18 @@
         <v/>
       </c>
       <c r="L102" t="str">
-        <v>'From Me To You' by The Beatles, performed by The Young Analogues - The Analogues</v>
+        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video) - Kygo and Dan Tyminski</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video]</v>
+        <v>The Warning - Ego (Official Video)</v>
       </c>
       <c r="B103" t="str">
-        <v>2 weeks ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C103" t="str">
-        <v>https://www.youtube.com/watch?v=O67Q25sMhyU</v>
+        <v>https://www.youtube.com/watch?v=CG6Q5i75bR4</v>
       </c>
       <c r="D103" t="str">
         <v>2026-06-03</v>
@@ -4289,13 +4289,13 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>2 weeks ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G103" t="str">
         <v/>
       </c>
       <c r="H103" t="str">
-        <v>Rod Stewart</v>
+        <v>The Warning</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4307,18 +4307,18 @@
         <v/>
       </c>
       <c r="L103" t="str">
-        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video] - Rod Stewart</v>
+        <v>The Warning - Ego (Official Video) - The Warning</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>snake the drain</v>
+        <v>paris jackson - teenage drama (official lyric video)</v>
       </c>
       <c r="B104" t="str">
-        <v/>
+        <v>12d ago</v>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/snake-the-drain/6771506655</v>
+        <v>https://www.youtube.com/watch?v=kVfDArNljos</v>
       </c>
       <c r="D104" t="str">
         <v>2026-06-03</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>this time it’s different / snake the drain - Single</v>
+        <v>12d ago</v>
       </c>
       <c r="G104" t="str">
-        <v>3:08</v>
+        <v/>
       </c>
       <c r="H104" t="str">
-        <v>Devon Again</v>
+        <v>paris jackson</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/devon-again/1574318250</v>
+        <v/>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/snake-the-drain/6771506650</v>
+        <v/>
       </c>
       <c r="L104" t="str">
-        <v>snake the drain - Devon Again</v>
+        <v>paris jackson - teenage drama (official lyric video) - paris jackson</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>hate that i made you love me</v>
+        <v>Minelli - Sun Goes Down | Official Visualizer</v>
       </c>
       <c r="B105" t="str">
-        <v/>
+        <v>12d ago</v>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/hate-that-i-made-you-love-me/6763656876</v>
+        <v>https://www.youtube.com/watch?v=xOsjm-AwN5I</v>
       </c>
       <c r="D105" t="str">
         <v>2026-06-03</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>petal</v>
+        <v>12d ago</v>
       </c>
       <c r="G105" t="str">
-        <v>3:17</v>
+        <v/>
       </c>
       <c r="H105" t="str">
-        <v>Ariana Grande</v>
+        <v>Minelli</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/ariana-grande/412778295</v>
+        <v/>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/hate-that-i-made-you-love-me/1895420989</v>
+        <v/>
       </c>
       <c r="L105" t="str">
-        <v>hate that i made you love me - Ariana Grande</v>
+        <v>Minelli - Sun Goes Down | Official Visualizer - Minelli</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Come Inside</v>
+        <v>Maggie Rose - Gentle Man (Official Studio Video)</v>
       </c>
       <c r="B106" t="str">
-        <v/>
+        <v>12d ago</v>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/come-inside/1887403093</v>
+        <v>https://www.youtube.com/watch?v=aWNK-vWrN60</v>
       </c>
       <c r="D106" t="str">
         <v>2026-06-03</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>The Boys of Dungeon Lane</v>
+        <v>12d ago</v>
       </c>
       <c r="G106" t="str">
-        <v>3:13</v>
+        <v/>
       </c>
       <c r="H106" t="str">
-        <v>Paul McCartney</v>
+        <v>Maggie Rose</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/paul-mccartney/12224</v>
+        <v/>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/come-inside/1887402919</v>
+        <v/>
       </c>
       <c r="L106" t="str">
-        <v>Come Inside - Paul McCartney</v>
+        <v>Maggie Rose - Gentle Man (Official Studio Video) - Maggie Rose</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Game Time</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer]</v>
       </c>
       <c r="B107" t="str">
-        <v/>
+        <v>12d ago</v>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/game-time/6771157200</v>
+        <v>https://www.youtube.com/watch?v=mN5AZBrVq9I</v>
       </c>
       <c r="D107" t="str">
         <v>2026-06-03</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>Game Time (FIFA World Cup 2026™) - Single</v>
+        <v>12d ago</v>
       </c>
       <c r="G107" t="str">
-        <v>3:26</v>
+        <v/>
       </c>
       <c r="H107" t="str">
-        <v>Future</v>
+        <v>David Guetta</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/future/128050210</v>
+        <v/>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/game-time/6771157186</v>
+        <v/>
       </c>
       <c r="L107" t="str">
-        <v>Game Time - Future</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer] - David Guetta</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Motion Party (Remix)</v>
+        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video)</v>
       </c>
       <c r="B108" t="str">
-        <v/>
+        <v>12d ago</v>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/motion-party-remix/6773413965</v>
+        <v>https://www.youtube.com/watch?v=0PTufEGRAVQ</v>
       </c>
       <c r="D108" t="str">
         <v>2026-06-03</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Motion Party (Remix) - Single</v>
+        <v>12d ago</v>
       </c>
       <c r="G108" t="str">
-        <v>2:36</v>
+        <v/>
       </c>
       <c r="H108" t="str">
-        <v>Bossman Dlow</v>
+        <v>Chris Young and Shaylen</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/bossman-dlow/1474308236</v>
+        <v/>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/motion-party-remix/6773413953</v>
+        <v/>
       </c>
       <c r="L108" t="str">
-        <v>Motion Party (Remix) - Bossman Dlow</v>
+        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video) - Chris Young and Shaylen</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Aquel diciembre</v>
+        <v>Lauv - Pretty Little Things</v>
       </c>
       <c r="B109" t="str">
-        <v/>
+        <v>12d ago</v>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/aquel-diciembre/6769580010</v>
+        <v>https://www.youtube.com/watch?v=_JBfanFvHnA</v>
       </c>
       <c r="D109" t="str">
         <v>2026-06-03</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>Do Not Disturb: Late Checkout</v>
+        <v>12d ago</v>
       </c>
       <c r="G109" t="str">
-        <v>3:22</v>
+        <v/>
       </c>
       <c r="H109" t="str">
-        <v>Young Miko</v>
+        <v>Lauv</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/young-miko/1576521417</v>
+        <v/>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/aquel-diciembre/6769579992</v>
+        <v/>
       </c>
       <c r="L109" t="str">
-        <v>Aquel diciembre - Young Miko</v>
+        <v>Lauv - Pretty Little Things - Lauv</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Handle</v>
+        <v>Icona Pop - Butterfly Feelings (Official Audio)</v>
       </c>
       <c r="B110" t="str">
-        <v/>
+        <v>12d ago</v>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/handle/6771922623</v>
+        <v>https://www.youtube.com/watch?v=bXA_Q75QZTs</v>
       </c>
       <c r="D110" t="str">
         <v>2026-06-03</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Blue Island</v>
+        <v>12d ago</v>
       </c>
       <c r="G110" t="str">
-        <v>3:06</v>
+        <v/>
       </c>
       <c r="H110" t="str">
-        <v>Ravyn Lenae</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/ravyn-lenae/1044417443</v>
+        <v/>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/handle/6771922622</v>
+        <v/>
       </c>
       <c r="L110" t="str">
-        <v>Handle - Ravyn Lenae</v>
+        <v>Icona Pop - Butterfly Feelings (Official Audio) - Icona Pop</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Every Single Weekend (feat. Jamie xx)</v>
+        <v>Will Swinton - Only One (Official Video)</v>
       </c>
       <c r="B111" t="str">
-        <v/>
+        <v>12d ago</v>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/every-single-weekend-feat-jamie-xx/6770445933</v>
+        <v>https://www.youtube.com/watch?v=A0KzP-zm9hA</v>
       </c>
       <c r="D111" t="str">
         <v>2026-06-03</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Every Single Weekend (feat. Jamie xx) - Single</v>
+        <v>12d ago</v>
       </c>
       <c r="G111" t="str">
-        <v>2:10</v>
+        <v/>
       </c>
       <c r="H111" t="str">
-        <v>The Avalanches</v>
+        <v>Will Swinton</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/the-avalanches/27524431</v>
+        <v/>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/every-single-weekend-feat-jamie-xx/6770445752</v>
+        <v/>
       </c>
       <c r="L111" t="str">
-        <v>Every Single Weekend (feat. Jamie xx) - The Avalanches</v>
+        <v>Will Swinton - Only One (Official Video) - Will Swinton</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>The Wave</v>
+        <v>Dean Lewis - Escape (Official Video)</v>
       </c>
       <c r="B112" t="str">
-        <v/>
+        <v>12d ago</v>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/the-wave/1886730541</v>
+        <v>https://www.youtube.com/watch?v=BZRaTXCkhcg</v>
       </c>
       <c r="D112" t="str">
         <v>2026-06-03</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Sunshine</v>
+        <v>12d ago</v>
       </c>
       <c r="G112" t="str">
-        <v>3:22</v>
+        <v/>
       </c>
       <c r="H112" t="str">
-        <v>Jungle</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/jungle/825833522</v>
+        <v/>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/the-wave/1886730527</v>
+        <v/>
       </c>
       <c r="L112" t="str">
-        <v>The Wave - Jungle</v>
+        <v>Dean Lewis - Escape (Official Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>STOP</v>
+        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico]</v>
       </c>
       <c r="B113" t="str">
-        <v/>
+        <v>12d ago</v>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/stop/6771161771</v>
+        <v>https://www.youtube.com/watch?v=PNm0hf_zZJY</v>
       </c>
       <c r="D113" t="str">
         <v>2026-06-03</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>are you mad at me? - Single</v>
+        <v>12d ago</v>
       </c>
       <c r="G113" t="str">
-        <v>2:56</v>
+        <v/>
       </c>
       <c r="H113" t="str">
-        <v>Bella Kay</v>
+        <v>Dua Lipa and OficialMana</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
+        <v/>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/stop/6771161760</v>
+        <v/>
       </c>
       <c r="L113" t="str">
-        <v>STOP - Bella Kay</v>
+        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico] - Dua Lipa and OficialMana</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Here (Apple Music Sessions)</v>
+        <v>Niall Horan - End of an Era (Lyric Video)</v>
       </c>
       <c r="B114" t="str">
-        <v/>
+        <v>12d ago</v>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/here-apple-music-sessions/1878235516</v>
+        <v>https://www.youtube.com/watch?v=EUNNmAAe5gQ</v>
       </c>
       <c r="D114" t="str">
         <v>2026-06-03</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Apple Music Sessions</v>
+        <v>12d ago</v>
       </c>
       <c r="G114" t="str">
-        <v>3:08</v>
+        <v/>
       </c>
       <c r="H114" t="str">
-        <v>Mumford &amp; Sons</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/mumford-sons/307699986</v>
+        <v/>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/here-apple-music-sessions/1878235330</v>
+        <v/>
       </c>
       <c r="L114" t="str">
-        <v>Here (Apple Music Sessions) - Mumford &amp; Sons</v>
+        <v>Niall Horan - End of an Era (Lyric Video) - Niall Horan</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Talk On The Hill</v>
+        <v>Olivia Rodrigo - the cure (Official Music Video)</v>
       </c>
       <c r="B115" t="str">
-        <v/>
+        <v>12d ago</v>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/talk-on-the-hill/6769524458</v>
+        <v>https://www.youtube.com/watch?v=B402rKl4bUg</v>
       </c>
       <c r="D115" t="str">
         <v>2026-06-03</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>The Thread</v>
+        <v>12d ago</v>
       </c>
       <c r="G115" t="str">
-        <v>3:27</v>
+        <v/>
       </c>
       <c r="H115" t="str">
-        <v>WILLOW</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/willow/400531893</v>
+        <v/>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/talk-on-the-hill/6769524450</v>
+        <v/>
       </c>
       <c r="L115" t="str">
-        <v>Talk On The Hill - WILLOW</v>
+        <v>Olivia Rodrigo - the cure (Official Music Video) - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>No Fear</v>
+        <v>Ruel - Debbie Don't Cry (Official Music Video)</v>
       </c>
       <c r="B116" t="str">
-        <v/>
+        <v>12d ago</v>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/no-fear/1880484493</v>
+        <v>https://www.youtube.com/watch?v=iz7wuk0GOwI</v>
       </c>
       <c r="D116" t="str">
         <v>2026-06-03</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>For Love of Grace &amp; the Hereafter</v>
+        <v>12d ago</v>
       </c>
       <c r="G116" t="str">
-        <v>3:38</v>
+        <v/>
       </c>
       <c r="H116" t="str">
-        <v>Iceage</v>
+        <v>RUEL</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/iceage/406846711</v>
+        <v/>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/no-fear/1880484160</v>
+        <v/>
       </c>
       <c r="L116" t="str">
-        <v>No Fear - Iceage</v>
+        <v>Ruel - Debbie Don't Cry (Official Music Video) - RUEL</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Hostage</v>
+        <v>TINI - Down (LIVE)</v>
       </c>
       <c r="B117" t="str">
-        <v/>
+        <v>12d ago</v>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/hostage/6774372288</v>
+        <v>https://www.youtube.com/watch?v=ADbFeQUPTrk</v>
       </c>
       <c r="D117" t="str">
         <v>2026-06-03</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Big Mama</v>
+        <v>12d ago</v>
       </c>
       <c r="G117" t="str">
-        <v>3:11</v>
+        <v/>
       </c>
       <c r="H117" t="str">
-        <v>Latto</v>
+        <v>TINI</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/latto/419799506</v>
+        <v/>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/hostage/6774372200</v>
+        <v/>
       </c>
       <c r="L117" t="str">
-        <v>Hostage - Latto</v>
+        <v>TINI - Down (LIVE) - TINI</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Sad Girls</v>
+        <v>Charli xcx - SS26 (Official Video)</v>
       </c>
       <c r="B118" t="str">
-        <v/>
+        <v>12d ago</v>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/sad-girls/6768814374</v>
+        <v>https://www.youtube.com/watch?v=twLhSqabby0</v>
       </c>
       <c r="D118" t="str">
         <v>2026-06-03</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Sad Girls - Single</v>
+        <v>12d ago</v>
       </c>
       <c r="G118" t="str">
-        <v>2:48</v>
+        <v/>
       </c>
       <c r="H118" t="str">
-        <v>Bebe Rexha</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/bebe-rexha/466059563</v>
+        <v/>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/sad-girls/6768814373</v>
+        <v/>
       </c>
       <c r="L118" t="str">
-        <v>Sad Girls - Bebe Rexha</v>
+        <v>Charli xcx - SS26 (Official Video) - Charli xcx</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Salvame Hoy (feat. Gabito Ballesteros)</v>
+        <v>Dua Lipa - Live From Mexico</v>
       </c>
       <c r="B119" t="str">
-        <v/>
+        <v>13d ago</v>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/salvame-hoy-feat-gabito-ballesteros/6765697019</v>
+        <v>https://www.youtube.com/watch?v=vZYVkitGXBU</v>
       </c>
       <c r="D119" t="str">
         <v>2026-06-03</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Salvame Hoy (feat. Gabito Ballesteros) - Single</v>
+        <v>13d ago</v>
       </c>
       <c r="G119" t="str">
-        <v>3:35</v>
+        <v/>
       </c>
       <c r="H119" t="str">
-        <v>Jennifer Lopez</v>
+        <v>Dua Lipa</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/jennifer-lopez/463009</v>
+        <v/>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/salvame-hoy-feat-gabito-ballesteros/1896041010</v>
+        <v/>
       </c>
       <c r="L119" t="str">
-        <v>Salvame Hoy (feat. Gabito Ballesteros) - Jennifer Lopez</v>
+        <v>Dua Lipa - Live From Mexico - Dua Lipa</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Rubio</v>
+        <v>Matilda Mann - 'The Fig Tree' (Official Video)</v>
       </c>
       <c r="B120" t="str">
-        <v/>
+        <v>13d ago</v>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/rubio/6770655339</v>
+        <v>https://www.youtube.com/watch?v=XPyubkkkw44</v>
       </c>
       <c r="D120" t="str">
         <v>2026-06-03</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>La Voz Favorita</v>
+        <v>13d ago</v>
       </c>
       <c r="G120" t="str">
-        <v>4:42</v>
+        <v/>
       </c>
       <c r="H120" t="str">
-        <v>Jay Wheeler</v>
+        <v>Matilda Mann</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/jay-wheeler/164376380</v>
+        <v/>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/rubio/6770654729</v>
+        <v/>
       </c>
       <c r="L120" t="str">
-        <v>Rubio - Jay Wheeler</v>
+        <v>Matilda Mann - 'The Fig Tree' (Official Video) - Matilda Mann</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Pary</v>
+        <v>High Hopes 3000</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/pary/6767367748</v>
+        <v>https://music.apple.com/us/song/high-hopes-3000/6772366438</v>
       </c>
       <c r="D121" t="str">
         <v>2026-06-03</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Con dolor - EP</v>
+        <v>Chuck Timely &amp; The Hourglass</v>
       </c>
       <c r="G121" t="str">
-        <v>2:52</v>
+        <v>4:05</v>
       </c>
       <c r="H121" t="str">
-        <v>Grupo Frontera</v>
+        <v>ROLE MODEL</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
+        <v>https://music.apple.com/us/artist/role-model/199215762</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/pary/6767367501</v>
+        <v>https://music.apple.com/us/album/high-hopes-3000/6772366436</v>
       </c>
       <c r="L121" t="str">
-        <v>Pary - Grupo Frontera</v>
+        <v>High Hopes 3000 - ROLE MODEL</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Think As You Drunk</v>
+        <v>hate that i made you love me</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/think-as-you-drunk/6770725979</v>
+        <v>https://music.apple.com/us/song/hate-that-i-made-you-love-me/6763656876</v>
       </c>
       <c r="D122" t="str">
         <v>2026-06-03</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>That's Just Me</v>
+        <v>petal</v>
       </c>
       <c r="G122" t="str">
-        <v>3:48</v>
+        <v>3:17</v>
       </c>
       <c r="H122" t="str">
-        <v>Riley Green</v>
+        <v>Ariana Grande</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/riley-green/662432971</v>
+        <v>https://music.apple.com/us/artist/ariana-grande/412778295</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/think-as-you-drunk/6770725355</v>
+        <v>https://music.apple.com/us/album/hate-that-i-made-you-love-me/1895420989</v>
       </c>
       <c r="L122" t="str">
-        <v>Think As You Drunk - Riley Green</v>
+        <v>hate that i made you love me - Ariana Grande</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Play Your Games</v>
+        <v>Come Inside</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/play-your-games/6772932837</v>
+        <v>https://music.apple.com/us/song/come-inside/1887403093</v>
       </c>
       <c r="D123" t="str">
         <v>2026-06-03</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Play Your Games - Single</v>
+        <v>The Boys of Dungeon Lane</v>
       </c>
       <c r="G123" t="str">
-        <v>3:15</v>
+        <v>3:13</v>
       </c>
       <c r="H123" t="str">
-        <v>Greta Van Fleet</v>
+        <v>Paul McCartney</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/greta-van-fleet/646178956</v>
+        <v>https://music.apple.com/us/artist/paul-mccartney/12224</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/play-your-games/6772932835</v>
+        <v>https://music.apple.com/us/album/come-inside/1887402919</v>
       </c>
       <c r="L123" t="str">
-        <v>Play Your Games - Greta Van Fleet</v>
+        <v>Come Inside - Paul McCartney</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello)</v>
+        <v>Game Time</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/adjourn-it-feat-serj-tankian-roman-morello/6769340216</v>
+        <v>https://music.apple.com/us/song/game-time/6771157200</v>
       </c>
       <c r="D124" t="str">
         <v>2026-06-03</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello) - Single</v>
+        <v>Game Time (FIFA World Cup 2026™) - Single</v>
       </c>
       <c r="G124" t="str">
-        <v>2:47</v>
+        <v>3:26</v>
       </c>
       <c r="H124" t="str">
-        <v>Tom Morello</v>
+        <v>Future</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/tom-morello/466357</v>
+        <v>https://music.apple.com/us/artist/future/128050210</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/adjourn-it-feat-serj-tankian-roman-morello/6769340214</v>
+        <v>https://music.apple.com/us/album/game-time/6771157186</v>
       </c>
       <c r="L124" t="str">
-        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello) - Tom Morello</v>
+        <v>Game Time - Future</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Essex_Honey.mp3</v>
+        <v>Motion Party (Remix)</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/essex-honey-mp3/6771169447</v>
+        <v>https://music.apple.com/us/song/motion-party-remix/6773413965</v>
       </c>
       <c r="D125" t="str">
         <v>2026-06-03</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Essex_Honey.mp3 - Single</v>
+        <v>Motion Party (Remix) - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>4:49</v>
+        <v>2:36</v>
       </c>
       <c r="H125" t="str">
-        <v>Blood Orange</v>
+        <v>Bossman Dlow</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/blood-orange/440698865</v>
+        <v>https://music.apple.com/us/artist/bossman-dlow/1474308236</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/essex-honey-mp3/6771169151</v>
+        <v>https://music.apple.com/us/album/motion-party-remix/6773413953</v>
       </c>
       <c r="L125" t="str">
-        <v>Essex_Honey.mp3 - Blood Orange</v>
+        <v>Motion Party (Remix) - Bossman Dlow</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>minute</v>
+        <v>Aquel diciembre</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/minute/1875303122</v>
+        <v>https://music.apple.com/us/song/aquel-diciembre/6769580010</v>
       </c>
       <c r="D126" t="str">
         <v>2026-06-03</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>ghosted - EP</v>
+        <v>Do Not Disturb: Late Checkout</v>
       </c>
       <c r="G126" t="str">
-        <v>2:59</v>
+        <v>3:22</v>
       </c>
       <c r="H126" t="str">
-        <v>Saint Harison</v>
+        <v>Young Miko</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/saint-harison/1639595302</v>
+        <v>https://music.apple.com/us/artist/young-miko/1576521417</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/minute/1875302904</v>
+        <v>https://music.apple.com/us/album/aquel-diciembre/6769579992</v>
       </c>
       <c r="L126" t="str">
-        <v>minute - Saint Harison</v>
+        <v>Aquel diciembre - Young Miko</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>THE LIVING</v>
+        <v>Handle</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/the-living/1894092345</v>
+        <v>https://music.apple.com/us/song/handle/6771922623</v>
       </c>
       <c r="D127" t="str">
         <v>2026-06-03</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>COSMIC OPERA ACT II</v>
+        <v>Blue Island</v>
       </c>
       <c r="G127" t="str">
-        <v>2:48</v>
+        <v>3:06</v>
       </c>
       <c r="H127" t="str">
-        <v>Labrinth</v>
+        <v>Ravyn Lenae</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
+        <v>https://music.apple.com/us/artist/ravyn-lenae/1044417443</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/the-living/1894092339</v>
+        <v>https://music.apple.com/us/album/handle/6771922622</v>
       </c>
       <c r="L127" t="str">
-        <v>THE LIVING - Labrinth</v>
+        <v>Handle - Ravyn Lenae</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Thug</v>
+        <v>snake the drain</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/thug/6769289966</v>
+        <v>https://music.apple.com/us/song/snake-the-drain/6771506655</v>
       </c>
       <c r="D128" t="str">
         <v>2026-06-03</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Thug - Single</v>
+        <v>this time it’s different / snake the drain - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>2:25</v>
+        <v>3:08</v>
       </c>
       <c r="H128" t="str">
-        <v>G Herbo</v>
+        <v>Devon Again</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/g-herbo/1036753321</v>
+        <v>https://music.apple.com/us/artist/devon-again/1574318250</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/thug/6769289953</v>
+        <v>https://music.apple.com/us/album/snake-the-drain/6771506650</v>
       </c>
       <c r="L128" t="str">
-        <v>Thug - G Herbo</v>
+        <v>snake the drain - Devon Again</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Clap</v>
+        <v>The Wave</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/clap/6769903711</v>
+        <v>https://music.apple.com/us/song/the-wave/1886730541</v>
       </c>
       <c r="D129" t="str">
         <v>2026-06-03</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Clap - Single</v>
+        <v>Sunshine</v>
       </c>
       <c r="G129" t="str">
-        <v>2:04</v>
+        <v>3:22</v>
       </c>
       <c r="H129" t="str">
-        <v>Polo G</v>
+        <v>Jungle</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/polo-g/1159371412</v>
+        <v>https://music.apple.com/us/artist/jungle/825833522</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/clap/6769903710</v>
+        <v>https://music.apple.com/us/album/the-wave/1886730527</v>
       </c>
       <c r="L129" t="str">
-        <v>Clap - Polo G</v>
+        <v>The Wave - Jungle</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>GANG BIZNESS</v>
+        <v>Every Single Weekend (feat. Jamie xx)</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/gang-bizness/6772383809</v>
+        <v>https://music.apple.com/us/song/every-single-weekend-feat-jamie-xx/6770445933</v>
       </c>
       <c r="D130" t="str">
         <v>2026-06-03</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>THE GENTLEMEN'S CLUB</v>
+        <v>Every Single Weekend (feat. Jamie xx) - Single</v>
       </c>
       <c r="G130" t="str">
-        <v>2:47</v>
+        <v>2:10</v>
       </c>
       <c r="H130" t="str">
-        <v>YG</v>
+        <v>The Avalanches</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/yg/189792075</v>
+        <v>https://music.apple.com/us/artist/the-avalanches/27524431</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/gang-bizness/6772383681</v>
+        <v>https://music.apple.com/us/album/every-single-weekend-feat-jamie-xx/6770445752</v>
       </c>
       <c r="L130" t="str">
-        <v>GANG BIZNESS - YG</v>
+        <v>Every Single Weekend (feat. Jamie xx) - The Avalanches</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>UR HEARTBEAT (WHO DO U THINK ABOUT AT 2AM?)</v>
+        <v>STOP</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/ur-heartbeat-who-do-u-think-about-at-2am/6765534140</v>
+        <v>https://music.apple.com/us/song/stop/6771161771</v>
       </c>
       <c r="D131" t="str">
         <v>2026-06-03</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>A LITTLE VENGEANCE</v>
+        <v>are you mad at me? - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>2:50</v>
+        <v>2:56</v>
       </c>
       <c r="H131" t="str">
-        <v>Jessie Reyez</v>
+        <v>Bella Kay</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
+        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/ur-heartbeat-who-do-u-think-about-at-2am/1895983502</v>
+        <v>https://music.apple.com/us/album/stop/6771161760</v>
       </c>
       <c r="L131" t="str">
-        <v>UR HEARTBEAT (WHO DO U THINK ABOUT AT 2AM?) - Jessie Reyez</v>
+        <v>STOP - Bella Kay</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Joshua Tree</v>
+        <v>Here (Apple Music Sessions)</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/joshua-tree/6771859148</v>
+        <v>https://music.apple.com/us/song/here-apple-music-sessions/1878235516</v>
       </c>
       <c r="D132" t="str">
         <v>2026-06-03</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Euphoria: Season 3 (HBO Original Series Soundtrack)</v>
+        <v>Apple Music Sessions</v>
       </c>
       <c r="G132" t="str">
-        <v>2:50</v>
+        <v>3:08</v>
       </c>
       <c r="H132" t="str">
-        <v>Hans Zimmer</v>
+        <v>Mumford &amp; Sons</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/hans-zimmer/454295032</v>
+        <v>https://music.apple.com/us/artist/mumford-sons/307699986</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/joshua-tree/6771858464</v>
+        <v>https://music.apple.com/us/album/here-apple-music-sessions/1878235330</v>
       </c>
       <c r="L132" t="str">
-        <v>Joshua Tree - Hans Zimmer</v>
+        <v>Here (Apple Music Sessions) - Mumford &amp; Sons</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Mi Gran Amor</v>
+        <v>Talk On The Hill</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/mi-gran-amor/6773365775</v>
+        <v>https://music.apple.com/us/song/talk-on-the-hill/6769524458</v>
       </c>
       <c r="D133" t="str">
         <v>2026-06-03</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Mi Gran Amor - Single</v>
+        <v>The Thread</v>
       </c>
       <c r="G133" t="str">
-        <v>3:37</v>
+        <v>3:27</v>
       </c>
       <c r="H133" t="str">
-        <v>Santana</v>
+        <v>WILLOW</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/santana/217174</v>
+        <v>https://music.apple.com/us/artist/willow/400531893</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/mi-gran-amor/6773365236</v>
+        <v>https://music.apple.com/us/album/talk-on-the-hill/6769524450</v>
       </c>
       <c r="L133" t="str">
-        <v>Mi Gran Amor - Santana</v>
+        <v>Talk On The Hill - WILLOW</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>london</v>
+        <v>No Fear</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/london/6770745672</v>
+        <v>https://music.apple.com/us/song/no-fear/1880484493</v>
       </c>
       <c r="D134" t="str">
         <v>2026-06-03</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>stardust - EP</v>
+        <v>For Love of Grace &amp; the Hereafter</v>
       </c>
       <c r="G134" t="str">
-        <v>3:23</v>
+        <v>3:38</v>
       </c>
       <c r="H134" t="str">
-        <v>Freya Skye</v>
+        <v>Iceage</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/freya-skye/1541643053</v>
+        <v>https://music.apple.com/us/artist/iceage/406846711</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/london/6770745662</v>
+        <v>https://music.apple.com/us/album/no-fear/1880484160</v>
       </c>
       <c r="L134" t="str">
-        <v>london - Freya Skye</v>
+        <v>No Fear - Iceage</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Caution</v>
+        <v>Hostage</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/caution/6768487482</v>
+        <v>https://music.apple.com/us/song/hostage/6774372288</v>
       </c>
       <c r="D135" t="str">
         <v>2026-06-03</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>K-POPS! (Music from and inspired by K-POPS! Motion Picture)</v>
+        <v>Big Mama</v>
       </c>
       <c r="G135" t="str">
-        <v>2:43</v>
+        <v>3:11</v>
       </c>
       <c r="H135" t="str">
-        <v>NMIXX</v>
+        <v>Latto</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/nmixx/1600411676</v>
+        <v>https://music.apple.com/us/artist/latto/419799506</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/caution/6768487478</v>
+        <v>https://music.apple.com/us/album/hostage/6774372200</v>
       </c>
       <c r="L135" t="str">
-        <v>Caution - NMIXX</v>
+        <v>Hostage - Latto</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>LEMONADE (feat. Becky G)</v>
+        <v>Sad Girls</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/lemonade-feat-becky-g/1893742425</v>
+        <v>https://music.apple.com/us/song/sad-girls/6768814374</v>
       </c>
       <c r="D136" t="str">
         <v>2026-06-03</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>LEMONADE - The 2nd Album</v>
+        <v>Sad Girls - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>3:07</v>
+        <v>2:48</v>
       </c>
       <c r="H136" t="str">
-        <v>aespa</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
+        <v>https://music.apple.com/us/artist/bebe-rexha/466059563</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/lemonade-feat-becky-g/1893742002</v>
+        <v>https://music.apple.com/us/album/sad-girls/6768814373</v>
       </c>
       <c r="L136" t="str">
-        <v>LEMONADE (feat. Becky G) - aespa</v>
+        <v>Sad Girls - Bebe Rexha</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Take Me Back (Leave Me There)</v>
+        <v>Salvame Hoy (feat. Gabito Ballesteros)</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/take-me-back-leave-me-there/1892466278</v>
+        <v>https://music.apple.com/us/song/salvame-hoy-feat-gabito-ballesteros/6765697019</v>
       </c>
       <c r="D137" t="str">
         <v>2026-06-03</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Banks Of The Trinity</v>
+        <v>Salvame Hoy (feat. Gabito Ballesteros) - Single</v>
       </c>
       <c r="G137" t="str">
-        <v>2:58</v>
+        <v>3:35</v>
       </c>
       <c r="H137" t="str">
-        <v>Cody Johnson</v>
+        <v>Jennifer Lopez</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
+        <v>https://music.apple.com/us/artist/jennifer-lopez/463009</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/take-me-back-leave-me-there/1892465981</v>
+        <v>https://music.apple.com/us/album/salvame-hoy-feat-gabito-ballesteros/1896041010</v>
       </c>
       <c r="L137" t="str">
-        <v>Take Me Back (Leave Me There) - Cody Johnson</v>
+        <v>Salvame Hoy (feat. Gabito Ballesteros) - Jennifer Lopez</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Cheap Thrills</v>
+        <v>Rubio</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/cheap-thrills/6771156732</v>
+        <v>https://music.apple.com/us/song/rubio/6770655339</v>
       </c>
       <c r="D138" t="str">
         <v>2026-06-03</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Cheap Thrills - Single</v>
+        <v>La Voz Favorita</v>
       </c>
       <c r="G138" t="str">
-        <v>2:42</v>
+        <v>4:42</v>
       </c>
       <c r="H138" t="str">
-        <v>Gavin Adcock</v>
+        <v>Jay Wheeler</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/gavin-adcock/1580645019</v>
+        <v>https://music.apple.com/us/artist/jay-wheeler/164376380</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/cheap-thrills/6771156723</v>
+        <v>https://music.apple.com/us/album/rubio/6770654729</v>
       </c>
       <c r="L138" t="str">
-        <v>Cheap Thrills - Gavin Adcock</v>
+        <v>Rubio - Jay Wheeler</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>ME VALE V</v>
+        <v>Pary</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/me-vale-v/6769567844</v>
+        <v>https://music.apple.com/us/song/pary/6767367748</v>
       </c>
       <c r="D139" t="str">
         <v>2026-06-03</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>ACOMODO</v>
+        <v>Con dolor - EP</v>
       </c>
       <c r="G139" t="str">
-        <v>3:06</v>
+        <v>2:52</v>
       </c>
       <c r="H139" t="str">
-        <v>Tito Double P</v>
+        <v>Grupo Frontera</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/tito-double-p/1690905306</v>
+        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/me-vale-v/6769567568</v>
+        <v>https://music.apple.com/us/album/pary/6767367501</v>
       </c>
       <c r="L139" t="str">
-        <v>ME VALE V - Tito Double P</v>
+        <v>Pary - Grupo Frontera</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Bug In The Cake</v>
+        <v>Think As You Drunk</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/bug-in-the-cake/1880470542</v>
+        <v>https://music.apple.com/us/song/think-as-you-drunk/6770725979</v>
       </c>
       <c r="D140" t="str">
         <v>2026-06-03</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Be Sweet To Me</v>
+        <v>That's Just Me</v>
       </c>
       <c r="G140" t="str">
-        <v>2:48</v>
+        <v>3:48</v>
       </c>
       <c r="H140" t="str">
-        <v>Violet Grohl</v>
+        <v>Riley Green</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
+        <v>https://music.apple.com/us/artist/riley-green/662432971</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/bug-in-the-cake/1880470537</v>
+        <v>https://music.apple.com/us/album/think-as-you-drunk/6770725355</v>
       </c>
       <c r="L140" t="str">
-        <v>Bug In The Cake - Violet Grohl</v>
+        <v>Think As You Drunk - Riley Green</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Coil</v>
+        <v>Play Your Games</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/coil/6766858354</v>
+        <v>https://music.apple.com/us/song/play-your-games/6772932837</v>
       </c>
       <c r="D141" t="str">
         <v>2026-06-03</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Rumspringa</v>
+        <v>Play Your Games - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>3:54</v>
+        <v>3:15</v>
       </c>
       <c r="H141" t="str">
-        <v>ear</v>
+        <v>Greta Van Fleet</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/ear/1829661500</v>
+        <v>https://music.apple.com/us/artist/greta-van-fleet/646178956</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/coil/6766858352</v>
+        <v>https://music.apple.com/us/album/play-your-games/6772932835</v>
       </c>
       <c r="L141" t="str">
-        <v>Coil - ear</v>
+        <v>Play Your Games - Greta Van Fleet</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Smugglers &amp; Scholars (feat. Killer Mike)</v>
+        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello)</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/smugglers-scholars-feat-killer-mike/6769424017</v>
+        <v>https://music.apple.com/us/song/adjourn-it-feat-serj-tankian-roman-morello/6769340216</v>
       </c>
       <c r="D142" t="str">
         <v>2026-06-03</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Smugglers &amp; Scholars (feat. Killer Mike) - Single</v>
+        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello) - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>3:30</v>
+        <v>2:47</v>
       </c>
       <c r="H142" t="str">
-        <v>Kneecap</v>
+        <v>Tom Morello</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
+        <v>https://music.apple.com/us/artist/tom-morello/466357</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/smugglers-scholars-feat-killer-mike/6769423676</v>
+        <v>https://music.apple.com/us/album/adjourn-it-feat-serj-tankian-roman-morello/6769340214</v>
       </c>
       <c r="L142" t="str">
-        <v>Smugglers &amp; Scholars (feat. Killer Mike) - Kneecap</v>
+        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello) - Tom Morello</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Out of my Head</v>
+        <v>Essex_Honey.mp3</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/out-of-my-head/6767725166</v>
+        <v>https://music.apple.com/us/song/essex-honey-mp3/6771169447</v>
       </c>
       <c r="D143" t="str">
         <v>2026-06-03</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>I Forgot / Out of my Head - Single</v>
+        <v>Essex_Honey.mp3 - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>3:04</v>
+        <v>4:49</v>
       </c>
       <c r="H143" t="str">
-        <v>Cara Delevingne</v>
+        <v>Blood Orange</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/cara-delevingne/1204798982</v>
+        <v>https://music.apple.com/us/artist/blood-orange/440698865</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/out-of-my-head/6767725156</v>
+        <v>https://music.apple.com/us/album/essex-honey-mp3/6771169151</v>
       </c>
       <c r="L143" t="str">
-        <v>Out of my Head - Cara Delevingne</v>
+        <v>Essex_Honey.mp3 - Blood Orange</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Passenger Princess</v>
+        <v>minute</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/passenger-princess/6771012228</v>
+        <v>https://music.apple.com/us/song/minute/1875303122</v>
       </c>
       <c r="D144" t="str">
         <v>2026-06-03</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Passenger Princess - Single</v>
+        <v>ghosted - EP</v>
       </c>
       <c r="G144" t="str">
-        <v>3:18</v>
+        <v>2:59</v>
       </c>
       <c r="H144" t="str">
-        <v>Perrie</v>
+        <v>Saint Harison</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/perrie/1729865272</v>
+        <v>https://music.apple.com/us/artist/saint-harison/1639595302</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/passenger-princess/6771012223</v>
+        <v>https://music.apple.com/us/album/minute/1875302904</v>
       </c>
       <c r="L144" t="str">
-        <v>Passenger Princess - Perrie</v>
+        <v>minute - Saint Harison</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Man of the House</v>
+        <v>THE LIVING</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/man-of-the-house/1893733057</v>
+        <v>https://music.apple.com/us/song/the-living/1894092345</v>
       </c>
       <c r="D145" t="str">
         <v>2026-06-03</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>SE9</v>
+        <v>COSMIC OPERA ACT II</v>
       </c>
       <c r="G145" t="str">
-        <v>2:35</v>
+        <v>2:48</v>
       </c>
       <c r="H145" t="str">
-        <v>Skye Newman</v>
+        <v>Labrinth</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/skye-newman/1799174381</v>
+        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/man-of-the-house/1893733056</v>
+        <v>https://music.apple.com/us/album/the-living/1894092339</v>
       </c>
       <c r="L145" t="str">
-        <v>Man of the House - Skye Newman</v>
+        <v>THE LIVING - Labrinth</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Beautiful Freeks</v>
+        <v>Thug</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/beautiful-freeks/6764602396</v>
+        <v>https://music.apple.com/us/song/thug/6769289966</v>
       </c>
       <c r="D146" t="str">
         <v>2026-06-03</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Beautiful Freeks - Single</v>
+        <v>Thug - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>2:37</v>
+        <v>2:25</v>
       </c>
       <c r="H146" t="str">
-        <v>MEEK</v>
+        <v>G Herbo</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/meek/1784432868</v>
+        <v>https://music.apple.com/us/artist/g-herbo/1036753321</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/beautiful-freeks/6764602393</v>
+        <v>https://music.apple.com/us/album/thug/6769289953</v>
       </c>
       <c r="L146" t="str">
-        <v>Beautiful Freeks - MEEK</v>
+        <v>Thug - G Herbo</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Slave to the Rithm (feat. Bring Me The Horizon) [I Hate Models Never Alone Remix]</v>
+        <v>Clap</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/slave-to-the-rithm-feat-bring-me-the-horizon-i/6771972616</v>
+        <v>https://music.apple.com/us/song/clap/6769903711</v>
       </c>
       <c r="D147" t="str">
         <v>2026-06-03</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Slave to the Rithm (I Hate Models Never Alone Remix) [feat. Bring Me The Horizon] - Single</v>
+        <v>Clap - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>4:34</v>
+        <v>2:04</v>
       </c>
       <c r="H147" t="str">
-        <v>ILLENIUM</v>
+        <v>Polo G</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/illenium/645420096</v>
+        <v>https://music.apple.com/us/artist/polo-g/1159371412</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/slave-to-the-rithm-feat-bring-me-the-horizon-i/6771972613</v>
+        <v>https://music.apple.com/us/album/clap/6769903710</v>
       </c>
       <c r="L147" t="str">
-        <v>Slave to the Rithm (feat. Bring Me The Horizon) [I Hate Models Never Alone Remix] - ILLENIUM</v>
+        <v>Clap - Polo G</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Beg For Me (JADE Remix)</v>
+        <v>GANG BIZNESS</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/beg-for-me-jade-remix/6771474203</v>
+        <v>https://music.apple.com/us/song/gang-bizness/6772383809</v>
       </c>
       <c r="D148" t="str">
         <v>2026-06-03</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Beg For Me (Remix) - Single</v>
+        <v>THE GENTLEMEN'S CLUB</v>
       </c>
       <c r="G148" t="str">
-        <v>2:50</v>
+        <v>2:47</v>
       </c>
       <c r="H148" t="str">
-        <v>Lily Allen</v>
+        <v>YG</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/lily-allen/157063999</v>
+        <v>https://music.apple.com/us/artist/yg/189792075</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/beg-for-me-jade-remix/6771474201</v>
+        <v>https://music.apple.com/us/album/gang-bizness/6772383681</v>
       </c>
       <c r="L148" t="str">
-        <v>Beg For Me (JADE Remix) - Lily Allen</v>
+        <v>GANG BIZNESS - YG</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>ABOVE IT</v>
+        <v>UR HEARTBEAT (WHO DO U THINK ABOUT AT 2AM?)</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/above-it/6766248703</v>
+        <v>https://music.apple.com/us/song/ur-heartbeat-who-do-u-think-about-at-2am/6765534140</v>
       </c>
       <c r="D149" t="str">
         <v>2026-06-03</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>GET THE TABLES - Single</v>
+        <v>A LITTLE VENGEANCE</v>
       </c>
       <c r="G149" t="str">
-        <v>1:45</v>
+        <v>2:50</v>
       </c>
       <c r="H149" t="str">
-        <v>Andy Mineo</v>
+        <v>Jessie Reyez</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/andy-mineo/257538441</v>
+        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/above-it/6766248699</v>
+        <v>https://music.apple.com/us/album/ur-heartbeat-who-do-u-think-about-at-2am/1895983502</v>
       </c>
       <c r="L149" t="str">
-        <v>ABOVE IT - Andy Mineo</v>
+        <v>UR HEARTBEAT (WHO DO U THINK ABOUT AT 2AM?) - Jessie Reyez</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>THE JESUS GENERATION</v>
+        <v>Joshua Tree</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/the-jesus-generation/6773948895</v>
+        <v>https://music.apple.com/us/song/joshua-tree/6771859148</v>
       </c>
       <c r="D150" t="str">
         <v>2026-06-03</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>THE JESUS GENERATION - Single</v>
+        <v>Euphoria: Season 3 (HBO Original Series Soundtrack)</v>
       </c>
       <c r="G150" t="str">
-        <v>4:15</v>
+        <v>2:50</v>
       </c>
       <c r="H150" t="str">
-        <v>Forrest Frank</v>
+        <v>Hans Zimmer</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/forrest-frank/1436657314</v>
+        <v>https://music.apple.com/us/artist/hans-zimmer/454295032</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/the-jesus-generation/6773948742</v>
+        <v>https://music.apple.com/us/album/joshua-tree/6771858464</v>
       </c>
       <c r="L150" t="str">
-        <v>THE JESUS GENERATION - Forrest Frank</v>
+        <v>Joshua Tree - Hans Zimmer</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Is It Over Now?</v>
+        <v>Mi Gran Amor</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/is-it-over-now/6767564750</v>
+        <v>https://music.apple.com/us/song/mi-gran-amor/6773365775</v>
       </c>
       <c r="D151" t="str">
         <v>2026-06-03</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Is It Over Now? - Single</v>
+        <v>Mi Gran Amor - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>3:39</v>
+        <v>3:37</v>
       </c>
       <c r="H151" t="str">
-        <v>Elderbrook</v>
+        <v>Santana</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/elderbrook/736829657</v>
+        <v>https://music.apple.com/us/artist/santana/217174</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/is-it-over-now/6767564746</v>
+        <v>https://music.apple.com/us/album/mi-gran-amor/6773365236</v>
       </c>
       <c r="L151" t="str">
-        <v>Is It Over Now? - Elderbrook</v>
+        <v>Mi Gran Amor - Santana</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>12 Steps</v>
+        <v>london</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/12-steps/6769559623</v>
+        <v>https://music.apple.com/us/song/london/6770745672</v>
       </c>
       <c r="D152" t="str">
         <v>2026-06-03</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>12 Steps - Single</v>
+        <v>stardust - EP</v>
       </c>
       <c r="G152" t="str">
-        <v>3:11</v>
+        <v>3:23</v>
       </c>
       <c r="H152" t="str">
-        <v>Dexter and The Moonrocks</v>
+        <v>Freya Skye</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/dexter-and-the-moonrocks/1581657500</v>
+        <v>https://music.apple.com/us/artist/freya-skye/1541643053</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/12-steps/6769559618</v>
+        <v>https://music.apple.com/us/album/london/6770745662</v>
       </c>
       <c r="L152" t="str">
-        <v>12 Steps - Dexter and The Moonrocks</v>
+        <v>london - Freya Skye</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Over And Over</v>
+        <v>Caution</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/over-and-over/6771585908</v>
+        <v>https://music.apple.com/us/song/caution/6768487482</v>
       </c>
       <c r="D153" t="str">
         <v>2026-06-03</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>It's A Dying Art</v>
+        <v>K-POPS! (Music from and inspired by K-POPS! Motion Picture)</v>
       </c>
       <c r="G153" t="str">
-        <v>4:38</v>
+        <v>2:43</v>
       </c>
       <c r="H153" t="str">
-        <v>Little Big Town</v>
+        <v>NMIXX</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/little-big-town/513770</v>
+        <v>https://music.apple.com/us/artist/nmixx/1600411676</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/over-and-over/6771585889</v>
+        <v>https://music.apple.com/us/album/caution/6768487478</v>
       </c>
       <c r="L153" t="str">
-        <v>Over And Over - Little Big Town</v>
+        <v>Caution - NMIXX</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>AMAPOLA</v>
+        <v>LEMONADE (feat. Becky G)</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/amapola/6769560428</v>
+        <v>https://music.apple.com/us/song/lemonade-feat-becky-g/1893742425</v>
       </c>
       <c r="D154" t="str">
         <v>2026-06-03</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Ricky y Mau</v>
+        <v>LEMONADE - The 2nd Album</v>
       </c>
       <c r="G154" t="str">
-        <v>2:22</v>
+        <v>3:07</v>
       </c>
       <c r="H154" t="str">
-        <v>Mau y Ricky</v>
+        <v>aespa</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/mau-y-ricky/1096068683</v>
+        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/amapola/6769559985</v>
+        <v>https://music.apple.com/us/album/lemonade-feat-becky-g/1893742002</v>
       </c>
       <c r="L154" t="str">
-        <v>AMAPOLA - Mau y Ricky</v>
+        <v>LEMONADE (feat. Becky G) - aespa</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Mad About It</v>
+        <v>Take Me Back (Leave Me There)</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/mad-about-it/6767425272</v>
+        <v>https://music.apple.com/us/song/take-me-back-leave-me-there/1892466278</v>
       </c>
       <c r="D155" t="str">
         <v>2026-06-03</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Mad About It - Single</v>
+        <v>Banks Of The Trinity</v>
       </c>
       <c r="G155" t="str">
-        <v>2:37</v>
+        <v>2:58</v>
       </c>
       <c r="H155" t="str">
-        <v>Dasha</v>
+        <v>Cody Johnson</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/dasha/1462663731</v>
+        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/mad-about-it/6767425271</v>
+        <v>https://music.apple.com/us/album/take-me-back-leave-me-there/1892465981</v>
       </c>
       <c r="L155" t="str">
-        <v>Mad About It - Dasha</v>
+        <v>Take Me Back (Leave Me There) - Cody Johnson</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Love’s a Gun</v>
+        <v>Cheap Thrills</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/loves-a-gun/6771898253</v>
+        <v>https://music.apple.com/us/song/cheap-thrills/6771156732</v>
       </c>
       <c r="D156" t="str">
         <v>2026-06-03</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Love’s a Gun - Single</v>
+        <v>Cheap Thrills - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>2:59</v>
+        <v>2:42</v>
       </c>
       <c r="H156" t="str">
-        <v>Daniel Seavey</v>
+        <v>Gavin Adcock</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/daniel-seavey/1646124302</v>
+        <v>https://music.apple.com/us/artist/gavin-adcock/1580645019</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/loves-a-gun/6771897951</v>
+        <v>https://music.apple.com/us/album/cheap-thrills/6771156723</v>
       </c>
       <c r="L156" t="str">
-        <v>Love’s a Gun - Daniel Seavey</v>
+        <v>Cheap Thrills - Gavin Adcock</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Long Story Short</v>
+        <v>ME VALE V</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/long-story-short/6770700866</v>
+        <v>https://music.apple.com/us/song/me-vale-v/6769567844</v>
       </c>
       <c r="D157" t="str">
         <v>2026-06-03</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Long Story Short - Single</v>
+        <v>ACOMODO</v>
       </c>
       <c r="G157" t="str">
-        <v>2:48</v>
+        <v>3:06</v>
       </c>
       <c r="H157" t="str">
-        <v>Knox</v>
+        <v>Tito Double P</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/knox/1547519433</v>
+        <v>https://music.apple.com/us/artist/tito-double-p/1690905306</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/long-story-short/6770700853</v>
+        <v>https://music.apple.com/us/album/me-vale-v/6769567568</v>
       </c>
       <c r="L157" t="str">
-        <v>Long Story Short - Knox</v>
+        <v>ME VALE V - Tito Double P</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Dior</v>
+        <v>Bug In The Cake</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/dior/1892136721</v>
+        <v>https://music.apple.com/us/song/bug-in-the-cake/1880470542</v>
       </c>
       <c r="D158" t="str">
         <v>2026-06-03</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>bitknot</v>
+        <v>Be Sweet To Me</v>
       </c>
       <c r="G158" t="str">
-        <v>3:32</v>
+        <v>2:48</v>
       </c>
       <c r="H158" t="str">
-        <v>feeble little horse</v>
+        <v>Violet Grohl</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/feeble-little-horse/1564273208</v>
+        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/dior/1892136714</v>
+        <v>https://music.apple.com/us/album/bug-in-the-cake/1880470537</v>
       </c>
       <c r="L158" t="str">
-        <v>Dior - feeble little horse</v>
+        <v>Bug In The Cake - Violet Grohl</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>blue jeans</v>
+        <v>Coil</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/blue-jeans/6770529591</v>
+        <v>https://music.apple.com/us/song/coil/6766858354</v>
       </c>
       <c r="D159" t="str">
         <v>2026-06-03</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>blue jeans - Single</v>
+        <v>Rumspringa</v>
       </c>
       <c r="G159" t="str">
-        <v>2:37</v>
+        <v>3:54</v>
       </c>
       <c r="H159" t="str">
-        <v>Nightly</v>
+        <v>ear</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/nightly/352310972</v>
+        <v>https://music.apple.com/us/artist/ear/1829661500</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/blue-jeans/6770529589</v>
+        <v>https://music.apple.com/us/album/coil/6766858352</v>
       </c>
       <c r="L159" t="str">
-        <v>blue jeans - Nightly</v>
+        <v>Coil - ear</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Que Gacho</v>
+        <v>Smugglers &amp; Scholars (feat. Killer Mike)</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/que-gacho/6770628420</v>
+        <v>https://music.apple.com/us/song/smugglers-scholars-feat-killer-mike/6769424017</v>
       </c>
       <c r="D160" t="str">
         <v>2026-06-03</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Que Gacho - Single</v>
+        <v>Smugglers &amp; Scholars (feat. Killer Mike) - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>3:13</v>
+        <v>3:30</v>
       </c>
       <c r="H160" t="str">
-        <v>Luis R Conriquez</v>
+        <v>Kneecap</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
+        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/que-gacho/6770628419</v>
+        <v>https://music.apple.com/us/album/smugglers-scholars-feat-killer-mike/6769423676</v>
       </c>
       <c r="L160" t="str">
-        <v>Que Gacho - Luis R Conriquez</v>
+        <v>Smugglers &amp; Scholars (feat. Killer Mike) - Kneecap</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>same God</v>
+        <v>Out of my Head</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/same-god/1878232616</v>
+        <v>https://music.apple.com/us/song/out-of-my-head/6767725166</v>
       </c>
       <c r="D161" t="str">
         <v>2026-06-03</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>I HOPE THIS HELPS</v>
+        <v>I Forgot / Out of my Head - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>3:34</v>
+        <v>3:04</v>
       </c>
       <c r="H161" t="str">
-        <v>Alana Springsteen</v>
+        <v>Cara Delevingne</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/alana-springsteen/1309335606</v>
+        <v>https://music.apple.com/us/artist/cara-delevingne/1204798982</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/same-god/1878232194</v>
+        <v>https://music.apple.com/us/album/out-of-my-head/6767725156</v>
       </c>
       <c r="L161" t="str">
-        <v>same God - Alana Springsteen</v>
+        <v>Out of my Head - Cara Delevingne</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>emotional swaggage</v>
+        <v>Passenger Princess</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/emotional-swaggage/6767397453</v>
+        <v>https://music.apple.com/us/song/passenger-princess/6771012228</v>
       </c>
       <c r="D162" t="str">
         <v>2026-06-03</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>IDCASH</v>
+        <v>Passenger Princess - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>2:12</v>
+        <v>3:18</v>
       </c>
       <c r="H162" t="str">
-        <v>IDK</v>
+        <v>Perrie</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/idk/1578186947</v>
+        <v>https://music.apple.com/us/artist/perrie/1729865272</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/emotional-swaggage/6767397348</v>
+        <v>https://music.apple.com/us/album/passenger-princess/6771012223</v>
       </c>
       <c r="L162" t="str">
-        <v>emotional swaggage - IDK</v>
+        <v>Passenger Princess - Perrie</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Baby Driver</v>
+        <v>Man of the House</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/baby-driver/6769152279</v>
+        <v>https://music.apple.com/us/song/man-of-the-house/1893733057</v>
       </c>
       <c r="D163" t="str">
         <v>2026-06-03</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Baby Driver - Single</v>
+        <v>SE9</v>
       </c>
       <c r="G163" t="str">
-        <v>3:36</v>
+        <v>2:35</v>
       </c>
       <c r="H163" t="str">
-        <v>070 Shake</v>
+        <v>Skye Newman</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/070-shake/1097177293</v>
+        <v>https://music.apple.com/us/artist/skye-newman/1799174381</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/baby-driver/6769152273</v>
+        <v>https://music.apple.com/us/album/man-of-the-house/1893733056</v>
       </c>
       <c r="L163" t="str">
-        <v>Baby Driver - 070 Shake</v>
+        <v>Man of the House - Skye Newman</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>More! More! More!</v>
+        <v>Beautiful Freeks</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/more-more-more/6770600105</v>
+        <v>https://music.apple.com/us/song/beautiful-freeks/6764602396</v>
       </c>
       <c r="D164" t="str">
         <v>2026-06-03</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>REBECCA</v>
+        <v>Beautiful Freeks - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>2:55</v>
+        <v>2:37</v>
       </c>
       <c r="H164" t="str">
-        <v>Becky Hill</v>
+        <v>MEEK</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/becky-hill/533839517</v>
+        <v>https://music.apple.com/us/artist/meek/1784432868</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/more-more-more/6770600098</v>
+        <v>https://music.apple.com/us/album/beautiful-freeks/6764602393</v>
       </c>
       <c r="L164" t="str">
-        <v>More! More! More! - Becky Hill</v>
+        <v>Beautiful Freeks - MEEK</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Young Again</v>
+        <v>Slave to the Rithm (feat. Bring Me The Horizon) [I Hate Models Never Alone Remix]</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/young-again/1877229743</v>
+        <v>https://music.apple.com/us/song/slave-to-the-rithm-feat-bring-me-the-horizon-i/6771972616</v>
       </c>
       <c r="D165" t="str">
         <v>2026-06-03</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>EI8HT</v>
+        <v>Slave to the Rithm (I Hate Models Never Alone Remix) [feat. Bring Me The Horizon] - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>3:36</v>
+        <v>4:34</v>
       </c>
       <c r="H165" t="str">
-        <v>Shinedown</v>
+        <v>ILLENIUM</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/shinedown/1883858</v>
+        <v>https://music.apple.com/us/artist/illenium/645420096</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/young-again/1877229738</v>
+        <v>https://music.apple.com/us/album/slave-to-the-rithm-feat-bring-me-the-horizon-i/6771972613</v>
       </c>
       <c r="L165" t="str">
-        <v>Young Again - Shinedown</v>
+        <v>Slave to the Rithm (feat. Bring Me The Horizon) [I Hate Models Never Alone Remix] - ILLENIUM</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>skinny dip</v>
+        <v>Beg For Me (JADE Remix)</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/skinny-dip/6769856281</v>
+        <v>https://music.apple.com/us/song/beg-for-me-jade-remix/6771474203</v>
       </c>
       <c r="D166" t="str">
         <v>2026-06-03</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>skinny dip - Single</v>
+        <v>Beg For Me (Remix) - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>3:12</v>
+        <v>2:50</v>
       </c>
       <c r="H166" t="str">
-        <v>almost monday</v>
+        <v>Lily Allen</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/almost-monday/1300723925</v>
+        <v>https://music.apple.com/us/artist/lily-allen/157063999</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/skinny-dip/6769855907</v>
+        <v>https://music.apple.com/us/album/beg-for-me-jade-remix/6771474201</v>
       </c>
       <c r="L166" t="str">
-        <v>skinny dip - almost monday</v>
+        <v>Beg For Me (JADE Remix) - Lily Allen</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>girls like girls (from the motion picture)</v>
+        <v>ABOVE IT</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/girls-like-girls-from-the-motion-picture/1893704575</v>
+        <v>https://music.apple.com/us/song/above-it/6766248703</v>
       </c>
       <c r="D167" t="str">
         <v>2026-06-03</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>girls like girls the album</v>
+        <v>GET THE TABLES - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>4:14</v>
+        <v>1:45</v>
       </c>
       <c r="H167" t="str">
-        <v>Hayley Kiyoko</v>
+        <v>Andy Mineo</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/hayley-kiyoko/325569584</v>
+        <v>https://music.apple.com/us/artist/andy-mineo/257538441</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/girls-like-girls-from-the-motion-picture/1893704396</v>
+        <v>https://music.apple.com/us/album/above-it/6766248699</v>
       </c>
       <c r="L167" t="str">
-        <v>girls like girls (from the motion picture) - Hayley Kiyoko</v>
+        <v>ABOVE IT - Andy Mineo</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Better Off</v>
+        <v>THE JESUS GENERATION</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/better-off/6772045367</v>
+        <v>https://music.apple.com/us/song/the-jesus-generation/6773948895</v>
       </c>
       <c r="D168" t="str">
         <v>2026-06-03</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Stages</v>
+        <v>THE JESUS GENERATION - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>3:16</v>
+        <v>4:15</v>
       </c>
       <c r="H168" t="str">
-        <v>Lauren Alaina</v>
+        <v>Forrest Frank</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/lauren-alaina/425028816</v>
+        <v>https://music.apple.com/us/artist/forrest-frank/1436657314</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/better-off/6772044978</v>
+        <v>https://music.apple.com/us/album/the-jesus-generation/6773948742</v>
       </c>
       <c r="L168" t="str">
-        <v>Better Off - Lauren Alaina</v>
+        <v>THE JESUS GENERATION - Forrest Frank</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Everythang Pinka (feat. Teezo Touchdown)</v>
+        <v>Is It Over Now?</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/everythang-pinka-feat-teezo-touchdown/6772026590</v>
+        <v>https://music.apple.com/us/song/is-it-over-now/6767564750</v>
       </c>
       <c r="D169" t="str">
         <v>2026-06-03</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Everythang Pinka (feat. Teezo Touchdown) - Single</v>
+        <v>Is It Over Now? - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>2:48</v>
+        <v>3:39</v>
       </c>
       <c r="H169" t="str">
-        <v>Monaleo</v>
+        <v>Elderbrook</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/monaleo/1495603374</v>
+        <v>https://music.apple.com/us/artist/elderbrook/736829657</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/everythang-pinka-feat-teezo-touchdown/6772026586</v>
+        <v>https://music.apple.com/us/album/is-it-over-now/6767564746</v>
       </c>
       <c r="L169" t="str">
-        <v>Everythang Pinka (feat. Teezo Touchdown) - Monaleo</v>
+        <v>Is It Over Now? - Elderbrook</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Lost in translation...</v>
+        <v>12 Steps</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/lost-in-translation/1870971556</v>
+        <v>https://music.apple.com/us/song/12-steps/6769559623</v>
       </c>
       <c r="D170" t="str">
         <v>2026-06-03</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Dream inside a dream…</v>
+        <v>12 Steps - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>3:30</v>
+        <v>3:11</v>
       </c>
       <c r="H170" t="str">
-        <v>R3HAB</v>
+        <v>Dexter and The Moonrocks</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/r3hab/331900515</v>
+        <v>https://music.apple.com/us/artist/dexter-and-the-moonrocks/1581657500</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/lost-in-translation/1870971550</v>
+        <v>https://music.apple.com/us/album/12-steps/6769559618</v>
       </c>
       <c r="L170" t="str">
-        <v>Lost in translation... - R3HAB</v>
+        <v>12 Steps - Dexter and The Moonrocks</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Call Security</v>
+        <v>Over And Over</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/call-security/6769296603</v>
+        <v>https://music.apple.com/us/song/over-and-over/6771585908</v>
       </c>
       <c r="D171" t="str">
         <v>2026-06-03</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>U, Me &amp; My Ego</v>
+        <v>It's A Dying Art</v>
       </c>
       <c r="G171" t="str">
-        <v>3:22</v>
+        <v>4:38</v>
       </c>
       <c r="H171" t="str">
-        <v>Chxrry</v>
+        <v>Little Big Town</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/chxrry/1520135642</v>
+        <v>https://music.apple.com/us/artist/little-big-town/513770</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/call-security/6769296591</v>
+        <v>https://music.apple.com/us/album/over-and-over/6771585889</v>
       </c>
       <c r="L171" t="str">
-        <v>Call Security - Chxrry</v>
+        <v>Over And Over - Little Big Town</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>chaotic</v>
+        <v>AMAPOLA</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/chaotic/6767629281</v>
+        <v>https://music.apple.com/us/song/amapola/6769560428</v>
       </c>
       <c r="D172" t="str">
         <v>2026-06-03</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>scars to prove it</v>
+        <v>Ricky y Mau</v>
       </c>
       <c r="G172" t="str">
-        <v>3:14</v>
+        <v>2:22</v>
       </c>
       <c r="H172" t="str">
-        <v>Hailey Picardi</v>
+        <v>Mau y Ricky</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
+        <v>https://music.apple.com/us/artist/mau-y-ricky/1096068683</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/chaotic/6767626506</v>
+        <v>https://music.apple.com/us/album/amapola/6769559985</v>
       </c>
       <c r="L172" t="str">
-        <v>chaotic - Hailey Picardi</v>
+        <v>AMAPOLA - Mau y Ricky</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Keep It To Yourself</v>
+        <v>Mad About It</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/keep-it-to-yourself/6771099675</v>
+        <v>https://music.apple.com/us/song/mad-about-it/6767425272</v>
       </c>
       <c r="D173" t="str">
         <v>2026-06-03</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>LOVE IS THE LAW</v>
+        <v>Mad About It - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>4:17</v>
+        <v>2:37</v>
       </c>
       <c r="H173" t="str">
-        <v>Love Spells</v>
+        <v>Dasha</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/love-spells/1597025563</v>
+        <v>https://music.apple.com/us/artist/dasha/1462663731</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/keep-it-to-yourself/6771099661</v>
+        <v>https://music.apple.com/us/album/mad-about-it/6767425271</v>
       </c>
       <c r="L173" t="str">
-        <v>Keep It To Yourself - Love Spells</v>
+        <v>Mad About It - Dasha</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Something to Someone</v>
+        <v>Love’s a Gun</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/something-to-someone/6767255424</v>
+        <v>https://music.apple.com/us/song/loves-a-gun/6771898253</v>
       </c>
       <c r="D174" t="str">
         <v>2026-06-03</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Something to Someone - Single</v>
+        <v>Love’s a Gun - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>3:55</v>
+        <v>2:59</v>
       </c>
       <c r="H174" t="str">
-        <v>Max McNown</v>
+        <v>Daniel Seavey</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
+        <v>https://music.apple.com/us/artist/daniel-seavey/1646124302</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/something-to-someone/1896445136</v>
+        <v>https://music.apple.com/us/album/loves-a-gun/6771897951</v>
       </c>
       <c r="L174" t="str">
-        <v>Something to Someone - Max McNown</v>
+        <v>Love’s a Gun - Daniel Seavey</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Green Screen (1pm)</v>
+        <v>Long Story Short</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/green-screen-1pm/6766279426</v>
+        <v>https://music.apple.com/us/song/long-story-short/6770700866</v>
       </c>
       <c r="D175" t="str">
         <v>2026-06-03</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>The Hours: High Noon</v>
+        <v>Long Story Short - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>2:10</v>
+        <v>2:48</v>
       </c>
       <c r="H175" t="str">
-        <v>Cautious Clay</v>
+        <v>Knox</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/cautious-clay/1064628701</v>
+        <v>https://music.apple.com/us/artist/knox/1547519433</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/green-screen-1pm/1896264236</v>
+        <v>https://music.apple.com/us/album/long-story-short/6770700853</v>
       </c>
       <c r="L175" t="str">
-        <v>Green Screen (1pm) - Cautious Clay</v>
+        <v>Long Story Short - Knox</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Scoreboard</v>
+        <v>Dior</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/scoreboard/6767255746</v>
+        <v>https://music.apple.com/us/song/dior/1892136721</v>
       </c>
       <c r="D176" t="str">
         <v>2026-06-03</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>I Just Wanna Be Loved</v>
+        <v>bitknot</v>
       </c>
       <c r="G176" t="str">
-        <v>3:24</v>
+        <v>3:32</v>
       </c>
       <c r="H176" t="str">
-        <v>Gabriella Rose</v>
+        <v>feeble little horse</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/gabriella-rose/645706232</v>
+        <v>https://music.apple.com/us/artist/feeble-little-horse/1564273208</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/scoreboard/1896445371</v>
+        <v>https://music.apple.com/us/album/dior/1892136714</v>
       </c>
       <c r="L176" t="str">
-        <v>Scoreboard - Gabriella Rose</v>
+        <v>Dior - feeble little horse</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>High</v>
+        <v>blue jeans</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/high/6773775211</v>
+        <v>https://music.apple.com/us/song/blue-jeans/6770529591</v>
       </c>
       <c r="D177" t="str">
         <v>2026-06-03</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Payback Is A Dog (EP)</v>
+        <v>blue jeans - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>2:55</v>
+        <v>2:37</v>
       </c>
       <c r="H177" t="str">
-        <v>Nia Smith</v>
+        <v>Nightly</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/nia-smith/1755576018</v>
+        <v>https://music.apple.com/us/artist/nightly/352310972</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/high/6773775203</v>
+        <v>https://music.apple.com/us/album/blue-jeans/6770529589</v>
       </c>
       <c r="L177" t="str">
-        <v>High - Nia Smith</v>
+        <v>blue jeans - Nightly</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Ay Gyal</v>
+        <v>Que Gacho</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/ay-gyal/6771885805</v>
+        <v>https://music.apple.com/us/song/que-gacho/6770628420</v>
       </c>
       <c r="D178" t="str">
         <v>2026-06-03</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Ay Gyal - Single</v>
+        <v>Que Gacho - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>2:12</v>
+        <v>3:13</v>
       </c>
       <c r="H178" t="str">
-        <v>1Ski OG</v>
+        <v>Luis R Conriquez</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
+        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/ay-gyal/6771885803</v>
+        <v>https://music.apple.com/us/album/que-gacho/6770628419</v>
       </c>
       <c r="L178" t="str">
-        <v>Ay Gyal - 1Ski OG</v>
+        <v>Que Gacho - Luis R Conriquez</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>always knew</v>
+        <v>same God</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/always-knew/6762864274</v>
+        <v>https://music.apple.com/us/song/same-god/1878232616</v>
       </c>
       <c r="D179" t="str">
         <v>2026-06-03</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>always knew - Single</v>
+        <v>I HOPE THIS HELPS</v>
       </c>
       <c r="G179" t="str">
-        <v>3:25</v>
+        <v>3:34</v>
       </c>
       <c r="H179" t="str">
-        <v>Biscits</v>
+        <v>Alana Springsteen</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/biscits/1185553226</v>
+        <v>https://music.apple.com/us/artist/alana-springsteen/1309335606</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/always-knew/1895047928</v>
+        <v>https://music.apple.com/us/album/same-god/1878232194</v>
       </c>
       <c r="L179" t="str">
-        <v>always knew - Biscits</v>
+        <v>same God - Alana Springsteen</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Cigarette Burns</v>
+        <v>emotional swaggage</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/cigarette-burns/6770691000</v>
+        <v>https://music.apple.com/us/song/emotional-swaggage/6767397453</v>
       </c>
       <c r="D180" t="str">
         <v>2026-06-03</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Heartland Rock and Roll</v>
+        <v>IDCASH</v>
       </c>
       <c r="G180" t="str">
-        <v>2:41</v>
+        <v>2:12</v>
       </c>
       <c r="H180" t="str">
-        <v>Corey Kent</v>
+        <v>IDK</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/corey-kent/1171544097</v>
+        <v>https://music.apple.com/us/artist/idk/1578186947</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/cigarette-burns/6770690867</v>
+        <v>https://music.apple.com/us/album/emotional-swaggage/6767397348</v>
       </c>
       <c r="L180" t="str">
-        <v>Cigarette Burns - Corey Kent</v>
+        <v>emotional swaggage - IDK</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Let You Down</v>
+        <v>Baby Driver</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/let-you-down/6773362320</v>
+        <v>https://music.apple.com/us/song/baby-driver/6769152279</v>
       </c>
       <c r="D181" t="str">
         <v>2026-06-03</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>El Relevo</v>
+        <v>Baby Driver - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>4:14</v>
+        <v>3:36</v>
       </c>
       <c r="H181" t="str">
-        <v>Luis Figueroa</v>
+        <v>070 Shake</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/luis-figueroa/395266944</v>
+        <v>https://music.apple.com/us/artist/070-shake/1097177293</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/let-you-down/6773362108</v>
+        <v>https://music.apple.com/us/album/baby-driver/6769152273</v>
       </c>
       <c r="L181" t="str">
-        <v>Let You Down - Luis Figueroa</v>
+        <v>Baby Driver - 070 Shake</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Starless</v>
+        <v>More! More! More!</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/starless/6770568779</v>
+        <v>https://music.apple.com/us/song/more-more-more/6770600105</v>
       </c>
       <c r="D182" t="str">
         <v>2026-06-03</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Starless - Single</v>
+        <v>REBECCA</v>
       </c>
       <c r="G182" t="str">
-        <v>4:32</v>
+        <v>2:55</v>
       </c>
       <c r="H182" t="str">
-        <v>A Perfect Circle</v>
+        <v>Becky Hill</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/a-perfect-circle/652503</v>
+        <v>https://music.apple.com/us/artist/becky-hill/533839517</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/starless/6770568776</v>
+        <v>https://music.apple.com/us/album/more-more-more/6770600098</v>
       </c>
       <c r="L182" t="str">
-        <v>Starless - A Perfect Circle</v>
+        <v>More! More! More! - Becky Hill</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Looking For You</v>
+        <v>Young Again</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/looking-for-you/6768355609</v>
+        <v>https://music.apple.com/us/song/young-again/1877229743</v>
       </c>
       <c r="D183" t="str">
         <v>2026-06-03</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Looking For You - Single</v>
+        <v>EI8HT</v>
       </c>
       <c r="G183" t="str">
-        <v>3:19</v>
+        <v>3:36</v>
       </c>
       <c r="H183" t="str">
-        <v>Gable Price and Friends</v>
+        <v>Shinedown</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/gable-price-and-friends/1441378212</v>
+        <v>https://music.apple.com/us/artist/shinedown/1883858</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/looking-for-you/6768355596</v>
+        <v>https://music.apple.com/us/album/young-again/1877229738</v>
       </c>
       <c r="L183" t="str">
-        <v>Looking For You - Gable Price and Friends</v>
+        <v>Young Again - Shinedown</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>FOCUSED</v>
+        <v>skinny dip</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/focused/1887909237</v>
+        <v>https://music.apple.com/us/song/skinny-dip/6769856281</v>
       </c>
       <c r="D184" t="str">
         <v>2026-06-03</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>FOCUSED - Single</v>
+        <v>skinny dip - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>2:23</v>
+        <v>3:12</v>
       </c>
       <c r="H184" t="str">
-        <v>Shepherd</v>
+        <v>almost monday</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/shepherd/1192803216</v>
+        <v>https://music.apple.com/us/artist/almost-monday/1300723925</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/focused/1887909236</v>
+        <v>https://music.apple.com/us/album/skinny-dip/6769855907</v>
       </c>
       <c r="L184" t="str">
-        <v>FOCUSED - Shepherd</v>
+        <v>skinny dip - almost monday</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Tú Ni En Cuenta</v>
+        <v>girls like girls (from the motion picture)</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/tu-ni-en-cuenta/6767701804</v>
+        <v>https://music.apple.com/us/song/girls-like-girls-from-the-motion-picture/1893704575</v>
       </c>
       <c r="D185" t="str">
         <v>2026-06-03</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Tú Ni En Cuenta - Single</v>
+        <v>girls like girls the album</v>
       </c>
       <c r="G185" t="str">
-        <v>3:23</v>
+        <v>4:14</v>
       </c>
       <c r="H185" t="str">
-        <v>Banda MS de Sergio Lizárraga</v>
+        <v>Hayley Kiyoko</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/banda-ms-de-sergio-liz%C3%A1rraga/413048014</v>
+        <v>https://music.apple.com/us/artist/hayley-kiyoko/325569584</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/tu-ni-en-cuenta/6767701803</v>
+        <v>https://music.apple.com/us/album/girls-like-girls-from-the-motion-picture/1893704396</v>
       </c>
       <c r="L185" t="str">
-        <v>Tú Ni En Cuenta - Banda MS de Sergio Lizárraga</v>
+        <v>girls like girls (from the motion picture) - Hayley Kiyoko</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>dream state</v>
+        <v>Better Off</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/dream-state/6765596009</v>
+        <v>https://music.apple.com/us/song/better-off/6772045367</v>
       </c>
       <c r="D186" t="str">
         <v>2026-06-03</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>dream state - Single</v>
+        <v>Stages</v>
       </c>
       <c r="G186" t="str">
-        <v>4:01</v>
+        <v>3:16</v>
       </c>
       <c r="H186" t="str">
-        <v>Martin Luke Brown</v>
+        <v>Lauren Alaina</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/martin-luke-brown/883292185</v>
+        <v>https://music.apple.com/us/artist/lauren-alaina/425028816</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/dream-state/1896004790</v>
+        <v>https://music.apple.com/us/album/better-off/6772044978</v>
       </c>
       <c r="L186" t="str">
-        <v>dream state - Martin Luke Brown</v>
+        <v>Better Off - Lauren Alaina</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Needle (feat. Spencer Cullum)</v>
+        <v>Everythang Pinka (feat. Teezo Touchdown)</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/needle-feat-spencer-cullum/6767618217</v>
+        <v>https://music.apple.com/us/song/everythang-pinka-feat-teezo-touchdown/6772026590</v>
       </c>
       <c r="D187" t="str">
         <v>2026-06-03</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Needle (feat. Spencer Cullum) - Single</v>
+        <v>Everythang Pinka (feat. Teezo Touchdown) - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>3:39</v>
+        <v>2:48</v>
       </c>
       <c r="H187" t="str">
-        <v>Mynolia</v>
+        <v>Monaleo</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/mynolia/1444347510</v>
+        <v>https://music.apple.com/us/artist/monaleo/1495603374</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/needle-feat-spencer-cullum/6767618203</v>
+        <v>https://music.apple.com/us/album/everythang-pinka-feat-teezo-touchdown/6772026586</v>
       </c>
       <c r="L187" t="str">
-        <v>Needle (feat. Spencer Cullum) - Mynolia</v>
+        <v>Everythang Pinka (feat. Teezo Touchdown) - Monaleo</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>You Retreat In Time And Space</v>
+        <v>Lost in translation...</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/you-retreat-in-time-and-space/1890015660</v>
+        <v>https://music.apple.com/us/song/lost-in-translation/1870971556</v>
       </c>
       <c r="D188" t="str">
         <v>2026-06-03</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Inferno</v>
+        <v>Dream inside a dream…</v>
       </c>
       <c r="G188" t="str">
-        <v>5:25</v>
+        <v>3:30</v>
       </c>
       <c r="H188" t="str">
-        <v>Boards of Canada</v>
+        <v>R3HAB</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/boards-of-canada/2989314</v>
+        <v>https://music.apple.com/us/artist/r3hab/331900515</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/you-retreat-in-time-and-space/1890015523</v>
+        <v>https://music.apple.com/us/album/lost-in-translation/1870971550</v>
       </c>
       <c r="L188" t="str">
-        <v>You Retreat In Time And Space - Boards of Canada</v>
+        <v>Lost in translation... - R3HAB</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>It's Happening (To Me)</v>
+        <v>Call Security</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/its-happening-to-me/6764723461</v>
+        <v>https://music.apple.com/us/song/call-security/6769296603</v>
       </c>
       <c r="D189" t="str">
         <v>2026-06-03</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>It's Happening (To Me) - Single</v>
+        <v>U, Me &amp; My Ego</v>
       </c>
       <c r="G189" t="str">
-        <v>2:34</v>
+        <v>3:22</v>
       </c>
       <c r="H189" t="str">
-        <v>Delroy Edwards</v>
+        <v>Chxrry</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/delroy-edwards/591790909</v>
+        <v>https://music.apple.com/us/artist/chxrry/1520135642</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/its-happening-to-me/1895893472</v>
+        <v>https://music.apple.com/us/album/call-security/6769296591</v>
       </c>
       <c r="L189" t="str">
-        <v>It's Happening (To Me) - Delroy Edwards</v>
+        <v>Call Security - Chxrry</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>FCUK</v>
+        <v>chaotic</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/fcuk/6769623577</v>
+        <v>https://music.apple.com/us/song/chaotic/6767629281</v>
       </c>
       <c r="D190" t="str">
         <v>2026-06-03</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>FCUK - Single</v>
+        <v>scars to prove it</v>
       </c>
       <c r="G190" t="str">
-        <v>2:22</v>
+        <v>3:14</v>
       </c>
       <c r="H190" t="str">
-        <v>H.LLS</v>
+        <v>Hailey Picardi</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/h-lls/1751287958</v>
+        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/fcuk/6769623566</v>
+        <v>https://music.apple.com/us/album/chaotic/6767626506</v>
       </c>
       <c r="L190" t="str">
-        <v>FCUK - H.LLS</v>
+        <v>chaotic - Hailey Picardi</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Higher</v>
+        <v>Keep It To Yourself</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/higher/1880124200</v>
+        <v>https://music.apple.com/us/song/keep-it-to-yourself/6771099675</v>
       </c>
       <c r="D191" t="str">
         <v>2026-06-03</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Run, Run Pure Beauty</v>
+        <v>LOVE IS THE LAW</v>
       </c>
       <c r="G191" t="str">
-        <v>4:06</v>
+        <v>4:17</v>
       </c>
       <c r="H191" t="str">
-        <v>Francis of Delirium</v>
+        <v>Love Spells</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/francis-of-delirium/1485902996</v>
+        <v>https://music.apple.com/us/artist/love-spells/1597025563</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/higher/1880123731</v>
+        <v>https://music.apple.com/us/album/keep-it-to-yourself/6771099661</v>
       </c>
       <c r="L191" t="str">
-        <v>Higher - Francis of Delirium</v>
+        <v>Keep It To Yourself - Love Spells</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>B.U.N</v>
+        <v>Something to Someone</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/b-u-n/6763272338</v>
+        <v>https://music.apple.com/us/song/something-to-someone/6767255424</v>
       </c>
       <c r="D192" t="str">
         <v>2026-06-03</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>B.U.N - Single</v>
+        <v>Something to Someone - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>3:43</v>
+        <v>3:55</v>
       </c>
       <c r="H192" t="str">
-        <v>Roll Deep</v>
+        <v>Max McNown</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/roll-deep/3083873</v>
+        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/b-u-n/1895242397</v>
+        <v>https://music.apple.com/us/album/something-to-someone/1896445136</v>
       </c>
       <c r="L192" t="str">
-        <v>B.U.N - Roll Deep</v>
+        <v>Something to Someone - Max McNown</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Only Love (feat. Pa Salieu)</v>
+        <v>Green Screen (1pm)</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/only-love-feat-pa-salieu/6767014290</v>
+        <v>https://music.apple.com/us/song/green-screen-1pm/6766279426</v>
       </c>
       <c r="D193" t="str">
         <v>2026-06-03</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Here Because of Hope</v>
+        <v>The Hours: High Noon</v>
       </c>
       <c r="G193" t="str">
-        <v>3:22</v>
+        <v>2:10</v>
       </c>
       <c r="H193" t="str">
-        <v>Ezra Collective</v>
+        <v>Cautious Clay</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/ezra-collective/1103640281</v>
+        <v>https://music.apple.com/us/artist/cautious-clay/1064628701</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/only-love-feat-pa-salieu/6767014278</v>
+        <v>https://music.apple.com/us/album/green-screen-1pm/1896264236</v>
       </c>
       <c r="L193" t="str">
-        <v>Only Love (feat. Pa Salieu) - Ezra Collective</v>
+        <v>Green Screen (1pm) - Cautious Clay</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Beautiful Things 1st scene/audition</v>
+        <v>Scoreboard</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/beautiful-things-1st-scene-audition/6771942631</v>
+        <v>https://music.apple.com/us/song/scoreboard/6767255746</v>
       </c>
       <c r="D194" t="str">
         <v>2026-06-03</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>UNDRA</v>
+        <v>I Just Wanna Be Loved</v>
       </c>
       <c r="G194" t="str">
-        <v>2:49</v>
+        <v>3:24</v>
       </c>
       <c r="H194" t="str">
-        <v>reggie</v>
+        <v>Gabriella Rose</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/reggie/1526587068</v>
+        <v>https://music.apple.com/us/artist/gabriella-rose/645706232</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/beautiful-things-1st-scene-audition/6771942630</v>
+        <v>https://music.apple.com/us/album/scoreboard/1896445371</v>
       </c>
       <c r="L194" t="str">
-        <v>Beautiful Things 1st scene/audition - reggie</v>
+        <v>Scoreboard - Gabriella Rose</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>HEAVEN'S ON FIRE</v>
+        <v>High</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/heavens-on-fire/6771110730</v>
+        <v>https://music.apple.com/us/song/high/6773775211</v>
       </c>
       <c r="D195" t="str">
         <v>2026-06-03</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>HEAVEN'S ON FIRE</v>
+        <v>Payback Is A Dog (EP)</v>
       </c>
       <c r="G195" t="str">
-        <v>2:54</v>
+        <v>2:55</v>
       </c>
       <c r="H195" t="str">
-        <v>Johnny Huynh</v>
+        <v>Nia Smith</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/johnny-huynh/1708540956</v>
+        <v>https://music.apple.com/us/artist/nia-smith/1755576018</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/heavens-on-fire/6771110729</v>
+        <v>https://music.apple.com/us/album/high/6773775203</v>
       </c>
       <c r="L195" t="str">
-        <v>HEAVEN'S ON FIRE - Johnny Huynh</v>
+        <v>High - Nia Smith</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Fallen Angel</v>
+        <v>Ay Gyal</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/fallen-angel/6771161222</v>
+        <v>https://music.apple.com/us/song/ay-gyal/6771885805</v>
       </c>
       <c r="D196" t="str">
         <v>2026-06-03</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>You Don't Know My Name</v>
+        <v>Ay Gyal - Single</v>
       </c>
       <c r="G196" t="str">
-        <v>3:05</v>
+        <v>2:12</v>
       </c>
       <c r="H196" t="str">
-        <v>Baby J</v>
+        <v>1Ski OG</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/baby-j/1513690931</v>
+        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/fallen-angel/6771161180</v>
+        <v>https://music.apple.com/us/album/ay-gyal/6771885803</v>
       </c>
       <c r="L196" t="str">
-        <v>Fallen Angel - Baby J</v>
+        <v>Ay Gyal - 1Ski OG</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>The Last Encounter</v>
+        <v>always knew</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/the-last-encounter/6767395134</v>
+        <v>https://music.apple.com/us/song/always-knew/6762864274</v>
       </c>
       <c r="D197" t="str">
         <v>2026-06-03</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>The Last Encounter - Single</v>
+        <v>always knew - Single</v>
       </c>
       <c r="G197" t="str">
-        <v>3:04</v>
+        <v>3:25</v>
       </c>
       <c r="H197" t="str">
-        <v>Sofia Camara</v>
+        <v>Biscits</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/sofia-camara/1506432156</v>
+        <v>https://music.apple.com/us/artist/biscits/1185553226</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/the-last-encounter/6767395133</v>
+        <v>https://music.apple.com/us/album/always-knew/1895047928</v>
       </c>
       <c r="L197" t="str">
-        <v>The Last Encounter - Sofia Camara</v>
+        <v>always knew - Biscits</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>we fall</v>
+        <v>Cigarette Burns</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/we-fall/6769218917</v>
+        <v>https://music.apple.com/us/song/cigarette-burns/6770691000</v>
       </c>
       <c r="D198" t="str">
         <v>2026-06-03</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>we fall - Single</v>
+        <v>Heartland Rock and Roll</v>
       </c>
       <c r="G198" t="str">
-        <v>4:01</v>
+        <v>2:41</v>
       </c>
       <c r="H198" t="str">
-        <v>MOIO</v>
+        <v>Corey Kent</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/moio/1664183608</v>
+        <v>https://music.apple.com/us/artist/corey-kent/1171544097</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/we-fall/6769218915</v>
+        <v>https://music.apple.com/us/album/cigarette-burns/6770690867</v>
       </c>
       <c r="L198" t="str">
-        <v>we fall - MOIO</v>
+        <v>Cigarette Burns - Corey Kent</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>You Don't Know Me</v>
+        <v>Let You Down</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/you-dont-know-me/6769214417</v>
+        <v>https://music.apple.com/us/song/let-you-down/6773362320</v>
       </c>
       <c r="D199" t="str">
         <v>2026-06-03</v>
@@ -7937,36 +7937,36 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>You Don’t Know Me - Single</v>
+        <v>El Relevo</v>
       </c>
       <c r="G199" t="str">
-        <v>3:50</v>
+        <v>4:14</v>
       </c>
       <c r="H199" t="str">
-        <v>Isabel Dumaa</v>
+        <v>Luis Figueroa</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/isabel-dumaa/1631481156</v>
+        <v>https://music.apple.com/us/artist/luis-figueroa/395266944</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/you-dont-know-me/6769214410</v>
+        <v>https://music.apple.com/us/album/let-you-down/6773362108</v>
       </c>
       <c r="L199" t="str">
-        <v>You Don't Know Me - Isabel Dumaa</v>
+        <v>Let You Down - Luis Figueroa</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Hold Up, Say What?</v>
+        <v>Starless</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/hold-up-say-what/1879853511</v>
+        <v>https://music.apple.com/us/song/starless/6770568779</v>
       </c>
       <c r="D200" t="str">
         <v>2026-06-03</v>
@@ -7975,36 +7975,36 @@
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>House Of Mirrors</v>
+        <v>Starless - Single</v>
       </c>
       <c r="G200" t="str">
-        <v>4:04</v>
+        <v>4:32</v>
       </c>
       <c r="H200" t="str">
-        <v>All Them Witches</v>
+        <v>A Perfect Circle</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/all-them-witches/534924603</v>
+        <v>https://music.apple.com/us/artist/a-perfect-circle/652503</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/hold-up-say-what/1879853502</v>
+        <v>https://music.apple.com/us/album/starless/6770568776</v>
       </c>
       <c r="L200" t="str">
-        <v>Hold Up, Say What? - All Them Witches</v>
+        <v>Starless - A Perfect Circle</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Iodine</v>
+        <v>Looking For You</v>
       </c>
       <c r="B201" t="str">
         <v/>
       </c>
       <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/iodine/1871211805</v>
+        <v>https://music.apple.com/us/song/looking-for-you/6768355609</v>
       </c>
       <c r="D201" t="str">
         <v>2026-06-03</v>
@@ -8013,36 +8013,36 @@
         <v/>
       </c>
       <c r="F201" t="str">
-        <v>Neverending</v>
+        <v>Looking For You - Single</v>
       </c>
       <c r="G201" t="str">
-        <v>3:40</v>
+        <v>3:19</v>
       </c>
       <c r="H201" t="str">
-        <v>Monolord</v>
+        <v>Gable Price and Friends</v>
       </c>
       <c r="I201" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/monolord/833749384</v>
+        <v>https://music.apple.com/us/artist/gable-price-and-friends/1441378212</v>
       </c>
       <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/iodine/1871211801</v>
+        <v>https://music.apple.com/us/album/looking-for-you/6768355596</v>
       </c>
       <c r="L201" t="str">
-        <v>Iodine - Monolord</v>
+        <v>Looking For You - Gable Price and Friends</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>I Speak Forgotten Voices</v>
+        <v>FOCUSED</v>
       </c>
       <c r="B202" t="str">
         <v/>
       </c>
       <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/i-speak-forgotten-voices/1878083625</v>
+        <v>https://music.apple.com/us/song/focused/1887909237</v>
       </c>
       <c r="D202" t="str">
         <v>2026-06-03</v>
@@ -8051,68 +8051,752 @@
         <v/>
       </c>
       <c r="F202" t="str">
-        <v>...By the Word...</v>
+        <v>FOCUSED - Single</v>
       </c>
       <c r="G202" t="str">
-        <v>5:01</v>
+        <v>2:23</v>
       </c>
       <c r="H202" t="str">
-        <v>Trelldom</v>
+        <v>Shepherd</v>
       </c>
       <c r="I202" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/trelldom/256586618</v>
+        <v>https://music.apple.com/us/artist/shepherd/1192803216</v>
       </c>
       <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/i-speak-forgotten-voices/1878083622</v>
+        <v>https://music.apple.com/us/album/focused/1887909236</v>
       </c>
       <c r="L202" t="str">
-        <v>I Speak Forgotten Voices - Trelldom</v>
+        <v>FOCUSED - Shepherd</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
+        <v>Tú Ni En Cuenta</v>
+      </c>
+      <c r="B203" t="str">
+        <v/>
+      </c>
+      <c r="C203" t="str">
+        <v>https://music.apple.com/us/song/tu-ni-en-cuenta/6767701804</v>
+      </c>
+      <c r="D203" t="str">
+        <v>2026-06-03</v>
+      </c>
+      <c r="E203" t="str">
+        <v/>
+      </c>
+      <c r="F203" t="str">
+        <v>Tú Ni En Cuenta - Single</v>
+      </c>
+      <c r="G203" t="str">
+        <v>3:23</v>
+      </c>
+      <c r="H203" t="str">
+        <v>Banda MS de Sergio Lizárraga</v>
+      </c>
+      <c r="I203" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J203" t="str">
+        <v>https://music.apple.com/us/artist/banda-ms-de-sergio-liz%C3%A1rraga/413048014</v>
+      </c>
+      <c r="K203" t="str">
+        <v>https://music.apple.com/us/album/tu-ni-en-cuenta/6767701803</v>
+      </c>
+      <c r="L203" t="str">
+        <v>Tú Ni En Cuenta - Banda MS de Sergio Lizárraga</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
+        <v>dream state</v>
+      </c>
+      <c r="B204" t="str">
+        <v/>
+      </c>
+      <c r="C204" t="str">
+        <v>https://music.apple.com/us/song/dream-state/6765596009</v>
+      </c>
+      <c r="D204" t="str">
+        <v>2026-06-03</v>
+      </c>
+      <c r="E204" t="str">
+        <v/>
+      </c>
+      <c r="F204" t="str">
+        <v>dream state - Single</v>
+      </c>
+      <c r="G204" t="str">
+        <v>4:01</v>
+      </c>
+      <c r="H204" t="str">
+        <v>Martin Luke Brown</v>
+      </c>
+      <c r="I204" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J204" t="str">
+        <v>https://music.apple.com/us/artist/martin-luke-brown/883292185</v>
+      </c>
+      <c r="K204" t="str">
+        <v>https://music.apple.com/us/album/dream-state/1896004790</v>
+      </c>
+      <c r="L204" t="str">
+        <v>dream state - Martin Luke Brown</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v>Needle (feat. Spencer Cullum)</v>
+      </c>
+      <c r="B205" t="str">
+        <v/>
+      </c>
+      <c r="C205" t="str">
+        <v>https://music.apple.com/us/song/needle-feat-spencer-cullum/6767618217</v>
+      </c>
+      <c r="D205" t="str">
+        <v>2026-06-03</v>
+      </c>
+      <c r="E205" t="str">
+        <v/>
+      </c>
+      <c r="F205" t="str">
+        <v>Needle (feat. Spencer Cullum) - Single</v>
+      </c>
+      <c r="G205" t="str">
+        <v>3:39</v>
+      </c>
+      <c r="H205" t="str">
+        <v>Mynolia</v>
+      </c>
+      <c r="I205" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J205" t="str">
+        <v>https://music.apple.com/us/artist/mynolia/1444347510</v>
+      </c>
+      <c r="K205" t="str">
+        <v>https://music.apple.com/us/album/needle-feat-spencer-cullum/6767618203</v>
+      </c>
+      <c r="L205" t="str">
+        <v>Needle (feat. Spencer Cullum) - Mynolia</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="str">
+        <v>You Retreat In Time And Space</v>
+      </c>
+      <c r="B206" t="str">
+        <v/>
+      </c>
+      <c r="C206" t="str">
+        <v>https://music.apple.com/us/song/you-retreat-in-time-and-space/1890015660</v>
+      </c>
+      <c r="D206" t="str">
+        <v>2026-06-03</v>
+      </c>
+      <c r="E206" t="str">
+        <v/>
+      </c>
+      <c r="F206" t="str">
+        <v>Inferno</v>
+      </c>
+      <c r="G206" t="str">
+        <v>5:25</v>
+      </c>
+      <c r="H206" t="str">
+        <v>Boards of Canada</v>
+      </c>
+      <c r="I206" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J206" t="str">
+        <v>https://music.apple.com/us/artist/boards-of-canada/2989314</v>
+      </c>
+      <c r="K206" t="str">
+        <v>https://music.apple.com/us/album/you-retreat-in-time-and-space/1890015523</v>
+      </c>
+      <c r="L206" t="str">
+        <v>You Retreat In Time And Space - Boards of Canada</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
+        <v>It's Happening (To Me)</v>
+      </c>
+      <c r="B207" t="str">
+        <v/>
+      </c>
+      <c r="C207" t="str">
+        <v>https://music.apple.com/us/song/its-happening-to-me/6764723461</v>
+      </c>
+      <c r="D207" t="str">
+        <v>2026-06-03</v>
+      </c>
+      <c r="E207" t="str">
+        <v/>
+      </c>
+      <c r="F207" t="str">
+        <v>It's Happening (To Me) - Single</v>
+      </c>
+      <c r="G207" t="str">
+        <v>2:34</v>
+      </c>
+      <c r="H207" t="str">
+        <v>Delroy Edwards</v>
+      </c>
+      <c r="I207" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J207" t="str">
+        <v>https://music.apple.com/us/artist/delroy-edwards/591790909</v>
+      </c>
+      <c r="K207" t="str">
+        <v>https://music.apple.com/us/album/its-happening-to-me/1895893472</v>
+      </c>
+      <c r="L207" t="str">
+        <v>It's Happening (To Me) - Delroy Edwards</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="str">
+        <v>FCUK</v>
+      </c>
+      <c r="B208" t="str">
+        <v/>
+      </c>
+      <c r="C208" t="str">
+        <v>https://music.apple.com/us/song/fcuk/6769623577</v>
+      </c>
+      <c r="D208" t="str">
+        <v>2026-06-03</v>
+      </c>
+      <c r="E208" t="str">
+        <v/>
+      </c>
+      <c r="F208" t="str">
+        <v>FCUK - Single</v>
+      </c>
+      <c r="G208" t="str">
+        <v>2:22</v>
+      </c>
+      <c r="H208" t="str">
+        <v>H.LLS</v>
+      </c>
+      <c r="I208" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J208" t="str">
+        <v>https://music.apple.com/us/artist/h-lls/1751287958</v>
+      </c>
+      <c r="K208" t="str">
+        <v>https://music.apple.com/us/album/fcuk/6769623566</v>
+      </c>
+      <c r="L208" t="str">
+        <v>FCUK - H.LLS</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="str">
+        <v>Higher</v>
+      </c>
+      <c r="B209" t="str">
+        <v/>
+      </c>
+      <c r="C209" t="str">
+        <v>https://music.apple.com/us/song/higher/1880124200</v>
+      </c>
+      <c r="D209" t="str">
+        <v>2026-06-03</v>
+      </c>
+      <c r="E209" t="str">
+        <v/>
+      </c>
+      <c r="F209" t="str">
+        <v>Run, Run Pure Beauty</v>
+      </c>
+      <c r="G209" t="str">
+        <v>4:06</v>
+      </c>
+      <c r="H209" t="str">
+        <v>Francis of Delirium</v>
+      </c>
+      <c r="I209" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J209" t="str">
+        <v>https://music.apple.com/us/artist/francis-of-delirium/1485902996</v>
+      </c>
+      <c r="K209" t="str">
+        <v>https://music.apple.com/us/album/higher/1880123731</v>
+      </c>
+      <c r="L209" t="str">
+        <v>Higher - Francis of Delirium</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="str">
+        <v>B.U.N</v>
+      </c>
+      <c r="B210" t="str">
+        <v/>
+      </c>
+      <c r="C210" t="str">
+        <v>https://music.apple.com/us/song/b-u-n/6763272338</v>
+      </c>
+      <c r="D210" t="str">
+        <v>2026-06-03</v>
+      </c>
+      <c r="E210" t="str">
+        <v/>
+      </c>
+      <c r="F210" t="str">
+        <v>B.U.N - Single</v>
+      </c>
+      <c r="G210" t="str">
+        <v>3:43</v>
+      </c>
+      <c r="H210" t="str">
+        <v>Roll Deep</v>
+      </c>
+      <c r="I210" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J210" t="str">
+        <v>https://music.apple.com/us/artist/roll-deep/3083873</v>
+      </c>
+      <c r="K210" t="str">
+        <v>https://music.apple.com/us/album/b-u-n/1895242397</v>
+      </c>
+      <c r="L210" t="str">
+        <v>B.U.N - Roll Deep</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="str">
+        <v>Only Love (feat. Pa Salieu)</v>
+      </c>
+      <c r="B211" t="str">
+        <v/>
+      </c>
+      <c r="C211" t="str">
+        <v>https://music.apple.com/us/song/only-love-feat-pa-salieu/6767014290</v>
+      </c>
+      <c r="D211" t="str">
+        <v>2026-06-03</v>
+      </c>
+      <c r="E211" t="str">
+        <v/>
+      </c>
+      <c r="F211" t="str">
+        <v>Here Because of Hope</v>
+      </c>
+      <c r="G211" t="str">
+        <v>3:22</v>
+      </c>
+      <c r="H211" t="str">
+        <v>Ezra Collective</v>
+      </c>
+      <c r="I211" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J211" t="str">
+        <v>https://music.apple.com/us/artist/ezra-collective/1103640281</v>
+      </c>
+      <c r="K211" t="str">
+        <v>https://music.apple.com/us/album/only-love-feat-pa-salieu/6767014278</v>
+      </c>
+      <c r="L211" t="str">
+        <v>Only Love (feat. Pa Salieu) - Ezra Collective</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="str">
+        <v>Beautiful Things 1st scene/audition</v>
+      </c>
+      <c r="B212" t="str">
+        <v/>
+      </c>
+      <c r="C212" t="str">
+        <v>https://music.apple.com/us/song/beautiful-things-1st-scene-audition/6771942631</v>
+      </c>
+      <c r="D212" t="str">
+        <v>2026-06-03</v>
+      </c>
+      <c r="E212" t="str">
+        <v/>
+      </c>
+      <c r="F212" t="str">
+        <v>UNDRA</v>
+      </c>
+      <c r="G212" t="str">
+        <v>2:49</v>
+      </c>
+      <c r="H212" t="str">
+        <v>reggie</v>
+      </c>
+      <c r="I212" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J212" t="str">
+        <v>https://music.apple.com/us/artist/reggie/1526587068</v>
+      </c>
+      <c r="K212" t="str">
+        <v>https://music.apple.com/us/album/beautiful-things-1st-scene-audition/6771942630</v>
+      </c>
+      <c r="L212" t="str">
+        <v>Beautiful Things 1st scene/audition - reggie</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="str">
+        <v>HEAVEN'S ON FIRE</v>
+      </c>
+      <c r="B213" t="str">
+        <v/>
+      </c>
+      <c r="C213" t="str">
+        <v>https://music.apple.com/us/song/heavens-on-fire/6771110730</v>
+      </c>
+      <c r="D213" t="str">
+        <v>2026-06-03</v>
+      </c>
+      <c r="E213" t="str">
+        <v/>
+      </c>
+      <c r="F213" t="str">
+        <v>HEAVEN'S ON FIRE</v>
+      </c>
+      <c r="G213" t="str">
+        <v>2:54</v>
+      </c>
+      <c r="H213" t="str">
+        <v>Johnny Huynh</v>
+      </c>
+      <c r="I213" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J213" t="str">
+        <v>https://music.apple.com/us/artist/johnny-huynh/1708540956</v>
+      </c>
+      <c r="K213" t="str">
+        <v>https://music.apple.com/us/album/heavens-on-fire/6771110729</v>
+      </c>
+      <c r="L213" t="str">
+        <v>HEAVEN'S ON FIRE - Johnny Huynh</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="str">
+        <v>Fallen Angel</v>
+      </c>
+      <c r="B214" t="str">
+        <v/>
+      </c>
+      <c r="C214" t="str">
+        <v>https://music.apple.com/us/song/fallen-angel/6771161222</v>
+      </c>
+      <c r="D214" t="str">
+        <v>2026-06-03</v>
+      </c>
+      <c r="E214" t="str">
+        <v/>
+      </c>
+      <c r="F214" t="str">
+        <v>You Don't Know My Name</v>
+      </c>
+      <c r="G214" t="str">
+        <v>3:05</v>
+      </c>
+      <c r="H214" t="str">
+        <v>Baby J</v>
+      </c>
+      <c r="I214" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J214" t="str">
+        <v>https://music.apple.com/us/artist/baby-j/1513690931</v>
+      </c>
+      <c r="K214" t="str">
+        <v>https://music.apple.com/us/album/fallen-angel/6771161180</v>
+      </c>
+      <c r="L214" t="str">
+        <v>Fallen Angel - Baby J</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="str">
+        <v>The Last Encounter</v>
+      </c>
+      <c r="B215" t="str">
+        <v/>
+      </c>
+      <c r="C215" t="str">
+        <v>https://music.apple.com/us/song/the-last-encounter/6767395134</v>
+      </c>
+      <c r="D215" t="str">
+        <v>2026-06-03</v>
+      </c>
+      <c r="E215" t="str">
+        <v/>
+      </c>
+      <c r="F215" t="str">
+        <v>The Last Encounter - Single</v>
+      </c>
+      <c r="G215" t="str">
+        <v>3:04</v>
+      </c>
+      <c r="H215" t="str">
+        <v>Sofia Camara</v>
+      </c>
+      <c r="I215" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J215" t="str">
+        <v>https://music.apple.com/us/artist/sofia-camara/1506432156</v>
+      </c>
+      <c r="K215" t="str">
+        <v>https://music.apple.com/us/album/the-last-encounter/6767395133</v>
+      </c>
+      <c r="L215" t="str">
+        <v>The Last Encounter - Sofia Camara</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="str">
+        <v>we fall</v>
+      </c>
+      <c r="B216" t="str">
+        <v/>
+      </c>
+      <c r="C216" t="str">
+        <v>https://music.apple.com/us/song/we-fall/6769218917</v>
+      </c>
+      <c r="D216" t="str">
+        <v>2026-06-03</v>
+      </c>
+      <c r="E216" t="str">
+        <v/>
+      </c>
+      <c r="F216" t="str">
+        <v>we fall - Single</v>
+      </c>
+      <c r="G216" t="str">
+        <v>4:01</v>
+      </c>
+      <c r="H216" t="str">
+        <v>MOIO</v>
+      </c>
+      <c r="I216" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J216" t="str">
+        <v>https://music.apple.com/us/artist/moio/1664183608</v>
+      </c>
+      <c r="K216" t="str">
+        <v>https://music.apple.com/us/album/we-fall/6769218915</v>
+      </c>
+      <c r="L216" t="str">
+        <v>we fall - MOIO</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="str">
+        <v>You Don't Know Me</v>
+      </c>
+      <c r="B217" t="str">
+        <v/>
+      </c>
+      <c r="C217" t="str">
+        <v>https://music.apple.com/us/song/you-dont-know-me/6769214417</v>
+      </c>
+      <c r="D217" t="str">
+        <v>2026-06-03</v>
+      </c>
+      <c r="E217" t="str">
+        <v/>
+      </c>
+      <c r="F217" t="str">
+        <v>You Don’t Know Me - Single</v>
+      </c>
+      <c r="G217" t="str">
+        <v>3:50</v>
+      </c>
+      <c r="H217" t="str">
+        <v>Isabel Dumaa</v>
+      </c>
+      <c r="I217" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J217" t="str">
+        <v>https://music.apple.com/us/artist/isabel-dumaa/1631481156</v>
+      </c>
+      <c r="K217" t="str">
+        <v>https://music.apple.com/us/album/you-dont-know-me/6769214410</v>
+      </c>
+      <c r="L217" t="str">
+        <v>You Don't Know Me - Isabel Dumaa</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="str">
+        <v>Hold Up, Say What?</v>
+      </c>
+      <c r="B218" t="str">
+        <v/>
+      </c>
+      <c r="C218" t="str">
+        <v>https://music.apple.com/us/song/hold-up-say-what/1879853511</v>
+      </c>
+      <c r="D218" t="str">
+        <v>2026-06-03</v>
+      </c>
+      <c r="E218" t="str">
+        <v/>
+      </c>
+      <c r="F218" t="str">
+        <v>House Of Mirrors</v>
+      </c>
+      <c r="G218" t="str">
+        <v>4:04</v>
+      </c>
+      <c r="H218" t="str">
+        <v>All Them Witches</v>
+      </c>
+      <c r="I218" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J218" t="str">
+        <v>https://music.apple.com/us/artist/all-them-witches/534924603</v>
+      </c>
+      <c r="K218" t="str">
+        <v>https://music.apple.com/us/album/hold-up-say-what/1879853502</v>
+      </c>
+      <c r="L218" t="str">
+        <v>Hold Up, Say What? - All Them Witches</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="str">
+        <v>Iodine</v>
+      </c>
+      <c r="B219" t="str">
+        <v/>
+      </c>
+      <c r="C219" t="str">
+        <v>https://music.apple.com/us/song/iodine/1871211805</v>
+      </c>
+      <c r="D219" t="str">
+        <v>2026-06-03</v>
+      </c>
+      <c r="E219" t="str">
+        <v/>
+      </c>
+      <c r="F219" t="str">
+        <v>Neverending</v>
+      </c>
+      <c r="G219" t="str">
+        <v>3:40</v>
+      </c>
+      <c r="H219" t="str">
+        <v>Monolord</v>
+      </c>
+      <c r="I219" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J219" t="str">
+        <v>https://music.apple.com/us/artist/monolord/833749384</v>
+      </c>
+      <c r="K219" t="str">
+        <v>https://music.apple.com/us/album/iodine/1871211801</v>
+      </c>
+      <c r="L219" t="str">
+        <v>Iodine - Monolord</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="str">
+        <v>I Speak Forgotten Voices</v>
+      </c>
+      <c r="B220" t="str">
+        <v/>
+      </c>
+      <c r="C220" t="str">
+        <v>https://music.apple.com/us/song/i-speak-forgotten-voices/1878083625</v>
+      </c>
+      <c r="D220" t="str">
+        <v>2026-06-03</v>
+      </c>
+      <c r="E220" t="str">
+        <v/>
+      </c>
+      <c r="F220" t="str">
+        <v>...By the Word...</v>
+      </c>
+      <c r="G220" t="str">
+        <v>5:01</v>
+      </c>
+      <c r="H220" t="str">
+        <v>Trelldom</v>
+      </c>
+      <c r="I220" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J220" t="str">
+        <v>https://music.apple.com/us/artist/trelldom/256586618</v>
+      </c>
+      <c r="K220" t="str">
+        <v>https://music.apple.com/us/album/i-speak-forgotten-voices/1878083622</v>
+      </c>
+      <c r="L220" t="str">
+        <v>I Speak Forgotten Voices - Trelldom</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="str">
         <v>Rats in the Temple</v>
       </c>
-      <c r="B203" t="str">
-        <v/>
-      </c>
-      <c r="C203" t="str">
+      <c r="B221" t="str">
+        <v/>
+      </c>
+      <c r="C221" t="str">
         <v>https://music.apple.com/us/song/rats-in-the-temple/6764627559</v>
       </c>
-      <c r="D203" t="str">
-        <v>2026-06-03</v>
-      </c>
-      <c r="E203" t="str">
-        <v/>
-      </c>
-      <c r="F203" t="str">
+      <c r="D221" t="str">
+        <v>2026-06-03</v>
+      </c>
+      <c r="E221" t="str">
+        <v/>
+      </c>
+      <c r="F221" t="str">
         <v>Rats in the Temple</v>
       </c>
-      <c r="G203" t="str">
+      <c r="G221" t="str">
         <v>4:45</v>
       </c>
-      <c r="H203" t="str">
+      <c r="H221" t="str">
         <v>Flotsam and Jetsam</v>
       </c>
-      <c r="I203" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J203" t="str">
+      <c r="I221" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J221" t="str">
         <v>https://music.apple.com/us/artist/flotsam-and-jetsam/162270</v>
       </c>
-      <c r="K203" t="str">
+      <c r="K221" t="str">
         <v>https://music.apple.com/us/album/rats-in-the-temple/1895855647</v>
       </c>
-      <c r="L203" t="str">
+      <c r="L221" t="str">
         <v>Rats in the Temple - Flotsam and Jetsam</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L203"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L221"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-06-week01/titles.xlsx
+++ b/data/global/2026-06-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L221"/>
+  <dimension ref="A1:L202"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מירי מסיקה - לב לבן קאבר</v>
+        <v>Just Slide Official Music Video | Kelly Boesch | 4K</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-06-03</v>
+        <v>10h ago</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411187&amp;sid=8c32dea66695624c346eddfe12cc9153</v>
+        <v>https://www.youtube.com/watch?v=lC14fuU8aPc</v>
       </c>
       <c r="D2" t="str">
         <v>2026-06-03</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>10h ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>Kelly Boesch AI Art</v>
       </c>
       <c r="I2" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מירי מסיקה - לב לבן קאבר</v>
+        <v>Just Slide Official Music Video | Kelly Boesch | 4K - Kelly Boesch AI Art</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>אמיר אליהו - כסף הכסף קאבר</v>
+        <v>Europe - The Cult of Ignorance (Official Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-06-03</v>
+        <v>12h ago</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411182&amp;sid=8c32dea66695624c346eddfe12cc9153</v>
+        <v>https://www.youtube.com/watch?v=p-IOsjOJpnA</v>
       </c>
       <c r="D3" t="str">
         <v>2026-06-03</v>
@@ -489,16 +489,16 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v/>
+        <v>12h ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
       </c>
       <c r="H3" t="str">
-        <v/>
+        <v>Europe</v>
       </c>
       <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>אמיר אליהו - כסף הכסף קאבר</v>
+        <v>Europe - The Cult of Ignorance (Official Video) - Europe</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>שלומי הלימי - נווה הדרים קאבר</v>
+        <v>Air Supply - Sweet Dreams (Official Lyric Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-06-03</v>
+        <v>16h ago</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411199&amp;sid=a85ca8ef30bfde649d428d952bc8fa37</v>
+        <v>https://www.youtube.com/watch?v=axiK2vYjXio</v>
       </c>
       <c r="D4" t="str">
         <v>2026-06-03</v>
@@ -527,16 +527,16 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v/>
+        <v>16h ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
       </c>
       <c r="H4" t="str">
-        <v/>
+        <v>Air Supply</v>
       </c>
       <c r="I4" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>שלומי הלימי - נווה הדרים קאבר</v>
+        <v>Air Supply - Sweet Dreams (Official Lyric Video) - Air Supply</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>שיר לוי - פרחים מנייר קאבר</v>
+        <v>Culture Club - Cold Shoulder</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-06-03</v>
+        <v>1d ago</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411198&amp;sid=a85ca8ef30bfde649d428d952bc8fa37</v>
+        <v>https://www.youtube.com/watch?v=-YV4SCXFNyg</v>
       </c>
       <c r="D5" t="str">
         <v>2026-06-03</v>
@@ -565,16 +565,16 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v/>
+        <v>1d ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
       </c>
       <c r="H5" t="str">
-        <v/>
+        <v>Culture Club</v>
       </c>
       <c r="I5" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>שיר לוי - פרחים מנייר קאבר</v>
+        <v>Culture Club - Cold Shoulder - Culture Club</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>שילת סופר - נווה הדרים קאבר</v>
+        <v>Julia Cole - Treat Me Like Dirt (Official Lyric Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-06-03</v>
+        <v>1d ago</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411197&amp;sid=a85ca8ef30bfde649d428d952bc8fa37</v>
+        <v>https://www.youtube.com/watch?v=TS2Mgp5F0cs</v>
       </c>
       <c r="D6" t="str">
         <v>2026-06-03</v>
@@ -603,16 +603,16 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v/>
+        <v>1d ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
       </c>
       <c r="H6" t="str">
-        <v/>
+        <v>Julia Cole Music</v>
       </c>
       <c r="I6" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>שילת סופר - נווה הדרים קאבר</v>
+        <v>Julia Cole - Treat Me Like Dirt (Official Lyric Video) - Julia Cole Music</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>שי עמר - את יפה קאבר</v>
+        <v>Allen Stone - A Fathers Song - Placeholder Sessions</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-06-03</v>
+        <v>1d ago</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411196&amp;sid=a85ca8ef30bfde649d428d952bc8fa37</v>
+        <v>https://www.youtube.com/watch?v=JPetpt4QMPE</v>
       </c>
       <c r="D7" t="str">
         <v>2026-06-03</v>
@@ -641,16 +641,16 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v/>
+        <v>1d ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v/>
+        <v>Allen Stone and Placeholder Sessions</v>
       </c>
       <c r="I7" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J7" t="str">
         <v/>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>שי עמר - את יפה קאבר</v>
+        <v>Allen Stone - A Fathers Song - Placeholder Sessions - Allen Stone and Placeholder Sessions</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>רפא' - מאשאפ בואי &amp; ציון</v>
+        <v>Morgan Wallen - Don't We (Live From Tuscaloosa)</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-06-03</v>
+        <v>1d ago</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411195&amp;sid=a85ca8ef30bfde649d428d952bc8fa37</v>
+        <v>https://www.youtube.com/watch?v=qhmWM3uXPAU</v>
       </c>
       <c r="D8" t="str">
         <v>2026-06-03</v>
@@ -679,16 +679,16 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v/>
+        <v>1d ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8" t="str">
-        <v/>
+        <v>Morgan Wallen</v>
       </c>
       <c r="I8" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>רפא' - מאשאפ בואי &amp; ציון</v>
+        <v>Morgan Wallen - Don't We (Live From Tuscaloosa) - Morgan Wallen</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>בנימין עזר &amp; דוד עזר - קולות קאבר</v>
+        <v>Billy Idol - John Wayne feat. Alison Mosshart (Official Music Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-06-03</v>
+        <v>1d ago</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411194&amp;sid=a85ca8ef30bfde649d428d952bc8fa37</v>
+        <v>https://www.youtube.com/watch?v=47LNk7oiTVI</v>
       </c>
       <c r="D9" t="str">
         <v>2026-06-03</v>
@@ -717,16 +717,16 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v/>
+        <v>1d ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v/>
+        <v>Billy Idol</v>
       </c>
       <c r="I9" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J9" t="str">
         <v/>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>בנימין עזר &amp; דוד עזר - קולות קאבר</v>
+        <v>Billy Idol - John Wayne feat. Alison Mosshart (Official Music Video) - Billy Idol</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>רזיאל עורקבי - נווה הדרים קאבר</v>
+        <v>'It's Unusual' Official Music Video - Kelly Boesch | 4K</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-06-03</v>
+        <v>5d ago</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411193&amp;sid=a85ca8ef30bfde649d428d952bc8fa37</v>
+        <v>https://www.youtube.com/watch?v=Ru3fB2l1RSo</v>
       </c>
       <c r="D10" t="str">
         <v>2026-06-03</v>
@@ -755,16 +755,16 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v/>
+        <v>5d ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v/>
+        <v>Kelly Boesch AI Art</v>
       </c>
       <c r="I10" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J10" t="str">
         <v/>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>רזיאל עורקבי - נווה הדרים קאבר</v>
+        <v>'It's Unusual' Official Music Video - Kelly Boesch | 4K - Kelly Boesch AI Art</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>רביד שלו - גן עדן קאבר</v>
+        <v>Icona Pop - Butterfly Feelings (Official Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>2026-06-03</v>
+        <v>1d ago</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411192&amp;sid=a85ca8ef30bfde649d428d952bc8fa37</v>
+        <v>https://www.youtube.com/watch?v=AMW1Zq9RbIU</v>
       </c>
       <c r="D11" t="str">
         <v>2026-06-03</v>
@@ -793,16 +793,16 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v/>
+        <v>1d ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v/>
+        <v>Icona Pop</v>
       </c>
       <c r="I11" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J11" t="str">
         <v/>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>רביד שלו - גן עדן קאבר</v>
+        <v>Icona Pop - Butterfly Feelings (Official Video) - Icona Pop</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>עומר יונה - לא תשבור אותי קאבר</v>
+        <v>Hippo Campus - South</v>
       </c>
       <c r="B12" t="str">
-        <v>2026-06-03</v>
+        <v>2d ago</v>
       </c>
       <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411191&amp;sid=a85ca8ef30bfde649d428d952bc8fa37</v>
+        <v>https://www.youtube.com/watch?v=FYOmFfV7Ojo</v>
       </c>
       <c r="D12" t="str">
         <v>2026-06-03</v>
@@ -831,16 +831,16 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v/>
+        <v>2d ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
       </c>
       <c r="H12" t="str">
-        <v/>
+        <v>Hippo Campus</v>
       </c>
       <c r="I12" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J12" t="str">
         <v/>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>עומר יונה - לא תשבור אותי קאבר</v>
+        <v>Hippo Campus - South - Hippo Campus</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>נתנאל ואנונו - נווה הדרים קאבר</v>
+        <v>elijah woods - Old (Treehouse Sessions)</v>
       </c>
       <c r="B13" t="str">
-        <v>2026-06-03</v>
+        <v>2d ago</v>
       </c>
       <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411190&amp;sid=a85ca8ef30bfde649d428d952bc8fa37</v>
+        <v>https://www.youtube.com/watch?v=yDlkPdR_6zM</v>
       </c>
       <c r="D13" t="str">
         <v>2026-06-03</v>
@@ -869,16 +869,16 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v/>
+        <v>2d ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
       </c>
       <c r="H13" t="str">
-        <v/>
+        <v>elijah woods</v>
       </c>
       <c r="I13" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J13" t="str">
         <v/>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>נתנאל ואנונו - נווה הדרים קאבר</v>
+        <v>elijah woods - Old (Treehouse Sessions) - elijah woods</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>נתי כהן - בראשית עולם קאבר</v>
+        <v>Nothing But Thieves - Evolution (Official Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>2026-06-03</v>
+        <v>2d ago</v>
       </c>
       <c r="C14" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411189&amp;sid=a85ca8ef30bfde649d428d952bc8fa37</v>
+        <v>https://www.youtube.com/watch?v=hmjfuuuRRYU</v>
       </c>
       <c r="D14" t="str">
         <v>2026-06-03</v>
@@ -907,16 +907,16 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v/>
+        <v>2d ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
       </c>
       <c r="H14" t="str">
-        <v/>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I14" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J14" t="str">
         <v/>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>נתי כהן - בראשית עולם קאבר</v>
+        <v>Nothing But Thieves - Evolution (Official Video) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>נועם דדון - שיר לערב חג קאבר</v>
+        <v>Ariana Grande - hate that i made you love me</v>
       </c>
       <c r="B15" t="str">
-        <v>2026-06-03</v>
+        <v>2d ago</v>
       </c>
       <c r="C15" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411188&amp;sid=a85ca8ef30bfde649d428d952bc8fa37</v>
+        <v>https://www.youtube.com/watch?v=82-jTNka3uc</v>
       </c>
       <c r="D15" t="str">
         <v>2026-06-03</v>
@@ -945,16 +945,16 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v/>
+        <v>2d ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
       </c>
       <c r="H15" t="str">
-        <v/>
+        <v>Ariana Grande</v>
       </c>
       <c r="I15" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J15" t="str">
         <v/>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>נועם דדון - שיר לערב חג קאבר</v>
+        <v>Ariana Grande - hate that i made you love me - Ariana Grande</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>לינוי הגג - הכל שתיקות קאבר</v>
+        <v>LAUREL - Fire Breather</v>
       </c>
       <c r="B16" t="str">
-        <v>2026-06-03</v>
+        <v>2d ago</v>
       </c>
       <c r="C16" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411186&amp;sid=a85ca8ef30bfde649d428d952bc8fa37</v>
+        <v>https://www.youtube.com/watch?v=rtyavLIJjy0</v>
       </c>
       <c r="D16" t="str">
         <v>2026-06-03</v>
@@ -983,16 +983,16 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v/>
+        <v>2d ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
       </c>
       <c r="H16" t="str">
-        <v/>
+        <v>LAUREL</v>
       </c>
       <c r="I16" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J16" t="str">
         <v/>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>לינוי הגג - הכל שתיקות קאבר</v>
+        <v>LAUREL - Fire Breather - LAUREL</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>לביא לוי - נווה הדרים קאבר</v>
+        <v>The Warning - Ego (Performance Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>2026-06-03</v>
+        <v>4d ago</v>
       </c>
       <c r="C17" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411184&amp;sid=a85ca8ef30bfde649d428d952bc8fa37</v>
+        <v>https://www.youtube.com/watch?v=7PApWObImjo</v>
       </c>
       <c r="D17" t="str">
         <v>2026-06-03</v>
@@ -1021,16 +1021,16 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v/>
+        <v>4d ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
       </c>
       <c r="H17" t="str">
-        <v/>
+        <v>The Warning</v>
       </c>
       <c r="I17" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J17" t="str">
         <v/>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>לביא לוי - נווה הדרים קאבר</v>
+        <v>The Warning - Ego (Performance Video) - The Warning</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>יאיר ברוך - נווה הדרים קאבר</v>
+        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (feat. Gabito Ballesteros) [Official Lyric Video]</v>
       </c>
       <c r="B18" t="str">
-        <v>2026-06-03</v>
+        <v>4d ago</v>
       </c>
       <c r="C18" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411183&amp;sid=a85ca8ef30bfde649d428d952bc8fa37</v>
+        <v>https://www.youtube.com/watch?v=vruZSAYJBe4</v>
       </c>
       <c r="D18" t="str">
         <v>2026-06-03</v>
@@ -1059,16 +1059,16 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v/>
+        <v>4d ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
       </c>
       <c r="H18" t="str">
-        <v/>
+        <v>David Guetta and Jennifer Lopez</v>
       </c>
       <c r="I18" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J18" t="str">
         <v/>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>יאיר ברוך - נווה הדרים קאבר</v>
+        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (feat. Gabito Ballesteros) [Official Lyric Video] - David Guetta and Jennifer Lopez</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>אילון לוי - עוד ישמע קאבר</v>
+        <v>Armin van Buuren - Equanimity (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B19" t="str">
-        <v>2026-06-03</v>
+        <v>4d ago</v>
       </c>
       <c r="C19" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411181&amp;sid=a85ca8ef30bfde649d428d952bc8fa37</v>
+        <v>https://www.youtube.com/watch?v=k93t10R-Qrg</v>
       </c>
       <c r="D19" t="str">
         <v>2026-06-03</v>
@@ -1097,16 +1097,16 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v/>
+        <v>4d ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
       </c>
       <c r="H19" t="str">
-        <v/>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I19" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J19" t="str">
         <v/>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>אילון לוי - עוד ישמע קאבר</v>
+        <v>Armin van Buuren - Equanimity (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>אבישי עוזיאל - מחזיק לך תיד קאבר</v>
+        <v>“I Didn’t Know What Time It Was” - Andrew Bird Jazz Trio (Live from The Green Mill)</v>
       </c>
       <c r="B20" t="str">
-        <v>2026-06-03</v>
+        <v>5d ago</v>
       </c>
       <c r="C20" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411180&amp;sid=a85ca8ef30bfde649d428d952bc8fa37</v>
+        <v>https://www.youtube.com/watch?v=XyRgdfXo2nI</v>
       </c>
       <c r="D20" t="str">
         <v>2026-06-03</v>
@@ -1135,16 +1135,16 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v/>
+        <v>5d ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
       </c>
       <c r="H20" t="str">
-        <v/>
+        <v>Andrew Bird</v>
       </c>
       <c r="I20" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J20" t="str">
         <v/>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>אבישי עוזיאל - מחזיק לך תיד קאבר</v>
+        <v>“I Didn’t Know What Time It Was” - Andrew Bird Jazz Trio (Live from The Green Mill) - Andrew Bird</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Just Slide Official Music Video | Kelly Boesch | 4K</v>
+        <v>Freya Ridings - Mother Of Pearl (Official Lyric Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>8h ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=lC14fuU8aPc</v>
+        <v>https://www.youtube.com/watch?v=7SGzYAZ0oxM</v>
       </c>
       <c r="D21" t="str">
         <v>2026-06-03</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>8h ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>Kelly Boesch AI Art</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Just Slide Official Music Video | Kelly Boesch | 4K - Kelly Boesch AI Art</v>
+        <v>Freya Ridings - Mother Of Pearl (Official Lyric Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Europe - The Cult of Ignorance (Official Video)</v>
+        <v>Danny Gokey - God's Not (Official Music Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>10h ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=p-IOsjOJpnA</v>
+        <v>https://www.youtube.com/watch?v=oGpKqX6ftcU</v>
       </c>
       <c r="D22" t="str">
         <v>2026-06-03</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>10h ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>Europe</v>
+        <v>Danny Gokey</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Europe - The Cult of Ignorance (Official Video) - Europe</v>
+        <v>Danny Gokey - God's Not (Official Music Video) - Danny Gokey</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Air Supply - Sweet Dreams (Official Lyric Video)</v>
+        <v>Armik - Brisas (2026 Remaster/Remix) (Exciting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B23" t="str">
-        <v>14h ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=axiK2vYjXio</v>
+        <v>https://www.youtube.com/watch?v=51Zu2iU2z2Q</v>
       </c>
       <c r="D23" t="str">
         <v>2026-06-03</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>14h ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>Air Supply</v>
+        <v>Armik</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Air Supply - Sweet Dreams (Official Lyric Video) - Air Supply</v>
+        <v>Armik - Brisas (2026 Remaster/Remix) (Exciting Rumba Flamenco, Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Culture Club - Cold Shoulder</v>
+        <v>Holly Humberstone - Lucy (Free People Sessions)</v>
       </c>
       <c r="B24" t="str">
-        <v>22h ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=-YV4SCXFNyg</v>
+        <v>https://www.youtube.com/watch?v=c1GR2TTs9W8</v>
       </c>
       <c r="D24" t="str">
         <v>2026-06-03</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>22h ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>Culture Club</v>
+        <v>Holly Humberstone and Free People</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Culture Club - Cold Shoulder - Culture Club</v>
+        <v>Holly Humberstone - Lucy (Free People Sessions) - Holly Humberstone and Free People</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Julia Cole - Treat Me Like Dirt (Official Lyric Video)</v>
+        <v>The Offspring - Why Don’t You Get a Job? | Live at BeachLife Festival 2026</v>
       </c>
       <c r="B25" t="str">
-        <v>22h ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=TS2Mgp5F0cs</v>
+        <v>https://www.youtube.com/watch?v=zRJ2etb_rpI</v>
       </c>
       <c r="D25" t="str">
         <v>2026-06-03</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>22h ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>Julia Cole Music</v>
+        <v>The Offspring</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Julia Cole - Treat Me Like Dirt (Official Lyric Video) - Julia Cole Music</v>
+        <v>The Offspring - Why Don’t You Get a Job? | Live at BeachLife Festival 2026 - The Offspring</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Allen Stone - A Fathers Song - Placeholder Sessions</v>
+        <v>Jagwar Twin, sir lucius - bad feeling (oompa loompa) (Visualizer)</v>
       </c>
       <c r="B26" t="str">
-        <v>23h ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=JPetpt4QMPE</v>
+        <v>https://www.youtube.com/watch?v=XGgI5HvR-gg</v>
       </c>
       <c r="D26" t="str">
         <v>2026-06-03</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>23h ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>Allen Stone and Placeholder Sessions</v>
+        <v>Jagwar Twin</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Allen Stone - A Fathers Song - Placeholder Sessions - Allen Stone and Placeholder Sessions</v>
+        <v>Jagwar Twin, sir lucius - bad feeling (oompa loompa) (Visualizer) - Jagwar Twin</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Morgan Wallen - Don't We (Live From Tuscaloosa)</v>
+        <v>Nathan Evans x SAINT PHNX - Home (World Cup 2026) (Official Music Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>1d ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=qhmWM3uXPAU</v>
+        <v>https://www.youtube.com/watch?v=lRBNYETENNg</v>
       </c>
       <c r="D27" t="str">
         <v>2026-06-03</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>1d ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
       </c>
       <c r="H27" t="str">
-        <v>Morgan Wallen</v>
+        <v>NathanEvanss</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Morgan Wallen - Don't We (Live From Tuscaloosa) - Morgan Wallen</v>
+        <v>Nathan Evans x SAINT PHNX - Home (World Cup 2026) (Official Music Video) - NathanEvanss</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Billy Idol - John Wayne feat. Alison Mosshart (Official Music Video)</v>
+        <v>Greta Van Fleet - Play Your Games (Official Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>1d ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=47LNk7oiTVI</v>
+        <v>https://www.youtube.com/watch?v=CJsfI1QVBEM</v>
       </c>
       <c r="D28" t="str">
         <v>2026-06-03</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>1d ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>Billy Idol</v>
+        <v>Greta Van Fleet</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Billy Idol - John Wayne feat. Alison Mosshart (Official Music Video) - Billy Idol</v>
+        <v>Greta Van Fleet - Play Your Games (Official Video) - Greta Van Fleet</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>'It's Unusual' Official Music Video - Kelly Boesch | 4K</v>
+        <v>Lola Young – From Down Here (From a Living Room)</v>
       </c>
       <c r="B29" t="str">
         <v>5d ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=Ru3fB2l1RSo</v>
+        <v>https://www.youtube.com/watch?v=uF5HUfho2NU</v>
       </c>
       <c r="D29" t="str">
         <v>2026-06-03</v>
@@ -1483,7 +1483,7 @@
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>Kelly Boesch AI Art</v>
+        <v>Lola Young</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>'It's Unusual' Official Music Video - Kelly Boesch | 4K - Kelly Boesch AI Art</v>
+        <v>Lola Young – From Down Here (From a Living Room) - Lola Young</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Icona Pop - Butterfly Feelings (Official Video)</v>
+        <v>Lawrence - Rain Check ft. Quinn XCII (Lyric Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>1d ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=AMW1Zq9RbIU</v>
+        <v>https://www.youtube.com/watch?v=xXeyznlIrFY</v>
       </c>
       <c r="D30" t="str">
         <v>2026-06-03</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>1d ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>Icona Pop</v>
+        <v>Lawrence and Quinn XCII</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Icona Pop - Butterfly Feelings (Official Video) - Icona Pop</v>
+        <v>Lawrence - Rain Check ft. Quinn XCII (Lyric Video) - Lawrence and Quinn XCII</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Hippo Campus - South</v>
+        <v>ANTONIA - NO HATE | Official Music Video</v>
       </c>
       <c r="B31" t="str">
-        <v>2d ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=FYOmFfV7Ojo</v>
+        <v>https://www.youtube.com/watch?v=rhlONr1DTj0</v>
       </c>
       <c r="D31" t="str">
         <v>2026-06-03</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>2d ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>Hippo Campus</v>
+        <v>ANTONIA</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Hippo Campus - South - Hippo Campus</v>
+        <v>ANTONIA - NO HATE | Official Music Video - ANTONIA</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>elijah woods - Old (Treehouse Sessions)</v>
+        <v>R3HAB - "Lost in translation..." (Official Lyric Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>2d ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=yDlkPdR_6zM</v>
+        <v>https://www.youtube.com/watch?v=TbJtz0oy2cI</v>
       </c>
       <c r="D32" t="str">
         <v>2026-06-03</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>2d ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
       </c>
       <c r="H32" t="str">
-        <v>elijah woods</v>
+        <v>R3HAB</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>elijah woods - Old (Treehouse Sessions) - elijah woods</v>
+        <v>R3HAB - "Lost in translation..." (Official Lyric Video) - R3HAB</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Nothing But Thieves - Evolution (Official Video)</v>
+        <v>Pink Floyd - Shine On You Crazy Diamond (Parts 1-5) - Live in Venice (Official Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>2d ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=hmjfuuuRRYU</v>
+        <v>https://www.youtube.com/watch?v=kwiawhDk2TM</v>
       </c>
       <c r="D33" t="str">
         <v>2026-06-03</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>2d ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Pink Floyd</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Nothing But Thieves - Evolution (Official Video) - Nothing But Thieves</v>
+        <v>Pink Floyd - Shine On You Crazy Diamond (Parts 1-5) - Live in Venice (Official Video) - Pink Floyd</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Ariana Grande - hate that i made you love me</v>
+        <v>SHADE - TOXIC</v>
       </c>
       <c r="B34" t="str">
-        <v>2d ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=82-jTNka3uc</v>
+        <v>https://www.youtube.com/watch?v=A3km0zrBKSg</v>
       </c>
       <c r="D34" t="str">
         <v>2026-06-03</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>2d ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>Ariana Grande</v>
+        <v>Shade Official Channel</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Ariana Grande - hate that i made you love me - Ariana Grande</v>
+        <v>SHADE - TOXIC - Shade Official Channel</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>LAUREL - Fire Breather</v>
+        <v>Dua Lipa - Physical (Live From Mexico)</v>
       </c>
       <c r="B35" t="str">
-        <v>2d ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=rtyavLIJjy0</v>
+        <v>https://www.youtube.com/watch?v=xZAe-d3bXTs</v>
       </c>
       <c r="D35" t="str">
         <v>2026-06-03</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>2d ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
       </c>
       <c r="H35" t="str">
-        <v>LAUREL</v>
+        <v>Dua Lipa</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>LAUREL - Fire Breather - LAUREL</v>
+        <v>Dua Lipa - Physical (Live From Mexico) - Dua Lipa</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>The Warning - Ego (Performance Video)</v>
+        <v>Dagny - Rain (Lyric Video)</v>
       </c>
       <c r="B36" t="str">
-        <v>4d ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=7PApWObImjo</v>
+        <v>https://www.youtube.com/watch?v=j3ZJwczZoUQ</v>
       </c>
       <c r="D36" t="str">
         <v>2026-06-03</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>4d ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>The Warning</v>
+        <v>Dagny</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>The Warning - Ego (Performance Video) - The Warning</v>
+        <v>Dagny - Rain (Lyric Video) - Dagny</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (feat. Gabito Ballesteros) [Official Lyric Video]</v>
+        <v>Modern Talking - Cheri Cheri Lady (Auf los geht's los, 14.09.1985)</v>
       </c>
       <c r="B37" t="str">
-        <v>4d ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=vruZSAYJBe4</v>
+        <v>https://www.youtube.com/watch?v=c0LtTVKNwNA</v>
       </c>
       <c r="D37" t="str">
         <v>2026-06-03</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>4d ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>David Guetta and Jennifer Lopez</v>
+        <v>Modern Talking Offiziell</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (feat. Gabito Ballesteros) [Official Lyric Video] - David Guetta and Jennifer Lopez</v>
+        <v>Modern Talking - Cheri Cheri Lady (Auf los geht's los, 14.09.1985) - Modern Talking Offiziell</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Armin van Buuren - Equanimity (from 'Piano' album) [Official Video]</v>
+        <v>The Chemical Brothers - Go (Live Show Visual)</v>
       </c>
       <c r="B38" t="str">
-        <v>4d ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=k93t10R-Qrg</v>
+        <v>https://www.youtube.com/watch?v=fHCIchBq8CM</v>
       </c>
       <c r="D38" t="str">
         <v>2026-06-03</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>4d ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
       </c>
       <c r="H38" t="str">
-        <v>Armin van Buuren</v>
+        <v>The Chemical Brothers</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Armin van Buuren - Equanimity (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>The Chemical Brothers - Go (Live Show Visual) - The Chemical Brothers</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>“I Didn’t Know What Time It Was” - Andrew Bird Jazz Trio (Live from The Green Mill)</v>
+        <v>Jonas Blue - Girl (Official Lyric Video)</v>
       </c>
       <c r="B39" t="str">
         <v>5d ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=XyRgdfXo2nI</v>
+        <v>https://www.youtube.com/watch?v=FTUe3jzUqXU</v>
       </c>
       <c r="D39" t="str">
         <v>2026-06-03</v>
@@ -1863,7 +1863,7 @@
         <v/>
       </c>
       <c r="H39" t="str">
-        <v>Andrew Bird</v>
+        <v>Defected Records and Jonas Blue</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>“I Didn’t Know What Time It Was” - Andrew Bird Jazz Trio (Live from The Green Mill) - Andrew Bird</v>
+        <v>Jonas Blue - Girl (Official Lyric Video) - Defected Records and Jonas Blue</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Freya Ridings - Mother Of Pearl (Official Lyric Video)</v>
+        <v>Dogpark - Don't Lie (Visualizer)</v>
       </c>
       <c r="B40" t="str">
         <v>5d ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=7SGzYAZ0oxM</v>
+        <v>https://www.youtube.com/watch?v=is7qKBRycJI</v>
       </c>
       <c r="D40" t="str">
         <v>2026-06-03</v>
@@ -1901,7 +1901,7 @@
         <v/>
       </c>
       <c r="H40" t="str">
-        <v>Freya Ridings</v>
+        <v>Dogpark</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Freya Ridings - Mother Of Pearl (Official Lyric Video) - Freya Ridings</v>
+        <v>Dogpark - Don't Lie (Visualizer) - Dogpark</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Danny Gokey - God's Not (Official Music Video)</v>
+        <v>elijah woods - L-O-V-E (Treehouse Sessions)</v>
       </c>
       <c r="B41" t="str">
         <v>5d ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=oGpKqX6ftcU</v>
+        <v>https://www.youtube.com/watch?v=q5kN7eH6rgo</v>
       </c>
       <c r="D41" t="str">
         <v>2026-06-03</v>
@@ -1939,7 +1939,7 @@
         <v/>
       </c>
       <c r="H41" t="str">
-        <v>Danny Gokey</v>
+        <v>elijah woods</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Danny Gokey - God's Not (Official Music Video) - Danny Gokey</v>
+        <v>elijah woods - L-O-V-E (Treehouse Sessions) - elijah woods</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Armik - Brisas (2026 Remaster/Remix) (Exciting Rumba Flamenco, Spanish Guitar)</v>
+        <v>Lauren Alaina - Better Off (Official Audio)</v>
       </c>
       <c r="B42" t="str">
         <v>5d ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=51Zu2iU2z2Q</v>
+        <v>https://www.youtube.com/watch?v=Vj-ong3XNHM</v>
       </c>
       <c r="D42" t="str">
         <v>2026-06-03</v>
@@ -1977,7 +1977,7 @@
         <v/>
       </c>
       <c r="H42" t="str">
-        <v>Armik</v>
+        <v>Lauren Alaina</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Armik - Brisas (2026 Remaster/Remix) (Exciting Rumba Flamenco, Spanish Guitar) - Armik</v>
+        <v>Lauren Alaina - Better Off (Official Audio) - Lauren Alaina</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Holly Humberstone - Lucy (Free People Sessions)</v>
+        <v>Lauren Sanderson - ARE YOU REALLY HERE? (Lyric Video)</v>
       </c>
       <c r="B43" t="str">
         <v>5d ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=c1GR2TTs9W8</v>
+        <v>https://www.youtube.com/watch?v=u7Et_hbMZUA</v>
       </c>
       <c r="D43" t="str">
         <v>2026-06-03</v>
@@ -2015,7 +2015,7 @@
         <v/>
       </c>
       <c r="H43" t="str">
-        <v>Holly Humberstone and Free People</v>
+        <v>Lauren Sanderson</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Holly Humberstone - Lucy (Free People Sessions) - Holly Humberstone and Free People</v>
+        <v>Lauren Sanderson - ARE YOU REALLY HERE? (Lyric Video) - Lauren Sanderson</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>The Offspring - Why Don’t You Get a Job? | Live at BeachLife Festival 2026</v>
+        <v>Nightly – blue jeans (Official Lyric Video)</v>
       </c>
       <c r="B44" t="str">
         <v>5d ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=zRJ2etb_rpI</v>
+        <v>https://www.youtube.com/watch?v=LnA3xkXUwaM</v>
       </c>
       <c r="D44" t="str">
         <v>2026-06-03</v>
@@ -2053,7 +2053,7 @@
         <v/>
       </c>
       <c r="H44" t="str">
-        <v>The Offspring</v>
+        <v>NIGHTLY</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>The Offspring - Why Don’t You Get a Job? | Live at BeachLife Festival 2026 - The Offspring</v>
+        <v>Nightly – blue jeans (Official Lyric Video) - NIGHTLY</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Jagwar Twin, sir lucius - bad feeling (oompa loompa) (Visualizer)</v>
+        <v>Dasha - Mad About It (Official Visualizer)</v>
       </c>
       <c r="B45" t="str">
         <v>5d ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=XGgI5HvR-gg</v>
+        <v>https://www.youtube.com/watch?v=Ae1gf_7p3H8</v>
       </c>
       <c r="D45" t="str">
         <v>2026-06-03</v>
@@ -2091,7 +2091,7 @@
         <v/>
       </c>
       <c r="H45" t="str">
-        <v>Jagwar Twin</v>
+        <v>Dasha</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Jagwar Twin, sir lucius - bad feeling (oompa loompa) (Visualizer) - Jagwar Twin</v>
+        <v>Dasha - Mad About It (Official Visualizer) - Dasha</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Nathan Evans x SAINT PHNX - Home (World Cup 2026) (Official Music Video)</v>
+        <v>Max McNown - Something To Someone (Performance Video)</v>
       </c>
       <c r="B46" t="str">
         <v>5d ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=lRBNYETENNg</v>
+        <v>https://www.youtube.com/watch?v=4Ki4ejT86YM</v>
       </c>
       <c r="D46" t="str">
         <v>2026-06-03</v>
@@ -2129,7 +2129,7 @@
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>NathanEvanss</v>
+        <v>Max McNown</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Nathan Evans x SAINT PHNX - Home (World Cup 2026) (Official Music Video) - NathanEvanss</v>
+        <v>Max McNown - Something To Someone (Performance Video) - Max McNown</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Greta Van Fleet - Play Your Games (Official Video)</v>
+        <v>Bebe Rexha &amp; David Guetta - Sad Girls (Official Visual)</v>
       </c>
       <c r="B47" t="str">
         <v>5d ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=CJsfI1QVBEM</v>
+        <v>https://www.youtube.com/watch?v=P8UqZ5IF-QE</v>
       </c>
       <c r="D47" t="str">
         <v>2026-06-03</v>
@@ -2167,7 +2167,7 @@
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>Greta Van Fleet</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Greta Van Fleet - Play Your Games (Official Video) - Greta Van Fleet</v>
+        <v>Bebe Rexha &amp; David Guetta - Sad Girls (Official Visual) - Bebe Rexha</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Lola Young – From Down Here (From a Living Room)</v>
+        <v>Knox - Long Story Short (Official Video)</v>
       </c>
       <c r="B48" t="str">
         <v>5d ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=uF5HUfho2NU</v>
+        <v>https://www.youtube.com/watch?v=5OGY6hCELfg</v>
       </c>
       <c r="D48" t="str">
         <v>2026-06-03</v>
@@ -2205,7 +2205,7 @@
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>Lola Young</v>
+        <v>Knox</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Lola Young – From Down Here (From a Living Room) - Lola Young</v>
+        <v>Knox - Long Story Short (Official Video) - Knox</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Lawrence - Rain Check ft. Quinn XCII (Lyric Video)</v>
+        <v>Sofia Camara - The Last Encounter</v>
       </c>
       <c r="B49" t="str">
         <v>5d ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=xXeyznlIrFY</v>
+        <v>https://www.youtube.com/watch?v=E9kN4HLGG1c</v>
       </c>
       <c r="D49" t="str">
         <v>2026-06-03</v>
@@ -2243,7 +2243,7 @@
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>Lawrence and Quinn XCII</v>
+        <v>Sofia Camara</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Lawrence - Rain Check ft. Quinn XCII (Lyric Video) - Lawrence and Quinn XCII</v>
+        <v>Sofia Camara - The Last Encounter - Sofia Camara</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>ANTONIA - NO HATE | Official Music Video</v>
+        <v>Official Music Video: "Flowers" -- Alexander James</v>
       </c>
       <c r="B50" t="str">
         <v>5d ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=rhlONr1DTj0</v>
+        <v>https://www.youtube.com/watch?v=aZ4WP0P92tM</v>
       </c>
       <c r="D50" t="str">
         <v>2026-06-03</v>
@@ -2281,7 +2281,7 @@
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>ANTONIA</v>
+        <v>Alexander James</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>ANTONIA - NO HATE | Official Music Video - ANTONIA</v>
+        <v>Official Music Video: "Flowers" -- Alexander James - Alexander James</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>R3HAB - "Lost in translation..." (Official Lyric Video)</v>
+        <v>almost monday - skinny dip (official video)</v>
       </c>
       <c r="B51" t="str">
         <v>5d ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=TbJtz0oy2cI</v>
+        <v>https://www.youtube.com/watch?v=hOxZDoaIzKQ</v>
       </c>
       <c r="D51" t="str">
         <v>2026-06-03</v>
@@ -2319,7 +2319,7 @@
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>R3HAB</v>
+        <v>almost monday</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>R3HAB - "Lost in translation..." (Official Lyric Video) - R3HAB</v>
+        <v>almost monday - skinny dip (official video) - almost monday</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Pink Floyd - Shine On You Crazy Diamond (Parts 1-5) - Live in Venice (Official Video)</v>
+        <v>Kip Moore - The Darkness (Official)</v>
       </c>
       <c r="B52" t="str">
         <v>5d ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=kwiawhDk2TM</v>
+        <v>https://www.youtube.com/watch?v=lTqqixCt5Mk</v>
       </c>
       <c r="D52" t="str">
         <v>2026-06-03</v>
@@ -2357,7 +2357,7 @@
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>Pink Floyd</v>
+        <v>Kip Moore</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Pink Floyd - Shine On You Crazy Diamond (Parts 1-5) - Live in Venice (Official Video) - Pink Floyd</v>
+        <v>Kip Moore - The Darkness (Official) - Kip Moore</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>SHADE - TOXIC</v>
+        <v>Paul McCartney - Come Inside (Lyric Video)</v>
       </c>
       <c r="B53" t="str">
         <v>5d ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=A3km0zrBKSg</v>
+        <v>https://www.youtube.com/watch?v=C8Zw_Cbm2V0</v>
       </c>
       <c r="D53" t="str">
         <v>2026-06-03</v>
@@ -2395,7 +2395,7 @@
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>Shade Official Channel</v>
+        <v>PAUL McCARTNEY</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>SHADE - TOXIC - Shade Official Channel</v>
+        <v>Paul McCartney - Come Inside (Lyric Video) - PAUL McCARTNEY</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Dua Lipa - Physical (Live From Mexico)</v>
+        <v>Santana, Becky G - Mi Gran Amor (Official Lyric Video)</v>
       </c>
       <c r="B54" t="str">
         <v>5d ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=xZAe-d3bXTs</v>
+        <v>https://www.youtube.com/watch?v=btdBd_Yee8E</v>
       </c>
       <c r="D54" t="str">
         <v>2026-06-03</v>
@@ -2433,7 +2433,7 @@
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>Dua Lipa</v>
+        <v>Santana</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Dua Lipa - Physical (Live From Mexico) - Dua Lipa</v>
+        <v>Santana, Becky G - Mi Gran Amor (Official Lyric Video) - Santana</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Dagny - Rain (Lyric Video)</v>
+        <v>Dua Lipa - Training Season (Live From Mexico)</v>
       </c>
       <c r="B55" t="str">
-        <v>5d ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=j3ZJwczZoUQ</v>
+        <v>https://www.youtube.com/watch?v=Va8Udsvqigs</v>
       </c>
       <c r="D55" t="str">
         <v>2026-06-03</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>5d ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>Dagny</v>
+        <v>Dua Lipa</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Dagny - Rain (Lyric Video) - Dagny</v>
+        <v>Dua Lipa - Training Season (Live From Mexico) - Dua Lipa</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Modern Talking - Cheri Cheri Lady (Auf los geht's los, 14.09.1985)</v>
+        <v>Charley - Liar</v>
       </c>
       <c r="B56" t="str">
-        <v>5d ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=c0LtTVKNwNA</v>
+        <v>https://www.youtube.com/watch?v=3Erfj2Eecgw</v>
       </c>
       <c r="D56" t="str">
         <v>2026-06-03</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>5d ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>Modern Talking Offiziell</v>
+        <v>Charley</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Modern Talking - Cheri Cheri Lady (Auf los geht's los, 14.09.1985) - Modern Talking Offiziell</v>
+        <v>Charley - Liar - Charley</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>The Chemical Brothers - Go (Live Show Visual)</v>
+        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (ft Gabito Ballesteros) [Visualizer]</v>
       </c>
       <c r="B57" t="str">
-        <v>5d ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=fHCIchBq8CM</v>
+        <v>https://www.youtube.com/watch?v=em5ryETDkAo</v>
       </c>
       <c r="D57" t="str">
         <v>2026-06-03</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>5d ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>The Chemical Brothers</v>
+        <v>David Guetta and Jennifer Lopez</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>The Chemical Brothers - Go (Live Show Visual) - The Chemical Brothers</v>
+        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (ft Gabito Ballesteros) [Visualizer] - David Guetta and Jennifer Lopez</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Jonas Blue - Girl (Official Lyric Video)</v>
+        <v>Jordana Bryant - Too Little Too Late (Official Audio)</v>
       </c>
       <c r="B58" t="str">
-        <v>5d ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=FTUe3jzUqXU</v>
+        <v>https://www.youtube.com/watch?v=AmwNx9qlOpA</v>
       </c>
       <c r="D58" t="str">
         <v>2026-06-03</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>5d ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>Defected Records and Jonas Blue</v>
+        <v>Jordana Bryant</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Jonas Blue - Girl (Official Lyric Video) - Defected Records and Jonas Blue</v>
+        <v>Jordana Bryant - Too Little Too Late (Official Audio) - Jordana Bryant</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Dogpark - Don't Lie (Visualizer)</v>
+        <v>Lewis Capaldi - Stay Love (Official Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>5d ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=is7qKBRycJI</v>
+        <v>https://www.youtube.com/watch?v=9Pud3BqPpq0</v>
       </c>
       <c r="D59" t="str">
         <v>2026-06-03</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>5d ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>Dogpark</v>
+        <v>Lewis Capaldi</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Dogpark - Don't Lie (Visualizer) - Dogpark</v>
+        <v>Lewis Capaldi - Stay Love (Official Video) - Lewis Capaldi</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>elijah woods - L-O-V-E (Treehouse Sessions)</v>
+        <v>Surreal World of Oddities - Pulling At My Strings - Official Music Video | 4K</v>
       </c>
       <c r="B60" t="str">
-        <v>5d ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=q5kN7eH6rgo</v>
+        <v>https://www.youtube.com/watch?v=fMt-f2aUW3c</v>
       </c>
       <c r="D60" t="str">
         <v>2026-06-03</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>5d ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>elijah woods</v>
+        <v>Kelly Boesch AI Art</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>elijah woods - L-O-V-E (Treehouse Sessions) - elijah woods</v>
+        <v>Surreal World of Oddities - Pulling At My Strings - Official Music Video | 4K - Kelly Boesch AI Art</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Lauren Alaina - Better Off (Official Audio)</v>
+        <v>Julia Cole - Love You to Death (Official Video)</v>
       </c>
       <c r="B61" t="str">
-        <v>5d ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=Vj-ong3XNHM</v>
+        <v>https://www.youtube.com/watch?v=dWgmFc2QuLY</v>
       </c>
       <c r="D61" t="str">
         <v>2026-06-03</v>
@@ -2693,13 +2693,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>5d ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>Lauren Alaina</v>
+        <v>Julia Cole Music</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Lauren Alaina - Better Off (Official Audio) - Lauren Alaina</v>
+        <v>Julia Cole - Love You to Death (Official Video) - Julia Cole Music</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Lauren Sanderson - ARE YOU REALLY HERE? (Lyric Video)</v>
+        <v>Victor Biliac - De-ai fi tu salcie la mal ( Cover Edit )</v>
       </c>
       <c r="B62" t="str">
-        <v>5d ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=u7Et_hbMZUA</v>
+        <v>https://www.youtube.com/watch?v=v3c0kG-V2zk</v>
       </c>
       <c r="D62" t="str">
         <v>2026-06-03</v>
@@ -2731,13 +2731,13 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>5d ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>Lauren Sanderson</v>
+        <v>VictorBiliac</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Lauren Sanderson - ARE YOU REALLY HERE? (Lyric Video) - Lauren Sanderson</v>
+        <v>Victor Biliac - De-ai fi tu salcie la mal ( Cover Edit ) - VictorBiliac</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Nightly – blue jeans (Official Lyric Video)</v>
+        <v>Lolo Zouaï - Coquelicot (feat. disiz) (Official Video)</v>
       </c>
       <c r="B63" t="str">
-        <v>5d ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=LnA3xkXUwaM</v>
+        <v>https://www.youtube.com/watch?v=-4p6FkrOGT4</v>
       </c>
       <c r="D63" t="str">
         <v>2026-06-03</v>
@@ -2769,13 +2769,13 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>5d ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>NIGHTLY</v>
+        <v>Lolo Zouaï and disiz</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Nightly – blue jeans (Official Lyric Video) - NIGHTLY</v>
+        <v>Lolo Zouaï - Coquelicot (feat. disiz) (Official Video) - Lolo Zouaï and disiz</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Dasha - Mad About It (Official Visualizer)</v>
+        <v>Jungle - The Wave (Official Video)</v>
       </c>
       <c r="B64" t="str">
-        <v>5d ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=Ae1gf_7p3H8</v>
+        <v>https://www.youtube.com/watch?v=DW1vUkqNvqQ</v>
       </c>
       <c r="D64" t="str">
         <v>2026-06-03</v>
@@ -2807,13 +2807,13 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>5d ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>Dasha</v>
+        <v>Jungle4eva</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Dasha - Mad About It (Official Visualizer) - Dasha</v>
+        <v>Jungle - The Wave (Official Video) - Jungle4eva</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Max McNown - Something To Someone (Performance Video)</v>
+        <v>Daytime TV – Sun (Official Music Video)</v>
       </c>
       <c r="B65" t="str">
-        <v>5d ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=4Ki4ejT86YM</v>
+        <v>https://www.youtube.com/watch?v=Jqo4ra_ch-M</v>
       </c>
       <c r="D65" t="str">
         <v>2026-06-03</v>
@@ -2845,13 +2845,13 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>5d ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>Max McNown</v>
+        <v>DAYTIME TV</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Max McNown - Something To Someone (Performance Video) - Max McNown</v>
+        <v>Daytime TV – Sun (Official Music Video) - DAYTIME TV</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Bebe Rexha &amp; David Guetta - Sad Girls (Official Visual)</v>
+        <v>Surreal and Strange AI Video | Not Made For The Cage | Kelly Boesch - 4K</v>
       </c>
       <c r="B66" t="str">
-        <v>5d ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=P8UqZ5IF-QE</v>
+        <v>https://www.youtube.com/watch?v=ACNj3L2bzV8</v>
       </c>
       <c r="D66" t="str">
         <v>2026-06-03</v>
@@ -2883,13 +2883,13 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>5d ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>Bebe Rexha</v>
+        <v>Kelly Boesch AI Art</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Bebe Rexha &amp; David Guetta - Sad Girls (Official Visual) - Bebe Rexha</v>
+        <v>Surreal and Strange AI Video | Not Made For The Cage | Kelly Boesch - 4K - Kelly Boesch AI Art</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Knox - Long Story Short (Official Video)</v>
+        <v>Bruno Mars - Risk It All [Live From The Romantic Tour]</v>
       </c>
       <c r="B67" t="str">
-        <v>5d ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=5OGY6hCELfg</v>
+        <v>https://www.youtube.com/watch?v=aFbueod4reQ</v>
       </c>
       <c r="D67" t="str">
         <v>2026-06-03</v>
@@ -2921,13 +2921,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>5d ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>Knox</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Knox - Long Story Short (Official Video) - Knox</v>
+        <v>Bruno Mars - Risk It All [Live From The Romantic Tour] - Bruno Mars</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Sofia Camara - The Last Encounter</v>
+        <v>Keith Urban - Summer Breeze (52nd American Music Awards)</v>
       </c>
       <c r="B68" t="str">
-        <v>5d ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=E9kN4HLGG1c</v>
+        <v>https://www.youtube.com/watch?v=zn-4eVoqofQ</v>
       </c>
       <c r="D68" t="str">
         <v>2026-06-03</v>
@@ -2959,13 +2959,13 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>5d ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>Sofia Camara</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Sofia Camara - The Last Encounter - Sofia Camara</v>
+        <v>Keith Urban - Summer Breeze (52nd American Music Awards) - Keith Urban</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Official Music Video: "Flowers" -- Alexander James</v>
+        <v>Nelly Furtado, Boi-1Da, Canada Soccer - ELECTRIC CIRCUS (Official Music Video)</v>
       </c>
       <c r="B69" t="str">
-        <v>5d ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=aZ4WP0P92tM</v>
+        <v>https://www.youtube.com/watch?v=lHYEMWFuErM</v>
       </c>
       <c r="D69" t="str">
         <v>2026-06-03</v>
@@ -2997,13 +2997,13 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>5d ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>Alexander James</v>
+        <v>Nelly Furtado</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Official Music Video: "Flowers" -- Alexander James - Alexander James</v>
+        <v>Nelly Furtado, Boi-1Da, Canada Soccer - ELECTRIC CIRCUS (Official Music Video) - Nelly Furtado</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>almost monday - skinny dip (official video)</v>
+        <v>Teddy Swims - Mr. Know It All (Live from the AMAs)</v>
       </c>
       <c r="B70" t="str">
-        <v>5d ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=hOxZDoaIzKQ</v>
+        <v>https://www.youtube.com/watch?v=ttM4gWkhZBk</v>
       </c>
       <c r="D70" t="str">
         <v>2026-06-03</v>
@@ -3035,13 +3035,13 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>5d ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>almost monday</v>
+        <v>Teddy Swims and American Music Awards</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>almost monday - skinny dip (official video) - almost monday</v>
+        <v>Teddy Swims - Mr. Know It All (Live from the AMAs) - Teddy Swims and American Music Awards</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Kip Moore - The Darkness (Official)</v>
+        <v>Shakira, Burna Boy - Dai Dai (Official Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>5d ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=lTqqixCt5Mk</v>
+        <v>https://www.youtube.com/watch?v=fcnDmrtj6Sk</v>
       </c>
       <c r="D71" t="str">
         <v>2026-06-03</v>
@@ -3073,13 +3073,13 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>5d ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>Kip Moore</v>
+        <v>Shakira and 2 more</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Kip Moore - The Darkness (Official) - Kip Moore</v>
+        <v>Shakira, Burna Boy - Dai Dai (Official Video) - Shakira and 2 more</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Paul McCartney - Come Inside (Lyric Video)</v>
+        <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards)</v>
       </c>
       <c r="B72" t="str">
-        <v>5d ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=C8Zw_Cbm2V0</v>
+        <v>https://www.youtube.com/watch?v=wacpnp83cJg</v>
       </c>
       <c r="D72" t="str">
         <v>2026-06-03</v>
@@ -3111,13 +3111,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>5d ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>PAUL McCARTNEY</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Paul McCartney - Come Inside (Lyric Video) - PAUL McCARTNEY</v>
+        <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards) - Lainey Wilson</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Santana, Becky G - Mi Gran Amor (Official Lyric Video)</v>
+        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ]</v>
       </c>
       <c r="B73" t="str">
-        <v>5d ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=btdBd_Yee8E</v>
+        <v>https://www.youtube.com/watch?v=w8FTnkNVmq0</v>
       </c>
       <c r="D73" t="str">
         <v>2026-06-03</v>
@@ -3149,13 +3149,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>5d ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>Santana</v>
+        <v>Duran Duran</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Santana, Becky G - Mi Gran Amor (Official Lyric Video) - Santana</v>
+        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ] - Duran Duran</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Dua Lipa - Training Season (Live From Mexico)</v>
+        <v>Nico Santos - Optimist</v>
       </c>
       <c r="B74" t="str">
-        <v>5d ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=Va8Udsvqigs</v>
+        <v>https://www.youtube.com/watch?v=JA6PIcBeKZ0</v>
       </c>
       <c r="D74" t="str">
         <v>2026-06-03</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>5d ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>Dua Lipa</v>
+        <v>Nico Santos</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Dua Lipa - Training Season (Live From Mexico) - Dua Lipa</v>
+        <v>Nico Santos - Optimist - Nico Santos</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Charley - Liar</v>
+        <v>Def Leppard - Personal Jesus (Live at Caesars Palace)</v>
       </c>
       <c r="B75" t="str">
-        <v>5d ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=3Erfj2Eecgw</v>
+        <v>https://www.youtube.com/watch?v=k5SRMgdG4L4</v>
       </c>
       <c r="D75" t="str">
         <v>2026-06-03</v>
@@ -3225,13 +3225,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>5d ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>Charley</v>
+        <v>DEF LEPPARD</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Charley - Liar - Charley</v>
+        <v>Def Leppard - Personal Jesus (Live at Caesars Palace) - DEF LEPPARD</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (ft Gabito Ballesteros) [Visualizer]</v>
+        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer)</v>
       </c>
       <c r="B76" t="str">
-        <v>5d ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=em5ryETDkAo</v>
+        <v>https://www.youtube.com/watch?v=eWSwy9GU2L8</v>
       </c>
       <c r="D76" t="str">
         <v>2026-06-03</v>
@@ -3263,13 +3263,13 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>5d ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>David Guetta and Jennifer Lopez</v>
+        <v>Will Linley</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (ft Gabito Ballesteros) [Visualizer] - David Guetta and Jennifer Lopez</v>
+        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer) - Will Linley</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Jordana Bryant - Too Little Too Late (Official Audio)</v>
+        <v>Kylie Minogue - Story (Official Lyric Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>6d ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=AmwNx9qlOpA</v>
+        <v>https://www.youtube.com/watch?v=fv7_1qKo8mg</v>
       </c>
       <c r="D77" t="str">
         <v>2026-06-03</v>
@@ -3301,13 +3301,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>6d ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>Jordana Bryant</v>
+        <v>Kylie Minogue</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Jordana Bryant - Too Little Too Late (Official Audio) - Jordana Bryant</v>
+        <v>Kylie Minogue - Story (Official Lyric Video) - Kylie Minogue</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Lewis Capaldi - Stay Love (Official Video)</v>
+        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video)</v>
       </c>
       <c r="B78" t="str">
-        <v>6d ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=9Pud3BqPpq0</v>
+        <v>https://www.youtube.com/watch?v=3KUQx2s1fQc</v>
       </c>
       <c r="D78" t="str">
         <v>2026-06-03</v>
@@ -3339,13 +3339,13 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>6d ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>Lewis Capaldi</v>
+        <v>Billy Raffoul</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Lewis Capaldi - Stay Love (Official Video) - Lewis Capaldi</v>
+        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video) - Billy Raffoul</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Surreal World of Oddities - Pulling At My Strings - Official Music Video | 4K</v>
+        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025)</v>
       </c>
       <c r="B79" t="str">
-        <v>7d ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=fMt-f2aUW3c</v>
+        <v>https://www.youtube.com/watch?v=vWf4uiLvwF8</v>
       </c>
       <c r="D79" t="str">
         <v>2026-06-03</v>
@@ -3377,13 +3377,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>7d ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>Kelly Boesch AI Art</v>
+        <v>The Offspring</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Surreal World of Oddities - Pulling At My Strings - Official Music Video | 4K - Kelly Boesch AI Art</v>
+        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025) - The Offspring</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Julia Cole - Love You to Death (Official Video)</v>
+        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024)</v>
       </c>
       <c r="B80" t="str">
-        <v>6d ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=dWgmFc2QuLY</v>
+        <v>https://www.youtube.com/watch?v=9xjMaXegmWM</v>
       </c>
       <c r="D80" t="str">
         <v>2026-06-03</v>
@@ -3415,13 +3415,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>6d ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>Julia Cole Music</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Julia Cole - Love You to Death (Official Video) - Julia Cole Music</v>
+        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024) - David Gilmour</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Victor Biliac - De-ai fi tu salcie la mal ( Cover Edit )</v>
+        <v>Scorpions - Delicate Dance (Madison Square Garden 2022)</v>
       </c>
       <c r="B81" t="str">
-        <v>7d ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=v3c0kG-V2zk</v>
+        <v>https://www.youtube.com/watch?v=yAjEr9WLTnU</v>
       </c>
       <c r="D81" t="str">
         <v>2026-06-03</v>
@@ -3453,13 +3453,13 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>7d ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
       </c>
       <c r="H81" t="str">
-        <v>VictorBiliac</v>
+        <v>Scorpions</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Victor Biliac - De-ai fi tu salcie la mal ( Cover Edit ) - VictorBiliac</v>
+        <v>Scorpions - Delicate Dance (Madison Square Garden 2022) - Scorpions</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Lolo Zouaï - Coquelicot (feat. disiz) (Official Video)</v>
+        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston)</v>
       </c>
       <c r="B82" t="str">
-        <v>7d ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=-4p6FkrOGT4</v>
+        <v>https://www.youtube.com/watch?v=oRw4PqBzGc0</v>
       </c>
       <c r="D82" t="str">
         <v>2026-06-03</v>
@@ -3491,13 +3491,13 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>7d ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
       </c>
       <c r="H82" t="str">
-        <v>Lolo Zouaï and disiz</v>
+        <v>Brandon Lake and NICK JONAS</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Lolo Zouaï - Coquelicot (feat. disiz) (Official Video) - Lolo Zouaï and disiz</v>
+        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston) - Brandon Lake and NICK JONAS</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Jungle - The Wave (Official Video)</v>
+        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B83" t="str">
-        <v>7d ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=DW1vUkqNvqQ</v>
+        <v>https://www.youtube.com/watch?v=OKf_IOGxFQo</v>
       </c>
       <c r="D83" t="str">
         <v>2026-06-03</v>
@@ -3529,13 +3529,13 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>7d ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
       </c>
       <c r="H83" t="str">
-        <v>Jungle4eva</v>
+        <v>Kygo and Dan Tyminski</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Jungle - The Wave (Official Video) - Jungle4eva</v>
+        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video) - Kygo and Dan Tyminski</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Daytime TV – Sun (Official Music Video)</v>
+        <v>The Warning - Ego (Official Video)</v>
       </c>
       <c r="B84" t="str">
-        <v>7d ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=Jqo4ra_ch-M</v>
+        <v>https://www.youtube.com/watch?v=CG6Q5i75bR4</v>
       </c>
       <c r="D84" t="str">
         <v>2026-06-03</v>
@@ -3567,13 +3567,13 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>7d ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
       </c>
       <c r="H84" t="str">
-        <v>DAYTIME TV</v>
+        <v>The Warning</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Daytime TV – Sun (Official Music Video) - DAYTIME TV</v>
+        <v>The Warning - Ego (Official Video) - The Warning</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Surreal and Strange AI Video | Not Made For The Cage | Kelly Boesch - 4K</v>
+        <v>paris jackson - teenage drama (official lyric video)</v>
       </c>
       <c r="B85" t="str">
-        <v>2w ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=ACNj3L2bzV8</v>
+        <v>https://www.youtube.com/watch?v=kVfDArNljos</v>
       </c>
       <c r="D85" t="str">
         <v>2026-06-03</v>
@@ -3605,13 +3605,13 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>2w ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
       </c>
       <c r="H85" t="str">
-        <v>Kelly Boesch AI Art</v>
+        <v>paris jackson</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Surreal and Strange AI Video | Not Made For The Cage | Kelly Boesch - 4K - Kelly Boesch AI Art</v>
+        <v>paris jackson - teenage drama (official lyric video) - paris jackson</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Bruno Mars - Risk It All [Live From The Romantic Tour]</v>
+        <v>Minelli - Sun Goes Down | Official Visualizer</v>
       </c>
       <c r="B86" t="str">
-        <v>8d ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=aFbueod4reQ</v>
+        <v>https://www.youtube.com/watch?v=xOsjm-AwN5I</v>
       </c>
       <c r="D86" t="str">
         <v>2026-06-03</v>
@@ -3643,13 +3643,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>8d ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>Bruno Mars</v>
+        <v>Minelli</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Bruno Mars - Risk It All [Live From The Romantic Tour] - Bruno Mars</v>
+        <v>Minelli - Sun Goes Down | Official Visualizer - Minelli</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Keith Urban - Summer Breeze (52nd American Music Awards)</v>
+        <v>Maggie Rose - Gentle Man (Official Studio Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>8d ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=zn-4eVoqofQ</v>
+        <v>https://www.youtube.com/watch?v=aWNK-vWrN60</v>
       </c>
       <c r="D87" t="str">
         <v>2026-06-03</v>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>8d ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>Keith Urban</v>
+        <v>Maggie Rose</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Keith Urban - Summer Breeze (52nd American Music Awards) - Keith Urban</v>
+        <v>Maggie Rose - Gentle Man (Official Studio Video) - Maggie Rose</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Nelly Furtado, Boi-1Da, Canada Soccer - ELECTRIC CIRCUS (Official Music Video)</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer]</v>
       </c>
       <c r="B88" t="str">
-        <v>8d ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=lHYEMWFuErM</v>
+        <v>https://www.youtube.com/watch?v=mN5AZBrVq9I</v>
       </c>
       <c r="D88" t="str">
         <v>2026-06-03</v>
@@ -3719,13 +3719,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>8d ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>Nelly Furtado</v>
+        <v>David Guetta</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Nelly Furtado, Boi-1Da, Canada Soccer - ELECTRIC CIRCUS (Official Music Video) - Nelly Furtado</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer] - David Guetta</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Teddy Swims - Mr. Know It All (Live from the AMAs)</v>
+        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>8d ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=ttM4gWkhZBk</v>
+        <v>https://www.youtube.com/watch?v=0PTufEGRAVQ</v>
       </c>
       <c r="D89" t="str">
         <v>2026-06-03</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>8d ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>Teddy Swims and American Music Awards</v>
+        <v>Chris Young and Shaylen</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Teddy Swims - Mr. Know It All (Live from the AMAs) - Teddy Swims and American Music Awards</v>
+        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video) - Chris Young and Shaylen</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Shakira, Burna Boy - Dai Dai (Official Video)</v>
+        <v>Lauv - Pretty Little Things</v>
       </c>
       <c r="B90" t="str">
-        <v>11d ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=fcnDmrtj6Sk</v>
+        <v>https://www.youtube.com/watch?v=_JBfanFvHnA</v>
       </c>
       <c r="D90" t="str">
         <v>2026-06-03</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>11d ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>Shakira and 2 more</v>
+        <v>Lauv</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Shakira, Burna Boy - Dai Dai (Official Video) - Shakira and 2 more</v>
+        <v>Lauv - Pretty Little Things - Lauv</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards)</v>
+        <v>Icona Pop - Butterfly Feelings (Official Audio)</v>
       </c>
       <c r="B91" t="str">
-        <v>11d ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=wacpnp83cJg</v>
+        <v>https://www.youtube.com/watch?v=bXA_Q75QZTs</v>
       </c>
       <c r="D91" t="str">
         <v>2026-06-03</v>
@@ -3833,13 +3833,13 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>11d ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>Lainey Wilson</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards) - Lainey Wilson</v>
+        <v>Icona Pop - Butterfly Feelings (Official Audio) - Icona Pop</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ]</v>
+        <v>Will Swinton - Only One (Official Video)</v>
       </c>
       <c r="B92" t="str">
         <v>12d ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=w8FTnkNVmq0</v>
+        <v>https://www.youtube.com/watch?v=A0KzP-zm9hA</v>
       </c>
       <c r="D92" t="str">
         <v>2026-06-03</v>
@@ -3877,7 +3877,7 @@
         <v/>
       </c>
       <c r="H92" t="str">
-        <v>Duran Duran</v>
+        <v>Will Swinton</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ] - Duran Duran</v>
+        <v>Will Swinton - Only One (Official Video) - Will Swinton</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Nico Santos - Optimist</v>
+        <v>Dean Lewis - Escape (Official Video)</v>
       </c>
       <c r="B93" t="str">
-        <v>2w ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=JA6PIcBeKZ0</v>
+        <v>https://www.youtube.com/watch?v=BZRaTXCkhcg</v>
       </c>
       <c r="D93" t="str">
         <v>2026-06-03</v>
@@ -3909,13 +3909,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>2w ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>Nico Santos</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Nico Santos - Optimist - Nico Santos</v>
+        <v>Dean Lewis - Escape (Official Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Def Leppard - Personal Jesus (Live at Caesars Palace)</v>
+        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico]</v>
       </c>
       <c r="B94" t="str">
-        <v>11d ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=k5SRMgdG4L4</v>
+        <v>https://www.youtube.com/watch?v=PNm0hf_zZJY</v>
       </c>
       <c r="D94" t="str">
         <v>2026-06-03</v>
@@ -3947,13 +3947,13 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>11d ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
       </c>
       <c r="H94" t="str">
-        <v>DEF LEPPARD</v>
+        <v>Dua Lipa and OficialMana</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Def Leppard - Personal Jesus (Live at Caesars Palace) - DEF LEPPARD</v>
+        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico] - Dua Lipa and OficialMana</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer)</v>
+        <v>Niall Horan - End of an Era (Lyric Video)</v>
       </c>
       <c r="B95" t="str">
         <v>12d ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=eWSwy9GU2L8</v>
+        <v>https://www.youtube.com/watch?v=EUNNmAAe5gQ</v>
       </c>
       <c r="D95" t="str">
         <v>2026-06-03</v>
@@ -3991,7 +3991,7 @@
         <v/>
       </c>
       <c r="H95" t="str">
-        <v>Will Linley</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer) - Will Linley</v>
+        <v>Niall Horan - End of an Era (Lyric Video) - Niall Horan</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Kylie Minogue - Story (Official Lyric Video)</v>
+        <v>Olivia Rodrigo - the cure (Official Music Video)</v>
       </c>
       <c r="B96" t="str">
         <v>12d ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=fv7_1qKo8mg</v>
+        <v>https://www.youtube.com/watch?v=B402rKl4bUg</v>
       </c>
       <c r="D96" t="str">
         <v>2026-06-03</v>
@@ -4029,7 +4029,7 @@
         <v/>
       </c>
       <c r="H96" t="str">
-        <v>Kylie Minogue</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Kylie Minogue - Story (Official Lyric Video) - Kylie Minogue</v>
+        <v>Olivia Rodrigo - the cure (Official Music Video) - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video)</v>
+        <v>Ruel - Debbie Don't Cry (Official Music Video)</v>
       </c>
       <c r="B97" t="str">
         <v>12d ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=3KUQx2s1fQc</v>
+        <v>https://www.youtube.com/watch?v=iz7wuk0GOwI</v>
       </c>
       <c r="D97" t="str">
         <v>2026-06-03</v>
@@ -4067,7 +4067,7 @@
         <v/>
       </c>
       <c r="H97" t="str">
-        <v>Billy Raffoul</v>
+        <v>RUEL</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video) - Billy Raffoul</v>
+        <v>Ruel - Debbie Don't Cry (Official Music Video) - RUEL</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025)</v>
+        <v>TINI - Down (LIVE)</v>
       </c>
       <c r="B98" t="str">
         <v>12d ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=vWf4uiLvwF8</v>
+        <v>https://www.youtube.com/watch?v=ADbFeQUPTrk</v>
       </c>
       <c r="D98" t="str">
         <v>2026-06-03</v>
@@ -4105,7 +4105,7 @@
         <v/>
       </c>
       <c r="H98" t="str">
-        <v>The Offspring</v>
+        <v>TINI</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025) - The Offspring</v>
+        <v>TINI - Down (LIVE) - TINI</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024)</v>
+        <v>Charli xcx - SS26 (Official Video)</v>
       </c>
       <c r="B99" t="str">
-        <v>12d ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=9xjMaXegmWM</v>
+        <v>https://www.youtube.com/watch?v=twLhSqabby0</v>
       </c>
       <c r="D99" t="str">
         <v>2026-06-03</v>
@@ -4137,13 +4137,13 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>12d ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
       </c>
       <c r="H99" t="str">
-        <v>David Gilmour</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024) - David Gilmour</v>
+        <v>Charli xcx - SS26 (Official Video) - Charli xcx</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Scorpions - Delicate Dance (Madison Square Garden 2022)</v>
+        <v>Dua Lipa - Live From Mexico</v>
       </c>
       <c r="B100" t="str">
-        <v>12d ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=yAjEr9WLTnU</v>
+        <v>https://www.youtube.com/watch?v=vZYVkitGXBU</v>
       </c>
       <c r="D100" t="str">
         <v>2026-06-03</v>
@@ -4175,13 +4175,13 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>12d ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
       </c>
       <c r="H100" t="str">
-        <v>Scorpions</v>
+        <v>Dua Lipa</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Scorpions - Delicate Dance (Madison Square Garden 2022) - Scorpions</v>
+        <v>Dua Lipa - Live From Mexico - Dua Lipa</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston)</v>
+        <v>Matilda Mann - 'The Fig Tree' (Official Video)</v>
       </c>
       <c r="B101" t="str">
-        <v>12d ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=oRw4PqBzGc0</v>
+        <v>https://www.youtube.com/watch?v=XPyubkkkw44</v>
       </c>
       <c r="D101" t="str">
         <v>2026-06-03</v>
@@ -4213,13 +4213,13 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>12d ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G101" t="str">
         <v/>
       </c>
       <c r="H101" t="str">
-        <v>Brandon Lake and NICK JONAS</v>
+        <v>Matilda Mann</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston) - Brandon Lake and NICK JONAS</v>
+        <v>Matilda Mann - 'The Fig Tree' (Official Video) - Matilda Mann</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video)</v>
+        <v>High Hopes 3000</v>
       </c>
       <c r="B102" t="str">
-        <v>12d ago</v>
+        <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=OKf_IOGxFQo</v>
+        <v>https://music.apple.com/us/song/high-hopes-3000/6772366438</v>
       </c>
       <c r="D102" t="str">
         <v>2026-06-03</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>12d ago</v>
+        <v>Chuck Timely &amp; The Hourglass</v>
       </c>
       <c r="G102" t="str">
-        <v/>
+        <v>4:05</v>
       </c>
       <c r="H102" t="str">
-        <v>Kygo and Dan Tyminski</v>
+        <v>ROLE MODEL</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/role-model/199215762</v>
       </c>
       <c r="K102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/high-hopes-3000/6772366436</v>
       </c>
       <c r="L102" t="str">
-        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video) - Kygo and Dan Tyminski</v>
+        <v>High Hopes 3000 - ROLE MODEL</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>The Warning - Ego (Official Video)</v>
+        <v>hate that i made you love me</v>
       </c>
       <c r="B103" t="str">
-        <v>12d ago</v>
+        <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://www.youtube.com/watch?v=CG6Q5i75bR4</v>
+        <v>https://music.apple.com/us/song/hate-that-i-made-you-love-me/6763656876</v>
       </c>
       <c r="D103" t="str">
         <v>2026-06-03</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>12d ago</v>
+        <v>petal</v>
       </c>
       <c r="G103" t="str">
-        <v/>
+        <v>3:17</v>
       </c>
       <c r="H103" t="str">
-        <v>The Warning</v>
+        <v>Ariana Grande</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/ariana-grande/412778295</v>
       </c>
       <c r="K103" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/hate-that-i-made-you-love-me/1895420989</v>
       </c>
       <c r="L103" t="str">
-        <v>The Warning - Ego (Official Video) - The Warning</v>
+        <v>hate that i made you love me - Ariana Grande</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>paris jackson - teenage drama (official lyric video)</v>
+        <v>Come Inside</v>
       </c>
       <c r="B104" t="str">
-        <v>12d ago</v>
+        <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://www.youtube.com/watch?v=kVfDArNljos</v>
+        <v>https://music.apple.com/us/song/come-inside/1887403093</v>
       </c>
       <c r="D104" t="str">
         <v>2026-06-03</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>12d ago</v>
+        <v>The Boys of Dungeon Lane</v>
       </c>
       <c r="G104" t="str">
-        <v/>
+        <v>3:13</v>
       </c>
       <c r="H104" t="str">
-        <v>paris jackson</v>
+        <v>Paul McCartney</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/paul-mccartney/12224</v>
       </c>
       <c r="K104" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/come-inside/1887402919</v>
       </c>
       <c r="L104" t="str">
-        <v>paris jackson - teenage drama (official lyric video) - paris jackson</v>
+        <v>Come Inside - Paul McCartney</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Minelli - Sun Goes Down | Official Visualizer</v>
+        <v>Game Time</v>
       </c>
       <c r="B105" t="str">
-        <v>12d ago</v>
+        <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://www.youtube.com/watch?v=xOsjm-AwN5I</v>
+        <v>https://music.apple.com/us/song/game-time/6771157200</v>
       </c>
       <c r="D105" t="str">
         <v>2026-06-03</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>12d ago</v>
+        <v>Game Time (FIFA World Cup 2026™) - Single</v>
       </c>
       <c r="G105" t="str">
-        <v/>
+        <v>3:26</v>
       </c>
       <c r="H105" t="str">
-        <v>Minelli</v>
+        <v>Future</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/future/128050210</v>
       </c>
       <c r="K105" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/game-time/6771157186</v>
       </c>
       <c r="L105" t="str">
-        <v>Minelli - Sun Goes Down | Official Visualizer - Minelli</v>
+        <v>Game Time - Future</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Maggie Rose - Gentle Man (Official Studio Video)</v>
+        <v>Motion Party (Remix)</v>
       </c>
       <c r="B106" t="str">
-        <v>12d ago</v>
+        <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://www.youtube.com/watch?v=aWNK-vWrN60</v>
+        <v>https://music.apple.com/us/song/motion-party-remix/6773413965</v>
       </c>
       <c r="D106" t="str">
         <v>2026-06-03</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>12d ago</v>
+        <v>Motion Party (Remix) - Single</v>
       </c>
       <c r="G106" t="str">
-        <v/>
+        <v>2:36</v>
       </c>
       <c r="H106" t="str">
-        <v>Maggie Rose</v>
+        <v>Bossman Dlow</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/bossman-dlow/1474308236</v>
       </c>
       <c r="K106" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/motion-party-remix/6773413953</v>
       </c>
       <c r="L106" t="str">
-        <v>Maggie Rose - Gentle Man (Official Studio Video) - Maggie Rose</v>
+        <v>Motion Party (Remix) - Bossman Dlow</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer]</v>
+        <v>Aquel diciembre</v>
       </c>
       <c r="B107" t="str">
-        <v>12d ago</v>
+        <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://www.youtube.com/watch?v=mN5AZBrVq9I</v>
+        <v>https://music.apple.com/us/song/aquel-diciembre/6769580010</v>
       </c>
       <c r="D107" t="str">
         <v>2026-06-03</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>12d ago</v>
+        <v>Do Not Disturb: Late Checkout</v>
       </c>
       <c r="G107" t="str">
-        <v/>
+        <v>3:22</v>
       </c>
       <c r="H107" t="str">
-        <v>David Guetta</v>
+        <v>Young Miko</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/young-miko/1576521417</v>
       </c>
       <c r="K107" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/aquel-diciembre/6769579992</v>
       </c>
       <c r="L107" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer] - David Guetta</v>
+        <v>Aquel diciembre - Young Miko</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video)</v>
+        <v>Handle</v>
       </c>
       <c r="B108" t="str">
-        <v>12d ago</v>
+        <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://www.youtube.com/watch?v=0PTufEGRAVQ</v>
+        <v>https://music.apple.com/us/song/handle/6771922623</v>
       </c>
       <c r="D108" t="str">
         <v>2026-06-03</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>12d ago</v>
+        <v>Blue Island</v>
       </c>
       <c r="G108" t="str">
-        <v/>
+        <v>3:06</v>
       </c>
       <c r="H108" t="str">
-        <v>Chris Young and Shaylen</v>
+        <v>Ravyn Lenae</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/ravyn-lenae/1044417443</v>
       </c>
       <c r="K108" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/handle/6771922622</v>
       </c>
       <c r="L108" t="str">
-        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video) - Chris Young and Shaylen</v>
+        <v>Handle - Ravyn Lenae</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Lauv - Pretty Little Things</v>
+        <v>snake the drain</v>
       </c>
       <c r="B109" t="str">
-        <v>12d ago</v>
+        <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://www.youtube.com/watch?v=_JBfanFvHnA</v>
+        <v>https://music.apple.com/us/song/snake-the-drain/6771506655</v>
       </c>
       <c r="D109" t="str">
         <v>2026-06-03</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>12d ago</v>
+        <v>this time it’s different / snake the drain - Single</v>
       </c>
       <c r="G109" t="str">
-        <v/>
+        <v>3:08</v>
       </c>
       <c r="H109" t="str">
-        <v>Lauv</v>
+        <v>Devon Again</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/devon-again/1574318250</v>
       </c>
       <c r="K109" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/snake-the-drain/6771506650</v>
       </c>
       <c r="L109" t="str">
-        <v>Lauv - Pretty Little Things - Lauv</v>
+        <v>snake the drain - Devon Again</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Icona Pop - Butterfly Feelings (Official Audio)</v>
+        <v>The Wave</v>
       </c>
       <c r="B110" t="str">
-        <v>12d ago</v>
+        <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://www.youtube.com/watch?v=bXA_Q75QZTs</v>
+        <v>https://music.apple.com/us/song/the-wave/1886730541</v>
       </c>
       <c r="D110" t="str">
         <v>2026-06-03</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>12d ago</v>
+        <v>Sunshine</v>
       </c>
       <c r="G110" t="str">
-        <v/>
+        <v>3:22</v>
       </c>
       <c r="H110" t="str">
-        <v>Icona Pop</v>
+        <v>Jungle</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/jungle/825833522</v>
       </c>
       <c r="K110" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/the-wave/1886730527</v>
       </c>
       <c r="L110" t="str">
-        <v>Icona Pop - Butterfly Feelings (Official Audio) - Icona Pop</v>
+        <v>The Wave - Jungle</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Will Swinton - Only One (Official Video)</v>
+        <v>Every Single Weekend (feat. Jamie xx)</v>
       </c>
       <c r="B111" t="str">
-        <v>12d ago</v>
+        <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://www.youtube.com/watch?v=A0KzP-zm9hA</v>
+        <v>https://music.apple.com/us/song/every-single-weekend-feat-jamie-xx/6770445933</v>
       </c>
       <c r="D111" t="str">
         <v>2026-06-03</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>12d ago</v>
+        <v>Every Single Weekend (feat. Jamie xx) - Single</v>
       </c>
       <c r="G111" t="str">
-        <v/>
+        <v>2:10</v>
       </c>
       <c r="H111" t="str">
-        <v>Will Swinton</v>
+        <v>The Avalanches</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/the-avalanches/27524431</v>
       </c>
       <c r="K111" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/every-single-weekend-feat-jamie-xx/6770445752</v>
       </c>
       <c r="L111" t="str">
-        <v>Will Swinton - Only One (Official Video) - Will Swinton</v>
+        <v>Every Single Weekend (feat. Jamie xx) - The Avalanches</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Dean Lewis - Escape (Official Video)</v>
+        <v>STOP</v>
       </c>
       <c r="B112" t="str">
-        <v>12d ago</v>
+        <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://www.youtube.com/watch?v=BZRaTXCkhcg</v>
+        <v>https://music.apple.com/us/song/stop/6771161771</v>
       </c>
       <c r="D112" t="str">
         <v>2026-06-03</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>12d ago</v>
+        <v>are you mad at me? - Single</v>
       </c>
       <c r="G112" t="str">
-        <v/>
+        <v>2:56</v>
       </c>
       <c r="H112" t="str">
-        <v>Dean Lewis</v>
+        <v>Bella Kay</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
       </c>
       <c r="K112" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/stop/6771161760</v>
       </c>
       <c r="L112" t="str">
-        <v>Dean Lewis - Escape (Official Video) - Dean Lewis</v>
+        <v>STOP - Bella Kay</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico]</v>
+        <v>Here (Apple Music Sessions)</v>
       </c>
       <c r="B113" t="str">
-        <v>12d ago</v>
+        <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://www.youtube.com/watch?v=PNm0hf_zZJY</v>
+        <v>https://music.apple.com/us/song/here-apple-music-sessions/1878235516</v>
       </c>
       <c r="D113" t="str">
         <v>2026-06-03</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>12d ago</v>
+        <v>Apple Music Sessions</v>
       </c>
       <c r="G113" t="str">
-        <v/>
+        <v>3:08</v>
       </c>
       <c r="H113" t="str">
-        <v>Dua Lipa and OficialMana</v>
+        <v>Mumford &amp; Sons</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/mumford-sons/307699986</v>
       </c>
       <c r="K113" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/here-apple-music-sessions/1878235330</v>
       </c>
       <c r="L113" t="str">
-        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico] - Dua Lipa and OficialMana</v>
+        <v>Here (Apple Music Sessions) - Mumford &amp; Sons</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Niall Horan - End of an Era (Lyric Video)</v>
+        <v>Talk On The Hill</v>
       </c>
       <c r="B114" t="str">
-        <v>12d ago</v>
+        <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://www.youtube.com/watch?v=EUNNmAAe5gQ</v>
+        <v>https://music.apple.com/us/song/talk-on-the-hill/6769524458</v>
       </c>
       <c r="D114" t="str">
         <v>2026-06-03</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>12d ago</v>
+        <v>The Thread</v>
       </c>
       <c r="G114" t="str">
-        <v/>
+        <v>3:27</v>
       </c>
       <c r="H114" t="str">
-        <v>Niall Horan</v>
+        <v>WILLOW</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/willow/400531893</v>
       </c>
       <c r="K114" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/talk-on-the-hill/6769524450</v>
       </c>
       <c r="L114" t="str">
-        <v>Niall Horan - End of an Era (Lyric Video) - Niall Horan</v>
+        <v>Talk On The Hill - WILLOW</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Olivia Rodrigo - the cure (Official Music Video)</v>
+        <v>No Fear</v>
       </c>
       <c r="B115" t="str">
-        <v>12d ago</v>
+        <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://www.youtube.com/watch?v=B402rKl4bUg</v>
+        <v>https://music.apple.com/us/song/no-fear/1880484493</v>
       </c>
       <c r="D115" t="str">
         <v>2026-06-03</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>12d ago</v>
+        <v>For Love of Grace &amp; the Hereafter</v>
       </c>
       <c r="G115" t="str">
-        <v/>
+        <v>3:38</v>
       </c>
       <c r="H115" t="str">
-        <v>Olivia Rodrigo</v>
+        <v>Iceage</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/iceage/406846711</v>
       </c>
       <c r="K115" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/no-fear/1880484160</v>
       </c>
       <c r="L115" t="str">
-        <v>Olivia Rodrigo - the cure (Official Music Video) - Olivia Rodrigo</v>
+        <v>No Fear - Iceage</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Ruel - Debbie Don't Cry (Official Music Video)</v>
+        <v>Hostage</v>
       </c>
       <c r="B116" t="str">
-        <v>12d ago</v>
+        <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://www.youtube.com/watch?v=iz7wuk0GOwI</v>
+        <v>https://music.apple.com/us/song/hostage/6774372288</v>
       </c>
       <c r="D116" t="str">
         <v>2026-06-03</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>12d ago</v>
+        <v>Big Mama</v>
       </c>
       <c r="G116" t="str">
-        <v/>
+        <v>3:11</v>
       </c>
       <c r="H116" t="str">
-        <v>RUEL</v>
+        <v>Latto</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/latto/419799506</v>
       </c>
       <c r="K116" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/hostage/6774372200</v>
       </c>
       <c r="L116" t="str">
-        <v>Ruel - Debbie Don't Cry (Official Music Video) - RUEL</v>
+        <v>Hostage - Latto</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>TINI - Down (LIVE)</v>
+        <v>Sad Girls</v>
       </c>
       <c r="B117" t="str">
-        <v>12d ago</v>
+        <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://www.youtube.com/watch?v=ADbFeQUPTrk</v>
+        <v>https://music.apple.com/us/song/sad-girls/6768814374</v>
       </c>
       <c r="D117" t="str">
         <v>2026-06-03</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>12d ago</v>
+        <v>Sad Girls - Single</v>
       </c>
       <c r="G117" t="str">
-        <v/>
+        <v>2:48</v>
       </c>
       <c r="H117" t="str">
-        <v>TINI</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/bebe-rexha/466059563</v>
       </c>
       <c r="K117" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/sad-girls/6768814373</v>
       </c>
       <c r="L117" t="str">
-        <v>TINI - Down (LIVE) - TINI</v>
+        <v>Sad Girls - Bebe Rexha</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Charli xcx - SS26 (Official Video)</v>
+        <v>Salvame Hoy (feat. Gabito Ballesteros)</v>
       </c>
       <c r="B118" t="str">
-        <v>12d ago</v>
+        <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://www.youtube.com/watch?v=twLhSqabby0</v>
+        <v>https://music.apple.com/us/song/salvame-hoy-feat-gabito-ballesteros/6765697019</v>
       </c>
       <c r="D118" t="str">
         <v>2026-06-03</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>12d ago</v>
+        <v>Salvame Hoy (feat. Gabito Ballesteros) - Single</v>
       </c>
       <c r="G118" t="str">
-        <v/>
+        <v>3:35</v>
       </c>
       <c r="H118" t="str">
-        <v>Charli xcx</v>
+        <v>Jennifer Lopez</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/jennifer-lopez/463009</v>
       </c>
       <c r="K118" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/salvame-hoy-feat-gabito-ballesteros/1896041010</v>
       </c>
       <c r="L118" t="str">
-        <v>Charli xcx - SS26 (Official Video) - Charli xcx</v>
+        <v>Salvame Hoy (feat. Gabito Ballesteros) - Jennifer Lopez</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Dua Lipa - Live From Mexico</v>
+        <v>Rubio</v>
       </c>
       <c r="B119" t="str">
-        <v>13d ago</v>
+        <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://www.youtube.com/watch?v=vZYVkitGXBU</v>
+        <v>https://music.apple.com/us/song/rubio/6770655339</v>
       </c>
       <c r="D119" t="str">
         <v>2026-06-03</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>13d ago</v>
+        <v>La Voz Favorita</v>
       </c>
       <c r="G119" t="str">
-        <v/>
+        <v>4:42</v>
       </c>
       <c r="H119" t="str">
-        <v>Dua Lipa</v>
+        <v>Jay Wheeler</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/jay-wheeler/164376380</v>
       </c>
       <c r="K119" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/rubio/6770654729</v>
       </c>
       <c r="L119" t="str">
-        <v>Dua Lipa - Live From Mexico - Dua Lipa</v>
+        <v>Rubio - Jay Wheeler</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Matilda Mann - 'The Fig Tree' (Official Video)</v>
+        <v>Pary</v>
       </c>
       <c r="B120" t="str">
-        <v>13d ago</v>
+        <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://www.youtube.com/watch?v=XPyubkkkw44</v>
+        <v>https://music.apple.com/us/song/pary/6767367748</v>
       </c>
       <c r="D120" t="str">
         <v>2026-06-03</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>13d ago</v>
+        <v>Con dolor - EP</v>
       </c>
       <c r="G120" t="str">
-        <v/>
+        <v>2:52</v>
       </c>
       <c r="H120" t="str">
-        <v>Matilda Mann</v>
+        <v>Grupo Frontera</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
       </c>
       <c r="K120" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/pary/6767367501</v>
       </c>
       <c r="L120" t="str">
-        <v>Matilda Mann - 'The Fig Tree' (Official Video) - Matilda Mann</v>
+        <v>Pary - Grupo Frontera</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>High Hopes 3000</v>
+        <v>Think As You Drunk</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/high-hopes-3000/6772366438</v>
+        <v>https://music.apple.com/us/song/think-as-you-drunk/6770725979</v>
       </c>
       <c r="D121" t="str">
         <v>2026-06-03</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Chuck Timely &amp; The Hourglass</v>
+        <v>That's Just Me</v>
       </c>
       <c r="G121" t="str">
-        <v>4:05</v>
+        <v>3:48</v>
       </c>
       <c r="H121" t="str">
-        <v>ROLE MODEL</v>
+        <v>Riley Green</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/role-model/199215762</v>
+        <v>https://music.apple.com/us/artist/riley-green/662432971</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/high-hopes-3000/6772366436</v>
+        <v>https://music.apple.com/us/album/think-as-you-drunk/6770725355</v>
       </c>
       <c r="L121" t="str">
-        <v>High Hopes 3000 - ROLE MODEL</v>
+        <v>Think As You Drunk - Riley Green</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>hate that i made you love me</v>
+        <v>Play Your Games</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/hate-that-i-made-you-love-me/6763656876</v>
+        <v>https://music.apple.com/us/song/play-your-games/6772932837</v>
       </c>
       <c r="D122" t="str">
         <v>2026-06-03</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>petal</v>
+        <v>Play Your Games - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>3:17</v>
+        <v>3:15</v>
       </c>
       <c r="H122" t="str">
-        <v>Ariana Grande</v>
+        <v>Greta Van Fleet</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/ariana-grande/412778295</v>
+        <v>https://music.apple.com/us/artist/greta-van-fleet/646178956</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/hate-that-i-made-you-love-me/1895420989</v>
+        <v>https://music.apple.com/us/album/play-your-games/6772932835</v>
       </c>
       <c r="L122" t="str">
-        <v>hate that i made you love me - Ariana Grande</v>
+        <v>Play Your Games - Greta Van Fleet</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Come Inside</v>
+        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello)</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/come-inside/1887403093</v>
+        <v>https://music.apple.com/us/song/adjourn-it-feat-serj-tankian-roman-morello/6769340216</v>
       </c>
       <c r="D123" t="str">
         <v>2026-06-03</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>The Boys of Dungeon Lane</v>
+        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello) - Single</v>
       </c>
       <c r="G123" t="str">
-        <v>3:13</v>
+        <v>2:47</v>
       </c>
       <c r="H123" t="str">
-        <v>Paul McCartney</v>
+        <v>Tom Morello</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/paul-mccartney/12224</v>
+        <v>https://music.apple.com/us/artist/tom-morello/466357</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/come-inside/1887402919</v>
+        <v>https://music.apple.com/us/album/adjourn-it-feat-serj-tankian-roman-morello/6769340214</v>
       </c>
       <c r="L123" t="str">
-        <v>Come Inside - Paul McCartney</v>
+        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello) - Tom Morello</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Game Time</v>
+        <v>Essex_Honey.mp3</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/game-time/6771157200</v>
+        <v>https://music.apple.com/us/song/essex-honey-mp3/6771169447</v>
       </c>
       <c r="D124" t="str">
         <v>2026-06-03</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Game Time (FIFA World Cup 2026™) - Single</v>
+        <v>Essex_Honey.mp3 - Single</v>
       </c>
       <c r="G124" t="str">
-        <v>3:26</v>
+        <v>4:49</v>
       </c>
       <c r="H124" t="str">
-        <v>Future</v>
+        <v>Blood Orange</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/future/128050210</v>
+        <v>https://music.apple.com/us/artist/blood-orange/440698865</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/game-time/6771157186</v>
+        <v>https://music.apple.com/us/album/essex-honey-mp3/6771169151</v>
       </c>
       <c r="L124" t="str">
-        <v>Game Time - Future</v>
+        <v>Essex_Honey.mp3 - Blood Orange</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Motion Party (Remix)</v>
+        <v>minute</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/motion-party-remix/6773413965</v>
+        <v>https://music.apple.com/us/song/minute/1875303122</v>
       </c>
       <c r="D125" t="str">
         <v>2026-06-03</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Motion Party (Remix) - Single</v>
+        <v>ghosted - EP</v>
       </c>
       <c r="G125" t="str">
-        <v>2:36</v>
+        <v>2:59</v>
       </c>
       <c r="H125" t="str">
-        <v>Bossman Dlow</v>
+        <v>Saint Harison</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/bossman-dlow/1474308236</v>
+        <v>https://music.apple.com/us/artist/saint-harison/1639595302</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/motion-party-remix/6773413953</v>
+        <v>https://music.apple.com/us/album/minute/1875302904</v>
       </c>
       <c r="L125" t="str">
-        <v>Motion Party (Remix) - Bossman Dlow</v>
+        <v>minute - Saint Harison</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Aquel diciembre</v>
+        <v>THE LIVING</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/aquel-diciembre/6769580010</v>
+        <v>https://music.apple.com/us/song/the-living/1894092345</v>
       </c>
       <c r="D126" t="str">
         <v>2026-06-03</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Do Not Disturb: Late Checkout</v>
+        <v>COSMIC OPERA ACT II</v>
       </c>
       <c r="G126" t="str">
-        <v>3:22</v>
+        <v>2:48</v>
       </c>
       <c r="H126" t="str">
-        <v>Young Miko</v>
+        <v>Labrinth</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/young-miko/1576521417</v>
+        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/aquel-diciembre/6769579992</v>
+        <v>https://music.apple.com/us/album/the-living/1894092339</v>
       </c>
       <c r="L126" t="str">
-        <v>Aquel diciembre - Young Miko</v>
+        <v>THE LIVING - Labrinth</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Handle</v>
+        <v>Thug</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/handle/6771922623</v>
+        <v>https://music.apple.com/us/song/thug/6769289966</v>
       </c>
       <c r="D127" t="str">
         <v>2026-06-03</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Blue Island</v>
+        <v>Thug - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>3:06</v>
+        <v>2:25</v>
       </c>
       <c r="H127" t="str">
-        <v>Ravyn Lenae</v>
+        <v>G Herbo</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/ravyn-lenae/1044417443</v>
+        <v>https://music.apple.com/us/artist/g-herbo/1036753321</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/handle/6771922622</v>
+        <v>https://music.apple.com/us/album/thug/6769289953</v>
       </c>
       <c r="L127" t="str">
-        <v>Handle - Ravyn Lenae</v>
+        <v>Thug - G Herbo</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>snake the drain</v>
+        <v>Clap</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/snake-the-drain/6771506655</v>
+        <v>https://music.apple.com/us/song/clap/6769903711</v>
       </c>
       <c r="D128" t="str">
         <v>2026-06-03</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>this time it’s different / snake the drain - Single</v>
+        <v>Clap - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>3:08</v>
+        <v>2:04</v>
       </c>
       <c r="H128" t="str">
-        <v>Devon Again</v>
+        <v>Polo G</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/devon-again/1574318250</v>
+        <v>https://music.apple.com/us/artist/polo-g/1159371412</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/snake-the-drain/6771506650</v>
+        <v>https://music.apple.com/us/album/clap/6769903710</v>
       </c>
       <c r="L128" t="str">
-        <v>snake the drain - Devon Again</v>
+        <v>Clap - Polo G</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>The Wave</v>
+        <v>GANG BIZNESS</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/the-wave/1886730541</v>
+        <v>https://music.apple.com/us/song/gang-bizness/6772383809</v>
       </c>
       <c r="D129" t="str">
         <v>2026-06-03</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Sunshine</v>
+        <v>THE GENTLEMEN'S CLUB</v>
       </c>
       <c r="G129" t="str">
-        <v>3:22</v>
+        <v>2:47</v>
       </c>
       <c r="H129" t="str">
-        <v>Jungle</v>
+        <v>YG</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/jungle/825833522</v>
+        <v>https://music.apple.com/us/artist/yg/189792075</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/the-wave/1886730527</v>
+        <v>https://music.apple.com/us/album/gang-bizness/6772383681</v>
       </c>
       <c r="L129" t="str">
-        <v>The Wave - Jungle</v>
+        <v>GANG BIZNESS - YG</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Every Single Weekend (feat. Jamie xx)</v>
+        <v>UR HEARTBEAT (WHO DO U THINK ABOUT AT 2AM?)</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/every-single-weekend-feat-jamie-xx/6770445933</v>
+        <v>https://music.apple.com/us/song/ur-heartbeat-who-do-u-think-about-at-2am/6765534140</v>
       </c>
       <c r="D130" t="str">
         <v>2026-06-03</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Every Single Weekend (feat. Jamie xx) - Single</v>
+        <v>A LITTLE VENGEANCE</v>
       </c>
       <c r="G130" t="str">
-        <v>2:10</v>
+        <v>2:50</v>
       </c>
       <c r="H130" t="str">
-        <v>The Avalanches</v>
+        <v>Jessie Reyez</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/the-avalanches/27524431</v>
+        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/every-single-weekend-feat-jamie-xx/6770445752</v>
+        <v>https://music.apple.com/us/album/ur-heartbeat-who-do-u-think-about-at-2am/1895983502</v>
       </c>
       <c r="L130" t="str">
-        <v>Every Single Weekend (feat. Jamie xx) - The Avalanches</v>
+        <v>UR HEARTBEAT (WHO DO U THINK ABOUT AT 2AM?) - Jessie Reyez</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>STOP</v>
+        <v>Joshua Tree</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/stop/6771161771</v>
+        <v>https://music.apple.com/us/song/joshua-tree/6771859148</v>
       </c>
       <c r="D131" t="str">
         <v>2026-06-03</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>are you mad at me? - Single</v>
+        <v>Euphoria: Season 3 (HBO Original Series Soundtrack)</v>
       </c>
       <c r="G131" t="str">
-        <v>2:56</v>
+        <v>2:50</v>
       </c>
       <c r="H131" t="str">
-        <v>Bella Kay</v>
+        <v>Hans Zimmer</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
+        <v>https://music.apple.com/us/artist/hans-zimmer/454295032</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/stop/6771161760</v>
+        <v>https://music.apple.com/us/album/joshua-tree/6771858464</v>
       </c>
       <c r="L131" t="str">
-        <v>STOP - Bella Kay</v>
+        <v>Joshua Tree - Hans Zimmer</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Here (Apple Music Sessions)</v>
+        <v>Mi Gran Amor</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/here-apple-music-sessions/1878235516</v>
+        <v>https://music.apple.com/us/song/mi-gran-amor/6773365775</v>
       </c>
       <c r="D132" t="str">
         <v>2026-06-03</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Apple Music Sessions</v>
+        <v>Mi Gran Amor - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>3:08</v>
+        <v>3:37</v>
       </c>
       <c r="H132" t="str">
-        <v>Mumford &amp; Sons</v>
+        <v>Santana</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/mumford-sons/307699986</v>
+        <v>https://music.apple.com/us/artist/santana/217174</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/here-apple-music-sessions/1878235330</v>
+        <v>https://music.apple.com/us/album/mi-gran-amor/6773365236</v>
       </c>
       <c r="L132" t="str">
-        <v>Here (Apple Music Sessions) - Mumford &amp; Sons</v>
+        <v>Mi Gran Amor - Santana</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Talk On The Hill</v>
+        <v>london</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/talk-on-the-hill/6769524458</v>
+        <v>https://music.apple.com/us/song/london/6770745672</v>
       </c>
       <c r="D133" t="str">
         <v>2026-06-03</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>The Thread</v>
+        <v>stardust - EP</v>
       </c>
       <c r="G133" t="str">
-        <v>3:27</v>
+        <v>3:23</v>
       </c>
       <c r="H133" t="str">
-        <v>WILLOW</v>
+        <v>Freya Skye</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/willow/400531893</v>
+        <v>https://music.apple.com/us/artist/freya-skye/1541643053</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/talk-on-the-hill/6769524450</v>
+        <v>https://music.apple.com/us/album/london/6770745662</v>
       </c>
       <c r="L133" t="str">
-        <v>Talk On The Hill - WILLOW</v>
+        <v>london - Freya Skye</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>No Fear</v>
+        <v>Caution</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/no-fear/1880484493</v>
+        <v>https://music.apple.com/us/song/caution/6768487482</v>
       </c>
       <c r="D134" t="str">
         <v>2026-06-03</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>For Love of Grace &amp; the Hereafter</v>
+        <v>K-POPS! (Music from and inspired by K-POPS! Motion Picture)</v>
       </c>
       <c r="G134" t="str">
-        <v>3:38</v>
+        <v>2:43</v>
       </c>
       <c r="H134" t="str">
-        <v>Iceage</v>
+        <v>NMIXX</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/iceage/406846711</v>
+        <v>https://music.apple.com/us/artist/nmixx/1600411676</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/no-fear/1880484160</v>
+        <v>https://music.apple.com/us/album/caution/6768487478</v>
       </c>
       <c r="L134" t="str">
-        <v>No Fear - Iceage</v>
+        <v>Caution - NMIXX</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Hostage</v>
+        <v>LEMONADE (feat. Becky G)</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/hostage/6774372288</v>
+        <v>https://music.apple.com/us/song/lemonade-feat-becky-g/1893742425</v>
       </c>
       <c r="D135" t="str">
         <v>2026-06-03</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Big Mama</v>
+        <v>LEMONADE - The 2nd Album</v>
       </c>
       <c r="G135" t="str">
-        <v>3:11</v>
+        <v>3:07</v>
       </c>
       <c r="H135" t="str">
-        <v>Latto</v>
+        <v>aespa</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/latto/419799506</v>
+        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/hostage/6774372200</v>
+        <v>https://music.apple.com/us/album/lemonade-feat-becky-g/1893742002</v>
       </c>
       <c r="L135" t="str">
-        <v>Hostage - Latto</v>
+        <v>LEMONADE (feat. Becky G) - aespa</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Sad Girls</v>
+        <v>Take Me Back (Leave Me There)</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/sad-girls/6768814374</v>
+        <v>https://music.apple.com/us/song/take-me-back-leave-me-there/1892466278</v>
       </c>
       <c r="D136" t="str">
         <v>2026-06-03</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Sad Girls - Single</v>
+        <v>Banks Of The Trinity</v>
       </c>
       <c r="G136" t="str">
-        <v>2:48</v>
+        <v>2:58</v>
       </c>
       <c r="H136" t="str">
-        <v>Bebe Rexha</v>
+        <v>Cody Johnson</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/bebe-rexha/466059563</v>
+        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/sad-girls/6768814373</v>
+        <v>https://music.apple.com/us/album/take-me-back-leave-me-there/1892465981</v>
       </c>
       <c r="L136" t="str">
-        <v>Sad Girls - Bebe Rexha</v>
+        <v>Take Me Back (Leave Me There) - Cody Johnson</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Salvame Hoy (feat. Gabito Ballesteros)</v>
+        <v>Cheap Thrills</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/salvame-hoy-feat-gabito-ballesteros/6765697019</v>
+        <v>https://music.apple.com/us/song/cheap-thrills/6771156732</v>
       </c>
       <c r="D137" t="str">
         <v>2026-06-03</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Salvame Hoy (feat. Gabito Ballesteros) - Single</v>
+        <v>Cheap Thrills - Single</v>
       </c>
       <c r="G137" t="str">
-        <v>3:35</v>
+        <v>2:42</v>
       </c>
       <c r="H137" t="str">
-        <v>Jennifer Lopez</v>
+        <v>Gavin Adcock</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/jennifer-lopez/463009</v>
+        <v>https://music.apple.com/us/artist/gavin-adcock/1580645019</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/salvame-hoy-feat-gabito-ballesteros/1896041010</v>
+        <v>https://music.apple.com/us/album/cheap-thrills/6771156723</v>
       </c>
       <c r="L137" t="str">
-        <v>Salvame Hoy (feat. Gabito Ballesteros) - Jennifer Lopez</v>
+        <v>Cheap Thrills - Gavin Adcock</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Rubio</v>
+        <v>ME VALE V</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/rubio/6770655339</v>
+        <v>https://music.apple.com/us/song/me-vale-v/6769567844</v>
       </c>
       <c r="D138" t="str">
         <v>2026-06-03</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>La Voz Favorita</v>
+        <v>ACOMODO</v>
       </c>
       <c r="G138" t="str">
-        <v>4:42</v>
+        <v>3:06</v>
       </c>
       <c r="H138" t="str">
-        <v>Jay Wheeler</v>
+        <v>Tito Double P</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/jay-wheeler/164376380</v>
+        <v>https://music.apple.com/us/artist/tito-double-p/1690905306</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/rubio/6770654729</v>
+        <v>https://music.apple.com/us/album/me-vale-v/6769567568</v>
       </c>
       <c r="L138" t="str">
-        <v>Rubio - Jay Wheeler</v>
+        <v>ME VALE V - Tito Double P</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Pary</v>
+        <v>Bug In The Cake</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/pary/6767367748</v>
+        <v>https://music.apple.com/us/song/bug-in-the-cake/1880470542</v>
       </c>
       <c r="D139" t="str">
         <v>2026-06-03</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Con dolor - EP</v>
+        <v>Be Sweet To Me</v>
       </c>
       <c r="G139" t="str">
-        <v>2:52</v>
+        <v>2:48</v>
       </c>
       <c r="H139" t="str">
-        <v>Grupo Frontera</v>
+        <v>Violet Grohl</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
+        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/pary/6767367501</v>
+        <v>https://music.apple.com/us/album/bug-in-the-cake/1880470537</v>
       </c>
       <c r="L139" t="str">
-        <v>Pary - Grupo Frontera</v>
+        <v>Bug In The Cake - Violet Grohl</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Think As You Drunk</v>
+        <v>Coil</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/think-as-you-drunk/6770725979</v>
+        <v>https://music.apple.com/us/song/coil/6766858354</v>
       </c>
       <c r="D140" t="str">
         <v>2026-06-03</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>That's Just Me</v>
+        <v>Rumspringa</v>
       </c>
       <c r="G140" t="str">
-        <v>3:48</v>
+        <v>3:54</v>
       </c>
       <c r="H140" t="str">
-        <v>Riley Green</v>
+        <v>ear</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/riley-green/662432971</v>
+        <v>https://music.apple.com/us/artist/ear/1829661500</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/think-as-you-drunk/6770725355</v>
+        <v>https://music.apple.com/us/album/coil/6766858352</v>
       </c>
       <c r="L140" t="str">
-        <v>Think As You Drunk - Riley Green</v>
+        <v>Coil - ear</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Play Your Games</v>
+        <v>Smugglers &amp; Scholars (feat. Killer Mike)</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/play-your-games/6772932837</v>
+        <v>https://music.apple.com/us/song/smugglers-scholars-feat-killer-mike/6769424017</v>
       </c>
       <c r="D141" t="str">
         <v>2026-06-03</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Play Your Games - Single</v>
+        <v>Smugglers &amp; Scholars (feat. Killer Mike) - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>3:15</v>
+        <v>3:30</v>
       </c>
       <c r="H141" t="str">
-        <v>Greta Van Fleet</v>
+        <v>Kneecap</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/greta-van-fleet/646178956</v>
+        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/play-your-games/6772932835</v>
+        <v>https://music.apple.com/us/album/smugglers-scholars-feat-killer-mike/6769423676</v>
       </c>
       <c r="L141" t="str">
-        <v>Play Your Games - Greta Van Fleet</v>
+        <v>Smugglers &amp; Scholars (feat. Killer Mike) - Kneecap</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello)</v>
+        <v>Out of my Head</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/adjourn-it-feat-serj-tankian-roman-morello/6769340216</v>
+        <v>https://music.apple.com/us/song/out-of-my-head/6767725166</v>
       </c>
       <c r="D142" t="str">
         <v>2026-06-03</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello) - Single</v>
+        <v>I Forgot / Out of my Head - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>2:47</v>
+        <v>3:04</v>
       </c>
       <c r="H142" t="str">
-        <v>Tom Morello</v>
+        <v>Cara Delevingne</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/tom-morello/466357</v>
+        <v>https://music.apple.com/us/artist/cara-delevingne/1204798982</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/adjourn-it-feat-serj-tankian-roman-morello/6769340214</v>
+        <v>https://music.apple.com/us/album/out-of-my-head/6767725156</v>
       </c>
       <c r="L142" t="str">
-        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello) - Tom Morello</v>
+        <v>Out of my Head - Cara Delevingne</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Essex_Honey.mp3</v>
+        <v>Passenger Princess</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/essex-honey-mp3/6771169447</v>
+        <v>https://music.apple.com/us/song/passenger-princess/6771012228</v>
       </c>
       <c r="D143" t="str">
         <v>2026-06-03</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Essex_Honey.mp3 - Single</v>
+        <v>Passenger Princess - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>4:49</v>
+        <v>3:18</v>
       </c>
       <c r="H143" t="str">
-        <v>Blood Orange</v>
+        <v>Perrie</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/blood-orange/440698865</v>
+        <v>https://music.apple.com/us/artist/perrie/1729865272</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/essex-honey-mp3/6771169151</v>
+        <v>https://music.apple.com/us/album/passenger-princess/6771012223</v>
       </c>
       <c r="L143" t="str">
-        <v>Essex_Honey.mp3 - Blood Orange</v>
+        <v>Passenger Princess - Perrie</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>minute</v>
+        <v>Man of the House</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/minute/1875303122</v>
+        <v>https://music.apple.com/us/song/man-of-the-house/1893733057</v>
       </c>
       <c r="D144" t="str">
         <v>2026-06-03</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>ghosted - EP</v>
+        <v>SE9</v>
       </c>
       <c r="G144" t="str">
-        <v>2:59</v>
+        <v>2:35</v>
       </c>
       <c r="H144" t="str">
-        <v>Saint Harison</v>
+        <v>Skye Newman</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/saint-harison/1639595302</v>
+        <v>https://music.apple.com/us/artist/skye-newman/1799174381</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/minute/1875302904</v>
+        <v>https://music.apple.com/us/album/man-of-the-house/1893733056</v>
       </c>
       <c r="L144" t="str">
-        <v>minute - Saint Harison</v>
+        <v>Man of the House - Skye Newman</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>THE LIVING</v>
+        <v>Beautiful Freeks</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/the-living/1894092345</v>
+        <v>https://music.apple.com/us/song/beautiful-freeks/6764602396</v>
       </c>
       <c r="D145" t="str">
         <v>2026-06-03</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>COSMIC OPERA ACT II</v>
+        <v>Beautiful Freeks - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>2:48</v>
+        <v>2:37</v>
       </c>
       <c r="H145" t="str">
-        <v>Labrinth</v>
+        <v>MEEK</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
+        <v>https://music.apple.com/us/artist/meek/1784432868</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/the-living/1894092339</v>
+        <v>https://music.apple.com/us/album/beautiful-freeks/6764602393</v>
       </c>
       <c r="L145" t="str">
-        <v>THE LIVING - Labrinth</v>
+        <v>Beautiful Freeks - MEEK</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Thug</v>
+        <v>Slave to the Rithm (feat. Bring Me The Horizon) [I Hate Models Never Alone Remix]</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/thug/6769289966</v>
+        <v>https://music.apple.com/us/song/slave-to-the-rithm-feat-bring-me-the-horizon-i/6771972616</v>
       </c>
       <c r="D146" t="str">
         <v>2026-06-03</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Thug - Single</v>
+        <v>Slave to the Rithm (I Hate Models Never Alone Remix) [feat. Bring Me The Horizon] - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>2:25</v>
+        <v>4:34</v>
       </c>
       <c r="H146" t="str">
-        <v>G Herbo</v>
+        <v>ILLENIUM</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/g-herbo/1036753321</v>
+        <v>https://music.apple.com/us/artist/illenium/645420096</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/thug/6769289953</v>
+        <v>https://music.apple.com/us/album/slave-to-the-rithm-feat-bring-me-the-horizon-i/6771972613</v>
       </c>
       <c r="L146" t="str">
-        <v>Thug - G Herbo</v>
+        <v>Slave to the Rithm (feat. Bring Me The Horizon) [I Hate Models Never Alone Remix] - ILLENIUM</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Clap</v>
+        <v>Beg For Me (JADE Remix)</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/clap/6769903711</v>
+        <v>https://music.apple.com/us/song/beg-for-me-jade-remix/6771474203</v>
       </c>
       <c r="D147" t="str">
         <v>2026-06-03</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Clap - Single</v>
+        <v>Beg For Me (Remix) - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>2:04</v>
+        <v>2:50</v>
       </c>
       <c r="H147" t="str">
-        <v>Polo G</v>
+        <v>Lily Allen</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/polo-g/1159371412</v>
+        <v>https://music.apple.com/us/artist/lily-allen/157063999</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/clap/6769903710</v>
+        <v>https://music.apple.com/us/album/beg-for-me-jade-remix/6771474201</v>
       </c>
       <c r="L147" t="str">
-        <v>Clap - Polo G</v>
+        <v>Beg For Me (JADE Remix) - Lily Allen</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>GANG BIZNESS</v>
+        <v>ABOVE IT</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/gang-bizness/6772383809</v>
+        <v>https://music.apple.com/us/song/above-it/6766248703</v>
       </c>
       <c r="D148" t="str">
         <v>2026-06-03</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>THE GENTLEMEN'S CLUB</v>
+        <v>GET THE TABLES - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>2:47</v>
+        <v>1:45</v>
       </c>
       <c r="H148" t="str">
-        <v>YG</v>
+        <v>Andy Mineo</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/yg/189792075</v>
+        <v>https://music.apple.com/us/artist/andy-mineo/257538441</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/gang-bizness/6772383681</v>
+        <v>https://music.apple.com/us/album/above-it/6766248699</v>
       </c>
       <c r="L148" t="str">
-        <v>GANG BIZNESS - YG</v>
+        <v>ABOVE IT - Andy Mineo</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>UR HEARTBEAT (WHO DO U THINK ABOUT AT 2AM?)</v>
+        <v>THE JESUS GENERATION</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/ur-heartbeat-who-do-u-think-about-at-2am/6765534140</v>
+        <v>https://music.apple.com/us/song/the-jesus-generation/6773948895</v>
       </c>
       <c r="D149" t="str">
         <v>2026-06-03</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>A LITTLE VENGEANCE</v>
+        <v>THE JESUS GENERATION - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>2:50</v>
+        <v>4:15</v>
       </c>
       <c r="H149" t="str">
-        <v>Jessie Reyez</v>
+        <v>Forrest Frank</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
+        <v>https://music.apple.com/us/artist/forrest-frank/1436657314</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/ur-heartbeat-who-do-u-think-about-at-2am/1895983502</v>
+        <v>https://music.apple.com/us/album/the-jesus-generation/6773948742</v>
       </c>
       <c r="L149" t="str">
-        <v>UR HEARTBEAT (WHO DO U THINK ABOUT AT 2AM?) - Jessie Reyez</v>
+        <v>THE JESUS GENERATION - Forrest Frank</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Joshua Tree</v>
+        <v>Is It Over Now?</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/joshua-tree/6771859148</v>
+        <v>https://music.apple.com/us/song/is-it-over-now/6767564750</v>
       </c>
       <c r="D150" t="str">
         <v>2026-06-03</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Euphoria: Season 3 (HBO Original Series Soundtrack)</v>
+        <v>Is It Over Now? - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>2:50</v>
+        <v>3:39</v>
       </c>
       <c r="H150" t="str">
-        <v>Hans Zimmer</v>
+        <v>Elderbrook</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/hans-zimmer/454295032</v>
+        <v>https://music.apple.com/us/artist/elderbrook/736829657</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/joshua-tree/6771858464</v>
+        <v>https://music.apple.com/us/album/is-it-over-now/6767564746</v>
       </c>
       <c r="L150" t="str">
-        <v>Joshua Tree - Hans Zimmer</v>
+        <v>Is It Over Now? - Elderbrook</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Mi Gran Amor</v>
+        <v>12 Steps</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/mi-gran-amor/6773365775</v>
+        <v>https://music.apple.com/us/song/12-steps/6769559623</v>
       </c>
       <c r="D151" t="str">
         <v>2026-06-03</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Mi Gran Amor - Single</v>
+        <v>12 Steps - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>3:37</v>
+        <v>3:11</v>
       </c>
       <c r="H151" t="str">
-        <v>Santana</v>
+        <v>Dexter and The Moonrocks</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/santana/217174</v>
+        <v>https://music.apple.com/us/artist/dexter-and-the-moonrocks/1581657500</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/mi-gran-amor/6773365236</v>
+        <v>https://music.apple.com/us/album/12-steps/6769559618</v>
       </c>
       <c r="L151" t="str">
-        <v>Mi Gran Amor - Santana</v>
+        <v>12 Steps - Dexter and The Moonrocks</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>london</v>
+        <v>Over And Over</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/london/6770745672</v>
+        <v>https://music.apple.com/us/song/over-and-over/6771585908</v>
       </c>
       <c r="D152" t="str">
         <v>2026-06-03</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>stardust - EP</v>
+        <v>It's A Dying Art</v>
       </c>
       <c r="G152" t="str">
-        <v>3:23</v>
+        <v>4:38</v>
       </c>
       <c r="H152" t="str">
-        <v>Freya Skye</v>
+        <v>Little Big Town</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/freya-skye/1541643053</v>
+        <v>https://music.apple.com/us/artist/little-big-town/513770</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/london/6770745662</v>
+        <v>https://music.apple.com/us/album/over-and-over/6771585889</v>
       </c>
       <c r="L152" t="str">
-        <v>london - Freya Skye</v>
+        <v>Over And Over - Little Big Town</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Caution</v>
+        <v>AMAPOLA</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str